--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="79">
+  <fonts count="81">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -468,6 +468,16 @@
       <color rgb="00334155"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -702,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="271">
+  <borders count="293">
     <border>
       <left/>
       <right/>
@@ -3621,11 +3631,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="416">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4363,6 +4589,189 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="280" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4436,41 +4845,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="/xl/media/image1.png"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4714,1734 +5088,2027 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="267" t="n"/>
-      <c r="B1" s="320" t="n"/>
-      <c r="C1" s="320" t="n"/>
-      <c r="D1" s="320" t="n"/>
-      <c r="E1" s="320" t="n"/>
-      <c r="F1" s="320" t="n"/>
-      <c r="G1" s="320" t="n"/>
-      <c r="H1" s="320" t="n"/>
-      <c r="I1" s="269" t="inlineStr">
+      <c r="A1" s="339" t="n"/>
+      <c r="B1" s="410" t="n"/>
+      <c r="C1" s="410" t="n"/>
+      <c r="D1" s="410" t="n"/>
+      <c r="E1" s="410" t="n"/>
+      <c r="F1" s="410" t="n"/>
+      <c r="G1" s="410" t="n"/>
+      <c r="H1" s="410" t="n"/>
+      <c r="I1" s="341" t="inlineStr">
         <is>
           <t>Outsource Dispatch Checklist</t>
         </is>
       </c>
-      <c r="J1" s="320" t="n"/>
-      <c r="K1" s="320" t="n"/>
-      <c r="L1" s="320" t="n"/>
-      <c r="M1" s="320" t="n"/>
-      <c r="N1" s="320" t="n"/>
-      <c r="O1" s="320" t="n"/>
-      <c r="P1" s="320" t="n"/>
-      <c r="Q1" s="320" t="n"/>
-      <c r="R1" s="320" t="n"/>
-      <c r="S1" s="320" t="n"/>
-      <c r="T1" s="320" t="n"/>
-      <c r="U1" s="320" t="n"/>
-      <c r="V1" s="320" t="n"/>
-      <c r="W1" s="320" t="n"/>
-      <c r="X1" s="320" t="n"/>
-      <c r="Y1" s="320" t="n"/>
-      <c r="Z1" s="320" t="n"/>
-      <c r="AA1" s="320" t="n"/>
-      <c r="AB1" s="320" t="n"/>
-      <c r="AC1" s="320" t="n"/>
-      <c r="AD1" s="320" t="n"/>
-      <c r="AE1" s="270" t="n"/>
-      <c r="AF1" s="317" t="n"/>
-      <c r="AG1" s="317" t="n"/>
-      <c r="AH1" s="318" t="n"/>
-      <c r="AI1" s="273" t="inlineStr">
+      <c r="J1" s="410" t="n"/>
+      <c r="K1" s="410" t="n"/>
+      <c r="L1" s="410" t="n"/>
+      <c r="M1" s="410" t="n"/>
+      <c r="N1" s="410" t="n"/>
+      <c r="O1" s="410" t="n"/>
+      <c r="P1" s="410" t="n"/>
+      <c r="Q1" s="410" t="n"/>
+      <c r="R1" s="410" t="n"/>
+      <c r="S1" s="410" t="n"/>
+      <c r="T1" s="410" t="n"/>
+      <c r="U1" s="410" t="n"/>
+      <c r="V1" s="410" t="n"/>
+      <c r="W1" s="410" t="n"/>
+      <c r="X1" s="410" t="n"/>
+      <c r="Y1" s="410" t="n"/>
+      <c r="Z1" s="410" t="n"/>
+      <c r="AA1" s="410" t="n"/>
+      <c r="AB1" s="410" t="n"/>
+      <c r="AC1" s="410" t="n"/>
+      <c r="AD1" s="410" t="n"/>
+      <c r="AE1" s="342" t="n"/>
+      <c r="AF1" s="411" t="n"/>
+      <c r="AG1" s="411" t="n"/>
+      <c r="AH1" s="412" t="n"/>
+      <c r="AI1" s="345" t="inlineStr">
         <is>
           <t>FRM-404</t>
         </is>
       </c>
-      <c r="AJ1" s="317" t="n"/>
-      <c r="AK1" s="317" t="n"/>
-      <c r="AL1" s="317" t="n"/>
-      <c r="AM1" s="317" t="n"/>
-      <c r="AN1" s="319" t="n"/>
+      <c r="AJ1" s="411" t="n"/>
+      <c r="AK1" s="411" t="n"/>
+      <c r="AL1" s="411" t="n"/>
+      <c r="AM1" s="411" t="n"/>
+      <c r="AN1" s="412" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="328" t="n"/>
-      <c r="I2" s="328" t="n"/>
-      <c r="AE2" s="270" t="n"/>
-      <c r="AF2" s="317" t="n"/>
-      <c r="AG2" s="317" t="n"/>
-      <c r="AH2" s="318" t="n"/>
-      <c r="AI2" s="273" t="inlineStr">
+      <c r="A2" s="413" t="n"/>
+      <c r="I2" s="413" t="n"/>
+      <c r="AE2" s="342" t="n"/>
+      <c r="AF2" s="411" t="n"/>
+      <c r="AG2" s="411" t="n"/>
+      <c r="AH2" s="412" t="n"/>
+      <c r="AI2" s="345" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="317" t="n"/>
-      <c r="AK2" s="317" t="n"/>
-      <c r="AL2" s="317" t="n"/>
-      <c r="AM2" s="317" t="n"/>
-      <c r="AN2" s="319" t="n"/>
+      <c r="AJ2" s="411" t="n"/>
+      <c r="AK2" s="411" t="n"/>
+      <c r="AL2" s="411" t="n"/>
+      <c r="AM2" s="411" t="n"/>
+      <c r="AN2" s="412" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="328" t="n"/>
-      <c r="I3" s="279" t="n"/>
-      <c r="J3" s="322" t="n"/>
-      <c r="K3" s="322" t="n"/>
-      <c r="L3" s="322" t="n"/>
-      <c r="M3" s="322" t="n"/>
-      <c r="N3" s="322" t="n"/>
-      <c r="O3" s="322" t="n"/>
-      <c r="P3" s="322" t="n"/>
-      <c r="Q3" s="322" t="n"/>
-      <c r="R3" s="322" t="n"/>
-      <c r="S3" s="322" t="n"/>
-      <c r="T3" s="322" t="n"/>
-      <c r="U3" s="322" t="n"/>
-      <c r="V3" s="322" t="n"/>
-      <c r="W3" s="322" t="n"/>
-      <c r="X3" s="322" t="n"/>
-      <c r="Y3" s="322" t="n"/>
-      <c r="Z3" s="322" t="n"/>
-      <c r="AA3" s="322" t="n"/>
-      <c r="AB3" s="322" t="n"/>
-      <c r="AC3" s="322" t="n"/>
-      <c r="AD3" s="322" t="n"/>
-      <c r="AE3" s="270" t="n"/>
-      <c r="AF3" s="317" t="n"/>
-      <c r="AG3" s="317" t="n"/>
-      <c r="AH3" s="318" t="n"/>
-      <c r="AI3" s="273" t="inlineStr">
+      <c r="A3" s="413" t="n"/>
+      <c r="I3" s="414" t="n"/>
+      <c r="J3" s="415" t="n"/>
+      <c r="K3" s="415" t="n"/>
+      <c r="L3" s="415" t="n"/>
+      <c r="M3" s="415" t="n"/>
+      <c r="N3" s="415" t="n"/>
+      <c r="O3" s="415" t="n"/>
+      <c r="P3" s="415" t="n"/>
+      <c r="Q3" s="415" t="n"/>
+      <c r="R3" s="415" t="n"/>
+      <c r="S3" s="415" t="n"/>
+      <c r="T3" s="415" t="n"/>
+      <c r="U3" s="415" t="n"/>
+      <c r="V3" s="415" t="n"/>
+      <c r="W3" s="415" t="n"/>
+      <c r="X3" s="415" t="n"/>
+      <c r="Y3" s="415" t="n"/>
+      <c r="Z3" s="415" t="n"/>
+      <c r="AA3" s="415" t="n"/>
+      <c r="AB3" s="415" t="n"/>
+      <c r="AC3" s="415" t="n"/>
+      <c r="AD3" s="415" t="n"/>
+      <c r="AE3" s="342" t="n"/>
+      <c r="AF3" s="411" t="n"/>
+      <c r="AG3" s="411" t="n"/>
+      <c r="AH3" s="412" t="n"/>
+      <c r="AI3" s="345" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="317" t="n"/>
-      <c r="AK3" s="317" t="n"/>
-      <c r="AL3" s="317" t="n"/>
-      <c r="AM3" s="317" t="n"/>
-      <c r="AN3" s="319" t="n"/>
+      <c r="AJ3" s="411" t="n"/>
+      <c r="AK3" s="411" t="n"/>
+      <c r="AL3" s="411" t="n"/>
+      <c r="AM3" s="411" t="n"/>
+      <c r="AN3" s="412" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="328" t="n"/>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="A4" s="413" t="n"/>
+      <c r="I4" s="350" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="270" t="n"/>
-      <c r="AF4" s="317" t="n"/>
-      <c r="AG4" s="317" t="n"/>
-      <c r="AH4" s="318" t="n"/>
-      <c r="AI4" s="273" t="inlineStr">
+      <c r="AE4" s="342" t="n"/>
+      <c r="AF4" s="411" t="n"/>
+      <c r="AG4" s="411" t="n"/>
+      <c r="AH4" s="412" t="n"/>
+      <c r="AI4" s="345" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="317" t="n"/>
-      <c r="AK4" s="317" t="n"/>
-      <c r="AL4" s="317" t="n"/>
-      <c r="AM4" s="317" t="n"/>
-      <c r="AN4" s="319" t="n"/>
+      <c r="AJ4" s="411" t="n"/>
+      <c r="AK4" s="411" t="n"/>
+      <c r="AL4" s="411" t="n"/>
+      <c r="AM4" s="411" t="n"/>
+      <c r="AN4" s="412" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="331" t="n"/>
-      <c r="B5" s="332" t="n"/>
-      <c r="C5" s="332" t="n"/>
-      <c r="D5" s="332" t="n"/>
-      <c r="E5" s="332" t="n"/>
-      <c r="F5" s="332" t="n"/>
-      <c r="G5" s="332" t="n"/>
-      <c r="H5" s="332" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="A5" s="414" t="n"/>
+      <c r="B5" s="415" t="n"/>
+      <c r="C5" s="415" t="n"/>
+      <c r="D5" s="415" t="n"/>
+      <c r="E5" s="415" t="n"/>
+      <c r="F5" s="415" t="n"/>
+      <c r="G5" s="415" t="n"/>
+      <c r="H5" s="415" t="n"/>
+      <c r="I5" s="351" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="332" t="n"/>
-      <c r="K5" s="332" t="n"/>
-      <c r="L5" s="332" t="n"/>
-      <c r="M5" s="332" t="n"/>
-      <c r="N5" s="332" t="n"/>
-      <c r="O5" s="332" t="n"/>
-      <c r="P5" s="332" t="n"/>
-      <c r="Q5" s="332" t="n"/>
-      <c r="R5" s="332" t="n"/>
-      <c r="S5" s="332" t="n"/>
-      <c r="T5" s="332" t="n"/>
-      <c r="U5" s="332" t="n"/>
-      <c r="V5" s="332" t="n"/>
-      <c r="W5" s="332" t="n"/>
-      <c r="X5" s="332" t="n"/>
-      <c r="Y5" s="332" t="n"/>
-      <c r="Z5" s="332" t="n"/>
-      <c r="AA5" s="332" t="n"/>
-      <c r="AB5" s="332" t="n"/>
-      <c r="AC5" s="332" t="n"/>
-      <c r="AD5" s="332" t="n"/>
-      <c r="AE5" s="270" t="n"/>
-      <c r="AF5" s="317" t="n"/>
-      <c r="AG5" s="317" t="n"/>
-      <c r="AH5" s="318" t="n"/>
-      <c r="AI5" s="273" t="inlineStr">
+      <c r="J5" s="415" t="n"/>
+      <c r="K5" s="415" t="n"/>
+      <c r="L5" s="415" t="n"/>
+      <c r="M5" s="415" t="n"/>
+      <c r="N5" s="415" t="n"/>
+      <c r="O5" s="415" t="n"/>
+      <c r="P5" s="415" t="n"/>
+      <c r="Q5" s="415" t="n"/>
+      <c r="R5" s="415" t="n"/>
+      <c r="S5" s="415" t="n"/>
+      <c r="T5" s="415" t="n"/>
+      <c r="U5" s="415" t="n"/>
+      <c r="V5" s="415" t="n"/>
+      <c r="W5" s="415" t="n"/>
+      <c r="X5" s="415" t="n"/>
+      <c r="Y5" s="415" t="n"/>
+      <c r="Z5" s="415" t="n"/>
+      <c r="AA5" s="415" t="n"/>
+      <c r="AB5" s="415" t="n"/>
+      <c r="AC5" s="415" t="n"/>
+      <c r="AD5" s="415" t="n"/>
+      <c r="AE5" s="342" t="n"/>
+      <c r="AF5" s="411" t="n"/>
+      <c r="AG5" s="411" t="n"/>
+      <c r="AH5" s="412" t="n"/>
+      <c r="AI5" s="345" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="317" t="n"/>
-      <c r="AK5" s="317" t="n"/>
-      <c r="AL5" s="317" t="n"/>
-      <c r="AM5" s="317" t="n"/>
-      <c r="AN5" s="319" t="n"/>
+      <c r="AJ5" s="411" t="n"/>
+      <c r="AK5" s="411" t="n"/>
+      <c r="AL5" s="411" t="n"/>
+      <c r="AM5" s="411" t="n"/>
+      <c r="AN5" s="412" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1" s="329">
-      <c r="A6" s="25" t="n"/>
+      <c r="A6" s="352" t="n"/>
+      <c r="B6" s="409" t="n"/>
+      <c r="C6" s="409" t="n"/>
+      <c r="D6" s="409" t="n"/>
+      <c r="E6" s="409" t="n"/>
+      <c r="F6" s="409" t="n"/>
+      <c r="G6" s="409" t="n"/>
+      <c r="H6" s="409" t="n"/>
+      <c r="I6" s="409" t="n"/>
+      <c r="J6" s="409" t="n"/>
+      <c r="K6" s="409" t="n"/>
+      <c r="L6" s="409" t="n"/>
+      <c r="M6" s="409" t="n"/>
+      <c r="N6" s="409" t="n"/>
+      <c r="O6" s="409" t="n"/>
+      <c r="P6" s="409" t="n"/>
+      <c r="Q6" s="409" t="n"/>
+      <c r="R6" s="409" t="n"/>
+      <c r="S6" s="409" t="n"/>
+      <c r="T6" s="409" t="n"/>
+      <c r="U6" s="409" t="n"/>
+      <c r="V6" s="409" t="n"/>
+      <c r="W6" s="409" t="n"/>
+      <c r="X6" s="409" t="n"/>
+      <c r="Y6" s="409" t="n"/>
+      <c r="Z6" s="409" t="n"/>
+      <c r="AA6" s="409" t="n"/>
+      <c r="AB6" s="409" t="n"/>
+      <c r="AC6" s="409" t="n"/>
+      <c r="AD6" s="409" t="n"/>
+      <c r="AE6" s="409" t="n"/>
+      <c r="AF6" s="409" t="n"/>
+      <c r="AG6" s="409" t="n"/>
+      <c r="AH6" s="409" t="n"/>
+      <c r="AI6" s="409" t="n"/>
+      <c r="AJ6" s="409" t="n"/>
+      <c r="AK6" s="409" t="n"/>
+      <c r="AL6" s="409" t="n"/>
+      <c r="AM6" s="409" t="n"/>
+      <c r="AN6" s="409" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="329">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="286" t="n"/>
+      <c r="B7" s="411" t="n"/>
+      <c r="C7" s="411" t="n"/>
+      <c r="D7" s="411" t="n"/>
+      <c r="E7" s="411" t="n"/>
+      <c r="F7" s="411" t="n"/>
+      <c r="G7" s="411" t="n"/>
+      <c r="H7" s="411" t="n"/>
+      <c r="I7" s="411" t="n"/>
+      <c r="J7" s="411" t="n"/>
+      <c r="K7" s="411" t="n"/>
+      <c r="L7" s="411" t="n"/>
+      <c r="M7" s="411" t="n"/>
+      <c r="N7" s="411" t="n"/>
+      <c r="O7" s="411" t="n"/>
+      <c r="P7" s="411" t="n"/>
+      <c r="Q7" s="411" t="n"/>
+      <c r="R7" s="411" t="n"/>
+      <c r="S7" s="411" t="n"/>
+      <c r="T7" s="411" t="n"/>
+      <c r="U7" s="411" t="n"/>
+      <c r="V7" s="411" t="n"/>
+      <c r="W7" s="411" t="n"/>
+      <c r="X7" s="411" t="n"/>
+      <c r="Y7" s="411" t="n"/>
+      <c r="Z7" s="411" t="n"/>
+      <c r="AA7" s="411" t="n"/>
+      <c r="AB7" s="411" t="n"/>
+      <c r="AC7" s="411" t="n"/>
+      <c r="AD7" s="411" t="n"/>
+      <c r="AE7" s="411" t="n"/>
+      <c r="AF7" s="411" t="n"/>
+      <c r="AG7" s="411" t="n"/>
+      <c r="AH7" s="411" t="n"/>
+      <c r="AI7" s="411" t="n"/>
+      <c r="AJ7" s="411" t="n"/>
+      <c r="AK7" s="411" t="n"/>
+      <c r="AL7" s="411" t="n"/>
+      <c r="AM7" s="411" t="n"/>
+      <c r="AN7" s="412" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="354" t="inlineStr">
         <is>
           <t>Outsource Dispatch ID</t>
         </is>
       </c>
-      <c r="B8" s="317" t="n"/>
-      <c r="C8" s="317" t="n"/>
-      <c r="D8" s="317" t="n"/>
-      <c r="E8" s="317" t="n"/>
-      <c r="F8" s="317" t="n"/>
-      <c r="G8" s="318" t="n"/>
-      <c r="H8" s="288" t="n"/>
-      <c r="I8" s="317" t="n"/>
-      <c r="J8" s="317" t="n"/>
-      <c r="K8" s="317" t="n"/>
-      <c r="L8" s="317" t="n"/>
-      <c r="M8" s="317" t="n"/>
-      <c r="N8" s="317" t="n"/>
-      <c r="O8" s="317" t="n"/>
-      <c r="P8" s="317" t="n"/>
-      <c r="Q8" s="317" t="n"/>
-      <c r="R8" s="317" t="n"/>
-      <c r="S8" s="317" t="n"/>
-      <c r="T8" s="318" t="n"/>
-      <c r="U8" s="289" t="inlineStr">
+      <c r="B8" s="399" t="n"/>
+      <c r="C8" s="399" t="n"/>
+      <c r="D8" s="399" t="n"/>
+      <c r="E8" s="399" t="n"/>
+      <c r="F8" s="399" t="n"/>
+      <c r="G8" s="400" t="n"/>
+      <c r="H8" s="357" t="n"/>
+      <c r="I8" s="399" t="n"/>
+      <c r="J8" s="399" t="n"/>
+      <c r="K8" s="399" t="n"/>
+      <c r="L8" s="399" t="n"/>
+      <c r="M8" s="399" t="n"/>
+      <c r="N8" s="399" t="n"/>
+      <c r="O8" s="399" t="n"/>
+      <c r="P8" s="399" t="n"/>
+      <c r="Q8" s="399" t="n"/>
+      <c r="R8" s="399" t="n"/>
+      <c r="S8" s="399" t="n"/>
+      <c r="T8" s="400" t="n"/>
+      <c r="U8" s="358" t="inlineStr">
         <is>
           <t>Dispatch Gate Status</t>
         </is>
       </c>
-      <c r="V8" s="317" t="n"/>
-      <c r="W8" s="317" t="n"/>
-      <c r="X8" s="317" t="n"/>
-      <c r="Y8" s="317" t="n"/>
-      <c r="Z8" s="317" t="n"/>
-      <c r="AA8" s="318" t="n"/>
-      <c r="AB8" s="290" t="n"/>
-      <c r="AC8" s="317" t="n"/>
-      <c r="AD8" s="317" t="n"/>
-      <c r="AE8" s="317" t="n"/>
-      <c r="AF8" s="317" t="n"/>
-      <c r="AG8" s="317" t="n"/>
-      <c r="AH8" s="317" t="n"/>
-      <c r="AI8" s="317" t="n"/>
-      <c r="AJ8" s="317" t="n"/>
-      <c r="AK8" s="317" t="n"/>
-      <c r="AL8" s="317" t="n"/>
-      <c r="AM8" s="317" t="n"/>
-      <c r="AN8" s="319" t="n"/>
+      <c r="V8" s="399" t="n"/>
+      <c r="W8" s="399" t="n"/>
+      <c r="X8" s="399" t="n"/>
+      <c r="Y8" s="399" t="n"/>
+      <c r="Z8" s="399" t="n"/>
+      <c r="AA8" s="400" t="n"/>
+      <c r="AB8" s="357" t="n"/>
+      <c r="AC8" s="399" t="n"/>
+      <c r="AD8" s="399" t="n"/>
+      <c r="AE8" s="399" t="n"/>
+      <c r="AF8" s="399" t="n"/>
+      <c r="AG8" s="399" t="n"/>
+      <c r="AH8" s="399" t="n"/>
+      <c r="AI8" s="399" t="n"/>
+      <c r="AJ8" s="399" t="n"/>
+      <c r="AK8" s="399" t="n"/>
+      <c r="AL8" s="399" t="n"/>
+      <c r="AM8" s="399" t="n"/>
+      <c r="AN8" s="400" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="354" t="inlineStr">
         <is>
           <t>Supplier / Processor</t>
         </is>
       </c>
-      <c r="B9" s="317" t="n"/>
-      <c r="C9" s="317" t="n"/>
-      <c r="D9" s="317" t="n"/>
-      <c r="E9" s="317" t="n"/>
-      <c r="F9" s="317" t="n"/>
-      <c r="G9" s="318" t="n"/>
-      <c r="H9" s="288" t="n"/>
-      <c r="I9" s="317" t="n"/>
-      <c r="J9" s="317" t="n"/>
-      <c r="K9" s="317" t="n"/>
-      <c r="L9" s="317" t="n"/>
-      <c r="M9" s="317" t="n"/>
-      <c r="N9" s="317" t="n"/>
-      <c r="O9" s="317" t="n"/>
-      <c r="P9" s="317" t="n"/>
-      <c r="Q9" s="317" t="n"/>
-      <c r="R9" s="317" t="n"/>
-      <c r="S9" s="317" t="n"/>
-      <c r="T9" s="318" t="n"/>
-      <c r="U9" s="289" t="inlineStr">
+      <c r="B9" s="399" t="n"/>
+      <c r="C9" s="399" t="n"/>
+      <c r="D9" s="399" t="n"/>
+      <c r="E9" s="399" t="n"/>
+      <c r="F9" s="399" t="n"/>
+      <c r="G9" s="400" t="n"/>
+      <c r="H9" s="357" t="n"/>
+      <c r="I9" s="399" t="n"/>
+      <c r="J9" s="399" t="n"/>
+      <c r="K9" s="399" t="n"/>
+      <c r="L9" s="399" t="n"/>
+      <c r="M9" s="399" t="n"/>
+      <c r="N9" s="399" t="n"/>
+      <c r="O9" s="399" t="n"/>
+      <c r="P9" s="399" t="n"/>
+      <c r="Q9" s="399" t="n"/>
+      <c r="R9" s="399" t="n"/>
+      <c r="S9" s="399" t="n"/>
+      <c r="T9" s="400" t="n"/>
+      <c r="U9" s="358" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="V9" s="317" t="n"/>
-      <c r="W9" s="317" t="n"/>
-      <c r="X9" s="317" t="n"/>
-      <c r="Y9" s="317" t="n"/>
-      <c r="Z9" s="317" t="n"/>
-      <c r="AA9" s="318" t="n"/>
-      <c r="AB9" s="290" t="n"/>
-      <c r="AC9" s="317" t="n"/>
-      <c r="AD9" s="317" t="n"/>
-      <c r="AE9" s="317" t="n"/>
-      <c r="AF9" s="317" t="n"/>
-      <c r="AG9" s="317" t="n"/>
-      <c r="AH9" s="317" t="n"/>
-      <c r="AI9" s="317" t="n"/>
-      <c r="AJ9" s="317" t="n"/>
-      <c r="AK9" s="317" t="n"/>
-      <c r="AL9" s="317" t="n"/>
-      <c r="AM9" s="317" t="n"/>
-      <c r="AN9" s="319" t="n"/>
+      <c r="V9" s="399" t="n"/>
+      <c r="W9" s="399" t="n"/>
+      <c r="X9" s="399" t="n"/>
+      <c r="Y9" s="399" t="n"/>
+      <c r="Z9" s="399" t="n"/>
+      <c r="AA9" s="400" t="n"/>
+      <c r="AB9" s="357" t="n"/>
+      <c r="AC9" s="399" t="n"/>
+      <c r="AD9" s="399" t="n"/>
+      <c r="AE9" s="399" t="n"/>
+      <c r="AF9" s="399" t="n"/>
+      <c r="AG9" s="399" t="n"/>
+      <c r="AH9" s="399" t="n"/>
+      <c r="AI9" s="399" t="n"/>
+      <c r="AJ9" s="399" t="n"/>
+      <c r="AK9" s="399" t="n"/>
+      <c r="AL9" s="399" t="n"/>
+      <c r="AM9" s="399" t="n"/>
+      <c r="AN9" s="400" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="354" t="inlineStr">
         <is>
           <t>PO / Work Order</t>
         </is>
       </c>
-      <c r="B10" s="317" t="n"/>
-      <c r="C10" s="317" t="n"/>
-      <c r="D10" s="317" t="n"/>
-      <c r="E10" s="317" t="n"/>
-      <c r="F10" s="317" t="n"/>
-      <c r="G10" s="318" t="n"/>
-      <c r="H10" s="288" t="n"/>
-      <c r="I10" s="317" t="n"/>
-      <c r="J10" s="317" t="n"/>
-      <c r="K10" s="317" t="n"/>
-      <c r="L10" s="317" t="n"/>
-      <c r="M10" s="317" t="n"/>
-      <c r="N10" s="317" t="n"/>
-      <c r="O10" s="317" t="n"/>
-      <c r="P10" s="317" t="n"/>
-      <c r="Q10" s="317" t="n"/>
-      <c r="R10" s="317" t="n"/>
-      <c r="S10" s="317" t="n"/>
-      <c r="T10" s="318" t="n"/>
-      <c r="U10" s="289" t="inlineStr">
+      <c r="B10" s="399" t="n"/>
+      <c r="C10" s="399" t="n"/>
+      <c r="D10" s="399" t="n"/>
+      <c r="E10" s="399" t="n"/>
+      <c r="F10" s="399" t="n"/>
+      <c r="G10" s="400" t="n"/>
+      <c r="H10" s="357" t="n"/>
+      <c r="I10" s="399" t="n"/>
+      <c r="J10" s="399" t="n"/>
+      <c r="K10" s="399" t="n"/>
+      <c r="L10" s="399" t="n"/>
+      <c r="M10" s="399" t="n"/>
+      <c r="N10" s="399" t="n"/>
+      <c r="O10" s="399" t="n"/>
+      <c r="P10" s="399" t="n"/>
+      <c r="Q10" s="399" t="n"/>
+      <c r="R10" s="399" t="n"/>
+      <c r="S10" s="399" t="n"/>
+      <c r="T10" s="400" t="n"/>
+      <c r="U10" s="358" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="317" t="n"/>
-      <c r="W10" s="317" t="n"/>
-      <c r="X10" s="317" t="n"/>
-      <c r="Y10" s="317" t="n"/>
-      <c r="Z10" s="317" t="n"/>
-      <c r="AA10" s="318" t="n"/>
-      <c r="AB10" s="290" t="n"/>
-      <c r="AC10" s="317" t="n"/>
-      <c r="AD10" s="317" t="n"/>
-      <c r="AE10" s="317" t="n"/>
-      <c r="AF10" s="317" t="n"/>
-      <c r="AG10" s="317" t="n"/>
-      <c r="AH10" s="317" t="n"/>
-      <c r="AI10" s="317" t="n"/>
-      <c r="AJ10" s="317" t="n"/>
-      <c r="AK10" s="317" t="n"/>
-      <c r="AL10" s="317" t="n"/>
-      <c r="AM10" s="317" t="n"/>
-      <c r="AN10" s="319" t="n"/>
+      <c r="V10" s="399" t="n"/>
+      <c r="W10" s="399" t="n"/>
+      <c r="X10" s="399" t="n"/>
+      <c r="Y10" s="399" t="n"/>
+      <c r="Z10" s="399" t="n"/>
+      <c r="AA10" s="400" t="n"/>
+      <c r="AB10" s="357" t="n"/>
+      <c r="AC10" s="399" t="n"/>
+      <c r="AD10" s="399" t="n"/>
+      <c r="AE10" s="399" t="n"/>
+      <c r="AF10" s="399" t="n"/>
+      <c r="AG10" s="399" t="n"/>
+      <c r="AH10" s="399" t="n"/>
+      <c r="AI10" s="399" t="n"/>
+      <c r="AJ10" s="399" t="n"/>
+      <c r="AK10" s="399" t="n"/>
+      <c r="AL10" s="399" t="n"/>
+      <c r="AM10" s="399" t="n"/>
+      <c r="AN10" s="400" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="354" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="317" t="n"/>
-      <c r="C11" s="317" t="n"/>
-      <c r="D11" s="317" t="n"/>
-      <c r="E11" s="317" t="n"/>
-      <c r="F11" s="317" t="n"/>
-      <c r="G11" s="318" t="n"/>
-      <c r="H11" s="288" t="n"/>
-      <c r="I11" s="317" t="n"/>
-      <c r="J11" s="317" t="n"/>
-      <c r="K11" s="317" t="n"/>
-      <c r="L11" s="317" t="n"/>
-      <c r="M11" s="317" t="n"/>
-      <c r="N11" s="317" t="n"/>
-      <c r="O11" s="317" t="n"/>
-      <c r="P11" s="317" t="n"/>
-      <c r="Q11" s="317" t="n"/>
-      <c r="R11" s="317" t="n"/>
-      <c r="S11" s="317" t="n"/>
-      <c r="T11" s="318" t="n"/>
-      <c r="U11" s="289" t="inlineStr">
+      <c r="B11" s="394" t="n"/>
+      <c r="C11" s="394" t="n"/>
+      <c r="D11" s="394" t="n"/>
+      <c r="E11" s="394" t="n"/>
+      <c r="F11" s="394" t="n"/>
+      <c r="G11" s="395" t="n"/>
+      <c r="H11" s="357" t="n"/>
+      <c r="I11" s="394" t="n"/>
+      <c r="J11" s="394" t="n"/>
+      <c r="K11" s="394" t="n"/>
+      <c r="L11" s="394" t="n"/>
+      <c r="M11" s="394" t="n"/>
+      <c r="N11" s="394" t="n"/>
+      <c r="O11" s="394" t="n"/>
+      <c r="P11" s="394" t="n"/>
+      <c r="Q11" s="394" t="n"/>
+      <c r="R11" s="394" t="n"/>
+      <c r="S11" s="394" t="n"/>
+      <c r="T11" s="395" t="n"/>
+      <c r="U11" s="358" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="317" t="n"/>
-      <c r="W11" s="317" t="n"/>
-      <c r="X11" s="317" t="n"/>
-      <c r="Y11" s="317" t="n"/>
-      <c r="Z11" s="317" t="n"/>
-      <c r="AA11" s="318" t="n"/>
-      <c r="AB11" s="290" t="n"/>
-      <c r="AC11" s="317" t="n"/>
-      <c r="AD11" s="317" t="n"/>
-      <c r="AE11" s="317" t="n"/>
-      <c r="AF11" s="317" t="n"/>
-      <c r="AG11" s="317" t="n"/>
-      <c r="AH11" s="317" t="n"/>
-      <c r="AI11" s="317" t="n"/>
-      <c r="AJ11" s="317" t="n"/>
-      <c r="AK11" s="317" t="n"/>
-      <c r="AL11" s="317" t="n"/>
-      <c r="AM11" s="317" t="n"/>
-      <c r="AN11" s="319" t="n"/>
+      <c r="V11" s="394" t="n"/>
+      <c r="W11" s="394" t="n"/>
+      <c r="X11" s="394" t="n"/>
+      <c r="Y11" s="394" t="n"/>
+      <c r="Z11" s="394" t="n"/>
+      <c r="AA11" s="395" t="n"/>
+      <c r="AB11" s="357" t="n"/>
+      <c r="AC11" s="394" t="n"/>
+      <c r="AD11" s="394" t="n"/>
+      <c r="AE11" s="394" t="n"/>
+      <c r="AF11" s="394" t="n"/>
+      <c r="AG11" s="394" t="n"/>
+      <c r="AH11" s="394" t="n"/>
+      <c r="AI11" s="394" t="n"/>
+      <c r="AJ11" s="394" t="n"/>
+      <c r="AK11" s="394" t="n"/>
+      <c r="AL11" s="394" t="n"/>
+      <c r="AM11" s="394" t="n"/>
+      <c r="AN11" s="395" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="354" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="317" t="n"/>
-      <c r="C12" s="317" t="n"/>
-      <c r="D12" s="317" t="n"/>
-      <c r="E12" s="317" t="n"/>
-      <c r="F12" s="317" t="n"/>
-      <c r="G12" s="318" t="n"/>
-      <c r="H12" s="288" t="n"/>
-      <c r="I12" s="317" t="n"/>
-      <c r="J12" s="317" t="n"/>
-      <c r="K12" s="317" t="n"/>
-      <c r="L12" s="317" t="n"/>
-      <c r="M12" s="317" t="n"/>
-      <c r="N12" s="317" t="n"/>
-      <c r="O12" s="317" t="n"/>
-      <c r="P12" s="317" t="n"/>
-      <c r="Q12" s="317" t="n"/>
-      <c r="R12" s="317" t="n"/>
-      <c r="S12" s="317" t="n"/>
-      <c r="T12" s="318" t="n"/>
-      <c r="U12" s="289" t="inlineStr">
+      <c r="B12" s="399" t="n"/>
+      <c r="C12" s="399" t="n"/>
+      <c r="D12" s="399" t="n"/>
+      <c r="E12" s="399" t="n"/>
+      <c r="F12" s="399" t="n"/>
+      <c r="G12" s="400" t="n"/>
+      <c r="H12" s="357" t="n"/>
+      <c r="I12" s="399" t="n"/>
+      <c r="J12" s="399" t="n"/>
+      <c r="K12" s="399" t="n"/>
+      <c r="L12" s="399" t="n"/>
+      <c r="M12" s="399" t="n"/>
+      <c r="N12" s="399" t="n"/>
+      <c r="O12" s="399" t="n"/>
+      <c r="P12" s="399" t="n"/>
+      <c r="Q12" s="399" t="n"/>
+      <c r="R12" s="399" t="n"/>
+      <c r="S12" s="399" t="n"/>
+      <c r="T12" s="400" t="n"/>
+      <c r="U12" s="358" t="inlineStr">
         <is>
           <t>Approval State</t>
         </is>
       </c>
-      <c r="V12" s="317" t="n"/>
-      <c r="W12" s="317" t="n"/>
-      <c r="X12" s="317" t="n"/>
-      <c r="Y12" s="317" t="n"/>
-      <c r="Z12" s="317" t="n"/>
-      <c r="AA12" s="318" t="n"/>
-      <c r="AB12" s="290" t="n"/>
-      <c r="AC12" s="317" t="n"/>
-      <c r="AD12" s="317" t="n"/>
-      <c r="AE12" s="317" t="n"/>
-      <c r="AF12" s="317" t="n"/>
-      <c r="AG12" s="317" t="n"/>
-      <c r="AH12" s="317" t="n"/>
-      <c r="AI12" s="317" t="n"/>
-      <c r="AJ12" s="317" t="n"/>
-      <c r="AK12" s="317" t="n"/>
-      <c r="AL12" s="317" t="n"/>
-      <c r="AM12" s="317" t="n"/>
-      <c r="AN12" s="319" t="n"/>
+      <c r="V12" s="399" t="n"/>
+      <c r="W12" s="399" t="n"/>
+      <c r="X12" s="399" t="n"/>
+      <c r="Y12" s="399" t="n"/>
+      <c r="Z12" s="399" t="n"/>
+      <c r="AA12" s="400" t="n"/>
+      <c r="AB12" s="357" t="n"/>
+      <c r="AC12" s="399" t="n"/>
+      <c r="AD12" s="399" t="n"/>
+      <c r="AE12" s="399" t="n"/>
+      <c r="AF12" s="399" t="n"/>
+      <c r="AG12" s="399" t="n"/>
+      <c r="AH12" s="399" t="n"/>
+      <c r="AI12" s="399" t="n"/>
+      <c r="AJ12" s="399" t="n"/>
+      <c r="AK12" s="399" t="n"/>
+      <c r="AL12" s="399" t="n"/>
+      <c r="AM12" s="399" t="n"/>
+      <c r="AN12" s="400" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="287" t="inlineStr">
+    <row r="13" ht="26" customHeight="1" s="329">
+      <c r="A13" s="354" t="inlineStr">
         <is>
           <t>Route Step / Due Date</t>
         </is>
       </c>
-      <c r="B13" s="317" t="n"/>
-      <c r="C13" s="317" t="n"/>
-      <c r="D13" s="317" t="n"/>
-      <c r="E13" s="317" t="n"/>
-      <c r="F13" s="317" t="n"/>
-      <c r="G13" s="318" t="n"/>
-      <c r="H13" s="288" t="n"/>
-      <c r="I13" s="317" t="n"/>
-      <c r="J13" s="317" t="n"/>
-      <c r="K13" s="317" t="n"/>
-      <c r="L13" s="317" t="n"/>
-      <c r="M13" s="317" t="n"/>
-      <c r="N13" s="317" t="n"/>
-      <c r="O13" s="317" t="n"/>
-      <c r="P13" s="317" t="n"/>
-      <c r="Q13" s="317" t="n"/>
-      <c r="R13" s="317" t="n"/>
-      <c r="S13" s="317" t="n"/>
-      <c r="T13" s="318" t="n"/>
-      <c r="U13" s="289" t="inlineStr">
+      <c r="B13" s="394" t="n"/>
+      <c r="C13" s="394" t="n"/>
+      <c r="D13" s="394" t="n"/>
+      <c r="E13" s="394" t="n"/>
+      <c r="F13" s="394" t="n"/>
+      <c r="G13" s="395" t="n"/>
+      <c r="H13" s="357" t="n"/>
+      <c r="I13" s="394" t="n"/>
+      <c r="J13" s="394" t="n"/>
+      <c r="K13" s="394" t="n"/>
+      <c r="L13" s="394" t="n"/>
+      <c r="M13" s="394" t="n"/>
+      <c r="N13" s="394" t="n"/>
+      <c r="O13" s="394" t="n"/>
+      <c r="P13" s="394" t="n"/>
+      <c r="Q13" s="394" t="n"/>
+      <c r="R13" s="394" t="n"/>
+      <c r="S13" s="394" t="n"/>
+      <c r="T13" s="395" t="n"/>
+      <c r="U13" s="358" t="inlineStr">
         <is>
           <t>Package Ref</t>
         </is>
       </c>
-      <c r="V13" s="317" t="n"/>
-      <c r="W13" s="317" t="n"/>
-      <c r="X13" s="317" t="n"/>
-      <c r="Y13" s="317" t="n"/>
-      <c r="Z13" s="317" t="n"/>
-      <c r="AA13" s="318" t="n"/>
-      <c r="AB13" s="290" t="n"/>
-      <c r="AC13" s="317" t="n"/>
-      <c r="AD13" s="317" t="n"/>
-      <c r="AE13" s="317" t="n"/>
-      <c r="AF13" s="317" t="n"/>
-      <c r="AG13" s="317" t="n"/>
-      <c r="AH13" s="317" t="n"/>
-      <c r="AI13" s="317" t="n"/>
-      <c r="AJ13" s="317" t="n"/>
-      <c r="AK13" s="317" t="n"/>
-      <c r="AL13" s="317" t="n"/>
-      <c r="AM13" s="317" t="n"/>
-      <c r="AN13" s="319" t="n"/>
+      <c r="V13" s="394" t="n"/>
+      <c r="W13" s="394" t="n"/>
+      <c r="X13" s="394" t="n"/>
+      <c r="Y13" s="394" t="n"/>
+      <c r="Z13" s="394" t="n"/>
+      <c r="AA13" s="395" t="n"/>
+      <c r="AB13" s="357" t="n"/>
+      <c r="AC13" s="394" t="n"/>
+      <c r="AD13" s="394" t="n"/>
+      <c r="AE13" s="394" t="n"/>
+      <c r="AF13" s="394" t="n"/>
+      <c r="AG13" s="394" t="n"/>
+      <c r="AH13" s="394" t="n"/>
+      <c r="AI13" s="394" t="n"/>
+      <c r="AJ13" s="394" t="n"/>
+      <c r="AK13" s="394" t="n"/>
+      <c r="AL13" s="394" t="n"/>
+      <c r="AM13" s="394" t="n"/>
+      <c r="AN13" s="395" t="n"/>
     </row>
     <row r="14" ht="4" customHeight="1" s="329">
-      <c r="A14" s="284" t="n"/>
+      <c r="A14" s="359" t="n"/>
+      <c r="B14" s="352" t="n"/>
+      <c r="C14" s="352" t="n"/>
+      <c r="D14" s="352" t="n"/>
+      <c r="E14" s="352" t="n"/>
+      <c r="F14" s="352" t="n"/>
+      <c r="G14" s="352" t="n"/>
+      <c r="H14" s="352" t="n"/>
+      <c r="I14" s="352" t="n"/>
+      <c r="J14" s="352" t="n"/>
+      <c r="K14" s="352" t="n"/>
+      <c r="L14" s="352" t="n"/>
+      <c r="M14" s="352" t="n"/>
+      <c r="N14" s="352" t="n"/>
+      <c r="O14" s="352" t="n"/>
+      <c r="P14" s="352" t="n"/>
+      <c r="Q14" s="352" t="n"/>
+      <c r="R14" s="352" t="n"/>
+      <c r="S14" s="352" t="n"/>
+      <c r="T14" s="352" t="n"/>
+      <c r="U14" s="352" t="n"/>
+      <c r="V14" s="352" t="n"/>
+      <c r="W14" s="352" t="n"/>
+      <c r="X14" s="352" t="n"/>
+      <c r="Y14" s="352" t="n"/>
+      <c r="Z14" s="352" t="n"/>
+      <c r="AA14" s="352" t="n"/>
+      <c r="AB14" s="352" t="n"/>
+      <c r="AC14" s="352" t="n"/>
+      <c r="AD14" s="352" t="n"/>
+      <c r="AE14" s="352" t="n"/>
+      <c r="AF14" s="352" t="n"/>
+      <c r="AG14" s="352" t="n"/>
+      <c r="AH14" s="352" t="n"/>
+      <c r="AI14" s="352" t="n"/>
+      <c r="AJ14" s="352" t="n"/>
+      <c r="AK14" s="352" t="n"/>
+      <c r="AL14" s="352" t="n"/>
+      <c r="AM14" s="352" t="n"/>
+      <c r="AN14" s="352" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="329">
-      <c r="A15" s="284" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="329">
+      <c r="A15" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
         </is>
       </c>
-      <c r="B15" s="285" t="n"/>
-      <c r="C15" s="285" t="n"/>
-      <c r="D15" s="285" t="n"/>
-      <c r="E15" s="285" t="n"/>
-      <c r="F15" s="285" t="n"/>
-      <c r="G15" s="285" t="n"/>
-      <c r="H15" s="285" t="n"/>
-      <c r="I15" s="285" t="n"/>
-      <c r="J15" s="285" t="n"/>
-      <c r="K15" s="285" t="n"/>
-      <c r="L15" s="285" t="n"/>
-      <c r="M15" s="285" t="n"/>
-      <c r="N15" s="285" t="n"/>
-      <c r="O15" s="285" t="n"/>
-      <c r="P15" s="285" t="n"/>
-      <c r="Q15" s="285" t="n"/>
-      <c r="R15" s="285" t="n"/>
-      <c r="S15" s="285" t="n"/>
-      <c r="T15" s="285" t="n"/>
-      <c r="U15" s="285" t="n"/>
-      <c r="V15" s="285" t="n"/>
-      <c r="W15" s="285" t="n"/>
-      <c r="X15" s="285" t="n"/>
-      <c r="Y15" s="285" t="n"/>
-      <c r="Z15" s="285" t="n"/>
-      <c r="AA15" s="285" t="n"/>
-      <c r="AB15" s="285" t="n"/>
-      <c r="AC15" s="285" t="n"/>
-      <c r="AD15" s="285" t="n"/>
-      <c r="AE15" s="285" t="n"/>
-      <c r="AF15" s="285" t="n"/>
-      <c r="AG15" s="285" t="n"/>
-      <c r="AH15" s="285" t="n"/>
-      <c r="AI15" s="285" t="n"/>
-      <c r="AJ15" s="285" t="n"/>
-      <c r="AK15" s="285" t="n"/>
-      <c r="AL15" s="285" t="n"/>
-      <c r="AM15" s="285" t="n"/>
-      <c r="AN15" s="286" t="n"/>
+      <c r="B15" s="399" t="n"/>
+      <c r="C15" s="399" t="n"/>
+      <c r="D15" s="399" t="n"/>
+      <c r="E15" s="399" t="n"/>
+      <c r="F15" s="399" t="n"/>
+      <c r="G15" s="399" t="n"/>
+      <c r="H15" s="399" t="n"/>
+      <c r="I15" s="399" t="n"/>
+      <c r="J15" s="399" t="n"/>
+      <c r="K15" s="399" t="n"/>
+      <c r="L15" s="399" t="n"/>
+      <c r="M15" s="399" t="n"/>
+      <c r="N15" s="399" t="n"/>
+      <c r="O15" s="399" t="n"/>
+      <c r="P15" s="399" t="n"/>
+      <c r="Q15" s="399" t="n"/>
+      <c r="R15" s="399" t="n"/>
+      <c r="S15" s="399" t="n"/>
+      <c r="T15" s="399" t="n"/>
+      <c r="U15" s="399" t="n"/>
+      <c r="V15" s="399" t="n"/>
+      <c r="W15" s="399" t="n"/>
+      <c r="X15" s="399" t="n"/>
+      <c r="Y15" s="399" t="n"/>
+      <c r="Z15" s="399" t="n"/>
+      <c r="AA15" s="399" t="n"/>
+      <c r="AB15" s="399" t="n"/>
+      <c r="AC15" s="399" t="n"/>
+      <c r="AD15" s="399" t="n"/>
+      <c r="AE15" s="399" t="n"/>
+      <c r="AF15" s="399" t="n"/>
+      <c r="AG15" s="399" t="n"/>
+      <c r="AH15" s="399" t="n"/>
+      <c r="AI15" s="399" t="n"/>
+      <c r="AJ15" s="399" t="n"/>
+      <c r="AK15" s="399" t="n"/>
+      <c r="AL15" s="399" t="n"/>
+      <c r="AM15" s="399" t="n"/>
+      <c r="AN15" s="400" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="287" t="inlineStr">
+      <c r="A16" s="354" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="B16" s="317" t="n"/>
-      <c r="C16" s="317" t="n"/>
-      <c r="D16" s="317" t="n"/>
-      <c r="E16" s="317" t="n"/>
-      <c r="F16" s="317" t="n"/>
-      <c r="G16" s="318" t="n"/>
-      <c r="H16" s="288" t="n"/>
-      <c r="I16" s="317" t="n"/>
-      <c r="J16" s="317" t="n"/>
-      <c r="K16" s="317" t="n"/>
-      <c r="L16" s="317" t="n"/>
-      <c r="M16" s="317" t="n"/>
-      <c r="N16" s="317" t="n"/>
-      <c r="O16" s="317" t="n"/>
-      <c r="P16" s="317" t="n"/>
-      <c r="Q16" s="317" t="n"/>
-      <c r="R16" s="317" t="n"/>
-      <c r="S16" s="317" t="n"/>
-      <c r="T16" s="318" t="n"/>
-      <c r="U16" s="289" t="inlineStr">
+      <c r="B16" s="399" t="n"/>
+      <c r="C16" s="399" t="n"/>
+      <c r="D16" s="399" t="n"/>
+      <c r="E16" s="399" t="n"/>
+      <c r="F16" s="399" t="n"/>
+      <c r="G16" s="400" t="n"/>
+      <c r="H16" s="357" t="n"/>
+      <c r="I16" s="399" t="n"/>
+      <c r="J16" s="399" t="n"/>
+      <c r="K16" s="399" t="n"/>
+      <c r="L16" s="399" t="n"/>
+      <c r="M16" s="399" t="n"/>
+      <c r="N16" s="399" t="n"/>
+      <c r="O16" s="399" t="n"/>
+      <c r="P16" s="399" t="n"/>
+      <c r="Q16" s="399" t="n"/>
+      <c r="R16" s="399" t="n"/>
+      <c r="S16" s="399" t="n"/>
+      <c r="T16" s="400" t="n"/>
+      <c r="U16" s="358" t="inlineStr">
         <is>
           <t>Linked Route / Package</t>
         </is>
       </c>
-      <c r="V16" s="317" t="n"/>
-      <c r="W16" s="317" t="n"/>
-      <c r="X16" s="317" t="n"/>
-      <c r="Y16" s="317" t="n"/>
-      <c r="Z16" s="317" t="n"/>
-      <c r="AA16" s="318" t="n"/>
-      <c r="AB16" s="290" t="n"/>
-      <c r="AC16" s="317" t="n"/>
-      <c r="AD16" s="317" t="n"/>
-      <c r="AE16" s="317" t="n"/>
-      <c r="AF16" s="317" t="n"/>
-      <c r="AG16" s="317" t="n"/>
-      <c r="AH16" s="317" t="n"/>
-      <c r="AI16" s="317" t="n"/>
-      <c r="AJ16" s="317" t="n"/>
-      <c r="AK16" s="317" t="n"/>
-      <c r="AL16" s="317" t="n"/>
-      <c r="AM16" s="317" t="n"/>
-      <c r="AN16" s="319" t="n"/>
+      <c r="V16" s="399" t="n"/>
+      <c r="W16" s="399" t="n"/>
+      <c r="X16" s="399" t="n"/>
+      <c r="Y16" s="399" t="n"/>
+      <c r="Z16" s="399" t="n"/>
+      <c r="AA16" s="400" t="n"/>
+      <c r="AB16" s="357" t="n"/>
+      <c r="AC16" s="399" t="n"/>
+      <c r="AD16" s="399" t="n"/>
+      <c r="AE16" s="399" t="n"/>
+      <c r="AF16" s="399" t="n"/>
+      <c r="AG16" s="399" t="n"/>
+      <c r="AH16" s="399" t="n"/>
+      <c r="AI16" s="399" t="n"/>
+      <c r="AJ16" s="399" t="n"/>
+      <c r="AK16" s="399" t="n"/>
+      <c r="AL16" s="399" t="n"/>
+      <c r="AM16" s="399" t="n"/>
+      <c r="AN16" s="400" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="287" t="inlineStr">
+      <c r="A17" s="354" t="inlineStr">
         <is>
           <t>Supplier / Customer Spec Ref</t>
         </is>
       </c>
-      <c r="B17" s="317" t="n"/>
-      <c r="C17" s="317" t="n"/>
-      <c r="D17" s="317" t="n"/>
-      <c r="E17" s="317" t="n"/>
-      <c r="F17" s="317" t="n"/>
-      <c r="G17" s="318" t="n"/>
-      <c r="H17" s="288" t="n"/>
-      <c r="I17" s="317" t="n"/>
-      <c r="J17" s="317" t="n"/>
-      <c r="K17" s="317" t="n"/>
-      <c r="L17" s="317" t="n"/>
-      <c r="M17" s="317" t="n"/>
-      <c r="N17" s="317" t="n"/>
-      <c r="O17" s="317" t="n"/>
-      <c r="P17" s="317" t="n"/>
-      <c r="Q17" s="317" t="n"/>
-      <c r="R17" s="317" t="n"/>
-      <c r="S17" s="317" t="n"/>
-      <c r="T17" s="318" t="n"/>
-      <c r="U17" s="289" t="inlineStr">
+      <c r="B17" s="399" t="n"/>
+      <c r="C17" s="399" t="n"/>
+      <c r="D17" s="399" t="n"/>
+      <c r="E17" s="399" t="n"/>
+      <c r="F17" s="399" t="n"/>
+      <c r="G17" s="400" t="n"/>
+      <c r="H17" s="357" t="n"/>
+      <c r="I17" s="399" t="n"/>
+      <c r="J17" s="399" t="n"/>
+      <c r="K17" s="399" t="n"/>
+      <c r="L17" s="399" t="n"/>
+      <c r="M17" s="399" t="n"/>
+      <c r="N17" s="399" t="n"/>
+      <c r="O17" s="399" t="n"/>
+      <c r="P17" s="399" t="n"/>
+      <c r="Q17" s="399" t="n"/>
+      <c r="R17" s="399" t="n"/>
+      <c r="S17" s="399" t="n"/>
+      <c r="T17" s="400" t="n"/>
+      <c r="U17" s="358" t="inlineStr">
         <is>
           <t>Open Actions Present (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="317" t="n"/>
-      <c r="W17" s="317" t="n"/>
-      <c r="X17" s="317" t="n"/>
-      <c r="Y17" s="317" t="n"/>
-      <c r="Z17" s="317" t="n"/>
-      <c r="AA17" s="318" t="n"/>
-      <c r="AB17" s="290" t="n"/>
-      <c r="AC17" s="317" t="n"/>
-      <c r="AD17" s="317" t="n"/>
-      <c r="AE17" s="317" t="n"/>
-      <c r="AF17" s="317" t="n"/>
-      <c r="AG17" s="317" t="n"/>
-      <c r="AH17" s="317" t="n"/>
-      <c r="AI17" s="317" t="n"/>
-      <c r="AJ17" s="317" t="n"/>
-      <c r="AK17" s="317" t="n"/>
-      <c r="AL17" s="317" t="n"/>
-      <c r="AM17" s="317" t="n"/>
-      <c r="AN17" s="319" t="n"/>
+      <c r="V17" s="399" t="n"/>
+      <c r="W17" s="399" t="n"/>
+      <c r="X17" s="399" t="n"/>
+      <c r="Y17" s="399" t="n"/>
+      <c r="Z17" s="399" t="n"/>
+      <c r="AA17" s="400" t="n"/>
+      <c r="AB17" s="357" t="n"/>
+      <c r="AC17" s="399" t="n"/>
+      <c r="AD17" s="399" t="n"/>
+      <c r="AE17" s="399" t="n"/>
+      <c r="AF17" s="399" t="n"/>
+      <c r="AG17" s="399" t="n"/>
+      <c r="AH17" s="399" t="n"/>
+      <c r="AI17" s="399" t="n"/>
+      <c r="AJ17" s="399" t="n"/>
+      <c r="AK17" s="399" t="n"/>
+      <c r="AL17" s="399" t="n"/>
+      <c r="AM17" s="399" t="n"/>
+      <c r="AN17" s="400" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="287" t="inlineStr">
+      <c r="A18" s="354" t="inlineStr">
         <is>
           <t>DISPATCH NOTES / CONDITIONALS</t>
         </is>
       </c>
-      <c r="B18" s="317" t="n"/>
-      <c r="C18" s="317" t="n"/>
-      <c r="D18" s="317" t="n"/>
-      <c r="E18" s="317" t="n"/>
-      <c r="F18" s="317" t="n"/>
-      <c r="G18" s="317" t="n"/>
-      <c r="H18" s="317" t="n"/>
-      <c r="I18" s="317" t="n"/>
-      <c r="J18" s="317" t="n"/>
-      <c r="K18" s="317" t="n"/>
-      <c r="L18" s="317" t="n"/>
-      <c r="M18" s="317" t="n"/>
-      <c r="N18" s="317" t="n"/>
-      <c r="O18" s="317" t="n"/>
-      <c r="P18" s="317" t="n"/>
-      <c r="Q18" s="317" t="n"/>
-      <c r="R18" s="317" t="n"/>
-      <c r="S18" s="317" t="n"/>
-      <c r="T18" s="317" t="n"/>
-      <c r="U18" s="317" t="n"/>
-      <c r="V18" s="317" t="n"/>
-      <c r="W18" s="317" t="n"/>
-      <c r="X18" s="317" t="n"/>
-      <c r="Y18" s="317" t="n"/>
-      <c r="Z18" s="317" t="n"/>
-      <c r="AA18" s="317" t="n"/>
-      <c r="AB18" s="317" t="n"/>
-      <c r="AC18" s="317" t="n"/>
-      <c r="AD18" s="317" t="n"/>
-      <c r="AE18" s="317" t="n"/>
-      <c r="AF18" s="317" t="n"/>
-      <c r="AG18" s="317" t="n"/>
-      <c r="AH18" s="317" t="n"/>
-      <c r="AI18" s="317" t="n"/>
-      <c r="AJ18" s="317" t="n"/>
-      <c r="AK18" s="317" t="n"/>
-      <c r="AL18" s="317" t="n"/>
-      <c r="AM18" s="317" t="n"/>
-      <c r="AN18" s="318" t="n"/>
+      <c r="B18" s="399" t="n"/>
+      <c r="C18" s="399" t="n"/>
+      <c r="D18" s="399" t="n"/>
+      <c r="E18" s="399" t="n"/>
+      <c r="F18" s="399" t="n"/>
+      <c r="G18" s="399" t="n"/>
+      <c r="H18" s="399" t="n"/>
+      <c r="I18" s="399" t="n"/>
+      <c r="J18" s="399" t="n"/>
+      <c r="K18" s="399" t="n"/>
+      <c r="L18" s="399" t="n"/>
+      <c r="M18" s="399" t="n"/>
+      <c r="N18" s="399" t="n"/>
+      <c r="O18" s="399" t="n"/>
+      <c r="P18" s="399" t="n"/>
+      <c r="Q18" s="399" t="n"/>
+      <c r="R18" s="399" t="n"/>
+      <c r="S18" s="399" t="n"/>
+      <c r="T18" s="399" t="n"/>
+      <c r="U18" s="399" t="n"/>
+      <c r="V18" s="399" t="n"/>
+      <c r="W18" s="399" t="n"/>
+      <c r="X18" s="399" t="n"/>
+      <c r="Y18" s="399" t="n"/>
+      <c r="Z18" s="399" t="n"/>
+      <c r="AA18" s="399" t="n"/>
+      <c r="AB18" s="399" t="n"/>
+      <c r="AC18" s="399" t="n"/>
+      <c r="AD18" s="399" t="n"/>
+      <c r="AE18" s="399" t="n"/>
+      <c r="AF18" s="399" t="n"/>
+      <c r="AG18" s="399" t="n"/>
+      <c r="AH18" s="399" t="n"/>
+      <c r="AI18" s="399" t="n"/>
+      <c r="AJ18" s="399" t="n"/>
+      <c r="AK18" s="399" t="n"/>
+      <c r="AL18" s="399" t="n"/>
+      <c r="AM18" s="399" t="n"/>
+      <c r="AN18" s="400" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="291" t="n"/>
-      <c r="B19" s="320" t="n"/>
-      <c r="C19" s="320" t="n"/>
-      <c r="D19" s="320" t="n"/>
-      <c r="E19" s="320" t="n"/>
-      <c r="F19" s="320" t="n"/>
-      <c r="G19" s="320" t="n"/>
-      <c r="H19" s="320" t="n"/>
-      <c r="I19" s="320" t="n"/>
-      <c r="J19" s="320" t="n"/>
-      <c r="K19" s="320" t="n"/>
-      <c r="L19" s="320" t="n"/>
-      <c r="M19" s="320" t="n"/>
-      <c r="N19" s="320" t="n"/>
-      <c r="O19" s="320" t="n"/>
-      <c r="P19" s="320" t="n"/>
-      <c r="Q19" s="320" t="n"/>
-      <c r="R19" s="320" t="n"/>
-      <c r="S19" s="320" t="n"/>
-      <c r="T19" s="320" t="n"/>
-      <c r="U19" s="320" t="n"/>
-      <c r="V19" s="320" t="n"/>
-      <c r="W19" s="320" t="n"/>
-      <c r="X19" s="320" t="n"/>
-      <c r="Y19" s="320" t="n"/>
-      <c r="Z19" s="320" t="n"/>
-      <c r="AA19" s="320" t="n"/>
-      <c r="AB19" s="320" t="n"/>
-      <c r="AC19" s="320" t="n"/>
-      <c r="AD19" s="320" t="n"/>
-      <c r="AE19" s="320" t="n"/>
-      <c r="AF19" s="320" t="n"/>
-      <c r="AG19" s="320" t="n"/>
-      <c r="AH19" s="320" t="n"/>
-      <c r="AI19" s="320" t="n"/>
-      <c r="AJ19" s="320" t="n"/>
-      <c r="AK19" s="320" t="n"/>
-      <c r="AL19" s="320" t="n"/>
-      <c r="AM19" s="320" t="n"/>
-      <c r="AN19" s="321" t="n"/>
+      <c r="A19" s="357" t="n"/>
+      <c r="B19" s="401" t="n"/>
+      <c r="C19" s="401" t="n"/>
+      <c r="D19" s="401" t="n"/>
+      <c r="E19" s="401" t="n"/>
+      <c r="F19" s="401" t="n"/>
+      <c r="G19" s="401" t="n"/>
+      <c r="H19" s="401" t="n"/>
+      <c r="I19" s="401" t="n"/>
+      <c r="J19" s="401" t="n"/>
+      <c r="K19" s="401" t="n"/>
+      <c r="L19" s="401" t="n"/>
+      <c r="M19" s="401" t="n"/>
+      <c r="N19" s="401" t="n"/>
+      <c r="O19" s="401" t="n"/>
+      <c r="P19" s="401" t="n"/>
+      <c r="Q19" s="401" t="n"/>
+      <c r="R19" s="401" t="n"/>
+      <c r="S19" s="401" t="n"/>
+      <c r="T19" s="401" t="n"/>
+      <c r="U19" s="401" t="n"/>
+      <c r="V19" s="401" t="n"/>
+      <c r="W19" s="401" t="n"/>
+      <c r="X19" s="401" t="n"/>
+      <c r="Y19" s="401" t="n"/>
+      <c r="Z19" s="401" t="n"/>
+      <c r="AA19" s="401" t="n"/>
+      <c r="AB19" s="401" t="n"/>
+      <c r="AC19" s="401" t="n"/>
+      <c r="AD19" s="401" t="n"/>
+      <c r="AE19" s="401" t="n"/>
+      <c r="AF19" s="401" t="n"/>
+      <c r="AG19" s="401" t="n"/>
+      <c r="AH19" s="401" t="n"/>
+      <c r="AI19" s="401" t="n"/>
+      <c r="AJ19" s="401" t="n"/>
+      <c r="AK19" s="401" t="n"/>
+      <c r="AL19" s="401" t="n"/>
+      <c r="AM19" s="401" t="n"/>
+      <c r="AN19" s="402" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="322" t="n"/>
-      <c r="B20" s="322" t="n"/>
-      <c r="C20" s="322" t="n"/>
-      <c r="D20" s="322" t="n"/>
-      <c r="E20" s="322" t="n"/>
-      <c r="F20" s="322" t="n"/>
-      <c r="G20" s="322" t="n"/>
-      <c r="H20" s="322" t="n"/>
-      <c r="I20" s="322" t="n"/>
-      <c r="J20" s="322" t="n"/>
-      <c r="K20" s="322" t="n"/>
-      <c r="L20" s="322" t="n"/>
-      <c r="M20" s="322" t="n"/>
-      <c r="N20" s="322" t="n"/>
-      <c r="O20" s="322" t="n"/>
-      <c r="P20" s="322" t="n"/>
-      <c r="Q20" s="322" t="n"/>
-      <c r="R20" s="322" t="n"/>
-      <c r="S20" s="322" t="n"/>
-      <c r="T20" s="322" t="n"/>
-      <c r="U20" s="322" t="n"/>
-      <c r="V20" s="322" t="n"/>
-      <c r="W20" s="322" t="n"/>
-      <c r="X20" s="322" t="n"/>
-      <c r="Y20" s="322" t="n"/>
-      <c r="Z20" s="322" t="n"/>
-      <c r="AA20" s="322" t="n"/>
-      <c r="AB20" s="322" t="n"/>
-      <c r="AC20" s="322" t="n"/>
-      <c r="AD20" s="322" t="n"/>
-      <c r="AE20" s="322" t="n"/>
-      <c r="AF20" s="322" t="n"/>
-      <c r="AG20" s="322" t="n"/>
-      <c r="AH20" s="322" t="n"/>
-      <c r="AI20" s="322" t="n"/>
-      <c r="AJ20" s="322" t="n"/>
-      <c r="AK20" s="322" t="n"/>
-      <c r="AL20" s="322" t="n"/>
-      <c r="AM20" s="322" t="n"/>
-      <c r="AN20" s="323" t="n"/>
+      <c r="A20" s="403" t="n"/>
+      <c r="B20" s="403" t="n"/>
+      <c r="C20" s="403" t="n"/>
+      <c r="D20" s="403" t="n"/>
+      <c r="E20" s="403" t="n"/>
+      <c r="F20" s="403" t="n"/>
+      <c r="G20" s="403" t="n"/>
+      <c r="H20" s="403" t="n"/>
+      <c r="I20" s="403" t="n"/>
+      <c r="J20" s="403" t="n"/>
+      <c r="K20" s="403" t="n"/>
+      <c r="L20" s="403" t="n"/>
+      <c r="M20" s="403" t="n"/>
+      <c r="N20" s="403" t="n"/>
+      <c r="O20" s="403" t="n"/>
+      <c r="P20" s="403" t="n"/>
+      <c r="Q20" s="403" t="n"/>
+      <c r="R20" s="403" t="n"/>
+      <c r="S20" s="403" t="n"/>
+      <c r="T20" s="403" t="n"/>
+      <c r="U20" s="403" t="n"/>
+      <c r="V20" s="403" t="n"/>
+      <c r="W20" s="403" t="n"/>
+      <c r="X20" s="403" t="n"/>
+      <c r="Y20" s="403" t="n"/>
+      <c r="Z20" s="403" t="n"/>
+      <c r="AA20" s="403" t="n"/>
+      <c r="AB20" s="403" t="n"/>
+      <c r="AC20" s="403" t="n"/>
+      <c r="AD20" s="403" t="n"/>
+      <c r="AE20" s="403" t="n"/>
+      <c r="AF20" s="403" t="n"/>
+      <c r="AG20" s="403" t="n"/>
+      <c r="AH20" s="403" t="n"/>
+      <c r="AI20" s="403" t="n"/>
+      <c r="AJ20" s="403" t="n"/>
+      <c r="AK20" s="403" t="n"/>
+      <c r="AL20" s="403" t="n"/>
+      <c r="AM20" s="403" t="n"/>
+      <c r="AN20" s="404" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="287" t="inlineStr">
+      <c r="A21" s="354" t="inlineStr">
         <is>
           <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
         </is>
       </c>
-      <c r="B21" s="317" t="n"/>
-      <c r="C21" s="317" t="n"/>
-      <c r="D21" s="317" t="n"/>
-      <c r="E21" s="317" t="n"/>
-      <c r="F21" s="317" t="n"/>
-      <c r="G21" s="317" t="n"/>
-      <c r="H21" s="317" t="n"/>
-      <c r="I21" s="317" t="n"/>
-      <c r="J21" s="317" t="n"/>
-      <c r="K21" s="317" t="n"/>
-      <c r="L21" s="317" t="n"/>
-      <c r="M21" s="317" t="n"/>
-      <c r="N21" s="317" t="n"/>
-      <c r="O21" s="317" t="n"/>
-      <c r="P21" s="317" t="n"/>
-      <c r="Q21" s="317" t="n"/>
-      <c r="R21" s="317" t="n"/>
-      <c r="S21" s="317" t="n"/>
-      <c r="T21" s="317" t="n"/>
-      <c r="U21" s="317" t="n"/>
-      <c r="V21" s="317" t="n"/>
-      <c r="W21" s="317" t="n"/>
-      <c r="X21" s="317" t="n"/>
-      <c r="Y21" s="317" t="n"/>
-      <c r="Z21" s="317" t="n"/>
-      <c r="AA21" s="317" t="n"/>
-      <c r="AB21" s="317" t="n"/>
-      <c r="AC21" s="317" t="n"/>
-      <c r="AD21" s="317" t="n"/>
-      <c r="AE21" s="317" t="n"/>
-      <c r="AF21" s="317" t="n"/>
-      <c r="AG21" s="317" t="n"/>
-      <c r="AH21" s="317" t="n"/>
-      <c r="AI21" s="317" t="n"/>
-      <c r="AJ21" s="317" t="n"/>
-      <c r="AK21" s="317" t="n"/>
-      <c r="AL21" s="317" t="n"/>
-      <c r="AM21" s="317" t="n"/>
-      <c r="AN21" s="318" t="n"/>
+      <c r="B21" s="399" t="n"/>
+      <c r="C21" s="399" t="n"/>
+      <c r="D21" s="399" t="n"/>
+      <c r="E21" s="399" t="n"/>
+      <c r="F21" s="399" t="n"/>
+      <c r="G21" s="399" t="n"/>
+      <c r="H21" s="399" t="n"/>
+      <c r="I21" s="399" t="n"/>
+      <c r="J21" s="399" t="n"/>
+      <c r="K21" s="399" t="n"/>
+      <c r="L21" s="399" t="n"/>
+      <c r="M21" s="399" t="n"/>
+      <c r="N21" s="399" t="n"/>
+      <c r="O21" s="399" t="n"/>
+      <c r="P21" s="399" t="n"/>
+      <c r="Q21" s="399" t="n"/>
+      <c r="R21" s="399" t="n"/>
+      <c r="S21" s="399" t="n"/>
+      <c r="T21" s="399" t="n"/>
+      <c r="U21" s="399" t="n"/>
+      <c r="V21" s="399" t="n"/>
+      <c r="W21" s="399" t="n"/>
+      <c r="X21" s="399" t="n"/>
+      <c r="Y21" s="399" t="n"/>
+      <c r="Z21" s="399" t="n"/>
+      <c r="AA21" s="399" t="n"/>
+      <c r="AB21" s="399" t="n"/>
+      <c r="AC21" s="399" t="n"/>
+      <c r="AD21" s="399" t="n"/>
+      <c r="AE21" s="399" t="n"/>
+      <c r="AF21" s="399" t="n"/>
+      <c r="AG21" s="399" t="n"/>
+      <c r="AH21" s="399" t="n"/>
+      <c r="AI21" s="399" t="n"/>
+      <c r="AJ21" s="399" t="n"/>
+      <c r="AK21" s="399" t="n"/>
+      <c r="AL21" s="399" t="n"/>
+      <c r="AM21" s="399" t="n"/>
+      <c r="AN21" s="400" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="291" t="n"/>
-      <c r="B22" s="320" t="n"/>
-      <c r="C22" s="320" t="n"/>
-      <c r="D22" s="320" t="n"/>
-      <c r="E22" s="320" t="n"/>
-      <c r="F22" s="320" t="n"/>
-      <c r="G22" s="320" t="n"/>
-      <c r="H22" s="320" t="n"/>
-      <c r="I22" s="320" t="n"/>
-      <c r="J22" s="320" t="n"/>
-      <c r="K22" s="320" t="n"/>
-      <c r="L22" s="320" t="n"/>
-      <c r="M22" s="320" t="n"/>
-      <c r="N22" s="320" t="n"/>
-      <c r="O22" s="320" t="n"/>
-      <c r="P22" s="320" t="n"/>
-      <c r="Q22" s="320" t="n"/>
-      <c r="R22" s="320" t="n"/>
-      <c r="S22" s="320" t="n"/>
-      <c r="T22" s="320" t="n"/>
-      <c r="U22" s="320" t="n"/>
-      <c r="V22" s="320" t="n"/>
-      <c r="W22" s="320" t="n"/>
-      <c r="X22" s="320" t="n"/>
-      <c r="Y22" s="320" t="n"/>
-      <c r="Z22" s="320" t="n"/>
-      <c r="AA22" s="320" t="n"/>
-      <c r="AB22" s="320" t="n"/>
-      <c r="AC22" s="320" t="n"/>
-      <c r="AD22" s="320" t="n"/>
-      <c r="AE22" s="320" t="n"/>
-      <c r="AF22" s="320" t="n"/>
-      <c r="AG22" s="320" t="n"/>
-      <c r="AH22" s="320" t="n"/>
-      <c r="AI22" s="320" t="n"/>
-      <c r="AJ22" s="320" t="n"/>
-      <c r="AK22" s="320" t="n"/>
-      <c r="AL22" s="320" t="n"/>
-      <c r="AM22" s="320" t="n"/>
-      <c r="AN22" s="321" t="n"/>
+      <c r="A22" s="357" t="n"/>
+      <c r="B22" s="401" t="n"/>
+      <c r="C22" s="401" t="n"/>
+      <c r="D22" s="401" t="n"/>
+      <c r="E22" s="401" t="n"/>
+      <c r="F22" s="401" t="n"/>
+      <c r="G22" s="401" t="n"/>
+      <c r="H22" s="401" t="n"/>
+      <c r="I22" s="401" t="n"/>
+      <c r="J22" s="401" t="n"/>
+      <c r="K22" s="401" t="n"/>
+      <c r="L22" s="401" t="n"/>
+      <c r="M22" s="401" t="n"/>
+      <c r="N22" s="401" t="n"/>
+      <c r="O22" s="401" t="n"/>
+      <c r="P22" s="401" t="n"/>
+      <c r="Q22" s="401" t="n"/>
+      <c r="R22" s="401" t="n"/>
+      <c r="S22" s="401" t="n"/>
+      <c r="T22" s="401" t="n"/>
+      <c r="U22" s="401" t="n"/>
+      <c r="V22" s="401" t="n"/>
+      <c r="W22" s="401" t="n"/>
+      <c r="X22" s="401" t="n"/>
+      <c r="Y22" s="401" t="n"/>
+      <c r="Z22" s="401" t="n"/>
+      <c r="AA22" s="401" t="n"/>
+      <c r="AB22" s="401" t="n"/>
+      <c r="AC22" s="401" t="n"/>
+      <c r="AD22" s="401" t="n"/>
+      <c r="AE22" s="401" t="n"/>
+      <c r="AF22" s="401" t="n"/>
+      <c r="AG22" s="401" t="n"/>
+      <c r="AH22" s="401" t="n"/>
+      <c r="AI22" s="401" t="n"/>
+      <c r="AJ22" s="401" t="n"/>
+      <c r="AK22" s="401" t="n"/>
+      <c r="AL22" s="401" t="n"/>
+      <c r="AM22" s="401" t="n"/>
+      <c r="AN22" s="402" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="322" t="n"/>
-      <c r="B23" s="322" t="n"/>
-      <c r="C23" s="322" t="n"/>
-      <c r="D23" s="322" t="n"/>
-      <c r="E23" s="322" t="n"/>
-      <c r="F23" s="322" t="n"/>
-      <c r="G23" s="322" t="n"/>
-      <c r="H23" s="322" t="n"/>
-      <c r="I23" s="322" t="n"/>
-      <c r="J23" s="322" t="n"/>
-      <c r="K23" s="322" t="n"/>
-      <c r="L23" s="322" t="n"/>
-      <c r="M23" s="322" t="n"/>
-      <c r="N23" s="322" t="n"/>
-      <c r="O23" s="322" t="n"/>
-      <c r="P23" s="322" t="n"/>
-      <c r="Q23" s="322" t="n"/>
-      <c r="R23" s="322" t="n"/>
-      <c r="S23" s="322" t="n"/>
-      <c r="T23" s="322" t="n"/>
-      <c r="U23" s="322" t="n"/>
-      <c r="V23" s="322" t="n"/>
-      <c r="W23" s="322" t="n"/>
-      <c r="X23" s="322" t="n"/>
-      <c r="Y23" s="322" t="n"/>
-      <c r="Z23" s="322" t="n"/>
-      <c r="AA23" s="322" t="n"/>
-      <c r="AB23" s="322" t="n"/>
-      <c r="AC23" s="322" t="n"/>
-      <c r="AD23" s="322" t="n"/>
-      <c r="AE23" s="322" t="n"/>
-      <c r="AF23" s="322" t="n"/>
-      <c r="AG23" s="322" t="n"/>
-      <c r="AH23" s="322" t="n"/>
-      <c r="AI23" s="322" t="n"/>
-      <c r="AJ23" s="322" t="n"/>
-      <c r="AK23" s="322" t="n"/>
-      <c r="AL23" s="322" t="n"/>
-      <c r="AM23" s="322" t="n"/>
-      <c r="AN23" s="323" t="n"/>
+      <c r="A23" s="403" t="n"/>
+      <c r="B23" s="403" t="n"/>
+      <c r="C23" s="403" t="n"/>
+      <c r="D23" s="403" t="n"/>
+      <c r="E23" s="403" t="n"/>
+      <c r="F23" s="403" t="n"/>
+      <c r="G23" s="403" t="n"/>
+      <c r="H23" s="403" t="n"/>
+      <c r="I23" s="403" t="n"/>
+      <c r="J23" s="403" t="n"/>
+      <c r="K23" s="403" t="n"/>
+      <c r="L23" s="403" t="n"/>
+      <c r="M23" s="403" t="n"/>
+      <c r="N23" s="403" t="n"/>
+      <c r="O23" s="403" t="n"/>
+      <c r="P23" s="403" t="n"/>
+      <c r="Q23" s="403" t="n"/>
+      <c r="R23" s="403" t="n"/>
+      <c r="S23" s="403" t="n"/>
+      <c r="T23" s="403" t="n"/>
+      <c r="U23" s="403" t="n"/>
+      <c r="V23" s="403" t="n"/>
+      <c r="W23" s="403" t="n"/>
+      <c r="X23" s="403" t="n"/>
+      <c r="Y23" s="403" t="n"/>
+      <c r="Z23" s="403" t="n"/>
+      <c r="AA23" s="403" t="n"/>
+      <c r="AB23" s="403" t="n"/>
+      <c r="AC23" s="403" t="n"/>
+      <c r="AD23" s="403" t="n"/>
+      <c r="AE23" s="403" t="n"/>
+      <c r="AF23" s="403" t="n"/>
+      <c r="AG23" s="403" t="n"/>
+      <c r="AH23" s="403" t="n"/>
+      <c r="AI23" s="403" t="n"/>
+      <c r="AJ23" s="403" t="n"/>
+      <c r="AK23" s="403" t="n"/>
+      <c r="AL23" s="403" t="n"/>
+      <c r="AM23" s="403" t="n"/>
+      <c r="AN23" s="404" t="n"/>
     </row>
     <row r="24" ht="4" customHeight="1" s="329">
-      <c r="A24" s="293" t="n"/>
-      <c r="C24" s="294" t="n"/>
-      <c r="F24" s="303" t="n"/>
-      <c r="T24" s="304" t="n"/>
-      <c r="AF24" s="297" t="n"/>
-      <c r="AJ24" s="297" t="n"/>
-      <c r="AM24" s="298" t="n"/>
+      <c r="A24" s="364" t="n"/>
+      <c r="B24" s="352" t="n"/>
+      <c r="C24" s="365" t="n"/>
+      <c r="D24" s="352" t="n"/>
+      <c r="E24" s="352" t="n"/>
+      <c r="F24" s="366" t="n"/>
+      <c r="G24" s="352" t="n"/>
+      <c r="H24" s="352" t="n"/>
+      <c r="I24" s="352" t="n"/>
+      <c r="J24" s="352" t="n"/>
+      <c r="K24" s="352" t="n"/>
+      <c r="L24" s="352" t="n"/>
+      <c r="M24" s="352" t="n"/>
+      <c r="N24" s="352" t="n"/>
+      <c r="O24" s="352" t="n"/>
+      <c r="P24" s="352" t="n"/>
+      <c r="Q24" s="352" t="n"/>
+      <c r="R24" s="352" t="n"/>
+      <c r="S24" s="352" t="n"/>
+      <c r="T24" s="367" t="n"/>
+      <c r="U24" s="352" t="n"/>
+      <c r="V24" s="352" t="n"/>
+      <c r="W24" s="352" t="n"/>
+      <c r="X24" s="352" t="n"/>
+      <c r="Y24" s="352" t="n"/>
+      <c r="Z24" s="352" t="n"/>
+      <c r="AA24" s="352" t="n"/>
+      <c r="AB24" s="352" t="n"/>
+      <c r="AC24" s="352" t="n"/>
+      <c r="AD24" s="352" t="n"/>
+      <c r="AE24" s="352" t="n"/>
+      <c r="AF24" s="368" t="n"/>
+      <c r="AG24" s="352" t="n"/>
+      <c r="AH24" s="352" t="n"/>
+      <c r="AI24" s="352" t="n"/>
+      <c r="AJ24" s="368" t="n"/>
+      <c r="AK24" s="352" t="n"/>
+      <c r="AL24" s="352" t="n"/>
+      <c r="AM24" s="369" t="n"/>
+      <c r="AN24" s="352" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1" s="329">
-      <c r="A25" s="284" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="329">
+      <c r="A25" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
         </is>
       </c>
-      <c r="B25" s="285" t="n"/>
-      <c r="C25" s="285" t="n"/>
-      <c r="D25" s="285" t="n"/>
-      <c r="E25" s="285" t="n"/>
-      <c r="F25" s="285" t="n"/>
-      <c r="G25" s="285" t="n"/>
-      <c r="H25" s="285" t="n"/>
-      <c r="I25" s="285" t="n"/>
-      <c r="J25" s="285" t="n"/>
-      <c r="K25" s="285" t="n"/>
-      <c r="L25" s="285" t="n"/>
-      <c r="M25" s="285" t="n"/>
-      <c r="N25" s="285" t="n"/>
-      <c r="O25" s="285" t="n"/>
-      <c r="P25" s="285" t="n"/>
-      <c r="Q25" s="285" t="n"/>
-      <c r="R25" s="285" t="n"/>
-      <c r="S25" s="285" t="n"/>
-      <c r="T25" s="285" t="n"/>
-      <c r="U25" s="285" t="n"/>
-      <c r="V25" s="285" t="n"/>
-      <c r="W25" s="285" t="n"/>
-      <c r="X25" s="285" t="n"/>
-      <c r="Y25" s="285" t="n"/>
-      <c r="Z25" s="285" t="n"/>
-      <c r="AA25" s="285" t="n"/>
-      <c r="AB25" s="285" t="n"/>
-      <c r="AC25" s="285" t="n"/>
-      <c r="AD25" s="285" t="n"/>
-      <c r="AE25" s="285" t="n"/>
-      <c r="AF25" s="285" t="n"/>
-      <c r="AG25" s="285" t="n"/>
-      <c r="AH25" s="285" t="n"/>
-      <c r="AI25" s="285" t="n"/>
-      <c r="AJ25" s="285" t="n"/>
-      <c r="AK25" s="285" t="n"/>
-      <c r="AL25" s="285" t="n"/>
-      <c r="AM25" s="285" t="n"/>
-      <c r="AN25" s="286" t="n"/>
+      <c r="B25" s="399" t="n"/>
+      <c r="C25" s="399" t="n"/>
+      <c r="D25" s="399" t="n"/>
+      <c r="E25" s="399" t="n"/>
+      <c r="F25" s="399" t="n"/>
+      <c r="G25" s="399" t="n"/>
+      <c r="H25" s="399" t="n"/>
+      <c r="I25" s="399" t="n"/>
+      <c r="J25" s="399" t="n"/>
+      <c r="K25" s="399" t="n"/>
+      <c r="L25" s="399" t="n"/>
+      <c r="M25" s="399" t="n"/>
+      <c r="N25" s="399" t="n"/>
+      <c r="O25" s="399" t="n"/>
+      <c r="P25" s="399" t="n"/>
+      <c r="Q25" s="399" t="n"/>
+      <c r="R25" s="399" t="n"/>
+      <c r="S25" s="399" t="n"/>
+      <c r="T25" s="399" t="n"/>
+      <c r="U25" s="399" t="n"/>
+      <c r="V25" s="399" t="n"/>
+      <c r="W25" s="399" t="n"/>
+      <c r="X25" s="399" t="n"/>
+      <c r="Y25" s="399" t="n"/>
+      <c r="Z25" s="399" t="n"/>
+      <c r="AA25" s="399" t="n"/>
+      <c r="AB25" s="399" t="n"/>
+      <c r="AC25" s="399" t="n"/>
+      <c r="AD25" s="399" t="n"/>
+      <c r="AE25" s="399" t="n"/>
+      <c r="AF25" s="399" t="n"/>
+      <c r="AG25" s="399" t="n"/>
+      <c r="AH25" s="399" t="n"/>
+      <c r="AI25" s="399" t="n"/>
+      <c r="AJ25" s="399" t="n"/>
+      <c r="AK25" s="399" t="n"/>
+      <c r="AL25" s="399" t="n"/>
+      <c r="AM25" s="399" t="n"/>
+      <c r="AN25" s="400" t="n"/>
     </row>
-    <row r="26" ht="17" customHeight="1" s="329">
-      <c r="A26" s="299" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="329">
+      <c r="A26" s="370" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="318" t="n"/>
-      <c r="C26" s="300" t="inlineStr">
+      <c r="B26" s="400" t="n"/>
+      <c r="C26" s="371" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="317" t="n"/>
-      <c r="E26" s="318" t="n"/>
-      <c r="F26" s="300" t="inlineStr">
+      <c r="D26" s="399" t="n"/>
+      <c r="E26" s="400" t="n"/>
+      <c r="F26" s="371" t="inlineStr">
         <is>
           <t>Requirement / Check</t>
         </is>
       </c>
-      <c r="G26" s="317" t="n"/>
-      <c r="H26" s="317" t="n"/>
-      <c r="I26" s="317" t="n"/>
-      <c r="J26" s="317" t="n"/>
-      <c r="K26" s="317" t="n"/>
-      <c r="L26" s="317" t="n"/>
-      <c r="M26" s="317" t="n"/>
-      <c r="N26" s="317" t="n"/>
-      <c r="O26" s="317" t="n"/>
-      <c r="P26" s="317" t="n"/>
-      <c r="Q26" s="317" t="n"/>
-      <c r="R26" s="317" t="n"/>
-      <c r="S26" s="318" t="n"/>
-      <c r="T26" s="300" t="inlineStr">
+      <c r="G26" s="399" t="n"/>
+      <c r="H26" s="399" t="n"/>
+      <c r="I26" s="399" t="n"/>
+      <c r="J26" s="399" t="n"/>
+      <c r="K26" s="399" t="n"/>
+      <c r="L26" s="399" t="n"/>
+      <c r="M26" s="399" t="n"/>
+      <c r="N26" s="399" t="n"/>
+      <c r="O26" s="399" t="n"/>
+      <c r="P26" s="399" t="n"/>
+      <c r="Q26" s="399" t="n"/>
+      <c r="R26" s="399" t="n"/>
+      <c r="S26" s="400" t="n"/>
+      <c r="T26" s="371" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="317" t="n"/>
-      <c r="V26" s="317" t="n"/>
-      <c r="W26" s="317" t="n"/>
-      <c r="X26" s="317" t="n"/>
-      <c r="Y26" s="317" t="n"/>
-      <c r="Z26" s="317" t="n"/>
-      <c r="AA26" s="317" t="n"/>
-      <c r="AB26" s="317" t="n"/>
-      <c r="AC26" s="317" t="n"/>
-      <c r="AD26" s="317" t="n"/>
-      <c r="AE26" s="318" t="n"/>
-      <c r="AF26" s="300" t="inlineStr">
+      <c r="U26" s="399" t="n"/>
+      <c r="V26" s="399" t="n"/>
+      <c r="W26" s="399" t="n"/>
+      <c r="X26" s="399" t="n"/>
+      <c r="Y26" s="399" t="n"/>
+      <c r="Z26" s="399" t="n"/>
+      <c r="AA26" s="399" t="n"/>
+      <c r="AB26" s="399" t="n"/>
+      <c r="AC26" s="399" t="n"/>
+      <c r="AD26" s="399" t="n"/>
+      <c r="AE26" s="400" t="n"/>
+      <c r="AF26" s="371" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="317" t="n"/>
-      <c r="AH26" s="317" t="n"/>
-      <c r="AI26" s="318" t="n"/>
-      <c r="AJ26" s="300" t="inlineStr">
+      <c r="AG26" s="399" t="n"/>
+      <c r="AH26" s="399" t="n"/>
+      <c r="AI26" s="400" t="n"/>
+      <c r="AJ26" s="371" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="317" t="n"/>
-      <c r="AL26" s="318" t="n"/>
-      <c r="AM26" s="301" t="inlineStr">
+      <c r="AK26" s="399" t="n"/>
+      <c r="AL26" s="400" t="n"/>
+      <c r="AM26" s="371" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="319" t="n"/>
+      <c r="AN26" s="400" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="293">
+      <c r="A27" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="323" t="n"/>
-      <c r="C27" s="302" t="inlineStr">
+      <c r="B27" s="404" t="n"/>
+      <c r="C27" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="322" t="n"/>
-      <c r="E27" s="323" t="n"/>
-      <c r="F27" s="303" t="n"/>
-      <c r="G27" s="322" t="n"/>
-      <c r="H27" s="322" t="n"/>
-      <c r="I27" s="322" t="n"/>
-      <c r="J27" s="322" t="n"/>
-      <c r="K27" s="322" t="n"/>
-      <c r="L27" s="322" t="n"/>
-      <c r="M27" s="322" t="n"/>
-      <c r="N27" s="322" t="n"/>
-      <c r="O27" s="322" t="n"/>
-      <c r="P27" s="322" t="n"/>
-      <c r="Q27" s="322" t="n"/>
-      <c r="R27" s="322" t="n"/>
-      <c r="S27" s="323" t="n"/>
-      <c r="T27" s="304" t="n"/>
-      <c r="U27" s="322" t="n"/>
-      <c r="V27" s="322" t="n"/>
-      <c r="W27" s="322" t="n"/>
-      <c r="X27" s="322" t="n"/>
-      <c r="Y27" s="322" t="n"/>
-      <c r="Z27" s="322" t="n"/>
-      <c r="AA27" s="322" t="n"/>
-      <c r="AB27" s="322" t="n"/>
-      <c r="AC27" s="322" t="n"/>
-      <c r="AD27" s="322" t="n"/>
-      <c r="AE27" s="323" t="n"/>
-      <c r="AF27" s="303" t="n"/>
-      <c r="AG27" s="322" t="n"/>
-      <c r="AH27" s="322" t="n"/>
-      <c r="AI27" s="323" t="n"/>
-      <c r="AJ27" s="303" t="n"/>
-      <c r="AK27" s="322" t="n"/>
-      <c r="AL27" s="323" t="n"/>
-      <c r="AM27" s="305" t="n"/>
-      <c r="AN27" s="324" t="n"/>
+      <c r="D27" s="403" t="n"/>
+      <c r="E27" s="404" t="n"/>
+      <c r="F27" s="374" t="n"/>
+      <c r="G27" s="403" t="n"/>
+      <c r="H27" s="403" t="n"/>
+      <c r="I27" s="403" t="n"/>
+      <c r="J27" s="403" t="n"/>
+      <c r="K27" s="403" t="n"/>
+      <c r="L27" s="403" t="n"/>
+      <c r="M27" s="403" t="n"/>
+      <c r="N27" s="403" t="n"/>
+      <c r="O27" s="403" t="n"/>
+      <c r="P27" s="403" t="n"/>
+      <c r="Q27" s="403" t="n"/>
+      <c r="R27" s="403" t="n"/>
+      <c r="S27" s="404" t="n"/>
+      <c r="T27" s="375" t="n"/>
+      <c r="U27" s="403" t="n"/>
+      <c r="V27" s="403" t="n"/>
+      <c r="W27" s="403" t="n"/>
+      <c r="X27" s="403" t="n"/>
+      <c r="Y27" s="403" t="n"/>
+      <c r="Z27" s="403" t="n"/>
+      <c r="AA27" s="403" t="n"/>
+      <c r="AB27" s="403" t="n"/>
+      <c r="AC27" s="403" t="n"/>
+      <c r="AD27" s="403" t="n"/>
+      <c r="AE27" s="404" t="n"/>
+      <c r="AF27" s="374" t="n"/>
+      <c r="AG27" s="403" t="n"/>
+      <c r="AH27" s="403" t="n"/>
+      <c r="AI27" s="404" t="n"/>
+      <c r="AJ27" s="374" t="n"/>
+      <c r="AK27" s="403" t="n"/>
+      <c r="AL27" s="404" t="n"/>
+      <c r="AM27" s="376" t="n"/>
+      <c r="AN27" s="404" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="293">
+      <c r="A28" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="323" t="n"/>
-      <c r="C28" s="302" t="inlineStr">
+      <c r="B28" s="404" t="n"/>
+      <c r="C28" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="322" t="n"/>
-      <c r="E28" s="323" t="n"/>
-      <c r="F28" s="303" t="n"/>
-      <c r="G28" s="322" t="n"/>
-      <c r="H28" s="322" t="n"/>
-      <c r="I28" s="322" t="n"/>
-      <c r="J28" s="322" t="n"/>
-      <c r="K28" s="322" t="n"/>
-      <c r="L28" s="322" t="n"/>
-      <c r="M28" s="322" t="n"/>
-      <c r="N28" s="322" t="n"/>
-      <c r="O28" s="322" t="n"/>
-      <c r="P28" s="322" t="n"/>
-      <c r="Q28" s="322" t="n"/>
-      <c r="R28" s="322" t="n"/>
-      <c r="S28" s="323" t="n"/>
-      <c r="T28" s="304" t="n"/>
-      <c r="U28" s="322" t="n"/>
-      <c r="V28" s="322" t="n"/>
-      <c r="W28" s="322" t="n"/>
-      <c r="X28" s="322" t="n"/>
-      <c r="Y28" s="322" t="n"/>
-      <c r="Z28" s="322" t="n"/>
-      <c r="AA28" s="322" t="n"/>
-      <c r="AB28" s="322" t="n"/>
-      <c r="AC28" s="322" t="n"/>
-      <c r="AD28" s="322" t="n"/>
-      <c r="AE28" s="323" t="n"/>
-      <c r="AF28" s="303" t="n"/>
-      <c r="AG28" s="322" t="n"/>
-      <c r="AH28" s="322" t="n"/>
-      <c r="AI28" s="323" t="n"/>
-      <c r="AJ28" s="303" t="n"/>
-      <c r="AK28" s="322" t="n"/>
-      <c r="AL28" s="323" t="n"/>
-      <c r="AM28" s="305" t="n"/>
-      <c r="AN28" s="324" t="n"/>
+      <c r="D28" s="403" t="n"/>
+      <c r="E28" s="404" t="n"/>
+      <c r="F28" s="374" t="n"/>
+      <c r="G28" s="403" t="n"/>
+      <c r="H28" s="403" t="n"/>
+      <c r="I28" s="403" t="n"/>
+      <c r="J28" s="403" t="n"/>
+      <c r="K28" s="403" t="n"/>
+      <c r="L28" s="403" t="n"/>
+      <c r="M28" s="403" t="n"/>
+      <c r="N28" s="403" t="n"/>
+      <c r="O28" s="403" t="n"/>
+      <c r="P28" s="403" t="n"/>
+      <c r="Q28" s="403" t="n"/>
+      <c r="R28" s="403" t="n"/>
+      <c r="S28" s="404" t="n"/>
+      <c r="T28" s="375" t="n"/>
+      <c r="U28" s="403" t="n"/>
+      <c r="V28" s="403" t="n"/>
+      <c r="W28" s="403" t="n"/>
+      <c r="X28" s="403" t="n"/>
+      <c r="Y28" s="403" t="n"/>
+      <c r="Z28" s="403" t="n"/>
+      <c r="AA28" s="403" t="n"/>
+      <c r="AB28" s="403" t="n"/>
+      <c r="AC28" s="403" t="n"/>
+      <c r="AD28" s="403" t="n"/>
+      <c r="AE28" s="404" t="n"/>
+      <c r="AF28" s="374" t="n"/>
+      <c r="AG28" s="403" t="n"/>
+      <c r="AH28" s="403" t="n"/>
+      <c r="AI28" s="404" t="n"/>
+      <c r="AJ28" s="374" t="n"/>
+      <c r="AK28" s="403" t="n"/>
+      <c r="AL28" s="404" t="n"/>
+      <c r="AM28" s="376" t="n"/>
+      <c r="AN28" s="404" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="293">
+      <c r="A29" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="323" t="n"/>
-      <c r="C29" s="302" t="inlineStr">
+      <c r="B29" s="404" t="n"/>
+      <c r="C29" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="322" t="n"/>
-      <c r="E29" s="323" t="n"/>
-      <c r="F29" s="303" t="n"/>
-      <c r="G29" s="322" t="n"/>
-      <c r="H29" s="322" t="n"/>
-      <c r="I29" s="322" t="n"/>
-      <c r="J29" s="322" t="n"/>
-      <c r="K29" s="322" t="n"/>
-      <c r="L29" s="322" t="n"/>
-      <c r="M29" s="322" t="n"/>
-      <c r="N29" s="322" t="n"/>
-      <c r="O29" s="322" t="n"/>
-      <c r="P29" s="322" t="n"/>
-      <c r="Q29" s="322" t="n"/>
-      <c r="R29" s="322" t="n"/>
-      <c r="S29" s="323" t="n"/>
-      <c r="T29" s="304" t="n"/>
-      <c r="U29" s="322" t="n"/>
-      <c r="V29" s="322" t="n"/>
-      <c r="W29" s="322" t="n"/>
-      <c r="X29" s="322" t="n"/>
-      <c r="Y29" s="322" t="n"/>
-      <c r="Z29" s="322" t="n"/>
-      <c r="AA29" s="322" t="n"/>
-      <c r="AB29" s="322" t="n"/>
-      <c r="AC29" s="322" t="n"/>
-      <c r="AD29" s="322" t="n"/>
-      <c r="AE29" s="323" t="n"/>
-      <c r="AF29" s="303" t="n"/>
-      <c r="AG29" s="322" t="n"/>
-      <c r="AH29" s="322" t="n"/>
-      <c r="AI29" s="323" t="n"/>
-      <c r="AJ29" s="303" t="n"/>
-      <c r="AK29" s="322" t="n"/>
-      <c r="AL29" s="323" t="n"/>
-      <c r="AM29" s="305" t="n"/>
-      <c r="AN29" s="324" t="n"/>
+      <c r="D29" s="403" t="n"/>
+      <c r="E29" s="404" t="n"/>
+      <c r="F29" s="374" t="n"/>
+      <c r="G29" s="403" t="n"/>
+      <c r="H29" s="403" t="n"/>
+      <c r="I29" s="403" t="n"/>
+      <c r="J29" s="403" t="n"/>
+      <c r="K29" s="403" t="n"/>
+      <c r="L29" s="403" t="n"/>
+      <c r="M29" s="403" t="n"/>
+      <c r="N29" s="403" t="n"/>
+      <c r="O29" s="403" t="n"/>
+      <c r="P29" s="403" t="n"/>
+      <c r="Q29" s="403" t="n"/>
+      <c r="R29" s="403" t="n"/>
+      <c r="S29" s="404" t="n"/>
+      <c r="T29" s="375" t="n"/>
+      <c r="U29" s="403" t="n"/>
+      <c r="V29" s="403" t="n"/>
+      <c r="W29" s="403" t="n"/>
+      <c r="X29" s="403" t="n"/>
+      <c r="Y29" s="403" t="n"/>
+      <c r="Z29" s="403" t="n"/>
+      <c r="AA29" s="403" t="n"/>
+      <c r="AB29" s="403" t="n"/>
+      <c r="AC29" s="403" t="n"/>
+      <c r="AD29" s="403" t="n"/>
+      <c r="AE29" s="404" t="n"/>
+      <c r="AF29" s="374" t="n"/>
+      <c r="AG29" s="403" t="n"/>
+      <c r="AH29" s="403" t="n"/>
+      <c r="AI29" s="404" t="n"/>
+      <c r="AJ29" s="374" t="n"/>
+      <c r="AK29" s="403" t="n"/>
+      <c r="AL29" s="404" t="n"/>
+      <c r="AM29" s="376" t="n"/>
+      <c r="AN29" s="404" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="293">
+      <c r="A30" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="323" t="n"/>
-      <c r="C30" s="302" t="inlineStr">
+      <c r="B30" s="404" t="n"/>
+      <c r="C30" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="322" t="n"/>
-      <c r="E30" s="323" t="n"/>
-      <c r="F30" s="303" t="n"/>
-      <c r="G30" s="322" t="n"/>
-      <c r="H30" s="322" t="n"/>
-      <c r="I30" s="322" t="n"/>
-      <c r="J30" s="322" t="n"/>
-      <c r="K30" s="322" t="n"/>
-      <c r="L30" s="322" t="n"/>
-      <c r="M30" s="322" t="n"/>
-      <c r="N30" s="322" t="n"/>
-      <c r="O30" s="322" t="n"/>
-      <c r="P30" s="322" t="n"/>
-      <c r="Q30" s="322" t="n"/>
-      <c r="R30" s="322" t="n"/>
-      <c r="S30" s="323" t="n"/>
-      <c r="T30" s="304" t="n"/>
-      <c r="U30" s="322" t="n"/>
-      <c r="V30" s="322" t="n"/>
-      <c r="W30" s="322" t="n"/>
-      <c r="X30" s="322" t="n"/>
-      <c r="Y30" s="322" t="n"/>
-      <c r="Z30" s="322" t="n"/>
-      <c r="AA30" s="322" t="n"/>
-      <c r="AB30" s="322" t="n"/>
-      <c r="AC30" s="322" t="n"/>
-      <c r="AD30" s="322" t="n"/>
-      <c r="AE30" s="323" t="n"/>
-      <c r="AF30" s="303" t="n"/>
-      <c r="AG30" s="322" t="n"/>
-      <c r="AH30" s="322" t="n"/>
-      <c r="AI30" s="323" t="n"/>
-      <c r="AJ30" s="303" t="n"/>
-      <c r="AK30" s="322" t="n"/>
-      <c r="AL30" s="323" t="n"/>
-      <c r="AM30" s="305" t="n"/>
-      <c r="AN30" s="324" t="n"/>
+      <c r="D30" s="403" t="n"/>
+      <c r="E30" s="404" t="n"/>
+      <c r="F30" s="374" t="n"/>
+      <c r="G30" s="403" t="n"/>
+      <c r="H30" s="403" t="n"/>
+      <c r="I30" s="403" t="n"/>
+      <c r="J30" s="403" t="n"/>
+      <c r="K30" s="403" t="n"/>
+      <c r="L30" s="403" t="n"/>
+      <c r="M30" s="403" t="n"/>
+      <c r="N30" s="403" t="n"/>
+      <c r="O30" s="403" t="n"/>
+      <c r="P30" s="403" t="n"/>
+      <c r="Q30" s="403" t="n"/>
+      <c r="R30" s="403" t="n"/>
+      <c r="S30" s="404" t="n"/>
+      <c r="T30" s="375" t="n"/>
+      <c r="U30" s="403" t="n"/>
+      <c r="V30" s="403" t="n"/>
+      <c r="W30" s="403" t="n"/>
+      <c r="X30" s="403" t="n"/>
+      <c r="Y30" s="403" t="n"/>
+      <c r="Z30" s="403" t="n"/>
+      <c r="AA30" s="403" t="n"/>
+      <c r="AB30" s="403" t="n"/>
+      <c r="AC30" s="403" t="n"/>
+      <c r="AD30" s="403" t="n"/>
+      <c r="AE30" s="404" t="n"/>
+      <c r="AF30" s="374" t="n"/>
+      <c r="AG30" s="403" t="n"/>
+      <c r="AH30" s="403" t="n"/>
+      <c r="AI30" s="404" t="n"/>
+      <c r="AJ30" s="374" t="n"/>
+      <c r="AK30" s="403" t="n"/>
+      <c r="AL30" s="404" t="n"/>
+      <c r="AM30" s="376" t="n"/>
+      <c r="AN30" s="404" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="293">
+      <c r="A31" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="323" t="n"/>
-      <c r="C31" s="302" t="inlineStr">
+      <c r="B31" s="404" t="n"/>
+      <c r="C31" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="322" t="n"/>
-      <c r="E31" s="323" t="n"/>
-      <c r="F31" s="303" t="n"/>
-      <c r="G31" s="322" t="n"/>
-      <c r="H31" s="322" t="n"/>
-      <c r="I31" s="322" t="n"/>
-      <c r="J31" s="322" t="n"/>
-      <c r="K31" s="322" t="n"/>
-      <c r="L31" s="322" t="n"/>
-      <c r="M31" s="322" t="n"/>
-      <c r="N31" s="322" t="n"/>
-      <c r="O31" s="322" t="n"/>
-      <c r="P31" s="322" t="n"/>
-      <c r="Q31" s="322" t="n"/>
-      <c r="R31" s="322" t="n"/>
-      <c r="S31" s="323" t="n"/>
-      <c r="T31" s="304" t="n"/>
-      <c r="U31" s="322" t="n"/>
-      <c r="V31" s="322" t="n"/>
-      <c r="W31" s="322" t="n"/>
-      <c r="X31" s="322" t="n"/>
-      <c r="Y31" s="322" t="n"/>
-      <c r="Z31" s="322" t="n"/>
-      <c r="AA31" s="322" t="n"/>
-      <c r="AB31" s="322" t="n"/>
-      <c r="AC31" s="322" t="n"/>
-      <c r="AD31" s="322" t="n"/>
-      <c r="AE31" s="323" t="n"/>
-      <c r="AF31" s="303" t="n"/>
-      <c r="AG31" s="322" t="n"/>
-      <c r="AH31" s="322" t="n"/>
-      <c r="AI31" s="323" t="n"/>
-      <c r="AJ31" s="303" t="n"/>
-      <c r="AK31" s="322" t="n"/>
-      <c r="AL31" s="323" t="n"/>
-      <c r="AM31" s="305" t="n"/>
-      <c r="AN31" s="324" t="n"/>
+      <c r="D31" s="403" t="n"/>
+      <c r="E31" s="404" t="n"/>
+      <c r="F31" s="374" t="n"/>
+      <c r="G31" s="403" t="n"/>
+      <c r="H31" s="403" t="n"/>
+      <c r="I31" s="403" t="n"/>
+      <c r="J31" s="403" t="n"/>
+      <c r="K31" s="403" t="n"/>
+      <c r="L31" s="403" t="n"/>
+      <c r="M31" s="403" t="n"/>
+      <c r="N31" s="403" t="n"/>
+      <c r="O31" s="403" t="n"/>
+      <c r="P31" s="403" t="n"/>
+      <c r="Q31" s="403" t="n"/>
+      <c r="R31" s="403" t="n"/>
+      <c r="S31" s="404" t="n"/>
+      <c r="T31" s="375" t="n"/>
+      <c r="U31" s="403" t="n"/>
+      <c r="V31" s="403" t="n"/>
+      <c r="W31" s="403" t="n"/>
+      <c r="X31" s="403" t="n"/>
+      <c r="Y31" s="403" t="n"/>
+      <c r="Z31" s="403" t="n"/>
+      <c r="AA31" s="403" t="n"/>
+      <c r="AB31" s="403" t="n"/>
+      <c r="AC31" s="403" t="n"/>
+      <c r="AD31" s="403" t="n"/>
+      <c r="AE31" s="404" t="n"/>
+      <c r="AF31" s="374" t="n"/>
+      <c r="AG31" s="403" t="n"/>
+      <c r="AH31" s="403" t="n"/>
+      <c r="AI31" s="404" t="n"/>
+      <c r="AJ31" s="374" t="n"/>
+      <c r="AK31" s="403" t="n"/>
+      <c r="AL31" s="404" t="n"/>
+      <c r="AM31" s="376" t="n"/>
+      <c r="AN31" s="404" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="293">
+      <c r="A32" s="372">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="323" t="n"/>
-      <c r="C32" s="302" t="inlineStr">
+      <c r="B32" s="404" t="n"/>
+      <c r="C32" s="373" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="322" t="n"/>
-      <c r="E32" s="323" t="n"/>
-      <c r="F32" s="303" t="n"/>
-      <c r="G32" s="322" t="n"/>
-      <c r="H32" s="322" t="n"/>
-      <c r="I32" s="322" t="n"/>
-      <c r="J32" s="322" t="n"/>
-      <c r="K32" s="322" t="n"/>
-      <c r="L32" s="322" t="n"/>
-      <c r="M32" s="322" t="n"/>
-      <c r="N32" s="322" t="n"/>
-      <c r="O32" s="322" t="n"/>
-      <c r="P32" s="322" t="n"/>
-      <c r="Q32" s="322" t="n"/>
-      <c r="R32" s="322" t="n"/>
-      <c r="S32" s="323" t="n"/>
-      <c r="T32" s="304" t="n"/>
-      <c r="U32" s="322" t="n"/>
-      <c r="V32" s="322" t="n"/>
-      <c r="W32" s="322" t="n"/>
-      <c r="X32" s="322" t="n"/>
-      <c r="Y32" s="322" t="n"/>
-      <c r="Z32" s="322" t="n"/>
-      <c r="AA32" s="322" t="n"/>
-      <c r="AB32" s="322" t="n"/>
-      <c r="AC32" s="322" t="n"/>
-      <c r="AD32" s="322" t="n"/>
-      <c r="AE32" s="323" t="n"/>
-      <c r="AF32" s="303" t="n"/>
-      <c r="AG32" s="322" t="n"/>
-      <c r="AH32" s="322" t="n"/>
-      <c r="AI32" s="323" t="n"/>
-      <c r="AJ32" s="303" t="n"/>
-      <c r="AK32" s="322" t="n"/>
-      <c r="AL32" s="323" t="n"/>
-      <c r="AM32" s="305" t="n"/>
-      <c r="AN32" s="324" t="n"/>
+      <c r="D32" s="403" t="n"/>
+      <c r="E32" s="404" t="n"/>
+      <c r="F32" s="374" t="n"/>
+      <c r="G32" s="403" t="n"/>
+      <c r="H32" s="403" t="n"/>
+      <c r="I32" s="403" t="n"/>
+      <c r="J32" s="403" t="n"/>
+      <c r="K32" s="403" t="n"/>
+      <c r="L32" s="403" t="n"/>
+      <c r="M32" s="403" t="n"/>
+      <c r="N32" s="403" t="n"/>
+      <c r="O32" s="403" t="n"/>
+      <c r="P32" s="403" t="n"/>
+      <c r="Q32" s="403" t="n"/>
+      <c r="R32" s="403" t="n"/>
+      <c r="S32" s="404" t="n"/>
+      <c r="T32" s="375" t="n"/>
+      <c r="U32" s="403" t="n"/>
+      <c r="V32" s="403" t="n"/>
+      <c r="W32" s="403" t="n"/>
+      <c r="X32" s="403" t="n"/>
+      <c r="Y32" s="403" t="n"/>
+      <c r="Z32" s="403" t="n"/>
+      <c r="AA32" s="403" t="n"/>
+      <c r="AB32" s="403" t="n"/>
+      <c r="AC32" s="403" t="n"/>
+      <c r="AD32" s="403" t="n"/>
+      <c r="AE32" s="404" t="n"/>
+      <c r="AF32" s="374" t="n"/>
+      <c r="AG32" s="403" t="n"/>
+      <c r="AH32" s="403" t="n"/>
+      <c r="AI32" s="404" t="n"/>
+      <c r="AJ32" s="374" t="n"/>
+      <c r="AK32" s="403" t="n"/>
+      <c r="AL32" s="404" t="n"/>
+      <c r="AM32" s="376" t="n"/>
+      <c r="AN32" s="404" t="n"/>
     </row>
     <row r="33" ht="4" customHeight="1" s="329">
-      <c r="A33" s="284" t="n"/>
+      <c r="A33" s="359" t="n"/>
+      <c r="B33" s="352" t="n"/>
+      <c r="C33" s="352" t="n"/>
+      <c r="D33" s="352" t="n"/>
+      <c r="E33" s="352" t="n"/>
+      <c r="F33" s="352" t="n"/>
+      <c r="G33" s="352" t="n"/>
+      <c r="H33" s="352" t="n"/>
+      <c r="I33" s="352" t="n"/>
+      <c r="J33" s="352" t="n"/>
+      <c r="K33" s="352" t="n"/>
+      <c r="L33" s="352" t="n"/>
+      <c r="M33" s="352" t="n"/>
+      <c r="N33" s="352" t="n"/>
+      <c r="O33" s="352" t="n"/>
+      <c r="P33" s="352" t="n"/>
+      <c r="Q33" s="352" t="n"/>
+      <c r="R33" s="352" t="n"/>
+      <c r="S33" s="352" t="n"/>
+      <c r="T33" s="352" t="n"/>
+      <c r="U33" s="352" t="n"/>
+      <c r="V33" s="352" t="n"/>
+      <c r="W33" s="352" t="n"/>
+      <c r="X33" s="352" t="n"/>
+      <c r="Y33" s="352" t="n"/>
+      <c r="Z33" s="352" t="n"/>
+      <c r="AA33" s="352" t="n"/>
+      <c r="AB33" s="352" t="n"/>
+      <c r="AC33" s="352" t="n"/>
+      <c r="AD33" s="352" t="n"/>
+      <c r="AE33" s="352" t="n"/>
+      <c r="AF33" s="352" t="n"/>
+      <c r="AG33" s="352" t="n"/>
+      <c r="AH33" s="352" t="n"/>
+      <c r="AI33" s="352" t="n"/>
+      <c r="AJ33" s="352" t="n"/>
+      <c r="AK33" s="352" t="n"/>
+      <c r="AL33" s="352" t="n"/>
+      <c r="AM33" s="352" t="n"/>
+      <c r="AN33" s="352" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1" s="329">
-      <c r="A34" s="284" t="inlineStr">
+    <row r="34" ht="20" customHeight="1" s="329">
+      <c r="A34" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="285" t="n"/>
-      <c r="C34" s="285" t="n"/>
-      <c r="D34" s="285" t="n"/>
-      <c r="E34" s="285" t="n"/>
-      <c r="F34" s="285" t="n"/>
-      <c r="G34" s="285" t="n"/>
-      <c r="H34" s="285" t="n"/>
-      <c r="I34" s="285" t="n"/>
-      <c r="J34" s="285" t="n"/>
-      <c r="K34" s="285" t="n"/>
-      <c r="L34" s="285" t="n"/>
-      <c r="M34" s="285" t="n"/>
-      <c r="N34" s="285" t="n"/>
-      <c r="O34" s="285" t="n"/>
-      <c r="P34" s="285" t="n"/>
-      <c r="Q34" s="285" t="n"/>
-      <c r="R34" s="285" t="n"/>
-      <c r="S34" s="285" t="n"/>
-      <c r="T34" s="285" t="n"/>
-      <c r="U34" s="285" t="n"/>
-      <c r="V34" s="285" t="n"/>
-      <c r="W34" s="285" t="n"/>
-      <c r="X34" s="285" t="n"/>
-      <c r="Y34" s="285" t="n"/>
-      <c r="Z34" s="285" t="n"/>
-      <c r="AA34" s="285" t="n"/>
-      <c r="AB34" s="285" t="n"/>
-      <c r="AC34" s="285" t="n"/>
-      <c r="AD34" s="285" t="n"/>
-      <c r="AE34" s="285" t="n"/>
-      <c r="AF34" s="285" t="n"/>
-      <c r="AG34" s="285" t="n"/>
-      <c r="AH34" s="285" t="n"/>
-      <c r="AI34" s="285" t="n"/>
-      <c r="AJ34" s="285" t="n"/>
-      <c r="AK34" s="285" t="n"/>
-      <c r="AL34" s="285" t="n"/>
-      <c r="AM34" s="285" t="n"/>
-      <c r="AN34" s="286" t="n"/>
+      <c r="B34" s="399" t="n"/>
+      <c r="C34" s="399" t="n"/>
+      <c r="D34" s="399" t="n"/>
+      <c r="E34" s="399" t="n"/>
+      <c r="F34" s="399" t="n"/>
+      <c r="G34" s="399" t="n"/>
+      <c r="H34" s="399" t="n"/>
+      <c r="I34" s="399" t="n"/>
+      <c r="J34" s="399" t="n"/>
+      <c r="K34" s="399" t="n"/>
+      <c r="L34" s="399" t="n"/>
+      <c r="M34" s="399" t="n"/>
+      <c r="N34" s="399" t="n"/>
+      <c r="O34" s="399" t="n"/>
+      <c r="P34" s="399" t="n"/>
+      <c r="Q34" s="399" t="n"/>
+      <c r="R34" s="399" t="n"/>
+      <c r="S34" s="399" t="n"/>
+      <c r="T34" s="399" t="n"/>
+      <c r="U34" s="399" t="n"/>
+      <c r="V34" s="399" t="n"/>
+      <c r="W34" s="399" t="n"/>
+      <c r="X34" s="399" t="n"/>
+      <c r="Y34" s="399" t="n"/>
+      <c r="Z34" s="399" t="n"/>
+      <c r="AA34" s="399" t="n"/>
+      <c r="AB34" s="399" t="n"/>
+      <c r="AC34" s="399" t="n"/>
+      <c r="AD34" s="399" t="n"/>
+      <c r="AE34" s="399" t="n"/>
+      <c r="AF34" s="399" t="n"/>
+      <c r="AG34" s="399" t="n"/>
+      <c r="AH34" s="399" t="n"/>
+      <c r="AI34" s="399" t="n"/>
+      <c r="AJ34" s="399" t="n"/>
+      <c r="AK34" s="399" t="n"/>
+      <c r="AL34" s="399" t="n"/>
+      <c r="AM34" s="399" t="n"/>
+      <c r="AN34" s="400" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="287" t="inlineStr">
+      <c r="A35" s="354" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="317" t="n"/>
-      <c r="C35" s="317" t="n"/>
-      <c r="D35" s="317" t="n"/>
-      <c r="E35" s="317" t="n"/>
-      <c r="F35" s="317" t="n"/>
-      <c r="G35" s="318" t="n"/>
-      <c r="H35" s="288" t="n"/>
-      <c r="I35" s="317" t="n"/>
-      <c r="J35" s="317" t="n"/>
-      <c r="K35" s="317" t="n"/>
-      <c r="L35" s="317" t="n"/>
-      <c r="M35" s="317" t="n"/>
-      <c r="N35" s="317" t="n"/>
-      <c r="O35" s="317" t="n"/>
-      <c r="P35" s="317" t="n"/>
-      <c r="Q35" s="317" t="n"/>
-      <c r="R35" s="317" t="n"/>
-      <c r="S35" s="317" t="n"/>
-      <c r="T35" s="318" t="n"/>
-      <c r="U35" s="289" t="inlineStr">
+      <c r="B35" s="399" t="n"/>
+      <c r="C35" s="399" t="n"/>
+      <c r="D35" s="399" t="n"/>
+      <c r="E35" s="399" t="n"/>
+      <c r="F35" s="399" t="n"/>
+      <c r="G35" s="400" t="n"/>
+      <c r="H35" s="357" t="n"/>
+      <c r="I35" s="399" t="n"/>
+      <c r="J35" s="399" t="n"/>
+      <c r="K35" s="399" t="n"/>
+      <c r="L35" s="399" t="n"/>
+      <c r="M35" s="399" t="n"/>
+      <c r="N35" s="399" t="n"/>
+      <c r="O35" s="399" t="n"/>
+      <c r="P35" s="399" t="n"/>
+      <c r="Q35" s="399" t="n"/>
+      <c r="R35" s="399" t="n"/>
+      <c r="S35" s="399" t="n"/>
+      <c r="T35" s="400" t="n"/>
+      <c r="U35" s="358" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="317" t="n"/>
-      <c r="W35" s="317" t="n"/>
-      <c r="X35" s="317" t="n"/>
-      <c r="Y35" s="317" t="n"/>
-      <c r="Z35" s="317" t="n"/>
-      <c r="AA35" s="318" t="n"/>
-      <c r="AB35" s="290" t="n"/>
-      <c r="AC35" s="317" t="n"/>
-      <c r="AD35" s="317" t="n"/>
-      <c r="AE35" s="317" t="n"/>
-      <c r="AF35" s="317" t="n"/>
-      <c r="AG35" s="317" t="n"/>
-      <c r="AH35" s="317" t="n"/>
-      <c r="AI35" s="317" t="n"/>
-      <c r="AJ35" s="317" t="n"/>
-      <c r="AK35" s="317" t="n"/>
-      <c r="AL35" s="317" t="n"/>
-      <c r="AM35" s="317" t="n"/>
-      <c r="AN35" s="319" t="n"/>
+      <c r="V35" s="399" t="n"/>
+      <c r="W35" s="399" t="n"/>
+      <c r="X35" s="399" t="n"/>
+      <c r="Y35" s="399" t="n"/>
+      <c r="Z35" s="399" t="n"/>
+      <c r="AA35" s="400" t="n"/>
+      <c r="AB35" s="357" t="n"/>
+      <c r="AC35" s="399" t="n"/>
+      <c r="AD35" s="399" t="n"/>
+      <c r="AE35" s="399" t="n"/>
+      <c r="AF35" s="399" t="n"/>
+      <c r="AG35" s="399" t="n"/>
+      <c r="AH35" s="399" t="n"/>
+      <c r="AI35" s="399" t="n"/>
+      <c r="AJ35" s="399" t="n"/>
+      <c r="AK35" s="399" t="n"/>
+      <c r="AL35" s="399" t="n"/>
+      <c r="AM35" s="399" t="n"/>
+      <c r="AN35" s="400" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="287" t="inlineStr">
+      <c r="A36" s="354" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="317" t="n"/>
-      <c r="C36" s="317" t="n"/>
-      <c r="D36" s="317" t="n"/>
-      <c r="E36" s="317" t="n"/>
-      <c r="F36" s="317" t="n"/>
-      <c r="G36" s="318" t="n"/>
-      <c r="H36" s="288" t="n"/>
-      <c r="I36" s="317" t="n"/>
-      <c r="J36" s="317" t="n"/>
-      <c r="K36" s="317" t="n"/>
-      <c r="L36" s="317" t="n"/>
-      <c r="M36" s="317" t="n"/>
-      <c r="N36" s="317" t="n"/>
-      <c r="O36" s="317" t="n"/>
-      <c r="P36" s="317" t="n"/>
-      <c r="Q36" s="317" t="n"/>
-      <c r="R36" s="317" t="n"/>
-      <c r="S36" s="317" t="n"/>
-      <c r="T36" s="318" t="n"/>
-      <c r="U36" s="289" t="inlineStr">
+      <c r="B36" s="399" t="n"/>
+      <c r="C36" s="399" t="n"/>
+      <c r="D36" s="399" t="n"/>
+      <c r="E36" s="399" t="n"/>
+      <c r="F36" s="399" t="n"/>
+      <c r="G36" s="400" t="n"/>
+      <c r="H36" s="357" t="n"/>
+      <c r="I36" s="399" t="n"/>
+      <c r="J36" s="399" t="n"/>
+      <c r="K36" s="399" t="n"/>
+      <c r="L36" s="399" t="n"/>
+      <c r="M36" s="399" t="n"/>
+      <c r="N36" s="399" t="n"/>
+      <c r="O36" s="399" t="n"/>
+      <c r="P36" s="399" t="n"/>
+      <c r="Q36" s="399" t="n"/>
+      <c r="R36" s="399" t="n"/>
+      <c r="S36" s="399" t="n"/>
+      <c r="T36" s="400" t="n"/>
+      <c r="U36" s="358" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="317" t="n"/>
-      <c r="W36" s="317" t="n"/>
-      <c r="X36" s="317" t="n"/>
-      <c r="Y36" s="317" t="n"/>
-      <c r="Z36" s="317" t="n"/>
-      <c r="AA36" s="318" t="n"/>
-      <c r="AB36" s="290" t="n"/>
-      <c r="AC36" s="317" t="n"/>
-      <c r="AD36" s="317" t="n"/>
-      <c r="AE36" s="317" t="n"/>
-      <c r="AF36" s="317" t="n"/>
-      <c r="AG36" s="317" t="n"/>
-      <c r="AH36" s="317" t="n"/>
-      <c r="AI36" s="317" t="n"/>
-      <c r="AJ36" s="317" t="n"/>
-      <c r="AK36" s="317" t="n"/>
-      <c r="AL36" s="317" t="n"/>
-      <c r="AM36" s="317" t="n"/>
-      <c r="AN36" s="319" t="n"/>
+      <c r="V36" s="399" t="n"/>
+      <c r="W36" s="399" t="n"/>
+      <c r="X36" s="399" t="n"/>
+      <c r="Y36" s="399" t="n"/>
+      <c r="Z36" s="399" t="n"/>
+      <c r="AA36" s="400" t="n"/>
+      <c r="AB36" s="357" t="n"/>
+      <c r="AC36" s="399" t="n"/>
+      <c r="AD36" s="399" t="n"/>
+      <c r="AE36" s="399" t="n"/>
+      <c r="AF36" s="399" t="n"/>
+      <c r="AG36" s="399" t="n"/>
+      <c r="AH36" s="399" t="n"/>
+      <c r="AI36" s="399" t="n"/>
+      <c r="AJ36" s="399" t="n"/>
+      <c r="AK36" s="399" t="n"/>
+      <c r="AL36" s="399" t="n"/>
+      <c r="AM36" s="399" t="n"/>
+      <c r="AN36" s="400" t="n"/>
     </row>
     <row r="37" ht="4" customHeight="1" s="329">
-      <c r="A37" s="293" t="n"/>
-      <c r="C37" s="303" t="n"/>
-      <c r="M37" s="303" t="n"/>
-      <c r="Y37" s="297" t="n"/>
-      <c r="AD37" s="297" t="n"/>
-      <c r="AI37" s="297" t="n"/>
-      <c r="AL37" s="306" t="n"/>
+      <c r="A37" s="364" t="n"/>
+      <c r="B37" s="352" t="n"/>
+      <c r="C37" s="366" t="n"/>
+      <c r="D37" s="352" t="n"/>
+      <c r="E37" s="352" t="n"/>
+      <c r="F37" s="352" t="n"/>
+      <c r="G37" s="352" t="n"/>
+      <c r="H37" s="352" t="n"/>
+      <c r="I37" s="352" t="n"/>
+      <c r="J37" s="352" t="n"/>
+      <c r="K37" s="352" t="n"/>
+      <c r="L37" s="352" t="n"/>
+      <c r="M37" s="366" t="n"/>
+      <c r="N37" s="352" t="n"/>
+      <c r="O37" s="352" t="n"/>
+      <c r="P37" s="352" t="n"/>
+      <c r="Q37" s="352" t="n"/>
+      <c r="R37" s="352" t="n"/>
+      <c r="S37" s="352" t="n"/>
+      <c r="T37" s="352" t="n"/>
+      <c r="U37" s="352" t="n"/>
+      <c r="V37" s="352" t="n"/>
+      <c r="W37" s="352" t="n"/>
+      <c r="X37" s="352" t="n"/>
+      <c r="Y37" s="368" t="n"/>
+      <c r="Z37" s="352" t="n"/>
+      <c r="AA37" s="352" t="n"/>
+      <c r="AB37" s="352" t="n"/>
+      <c r="AC37" s="352" t="n"/>
+      <c r="AD37" s="368" t="n"/>
+      <c r="AE37" s="352" t="n"/>
+      <c r="AF37" s="352" t="n"/>
+      <c r="AG37" s="352" t="n"/>
+      <c r="AH37" s="352" t="n"/>
+      <c r="AI37" s="368" t="n"/>
+      <c r="AJ37" s="352" t="n"/>
+      <c r="AK37" s="352" t="n"/>
+      <c r="AL37" s="368" t="n"/>
+      <c r="AM37" s="352" t="n"/>
+      <c r="AN37" s="352" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1" s="329">
-      <c r="A38" s="284" t="inlineStr">
+    <row r="38" ht="20" customHeight="1" s="329">
+      <c r="A38" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="285" t="n"/>
-      <c r="C38" s="285" t="n"/>
-      <c r="D38" s="285" t="n"/>
-      <c r="E38" s="285" t="n"/>
-      <c r="F38" s="285" t="n"/>
-      <c r="G38" s="285" t="n"/>
-      <c r="H38" s="285" t="n"/>
-      <c r="I38" s="285" t="n"/>
-      <c r="J38" s="285" t="n"/>
-      <c r="K38" s="285" t="n"/>
-      <c r="L38" s="285" t="n"/>
-      <c r="M38" s="285" t="n"/>
-      <c r="N38" s="285" t="n"/>
-      <c r="O38" s="285" t="n"/>
-      <c r="P38" s="285" t="n"/>
-      <c r="Q38" s="285" t="n"/>
-      <c r="R38" s="285" t="n"/>
-      <c r="S38" s="285" t="n"/>
-      <c r="T38" s="285" t="n"/>
-      <c r="U38" s="285" t="n"/>
-      <c r="V38" s="285" t="n"/>
-      <c r="W38" s="285" t="n"/>
-      <c r="X38" s="285" t="n"/>
-      <c r="Y38" s="285" t="n"/>
-      <c r="Z38" s="285" t="n"/>
-      <c r="AA38" s="285" t="n"/>
-      <c r="AB38" s="285" t="n"/>
-      <c r="AC38" s="285" t="n"/>
-      <c r="AD38" s="285" t="n"/>
-      <c r="AE38" s="285" t="n"/>
-      <c r="AF38" s="285" t="n"/>
-      <c r="AG38" s="285" t="n"/>
-      <c r="AH38" s="285" t="n"/>
-      <c r="AI38" s="285" t="n"/>
-      <c r="AJ38" s="285" t="n"/>
-      <c r="AK38" s="285" t="n"/>
-      <c r="AL38" s="285" t="n"/>
-      <c r="AM38" s="285" t="n"/>
-      <c r="AN38" s="286" t="n"/>
+      <c r="B38" s="399" t="n"/>
+      <c r="C38" s="399" t="n"/>
+      <c r="D38" s="399" t="n"/>
+      <c r="E38" s="399" t="n"/>
+      <c r="F38" s="399" t="n"/>
+      <c r="G38" s="399" t="n"/>
+      <c r="H38" s="399" t="n"/>
+      <c r="I38" s="399" t="n"/>
+      <c r="J38" s="399" t="n"/>
+      <c r="K38" s="399" t="n"/>
+      <c r="L38" s="399" t="n"/>
+      <c r="M38" s="399" t="n"/>
+      <c r="N38" s="399" t="n"/>
+      <c r="O38" s="399" t="n"/>
+      <c r="P38" s="399" t="n"/>
+      <c r="Q38" s="399" t="n"/>
+      <c r="R38" s="399" t="n"/>
+      <c r="S38" s="399" t="n"/>
+      <c r="T38" s="399" t="n"/>
+      <c r="U38" s="399" t="n"/>
+      <c r="V38" s="399" t="n"/>
+      <c r="W38" s="399" t="n"/>
+      <c r="X38" s="399" t="n"/>
+      <c r="Y38" s="399" t="n"/>
+      <c r="Z38" s="399" t="n"/>
+      <c r="AA38" s="399" t="n"/>
+      <c r="AB38" s="399" t="n"/>
+      <c r="AC38" s="399" t="n"/>
+      <c r="AD38" s="399" t="n"/>
+      <c r="AE38" s="399" t="n"/>
+      <c r="AF38" s="399" t="n"/>
+      <c r="AG38" s="399" t="n"/>
+      <c r="AH38" s="399" t="n"/>
+      <c r="AI38" s="399" t="n"/>
+      <c r="AJ38" s="399" t="n"/>
+      <c r="AK38" s="399" t="n"/>
+      <c r="AL38" s="399" t="n"/>
+      <c r="AM38" s="399" t="n"/>
+      <c r="AN38" s="400" t="n"/>
     </row>
-    <row r="39" ht="17" customHeight="1" s="329">
-      <c r="A39" s="325" t="inlineStr">
+    <row r="39" ht="20" customHeight="1" s="329">
+      <c r="A39" s="377" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="285" t="n"/>
-      <c r="C39" s="285" t="n"/>
-      <c r="D39" s="285" t="n"/>
-      <c r="E39" s="285" t="n"/>
-      <c r="F39" s="285" t="n"/>
-      <c r="G39" s="285" t="n"/>
-      <c r="H39" s="285" t="n"/>
-      <c r="I39" s="285" t="n"/>
-      <c r="J39" s="285" t="n"/>
-      <c r="K39" s="285" t="n"/>
-      <c r="L39" s="285" t="n"/>
-      <c r="M39" s="326" t="n"/>
-      <c r="N39" s="51" t="inlineStr">
+      <c r="B39" s="394" t="n"/>
+      <c r="C39" s="394" t="n"/>
+      <c r="D39" s="394" t="n"/>
+      <c r="E39" s="394" t="n"/>
+      <c r="F39" s="394" t="n"/>
+      <c r="G39" s="394" t="n"/>
+      <c r="H39" s="394" t="n"/>
+      <c r="I39" s="394" t="n"/>
+      <c r="J39" s="394" t="n"/>
+      <c r="K39" s="394" t="n"/>
+      <c r="L39" s="394" t="n"/>
+      <c r="M39" s="395" t="n"/>
+      <c r="N39" s="378" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="285" t="n"/>
-      <c r="P39" s="285" t="n"/>
-      <c r="Q39" s="285" t="n"/>
-      <c r="R39" s="285" t="n"/>
-      <c r="S39" s="285" t="n"/>
-      <c r="T39" s="285" t="n"/>
-      <c r="U39" s="285" t="n"/>
-      <c r="V39" s="285" t="n"/>
-      <c r="W39" s="285" t="n"/>
-      <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="285" t="n"/>
-      <c r="Z39" s="285" t="n"/>
-      <c r="AA39" s="307" t="inlineStr">
+      <c r="O39" s="394" t="n"/>
+      <c r="P39" s="394" t="n"/>
+      <c r="Q39" s="394" t="n"/>
+      <c r="R39" s="394" t="n"/>
+      <c r="S39" s="394" t="n"/>
+      <c r="T39" s="394" t="n"/>
+      <c r="U39" s="394" t="n"/>
+      <c r="V39" s="394" t="n"/>
+      <c r="W39" s="394" t="n"/>
+      <c r="X39" s="394" t="n"/>
+      <c r="Y39" s="394" t="n"/>
+      <c r="Z39" s="394" t="n"/>
+      <c r="AA39" s="379" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="285" t="n"/>
-      <c r="AC39" s="285" t="n"/>
-      <c r="AD39" s="285" t="n"/>
-      <c r="AE39" s="285" t="n"/>
-      <c r="AF39" s="285" t="n"/>
-      <c r="AG39" s="285" t="n"/>
-      <c r="AH39" s="285" t="n"/>
-      <c r="AI39" s="285" t="n"/>
-      <c r="AJ39" s="285" t="n"/>
-      <c r="AK39" s="285" t="n"/>
-      <c r="AL39" s="285" t="n"/>
-      <c r="AM39" s="285" t="n"/>
-      <c r="AN39" s="286" t="n"/>
+      <c r="AB39" s="394" t="n"/>
+      <c r="AC39" s="394" t="n"/>
+      <c r="AD39" s="394" t="n"/>
+      <c r="AE39" s="394" t="n"/>
+      <c r="AF39" s="394" t="n"/>
+      <c r="AG39" s="394" t="n"/>
+      <c r="AH39" s="394" t="n"/>
+      <c r="AI39" s="394" t="n"/>
+      <c r="AJ39" s="394" t="n"/>
+      <c r="AK39" s="394" t="n"/>
+      <c r="AL39" s="394" t="n"/>
+      <c r="AM39" s="394" t="n"/>
+      <c r="AN39" s="395" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1" s="329">
-      <c r="A40" s="308" t="inlineStr">
+    <row r="40" ht="20" customHeight="1" s="329">
+      <c r="A40" s="380" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="320" t="n"/>
-      <c r="C40" s="320" t="n"/>
-      <c r="D40" s="320" t="n"/>
-      <c r="E40" s="320" t="n"/>
-      <c r="F40" s="320" t="n"/>
-      <c r="G40" s="320" t="n"/>
-      <c r="H40" s="320" t="n"/>
-      <c r="I40" s="320" t="n"/>
-      <c r="J40" s="320" t="n"/>
-      <c r="K40" s="320" t="n"/>
-      <c r="L40" s="320" t="n"/>
-      <c r="M40" s="327" t="n"/>
-      <c r="N40" s="308" t="inlineStr">
+      <c r="B40" s="393" t="n"/>
+      <c r="C40" s="393" t="n"/>
+      <c r="D40" s="393" t="n"/>
+      <c r="E40" s="393" t="n"/>
+      <c r="F40" s="393" t="n"/>
+      <c r="G40" s="393" t="n"/>
+      <c r="H40" s="393" t="n"/>
+      <c r="I40" s="393" t="n"/>
+      <c r="J40" s="393" t="n"/>
+      <c r="K40" s="393" t="n"/>
+      <c r="L40" s="393" t="n"/>
+      <c r="M40" s="405" t="n"/>
+      <c r="N40" s="380" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="320" t="n"/>
-      <c r="P40" s="320" t="n"/>
-      <c r="Q40" s="320" t="n"/>
-      <c r="R40" s="320" t="n"/>
-      <c r="S40" s="320" t="n"/>
-      <c r="T40" s="320" t="n"/>
-      <c r="U40" s="320" t="n"/>
-      <c r="V40" s="320" t="n"/>
-      <c r="W40" s="320" t="n"/>
-      <c r="X40" s="320" t="n"/>
-      <c r="Y40" s="320" t="n"/>
-      <c r="Z40" s="327" t="n"/>
-      <c r="AA40" s="308" t="inlineStr">
+      <c r="O40" s="393" t="n"/>
+      <c r="P40" s="393" t="n"/>
+      <c r="Q40" s="393" t="n"/>
+      <c r="R40" s="393" t="n"/>
+      <c r="S40" s="393" t="n"/>
+      <c r="T40" s="393" t="n"/>
+      <c r="U40" s="393" t="n"/>
+      <c r="V40" s="393" t="n"/>
+      <c r="W40" s="393" t="n"/>
+      <c r="X40" s="393" t="n"/>
+      <c r="Y40" s="393" t="n"/>
+      <c r="Z40" s="405" t="n"/>
+      <c r="AA40" s="380" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="320" t="n"/>
-      <c r="AC40" s="320" t="n"/>
-      <c r="AD40" s="320" t="n"/>
-      <c r="AE40" s="320" t="n"/>
-      <c r="AF40" s="320" t="n"/>
-      <c r="AG40" s="320" t="n"/>
-      <c r="AH40" s="320" t="n"/>
-      <c r="AI40" s="320" t="n"/>
-      <c r="AJ40" s="320" t="n"/>
-      <c r="AK40" s="320" t="n"/>
-      <c r="AL40" s="320" t="n"/>
-      <c r="AM40" s="320" t="n"/>
-      <c r="AN40" s="327" t="n"/>
+      <c r="AB40" s="393" t="n"/>
+      <c r="AC40" s="393" t="n"/>
+      <c r="AD40" s="393" t="n"/>
+      <c r="AE40" s="393" t="n"/>
+      <c r="AF40" s="393" t="n"/>
+      <c r="AG40" s="393" t="n"/>
+      <c r="AH40" s="393" t="n"/>
+      <c r="AI40" s="393" t="n"/>
+      <c r="AJ40" s="393" t="n"/>
+      <c r="AK40" s="393" t="n"/>
+      <c r="AL40" s="393" t="n"/>
+      <c r="AM40" s="393" t="n"/>
+      <c r="AN40" s="405" t="n"/>
     </row>
-    <row r="41" ht="26" customHeight="1" s="329">
-      <c r="A41" s="328" t="n"/>
-      <c r="M41" s="330" t="n"/>
-      <c r="N41" s="328" t="n"/>
-      <c r="Z41" s="330" t="n"/>
-      <c r="AA41" s="328" t="n"/>
-      <c r="AN41" s="330" t="n"/>
+    <row r="41" ht="20" customHeight="1" s="329">
+      <c r="A41" s="406" t="n"/>
+      <c r="B41" s="383" t="n"/>
+      <c r="C41" s="383" t="n"/>
+      <c r="D41" s="383" t="n"/>
+      <c r="E41" s="383" t="n"/>
+      <c r="F41" s="383" t="n"/>
+      <c r="G41" s="383" t="n"/>
+      <c r="H41" s="383" t="n"/>
+      <c r="I41" s="383" t="n"/>
+      <c r="J41" s="383" t="n"/>
+      <c r="K41" s="383" t="n"/>
+      <c r="L41" s="383" t="n"/>
+      <c r="M41" s="407" t="n"/>
+      <c r="N41" s="406" t="n"/>
+      <c r="O41" s="383" t="n"/>
+      <c r="P41" s="383" t="n"/>
+      <c r="Q41" s="383" t="n"/>
+      <c r="R41" s="383" t="n"/>
+      <c r="S41" s="383" t="n"/>
+      <c r="T41" s="383" t="n"/>
+      <c r="U41" s="383" t="n"/>
+      <c r="V41" s="383" t="n"/>
+      <c r="W41" s="383" t="n"/>
+      <c r="X41" s="383" t="n"/>
+      <c r="Y41" s="383" t="n"/>
+      <c r="Z41" s="407" t="n"/>
+      <c r="AA41" s="406" t="n"/>
+      <c r="AB41" s="383" t="n"/>
+      <c r="AC41" s="383" t="n"/>
+      <c r="AD41" s="383" t="n"/>
+      <c r="AE41" s="383" t="n"/>
+      <c r="AF41" s="383" t="n"/>
+      <c r="AG41" s="383" t="n"/>
+      <c r="AH41" s="383" t="n"/>
+      <c r="AI41" s="383" t="n"/>
+      <c r="AJ41" s="383" t="n"/>
+      <c r="AK41" s="383" t="n"/>
+      <c r="AL41" s="383" t="n"/>
+      <c r="AM41" s="383" t="n"/>
+      <c r="AN41" s="407" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="329">
-      <c r="A42" s="331" t="n"/>
-      <c r="B42" s="332" t="n"/>
-      <c r="C42" s="332" t="n"/>
-      <c r="D42" s="332" t="n"/>
-      <c r="E42" s="332" t="n"/>
-      <c r="F42" s="332" t="n"/>
-      <c r="G42" s="332" t="n"/>
-      <c r="H42" s="332" t="n"/>
-      <c r="I42" s="332" t="n"/>
-      <c r="J42" s="332" t="n"/>
-      <c r="K42" s="332" t="n"/>
-      <c r="L42" s="332" t="n"/>
-      <c r="M42" s="333" t="n"/>
-      <c r="N42" s="331" t="n"/>
-      <c r="O42" s="332" t="n"/>
-      <c r="P42" s="332" t="n"/>
-      <c r="Q42" s="332" t="n"/>
-      <c r="R42" s="332" t="n"/>
-      <c r="S42" s="332" t="n"/>
-      <c r="T42" s="332" t="n"/>
-      <c r="U42" s="332" t="n"/>
-      <c r="V42" s="332" t="n"/>
-      <c r="W42" s="332" t="n"/>
-      <c r="X42" s="332" t="n"/>
-      <c r="Y42" s="332" t="n"/>
-      <c r="Z42" s="333" t="n"/>
-      <c r="AA42" s="331" t="n"/>
-      <c r="AB42" s="332" t="n"/>
-      <c r="AC42" s="332" t="n"/>
-      <c r="AD42" s="332" t="n"/>
-      <c r="AE42" s="332" t="n"/>
-      <c r="AF42" s="332" t="n"/>
-      <c r="AG42" s="332" t="n"/>
-      <c r="AH42" s="332" t="n"/>
-      <c r="AI42" s="332" t="n"/>
-      <c r="AJ42" s="332" t="n"/>
-      <c r="AK42" s="332" t="n"/>
-      <c r="AL42" s="332" t="n"/>
-      <c r="AM42" s="332" t="n"/>
-      <c r="AN42" s="333" t="n"/>
+    <row r="42" ht="20" customHeight="1" s="329">
+      <c r="A42" s="408" t="n"/>
+      <c r="B42" s="403" t="n"/>
+      <c r="C42" s="403" t="n"/>
+      <c r="D42" s="403" t="n"/>
+      <c r="E42" s="403" t="n"/>
+      <c r="F42" s="403" t="n"/>
+      <c r="G42" s="403" t="n"/>
+      <c r="H42" s="403" t="n"/>
+      <c r="I42" s="403" t="n"/>
+      <c r="J42" s="403" t="n"/>
+      <c r="K42" s="403" t="n"/>
+      <c r="L42" s="403" t="n"/>
+      <c r="M42" s="404" t="n"/>
+      <c r="N42" s="408" t="n"/>
+      <c r="O42" s="403" t="n"/>
+      <c r="P42" s="403" t="n"/>
+      <c r="Q42" s="403" t="n"/>
+      <c r="R42" s="403" t="n"/>
+      <c r="S42" s="403" t="n"/>
+      <c r="T42" s="403" t="n"/>
+      <c r="U42" s="403" t="n"/>
+      <c r="V42" s="403" t="n"/>
+      <c r="W42" s="403" t="n"/>
+      <c r="X42" s="403" t="n"/>
+      <c r="Y42" s="403" t="n"/>
+      <c r="Z42" s="404" t="n"/>
+      <c r="AA42" s="408" t="n"/>
+      <c r="AB42" s="403" t="n"/>
+      <c r="AC42" s="403" t="n"/>
+      <c r="AD42" s="403" t="n"/>
+      <c r="AE42" s="403" t="n"/>
+      <c r="AF42" s="403" t="n"/>
+      <c r="AG42" s="403" t="n"/>
+      <c r="AH42" s="403" t="n"/>
+      <c r="AI42" s="403" t="n"/>
+      <c r="AJ42" s="403" t="n"/>
+      <c r="AK42" s="403" t="n"/>
+      <c r="AL42" s="403" t="n"/>
+      <c r="AM42" s="403" t="n"/>
+      <c r="AN42" s="404" t="n"/>
     </row>
     <row r="43" ht="4" customHeight="1" s="329">
-      <c r="A43" s="309" t="n"/>
-      <c r="N43" s="309" t="n"/>
-      <c r="AA43" s="309" t="n"/>
+      <c r="A43" s="386" t="n"/>
+      <c r="B43" s="352" t="n"/>
+      <c r="C43" s="352" t="n"/>
+      <c r="D43" s="352" t="n"/>
+      <c r="E43" s="352" t="n"/>
+      <c r="F43" s="352" t="n"/>
+      <c r="G43" s="352" t="n"/>
+      <c r="H43" s="352" t="n"/>
+      <c r="I43" s="352" t="n"/>
+      <c r="J43" s="352" t="n"/>
+      <c r="K43" s="352" t="n"/>
+      <c r="L43" s="352" t="n"/>
+      <c r="M43" s="352" t="n"/>
+      <c r="N43" s="386" t="n"/>
+      <c r="O43" s="352" t="n"/>
+      <c r="P43" s="352" t="n"/>
+      <c r="Q43" s="352" t="n"/>
+      <c r="R43" s="352" t="n"/>
+      <c r="S43" s="352" t="n"/>
+      <c r="T43" s="352" t="n"/>
+      <c r="U43" s="352" t="n"/>
+      <c r="V43" s="352" t="n"/>
+      <c r="W43" s="352" t="n"/>
+      <c r="X43" s="352" t="n"/>
+      <c r="Y43" s="352" t="n"/>
+      <c r="Z43" s="352" t="n"/>
+      <c r="AA43" s="386" t="n"/>
+      <c r="AB43" s="352" t="n"/>
+      <c r="AC43" s="352" t="n"/>
+      <c r="AD43" s="352" t="n"/>
+      <c r="AE43" s="352" t="n"/>
+      <c r="AF43" s="352" t="n"/>
+      <c r="AG43" s="352" t="n"/>
+      <c r="AH43" s="352" t="n"/>
+      <c r="AI43" s="352" t="n"/>
+      <c r="AJ43" s="352" t="n"/>
+      <c r="AK43" s="352" t="n"/>
+      <c r="AL43" s="352" t="n"/>
+      <c r="AM43" s="352" t="n"/>
+      <c r="AN43" s="352" t="n"/>
     </row>
-    <row r="44" ht="24" customHeight="1" s="329">
-      <c r="A44" s="310" t="inlineStr">
+    <row r="44" ht="20" customHeight="1" s="329">
+      <c r="A44" s="387" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
         </is>
       </c>
+      <c r="B44" s="383" t="n"/>
+      <c r="C44" s="383" t="n"/>
+      <c r="D44" s="383" t="n"/>
+      <c r="E44" s="383" t="n"/>
+      <c r="F44" s="383" t="n"/>
+      <c r="G44" s="383" t="n"/>
+      <c r="H44" s="383" t="n"/>
+      <c r="I44" s="383" t="n"/>
+      <c r="J44" s="383" t="n"/>
+      <c r="K44" s="383" t="n"/>
+      <c r="L44" s="383" t="n"/>
+      <c r="M44" s="383" t="n"/>
+      <c r="N44" s="383" t="n"/>
+      <c r="O44" s="383" t="n"/>
+      <c r="P44" s="383" t="n"/>
+      <c r="Q44" s="383" t="n"/>
+      <c r="R44" s="383" t="n"/>
+      <c r="S44" s="383" t="n"/>
+      <c r="T44" s="383" t="n"/>
+      <c r="U44" s="383" t="n"/>
+      <c r="V44" s="383" t="n"/>
+      <c r="W44" s="383" t="n"/>
+      <c r="X44" s="383" t="n"/>
+      <c r="Y44" s="383" t="n"/>
+      <c r="Z44" s="383" t="n"/>
+      <c r="AA44" s="383" t="n"/>
+      <c r="AB44" s="383" t="n"/>
+      <c r="AC44" s="383" t="n"/>
+      <c r="AD44" s="383" t="n"/>
+      <c r="AE44" s="383" t="n"/>
+      <c r="AF44" s="383" t="n"/>
+      <c r="AG44" s="383" t="n"/>
+      <c r="AH44" s="383" t="n"/>
+      <c r="AI44" s="383" t="n"/>
+      <c r="AJ44" s="383" t="n"/>
+      <c r="AK44" s="383" t="n"/>
+      <c r="AL44" s="383" t="n"/>
+      <c r="AM44" s="383" t="n"/>
+      <c r="AN44" s="383" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -6587,7 +7254,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6840,17 +7506,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="329" min="1" max="1"/>
-    <col width="28" customWidth="1" style="329" min="2" max="2"/>
-    <col width="28" customWidth="1" style="329" min="3" max="3"/>
-    <col width="16" customWidth="1" style="329" min="4" max="4"/>
-    <col width="14" customWidth="1" style="329" min="5" max="5"/>
-    <col width="16" customWidth="1" style="329" min="6" max="6"/>
-    <col width="18" customWidth="1" style="329" min="7" max="7"/>
-    <col width="24" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
@@ -6859,6 +7557,45 @@
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
+      <c r="B1" s="347" t="n"/>
+      <c r="C1" s="347" t="n"/>
+      <c r="D1" s="347" t="n"/>
+      <c r="E1" s="347" t="n"/>
+      <c r="F1" s="347" t="n"/>
+      <c r="G1" s="347" t="n"/>
+      <c r="H1" s="347" t="n"/>
+      <c r="I1" s="347" t="n"/>
+      <c r="J1" s="347" t="n"/>
+      <c r="K1" s="347" t="n"/>
+      <c r="L1" s="347" t="n"/>
+      <c r="M1" s="347" t="n"/>
+      <c r="N1" s="347" t="n"/>
+      <c r="O1" s="347" t="n"/>
+      <c r="P1" s="347" t="n"/>
+      <c r="Q1" s="347" t="n"/>
+      <c r="R1" s="347" t="n"/>
+      <c r="S1" s="347" t="n"/>
+      <c r="T1" s="347" t="n"/>
+      <c r="U1" s="347" t="n"/>
+      <c r="V1" s="347" t="n"/>
+      <c r="W1" s="347" t="n"/>
+      <c r="X1" s="347" t="n"/>
+      <c r="Y1" s="347" t="n"/>
+      <c r="Z1" s="347" t="n"/>
+      <c r="AA1" s="347" t="n"/>
+      <c r="AB1" s="347" t="n"/>
+      <c r="AC1" s="347" t="n"/>
+      <c r="AD1" s="347" t="n"/>
+      <c r="AE1" s="347" t="n"/>
+      <c r="AF1" s="347" t="n"/>
+      <c r="AG1" s="347" t="n"/>
+      <c r="AH1" s="347" t="n"/>
+      <c r="AI1" s="347" t="n"/>
+      <c r="AJ1" s="347" t="n"/>
+      <c r="AK1" s="347" t="n"/>
+      <c r="AL1" s="347" t="n"/>
+      <c r="AM1" s="347" t="n"/>
+      <c r="AN1" s="347" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="335" t="inlineStr">
@@ -6866,109 +7603,611 @@
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
+      <c r="B2" s="347" t="n"/>
+      <c r="C2" s="347" t="n"/>
+      <c r="D2" s="347" t="n"/>
+      <c r="E2" s="347" t="n"/>
+      <c r="F2" s="347" t="n"/>
+      <c r="G2" s="347" t="n"/>
+      <c r="H2" s="347" t="n"/>
+      <c r="I2" s="347" t="n"/>
+      <c r="J2" s="347" t="n"/>
+      <c r="K2" s="347" t="n"/>
+      <c r="L2" s="347" t="n"/>
+      <c r="M2" s="347" t="n"/>
+      <c r="N2" s="347" t="n"/>
+      <c r="O2" s="347" t="n"/>
+      <c r="P2" s="347" t="n"/>
+      <c r="Q2" s="347" t="n"/>
+      <c r="R2" s="347" t="n"/>
+      <c r="S2" s="347" t="n"/>
+      <c r="T2" s="347" t="n"/>
+      <c r="U2" s="347" t="n"/>
+      <c r="V2" s="347" t="n"/>
+      <c r="W2" s="347" t="n"/>
+      <c r="X2" s="347" t="n"/>
+      <c r="Y2" s="347" t="n"/>
+      <c r="Z2" s="347" t="n"/>
+      <c r="AA2" s="347" t="n"/>
+      <c r="AB2" s="347" t="n"/>
+      <c r="AC2" s="347" t="n"/>
+      <c r="AD2" s="347" t="n"/>
+      <c r="AE2" s="347" t="n"/>
+      <c r="AF2" s="347" t="n"/>
+      <c r="AG2" s="347" t="n"/>
+      <c r="AH2" s="347" t="n"/>
+      <c r="AI2" s="347" t="n"/>
+      <c r="AJ2" s="347" t="n"/>
+      <c r="AK2" s="347" t="n"/>
+      <c r="AL2" s="347" t="n"/>
+      <c r="AM2" s="347" t="n"/>
+      <c r="AN2" s="347" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="347" t="n"/>
+      <c r="B3" s="347" t="n"/>
+      <c r="C3" s="347" t="n"/>
+      <c r="D3" s="347" t="n"/>
+      <c r="E3" s="347" t="n"/>
+      <c r="F3" s="347" t="n"/>
+      <c r="G3" s="347" t="n"/>
+      <c r="H3" s="347" t="n"/>
+      <c r="I3" s="347" t="n"/>
+      <c r="J3" s="347" t="n"/>
+      <c r="K3" s="347" t="n"/>
+      <c r="L3" s="347" t="n"/>
+      <c r="M3" s="347" t="n"/>
+      <c r="N3" s="347" t="n"/>
+      <c r="O3" s="347" t="n"/>
+      <c r="P3" s="347" t="n"/>
+      <c r="Q3" s="347" t="n"/>
+      <c r="R3" s="347" t="n"/>
+      <c r="S3" s="347" t="n"/>
+      <c r="T3" s="347" t="n"/>
+      <c r="U3" s="347" t="n"/>
+      <c r="V3" s="347" t="n"/>
+      <c r="W3" s="347" t="n"/>
+      <c r="X3" s="347" t="n"/>
+      <c r="Y3" s="347" t="n"/>
+      <c r="Z3" s="347" t="n"/>
+      <c r="AA3" s="347" t="n"/>
+      <c r="AB3" s="347" t="n"/>
+      <c r="AC3" s="347" t="n"/>
+      <c r="AD3" s="347" t="n"/>
+      <c r="AE3" s="347" t="n"/>
+      <c r="AF3" s="347" t="n"/>
+      <c r="AG3" s="347" t="n"/>
+      <c r="AH3" s="347" t="n"/>
+      <c r="AI3" s="347" t="n"/>
+      <c r="AJ3" s="347" t="n"/>
+      <c r="AK3" s="347" t="n"/>
+      <c r="AL3" s="347" t="n"/>
+      <c r="AM3" s="347" t="n"/>
+      <c r="AN3" s="347" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="388" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="388" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="388" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="336" t="inlineStr">
+      <c r="D4" s="388" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="336" t="inlineStr">
+      <c r="E4" s="388" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="336" t="inlineStr">
+      <c r="F4" s="388" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="336" t="inlineStr">
+      <c r="G4" s="388" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="336" t="inlineStr">
+      <c r="H4" s="388" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="I4" s="347" t="n"/>
+      <c r="J4" s="347" t="n"/>
+      <c r="K4" s="347" t="n"/>
+      <c r="L4" s="347" t="n"/>
+      <c r="M4" s="347" t="n"/>
+      <c r="N4" s="347" t="n"/>
+      <c r="O4" s="347" t="n"/>
+      <c r="P4" s="347" t="n"/>
+      <c r="Q4" s="347" t="n"/>
+      <c r="R4" s="347" t="n"/>
+      <c r="S4" s="347" t="n"/>
+      <c r="T4" s="347" t="n"/>
+      <c r="U4" s="347" t="n"/>
+      <c r="V4" s="347" t="n"/>
+      <c r="W4" s="347" t="n"/>
+      <c r="X4" s="347" t="n"/>
+      <c r="Y4" s="347" t="n"/>
+      <c r="Z4" s="347" t="n"/>
+      <c r="AA4" s="347" t="n"/>
+      <c r="AB4" s="347" t="n"/>
+      <c r="AC4" s="347" t="n"/>
+      <c r="AD4" s="347" t="n"/>
+      <c r="AE4" s="347" t="n"/>
+      <c r="AF4" s="347" t="n"/>
+      <c r="AG4" s="347" t="n"/>
+      <c r="AH4" s="347" t="n"/>
+      <c r="AI4" s="347" t="n"/>
+      <c r="AJ4" s="347" t="n"/>
+      <c r="AK4" s="347" t="n"/>
+      <c r="AL4" s="347" t="n"/>
+      <c r="AM4" s="347" t="n"/>
+      <c r="AN4" s="347" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5">
+      <c r="A5" s="347">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B5" s="347" t="n"/>
+      <c r="C5" s="347" t="n"/>
+      <c r="D5" s="347" t="n"/>
+      <c r="E5" s="347" t="n"/>
+      <c r="F5" s="347" t="n"/>
+      <c r="G5" s="347" t="n"/>
+      <c r="H5" s="347" t="n"/>
+      <c r="I5" s="347" t="n"/>
+      <c r="J5" s="347" t="n"/>
+      <c r="K5" s="347" t="n"/>
+      <c r="L5" s="347" t="n"/>
+      <c r="M5" s="347" t="n"/>
+      <c r="N5" s="347" t="n"/>
+      <c r="O5" s="347" t="n"/>
+      <c r="P5" s="347" t="n"/>
+      <c r="Q5" s="347" t="n"/>
+      <c r="R5" s="347" t="n"/>
+      <c r="S5" s="347" t="n"/>
+      <c r="T5" s="347" t="n"/>
+      <c r="U5" s="347" t="n"/>
+      <c r="V5" s="347" t="n"/>
+      <c r="W5" s="347" t="n"/>
+      <c r="X5" s="347" t="n"/>
+      <c r="Y5" s="347" t="n"/>
+      <c r="Z5" s="347" t="n"/>
+      <c r="AA5" s="347" t="n"/>
+      <c r="AB5" s="347" t="n"/>
+      <c r="AC5" s="347" t="n"/>
+      <c r="AD5" s="347" t="n"/>
+      <c r="AE5" s="347" t="n"/>
+      <c r="AF5" s="347" t="n"/>
+      <c r="AG5" s="347" t="n"/>
+      <c r="AH5" s="347" t="n"/>
+      <c r="AI5" s="347" t="n"/>
+      <c r="AJ5" s="347" t="n"/>
+      <c r="AK5" s="347" t="n"/>
+      <c r="AL5" s="347" t="n"/>
+      <c r="AM5" s="347" t="n"/>
+      <c r="AN5" s="347" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6">
+      <c r="A6" s="347">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B6" s="347" t="n"/>
+      <c r="C6" s="347" t="n"/>
+      <c r="D6" s="347" t="n"/>
+      <c r="E6" s="347" t="n"/>
+      <c r="F6" s="347" t="n"/>
+      <c r="G6" s="347" t="n"/>
+      <c r="H6" s="347" t="n"/>
+      <c r="I6" s="347" t="n"/>
+      <c r="J6" s="347" t="n"/>
+      <c r="K6" s="347" t="n"/>
+      <c r="L6" s="347" t="n"/>
+      <c r="M6" s="347" t="n"/>
+      <c r="N6" s="347" t="n"/>
+      <c r="O6" s="347" t="n"/>
+      <c r="P6" s="347" t="n"/>
+      <c r="Q6" s="347" t="n"/>
+      <c r="R6" s="347" t="n"/>
+      <c r="S6" s="347" t="n"/>
+      <c r="T6" s="347" t="n"/>
+      <c r="U6" s="347" t="n"/>
+      <c r="V6" s="347" t="n"/>
+      <c r="W6" s="347" t="n"/>
+      <c r="X6" s="347" t="n"/>
+      <c r="Y6" s="347" t="n"/>
+      <c r="Z6" s="347" t="n"/>
+      <c r="AA6" s="347" t="n"/>
+      <c r="AB6" s="347" t="n"/>
+      <c r="AC6" s="347" t="n"/>
+      <c r="AD6" s="347" t="n"/>
+      <c r="AE6" s="347" t="n"/>
+      <c r="AF6" s="347" t="n"/>
+      <c r="AG6" s="347" t="n"/>
+      <c r="AH6" s="347" t="n"/>
+      <c r="AI6" s="347" t="n"/>
+      <c r="AJ6" s="347" t="n"/>
+      <c r="AK6" s="347" t="n"/>
+      <c r="AL6" s="347" t="n"/>
+      <c r="AM6" s="347" t="n"/>
+      <c r="AN6" s="347" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7">
+      <c r="A7" s="347">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B7" s="347" t="n"/>
+      <c r="C7" s="347" t="n"/>
+      <c r="D7" s="347" t="n"/>
+      <c r="E7" s="347" t="n"/>
+      <c r="F7" s="347" t="n"/>
+      <c r="G7" s="347" t="n"/>
+      <c r="H7" s="347" t="n"/>
+      <c r="I7" s="347" t="n"/>
+      <c r="J7" s="347" t="n"/>
+      <c r="K7" s="347" t="n"/>
+      <c r="L7" s="347" t="n"/>
+      <c r="M7" s="347" t="n"/>
+      <c r="N7" s="347" t="n"/>
+      <c r="O7" s="347" t="n"/>
+      <c r="P7" s="347" t="n"/>
+      <c r="Q7" s="347" t="n"/>
+      <c r="R7" s="347" t="n"/>
+      <c r="S7" s="347" t="n"/>
+      <c r="T7" s="347" t="n"/>
+      <c r="U7" s="347" t="n"/>
+      <c r="V7" s="347" t="n"/>
+      <c r="W7" s="347" t="n"/>
+      <c r="X7" s="347" t="n"/>
+      <c r="Y7" s="347" t="n"/>
+      <c r="Z7" s="347" t="n"/>
+      <c r="AA7" s="347" t="n"/>
+      <c r="AB7" s="347" t="n"/>
+      <c r="AC7" s="347" t="n"/>
+      <c r="AD7" s="347" t="n"/>
+      <c r="AE7" s="347" t="n"/>
+      <c r="AF7" s="347" t="n"/>
+      <c r="AG7" s="347" t="n"/>
+      <c r="AH7" s="347" t="n"/>
+      <c r="AI7" s="347" t="n"/>
+      <c r="AJ7" s="347" t="n"/>
+      <c r="AK7" s="347" t="n"/>
+      <c r="AL7" s="347" t="n"/>
+      <c r="AM7" s="347" t="n"/>
+      <c r="AN7" s="347" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8">
+      <c r="A8" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B8" s="383" t="n"/>
+      <c r="C8" s="383" t="n"/>
+      <c r="D8" s="383" t="n"/>
+      <c r="E8" s="383" t="n"/>
+      <c r="F8" s="383" t="n"/>
+      <c r="G8" s="383" t="n"/>
+      <c r="H8" s="383" t="n"/>
+      <c r="I8" s="383" t="n"/>
+      <c r="J8" s="383" t="n"/>
+      <c r="K8" s="383" t="n"/>
+      <c r="L8" s="383" t="n"/>
+      <c r="M8" s="383" t="n"/>
+      <c r="N8" s="383" t="n"/>
+      <c r="O8" s="383" t="n"/>
+      <c r="P8" s="383" t="n"/>
+      <c r="Q8" s="383" t="n"/>
+      <c r="R8" s="383" t="n"/>
+      <c r="S8" s="383" t="n"/>
+      <c r="T8" s="383" t="n"/>
+      <c r="U8" s="383" t="n"/>
+      <c r="V8" s="383" t="n"/>
+      <c r="W8" s="383" t="n"/>
+      <c r="X8" s="383" t="n"/>
+      <c r="Y8" s="383" t="n"/>
+      <c r="Z8" s="383" t="n"/>
+      <c r="AA8" s="383" t="n"/>
+      <c r="AB8" s="383" t="n"/>
+      <c r="AC8" s="383" t="n"/>
+      <c r="AD8" s="383" t="n"/>
+      <c r="AE8" s="383" t="n"/>
+      <c r="AF8" s="383" t="n"/>
+      <c r="AG8" s="383" t="n"/>
+      <c r="AH8" s="383" t="n"/>
+      <c r="AI8" s="383" t="n"/>
+      <c r="AJ8" s="383" t="n"/>
+      <c r="AK8" s="383" t="n"/>
+      <c r="AL8" s="383" t="n"/>
+      <c r="AM8" s="383" t="n"/>
+      <c r="AN8" s="383" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9">
+      <c r="A9" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B9" s="383" t="n"/>
+      <c r="C9" s="383" t="n"/>
+      <c r="D9" s="383" t="n"/>
+      <c r="E9" s="383" t="n"/>
+      <c r="F9" s="383" t="n"/>
+      <c r="G9" s="383" t="n"/>
+      <c r="H9" s="383" t="n"/>
+      <c r="I9" s="383" t="n"/>
+      <c r="J9" s="383" t="n"/>
+      <c r="K9" s="383" t="n"/>
+      <c r="L9" s="383" t="n"/>
+      <c r="M9" s="383" t="n"/>
+      <c r="N9" s="383" t="n"/>
+      <c r="O9" s="383" t="n"/>
+      <c r="P9" s="383" t="n"/>
+      <c r="Q9" s="383" t="n"/>
+      <c r="R9" s="383" t="n"/>
+      <c r="S9" s="383" t="n"/>
+      <c r="T9" s="383" t="n"/>
+      <c r="U9" s="383" t="n"/>
+      <c r="V9" s="383" t="n"/>
+      <c r="W9" s="383" t="n"/>
+      <c r="X9" s="383" t="n"/>
+      <c r="Y9" s="383" t="n"/>
+      <c r="Z9" s="383" t="n"/>
+      <c r="AA9" s="383" t="n"/>
+      <c r="AB9" s="383" t="n"/>
+      <c r="AC9" s="383" t="n"/>
+      <c r="AD9" s="383" t="n"/>
+      <c r="AE9" s="383" t="n"/>
+      <c r="AF9" s="383" t="n"/>
+      <c r="AG9" s="383" t="n"/>
+      <c r="AH9" s="383" t="n"/>
+      <c r="AI9" s="383" t="n"/>
+      <c r="AJ9" s="383" t="n"/>
+      <c r="AK9" s="383" t="n"/>
+      <c r="AL9" s="383" t="n"/>
+      <c r="AM9" s="383" t="n"/>
+      <c r="AN9" s="383" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10">
+      <c r="A10" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B10" s="383" t="n"/>
+      <c r="C10" s="383" t="n"/>
+      <c r="D10" s="383" t="n"/>
+      <c r="E10" s="383" t="n"/>
+      <c r="F10" s="383" t="n"/>
+      <c r="G10" s="383" t="n"/>
+      <c r="H10" s="383" t="n"/>
+      <c r="I10" s="383" t="n"/>
+      <c r="J10" s="383" t="n"/>
+      <c r="K10" s="383" t="n"/>
+      <c r="L10" s="383" t="n"/>
+      <c r="M10" s="383" t="n"/>
+      <c r="N10" s="383" t="n"/>
+      <c r="O10" s="383" t="n"/>
+      <c r="P10" s="383" t="n"/>
+      <c r="Q10" s="383" t="n"/>
+      <c r="R10" s="383" t="n"/>
+      <c r="S10" s="383" t="n"/>
+      <c r="T10" s="383" t="n"/>
+      <c r="U10" s="383" t="n"/>
+      <c r="V10" s="383" t="n"/>
+      <c r="W10" s="383" t="n"/>
+      <c r="X10" s="383" t="n"/>
+      <c r="Y10" s="383" t="n"/>
+      <c r="Z10" s="383" t="n"/>
+      <c r="AA10" s="383" t="n"/>
+      <c r="AB10" s="383" t="n"/>
+      <c r="AC10" s="383" t="n"/>
+      <c r="AD10" s="383" t="n"/>
+      <c r="AE10" s="383" t="n"/>
+      <c r="AF10" s="383" t="n"/>
+      <c r="AG10" s="383" t="n"/>
+      <c r="AH10" s="383" t="n"/>
+      <c r="AI10" s="383" t="n"/>
+      <c r="AJ10" s="383" t="n"/>
+      <c r="AK10" s="383" t="n"/>
+      <c r="AL10" s="383" t="n"/>
+      <c r="AM10" s="383" t="n"/>
+      <c r="AN10" s="383" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11">
+      <c r="A11" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B11" s="383" t="n"/>
+      <c r="C11" s="383" t="n"/>
+      <c r="D11" s="383" t="n"/>
+      <c r="E11" s="383" t="n"/>
+      <c r="F11" s="383" t="n"/>
+      <c r="G11" s="383" t="n"/>
+      <c r="H11" s="383" t="n"/>
+      <c r="I11" s="383" t="n"/>
+      <c r="J11" s="383" t="n"/>
+      <c r="K11" s="383" t="n"/>
+      <c r="L11" s="383" t="n"/>
+      <c r="M11" s="383" t="n"/>
+      <c r="N11" s="383" t="n"/>
+      <c r="O11" s="383" t="n"/>
+      <c r="P11" s="383" t="n"/>
+      <c r="Q11" s="383" t="n"/>
+      <c r="R11" s="383" t="n"/>
+      <c r="S11" s="383" t="n"/>
+      <c r="T11" s="383" t="n"/>
+      <c r="U11" s="383" t="n"/>
+      <c r="V11" s="383" t="n"/>
+      <c r="W11" s="383" t="n"/>
+      <c r="X11" s="383" t="n"/>
+      <c r="Y11" s="383" t="n"/>
+      <c r="Z11" s="383" t="n"/>
+      <c r="AA11" s="383" t="n"/>
+      <c r="AB11" s="383" t="n"/>
+      <c r="AC11" s="383" t="n"/>
+      <c r="AD11" s="383" t="n"/>
+      <c r="AE11" s="383" t="n"/>
+      <c r="AF11" s="383" t="n"/>
+      <c r="AG11" s="383" t="n"/>
+      <c r="AH11" s="383" t="n"/>
+      <c r="AI11" s="383" t="n"/>
+      <c r="AJ11" s="383" t="n"/>
+      <c r="AK11" s="383" t="n"/>
+      <c r="AL11" s="383" t="n"/>
+      <c r="AM11" s="383" t="n"/>
+      <c r="AN11" s="383" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12">
+      <c r="A12" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B12" s="383" t="n"/>
+      <c r="C12" s="383" t="n"/>
+      <c r="D12" s="383" t="n"/>
+      <c r="E12" s="383" t="n"/>
+      <c r="F12" s="383" t="n"/>
+      <c r="G12" s="383" t="n"/>
+      <c r="H12" s="383" t="n"/>
+      <c r="I12" s="383" t="n"/>
+      <c r="J12" s="383" t="n"/>
+      <c r="K12" s="383" t="n"/>
+      <c r="L12" s="383" t="n"/>
+      <c r="M12" s="383" t="n"/>
+      <c r="N12" s="383" t="n"/>
+      <c r="O12" s="383" t="n"/>
+      <c r="P12" s="383" t="n"/>
+      <c r="Q12" s="383" t="n"/>
+      <c r="R12" s="383" t="n"/>
+      <c r="S12" s="383" t="n"/>
+      <c r="T12" s="383" t="n"/>
+      <c r="U12" s="383" t="n"/>
+      <c r="V12" s="383" t="n"/>
+      <c r="W12" s="383" t="n"/>
+      <c r="X12" s="383" t="n"/>
+      <c r="Y12" s="383" t="n"/>
+      <c r="Z12" s="383" t="n"/>
+      <c r="AA12" s="383" t="n"/>
+      <c r="AB12" s="383" t="n"/>
+      <c r="AC12" s="383" t="n"/>
+      <c r="AD12" s="383" t="n"/>
+      <c r="AE12" s="383" t="n"/>
+      <c r="AF12" s="383" t="n"/>
+      <c r="AG12" s="383" t="n"/>
+      <c r="AH12" s="383" t="n"/>
+      <c r="AI12" s="383" t="n"/>
+      <c r="AJ12" s="383" t="n"/>
+      <c r="AK12" s="383" t="n"/>
+      <c r="AL12" s="383" t="n"/>
+      <c r="AM12" s="383" t="n"/>
+      <c r="AN12" s="383" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13">
+      <c r="A13" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B13" s="383" t="n"/>
+      <c r="C13" s="383" t="n"/>
+      <c r="D13" s="383" t="n"/>
+      <c r="E13" s="383" t="n"/>
+      <c r="F13" s="383" t="n"/>
+      <c r="G13" s="383" t="n"/>
+      <c r="H13" s="383" t="n"/>
+      <c r="I13" s="383" t="n"/>
+      <c r="J13" s="383" t="n"/>
+      <c r="K13" s="383" t="n"/>
+      <c r="L13" s="383" t="n"/>
+      <c r="M13" s="383" t="n"/>
+      <c r="N13" s="383" t="n"/>
+      <c r="O13" s="383" t="n"/>
+      <c r="P13" s="383" t="n"/>
+      <c r="Q13" s="383" t="n"/>
+      <c r="R13" s="383" t="n"/>
+      <c r="S13" s="383" t="n"/>
+      <c r="T13" s="383" t="n"/>
+      <c r="U13" s="383" t="n"/>
+      <c r="V13" s="383" t="n"/>
+      <c r="W13" s="383" t="n"/>
+      <c r="X13" s="383" t="n"/>
+      <c r="Y13" s="383" t="n"/>
+      <c r="Z13" s="383" t="n"/>
+      <c r="AA13" s="383" t="n"/>
+      <c r="AB13" s="383" t="n"/>
+      <c r="AC13" s="383" t="n"/>
+      <c r="AD13" s="383" t="n"/>
+      <c r="AE13" s="383" t="n"/>
+      <c r="AF13" s="383" t="n"/>
+      <c r="AG13" s="383" t="n"/>
+      <c r="AH13" s="383" t="n"/>
+      <c r="AI13" s="383" t="n"/>
+      <c r="AJ13" s="383" t="n"/>
+      <c r="AK13" s="383" t="n"/>
+      <c r="AL13" s="383" t="n"/>
+      <c r="AM13" s="383" t="n"/>
+      <c r="AN13" s="383" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14">
+      <c r="A14" s="383">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B14" s="383" t="n"/>
+      <c r="C14" s="383" t="n"/>
+      <c r="D14" s="383" t="n"/>
+      <c r="E14" s="383" t="n"/>
+      <c r="F14" s="383" t="n"/>
+      <c r="G14" s="383" t="n"/>
+      <c r="H14" s="383" t="n"/>
+      <c r="I14" s="383" t="n"/>
+      <c r="J14" s="383" t="n"/>
+      <c r="K14" s="383" t="n"/>
+      <c r="L14" s="383" t="n"/>
+      <c r="M14" s="383" t="n"/>
+      <c r="N14" s="383" t="n"/>
+      <c r="O14" s="383" t="n"/>
+      <c r="P14" s="383" t="n"/>
+      <c r="Q14" s="383" t="n"/>
+      <c r="R14" s="383" t="n"/>
+      <c r="S14" s="383" t="n"/>
+      <c r="T14" s="383" t="n"/>
+      <c r="U14" s="383" t="n"/>
+      <c r="V14" s="383" t="n"/>
+      <c r="W14" s="383" t="n"/>
+      <c r="X14" s="383" t="n"/>
+      <c r="Y14" s="383" t="n"/>
+      <c r="Z14" s="383" t="n"/>
+      <c r="AA14" s="383" t="n"/>
+      <c r="AB14" s="383" t="n"/>
+      <c r="AC14" s="383" t="n"/>
+      <c r="AD14" s="383" t="n"/>
+      <c r="AE14" s="383" t="n"/>
+      <c r="AF14" s="383" t="n"/>
+      <c r="AG14" s="383" t="n"/>
+      <c r="AH14" s="383" t="n"/>
+      <c r="AI14" s="383" t="n"/>
+      <c r="AJ14" s="383" t="n"/>
+      <c r="AK14" s="383" t="n"/>
+      <c r="AL14" s="383" t="n"/>
+      <c r="AM14" s="383" t="n"/>
+      <c r="AN14" s="383" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -7005,7 +8244,8 @@
       <formula1>=LISTS!$D$2:$D$11</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7018,30 +8258,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="329" min="1" max="1"/>
-    <col width="52" customWidth="1" style="329" min="2" max="2"/>
-    <col width="65" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="18" customWidth="1" style="329" min="6" max="6"/>
-    <col width="24" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="337" t="inlineStr">
+      <c r="A1" s="389" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="411" t="n"/>
+      <c r="C1" s="411" t="n"/>
+      <c r="D1" s="411" t="n"/>
+      <c r="E1" s="411" t="n"/>
+      <c r="F1" s="411" t="n"/>
+      <c r="G1" s="412" t="n"/>
+      <c r="H1" s="347" t="n"/>
+      <c r="I1" s="347" t="n"/>
+      <c r="J1" s="347" t="n"/>
+      <c r="K1" s="347" t="n"/>
+      <c r="L1" s="347" t="n"/>
+      <c r="M1" s="347" t="n"/>
+      <c r="N1" s="347" t="n"/>
+      <c r="O1" s="347" t="n"/>
+      <c r="P1" s="347" t="n"/>
+      <c r="Q1" s="347" t="n"/>
+      <c r="R1" s="347" t="n"/>
+      <c r="S1" s="347" t="n"/>
+      <c r="T1" s="347" t="n"/>
+      <c r="U1" s="347" t="n"/>
+      <c r="V1" s="347" t="n"/>
+      <c r="W1" s="347" t="n"/>
+      <c r="X1" s="347" t="n"/>
+      <c r="Y1" s="347" t="n"/>
+      <c r="Z1" s="347" t="n"/>
+      <c r="AA1" s="347" t="n"/>
+      <c r="AB1" s="347" t="n"/>
+      <c r="AC1" s="347" t="n"/>
+      <c r="AD1" s="347" t="n"/>
+      <c r="AE1" s="347" t="n"/>
+      <c r="AF1" s="347" t="n"/>
+      <c r="AG1" s="347" t="n"/>
+      <c r="AH1" s="347" t="n"/>
+      <c r="AI1" s="347" t="n"/>
+      <c r="AJ1" s="347" t="n"/>
+      <c r="AK1" s="347" t="n"/>
+      <c r="AL1" s="347" t="n"/>
+      <c r="AM1" s="347" t="n"/>
+      <c r="AN1" s="347" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="338" t="inlineStr">
@@ -7049,49 +8355,197 @@
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
+      <c r="H2" s="347" t="n"/>
+      <c r="I2" s="347" t="n"/>
+      <c r="J2" s="347" t="n"/>
+      <c r="K2" s="347" t="n"/>
+      <c r="L2" s="347" t="n"/>
+      <c r="M2" s="347" t="n"/>
+      <c r="N2" s="347" t="n"/>
+      <c r="O2" s="347" t="n"/>
+      <c r="P2" s="347" t="n"/>
+      <c r="Q2" s="347" t="n"/>
+      <c r="R2" s="347" t="n"/>
+      <c r="S2" s="347" t="n"/>
+      <c r="T2" s="347" t="n"/>
+      <c r="U2" s="347" t="n"/>
+      <c r="V2" s="347" t="n"/>
+      <c r="W2" s="347" t="n"/>
+      <c r="X2" s="347" t="n"/>
+      <c r="Y2" s="347" t="n"/>
+      <c r="Z2" s="347" t="n"/>
+      <c r="AA2" s="347" t="n"/>
+      <c r="AB2" s="347" t="n"/>
+      <c r="AC2" s="347" t="n"/>
+      <c r="AD2" s="347" t="n"/>
+      <c r="AE2" s="347" t="n"/>
+      <c r="AF2" s="347" t="n"/>
+      <c r="AG2" s="347" t="n"/>
+      <c r="AH2" s="347" t="n"/>
+      <c r="AI2" s="347" t="n"/>
+      <c r="AJ2" s="347" t="n"/>
+      <c r="AK2" s="347" t="n"/>
+      <c r="AL2" s="347" t="n"/>
+      <c r="AM2" s="347" t="n"/>
+      <c r="AN2" s="347" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="347" t="n"/>
+      <c r="B3" s="347" t="n"/>
+      <c r="C3" s="347" t="n"/>
+      <c r="D3" s="347" t="n"/>
+      <c r="E3" s="347" t="n"/>
+      <c r="F3" s="347" t="n"/>
+      <c r="G3" s="347" t="n"/>
+      <c r="H3" s="347" t="n"/>
+      <c r="I3" s="347" t="n"/>
+      <c r="J3" s="347" t="n"/>
+      <c r="K3" s="347" t="n"/>
+      <c r="L3" s="347" t="n"/>
+      <c r="M3" s="347" t="n"/>
+      <c r="N3" s="347" t="n"/>
+      <c r="O3" s="347" t="n"/>
+      <c r="P3" s="347" t="n"/>
+      <c r="Q3" s="347" t="n"/>
+      <c r="R3" s="347" t="n"/>
+      <c r="S3" s="347" t="n"/>
+      <c r="T3" s="347" t="n"/>
+      <c r="U3" s="347" t="n"/>
+      <c r="V3" s="347" t="n"/>
+      <c r="W3" s="347" t="n"/>
+      <c r="X3" s="347" t="n"/>
+      <c r="Y3" s="347" t="n"/>
+      <c r="Z3" s="347" t="n"/>
+      <c r="AA3" s="347" t="n"/>
+      <c r="AB3" s="347" t="n"/>
+      <c r="AC3" s="347" t="n"/>
+      <c r="AD3" s="347" t="n"/>
+      <c r="AE3" s="347" t="n"/>
+      <c r="AF3" s="347" t="n"/>
+      <c r="AG3" s="347" t="n"/>
+      <c r="AH3" s="347" t="n"/>
+      <c r="AI3" s="347" t="n"/>
+      <c r="AJ3" s="347" t="n"/>
+      <c r="AK3" s="347" t="n"/>
+      <c r="AL3" s="347" t="n"/>
+      <c r="AM3" s="347" t="n"/>
+      <c r="AN3" s="347" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="388" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="388" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="388" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="347" t="n"/>
+      <c r="E4" s="347" t="n"/>
+      <c r="F4" s="347" t="n"/>
+      <c r="G4" s="347" t="n"/>
+      <c r="H4" s="347" t="n"/>
+      <c r="I4" s="347" t="n"/>
+      <c r="J4" s="347" t="n"/>
+      <c r="K4" s="347" t="n"/>
+      <c r="L4" s="347" t="n"/>
+      <c r="M4" s="347" t="n"/>
+      <c r="N4" s="347" t="n"/>
+      <c r="O4" s="347" t="n"/>
+      <c r="P4" s="347" t="n"/>
+      <c r="Q4" s="347" t="n"/>
+      <c r="R4" s="347" t="n"/>
+      <c r="S4" s="347" t="n"/>
+      <c r="T4" s="347" t="n"/>
+      <c r="U4" s="347" t="n"/>
+      <c r="V4" s="347" t="n"/>
+      <c r="W4" s="347" t="n"/>
+      <c r="X4" s="347" t="n"/>
+      <c r="Y4" s="347" t="n"/>
+      <c r="Z4" s="347" t="n"/>
+      <c r="AA4" s="347" t="n"/>
+      <c r="AB4" s="347" t="n"/>
+      <c r="AC4" s="347" t="n"/>
+      <c r="AD4" s="347" t="n"/>
+      <c r="AE4" s="347" t="n"/>
+      <c r="AF4" s="347" t="n"/>
+      <c r="AG4" s="347" t="n"/>
+      <c r="AH4" s="347" t="n"/>
+      <c r="AI4" s="347" t="n"/>
+      <c r="AJ4" s="347" t="n"/>
+      <c r="AK4" s="347" t="n"/>
+      <c r="AL4" s="347" t="n"/>
+      <c r="AM4" s="347" t="n"/>
+      <c r="AN4" s="347" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="315" t="inlineStr">
+      <c r="A5" s="390" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="316" t="inlineStr">
+      <c r="B5" s="391" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="316" t="inlineStr">
+      <c r="C5" s="391" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="347" t="n"/>
+      <c r="E5" s="347" t="n"/>
+      <c r="F5" s="347" t="n"/>
+      <c r="G5" s="347" t="n"/>
+      <c r="H5" s="347" t="n"/>
+      <c r="I5" s="347" t="n"/>
+      <c r="J5" s="347" t="n"/>
+      <c r="K5" s="347" t="n"/>
+      <c r="L5" s="347" t="n"/>
+      <c r="M5" s="347" t="n"/>
+      <c r="N5" s="347" t="n"/>
+      <c r="O5" s="347" t="n"/>
+      <c r="P5" s="347" t="n"/>
+      <c r="Q5" s="347" t="n"/>
+      <c r="R5" s="347" t="n"/>
+      <c r="S5" s="347" t="n"/>
+      <c r="T5" s="347" t="n"/>
+      <c r="U5" s="347" t="n"/>
+      <c r="V5" s="347" t="n"/>
+      <c r="W5" s="347" t="n"/>
+      <c r="X5" s="347" t="n"/>
+      <c r="Y5" s="347" t="n"/>
+      <c r="Z5" s="347" t="n"/>
+      <c r="AA5" s="347" t="n"/>
+      <c r="AB5" s="347" t="n"/>
+      <c r="AC5" s="347" t="n"/>
+      <c r="AD5" s="347" t="n"/>
+      <c r="AE5" s="347" t="n"/>
+      <c r="AF5" s="347" t="n"/>
+      <c r="AG5" s="347" t="n"/>
+      <c r="AH5" s="347" t="n"/>
+      <c r="AI5" s="347" t="n"/>
+      <c r="AJ5" s="347" t="n"/>
+      <c r="AK5" s="347" t="n"/>
+      <c r="AL5" s="347" t="n"/>
+      <c r="AM5" s="347" t="n"/>
+      <c r="AN5" s="347" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="315" t="inlineStr">
+      <c r="A6" s="390" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="316" t="inlineStr">
+      <c r="B6" s="391" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -7099,7 +8553,7 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="316" t="inlineStr">
+      <c r="C6" s="391" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -7107,142 +8561,475 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="347" t="n"/>
+      <c r="E6" s="347" t="n"/>
+      <c r="F6" s="347" t="n"/>
+      <c r="G6" s="347" t="n"/>
+      <c r="H6" s="347" t="n"/>
+      <c r="I6" s="347" t="n"/>
+      <c r="J6" s="347" t="n"/>
+      <c r="K6" s="347" t="n"/>
+      <c r="L6" s="347" t="n"/>
+      <c r="M6" s="347" t="n"/>
+      <c r="N6" s="347" t="n"/>
+      <c r="O6" s="347" t="n"/>
+      <c r="P6" s="347" t="n"/>
+      <c r="Q6" s="347" t="n"/>
+      <c r="R6" s="347" t="n"/>
+      <c r="S6" s="347" t="n"/>
+      <c r="T6" s="347" t="n"/>
+      <c r="U6" s="347" t="n"/>
+      <c r="V6" s="347" t="n"/>
+      <c r="W6" s="347" t="n"/>
+      <c r="X6" s="347" t="n"/>
+      <c r="Y6" s="347" t="n"/>
+      <c r="Z6" s="347" t="n"/>
+      <c r="AA6" s="347" t="n"/>
+      <c r="AB6" s="347" t="n"/>
+      <c r="AC6" s="347" t="n"/>
+      <c r="AD6" s="347" t="n"/>
+      <c r="AE6" s="347" t="n"/>
+      <c r="AF6" s="347" t="n"/>
+      <c r="AG6" s="347" t="n"/>
+      <c r="AH6" s="347" t="n"/>
+      <c r="AI6" s="347" t="n"/>
+      <c r="AJ6" s="347" t="n"/>
+      <c r="AK6" s="347" t="n"/>
+      <c r="AL6" s="347" t="n"/>
+      <c r="AM6" s="347" t="n"/>
+      <c r="AN6" s="347" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="315" t="inlineStr">
+      <c r="A7" s="390" t="inlineStr">
         <is>
           <t>SOP-401</t>
         </is>
       </c>
-      <c r="B7" s="316" t="inlineStr">
+      <c r="B7" s="391" t="inlineStr">
         <is>
           <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="316" t="inlineStr">
+      <c r="C7" s="391" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
         </is>
       </c>
+      <c r="D7" s="347" t="n"/>
+      <c r="E7" s="347" t="n"/>
+      <c r="F7" s="347" t="n"/>
+      <c r="G7" s="347" t="n"/>
+      <c r="H7" s="347" t="n"/>
+      <c r="I7" s="347" t="n"/>
+      <c r="J7" s="347" t="n"/>
+      <c r="K7" s="347" t="n"/>
+      <c r="L7" s="347" t="n"/>
+      <c r="M7" s="347" t="n"/>
+      <c r="N7" s="347" t="n"/>
+      <c r="O7" s="347" t="n"/>
+      <c r="P7" s="347" t="n"/>
+      <c r="Q7" s="347" t="n"/>
+      <c r="R7" s="347" t="n"/>
+      <c r="S7" s="347" t="n"/>
+      <c r="T7" s="347" t="n"/>
+      <c r="U7" s="347" t="n"/>
+      <c r="V7" s="347" t="n"/>
+      <c r="W7" s="347" t="n"/>
+      <c r="X7" s="347" t="n"/>
+      <c r="Y7" s="347" t="n"/>
+      <c r="Z7" s="347" t="n"/>
+      <c r="AA7" s="347" t="n"/>
+      <c r="AB7" s="347" t="n"/>
+      <c r="AC7" s="347" t="n"/>
+      <c r="AD7" s="347" t="n"/>
+      <c r="AE7" s="347" t="n"/>
+      <c r="AF7" s="347" t="n"/>
+      <c r="AG7" s="347" t="n"/>
+      <c r="AH7" s="347" t="n"/>
+      <c r="AI7" s="347" t="n"/>
+      <c r="AJ7" s="347" t="n"/>
+      <c r="AK7" s="347" t="n"/>
+      <c r="AL7" s="347" t="n"/>
+      <c r="AM7" s="347" t="n"/>
+      <c r="AN7" s="347" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="315" t="inlineStr">
+      <c r="A8" s="354" t="inlineStr">
         <is>
           <t>WI-206</t>
         </is>
       </c>
-      <c r="B8" s="316" t="inlineStr">
+      <c r="B8" s="392" t="inlineStr">
         <is>
           <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
         </is>
       </c>
-      <c r="C8" s="316" t="inlineStr">
+      <c r="C8" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
         </is>
       </c>
+      <c r="D8" s="383" t="n"/>
+      <c r="E8" s="383" t="n"/>
+      <c r="F8" s="383" t="n"/>
+      <c r="G8" s="383" t="n"/>
+      <c r="H8" s="383" t="n"/>
+      <c r="I8" s="383" t="n"/>
+      <c r="J8" s="383" t="n"/>
+      <c r="K8" s="383" t="n"/>
+      <c r="L8" s="383" t="n"/>
+      <c r="M8" s="383" t="n"/>
+      <c r="N8" s="383" t="n"/>
+      <c r="O8" s="383" t="n"/>
+      <c r="P8" s="383" t="n"/>
+      <c r="Q8" s="383" t="n"/>
+      <c r="R8" s="383" t="n"/>
+      <c r="S8" s="383" t="n"/>
+      <c r="T8" s="383" t="n"/>
+      <c r="U8" s="383" t="n"/>
+      <c r="V8" s="383" t="n"/>
+      <c r="W8" s="383" t="n"/>
+      <c r="X8" s="383" t="n"/>
+      <c r="Y8" s="383" t="n"/>
+      <c r="Z8" s="383" t="n"/>
+      <c r="AA8" s="383" t="n"/>
+      <c r="AB8" s="383" t="n"/>
+      <c r="AC8" s="383" t="n"/>
+      <c r="AD8" s="383" t="n"/>
+      <c r="AE8" s="383" t="n"/>
+      <c r="AF8" s="383" t="n"/>
+      <c r="AG8" s="383" t="n"/>
+      <c r="AH8" s="383" t="n"/>
+      <c r="AI8" s="383" t="n"/>
+      <c r="AJ8" s="383" t="n"/>
+      <c r="AK8" s="383" t="n"/>
+      <c r="AL8" s="383" t="n"/>
+      <c r="AM8" s="383" t="n"/>
+      <c r="AN8" s="383" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="315" t="inlineStr">
+      <c r="A9" s="354" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B9" s="316" t="inlineStr">
+      <c r="B9" s="392" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C9" s="316" t="inlineStr">
+      <c r="C9" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
+      <c r="D9" s="383" t="n"/>
+      <c r="E9" s="383" t="n"/>
+      <c r="F9" s="383" t="n"/>
+      <c r="G9" s="383" t="n"/>
+      <c r="H9" s="383" t="n"/>
+      <c r="I9" s="383" t="n"/>
+      <c r="J9" s="383" t="n"/>
+      <c r="K9" s="383" t="n"/>
+      <c r="L9" s="383" t="n"/>
+      <c r="M9" s="383" t="n"/>
+      <c r="N9" s="383" t="n"/>
+      <c r="O9" s="383" t="n"/>
+      <c r="P9" s="383" t="n"/>
+      <c r="Q9" s="383" t="n"/>
+      <c r="R9" s="383" t="n"/>
+      <c r="S9" s="383" t="n"/>
+      <c r="T9" s="383" t="n"/>
+      <c r="U9" s="383" t="n"/>
+      <c r="V9" s="383" t="n"/>
+      <c r="W9" s="383" t="n"/>
+      <c r="X9" s="383" t="n"/>
+      <c r="Y9" s="383" t="n"/>
+      <c r="Z9" s="383" t="n"/>
+      <c r="AA9" s="383" t="n"/>
+      <c r="AB9" s="383" t="n"/>
+      <c r="AC9" s="383" t="n"/>
+      <c r="AD9" s="383" t="n"/>
+      <c r="AE9" s="383" t="n"/>
+      <c r="AF9" s="383" t="n"/>
+      <c r="AG9" s="383" t="n"/>
+      <c r="AH9" s="383" t="n"/>
+      <c r="AI9" s="383" t="n"/>
+      <c r="AJ9" s="383" t="n"/>
+      <c r="AK9" s="383" t="n"/>
+      <c r="AL9" s="383" t="n"/>
+      <c r="AM9" s="383" t="n"/>
+      <c r="AN9" s="383" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="315" t="inlineStr">
+      <c r="A10" s="354" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B10" s="316" t="inlineStr">
+      <c r="B10" s="392" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C10" s="316" t="inlineStr">
+      <c r="C10" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
+      <c r="D10" s="383" t="n"/>
+      <c r="E10" s="383" t="n"/>
+      <c r="F10" s="383" t="n"/>
+      <c r="G10" s="383" t="n"/>
+      <c r="H10" s="383" t="n"/>
+      <c r="I10" s="383" t="n"/>
+      <c r="J10" s="383" t="n"/>
+      <c r="K10" s="383" t="n"/>
+      <c r="L10" s="383" t="n"/>
+      <c r="M10" s="383" t="n"/>
+      <c r="N10" s="383" t="n"/>
+      <c r="O10" s="383" t="n"/>
+      <c r="P10" s="383" t="n"/>
+      <c r="Q10" s="383" t="n"/>
+      <c r="R10" s="383" t="n"/>
+      <c r="S10" s="383" t="n"/>
+      <c r="T10" s="383" t="n"/>
+      <c r="U10" s="383" t="n"/>
+      <c r="V10" s="383" t="n"/>
+      <c r="W10" s="383" t="n"/>
+      <c r="X10" s="383" t="n"/>
+      <c r="Y10" s="383" t="n"/>
+      <c r="Z10" s="383" t="n"/>
+      <c r="AA10" s="383" t="n"/>
+      <c r="AB10" s="383" t="n"/>
+      <c r="AC10" s="383" t="n"/>
+      <c r="AD10" s="383" t="n"/>
+      <c r="AE10" s="383" t="n"/>
+      <c r="AF10" s="383" t="n"/>
+      <c r="AG10" s="383" t="n"/>
+      <c r="AH10" s="383" t="n"/>
+      <c r="AI10" s="383" t="n"/>
+      <c r="AJ10" s="383" t="n"/>
+      <c r="AK10" s="383" t="n"/>
+      <c r="AL10" s="383" t="n"/>
+      <c r="AM10" s="383" t="n"/>
+      <c r="AN10" s="383" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="315" t="inlineStr">
+      <c r="A11" s="354" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B11" s="316" t="inlineStr">
+      <c r="B11" s="392" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C11" s="316" t="inlineStr">
+      <c r="C11" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
+      <c r="D11" s="383" t="n"/>
+      <c r="E11" s="383" t="n"/>
+      <c r="F11" s="383" t="n"/>
+      <c r="G11" s="383" t="n"/>
+      <c r="H11" s="383" t="n"/>
+      <c r="I11" s="383" t="n"/>
+      <c r="J11" s="383" t="n"/>
+      <c r="K11" s="383" t="n"/>
+      <c r="L11" s="383" t="n"/>
+      <c r="M11" s="383" t="n"/>
+      <c r="N11" s="383" t="n"/>
+      <c r="O11" s="383" t="n"/>
+      <c r="P11" s="383" t="n"/>
+      <c r="Q11" s="383" t="n"/>
+      <c r="R11" s="383" t="n"/>
+      <c r="S11" s="383" t="n"/>
+      <c r="T11" s="383" t="n"/>
+      <c r="U11" s="383" t="n"/>
+      <c r="V11" s="383" t="n"/>
+      <c r="W11" s="383" t="n"/>
+      <c r="X11" s="383" t="n"/>
+      <c r="Y11" s="383" t="n"/>
+      <c r="Z11" s="383" t="n"/>
+      <c r="AA11" s="383" t="n"/>
+      <c r="AB11" s="383" t="n"/>
+      <c r="AC11" s="383" t="n"/>
+      <c r="AD11" s="383" t="n"/>
+      <c r="AE11" s="383" t="n"/>
+      <c r="AF11" s="383" t="n"/>
+      <c r="AG11" s="383" t="n"/>
+      <c r="AH11" s="383" t="n"/>
+      <c r="AI11" s="383" t="n"/>
+      <c r="AJ11" s="383" t="n"/>
+      <c r="AK11" s="383" t="n"/>
+      <c r="AL11" s="383" t="n"/>
+      <c r="AM11" s="383" t="n"/>
+      <c r="AN11" s="383" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="315" t="inlineStr">
+      <c r="A12" s="354" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B12" s="316" t="inlineStr">
+      <c r="B12" s="392" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C12" s="316" t="inlineStr">
+      <c r="C12" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
+      <c r="D12" s="383" t="n"/>
+      <c r="E12" s="383" t="n"/>
+      <c r="F12" s="383" t="n"/>
+      <c r="G12" s="383" t="n"/>
+      <c r="H12" s="383" t="n"/>
+      <c r="I12" s="383" t="n"/>
+      <c r="J12" s="383" t="n"/>
+      <c r="K12" s="383" t="n"/>
+      <c r="L12" s="383" t="n"/>
+      <c r="M12" s="383" t="n"/>
+      <c r="N12" s="383" t="n"/>
+      <c r="O12" s="383" t="n"/>
+      <c r="P12" s="383" t="n"/>
+      <c r="Q12" s="383" t="n"/>
+      <c r="R12" s="383" t="n"/>
+      <c r="S12" s="383" t="n"/>
+      <c r="T12" s="383" t="n"/>
+      <c r="U12" s="383" t="n"/>
+      <c r="V12" s="383" t="n"/>
+      <c r="W12" s="383" t="n"/>
+      <c r="X12" s="383" t="n"/>
+      <c r="Y12" s="383" t="n"/>
+      <c r="Z12" s="383" t="n"/>
+      <c r="AA12" s="383" t="n"/>
+      <c r="AB12" s="383" t="n"/>
+      <c r="AC12" s="383" t="n"/>
+      <c r="AD12" s="383" t="n"/>
+      <c r="AE12" s="383" t="n"/>
+      <c r="AF12" s="383" t="n"/>
+      <c r="AG12" s="383" t="n"/>
+      <c r="AH12" s="383" t="n"/>
+      <c r="AI12" s="383" t="n"/>
+      <c r="AJ12" s="383" t="n"/>
+      <c r="AK12" s="383" t="n"/>
+      <c r="AL12" s="383" t="n"/>
+      <c r="AM12" s="383" t="n"/>
+      <c r="AN12" s="383" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="383" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="383" t="inlineStr">
         <is>
           <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="383" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D13" s="383" t="n"/>
+      <c r="E13" s="383" t="n"/>
+      <c r="F13" s="383" t="n"/>
+      <c r="G13" s="383" t="n"/>
+      <c r="H13" s="383" t="n"/>
+      <c r="I13" s="383" t="n"/>
+      <c r="J13" s="383" t="n"/>
+      <c r="K13" s="383" t="n"/>
+      <c r="L13" s="383" t="n"/>
+      <c r="M13" s="383" t="n"/>
+      <c r="N13" s="383" t="n"/>
+      <c r="O13" s="383" t="n"/>
+      <c r="P13" s="383" t="n"/>
+      <c r="Q13" s="383" t="n"/>
+      <c r="R13" s="383" t="n"/>
+      <c r="S13" s="383" t="n"/>
+      <c r="T13" s="383" t="n"/>
+      <c r="U13" s="383" t="n"/>
+      <c r="V13" s="383" t="n"/>
+      <c r="W13" s="383" t="n"/>
+      <c r="X13" s="383" t="n"/>
+      <c r="Y13" s="383" t="n"/>
+      <c r="Z13" s="383" t="n"/>
+      <c r="AA13" s="383" t="n"/>
+      <c r="AB13" s="383" t="n"/>
+      <c r="AC13" s="383" t="n"/>
+      <c r="AD13" s="383" t="n"/>
+      <c r="AE13" s="383" t="n"/>
+      <c r="AF13" s="383" t="n"/>
+      <c r="AG13" s="383" t="n"/>
+      <c r="AH13" s="383" t="n"/>
+      <c r="AI13" s="383" t="n"/>
+      <c r="AJ13" s="383" t="n"/>
+      <c r="AK13" s="383" t="n"/>
+      <c r="AL13" s="383" t="n"/>
+      <c r="AM13" s="383" t="n"/>
+      <c r="AN13" s="383" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="383" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="383" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="383" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D14" s="383" t="n"/>
+      <c r="E14" s="383" t="n"/>
+      <c r="F14" s="383" t="n"/>
+      <c r="G14" s="383" t="n"/>
+      <c r="H14" s="383" t="n"/>
+      <c r="I14" s="383" t="n"/>
+      <c r="J14" s="383" t="n"/>
+      <c r="K14" s="383" t="n"/>
+      <c r="L14" s="383" t="n"/>
+      <c r="M14" s="383" t="n"/>
+      <c r="N14" s="383" t="n"/>
+      <c r="O14" s="383" t="n"/>
+      <c r="P14" s="383" t="n"/>
+      <c r="Q14" s="383" t="n"/>
+      <c r="R14" s="383" t="n"/>
+      <c r="S14" s="383" t="n"/>
+      <c r="T14" s="383" t="n"/>
+      <c r="U14" s="383" t="n"/>
+      <c r="V14" s="383" t="n"/>
+      <c r="W14" s="383" t="n"/>
+      <c r="X14" s="383" t="n"/>
+      <c r="Y14" s="383" t="n"/>
+      <c r="Z14" s="383" t="n"/>
+      <c r="AA14" s="383" t="n"/>
+      <c r="AB14" s="383" t="n"/>
+      <c r="AC14" s="383" t="n"/>
+      <c r="AD14" s="383" t="n"/>
+      <c r="AE14" s="383" t="n"/>
+      <c r="AF14" s="383" t="n"/>
+      <c r="AG14" s="383" t="n"/>
+      <c r="AH14" s="383" t="n"/>
+      <c r="AI14" s="383" t="n"/>
+      <c r="AJ14" s="383" t="n"/>
+      <c r="AK14" s="383" t="n"/>
+      <c r="AL14" s="383" t="n"/>
+      <c r="AM14" s="383" t="n"/>
+      <c r="AN14" s="383" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -7265,7 +9052,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7275,30 +9063,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="329" min="1" max="1"/>
-    <col width="52" customWidth="1" style="329" min="2" max="2"/>
-    <col width="65" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="18" customWidth="1" style="329" min="6" max="6"/>
-    <col width="24" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="337" t="inlineStr">
+      <c r="A1" s="389" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="411" t="n"/>
+      <c r="C1" s="411" t="n"/>
+      <c r="D1" s="411" t="n"/>
+      <c r="E1" s="411" t="n"/>
+      <c r="F1" s="411" t="n"/>
+      <c r="G1" s="412" t="n"/>
+      <c r="H1" s="347" t="n"/>
+      <c r="I1" s="347" t="n"/>
+      <c r="J1" s="347" t="n"/>
+      <c r="K1" s="347" t="n"/>
+      <c r="L1" s="347" t="n"/>
+      <c r="M1" s="347" t="n"/>
+      <c r="N1" s="347" t="n"/>
+      <c r="O1" s="347" t="n"/>
+      <c r="P1" s="347" t="n"/>
+      <c r="Q1" s="347" t="n"/>
+      <c r="R1" s="347" t="n"/>
+      <c r="S1" s="347" t="n"/>
+      <c r="T1" s="347" t="n"/>
+      <c r="U1" s="347" t="n"/>
+      <c r="V1" s="347" t="n"/>
+      <c r="W1" s="347" t="n"/>
+      <c r="X1" s="347" t="n"/>
+      <c r="Y1" s="347" t="n"/>
+      <c r="Z1" s="347" t="n"/>
+      <c r="AA1" s="347" t="n"/>
+      <c r="AB1" s="347" t="n"/>
+      <c r="AC1" s="347" t="n"/>
+      <c r="AD1" s="347" t="n"/>
+      <c r="AE1" s="347" t="n"/>
+      <c r="AF1" s="347" t="n"/>
+      <c r="AG1" s="347" t="n"/>
+      <c r="AH1" s="347" t="n"/>
+      <c r="AI1" s="347" t="n"/>
+      <c r="AJ1" s="347" t="n"/>
+      <c r="AK1" s="347" t="n"/>
+      <c r="AL1" s="347" t="n"/>
+      <c r="AM1" s="347" t="n"/>
+      <c r="AN1" s="347" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="338" t="inlineStr">
@@ -7306,49 +9160,197 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
+      <c r="H2" s="347" t="n"/>
+      <c r="I2" s="347" t="n"/>
+      <c r="J2" s="347" t="n"/>
+      <c r="K2" s="347" t="n"/>
+      <c r="L2" s="347" t="n"/>
+      <c r="M2" s="347" t="n"/>
+      <c r="N2" s="347" t="n"/>
+      <c r="O2" s="347" t="n"/>
+      <c r="P2" s="347" t="n"/>
+      <c r="Q2" s="347" t="n"/>
+      <c r="R2" s="347" t="n"/>
+      <c r="S2" s="347" t="n"/>
+      <c r="T2" s="347" t="n"/>
+      <c r="U2" s="347" t="n"/>
+      <c r="V2" s="347" t="n"/>
+      <c r="W2" s="347" t="n"/>
+      <c r="X2" s="347" t="n"/>
+      <c r="Y2" s="347" t="n"/>
+      <c r="Z2" s="347" t="n"/>
+      <c r="AA2" s="347" t="n"/>
+      <c r="AB2" s="347" t="n"/>
+      <c r="AC2" s="347" t="n"/>
+      <c r="AD2" s="347" t="n"/>
+      <c r="AE2" s="347" t="n"/>
+      <c r="AF2" s="347" t="n"/>
+      <c r="AG2" s="347" t="n"/>
+      <c r="AH2" s="347" t="n"/>
+      <c r="AI2" s="347" t="n"/>
+      <c r="AJ2" s="347" t="n"/>
+      <c r="AK2" s="347" t="n"/>
+      <c r="AL2" s="347" t="n"/>
+      <c r="AM2" s="347" t="n"/>
+      <c r="AN2" s="347" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="347" t="n"/>
+      <c r="B3" s="347" t="n"/>
+      <c r="C3" s="347" t="n"/>
+      <c r="D3" s="347" t="n"/>
+      <c r="E3" s="347" t="n"/>
+      <c r="F3" s="347" t="n"/>
+      <c r="G3" s="347" t="n"/>
+      <c r="H3" s="347" t="n"/>
+      <c r="I3" s="347" t="n"/>
+      <c r="J3" s="347" t="n"/>
+      <c r="K3" s="347" t="n"/>
+      <c r="L3" s="347" t="n"/>
+      <c r="M3" s="347" t="n"/>
+      <c r="N3" s="347" t="n"/>
+      <c r="O3" s="347" t="n"/>
+      <c r="P3" s="347" t="n"/>
+      <c r="Q3" s="347" t="n"/>
+      <c r="R3" s="347" t="n"/>
+      <c r="S3" s="347" t="n"/>
+      <c r="T3" s="347" t="n"/>
+      <c r="U3" s="347" t="n"/>
+      <c r="V3" s="347" t="n"/>
+      <c r="W3" s="347" t="n"/>
+      <c r="X3" s="347" t="n"/>
+      <c r="Y3" s="347" t="n"/>
+      <c r="Z3" s="347" t="n"/>
+      <c r="AA3" s="347" t="n"/>
+      <c r="AB3" s="347" t="n"/>
+      <c r="AC3" s="347" t="n"/>
+      <c r="AD3" s="347" t="n"/>
+      <c r="AE3" s="347" t="n"/>
+      <c r="AF3" s="347" t="n"/>
+      <c r="AG3" s="347" t="n"/>
+      <c r="AH3" s="347" t="n"/>
+      <c r="AI3" s="347" t="n"/>
+      <c r="AJ3" s="347" t="n"/>
+      <c r="AK3" s="347" t="n"/>
+      <c r="AL3" s="347" t="n"/>
+      <c r="AM3" s="347" t="n"/>
+      <c r="AN3" s="347" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="388" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="388" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="388" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="347" t="n"/>
+      <c r="E4" s="347" t="n"/>
+      <c r="F4" s="347" t="n"/>
+      <c r="G4" s="347" t="n"/>
+      <c r="H4" s="347" t="n"/>
+      <c r="I4" s="347" t="n"/>
+      <c r="J4" s="347" t="n"/>
+      <c r="K4" s="347" t="n"/>
+      <c r="L4" s="347" t="n"/>
+      <c r="M4" s="347" t="n"/>
+      <c r="N4" s="347" t="n"/>
+      <c r="O4" s="347" t="n"/>
+      <c r="P4" s="347" t="n"/>
+      <c r="Q4" s="347" t="n"/>
+      <c r="R4" s="347" t="n"/>
+      <c r="S4" s="347" t="n"/>
+      <c r="T4" s="347" t="n"/>
+      <c r="U4" s="347" t="n"/>
+      <c r="V4" s="347" t="n"/>
+      <c r="W4" s="347" t="n"/>
+      <c r="X4" s="347" t="n"/>
+      <c r="Y4" s="347" t="n"/>
+      <c r="Z4" s="347" t="n"/>
+      <c r="AA4" s="347" t="n"/>
+      <c r="AB4" s="347" t="n"/>
+      <c r="AC4" s="347" t="n"/>
+      <c r="AD4" s="347" t="n"/>
+      <c r="AE4" s="347" t="n"/>
+      <c r="AF4" s="347" t="n"/>
+      <c r="AG4" s="347" t="n"/>
+      <c r="AH4" s="347" t="n"/>
+      <c r="AI4" s="347" t="n"/>
+      <c r="AJ4" s="347" t="n"/>
+      <c r="AK4" s="347" t="n"/>
+      <c r="AL4" s="347" t="n"/>
+      <c r="AM4" s="347" t="n"/>
+      <c r="AN4" s="347" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="315" t="inlineStr">
+      <c r="A5" s="390" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="316" t="inlineStr">
+      <c r="B5" s="391" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="316" t="inlineStr">
+      <c r="C5" s="391" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="347" t="n"/>
+      <c r="E5" s="347" t="n"/>
+      <c r="F5" s="347" t="n"/>
+      <c r="G5" s="347" t="n"/>
+      <c r="H5" s="347" t="n"/>
+      <c r="I5" s="347" t="n"/>
+      <c r="J5" s="347" t="n"/>
+      <c r="K5" s="347" t="n"/>
+      <c r="L5" s="347" t="n"/>
+      <c r="M5" s="347" t="n"/>
+      <c r="N5" s="347" t="n"/>
+      <c r="O5" s="347" t="n"/>
+      <c r="P5" s="347" t="n"/>
+      <c r="Q5" s="347" t="n"/>
+      <c r="R5" s="347" t="n"/>
+      <c r="S5" s="347" t="n"/>
+      <c r="T5" s="347" t="n"/>
+      <c r="U5" s="347" t="n"/>
+      <c r="V5" s="347" t="n"/>
+      <c r="W5" s="347" t="n"/>
+      <c r="X5" s="347" t="n"/>
+      <c r="Y5" s="347" t="n"/>
+      <c r="Z5" s="347" t="n"/>
+      <c r="AA5" s="347" t="n"/>
+      <c r="AB5" s="347" t="n"/>
+      <c r="AC5" s="347" t="n"/>
+      <c r="AD5" s="347" t="n"/>
+      <c r="AE5" s="347" t="n"/>
+      <c r="AF5" s="347" t="n"/>
+      <c r="AG5" s="347" t="n"/>
+      <c r="AH5" s="347" t="n"/>
+      <c r="AI5" s="347" t="n"/>
+      <c r="AJ5" s="347" t="n"/>
+      <c r="AK5" s="347" t="n"/>
+      <c r="AL5" s="347" t="n"/>
+      <c r="AM5" s="347" t="n"/>
+      <c r="AN5" s="347" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="315" t="inlineStr">
+      <c r="A6" s="390" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="316" t="inlineStr">
+      <c r="B6" s="391" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -7356,7 +9358,7 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="316" t="inlineStr">
+      <c r="C6" s="391" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -7364,142 +9366,475 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="347" t="n"/>
+      <c r="E6" s="347" t="n"/>
+      <c r="F6" s="347" t="n"/>
+      <c r="G6" s="347" t="n"/>
+      <c r="H6" s="347" t="n"/>
+      <c r="I6" s="347" t="n"/>
+      <c r="J6" s="347" t="n"/>
+      <c r="K6" s="347" t="n"/>
+      <c r="L6" s="347" t="n"/>
+      <c r="M6" s="347" t="n"/>
+      <c r="N6" s="347" t="n"/>
+      <c r="O6" s="347" t="n"/>
+      <c r="P6" s="347" t="n"/>
+      <c r="Q6" s="347" t="n"/>
+      <c r="R6" s="347" t="n"/>
+      <c r="S6" s="347" t="n"/>
+      <c r="T6" s="347" t="n"/>
+      <c r="U6" s="347" t="n"/>
+      <c r="V6" s="347" t="n"/>
+      <c r="W6" s="347" t="n"/>
+      <c r="X6" s="347" t="n"/>
+      <c r="Y6" s="347" t="n"/>
+      <c r="Z6" s="347" t="n"/>
+      <c r="AA6" s="347" t="n"/>
+      <c r="AB6" s="347" t="n"/>
+      <c r="AC6" s="347" t="n"/>
+      <c r="AD6" s="347" t="n"/>
+      <c r="AE6" s="347" t="n"/>
+      <c r="AF6" s="347" t="n"/>
+      <c r="AG6" s="347" t="n"/>
+      <c r="AH6" s="347" t="n"/>
+      <c r="AI6" s="347" t="n"/>
+      <c r="AJ6" s="347" t="n"/>
+      <c r="AK6" s="347" t="n"/>
+      <c r="AL6" s="347" t="n"/>
+      <c r="AM6" s="347" t="n"/>
+      <c r="AN6" s="347" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="315" t="inlineStr">
+      <c r="A7" s="390" t="inlineStr">
         <is>
           <t>SOP-401</t>
         </is>
       </c>
-      <c r="B7" s="316" t="inlineStr">
+      <c r="B7" s="391" t="inlineStr">
         <is>
           <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="316" t="inlineStr">
+      <c r="C7" s="391" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
         </is>
       </c>
+      <c r="D7" s="347" t="n"/>
+      <c r="E7" s="347" t="n"/>
+      <c r="F7" s="347" t="n"/>
+      <c r="G7" s="347" t="n"/>
+      <c r="H7" s="347" t="n"/>
+      <c r="I7" s="347" t="n"/>
+      <c r="J7" s="347" t="n"/>
+      <c r="K7" s="347" t="n"/>
+      <c r="L7" s="347" t="n"/>
+      <c r="M7" s="347" t="n"/>
+      <c r="N7" s="347" t="n"/>
+      <c r="O7" s="347" t="n"/>
+      <c r="P7" s="347" t="n"/>
+      <c r="Q7" s="347" t="n"/>
+      <c r="R7" s="347" t="n"/>
+      <c r="S7" s="347" t="n"/>
+      <c r="T7" s="347" t="n"/>
+      <c r="U7" s="347" t="n"/>
+      <c r="V7" s="347" t="n"/>
+      <c r="W7" s="347" t="n"/>
+      <c r="X7" s="347" t="n"/>
+      <c r="Y7" s="347" t="n"/>
+      <c r="Z7" s="347" t="n"/>
+      <c r="AA7" s="347" t="n"/>
+      <c r="AB7" s="347" t="n"/>
+      <c r="AC7" s="347" t="n"/>
+      <c r="AD7" s="347" t="n"/>
+      <c r="AE7" s="347" t="n"/>
+      <c r="AF7" s="347" t="n"/>
+      <c r="AG7" s="347" t="n"/>
+      <c r="AH7" s="347" t="n"/>
+      <c r="AI7" s="347" t="n"/>
+      <c r="AJ7" s="347" t="n"/>
+      <c r="AK7" s="347" t="n"/>
+      <c r="AL7" s="347" t="n"/>
+      <c r="AM7" s="347" t="n"/>
+      <c r="AN7" s="347" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="315" t="inlineStr">
+      <c r="A8" s="354" t="inlineStr">
         <is>
           <t>WI-206</t>
         </is>
       </c>
-      <c r="B8" s="316" t="inlineStr">
+      <c r="B8" s="392" t="inlineStr">
         <is>
           <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
         </is>
       </c>
-      <c r="C8" s="316" t="inlineStr">
+      <c r="C8" s="392" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
         </is>
       </c>
+      <c r="D8" s="383" t="n"/>
+      <c r="E8" s="383" t="n"/>
+      <c r="F8" s="383" t="n"/>
+      <c r="G8" s="383" t="n"/>
+      <c r="H8" s="383" t="n"/>
+      <c r="I8" s="383" t="n"/>
+      <c r="J8" s="383" t="n"/>
+      <c r="K8" s="383" t="n"/>
+      <c r="L8" s="383" t="n"/>
+      <c r="M8" s="383" t="n"/>
+      <c r="N8" s="383" t="n"/>
+      <c r="O8" s="383" t="n"/>
+      <c r="P8" s="383" t="n"/>
+      <c r="Q8" s="383" t="n"/>
+      <c r="R8" s="383" t="n"/>
+      <c r="S8" s="383" t="n"/>
+      <c r="T8" s="383" t="n"/>
+      <c r="U8" s="383" t="n"/>
+      <c r="V8" s="383" t="n"/>
+      <c r="W8" s="383" t="n"/>
+      <c r="X8" s="383" t="n"/>
+      <c r="Y8" s="383" t="n"/>
+      <c r="Z8" s="383" t="n"/>
+      <c r="AA8" s="383" t="n"/>
+      <c r="AB8" s="383" t="n"/>
+      <c r="AC8" s="383" t="n"/>
+      <c r="AD8" s="383" t="n"/>
+      <c r="AE8" s="383" t="n"/>
+      <c r="AF8" s="383" t="n"/>
+      <c r="AG8" s="383" t="n"/>
+      <c r="AH8" s="383" t="n"/>
+      <c r="AI8" s="383" t="n"/>
+      <c r="AJ8" s="383" t="n"/>
+      <c r="AK8" s="383" t="n"/>
+      <c r="AL8" s="383" t="n"/>
+      <c r="AM8" s="383" t="n"/>
+      <c r="AN8" s="383" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="383" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
+      <c r="D9" s="383" t="n"/>
+      <c r="E9" s="383" t="n"/>
+      <c r="F9" s="383" t="n"/>
+      <c r="G9" s="383" t="n"/>
+      <c r="H9" s="383" t="n"/>
+      <c r="I9" s="383" t="n"/>
+      <c r="J9" s="383" t="n"/>
+      <c r="K9" s="383" t="n"/>
+      <c r="L9" s="383" t="n"/>
+      <c r="M9" s="383" t="n"/>
+      <c r="N9" s="383" t="n"/>
+      <c r="O9" s="383" t="n"/>
+      <c r="P9" s="383" t="n"/>
+      <c r="Q9" s="383" t="n"/>
+      <c r="R9" s="383" t="n"/>
+      <c r="S9" s="383" t="n"/>
+      <c r="T9" s="383" t="n"/>
+      <c r="U9" s="383" t="n"/>
+      <c r="V9" s="383" t="n"/>
+      <c r="W9" s="383" t="n"/>
+      <c r="X9" s="383" t="n"/>
+      <c r="Y9" s="383" t="n"/>
+      <c r="Z9" s="383" t="n"/>
+      <c r="AA9" s="383" t="n"/>
+      <c r="AB9" s="383" t="n"/>
+      <c r="AC9" s="383" t="n"/>
+      <c r="AD9" s="383" t="n"/>
+      <c r="AE9" s="383" t="n"/>
+      <c r="AF9" s="383" t="n"/>
+      <c r="AG9" s="383" t="n"/>
+      <c r="AH9" s="383" t="n"/>
+      <c r="AI9" s="383" t="n"/>
+      <c r="AJ9" s="383" t="n"/>
+      <c r="AK9" s="383" t="n"/>
+      <c r="AL9" s="383" t="n"/>
+      <c r="AM9" s="383" t="n"/>
+      <c r="AN9" s="383" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="383" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
+      <c r="D10" s="383" t="n"/>
+      <c r="E10" s="383" t="n"/>
+      <c r="F10" s="383" t="n"/>
+      <c r="G10" s="383" t="n"/>
+      <c r="H10" s="383" t="n"/>
+      <c r="I10" s="383" t="n"/>
+      <c r="J10" s="383" t="n"/>
+      <c r="K10" s="383" t="n"/>
+      <c r="L10" s="383" t="n"/>
+      <c r="M10" s="383" t="n"/>
+      <c r="N10" s="383" t="n"/>
+      <c r="O10" s="383" t="n"/>
+      <c r="P10" s="383" t="n"/>
+      <c r="Q10" s="383" t="n"/>
+      <c r="R10" s="383" t="n"/>
+      <c r="S10" s="383" t="n"/>
+      <c r="T10" s="383" t="n"/>
+      <c r="U10" s="383" t="n"/>
+      <c r="V10" s="383" t="n"/>
+      <c r="W10" s="383" t="n"/>
+      <c r="X10" s="383" t="n"/>
+      <c r="Y10" s="383" t="n"/>
+      <c r="Z10" s="383" t="n"/>
+      <c r="AA10" s="383" t="n"/>
+      <c r="AB10" s="383" t="n"/>
+      <c r="AC10" s="383" t="n"/>
+      <c r="AD10" s="383" t="n"/>
+      <c r="AE10" s="383" t="n"/>
+      <c r="AF10" s="383" t="n"/>
+      <c r="AG10" s="383" t="n"/>
+      <c r="AH10" s="383" t="n"/>
+      <c r="AI10" s="383" t="n"/>
+      <c r="AJ10" s="383" t="n"/>
+      <c r="AK10" s="383" t="n"/>
+      <c r="AL10" s="383" t="n"/>
+      <c r="AM10" s="383" t="n"/>
+      <c r="AN10" s="383" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="383" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="383" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
+      <c r="D11" s="383" t="n"/>
+      <c r="E11" s="383" t="n"/>
+      <c r="F11" s="383" t="n"/>
+      <c r="G11" s="383" t="n"/>
+      <c r="H11" s="383" t="n"/>
+      <c r="I11" s="383" t="n"/>
+      <c r="J11" s="383" t="n"/>
+      <c r="K11" s="383" t="n"/>
+      <c r="L11" s="383" t="n"/>
+      <c r="M11" s="383" t="n"/>
+      <c r="N11" s="383" t="n"/>
+      <c r="O11" s="383" t="n"/>
+      <c r="P11" s="383" t="n"/>
+      <c r="Q11" s="383" t="n"/>
+      <c r="R11" s="383" t="n"/>
+      <c r="S11" s="383" t="n"/>
+      <c r="T11" s="383" t="n"/>
+      <c r="U11" s="383" t="n"/>
+      <c r="V11" s="383" t="n"/>
+      <c r="W11" s="383" t="n"/>
+      <c r="X11" s="383" t="n"/>
+      <c r="Y11" s="383" t="n"/>
+      <c r="Z11" s="383" t="n"/>
+      <c r="AA11" s="383" t="n"/>
+      <c r="AB11" s="383" t="n"/>
+      <c r="AC11" s="383" t="n"/>
+      <c r="AD11" s="383" t="n"/>
+      <c r="AE11" s="383" t="n"/>
+      <c r="AF11" s="383" t="n"/>
+      <c r="AG11" s="383" t="n"/>
+      <c r="AH11" s="383" t="n"/>
+      <c r="AI11" s="383" t="n"/>
+      <c r="AJ11" s="383" t="n"/>
+      <c r="AK11" s="383" t="n"/>
+      <c r="AL11" s="383" t="n"/>
+      <c r="AM11" s="383" t="n"/>
+      <c r="AN11" s="383" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="383" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="383" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="383" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
+      <c r="D12" s="383" t="n"/>
+      <c r="E12" s="383" t="n"/>
+      <c r="F12" s="383" t="n"/>
+      <c r="G12" s="383" t="n"/>
+      <c r="H12" s="383" t="n"/>
+      <c r="I12" s="383" t="n"/>
+      <c r="J12" s="383" t="n"/>
+      <c r="K12" s="383" t="n"/>
+      <c r="L12" s="383" t="n"/>
+      <c r="M12" s="383" t="n"/>
+      <c r="N12" s="383" t="n"/>
+      <c r="O12" s="383" t="n"/>
+      <c r="P12" s="383" t="n"/>
+      <c r="Q12" s="383" t="n"/>
+      <c r="R12" s="383" t="n"/>
+      <c r="S12" s="383" t="n"/>
+      <c r="T12" s="383" t="n"/>
+      <c r="U12" s="383" t="n"/>
+      <c r="V12" s="383" t="n"/>
+      <c r="W12" s="383" t="n"/>
+      <c r="X12" s="383" t="n"/>
+      <c r="Y12" s="383" t="n"/>
+      <c r="Z12" s="383" t="n"/>
+      <c r="AA12" s="383" t="n"/>
+      <c r="AB12" s="383" t="n"/>
+      <c r="AC12" s="383" t="n"/>
+      <c r="AD12" s="383" t="n"/>
+      <c r="AE12" s="383" t="n"/>
+      <c r="AF12" s="383" t="n"/>
+      <c r="AG12" s="383" t="n"/>
+      <c r="AH12" s="383" t="n"/>
+      <c r="AI12" s="383" t="n"/>
+      <c r="AJ12" s="383" t="n"/>
+      <c r="AK12" s="383" t="n"/>
+      <c r="AL12" s="383" t="n"/>
+      <c r="AM12" s="383" t="n"/>
+      <c r="AN12" s="383" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="383" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="383" t="inlineStr">
         <is>
           <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="383" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D13" s="383" t="n"/>
+      <c r="E13" s="383" t="n"/>
+      <c r="F13" s="383" t="n"/>
+      <c r="G13" s="383" t="n"/>
+      <c r="H13" s="383" t="n"/>
+      <c r="I13" s="383" t="n"/>
+      <c r="J13" s="383" t="n"/>
+      <c r="K13" s="383" t="n"/>
+      <c r="L13" s="383" t="n"/>
+      <c r="M13" s="383" t="n"/>
+      <c r="N13" s="383" t="n"/>
+      <c r="O13" s="383" t="n"/>
+      <c r="P13" s="383" t="n"/>
+      <c r="Q13" s="383" t="n"/>
+      <c r="R13" s="383" t="n"/>
+      <c r="S13" s="383" t="n"/>
+      <c r="T13" s="383" t="n"/>
+      <c r="U13" s="383" t="n"/>
+      <c r="V13" s="383" t="n"/>
+      <c r="W13" s="383" t="n"/>
+      <c r="X13" s="383" t="n"/>
+      <c r="Y13" s="383" t="n"/>
+      <c r="Z13" s="383" t="n"/>
+      <c r="AA13" s="383" t="n"/>
+      <c r="AB13" s="383" t="n"/>
+      <c r="AC13" s="383" t="n"/>
+      <c r="AD13" s="383" t="n"/>
+      <c r="AE13" s="383" t="n"/>
+      <c r="AF13" s="383" t="n"/>
+      <c r="AG13" s="383" t="n"/>
+      <c r="AH13" s="383" t="n"/>
+      <c r="AI13" s="383" t="n"/>
+      <c r="AJ13" s="383" t="n"/>
+      <c r="AK13" s="383" t="n"/>
+      <c r="AL13" s="383" t="n"/>
+      <c r="AM13" s="383" t="n"/>
+      <c r="AN13" s="383" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="383" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="383" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="383" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D14" s="383" t="n"/>
+      <c r="E14" s="383" t="n"/>
+      <c r="F14" s="383" t="n"/>
+      <c r="G14" s="383" t="n"/>
+      <c r="H14" s="383" t="n"/>
+      <c r="I14" s="383" t="n"/>
+      <c r="J14" s="383" t="n"/>
+      <c r="K14" s="383" t="n"/>
+      <c r="L14" s="383" t="n"/>
+      <c r="M14" s="383" t="n"/>
+      <c r="N14" s="383" t="n"/>
+      <c r="O14" s="383" t="n"/>
+      <c r="P14" s="383" t="n"/>
+      <c r="Q14" s="383" t="n"/>
+      <c r="R14" s="383" t="n"/>
+      <c r="S14" s="383" t="n"/>
+      <c r="T14" s="383" t="n"/>
+      <c r="U14" s="383" t="n"/>
+      <c r="V14" s="383" t="n"/>
+      <c r="W14" s="383" t="n"/>
+      <c r="X14" s="383" t="n"/>
+      <c r="Y14" s="383" t="n"/>
+      <c r="Z14" s="383" t="n"/>
+      <c r="AA14" s="383" t="n"/>
+      <c r="AB14" s="383" t="n"/>
+      <c r="AC14" s="383" t="n"/>
+      <c r="AD14" s="383" t="n"/>
+      <c r="AE14" s="383" t="n"/>
+      <c r="AF14" s="383" t="n"/>
+      <c r="AG14" s="383" t="n"/>
+      <c r="AH14" s="383" t="n"/>
+      <c r="AI14" s="383" t="n"/>
+      <c r="AJ14" s="383" t="n"/>
+      <c r="AK14" s="383" t="n"/>
+      <c r="AL14" s="383" t="n"/>
+      <c r="AM14" s="383" t="n"/>
+      <c r="AN14" s="383" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -7522,6 +9857,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="81">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -478,8 +478,40 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -711,8 +743,33 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="293">
+  <borders count="321">
     <border>
       <left/>
       <right/>
@@ -3846,12 +3903,308 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="416">
+  <cellXfs count="528">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4772,6 +5125,284 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4845,6 +5476,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5088,573 +5809,636 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="339" t="n"/>
-      <c r="B1" s="410" t="n"/>
-      <c r="C1" s="410" t="n"/>
-      <c r="D1" s="410" t="n"/>
-      <c r="E1" s="410" t="n"/>
-      <c r="F1" s="410" t="n"/>
-      <c r="G1" s="410" t="n"/>
-      <c r="H1" s="410" t="n"/>
-      <c r="I1" s="341" t="inlineStr">
+      <c r="A1" s="416" t="n"/>
+      <c r="B1" s="417" t="n"/>
+      <c r="C1" s="417" t="n"/>
+      <c r="D1" s="417" t="n"/>
+      <c r="E1" s="417" t="n"/>
+      <c r="F1" s="417" t="n"/>
+      <c r="G1" s="417" t="n"/>
+      <c r="H1" s="418" t="n"/>
+      <c r="I1" s="419" t="inlineStr">
         <is>
           <t>Outsource Dispatch Checklist</t>
         </is>
       </c>
-      <c r="J1" s="410" t="n"/>
-      <c r="K1" s="410" t="n"/>
-      <c r="L1" s="410" t="n"/>
-      <c r="M1" s="410" t="n"/>
-      <c r="N1" s="410" t="n"/>
-      <c r="O1" s="410" t="n"/>
-      <c r="P1" s="410" t="n"/>
-      <c r="Q1" s="410" t="n"/>
-      <c r="R1" s="410" t="n"/>
-      <c r="S1" s="410" t="n"/>
-      <c r="T1" s="410" t="n"/>
-      <c r="U1" s="410" t="n"/>
-      <c r="V1" s="410" t="n"/>
-      <c r="W1" s="410" t="n"/>
-      <c r="X1" s="410" t="n"/>
-      <c r="Y1" s="410" t="n"/>
-      <c r="Z1" s="410" t="n"/>
-      <c r="AA1" s="410" t="n"/>
-      <c r="AB1" s="410" t="n"/>
-      <c r="AC1" s="410" t="n"/>
-      <c r="AD1" s="410" t="n"/>
-      <c r="AE1" s="342" t="n"/>
-      <c r="AF1" s="411" t="n"/>
-      <c r="AG1" s="411" t="n"/>
-      <c r="AH1" s="412" t="n"/>
-      <c r="AI1" s="345" t="inlineStr">
+      <c r="J1" s="420" t="n"/>
+      <c r="K1" s="420" t="n"/>
+      <c r="L1" s="420" t="n"/>
+      <c r="M1" s="420" t="n"/>
+      <c r="N1" s="420" t="n"/>
+      <c r="O1" s="420" t="n"/>
+      <c r="P1" s="420" t="n"/>
+      <c r="Q1" s="420" t="n"/>
+      <c r="R1" s="420" t="n"/>
+      <c r="S1" s="420" t="n"/>
+      <c r="T1" s="420" t="n"/>
+      <c r="U1" s="420" t="n"/>
+      <c r="V1" s="420" t="n"/>
+      <c r="W1" s="420" t="n"/>
+      <c r="X1" s="420" t="n"/>
+      <c r="Y1" s="420" t="n"/>
+      <c r="Z1" s="420" t="n"/>
+      <c r="AA1" s="420" t="n"/>
+      <c r="AB1" s="420" t="n"/>
+      <c r="AC1" s="420" t="n"/>
+      <c r="AD1" s="421" t="n"/>
+      <c r="AE1" s="422" t="n"/>
+      <c r="AF1" s="423" t="n"/>
+      <c r="AG1" s="423" t="n"/>
+      <c r="AH1" s="424" t="n"/>
+      <c r="AI1" s="425" t="inlineStr">
         <is>
           <t>FRM-404</t>
         </is>
       </c>
-      <c r="AJ1" s="411" t="n"/>
-      <c r="AK1" s="411" t="n"/>
-      <c r="AL1" s="411" t="n"/>
-      <c r="AM1" s="411" t="n"/>
-      <c r="AN1" s="412" t="n"/>
+      <c r="AJ1" s="426" t="n"/>
+      <c r="AK1" s="426" t="n"/>
+      <c r="AL1" s="426" t="n"/>
+      <c r="AM1" s="426" t="n"/>
+      <c r="AN1" s="427" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="413" t="n"/>
-      <c r="I2" s="413" t="n"/>
-      <c r="AE2" s="342" t="n"/>
-      <c r="AF2" s="411" t="n"/>
-      <c r="AG2" s="411" t="n"/>
-      <c r="AH2" s="412" t="n"/>
-      <c r="AI2" s="345" t="inlineStr">
+      <c r="A2" s="428" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="429" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="431" t="n"/>
+      <c r="K2" s="431" t="n"/>
+      <c r="L2" s="431" t="n"/>
+      <c r="M2" s="431" t="n"/>
+      <c r="N2" s="431" t="n"/>
+      <c r="O2" s="431" t="n"/>
+      <c r="P2" s="431" t="n"/>
+      <c r="Q2" s="431" t="n"/>
+      <c r="R2" s="431" t="n"/>
+      <c r="S2" s="431" t="n"/>
+      <c r="T2" s="431" t="n"/>
+      <c r="U2" s="431" t="n"/>
+      <c r="V2" s="431" t="n"/>
+      <c r="W2" s="431" t="n"/>
+      <c r="X2" s="431" t="n"/>
+      <c r="Y2" s="431" t="n"/>
+      <c r="Z2" s="431" t="n"/>
+      <c r="AA2" s="431" t="n"/>
+      <c r="AB2" s="431" t="n"/>
+      <c r="AC2" s="431" t="n"/>
+      <c r="AD2" s="432" t="n"/>
+      <c r="AE2" s="433" t="n"/>
+      <c r="AF2" s="434" t="n"/>
+      <c r="AG2" s="434" t="n"/>
+      <c r="AH2" s="435" t="n"/>
+      <c r="AI2" s="436" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="411" t="n"/>
-      <c r="AK2" s="411" t="n"/>
-      <c r="AL2" s="411" t="n"/>
-      <c r="AM2" s="411" t="n"/>
-      <c r="AN2" s="412" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="438" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="413" t="n"/>
-      <c r="I3" s="414" t="n"/>
-      <c r="J3" s="415" t="n"/>
-      <c r="K3" s="415" t="n"/>
-      <c r="L3" s="415" t="n"/>
-      <c r="M3" s="415" t="n"/>
-      <c r="N3" s="415" t="n"/>
-      <c r="O3" s="415" t="n"/>
-      <c r="P3" s="415" t="n"/>
-      <c r="Q3" s="415" t="n"/>
-      <c r="R3" s="415" t="n"/>
-      <c r="S3" s="415" t="n"/>
-      <c r="T3" s="415" t="n"/>
-      <c r="U3" s="415" t="n"/>
-      <c r="V3" s="415" t="n"/>
-      <c r="W3" s="415" t="n"/>
-      <c r="X3" s="415" t="n"/>
-      <c r="Y3" s="415" t="n"/>
-      <c r="Z3" s="415" t="n"/>
-      <c r="AA3" s="415" t="n"/>
-      <c r="AB3" s="415" t="n"/>
-      <c r="AC3" s="415" t="n"/>
-      <c r="AD3" s="415" t="n"/>
-      <c r="AE3" s="342" t="n"/>
-      <c r="AF3" s="411" t="n"/>
-      <c r="AG3" s="411" t="n"/>
-      <c r="AH3" s="412" t="n"/>
-      <c r="AI3" s="345" t="inlineStr">
+      <c r="A3" s="428" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="429" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="431" t="n"/>
+      <c r="K3" s="431" t="n"/>
+      <c r="L3" s="431" t="n"/>
+      <c r="M3" s="431" t="n"/>
+      <c r="N3" s="431" t="n"/>
+      <c r="O3" s="431" t="n"/>
+      <c r="P3" s="431" t="n"/>
+      <c r="Q3" s="431" t="n"/>
+      <c r="R3" s="431" t="n"/>
+      <c r="S3" s="431" t="n"/>
+      <c r="T3" s="431" t="n"/>
+      <c r="U3" s="431" t="n"/>
+      <c r="V3" s="431" t="n"/>
+      <c r="W3" s="431" t="n"/>
+      <c r="X3" s="431" t="n"/>
+      <c r="Y3" s="431" t="n"/>
+      <c r="Z3" s="431" t="n"/>
+      <c r="AA3" s="431" t="n"/>
+      <c r="AB3" s="431" t="n"/>
+      <c r="AC3" s="431" t="n"/>
+      <c r="AD3" s="432" t="n"/>
+      <c r="AE3" s="433" t="n"/>
+      <c r="AF3" s="434" t="n"/>
+      <c r="AG3" s="434" t="n"/>
+      <c r="AH3" s="435" t="n"/>
+      <c r="AI3" s="436" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="411" t="n"/>
-      <c r="AK3" s="411" t="n"/>
-      <c r="AL3" s="411" t="n"/>
-      <c r="AM3" s="411" t="n"/>
-      <c r="AN3" s="412" t="n"/>
+      <c r="AJ3" s="437" t="n"/>
+      <c r="AK3" s="437" t="n"/>
+      <c r="AL3" s="437" t="n"/>
+      <c r="AM3" s="437" t="n"/>
+      <c r="AN3" s="438" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="413" t="n"/>
-      <c r="I4" s="350" t="inlineStr">
+      <c r="A4" s="428" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="429" t="n"/>
+      <c r="I4" s="439" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="342" t="n"/>
-      <c r="AF4" s="411" t="n"/>
-      <c r="AG4" s="411" t="n"/>
-      <c r="AH4" s="412" t="n"/>
-      <c r="AI4" s="345" t="inlineStr">
+      <c r="J4" s="440" t="n"/>
+      <c r="K4" s="440" t="n"/>
+      <c r="L4" s="440" t="n"/>
+      <c r="M4" s="440" t="n"/>
+      <c r="N4" s="440" t="n"/>
+      <c r="O4" s="440" t="n"/>
+      <c r="P4" s="440" t="n"/>
+      <c r="Q4" s="440" t="n"/>
+      <c r="R4" s="440" t="n"/>
+      <c r="S4" s="440" t="n"/>
+      <c r="T4" s="440" t="n"/>
+      <c r="U4" s="440" t="n"/>
+      <c r="V4" s="440" t="n"/>
+      <c r="W4" s="440" t="n"/>
+      <c r="X4" s="440" t="n"/>
+      <c r="Y4" s="440" t="n"/>
+      <c r="Z4" s="440" t="n"/>
+      <c r="AA4" s="440" t="n"/>
+      <c r="AB4" s="440" t="n"/>
+      <c r="AC4" s="440" t="n"/>
+      <c r="AD4" s="441" t="n"/>
+      <c r="AE4" s="433" t="n"/>
+      <c r="AF4" s="434" t="n"/>
+      <c r="AG4" s="434" t="n"/>
+      <c r="AH4" s="435" t="n"/>
+      <c r="AI4" s="436" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="411" t="n"/>
-      <c r="AK4" s="411" t="n"/>
-      <c r="AL4" s="411" t="n"/>
-      <c r="AM4" s="411" t="n"/>
-      <c r="AN4" s="412" t="n"/>
+      <c r="AJ4" s="437" t="n"/>
+      <c r="AK4" s="437" t="n"/>
+      <c r="AL4" s="437" t="n"/>
+      <c r="AM4" s="437" t="n"/>
+      <c r="AN4" s="438" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="414" t="n"/>
-      <c r="B5" s="415" t="n"/>
-      <c r="C5" s="415" t="n"/>
-      <c r="D5" s="415" t="n"/>
-      <c r="E5" s="415" t="n"/>
-      <c r="F5" s="415" t="n"/>
-      <c r="G5" s="415" t="n"/>
-      <c r="H5" s="415" t="n"/>
-      <c r="I5" s="351" t="inlineStr">
+      <c r="A5" s="442" t="n"/>
+      <c r="B5" s="443" t="n"/>
+      <c r="C5" s="443" t="n"/>
+      <c r="D5" s="443" t="n"/>
+      <c r="E5" s="443" t="n"/>
+      <c r="F5" s="443" t="n"/>
+      <c r="G5" s="443" t="n"/>
+      <c r="H5" s="444" t="n"/>
+      <c r="I5" s="445" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="415" t="n"/>
-      <c r="K5" s="415" t="n"/>
-      <c r="L5" s="415" t="n"/>
-      <c r="M5" s="415" t="n"/>
-      <c r="N5" s="415" t="n"/>
-      <c r="O5" s="415" t="n"/>
-      <c r="P5" s="415" t="n"/>
-      <c r="Q5" s="415" t="n"/>
-      <c r="R5" s="415" t="n"/>
-      <c r="S5" s="415" t="n"/>
-      <c r="T5" s="415" t="n"/>
-      <c r="U5" s="415" t="n"/>
-      <c r="V5" s="415" t="n"/>
-      <c r="W5" s="415" t="n"/>
-      <c r="X5" s="415" t="n"/>
-      <c r="Y5" s="415" t="n"/>
-      <c r="Z5" s="415" t="n"/>
-      <c r="AA5" s="415" t="n"/>
-      <c r="AB5" s="415" t="n"/>
-      <c r="AC5" s="415" t="n"/>
-      <c r="AD5" s="415" t="n"/>
-      <c r="AE5" s="342" t="n"/>
-      <c r="AF5" s="411" t="n"/>
-      <c r="AG5" s="411" t="n"/>
-      <c r="AH5" s="412" t="n"/>
-      <c r="AI5" s="345" t="inlineStr">
+      <c r="J5" s="446" t="n"/>
+      <c r="K5" s="446" t="n"/>
+      <c r="L5" s="446" t="n"/>
+      <c r="M5" s="446" t="n"/>
+      <c r="N5" s="446" t="n"/>
+      <c r="O5" s="446" t="n"/>
+      <c r="P5" s="446" t="n"/>
+      <c r="Q5" s="446" t="n"/>
+      <c r="R5" s="446" t="n"/>
+      <c r="S5" s="446" t="n"/>
+      <c r="T5" s="446" t="n"/>
+      <c r="U5" s="446" t="n"/>
+      <c r="V5" s="446" t="n"/>
+      <c r="W5" s="446" t="n"/>
+      <c r="X5" s="446" t="n"/>
+      <c r="Y5" s="446" t="n"/>
+      <c r="Z5" s="446" t="n"/>
+      <c r="AA5" s="446" t="n"/>
+      <c r="AB5" s="446" t="n"/>
+      <c r="AC5" s="446" t="n"/>
+      <c r="AD5" s="447" t="n"/>
+      <c r="AE5" s="448" t="n"/>
+      <c r="AF5" s="449" t="n"/>
+      <c r="AG5" s="449" t="n"/>
+      <c r="AH5" s="450" t="n"/>
+      <c r="AI5" s="451" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="411" t="n"/>
-      <c r="AK5" s="411" t="n"/>
-      <c r="AL5" s="411" t="n"/>
-      <c r="AM5" s="411" t="n"/>
-      <c r="AN5" s="412" t="n"/>
+      <c r="AJ5" s="452" t="n"/>
+      <c r="AK5" s="452" t="n"/>
+      <c r="AL5" s="452" t="n"/>
+      <c r="AM5" s="452" t="n"/>
+      <c r="AN5" s="453" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1" s="329">
-      <c r="A6" s="352" t="n"/>
-      <c r="B6" s="409" t="n"/>
-      <c r="C6" s="409" t="n"/>
-      <c r="D6" s="409" t="n"/>
-      <c r="E6" s="409" t="n"/>
-      <c r="F6" s="409" t="n"/>
-      <c r="G6" s="409" t="n"/>
-      <c r="H6" s="409" t="n"/>
-      <c r="I6" s="409" t="n"/>
-      <c r="J6" s="409" t="n"/>
-      <c r="K6" s="409" t="n"/>
-      <c r="L6" s="409" t="n"/>
-      <c r="M6" s="409" t="n"/>
-      <c r="N6" s="409" t="n"/>
-      <c r="O6" s="409" t="n"/>
-      <c r="P6" s="409" t="n"/>
-      <c r="Q6" s="409" t="n"/>
-      <c r="R6" s="409" t="n"/>
-      <c r="S6" s="409" t="n"/>
-      <c r="T6" s="409" t="n"/>
-      <c r="U6" s="409" t="n"/>
-      <c r="V6" s="409" t="n"/>
-      <c r="W6" s="409" t="n"/>
-      <c r="X6" s="409" t="n"/>
-      <c r="Y6" s="409" t="n"/>
-      <c r="Z6" s="409" t="n"/>
-      <c r="AA6" s="409" t="n"/>
-      <c r="AB6" s="409" t="n"/>
-      <c r="AC6" s="409" t="n"/>
-      <c r="AD6" s="409" t="n"/>
-      <c r="AE6" s="409" t="n"/>
-      <c r="AF6" s="409" t="n"/>
-      <c r="AG6" s="409" t="n"/>
-      <c r="AH6" s="409" t="n"/>
-      <c r="AI6" s="409" t="n"/>
-      <c r="AJ6" s="409" t="n"/>
-      <c r="AK6" s="409" t="n"/>
-      <c r="AL6" s="409" t="n"/>
-      <c r="AM6" s="409" t="n"/>
-      <c r="AN6" s="409" t="n"/>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="454" t="n"/>
+      <c r="B6" s="454" t="n"/>
+      <c r="C6" s="454" t="n"/>
+      <c r="D6" s="454" t="n"/>
+      <c r="E6" s="454" t="n"/>
+      <c r="F6" s="454" t="n"/>
+      <c r="G6" s="454" t="n"/>
+      <c r="H6" s="454" t="n"/>
+      <c r="I6" s="454" t="n"/>
+      <c r="J6" s="454" t="n"/>
+      <c r="K6" s="454" t="n"/>
+      <c r="L6" s="454" t="n"/>
+      <c r="M6" s="454" t="n"/>
+      <c r="N6" s="454" t="n"/>
+      <c r="O6" s="454" t="n"/>
+      <c r="P6" s="454" t="n"/>
+      <c r="Q6" s="454" t="n"/>
+      <c r="R6" s="454" t="n"/>
+      <c r="S6" s="454" t="n"/>
+      <c r="T6" s="454" t="n"/>
+      <c r="U6" s="454" t="n"/>
+      <c r="V6" s="454" t="n"/>
+      <c r="W6" s="454" t="n"/>
+      <c r="X6" s="454" t="n"/>
+      <c r="Y6" s="454" t="n"/>
+      <c r="Z6" s="454" t="n"/>
+      <c r="AA6" s="454" t="n"/>
+      <c r="AB6" s="454" t="n"/>
+      <c r="AC6" s="454" t="n"/>
+      <c r="AD6" s="454" t="n"/>
+      <c r="AE6" s="454" t="n"/>
+      <c r="AF6" s="454" t="n"/>
+      <c r="AG6" s="454" t="n"/>
+      <c r="AH6" s="454" t="n"/>
+      <c r="AI6" s="454" t="n"/>
+      <c r="AJ6" s="454" t="n"/>
+      <c r="AK6" s="454" t="n"/>
+      <c r="AL6" s="454" t="n"/>
+      <c r="AM6" s="454" t="n"/>
+      <c r="AN6" s="454" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1" s="329">
-      <c r="A7" s="353" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="329">
+      <c r="A7" s="455" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="411" t="n"/>
-      <c r="C7" s="411" t="n"/>
-      <c r="D7" s="411" t="n"/>
-      <c r="E7" s="411" t="n"/>
-      <c r="F7" s="411" t="n"/>
-      <c r="G7" s="411" t="n"/>
-      <c r="H7" s="411" t="n"/>
-      <c r="I7" s="411" t="n"/>
-      <c r="J7" s="411" t="n"/>
-      <c r="K7" s="411" t="n"/>
-      <c r="L7" s="411" t="n"/>
-      <c r="M7" s="411" t="n"/>
-      <c r="N7" s="411" t="n"/>
-      <c r="O7" s="411" t="n"/>
-      <c r="P7" s="411" t="n"/>
-      <c r="Q7" s="411" t="n"/>
-      <c r="R7" s="411" t="n"/>
-      <c r="S7" s="411" t="n"/>
-      <c r="T7" s="411" t="n"/>
-      <c r="U7" s="411" t="n"/>
-      <c r="V7" s="411" t="n"/>
-      <c r="W7" s="411" t="n"/>
-      <c r="X7" s="411" t="n"/>
-      <c r="Y7" s="411" t="n"/>
-      <c r="Z7" s="411" t="n"/>
-      <c r="AA7" s="411" t="n"/>
-      <c r="AB7" s="411" t="n"/>
-      <c r="AC7" s="411" t="n"/>
-      <c r="AD7" s="411" t="n"/>
-      <c r="AE7" s="411" t="n"/>
-      <c r="AF7" s="411" t="n"/>
-      <c r="AG7" s="411" t="n"/>
-      <c r="AH7" s="411" t="n"/>
-      <c r="AI7" s="411" t="n"/>
-      <c r="AJ7" s="411" t="n"/>
-      <c r="AK7" s="411" t="n"/>
-      <c r="AL7" s="411" t="n"/>
-      <c r="AM7" s="411" t="n"/>
-      <c r="AN7" s="412" t="n"/>
+      <c r="B7" s="456" t="n"/>
+      <c r="C7" s="456" t="n"/>
+      <c r="D7" s="456" t="n"/>
+      <c r="E7" s="456" t="n"/>
+      <c r="F7" s="456" t="n"/>
+      <c r="G7" s="456" t="n"/>
+      <c r="H7" s="456" t="n"/>
+      <c r="I7" s="456" t="n"/>
+      <c r="J7" s="456" t="n"/>
+      <c r="K7" s="456" t="n"/>
+      <c r="L7" s="456" t="n"/>
+      <c r="M7" s="456" t="n"/>
+      <c r="N7" s="456" t="n"/>
+      <c r="O7" s="456" t="n"/>
+      <c r="P7" s="456" t="n"/>
+      <c r="Q7" s="456" t="n"/>
+      <c r="R7" s="456" t="n"/>
+      <c r="S7" s="456" t="n"/>
+      <c r="T7" s="456" t="n"/>
+      <c r="U7" s="456" t="n"/>
+      <c r="V7" s="456" t="n"/>
+      <c r="W7" s="456" t="n"/>
+      <c r="X7" s="456" t="n"/>
+      <c r="Y7" s="456" t="n"/>
+      <c r="Z7" s="456" t="n"/>
+      <c r="AA7" s="456" t="n"/>
+      <c r="AB7" s="456" t="n"/>
+      <c r="AC7" s="456" t="n"/>
+      <c r="AD7" s="456" t="n"/>
+      <c r="AE7" s="456" t="n"/>
+      <c r="AF7" s="456" t="n"/>
+      <c r="AG7" s="456" t="n"/>
+      <c r="AH7" s="456" t="n"/>
+      <c r="AI7" s="456" t="n"/>
+      <c r="AJ7" s="456" t="n"/>
+      <c r="AK7" s="456" t="n"/>
+      <c r="AL7" s="456" t="n"/>
+      <c r="AM7" s="456" t="n"/>
+      <c r="AN7" s="457" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="354" t="inlineStr">
+      <c r="A8" s="458" t="inlineStr">
         <is>
           <t>Outsource Dispatch ID</t>
         </is>
       </c>
-      <c r="B8" s="399" t="n"/>
-      <c r="C8" s="399" t="n"/>
-      <c r="D8" s="399" t="n"/>
-      <c r="E8" s="399" t="n"/>
-      <c r="F8" s="399" t="n"/>
-      <c r="G8" s="400" t="n"/>
-      <c r="H8" s="357" t="n"/>
-      <c r="I8" s="399" t="n"/>
-      <c r="J8" s="399" t="n"/>
-      <c r="K8" s="399" t="n"/>
-      <c r="L8" s="399" t="n"/>
-      <c r="M8" s="399" t="n"/>
-      <c r="N8" s="399" t="n"/>
-      <c r="O8" s="399" t="n"/>
-      <c r="P8" s="399" t="n"/>
-      <c r="Q8" s="399" t="n"/>
-      <c r="R8" s="399" t="n"/>
-      <c r="S8" s="399" t="n"/>
-      <c r="T8" s="400" t="n"/>
-      <c r="U8" s="358" t="inlineStr">
+      <c r="B8" s="459" t="n"/>
+      <c r="C8" s="459" t="n"/>
+      <c r="D8" s="459" t="n"/>
+      <c r="E8" s="459" t="n"/>
+      <c r="F8" s="459" t="n"/>
+      <c r="G8" s="459" t="n"/>
+      <c r="H8" s="460" t="n"/>
+      <c r="I8" s="459" t="n"/>
+      <c r="J8" s="459" t="n"/>
+      <c r="K8" s="459" t="n"/>
+      <c r="L8" s="459" t="n"/>
+      <c r="M8" s="459" t="n"/>
+      <c r="N8" s="459" t="n"/>
+      <c r="O8" s="459" t="n"/>
+      <c r="P8" s="459" t="n"/>
+      <c r="Q8" s="459" t="n"/>
+      <c r="R8" s="459" t="n"/>
+      <c r="S8" s="459" t="n"/>
+      <c r="T8" s="459" t="n"/>
+      <c r="U8" s="461" t="inlineStr">
         <is>
           <t>Dispatch Gate Status</t>
         </is>
       </c>
-      <c r="V8" s="399" t="n"/>
-      <c r="W8" s="399" t="n"/>
-      <c r="X8" s="399" t="n"/>
-      <c r="Y8" s="399" t="n"/>
-      <c r="Z8" s="399" t="n"/>
-      <c r="AA8" s="400" t="n"/>
-      <c r="AB8" s="357" t="n"/>
-      <c r="AC8" s="399" t="n"/>
-      <c r="AD8" s="399" t="n"/>
-      <c r="AE8" s="399" t="n"/>
-      <c r="AF8" s="399" t="n"/>
-      <c r="AG8" s="399" t="n"/>
-      <c r="AH8" s="399" t="n"/>
-      <c r="AI8" s="399" t="n"/>
-      <c r="AJ8" s="399" t="n"/>
-      <c r="AK8" s="399" t="n"/>
-      <c r="AL8" s="399" t="n"/>
-      <c r="AM8" s="399" t="n"/>
-      <c r="AN8" s="400" t="n"/>
+      <c r="V8" s="459" t="n"/>
+      <c r="W8" s="459" t="n"/>
+      <c r="X8" s="459" t="n"/>
+      <c r="Y8" s="459" t="n"/>
+      <c r="Z8" s="459" t="n"/>
+      <c r="AA8" s="459" t="n"/>
+      <c r="AB8" s="460" t="n"/>
+      <c r="AC8" s="459" t="n"/>
+      <c r="AD8" s="459" t="n"/>
+      <c r="AE8" s="459" t="n"/>
+      <c r="AF8" s="459" t="n"/>
+      <c r="AG8" s="459" t="n"/>
+      <c r="AH8" s="459" t="n"/>
+      <c r="AI8" s="459" t="n"/>
+      <c r="AJ8" s="459" t="n"/>
+      <c r="AK8" s="459" t="n"/>
+      <c r="AL8" s="459" t="n"/>
+      <c r="AM8" s="459" t="n"/>
+      <c r="AN8" s="462" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="354" t="inlineStr">
+      <c r="A9" s="463" t="inlineStr">
         <is>
           <t>Supplier / Processor</t>
         </is>
       </c>
-      <c r="B9" s="399" t="n"/>
-      <c r="C9" s="399" t="n"/>
-      <c r="D9" s="399" t="n"/>
-      <c r="E9" s="399" t="n"/>
-      <c r="F9" s="399" t="n"/>
-      <c r="G9" s="400" t="n"/>
-      <c r="H9" s="357" t="n"/>
-      <c r="I9" s="399" t="n"/>
-      <c r="J9" s="399" t="n"/>
-      <c r="K9" s="399" t="n"/>
-      <c r="L9" s="399" t="n"/>
-      <c r="M9" s="399" t="n"/>
-      <c r="N9" s="399" t="n"/>
-      <c r="O9" s="399" t="n"/>
-      <c r="P9" s="399" t="n"/>
-      <c r="Q9" s="399" t="n"/>
-      <c r="R9" s="399" t="n"/>
-      <c r="S9" s="399" t="n"/>
-      <c r="T9" s="400" t="n"/>
-      <c r="U9" s="358" t="inlineStr">
+      <c r="B9" s="343" t="n"/>
+      <c r="C9" s="343" t="n"/>
+      <c r="D9" s="343" t="n"/>
+      <c r="E9" s="343" t="n"/>
+      <c r="F9" s="343" t="n"/>
+      <c r="G9" s="343" t="n"/>
+      <c r="H9" s="464" t="n"/>
+      <c r="I9" s="343" t="n"/>
+      <c r="J9" s="343" t="n"/>
+      <c r="K9" s="343" t="n"/>
+      <c r="L9" s="343" t="n"/>
+      <c r="M9" s="343" t="n"/>
+      <c r="N9" s="343" t="n"/>
+      <c r="O9" s="343" t="n"/>
+      <c r="P9" s="343" t="n"/>
+      <c r="Q9" s="343" t="n"/>
+      <c r="R9" s="343" t="n"/>
+      <c r="S9" s="343" t="n"/>
+      <c r="T9" s="343" t="n"/>
+      <c r="U9" s="465" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="V9" s="399" t="n"/>
-      <c r="W9" s="399" t="n"/>
-      <c r="X9" s="399" t="n"/>
-      <c r="Y9" s="399" t="n"/>
-      <c r="Z9" s="399" t="n"/>
-      <c r="AA9" s="400" t="n"/>
-      <c r="AB9" s="357" t="n"/>
-      <c r="AC9" s="399" t="n"/>
-      <c r="AD9" s="399" t="n"/>
-      <c r="AE9" s="399" t="n"/>
-      <c r="AF9" s="399" t="n"/>
-      <c r="AG9" s="399" t="n"/>
-      <c r="AH9" s="399" t="n"/>
-      <c r="AI9" s="399" t="n"/>
-      <c r="AJ9" s="399" t="n"/>
-      <c r="AK9" s="399" t="n"/>
-      <c r="AL9" s="399" t="n"/>
-      <c r="AM9" s="399" t="n"/>
-      <c r="AN9" s="400" t="n"/>
+      <c r="V9" s="343" t="n"/>
+      <c r="W9" s="343" t="n"/>
+      <c r="X9" s="343" t="n"/>
+      <c r="Y9" s="343" t="n"/>
+      <c r="Z9" s="343" t="n"/>
+      <c r="AA9" s="343" t="n"/>
+      <c r="AB9" s="464" t="n"/>
+      <c r="AC9" s="343" t="n"/>
+      <c r="AD9" s="343" t="n"/>
+      <c r="AE9" s="343" t="n"/>
+      <c r="AF9" s="343" t="n"/>
+      <c r="AG9" s="343" t="n"/>
+      <c r="AH9" s="343" t="n"/>
+      <c r="AI9" s="343" t="n"/>
+      <c r="AJ9" s="343" t="n"/>
+      <c r="AK9" s="343" t="n"/>
+      <c r="AL9" s="343" t="n"/>
+      <c r="AM9" s="343" t="n"/>
+      <c r="AN9" s="466" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="354" t="inlineStr">
+      <c r="A10" s="463" t="inlineStr">
         <is>
           <t>PO / Work Order</t>
         </is>
       </c>
-      <c r="B10" s="399" t="n"/>
-      <c r="C10" s="399" t="n"/>
-      <c r="D10" s="399" t="n"/>
-      <c r="E10" s="399" t="n"/>
-      <c r="F10" s="399" t="n"/>
-      <c r="G10" s="400" t="n"/>
-      <c r="H10" s="357" t="n"/>
-      <c r="I10" s="399" t="n"/>
-      <c r="J10" s="399" t="n"/>
-      <c r="K10" s="399" t="n"/>
-      <c r="L10" s="399" t="n"/>
-      <c r="M10" s="399" t="n"/>
-      <c r="N10" s="399" t="n"/>
-      <c r="O10" s="399" t="n"/>
-      <c r="P10" s="399" t="n"/>
-      <c r="Q10" s="399" t="n"/>
-      <c r="R10" s="399" t="n"/>
-      <c r="S10" s="399" t="n"/>
-      <c r="T10" s="400" t="n"/>
-      <c r="U10" s="358" t="inlineStr">
+      <c r="B10" s="343" t="n"/>
+      <c r="C10" s="343" t="n"/>
+      <c r="D10" s="343" t="n"/>
+      <c r="E10" s="343" t="n"/>
+      <c r="F10" s="343" t="n"/>
+      <c r="G10" s="343" t="n"/>
+      <c r="H10" s="464" t="n"/>
+      <c r="I10" s="343" t="n"/>
+      <c r="J10" s="343" t="n"/>
+      <c r="K10" s="343" t="n"/>
+      <c r="L10" s="343" t="n"/>
+      <c r="M10" s="343" t="n"/>
+      <c r="N10" s="343" t="n"/>
+      <c r="O10" s="343" t="n"/>
+      <c r="P10" s="343" t="n"/>
+      <c r="Q10" s="343" t="n"/>
+      <c r="R10" s="343" t="n"/>
+      <c r="S10" s="343" t="n"/>
+      <c r="T10" s="343" t="n"/>
+      <c r="U10" s="465" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="399" t="n"/>
-      <c r="W10" s="399" t="n"/>
-      <c r="X10" s="399" t="n"/>
-      <c r="Y10" s="399" t="n"/>
-      <c r="Z10" s="399" t="n"/>
-      <c r="AA10" s="400" t="n"/>
-      <c r="AB10" s="357" t="n"/>
-      <c r="AC10" s="399" t="n"/>
-      <c r="AD10" s="399" t="n"/>
-      <c r="AE10" s="399" t="n"/>
-      <c r="AF10" s="399" t="n"/>
-      <c r="AG10" s="399" t="n"/>
-      <c r="AH10" s="399" t="n"/>
-      <c r="AI10" s="399" t="n"/>
-      <c r="AJ10" s="399" t="n"/>
-      <c r="AK10" s="399" t="n"/>
-      <c r="AL10" s="399" t="n"/>
-      <c r="AM10" s="399" t="n"/>
-      <c r="AN10" s="400" t="n"/>
+      <c r="V10" s="343" t="n"/>
+      <c r="W10" s="343" t="n"/>
+      <c r="X10" s="343" t="n"/>
+      <c r="Y10" s="343" t="n"/>
+      <c r="Z10" s="343" t="n"/>
+      <c r="AA10" s="343" t="n"/>
+      <c r="AB10" s="464" t="n"/>
+      <c r="AC10" s="343" t="n"/>
+      <c r="AD10" s="343" t="n"/>
+      <c r="AE10" s="343" t="n"/>
+      <c r="AF10" s="343" t="n"/>
+      <c r="AG10" s="343" t="n"/>
+      <c r="AH10" s="343" t="n"/>
+      <c r="AI10" s="343" t="n"/>
+      <c r="AJ10" s="343" t="n"/>
+      <c r="AK10" s="343" t="n"/>
+      <c r="AL10" s="343" t="n"/>
+      <c r="AM10" s="343" t="n"/>
+      <c r="AN10" s="466" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="354" t="inlineStr">
+    <row r="11" ht="26" customHeight="1" s="329">
+      <c r="A11" s="463" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="394" t="n"/>
-      <c r="C11" s="394" t="n"/>
-      <c r="D11" s="394" t="n"/>
-      <c r="E11" s="394" t="n"/>
-      <c r="F11" s="394" t="n"/>
-      <c r="G11" s="395" t="n"/>
-      <c r="H11" s="357" t="n"/>
-      <c r="I11" s="394" t="n"/>
-      <c r="J11" s="394" t="n"/>
-      <c r="K11" s="394" t="n"/>
-      <c r="L11" s="394" t="n"/>
-      <c r="M11" s="394" t="n"/>
-      <c r="N11" s="394" t="n"/>
-      <c r="O11" s="394" t="n"/>
-      <c r="P11" s="394" t="n"/>
-      <c r="Q11" s="394" t="n"/>
-      <c r="R11" s="394" t="n"/>
-      <c r="S11" s="394" t="n"/>
-      <c r="T11" s="395" t="n"/>
-      <c r="U11" s="358" t="inlineStr">
+      <c r="B11" s="343" t="n"/>
+      <c r="C11" s="343" t="n"/>
+      <c r="D11" s="343" t="n"/>
+      <c r="E11" s="343" t="n"/>
+      <c r="F11" s="343" t="n"/>
+      <c r="G11" s="343" t="n"/>
+      <c r="H11" s="464" t="n"/>
+      <c r="I11" s="343" t="n"/>
+      <c r="J11" s="343" t="n"/>
+      <c r="K11" s="343" t="n"/>
+      <c r="L11" s="343" t="n"/>
+      <c r="M11" s="343" t="n"/>
+      <c r="N11" s="343" t="n"/>
+      <c r="O11" s="343" t="n"/>
+      <c r="P11" s="343" t="n"/>
+      <c r="Q11" s="343" t="n"/>
+      <c r="R11" s="343" t="n"/>
+      <c r="S11" s="343" t="n"/>
+      <c r="T11" s="343" t="n"/>
+      <c r="U11" s="465" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="394" t="n"/>
-      <c r="W11" s="394" t="n"/>
-      <c r="X11" s="394" t="n"/>
-      <c r="Y11" s="394" t="n"/>
-      <c r="Z11" s="394" t="n"/>
-      <c r="AA11" s="395" t="n"/>
-      <c r="AB11" s="357" t="n"/>
-      <c r="AC11" s="394" t="n"/>
-      <c r="AD11" s="394" t="n"/>
-      <c r="AE11" s="394" t="n"/>
-      <c r="AF11" s="394" t="n"/>
-      <c r="AG11" s="394" t="n"/>
-      <c r="AH11" s="394" t="n"/>
-      <c r="AI11" s="394" t="n"/>
-      <c r="AJ11" s="394" t="n"/>
-      <c r="AK11" s="394" t="n"/>
-      <c r="AL11" s="394" t="n"/>
-      <c r="AM11" s="394" t="n"/>
-      <c r="AN11" s="395" t="n"/>
+      <c r="V11" s="343" t="n"/>
+      <c r="W11" s="343" t="n"/>
+      <c r="X11" s="343" t="n"/>
+      <c r="Y11" s="343" t="n"/>
+      <c r="Z11" s="343" t="n"/>
+      <c r="AA11" s="343" t="n"/>
+      <c r="AB11" s="464" t="n"/>
+      <c r="AC11" s="343" t="n"/>
+      <c r="AD11" s="343" t="n"/>
+      <c r="AE11" s="343" t="n"/>
+      <c r="AF11" s="343" t="n"/>
+      <c r="AG11" s="343" t="n"/>
+      <c r="AH11" s="343" t="n"/>
+      <c r="AI11" s="343" t="n"/>
+      <c r="AJ11" s="343" t="n"/>
+      <c r="AK11" s="343" t="n"/>
+      <c r="AL11" s="343" t="n"/>
+      <c r="AM11" s="343" t="n"/>
+      <c r="AN11" s="466" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="354" t="inlineStr">
+      <c r="A12" s="463" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="399" t="n"/>
-      <c r="C12" s="399" t="n"/>
-      <c r="D12" s="399" t="n"/>
-      <c r="E12" s="399" t="n"/>
-      <c r="F12" s="399" t="n"/>
-      <c r="G12" s="400" t="n"/>
-      <c r="H12" s="357" t="n"/>
-      <c r="I12" s="399" t="n"/>
-      <c r="J12" s="399" t="n"/>
-      <c r="K12" s="399" t="n"/>
-      <c r="L12" s="399" t="n"/>
-      <c r="M12" s="399" t="n"/>
-      <c r="N12" s="399" t="n"/>
-      <c r="O12" s="399" t="n"/>
-      <c r="P12" s="399" t="n"/>
-      <c r="Q12" s="399" t="n"/>
-      <c r="R12" s="399" t="n"/>
-      <c r="S12" s="399" t="n"/>
-      <c r="T12" s="400" t="n"/>
-      <c r="U12" s="358" t="inlineStr">
+      <c r="B12" s="343" t="n"/>
+      <c r="C12" s="343" t="n"/>
+      <c r="D12" s="343" t="n"/>
+      <c r="E12" s="343" t="n"/>
+      <c r="F12" s="343" t="n"/>
+      <c r="G12" s="343" t="n"/>
+      <c r="H12" s="464" t="n"/>
+      <c r="I12" s="343" t="n"/>
+      <c r="J12" s="343" t="n"/>
+      <c r="K12" s="343" t="n"/>
+      <c r="L12" s="343" t="n"/>
+      <c r="M12" s="343" t="n"/>
+      <c r="N12" s="343" t="n"/>
+      <c r="O12" s="343" t="n"/>
+      <c r="P12" s="343" t="n"/>
+      <c r="Q12" s="343" t="n"/>
+      <c r="R12" s="343" t="n"/>
+      <c r="S12" s="343" t="n"/>
+      <c r="T12" s="343" t="n"/>
+      <c r="U12" s="465" t="inlineStr">
         <is>
           <t>Approval State</t>
         </is>
       </c>
-      <c r="V12" s="399" t="n"/>
-      <c r="W12" s="399" t="n"/>
-      <c r="X12" s="399" t="n"/>
-      <c r="Y12" s="399" t="n"/>
-      <c r="Z12" s="399" t="n"/>
-      <c r="AA12" s="400" t="n"/>
-      <c r="AB12" s="357" t="n"/>
-      <c r="AC12" s="399" t="n"/>
-      <c r="AD12" s="399" t="n"/>
-      <c r="AE12" s="399" t="n"/>
-      <c r="AF12" s="399" t="n"/>
-      <c r="AG12" s="399" t="n"/>
-      <c r="AH12" s="399" t="n"/>
-      <c r="AI12" s="399" t="n"/>
-      <c r="AJ12" s="399" t="n"/>
-      <c r="AK12" s="399" t="n"/>
-      <c r="AL12" s="399" t="n"/>
-      <c r="AM12" s="399" t="n"/>
-      <c r="AN12" s="400" t="n"/>
+      <c r="V12" s="343" t="n"/>
+      <c r="W12" s="343" t="n"/>
+      <c r="X12" s="343" t="n"/>
+      <c r="Y12" s="343" t="n"/>
+      <c r="Z12" s="343" t="n"/>
+      <c r="AA12" s="343" t="n"/>
+      <c r="AB12" s="464" t="n"/>
+      <c r="AC12" s="343" t="n"/>
+      <c r="AD12" s="343" t="n"/>
+      <c r="AE12" s="343" t="n"/>
+      <c r="AF12" s="343" t="n"/>
+      <c r="AG12" s="343" t="n"/>
+      <c r="AH12" s="343" t="n"/>
+      <c r="AI12" s="343" t="n"/>
+      <c r="AJ12" s="343" t="n"/>
+      <c r="AK12" s="343" t="n"/>
+      <c r="AL12" s="343" t="n"/>
+      <c r="AM12" s="343" t="n"/>
+      <c r="AN12" s="466" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1" s="329">
-      <c r="A13" s="354" t="inlineStr">
+      <c r="A13" s="467" t="inlineStr">
         <is>
           <t>Route Step / Due Date</t>
         </is>
       </c>
-      <c r="B13" s="394" t="n"/>
-      <c r="C13" s="394" t="n"/>
-      <c r="D13" s="394" t="n"/>
-      <c r="E13" s="394" t="n"/>
-      <c r="F13" s="394" t="n"/>
-      <c r="G13" s="395" t="n"/>
-      <c r="H13" s="357" t="n"/>
-      <c r="I13" s="394" t="n"/>
-      <c r="J13" s="394" t="n"/>
-      <c r="K13" s="394" t="n"/>
-      <c r="L13" s="394" t="n"/>
-      <c r="M13" s="394" t="n"/>
-      <c r="N13" s="394" t="n"/>
-      <c r="O13" s="394" t="n"/>
-      <c r="P13" s="394" t="n"/>
-      <c r="Q13" s="394" t="n"/>
-      <c r="R13" s="394" t="n"/>
-      <c r="S13" s="394" t="n"/>
-      <c r="T13" s="395" t="n"/>
-      <c r="U13" s="358" t="inlineStr">
+      <c r="B13" s="468" t="n"/>
+      <c r="C13" s="468" t="n"/>
+      <c r="D13" s="468" t="n"/>
+      <c r="E13" s="468" t="n"/>
+      <c r="F13" s="468" t="n"/>
+      <c r="G13" s="468" t="n"/>
+      <c r="H13" s="469" t="n"/>
+      <c r="I13" s="468" t="n"/>
+      <c r="J13" s="468" t="n"/>
+      <c r="K13" s="468" t="n"/>
+      <c r="L13" s="468" t="n"/>
+      <c r="M13" s="468" t="n"/>
+      <c r="N13" s="468" t="n"/>
+      <c r="O13" s="468" t="n"/>
+      <c r="P13" s="468" t="n"/>
+      <c r="Q13" s="468" t="n"/>
+      <c r="R13" s="468" t="n"/>
+      <c r="S13" s="468" t="n"/>
+      <c r="T13" s="468" t="n"/>
+      <c r="U13" s="470" t="inlineStr">
         <is>
           <t>Package Ref</t>
         </is>
       </c>
-      <c r="V13" s="394" t="n"/>
-      <c r="W13" s="394" t="n"/>
-      <c r="X13" s="394" t="n"/>
-      <c r="Y13" s="394" t="n"/>
-      <c r="Z13" s="394" t="n"/>
-      <c r="AA13" s="395" t="n"/>
-      <c r="AB13" s="357" t="n"/>
-      <c r="AC13" s="394" t="n"/>
-      <c r="AD13" s="394" t="n"/>
-      <c r="AE13" s="394" t="n"/>
-      <c r="AF13" s="394" t="n"/>
-      <c r="AG13" s="394" t="n"/>
-      <c r="AH13" s="394" t="n"/>
-      <c r="AI13" s="394" t="n"/>
-      <c r="AJ13" s="394" t="n"/>
-      <c r="AK13" s="394" t="n"/>
-      <c r="AL13" s="394" t="n"/>
-      <c r="AM13" s="394" t="n"/>
-      <c r="AN13" s="395" t="n"/>
+      <c r="V13" s="468" t="n"/>
+      <c r="W13" s="468" t="n"/>
+      <c r="X13" s="468" t="n"/>
+      <c r="Y13" s="468" t="n"/>
+      <c r="Z13" s="468" t="n"/>
+      <c r="AA13" s="468" t="n"/>
+      <c r="AB13" s="469" t="n"/>
+      <c r="AC13" s="468" t="n"/>
+      <c r="AD13" s="468" t="n"/>
+      <c r="AE13" s="468" t="n"/>
+      <c r="AF13" s="468" t="n"/>
+      <c r="AG13" s="468" t="n"/>
+      <c r="AH13" s="468" t="n"/>
+      <c r="AI13" s="468" t="n"/>
+      <c r="AJ13" s="468" t="n"/>
+      <c r="AK13" s="468" t="n"/>
+      <c r="AL13" s="468" t="n"/>
+      <c r="AM13" s="468" t="n"/>
+      <c r="AN13" s="471" t="n"/>
     </row>
-    <row r="14" ht="4" customHeight="1" s="329">
+    <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="359" t="n"/>
       <c r="B14" s="352" t="n"/>
       <c r="C14" s="352" t="n"/>
@@ -5696,413 +6480,413 @@
       <c r="AM14" s="352" t="n"/>
       <c r="AN14" s="352" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="353" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="329">
+      <c r="A15" s="455" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
         </is>
       </c>
-      <c r="B15" s="399" t="n"/>
-      <c r="C15" s="399" t="n"/>
-      <c r="D15" s="399" t="n"/>
-      <c r="E15" s="399" t="n"/>
-      <c r="F15" s="399" t="n"/>
-      <c r="G15" s="399" t="n"/>
-      <c r="H15" s="399" t="n"/>
-      <c r="I15" s="399" t="n"/>
-      <c r="J15" s="399" t="n"/>
-      <c r="K15" s="399" t="n"/>
-      <c r="L15" s="399" t="n"/>
-      <c r="M15" s="399" t="n"/>
-      <c r="N15" s="399" t="n"/>
-      <c r="O15" s="399" t="n"/>
-      <c r="P15" s="399" t="n"/>
-      <c r="Q15" s="399" t="n"/>
-      <c r="R15" s="399" t="n"/>
-      <c r="S15" s="399" t="n"/>
-      <c r="T15" s="399" t="n"/>
-      <c r="U15" s="399" t="n"/>
-      <c r="V15" s="399" t="n"/>
-      <c r="W15" s="399" t="n"/>
-      <c r="X15" s="399" t="n"/>
-      <c r="Y15" s="399" t="n"/>
-      <c r="Z15" s="399" t="n"/>
-      <c r="AA15" s="399" t="n"/>
-      <c r="AB15" s="399" t="n"/>
-      <c r="AC15" s="399" t="n"/>
-      <c r="AD15" s="399" t="n"/>
-      <c r="AE15" s="399" t="n"/>
-      <c r="AF15" s="399" t="n"/>
-      <c r="AG15" s="399" t="n"/>
-      <c r="AH15" s="399" t="n"/>
-      <c r="AI15" s="399" t="n"/>
-      <c r="AJ15" s="399" t="n"/>
-      <c r="AK15" s="399" t="n"/>
-      <c r="AL15" s="399" t="n"/>
-      <c r="AM15" s="399" t="n"/>
-      <c r="AN15" s="400" t="n"/>
+      <c r="B15" s="456" t="n"/>
+      <c r="C15" s="456" t="n"/>
+      <c r="D15" s="456" t="n"/>
+      <c r="E15" s="456" t="n"/>
+      <c r="F15" s="456" t="n"/>
+      <c r="G15" s="456" t="n"/>
+      <c r="H15" s="456" t="n"/>
+      <c r="I15" s="456" t="n"/>
+      <c r="J15" s="456" t="n"/>
+      <c r="K15" s="456" t="n"/>
+      <c r="L15" s="456" t="n"/>
+      <c r="M15" s="456" t="n"/>
+      <c r="N15" s="456" t="n"/>
+      <c r="O15" s="456" t="n"/>
+      <c r="P15" s="456" t="n"/>
+      <c r="Q15" s="456" t="n"/>
+      <c r="R15" s="456" t="n"/>
+      <c r="S15" s="456" t="n"/>
+      <c r="T15" s="456" t="n"/>
+      <c r="U15" s="456" t="n"/>
+      <c r="V15" s="456" t="n"/>
+      <c r="W15" s="456" t="n"/>
+      <c r="X15" s="456" t="n"/>
+      <c r="Y15" s="456" t="n"/>
+      <c r="Z15" s="456" t="n"/>
+      <c r="AA15" s="456" t="n"/>
+      <c r="AB15" s="456" t="n"/>
+      <c r="AC15" s="456" t="n"/>
+      <c r="AD15" s="456" t="n"/>
+      <c r="AE15" s="456" t="n"/>
+      <c r="AF15" s="456" t="n"/>
+      <c r="AG15" s="456" t="n"/>
+      <c r="AH15" s="456" t="n"/>
+      <c r="AI15" s="456" t="n"/>
+      <c r="AJ15" s="456" t="n"/>
+      <c r="AK15" s="456" t="n"/>
+      <c r="AL15" s="456" t="n"/>
+      <c r="AM15" s="456" t="n"/>
+      <c r="AN15" s="457" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="354" t="inlineStr">
+      <c r="A16" s="458" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="B16" s="399" t="n"/>
-      <c r="C16" s="399" t="n"/>
-      <c r="D16" s="399" t="n"/>
-      <c r="E16" s="399" t="n"/>
-      <c r="F16" s="399" t="n"/>
-      <c r="G16" s="400" t="n"/>
-      <c r="H16" s="357" t="n"/>
-      <c r="I16" s="399" t="n"/>
-      <c r="J16" s="399" t="n"/>
-      <c r="K16" s="399" t="n"/>
-      <c r="L16" s="399" t="n"/>
-      <c r="M16" s="399" t="n"/>
-      <c r="N16" s="399" t="n"/>
-      <c r="O16" s="399" t="n"/>
-      <c r="P16" s="399" t="n"/>
-      <c r="Q16" s="399" t="n"/>
-      <c r="R16" s="399" t="n"/>
-      <c r="S16" s="399" t="n"/>
-      <c r="T16" s="400" t="n"/>
-      <c r="U16" s="358" t="inlineStr">
+      <c r="B16" s="459" t="n"/>
+      <c r="C16" s="459" t="n"/>
+      <c r="D16" s="459" t="n"/>
+      <c r="E16" s="459" t="n"/>
+      <c r="F16" s="459" t="n"/>
+      <c r="G16" s="459" t="n"/>
+      <c r="H16" s="460" t="n"/>
+      <c r="I16" s="459" t="n"/>
+      <c r="J16" s="459" t="n"/>
+      <c r="K16" s="459" t="n"/>
+      <c r="L16" s="459" t="n"/>
+      <c r="M16" s="459" t="n"/>
+      <c r="N16" s="459" t="n"/>
+      <c r="O16" s="459" t="n"/>
+      <c r="P16" s="459" t="n"/>
+      <c r="Q16" s="459" t="n"/>
+      <c r="R16" s="459" t="n"/>
+      <c r="S16" s="459" t="n"/>
+      <c r="T16" s="459" t="n"/>
+      <c r="U16" s="461" t="inlineStr">
         <is>
           <t>Linked Route / Package</t>
         </is>
       </c>
-      <c r="V16" s="399" t="n"/>
-      <c r="W16" s="399" t="n"/>
-      <c r="X16" s="399" t="n"/>
-      <c r="Y16" s="399" t="n"/>
-      <c r="Z16" s="399" t="n"/>
-      <c r="AA16" s="400" t="n"/>
-      <c r="AB16" s="357" t="n"/>
-      <c r="AC16" s="399" t="n"/>
-      <c r="AD16" s="399" t="n"/>
-      <c r="AE16" s="399" t="n"/>
-      <c r="AF16" s="399" t="n"/>
-      <c r="AG16" s="399" t="n"/>
-      <c r="AH16" s="399" t="n"/>
-      <c r="AI16" s="399" t="n"/>
-      <c r="AJ16" s="399" t="n"/>
-      <c r="AK16" s="399" t="n"/>
-      <c r="AL16" s="399" t="n"/>
-      <c r="AM16" s="399" t="n"/>
-      <c r="AN16" s="400" t="n"/>
+      <c r="V16" s="459" t="n"/>
+      <c r="W16" s="459" t="n"/>
+      <c r="X16" s="459" t="n"/>
+      <c r="Y16" s="459" t="n"/>
+      <c r="Z16" s="459" t="n"/>
+      <c r="AA16" s="459" t="n"/>
+      <c r="AB16" s="460" t="n"/>
+      <c r="AC16" s="459" t="n"/>
+      <c r="AD16" s="459" t="n"/>
+      <c r="AE16" s="459" t="n"/>
+      <c r="AF16" s="459" t="n"/>
+      <c r="AG16" s="459" t="n"/>
+      <c r="AH16" s="459" t="n"/>
+      <c r="AI16" s="459" t="n"/>
+      <c r="AJ16" s="459" t="n"/>
+      <c r="AK16" s="459" t="n"/>
+      <c r="AL16" s="459" t="n"/>
+      <c r="AM16" s="459" t="n"/>
+      <c r="AN16" s="462" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="354" t="inlineStr">
+      <c r="A17" s="463" t="inlineStr">
         <is>
           <t>Supplier / Customer Spec Ref</t>
         </is>
       </c>
-      <c r="B17" s="399" t="n"/>
-      <c r="C17" s="399" t="n"/>
-      <c r="D17" s="399" t="n"/>
-      <c r="E17" s="399" t="n"/>
-      <c r="F17" s="399" t="n"/>
-      <c r="G17" s="400" t="n"/>
-      <c r="H17" s="357" t="n"/>
-      <c r="I17" s="399" t="n"/>
-      <c r="J17" s="399" t="n"/>
-      <c r="K17" s="399" t="n"/>
-      <c r="L17" s="399" t="n"/>
-      <c r="M17" s="399" t="n"/>
-      <c r="N17" s="399" t="n"/>
-      <c r="O17" s="399" t="n"/>
-      <c r="P17" s="399" t="n"/>
-      <c r="Q17" s="399" t="n"/>
-      <c r="R17" s="399" t="n"/>
-      <c r="S17" s="399" t="n"/>
-      <c r="T17" s="400" t="n"/>
-      <c r="U17" s="358" t="inlineStr">
+      <c r="B17" s="343" t="n"/>
+      <c r="C17" s="343" t="n"/>
+      <c r="D17" s="343" t="n"/>
+      <c r="E17" s="343" t="n"/>
+      <c r="F17" s="343" t="n"/>
+      <c r="G17" s="343" t="n"/>
+      <c r="H17" s="464" t="n"/>
+      <c r="I17" s="343" t="n"/>
+      <c r="J17" s="343" t="n"/>
+      <c r="K17" s="343" t="n"/>
+      <c r="L17" s="343" t="n"/>
+      <c r="M17" s="343" t="n"/>
+      <c r="N17" s="343" t="n"/>
+      <c r="O17" s="343" t="n"/>
+      <c r="P17" s="343" t="n"/>
+      <c r="Q17" s="343" t="n"/>
+      <c r="R17" s="343" t="n"/>
+      <c r="S17" s="343" t="n"/>
+      <c r="T17" s="343" t="n"/>
+      <c r="U17" s="465" t="inlineStr">
         <is>
           <t>Open Actions Present (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="399" t="n"/>
-      <c r="W17" s="399" t="n"/>
-      <c r="X17" s="399" t="n"/>
-      <c r="Y17" s="399" t="n"/>
-      <c r="Z17" s="399" t="n"/>
-      <c r="AA17" s="400" t="n"/>
-      <c r="AB17" s="357" t="n"/>
-      <c r="AC17" s="399" t="n"/>
-      <c r="AD17" s="399" t="n"/>
-      <c r="AE17" s="399" t="n"/>
-      <c r="AF17" s="399" t="n"/>
-      <c r="AG17" s="399" t="n"/>
-      <c r="AH17" s="399" t="n"/>
-      <c r="AI17" s="399" t="n"/>
-      <c r="AJ17" s="399" t="n"/>
-      <c r="AK17" s="399" t="n"/>
-      <c r="AL17" s="399" t="n"/>
-      <c r="AM17" s="399" t="n"/>
-      <c r="AN17" s="400" t="n"/>
+      <c r="V17" s="343" t="n"/>
+      <c r="W17" s="343" t="n"/>
+      <c r="X17" s="343" t="n"/>
+      <c r="Y17" s="343" t="n"/>
+      <c r="Z17" s="343" t="n"/>
+      <c r="AA17" s="343" t="n"/>
+      <c r="AB17" s="464" t="n"/>
+      <c r="AC17" s="343" t="n"/>
+      <c r="AD17" s="343" t="n"/>
+      <c r="AE17" s="343" t="n"/>
+      <c r="AF17" s="343" t="n"/>
+      <c r="AG17" s="343" t="n"/>
+      <c r="AH17" s="343" t="n"/>
+      <c r="AI17" s="343" t="n"/>
+      <c r="AJ17" s="343" t="n"/>
+      <c r="AK17" s="343" t="n"/>
+      <c r="AL17" s="343" t="n"/>
+      <c r="AM17" s="343" t="n"/>
+      <c r="AN17" s="466" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="354" t="inlineStr">
+      <c r="A18" s="463" t="inlineStr">
         <is>
           <t>DISPATCH NOTES / CONDITIONALS</t>
         </is>
       </c>
-      <c r="B18" s="399" t="n"/>
-      <c r="C18" s="399" t="n"/>
-      <c r="D18" s="399" t="n"/>
-      <c r="E18" s="399" t="n"/>
-      <c r="F18" s="399" t="n"/>
-      <c r="G18" s="399" t="n"/>
-      <c r="H18" s="399" t="n"/>
-      <c r="I18" s="399" t="n"/>
-      <c r="J18" s="399" t="n"/>
-      <c r="K18" s="399" t="n"/>
-      <c r="L18" s="399" t="n"/>
-      <c r="M18" s="399" t="n"/>
-      <c r="N18" s="399" t="n"/>
-      <c r="O18" s="399" t="n"/>
-      <c r="P18" s="399" t="n"/>
-      <c r="Q18" s="399" t="n"/>
-      <c r="R18" s="399" t="n"/>
-      <c r="S18" s="399" t="n"/>
-      <c r="T18" s="399" t="n"/>
-      <c r="U18" s="399" t="n"/>
-      <c r="V18" s="399" t="n"/>
-      <c r="W18" s="399" t="n"/>
-      <c r="X18" s="399" t="n"/>
-      <c r="Y18" s="399" t="n"/>
-      <c r="Z18" s="399" t="n"/>
-      <c r="AA18" s="399" t="n"/>
-      <c r="AB18" s="399" t="n"/>
-      <c r="AC18" s="399" t="n"/>
-      <c r="AD18" s="399" t="n"/>
-      <c r="AE18" s="399" t="n"/>
-      <c r="AF18" s="399" t="n"/>
-      <c r="AG18" s="399" t="n"/>
-      <c r="AH18" s="399" t="n"/>
-      <c r="AI18" s="399" t="n"/>
-      <c r="AJ18" s="399" t="n"/>
-      <c r="AK18" s="399" t="n"/>
-      <c r="AL18" s="399" t="n"/>
-      <c r="AM18" s="399" t="n"/>
-      <c r="AN18" s="400" t="n"/>
+      <c r="B18" s="343" t="n"/>
+      <c r="C18" s="343" t="n"/>
+      <c r="D18" s="343" t="n"/>
+      <c r="E18" s="343" t="n"/>
+      <c r="F18" s="343" t="n"/>
+      <c r="G18" s="343" t="n"/>
+      <c r="H18" s="472" t="n"/>
+      <c r="I18" s="343" t="n"/>
+      <c r="J18" s="343" t="n"/>
+      <c r="K18" s="343" t="n"/>
+      <c r="L18" s="343" t="n"/>
+      <c r="M18" s="343" t="n"/>
+      <c r="N18" s="343" t="n"/>
+      <c r="O18" s="343" t="n"/>
+      <c r="P18" s="343" t="n"/>
+      <c r="Q18" s="343" t="n"/>
+      <c r="R18" s="343" t="n"/>
+      <c r="S18" s="343" t="n"/>
+      <c r="T18" s="343" t="n"/>
+      <c r="U18" s="472" t="n"/>
+      <c r="V18" s="343" t="n"/>
+      <c r="W18" s="343" t="n"/>
+      <c r="X18" s="343" t="n"/>
+      <c r="Y18" s="343" t="n"/>
+      <c r="Z18" s="343" t="n"/>
+      <c r="AA18" s="343" t="n"/>
+      <c r="AB18" s="472" t="n"/>
+      <c r="AC18" s="343" t="n"/>
+      <c r="AD18" s="343" t="n"/>
+      <c r="AE18" s="343" t="n"/>
+      <c r="AF18" s="343" t="n"/>
+      <c r="AG18" s="343" t="n"/>
+      <c r="AH18" s="343" t="n"/>
+      <c r="AI18" s="343" t="n"/>
+      <c r="AJ18" s="343" t="n"/>
+      <c r="AK18" s="343" t="n"/>
+      <c r="AL18" s="343" t="n"/>
+      <c r="AM18" s="343" t="n"/>
+      <c r="AN18" s="466" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="357" t="n"/>
-      <c r="B19" s="401" t="n"/>
-      <c r="C19" s="401" t="n"/>
-      <c r="D19" s="401" t="n"/>
-      <c r="E19" s="401" t="n"/>
-      <c r="F19" s="401" t="n"/>
-      <c r="G19" s="401" t="n"/>
-      <c r="H19" s="401" t="n"/>
-      <c r="I19" s="401" t="n"/>
-      <c r="J19" s="401" t="n"/>
-      <c r="K19" s="401" t="n"/>
-      <c r="L19" s="401" t="n"/>
-      <c r="M19" s="401" t="n"/>
-      <c r="N19" s="401" t="n"/>
-      <c r="O19" s="401" t="n"/>
-      <c r="P19" s="401" t="n"/>
-      <c r="Q19" s="401" t="n"/>
-      <c r="R19" s="401" t="n"/>
-      <c r="S19" s="401" t="n"/>
-      <c r="T19" s="401" t="n"/>
-      <c r="U19" s="401" t="n"/>
-      <c r="V19" s="401" t="n"/>
-      <c r="W19" s="401" t="n"/>
-      <c r="X19" s="401" t="n"/>
-      <c r="Y19" s="401" t="n"/>
-      <c r="Z19" s="401" t="n"/>
-      <c r="AA19" s="401" t="n"/>
-      <c r="AB19" s="401" t="n"/>
-      <c r="AC19" s="401" t="n"/>
-      <c r="AD19" s="401" t="n"/>
-      <c r="AE19" s="401" t="n"/>
-      <c r="AF19" s="401" t="n"/>
-      <c r="AG19" s="401" t="n"/>
-      <c r="AH19" s="401" t="n"/>
-      <c r="AI19" s="401" t="n"/>
-      <c r="AJ19" s="401" t="n"/>
-      <c r="AK19" s="401" t="n"/>
-      <c r="AL19" s="401" t="n"/>
-      <c r="AM19" s="401" t="n"/>
-      <c r="AN19" s="402" t="n"/>
+      <c r="A19" s="473" t="n"/>
+      <c r="B19" s="343" t="n"/>
+      <c r="C19" s="343" t="n"/>
+      <c r="D19" s="343" t="n"/>
+      <c r="E19" s="343" t="n"/>
+      <c r="F19" s="343" t="n"/>
+      <c r="G19" s="343" t="n"/>
+      <c r="H19" s="472" t="n"/>
+      <c r="I19" s="343" t="n"/>
+      <c r="J19" s="343" t="n"/>
+      <c r="K19" s="343" t="n"/>
+      <c r="L19" s="343" t="n"/>
+      <c r="M19" s="343" t="n"/>
+      <c r="N19" s="343" t="n"/>
+      <c r="O19" s="343" t="n"/>
+      <c r="P19" s="343" t="n"/>
+      <c r="Q19" s="343" t="n"/>
+      <c r="R19" s="343" t="n"/>
+      <c r="S19" s="343" t="n"/>
+      <c r="T19" s="343" t="n"/>
+      <c r="U19" s="472" t="n"/>
+      <c r="V19" s="343" t="n"/>
+      <c r="W19" s="343" t="n"/>
+      <c r="X19" s="343" t="n"/>
+      <c r="Y19" s="343" t="n"/>
+      <c r="Z19" s="343" t="n"/>
+      <c r="AA19" s="343" t="n"/>
+      <c r="AB19" s="472" t="n"/>
+      <c r="AC19" s="343" t="n"/>
+      <c r="AD19" s="343" t="n"/>
+      <c r="AE19" s="343" t="n"/>
+      <c r="AF19" s="343" t="n"/>
+      <c r="AG19" s="343" t="n"/>
+      <c r="AH19" s="343" t="n"/>
+      <c r="AI19" s="343" t="n"/>
+      <c r="AJ19" s="343" t="n"/>
+      <c r="AK19" s="343" t="n"/>
+      <c r="AL19" s="343" t="n"/>
+      <c r="AM19" s="343" t="n"/>
+      <c r="AN19" s="466" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="403" t="n"/>
-      <c r="B20" s="403" t="n"/>
-      <c r="C20" s="403" t="n"/>
-      <c r="D20" s="403" t="n"/>
-      <c r="E20" s="403" t="n"/>
-      <c r="F20" s="403" t="n"/>
-      <c r="G20" s="403" t="n"/>
-      <c r="H20" s="403" t="n"/>
-      <c r="I20" s="403" t="n"/>
-      <c r="J20" s="403" t="n"/>
-      <c r="K20" s="403" t="n"/>
-      <c r="L20" s="403" t="n"/>
-      <c r="M20" s="403" t="n"/>
-      <c r="N20" s="403" t="n"/>
-      <c r="O20" s="403" t="n"/>
-      <c r="P20" s="403" t="n"/>
-      <c r="Q20" s="403" t="n"/>
-      <c r="R20" s="403" t="n"/>
-      <c r="S20" s="403" t="n"/>
-      <c r="T20" s="403" t="n"/>
-      <c r="U20" s="403" t="n"/>
-      <c r="V20" s="403" t="n"/>
-      <c r="W20" s="403" t="n"/>
-      <c r="X20" s="403" t="n"/>
-      <c r="Y20" s="403" t="n"/>
-      <c r="Z20" s="403" t="n"/>
-      <c r="AA20" s="403" t="n"/>
-      <c r="AB20" s="403" t="n"/>
-      <c r="AC20" s="403" t="n"/>
-      <c r="AD20" s="403" t="n"/>
-      <c r="AE20" s="403" t="n"/>
-      <c r="AF20" s="403" t="n"/>
-      <c r="AG20" s="403" t="n"/>
-      <c r="AH20" s="403" t="n"/>
-      <c r="AI20" s="403" t="n"/>
-      <c r="AJ20" s="403" t="n"/>
-      <c r="AK20" s="403" t="n"/>
-      <c r="AL20" s="403" t="n"/>
-      <c r="AM20" s="403" t="n"/>
-      <c r="AN20" s="404" t="n"/>
+      <c r="A20" s="474" t="n"/>
+      <c r="B20" s="343" t="n"/>
+      <c r="C20" s="343" t="n"/>
+      <c r="D20" s="343" t="n"/>
+      <c r="E20" s="343" t="n"/>
+      <c r="F20" s="343" t="n"/>
+      <c r="G20" s="343" t="n"/>
+      <c r="H20" s="472" t="n"/>
+      <c r="I20" s="343" t="n"/>
+      <c r="J20" s="343" t="n"/>
+      <c r="K20" s="343" t="n"/>
+      <c r="L20" s="343" t="n"/>
+      <c r="M20" s="343" t="n"/>
+      <c r="N20" s="343" t="n"/>
+      <c r="O20" s="343" t="n"/>
+      <c r="P20" s="343" t="n"/>
+      <c r="Q20" s="343" t="n"/>
+      <c r="R20" s="343" t="n"/>
+      <c r="S20" s="343" t="n"/>
+      <c r="T20" s="343" t="n"/>
+      <c r="U20" s="472" t="n"/>
+      <c r="V20" s="343" t="n"/>
+      <c r="W20" s="343" t="n"/>
+      <c r="X20" s="343" t="n"/>
+      <c r="Y20" s="343" t="n"/>
+      <c r="Z20" s="343" t="n"/>
+      <c r="AA20" s="343" t="n"/>
+      <c r="AB20" s="472" t="n"/>
+      <c r="AC20" s="343" t="n"/>
+      <c r="AD20" s="343" t="n"/>
+      <c r="AE20" s="343" t="n"/>
+      <c r="AF20" s="343" t="n"/>
+      <c r="AG20" s="343" t="n"/>
+      <c r="AH20" s="343" t="n"/>
+      <c r="AI20" s="343" t="n"/>
+      <c r="AJ20" s="343" t="n"/>
+      <c r="AK20" s="343" t="n"/>
+      <c r="AL20" s="343" t="n"/>
+      <c r="AM20" s="343" t="n"/>
+      <c r="AN20" s="466" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="354" t="inlineStr">
+      <c r="A21" s="463" t="inlineStr">
         <is>
           <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
         </is>
       </c>
-      <c r="B21" s="399" t="n"/>
-      <c r="C21" s="399" t="n"/>
-      <c r="D21" s="399" t="n"/>
-      <c r="E21" s="399" t="n"/>
-      <c r="F21" s="399" t="n"/>
-      <c r="G21" s="399" t="n"/>
-      <c r="H21" s="399" t="n"/>
-      <c r="I21" s="399" t="n"/>
-      <c r="J21" s="399" t="n"/>
-      <c r="K21" s="399" t="n"/>
-      <c r="L21" s="399" t="n"/>
-      <c r="M21" s="399" t="n"/>
-      <c r="N21" s="399" t="n"/>
-      <c r="O21" s="399" t="n"/>
-      <c r="P21" s="399" t="n"/>
-      <c r="Q21" s="399" t="n"/>
-      <c r="R21" s="399" t="n"/>
-      <c r="S21" s="399" t="n"/>
-      <c r="T21" s="399" t="n"/>
-      <c r="U21" s="399" t="n"/>
-      <c r="V21" s="399" t="n"/>
-      <c r="W21" s="399" t="n"/>
-      <c r="X21" s="399" t="n"/>
-      <c r="Y21" s="399" t="n"/>
-      <c r="Z21" s="399" t="n"/>
-      <c r="AA21" s="399" t="n"/>
-      <c r="AB21" s="399" t="n"/>
-      <c r="AC21" s="399" t="n"/>
-      <c r="AD21" s="399" t="n"/>
-      <c r="AE21" s="399" t="n"/>
-      <c r="AF21" s="399" t="n"/>
-      <c r="AG21" s="399" t="n"/>
-      <c r="AH21" s="399" t="n"/>
-      <c r="AI21" s="399" t="n"/>
-      <c r="AJ21" s="399" t="n"/>
-      <c r="AK21" s="399" t="n"/>
-      <c r="AL21" s="399" t="n"/>
-      <c r="AM21" s="399" t="n"/>
-      <c r="AN21" s="400" t="n"/>
+      <c r="B21" s="343" t="n"/>
+      <c r="C21" s="343" t="n"/>
+      <c r="D21" s="343" t="n"/>
+      <c r="E21" s="343" t="n"/>
+      <c r="F21" s="343" t="n"/>
+      <c r="G21" s="343" t="n"/>
+      <c r="H21" s="472" t="n"/>
+      <c r="I21" s="343" t="n"/>
+      <c r="J21" s="343" t="n"/>
+      <c r="K21" s="343" t="n"/>
+      <c r="L21" s="343" t="n"/>
+      <c r="M21" s="343" t="n"/>
+      <c r="N21" s="343" t="n"/>
+      <c r="O21" s="343" t="n"/>
+      <c r="P21" s="343" t="n"/>
+      <c r="Q21" s="343" t="n"/>
+      <c r="R21" s="343" t="n"/>
+      <c r="S21" s="343" t="n"/>
+      <c r="T21" s="343" t="n"/>
+      <c r="U21" s="472" t="n"/>
+      <c r="V21" s="343" t="n"/>
+      <c r="W21" s="343" t="n"/>
+      <c r="X21" s="343" t="n"/>
+      <c r="Y21" s="343" t="n"/>
+      <c r="Z21" s="343" t="n"/>
+      <c r="AA21" s="343" t="n"/>
+      <c r="AB21" s="472" t="n"/>
+      <c r="AC21" s="343" t="n"/>
+      <c r="AD21" s="343" t="n"/>
+      <c r="AE21" s="343" t="n"/>
+      <c r="AF21" s="343" t="n"/>
+      <c r="AG21" s="343" t="n"/>
+      <c r="AH21" s="343" t="n"/>
+      <c r="AI21" s="343" t="n"/>
+      <c r="AJ21" s="343" t="n"/>
+      <c r="AK21" s="343" t="n"/>
+      <c r="AL21" s="343" t="n"/>
+      <c r="AM21" s="343" t="n"/>
+      <c r="AN21" s="466" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="357" t="n"/>
-      <c r="B22" s="401" t="n"/>
-      <c r="C22" s="401" t="n"/>
-      <c r="D22" s="401" t="n"/>
-      <c r="E22" s="401" t="n"/>
-      <c r="F22" s="401" t="n"/>
-      <c r="G22" s="401" t="n"/>
-      <c r="H22" s="401" t="n"/>
-      <c r="I22" s="401" t="n"/>
-      <c r="J22" s="401" t="n"/>
-      <c r="K22" s="401" t="n"/>
-      <c r="L22" s="401" t="n"/>
-      <c r="M22" s="401" t="n"/>
-      <c r="N22" s="401" t="n"/>
-      <c r="O22" s="401" t="n"/>
-      <c r="P22" s="401" t="n"/>
-      <c r="Q22" s="401" t="n"/>
-      <c r="R22" s="401" t="n"/>
-      <c r="S22" s="401" t="n"/>
-      <c r="T22" s="401" t="n"/>
-      <c r="U22" s="401" t="n"/>
-      <c r="V22" s="401" t="n"/>
-      <c r="W22" s="401" t="n"/>
-      <c r="X22" s="401" t="n"/>
-      <c r="Y22" s="401" t="n"/>
-      <c r="Z22" s="401" t="n"/>
-      <c r="AA22" s="401" t="n"/>
-      <c r="AB22" s="401" t="n"/>
-      <c r="AC22" s="401" t="n"/>
-      <c r="AD22" s="401" t="n"/>
-      <c r="AE22" s="401" t="n"/>
-      <c r="AF22" s="401" t="n"/>
-      <c r="AG22" s="401" t="n"/>
-      <c r="AH22" s="401" t="n"/>
-      <c r="AI22" s="401" t="n"/>
-      <c r="AJ22" s="401" t="n"/>
-      <c r="AK22" s="401" t="n"/>
-      <c r="AL22" s="401" t="n"/>
-      <c r="AM22" s="401" t="n"/>
-      <c r="AN22" s="402" t="n"/>
+      <c r="A22" s="473" t="n"/>
+      <c r="B22" s="343" t="n"/>
+      <c r="C22" s="343" t="n"/>
+      <c r="D22" s="343" t="n"/>
+      <c r="E22" s="343" t="n"/>
+      <c r="F22" s="343" t="n"/>
+      <c r="G22" s="343" t="n"/>
+      <c r="H22" s="472" t="n"/>
+      <c r="I22" s="343" t="n"/>
+      <c r="J22" s="343" t="n"/>
+      <c r="K22" s="343" t="n"/>
+      <c r="L22" s="343" t="n"/>
+      <c r="M22" s="343" t="n"/>
+      <c r="N22" s="343" t="n"/>
+      <c r="O22" s="343" t="n"/>
+      <c r="P22" s="343" t="n"/>
+      <c r="Q22" s="343" t="n"/>
+      <c r="R22" s="343" t="n"/>
+      <c r="S22" s="343" t="n"/>
+      <c r="T22" s="343" t="n"/>
+      <c r="U22" s="472" t="n"/>
+      <c r="V22" s="343" t="n"/>
+      <c r="W22" s="343" t="n"/>
+      <c r="X22" s="343" t="n"/>
+      <c r="Y22" s="343" t="n"/>
+      <c r="Z22" s="343" t="n"/>
+      <c r="AA22" s="343" t="n"/>
+      <c r="AB22" s="472" t="n"/>
+      <c r="AC22" s="343" t="n"/>
+      <c r="AD22" s="343" t="n"/>
+      <c r="AE22" s="343" t="n"/>
+      <c r="AF22" s="343" t="n"/>
+      <c r="AG22" s="343" t="n"/>
+      <c r="AH22" s="343" t="n"/>
+      <c r="AI22" s="343" t="n"/>
+      <c r="AJ22" s="343" t="n"/>
+      <c r="AK22" s="343" t="n"/>
+      <c r="AL22" s="343" t="n"/>
+      <c r="AM22" s="343" t="n"/>
+      <c r="AN22" s="466" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="403" t="n"/>
-      <c r="B23" s="403" t="n"/>
-      <c r="C23" s="403" t="n"/>
-      <c r="D23" s="403" t="n"/>
-      <c r="E23" s="403" t="n"/>
-      <c r="F23" s="403" t="n"/>
-      <c r="G23" s="403" t="n"/>
-      <c r="H23" s="403" t="n"/>
-      <c r="I23" s="403" t="n"/>
-      <c r="J23" s="403" t="n"/>
-      <c r="K23" s="403" t="n"/>
-      <c r="L23" s="403" t="n"/>
-      <c r="M23" s="403" t="n"/>
-      <c r="N23" s="403" t="n"/>
-      <c r="O23" s="403" t="n"/>
-      <c r="P23" s="403" t="n"/>
-      <c r="Q23" s="403" t="n"/>
-      <c r="R23" s="403" t="n"/>
-      <c r="S23" s="403" t="n"/>
-      <c r="T23" s="403" t="n"/>
-      <c r="U23" s="403" t="n"/>
-      <c r="V23" s="403" t="n"/>
-      <c r="W23" s="403" t="n"/>
-      <c r="X23" s="403" t="n"/>
-      <c r="Y23" s="403" t="n"/>
-      <c r="Z23" s="403" t="n"/>
-      <c r="AA23" s="403" t="n"/>
-      <c r="AB23" s="403" t="n"/>
-      <c r="AC23" s="403" t="n"/>
-      <c r="AD23" s="403" t="n"/>
-      <c r="AE23" s="403" t="n"/>
-      <c r="AF23" s="403" t="n"/>
-      <c r="AG23" s="403" t="n"/>
-      <c r="AH23" s="403" t="n"/>
-      <c r="AI23" s="403" t="n"/>
-      <c r="AJ23" s="403" t="n"/>
-      <c r="AK23" s="403" t="n"/>
-      <c r="AL23" s="403" t="n"/>
-      <c r="AM23" s="403" t="n"/>
-      <c r="AN23" s="404" t="n"/>
+      <c r="A23" s="475" t="n"/>
+      <c r="B23" s="468" t="n"/>
+      <c r="C23" s="468" t="n"/>
+      <c r="D23" s="468" t="n"/>
+      <c r="E23" s="468" t="n"/>
+      <c r="F23" s="468" t="n"/>
+      <c r="G23" s="468" t="n"/>
+      <c r="H23" s="476" t="n"/>
+      <c r="I23" s="468" t="n"/>
+      <c r="J23" s="468" t="n"/>
+      <c r="K23" s="468" t="n"/>
+      <c r="L23" s="468" t="n"/>
+      <c r="M23" s="468" t="n"/>
+      <c r="N23" s="468" t="n"/>
+      <c r="O23" s="468" t="n"/>
+      <c r="P23" s="468" t="n"/>
+      <c r="Q23" s="468" t="n"/>
+      <c r="R23" s="468" t="n"/>
+      <c r="S23" s="468" t="n"/>
+      <c r="T23" s="468" t="n"/>
+      <c r="U23" s="476" t="n"/>
+      <c r="V23" s="468" t="n"/>
+      <c r="W23" s="468" t="n"/>
+      <c r="X23" s="468" t="n"/>
+      <c r="Y23" s="468" t="n"/>
+      <c r="Z23" s="468" t="n"/>
+      <c r="AA23" s="468" t="n"/>
+      <c r="AB23" s="476" t="n"/>
+      <c r="AC23" s="468" t="n"/>
+      <c r="AD23" s="468" t="n"/>
+      <c r="AE23" s="468" t="n"/>
+      <c r="AF23" s="468" t="n"/>
+      <c r="AG23" s="468" t="n"/>
+      <c r="AH23" s="468" t="n"/>
+      <c r="AI23" s="468" t="n"/>
+      <c r="AJ23" s="468" t="n"/>
+      <c r="AK23" s="468" t="n"/>
+      <c r="AL23" s="468" t="n"/>
+      <c r="AM23" s="468" t="n"/>
+      <c r="AN23" s="471" t="n"/>
     </row>
-    <row r="24" ht="4" customHeight="1" s="329">
+    <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="364" t="n"/>
       <c r="B24" s="352" t="n"/>
       <c r="C24" s="365" t="n"/>
@@ -6144,417 +6928,417 @@
       <c r="AM24" s="369" t="n"/>
       <c r="AN24" s="352" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1" s="329">
-      <c r="A25" s="353" t="inlineStr">
+    <row r="25" ht="18" customHeight="1" s="329">
+      <c r="A25" s="455" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
         </is>
       </c>
-      <c r="B25" s="399" t="n"/>
-      <c r="C25" s="399" t="n"/>
-      <c r="D25" s="399" t="n"/>
-      <c r="E25" s="399" t="n"/>
-      <c r="F25" s="399" t="n"/>
-      <c r="G25" s="399" t="n"/>
-      <c r="H25" s="399" t="n"/>
-      <c r="I25" s="399" t="n"/>
-      <c r="J25" s="399" t="n"/>
-      <c r="K25" s="399" t="n"/>
-      <c r="L25" s="399" t="n"/>
-      <c r="M25" s="399" t="n"/>
-      <c r="N25" s="399" t="n"/>
-      <c r="O25" s="399" t="n"/>
-      <c r="P25" s="399" t="n"/>
-      <c r="Q25" s="399" t="n"/>
-      <c r="R25" s="399" t="n"/>
-      <c r="S25" s="399" t="n"/>
-      <c r="T25" s="399" t="n"/>
-      <c r="U25" s="399" t="n"/>
-      <c r="V25" s="399" t="n"/>
-      <c r="W25" s="399" t="n"/>
-      <c r="X25" s="399" t="n"/>
-      <c r="Y25" s="399" t="n"/>
-      <c r="Z25" s="399" t="n"/>
-      <c r="AA25" s="399" t="n"/>
-      <c r="AB25" s="399" t="n"/>
-      <c r="AC25" s="399" t="n"/>
-      <c r="AD25" s="399" t="n"/>
-      <c r="AE25" s="399" t="n"/>
-      <c r="AF25" s="399" t="n"/>
-      <c r="AG25" s="399" t="n"/>
-      <c r="AH25" s="399" t="n"/>
-      <c r="AI25" s="399" t="n"/>
-      <c r="AJ25" s="399" t="n"/>
-      <c r="AK25" s="399" t="n"/>
-      <c r="AL25" s="399" t="n"/>
-      <c r="AM25" s="399" t="n"/>
-      <c r="AN25" s="400" t="n"/>
+      <c r="B25" s="456" t="n"/>
+      <c r="C25" s="456" t="n"/>
+      <c r="D25" s="456" t="n"/>
+      <c r="E25" s="456" t="n"/>
+      <c r="F25" s="456" t="n"/>
+      <c r="G25" s="456" t="n"/>
+      <c r="H25" s="456" t="n"/>
+      <c r="I25" s="456" t="n"/>
+      <c r="J25" s="456" t="n"/>
+      <c r="K25" s="456" t="n"/>
+      <c r="L25" s="456" t="n"/>
+      <c r="M25" s="456" t="n"/>
+      <c r="N25" s="456" t="n"/>
+      <c r="O25" s="456" t="n"/>
+      <c r="P25" s="456" t="n"/>
+      <c r="Q25" s="456" t="n"/>
+      <c r="R25" s="456" t="n"/>
+      <c r="S25" s="456" t="n"/>
+      <c r="T25" s="456" t="n"/>
+      <c r="U25" s="456" t="n"/>
+      <c r="V25" s="456" t="n"/>
+      <c r="W25" s="456" t="n"/>
+      <c r="X25" s="456" t="n"/>
+      <c r="Y25" s="456" t="n"/>
+      <c r="Z25" s="456" t="n"/>
+      <c r="AA25" s="456" t="n"/>
+      <c r="AB25" s="456" t="n"/>
+      <c r="AC25" s="456" t="n"/>
+      <c r="AD25" s="456" t="n"/>
+      <c r="AE25" s="456" t="n"/>
+      <c r="AF25" s="456" t="n"/>
+      <c r="AG25" s="456" t="n"/>
+      <c r="AH25" s="456" t="n"/>
+      <c r="AI25" s="456" t="n"/>
+      <c r="AJ25" s="456" t="n"/>
+      <c r="AK25" s="456" t="n"/>
+      <c r="AL25" s="456" t="n"/>
+      <c r="AM25" s="456" t="n"/>
+      <c r="AN25" s="457" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="329">
-      <c r="A26" s="370" t="inlineStr">
+    <row r="26" ht="18" customHeight="1" s="329">
+      <c r="A26" s="477" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="400" t="n"/>
-      <c r="C26" s="371" t="inlineStr">
+      <c r="B26" s="478" t="n"/>
+      <c r="C26" s="479" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="399" t="n"/>
-      <c r="E26" s="400" t="n"/>
-      <c r="F26" s="371" t="inlineStr">
+      <c r="D26" s="478" t="n"/>
+      <c r="E26" s="478" t="n"/>
+      <c r="F26" s="479" t="inlineStr">
         <is>
           <t>Requirement / Check</t>
         </is>
       </c>
-      <c r="G26" s="399" t="n"/>
-      <c r="H26" s="399" t="n"/>
-      <c r="I26" s="399" t="n"/>
-      <c r="J26" s="399" t="n"/>
-      <c r="K26" s="399" t="n"/>
-      <c r="L26" s="399" t="n"/>
-      <c r="M26" s="399" t="n"/>
-      <c r="N26" s="399" t="n"/>
-      <c r="O26" s="399" t="n"/>
-      <c r="P26" s="399" t="n"/>
-      <c r="Q26" s="399" t="n"/>
-      <c r="R26" s="399" t="n"/>
-      <c r="S26" s="400" t="n"/>
-      <c r="T26" s="371" t="inlineStr">
+      <c r="G26" s="478" t="n"/>
+      <c r="H26" s="478" t="n"/>
+      <c r="I26" s="478" t="n"/>
+      <c r="J26" s="478" t="n"/>
+      <c r="K26" s="478" t="n"/>
+      <c r="L26" s="478" t="n"/>
+      <c r="M26" s="478" t="n"/>
+      <c r="N26" s="478" t="n"/>
+      <c r="O26" s="478" t="n"/>
+      <c r="P26" s="478" t="n"/>
+      <c r="Q26" s="478" t="n"/>
+      <c r="R26" s="478" t="n"/>
+      <c r="S26" s="478" t="n"/>
+      <c r="T26" s="479" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="399" t="n"/>
-      <c r="V26" s="399" t="n"/>
-      <c r="W26" s="399" t="n"/>
-      <c r="X26" s="399" t="n"/>
-      <c r="Y26" s="399" t="n"/>
-      <c r="Z26" s="399" t="n"/>
-      <c r="AA26" s="399" t="n"/>
-      <c r="AB26" s="399" t="n"/>
-      <c r="AC26" s="399" t="n"/>
-      <c r="AD26" s="399" t="n"/>
-      <c r="AE26" s="400" t="n"/>
-      <c r="AF26" s="371" t="inlineStr">
+      <c r="U26" s="478" t="n"/>
+      <c r="V26" s="478" t="n"/>
+      <c r="W26" s="478" t="n"/>
+      <c r="X26" s="478" t="n"/>
+      <c r="Y26" s="478" t="n"/>
+      <c r="Z26" s="478" t="n"/>
+      <c r="AA26" s="478" t="n"/>
+      <c r="AB26" s="478" t="n"/>
+      <c r="AC26" s="478" t="n"/>
+      <c r="AD26" s="478" t="n"/>
+      <c r="AE26" s="478" t="n"/>
+      <c r="AF26" s="479" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="399" t="n"/>
-      <c r="AH26" s="399" t="n"/>
-      <c r="AI26" s="400" t="n"/>
-      <c r="AJ26" s="371" t="inlineStr">
+      <c r="AG26" s="478" t="n"/>
+      <c r="AH26" s="478" t="n"/>
+      <c r="AI26" s="478" t="n"/>
+      <c r="AJ26" s="479" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="399" t="n"/>
-      <c r="AL26" s="400" t="n"/>
-      <c r="AM26" s="371" t="inlineStr">
+      <c r="AK26" s="478" t="n"/>
+      <c r="AL26" s="478" t="n"/>
+      <c r="AM26" s="479" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="400" t="n"/>
+      <c r="AN26" s="480" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="372">
+      <c r="A27" s="481">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="404" t="n"/>
-      <c r="C27" s="373" t="inlineStr">
+      <c r="B27" s="459" t="n"/>
+      <c r="C27" s="482" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="403" t="n"/>
-      <c r="E27" s="404" t="n"/>
-      <c r="F27" s="374" t="n"/>
-      <c r="G27" s="403" t="n"/>
-      <c r="H27" s="403" t="n"/>
-      <c r="I27" s="403" t="n"/>
-      <c r="J27" s="403" t="n"/>
-      <c r="K27" s="403" t="n"/>
-      <c r="L27" s="403" t="n"/>
-      <c r="M27" s="403" t="n"/>
-      <c r="N27" s="403" t="n"/>
-      <c r="O27" s="403" t="n"/>
-      <c r="P27" s="403" t="n"/>
-      <c r="Q27" s="403" t="n"/>
-      <c r="R27" s="403" t="n"/>
-      <c r="S27" s="404" t="n"/>
-      <c r="T27" s="375" t="n"/>
-      <c r="U27" s="403" t="n"/>
-      <c r="V27" s="403" t="n"/>
-      <c r="W27" s="403" t="n"/>
-      <c r="X27" s="403" t="n"/>
-      <c r="Y27" s="403" t="n"/>
-      <c r="Z27" s="403" t="n"/>
-      <c r="AA27" s="403" t="n"/>
-      <c r="AB27" s="403" t="n"/>
-      <c r="AC27" s="403" t="n"/>
-      <c r="AD27" s="403" t="n"/>
-      <c r="AE27" s="404" t="n"/>
-      <c r="AF27" s="374" t="n"/>
-      <c r="AG27" s="403" t="n"/>
-      <c r="AH27" s="403" t="n"/>
-      <c r="AI27" s="404" t="n"/>
-      <c r="AJ27" s="374" t="n"/>
-      <c r="AK27" s="403" t="n"/>
-      <c r="AL27" s="404" t="n"/>
-      <c r="AM27" s="376" t="n"/>
-      <c r="AN27" s="404" t="n"/>
+      <c r="D27" s="459" t="n"/>
+      <c r="E27" s="459" t="n"/>
+      <c r="F27" s="460" t="n"/>
+      <c r="G27" s="459" t="n"/>
+      <c r="H27" s="459" t="n"/>
+      <c r="I27" s="459" t="n"/>
+      <c r="J27" s="459" t="n"/>
+      <c r="K27" s="459" t="n"/>
+      <c r="L27" s="459" t="n"/>
+      <c r="M27" s="459" t="n"/>
+      <c r="N27" s="459" t="n"/>
+      <c r="O27" s="459" t="n"/>
+      <c r="P27" s="459" t="n"/>
+      <c r="Q27" s="459" t="n"/>
+      <c r="R27" s="459" t="n"/>
+      <c r="S27" s="459" t="n"/>
+      <c r="T27" s="483" t="n"/>
+      <c r="U27" s="459" t="n"/>
+      <c r="V27" s="459" t="n"/>
+      <c r="W27" s="459" t="n"/>
+      <c r="X27" s="459" t="n"/>
+      <c r="Y27" s="459" t="n"/>
+      <c r="Z27" s="459" t="n"/>
+      <c r="AA27" s="459" t="n"/>
+      <c r="AB27" s="459" t="n"/>
+      <c r="AC27" s="459" t="n"/>
+      <c r="AD27" s="459" t="n"/>
+      <c r="AE27" s="459" t="n"/>
+      <c r="AF27" s="460" t="n"/>
+      <c r="AG27" s="459" t="n"/>
+      <c r="AH27" s="459" t="n"/>
+      <c r="AI27" s="459" t="n"/>
+      <c r="AJ27" s="460" t="n"/>
+      <c r="AK27" s="459" t="n"/>
+      <c r="AL27" s="459" t="n"/>
+      <c r="AM27" s="484" t="n"/>
+      <c r="AN27" s="462" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="372">
+      <c r="A28" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="404" t="n"/>
-      <c r="C28" s="373" t="inlineStr">
+      <c r="B28" s="343" t="n"/>
+      <c r="C28" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="403" t="n"/>
-      <c r="E28" s="404" t="n"/>
-      <c r="F28" s="374" t="n"/>
-      <c r="G28" s="403" t="n"/>
-      <c r="H28" s="403" t="n"/>
-      <c r="I28" s="403" t="n"/>
-      <c r="J28" s="403" t="n"/>
-      <c r="K28" s="403" t="n"/>
-      <c r="L28" s="403" t="n"/>
-      <c r="M28" s="403" t="n"/>
-      <c r="N28" s="403" t="n"/>
-      <c r="O28" s="403" t="n"/>
-      <c r="P28" s="403" t="n"/>
-      <c r="Q28" s="403" t="n"/>
-      <c r="R28" s="403" t="n"/>
-      <c r="S28" s="404" t="n"/>
-      <c r="T28" s="375" t="n"/>
-      <c r="U28" s="403" t="n"/>
-      <c r="V28" s="403" t="n"/>
-      <c r="W28" s="403" t="n"/>
-      <c r="X28" s="403" t="n"/>
-      <c r="Y28" s="403" t="n"/>
-      <c r="Z28" s="403" t="n"/>
-      <c r="AA28" s="403" t="n"/>
-      <c r="AB28" s="403" t="n"/>
-      <c r="AC28" s="403" t="n"/>
-      <c r="AD28" s="403" t="n"/>
-      <c r="AE28" s="404" t="n"/>
-      <c r="AF28" s="374" t="n"/>
-      <c r="AG28" s="403" t="n"/>
-      <c r="AH28" s="403" t="n"/>
-      <c r="AI28" s="404" t="n"/>
-      <c r="AJ28" s="374" t="n"/>
-      <c r="AK28" s="403" t="n"/>
-      <c r="AL28" s="404" t="n"/>
-      <c r="AM28" s="376" t="n"/>
-      <c r="AN28" s="404" t="n"/>
+      <c r="D28" s="343" t="n"/>
+      <c r="E28" s="343" t="n"/>
+      <c r="F28" s="464" t="n"/>
+      <c r="G28" s="343" t="n"/>
+      <c r="H28" s="343" t="n"/>
+      <c r="I28" s="343" t="n"/>
+      <c r="J28" s="343" t="n"/>
+      <c r="K28" s="343" t="n"/>
+      <c r="L28" s="343" t="n"/>
+      <c r="M28" s="343" t="n"/>
+      <c r="N28" s="343" t="n"/>
+      <c r="O28" s="343" t="n"/>
+      <c r="P28" s="343" t="n"/>
+      <c r="Q28" s="343" t="n"/>
+      <c r="R28" s="343" t="n"/>
+      <c r="S28" s="343" t="n"/>
+      <c r="T28" s="487" t="n"/>
+      <c r="U28" s="343" t="n"/>
+      <c r="V28" s="343" t="n"/>
+      <c r="W28" s="343" t="n"/>
+      <c r="X28" s="343" t="n"/>
+      <c r="Y28" s="343" t="n"/>
+      <c r="Z28" s="343" t="n"/>
+      <c r="AA28" s="343" t="n"/>
+      <c r="AB28" s="343" t="n"/>
+      <c r="AC28" s="343" t="n"/>
+      <c r="AD28" s="343" t="n"/>
+      <c r="AE28" s="343" t="n"/>
+      <c r="AF28" s="464" t="n"/>
+      <c r="AG28" s="343" t="n"/>
+      <c r="AH28" s="343" t="n"/>
+      <c r="AI28" s="343" t="n"/>
+      <c r="AJ28" s="464" t="n"/>
+      <c r="AK28" s="343" t="n"/>
+      <c r="AL28" s="343" t="n"/>
+      <c r="AM28" s="488" t="n"/>
+      <c r="AN28" s="466" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="372">
+      <c r="A29" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="404" t="n"/>
-      <c r="C29" s="373" t="inlineStr">
+      <c r="B29" s="343" t="n"/>
+      <c r="C29" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="403" t="n"/>
-      <c r="E29" s="404" t="n"/>
-      <c r="F29" s="374" t="n"/>
-      <c r="G29" s="403" t="n"/>
-      <c r="H29" s="403" t="n"/>
-      <c r="I29" s="403" t="n"/>
-      <c r="J29" s="403" t="n"/>
-      <c r="K29" s="403" t="n"/>
-      <c r="L29" s="403" t="n"/>
-      <c r="M29" s="403" t="n"/>
-      <c r="N29" s="403" t="n"/>
-      <c r="O29" s="403" t="n"/>
-      <c r="P29" s="403" t="n"/>
-      <c r="Q29" s="403" t="n"/>
-      <c r="R29" s="403" t="n"/>
-      <c r="S29" s="404" t="n"/>
-      <c r="T29" s="375" t="n"/>
-      <c r="U29" s="403" t="n"/>
-      <c r="V29" s="403" t="n"/>
-      <c r="W29" s="403" t="n"/>
-      <c r="X29" s="403" t="n"/>
-      <c r="Y29" s="403" t="n"/>
-      <c r="Z29" s="403" t="n"/>
-      <c r="AA29" s="403" t="n"/>
-      <c r="AB29" s="403" t="n"/>
-      <c r="AC29" s="403" t="n"/>
-      <c r="AD29" s="403" t="n"/>
-      <c r="AE29" s="404" t="n"/>
-      <c r="AF29" s="374" t="n"/>
-      <c r="AG29" s="403" t="n"/>
-      <c r="AH29" s="403" t="n"/>
-      <c r="AI29" s="404" t="n"/>
-      <c r="AJ29" s="374" t="n"/>
-      <c r="AK29" s="403" t="n"/>
-      <c r="AL29" s="404" t="n"/>
-      <c r="AM29" s="376" t="n"/>
-      <c r="AN29" s="404" t="n"/>
+      <c r="D29" s="343" t="n"/>
+      <c r="E29" s="343" t="n"/>
+      <c r="F29" s="464" t="n"/>
+      <c r="G29" s="343" t="n"/>
+      <c r="H29" s="343" t="n"/>
+      <c r="I29" s="343" t="n"/>
+      <c r="J29" s="343" t="n"/>
+      <c r="K29" s="343" t="n"/>
+      <c r="L29" s="343" t="n"/>
+      <c r="M29" s="343" t="n"/>
+      <c r="N29" s="343" t="n"/>
+      <c r="O29" s="343" t="n"/>
+      <c r="P29" s="343" t="n"/>
+      <c r="Q29" s="343" t="n"/>
+      <c r="R29" s="343" t="n"/>
+      <c r="S29" s="343" t="n"/>
+      <c r="T29" s="487" t="n"/>
+      <c r="U29" s="343" t="n"/>
+      <c r="V29" s="343" t="n"/>
+      <c r="W29" s="343" t="n"/>
+      <c r="X29" s="343" t="n"/>
+      <c r="Y29" s="343" t="n"/>
+      <c r="Z29" s="343" t="n"/>
+      <c r="AA29" s="343" t="n"/>
+      <c r="AB29" s="343" t="n"/>
+      <c r="AC29" s="343" t="n"/>
+      <c r="AD29" s="343" t="n"/>
+      <c r="AE29" s="343" t="n"/>
+      <c r="AF29" s="464" t="n"/>
+      <c r="AG29" s="343" t="n"/>
+      <c r="AH29" s="343" t="n"/>
+      <c r="AI29" s="343" t="n"/>
+      <c r="AJ29" s="464" t="n"/>
+      <c r="AK29" s="343" t="n"/>
+      <c r="AL29" s="343" t="n"/>
+      <c r="AM29" s="488" t="n"/>
+      <c r="AN29" s="466" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="372">
+      <c r="A30" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="404" t="n"/>
-      <c r="C30" s="373" t="inlineStr">
+      <c r="B30" s="343" t="n"/>
+      <c r="C30" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="403" t="n"/>
-      <c r="E30" s="404" t="n"/>
-      <c r="F30" s="374" t="n"/>
-      <c r="G30" s="403" t="n"/>
-      <c r="H30" s="403" t="n"/>
-      <c r="I30" s="403" t="n"/>
-      <c r="J30" s="403" t="n"/>
-      <c r="K30" s="403" t="n"/>
-      <c r="L30" s="403" t="n"/>
-      <c r="M30" s="403" t="n"/>
-      <c r="N30" s="403" t="n"/>
-      <c r="O30" s="403" t="n"/>
-      <c r="P30" s="403" t="n"/>
-      <c r="Q30" s="403" t="n"/>
-      <c r="R30" s="403" t="n"/>
-      <c r="S30" s="404" t="n"/>
-      <c r="T30" s="375" t="n"/>
-      <c r="U30" s="403" t="n"/>
-      <c r="V30" s="403" t="n"/>
-      <c r="W30" s="403" t="n"/>
-      <c r="X30" s="403" t="n"/>
-      <c r="Y30" s="403" t="n"/>
-      <c r="Z30" s="403" t="n"/>
-      <c r="AA30" s="403" t="n"/>
-      <c r="AB30" s="403" t="n"/>
-      <c r="AC30" s="403" t="n"/>
-      <c r="AD30" s="403" t="n"/>
-      <c r="AE30" s="404" t="n"/>
-      <c r="AF30" s="374" t="n"/>
-      <c r="AG30" s="403" t="n"/>
-      <c r="AH30" s="403" t="n"/>
-      <c r="AI30" s="404" t="n"/>
-      <c r="AJ30" s="374" t="n"/>
-      <c r="AK30" s="403" t="n"/>
-      <c r="AL30" s="404" t="n"/>
-      <c r="AM30" s="376" t="n"/>
-      <c r="AN30" s="404" t="n"/>
+      <c r="D30" s="343" t="n"/>
+      <c r="E30" s="343" t="n"/>
+      <c r="F30" s="464" t="n"/>
+      <c r="G30" s="343" t="n"/>
+      <c r="H30" s="343" t="n"/>
+      <c r="I30" s="343" t="n"/>
+      <c r="J30" s="343" t="n"/>
+      <c r="K30" s="343" t="n"/>
+      <c r="L30" s="343" t="n"/>
+      <c r="M30" s="343" t="n"/>
+      <c r="N30" s="343" t="n"/>
+      <c r="O30" s="343" t="n"/>
+      <c r="P30" s="343" t="n"/>
+      <c r="Q30" s="343" t="n"/>
+      <c r="R30" s="343" t="n"/>
+      <c r="S30" s="343" t="n"/>
+      <c r="T30" s="487" t="n"/>
+      <c r="U30" s="343" t="n"/>
+      <c r="V30" s="343" t="n"/>
+      <c r="W30" s="343" t="n"/>
+      <c r="X30" s="343" t="n"/>
+      <c r="Y30" s="343" t="n"/>
+      <c r="Z30" s="343" t="n"/>
+      <c r="AA30" s="343" t="n"/>
+      <c r="AB30" s="343" t="n"/>
+      <c r="AC30" s="343" t="n"/>
+      <c r="AD30" s="343" t="n"/>
+      <c r="AE30" s="343" t="n"/>
+      <c r="AF30" s="464" t="n"/>
+      <c r="AG30" s="343" t="n"/>
+      <c r="AH30" s="343" t="n"/>
+      <c r="AI30" s="343" t="n"/>
+      <c r="AJ30" s="464" t="n"/>
+      <c r="AK30" s="343" t="n"/>
+      <c r="AL30" s="343" t="n"/>
+      <c r="AM30" s="488" t="n"/>
+      <c r="AN30" s="466" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="372">
+      <c r="A31" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="404" t="n"/>
-      <c r="C31" s="373" t="inlineStr">
+      <c r="B31" s="343" t="n"/>
+      <c r="C31" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="403" t="n"/>
-      <c r="E31" s="404" t="n"/>
-      <c r="F31" s="374" t="n"/>
-      <c r="G31" s="403" t="n"/>
-      <c r="H31" s="403" t="n"/>
-      <c r="I31" s="403" t="n"/>
-      <c r="J31" s="403" t="n"/>
-      <c r="K31" s="403" t="n"/>
-      <c r="L31" s="403" t="n"/>
-      <c r="M31" s="403" t="n"/>
-      <c r="N31" s="403" t="n"/>
-      <c r="O31" s="403" t="n"/>
-      <c r="P31" s="403" t="n"/>
-      <c r="Q31" s="403" t="n"/>
-      <c r="R31" s="403" t="n"/>
-      <c r="S31" s="404" t="n"/>
-      <c r="T31" s="375" t="n"/>
-      <c r="U31" s="403" t="n"/>
-      <c r="V31" s="403" t="n"/>
-      <c r="W31" s="403" t="n"/>
-      <c r="X31" s="403" t="n"/>
-      <c r="Y31" s="403" t="n"/>
-      <c r="Z31" s="403" t="n"/>
-      <c r="AA31" s="403" t="n"/>
-      <c r="AB31" s="403" t="n"/>
-      <c r="AC31" s="403" t="n"/>
-      <c r="AD31" s="403" t="n"/>
-      <c r="AE31" s="404" t="n"/>
-      <c r="AF31" s="374" t="n"/>
-      <c r="AG31" s="403" t="n"/>
-      <c r="AH31" s="403" t="n"/>
-      <c r="AI31" s="404" t="n"/>
-      <c r="AJ31" s="374" t="n"/>
-      <c r="AK31" s="403" t="n"/>
-      <c r="AL31" s="404" t="n"/>
-      <c r="AM31" s="376" t="n"/>
-      <c r="AN31" s="404" t="n"/>
+      <c r="D31" s="343" t="n"/>
+      <c r="E31" s="343" t="n"/>
+      <c r="F31" s="464" t="n"/>
+      <c r="G31" s="343" t="n"/>
+      <c r="H31" s="343" t="n"/>
+      <c r="I31" s="343" t="n"/>
+      <c r="J31" s="343" t="n"/>
+      <c r="K31" s="343" t="n"/>
+      <c r="L31" s="343" t="n"/>
+      <c r="M31" s="343" t="n"/>
+      <c r="N31" s="343" t="n"/>
+      <c r="O31" s="343" t="n"/>
+      <c r="P31" s="343" t="n"/>
+      <c r="Q31" s="343" t="n"/>
+      <c r="R31" s="343" t="n"/>
+      <c r="S31" s="343" t="n"/>
+      <c r="T31" s="487" t="n"/>
+      <c r="U31" s="343" t="n"/>
+      <c r="V31" s="343" t="n"/>
+      <c r="W31" s="343" t="n"/>
+      <c r="X31" s="343" t="n"/>
+      <c r="Y31" s="343" t="n"/>
+      <c r="Z31" s="343" t="n"/>
+      <c r="AA31" s="343" t="n"/>
+      <c r="AB31" s="343" t="n"/>
+      <c r="AC31" s="343" t="n"/>
+      <c r="AD31" s="343" t="n"/>
+      <c r="AE31" s="343" t="n"/>
+      <c r="AF31" s="464" t="n"/>
+      <c r="AG31" s="343" t="n"/>
+      <c r="AH31" s="343" t="n"/>
+      <c r="AI31" s="343" t="n"/>
+      <c r="AJ31" s="464" t="n"/>
+      <c r="AK31" s="343" t="n"/>
+      <c r="AL31" s="343" t="n"/>
+      <c r="AM31" s="488" t="n"/>
+      <c r="AN31" s="466" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="372">
+      <c r="A32" s="489">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="404" t="n"/>
-      <c r="C32" s="373" t="inlineStr">
+      <c r="B32" s="468" t="n"/>
+      <c r="C32" s="490" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="403" t="n"/>
-      <c r="E32" s="404" t="n"/>
-      <c r="F32" s="374" t="n"/>
-      <c r="G32" s="403" t="n"/>
-      <c r="H32" s="403" t="n"/>
-      <c r="I32" s="403" t="n"/>
-      <c r="J32" s="403" t="n"/>
-      <c r="K32" s="403" t="n"/>
-      <c r="L32" s="403" t="n"/>
-      <c r="M32" s="403" t="n"/>
-      <c r="N32" s="403" t="n"/>
-      <c r="O32" s="403" t="n"/>
-      <c r="P32" s="403" t="n"/>
-      <c r="Q32" s="403" t="n"/>
-      <c r="R32" s="403" t="n"/>
-      <c r="S32" s="404" t="n"/>
-      <c r="T32" s="375" t="n"/>
-      <c r="U32" s="403" t="n"/>
-      <c r="V32" s="403" t="n"/>
-      <c r="W32" s="403" t="n"/>
-      <c r="X32" s="403" t="n"/>
-      <c r="Y32" s="403" t="n"/>
-      <c r="Z32" s="403" t="n"/>
-      <c r="AA32" s="403" t="n"/>
-      <c r="AB32" s="403" t="n"/>
-      <c r="AC32" s="403" t="n"/>
-      <c r="AD32" s="403" t="n"/>
-      <c r="AE32" s="404" t="n"/>
-      <c r="AF32" s="374" t="n"/>
-      <c r="AG32" s="403" t="n"/>
-      <c r="AH32" s="403" t="n"/>
-      <c r="AI32" s="404" t="n"/>
-      <c r="AJ32" s="374" t="n"/>
-      <c r="AK32" s="403" t="n"/>
-      <c r="AL32" s="404" t="n"/>
-      <c r="AM32" s="376" t="n"/>
-      <c r="AN32" s="404" t="n"/>
+      <c r="D32" s="468" t="n"/>
+      <c r="E32" s="468" t="n"/>
+      <c r="F32" s="469" t="n"/>
+      <c r="G32" s="468" t="n"/>
+      <c r="H32" s="468" t="n"/>
+      <c r="I32" s="468" t="n"/>
+      <c r="J32" s="468" t="n"/>
+      <c r="K32" s="468" t="n"/>
+      <c r="L32" s="468" t="n"/>
+      <c r="M32" s="468" t="n"/>
+      <c r="N32" s="468" t="n"/>
+      <c r="O32" s="468" t="n"/>
+      <c r="P32" s="468" t="n"/>
+      <c r="Q32" s="468" t="n"/>
+      <c r="R32" s="468" t="n"/>
+      <c r="S32" s="468" t="n"/>
+      <c r="T32" s="491" t="n"/>
+      <c r="U32" s="468" t="n"/>
+      <c r="V32" s="468" t="n"/>
+      <c r="W32" s="468" t="n"/>
+      <c r="X32" s="468" t="n"/>
+      <c r="Y32" s="468" t="n"/>
+      <c r="Z32" s="468" t="n"/>
+      <c r="AA32" s="468" t="n"/>
+      <c r="AB32" s="468" t="n"/>
+      <c r="AC32" s="468" t="n"/>
+      <c r="AD32" s="468" t="n"/>
+      <c r="AE32" s="468" t="n"/>
+      <c r="AF32" s="469" t="n"/>
+      <c r="AG32" s="468" t="n"/>
+      <c r="AH32" s="468" t="n"/>
+      <c r="AI32" s="468" t="n"/>
+      <c r="AJ32" s="469" t="n"/>
+      <c r="AK32" s="468" t="n"/>
+      <c r="AL32" s="468" t="n"/>
+      <c r="AM32" s="492" t="n"/>
+      <c r="AN32" s="471" t="n"/>
     </row>
-    <row r="33" ht="4" customHeight="1" s="329">
+    <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="359" t="n"/>
       <c r="B33" s="352" t="n"/>
       <c r="C33" s="352" t="n"/>
@@ -6596,153 +7380,153 @@
       <c r="AM33" s="352" t="n"/>
       <c r="AN33" s="352" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1" s="329">
-      <c r="A34" s="353" t="inlineStr">
+    <row r="34" ht="18" customHeight="1" s="329">
+      <c r="A34" s="455" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="399" t="n"/>
-      <c r="C34" s="399" t="n"/>
-      <c r="D34" s="399" t="n"/>
-      <c r="E34" s="399" t="n"/>
-      <c r="F34" s="399" t="n"/>
-      <c r="G34" s="399" t="n"/>
-      <c r="H34" s="399" t="n"/>
-      <c r="I34" s="399" t="n"/>
-      <c r="J34" s="399" t="n"/>
-      <c r="K34" s="399" t="n"/>
-      <c r="L34" s="399" t="n"/>
-      <c r="M34" s="399" t="n"/>
-      <c r="N34" s="399" t="n"/>
-      <c r="O34" s="399" t="n"/>
-      <c r="P34" s="399" t="n"/>
-      <c r="Q34" s="399" t="n"/>
-      <c r="R34" s="399" t="n"/>
-      <c r="S34" s="399" t="n"/>
-      <c r="T34" s="399" t="n"/>
-      <c r="U34" s="399" t="n"/>
-      <c r="V34" s="399" t="n"/>
-      <c r="W34" s="399" t="n"/>
-      <c r="X34" s="399" t="n"/>
-      <c r="Y34" s="399" t="n"/>
-      <c r="Z34" s="399" t="n"/>
-      <c r="AA34" s="399" t="n"/>
-      <c r="AB34" s="399" t="n"/>
-      <c r="AC34" s="399" t="n"/>
-      <c r="AD34" s="399" t="n"/>
-      <c r="AE34" s="399" t="n"/>
-      <c r="AF34" s="399" t="n"/>
-      <c r="AG34" s="399" t="n"/>
-      <c r="AH34" s="399" t="n"/>
-      <c r="AI34" s="399" t="n"/>
-      <c r="AJ34" s="399" t="n"/>
-      <c r="AK34" s="399" t="n"/>
-      <c r="AL34" s="399" t="n"/>
-      <c r="AM34" s="399" t="n"/>
-      <c r="AN34" s="400" t="n"/>
+      <c r="B34" s="456" t="n"/>
+      <c r="C34" s="456" t="n"/>
+      <c r="D34" s="456" t="n"/>
+      <c r="E34" s="456" t="n"/>
+      <c r="F34" s="456" t="n"/>
+      <c r="G34" s="456" t="n"/>
+      <c r="H34" s="456" t="n"/>
+      <c r="I34" s="456" t="n"/>
+      <c r="J34" s="456" t="n"/>
+      <c r="K34" s="456" t="n"/>
+      <c r="L34" s="456" t="n"/>
+      <c r="M34" s="456" t="n"/>
+      <c r="N34" s="456" t="n"/>
+      <c r="O34" s="456" t="n"/>
+      <c r="P34" s="456" t="n"/>
+      <c r="Q34" s="456" t="n"/>
+      <c r="R34" s="456" t="n"/>
+      <c r="S34" s="456" t="n"/>
+      <c r="T34" s="456" t="n"/>
+      <c r="U34" s="456" t="n"/>
+      <c r="V34" s="456" t="n"/>
+      <c r="W34" s="456" t="n"/>
+      <c r="X34" s="456" t="n"/>
+      <c r="Y34" s="456" t="n"/>
+      <c r="Z34" s="456" t="n"/>
+      <c r="AA34" s="456" t="n"/>
+      <c r="AB34" s="456" t="n"/>
+      <c r="AC34" s="456" t="n"/>
+      <c r="AD34" s="456" t="n"/>
+      <c r="AE34" s="456" t="n"/>
+      <c r="AF34" s="456" t="n"/>
+      <c r="AG34" s="456" t="n"/>
+      <c r="AH34" s="456" t="n"/>
+      <c r="AI34" s="456" t="n"/>
+      <c r="AJ34" s="456" t="n"/>
+      <c r="AK34" s="456" t="n"/>
+      <c r="AL34" s="456" t="n"/>
+      <c r="AM34" s="456" t="n"/>
+      <c r="AN34" s="457" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="354" t="inlineStr">
+      <c r="A35" s="458" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="399" t="n"/>
-      <c r="C35" s="399" t="n"/>
-      <c r="D35" s="399" t="n"/>
-      <c r="E35" s="399" t="n"/>
-      <c r="F35" s="399" t="n"/>
-      <c r="G35" s="400" t="n"/>
-      <c r="H35" s="357" t="n"/>
-      <c r="I35" s="399" t="n"/>
-      <c r="J35" s="399" t="n"/>
-      <c r="K35" s="399" t="n"/>
-      <c r="L35" s="399" t="n"/>
-      <c r="M35" s="399" t="n"/>
-      <c r="N35" s="399" t="n"/>
-      <c r="O35" s="399" t="n"/>
-      <c r="P35" s="399" t="n"/>
-      <c r="Q35" s="399" t="n"/>
-      <c r="R35" s="399" t="n"/>
-      <c r="S35" s="399" t="n"/>
-      <c r="T35" s="400" t="n"/>
-      <c r="U35" s="358" t="inlineStr">
+      <c r="B35" s="459" t="n"/>
+      <c r="C35" s="459" t="n"/>
+      <c r="D35" s="459" t="n"/>
+      <c r="E35" s="459" t="n"/>
+      <c r="F35" s="459" t="n"/>
+      <c r="G35" s="459" t="n"/>
+      <c r="H35" s="460" t="n"/>
+      <c r="I35" s="459" t="n"/>
+      <c r="J35" s="459" t="n"/>
+      <c r="K35" s="459" t="n"/>
+      <c r="L35" s="459" t="n"/>
+      <c r="M35" s="459" t="n"/>
+      <c r="N35" s="459" t="n"/>
+      <c r="O35" s="459" t="n"/>
+      <c r="P35" s="459" t="n"/>
+      <c r="Q35" s="459" t="n"/>
+      <c r="R35" s="459" t="n"/>
+      <c r="S35" s="459" t="n"/>
+      <c r="T35" s="459" t="n"/>
+      <c r="U35" s="461" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="399" t="n"/>
-      <c r="W35" s="399" t="n"/>
-      <c r="X35" s="399" t="n"/>
-      <c r="Y35" s="399" t="n"/>
-      <c r="Z35" s="399" t="n"/>
-      <c r="AA35" s="400" t="n"/>
-      <c r="AB35" s="357" t="n"/>
-      <c r="AC35" s="399" t="n"/>
-      <c r="AD35" s="399" t="n"/>
-      <c r="AE35" s="399" t="n"/>
-      <c r="AF35" s="399" t="n"/>
-      <c r="AG35" s="399" t="n"/>
-      <c r="AH35" s="399" t="n"/>
-      <c r="AI35" s="399" t="n"/>
-      <c r="AJ35" s="399" t="n"/>
-      <c r="AK35" s="399" t="n"/>
-      <c r="AL35" s="399" t="n"/>
-      <c r="AM35" s="399" t="n"/>
-      <c r="AN35" s="400" t="n"/>
+      <c r="V35" s="459" t="n"/>
+      <c r="W35" s="459" t="n"/>
+      <c r="X35" s="459" t="n"/>
+      <c r="Y35" s="459" t="n"/>
+      <c r="Z35" s="459" t="n"/>
+      <c r="AA35" s="459" t="n"/>
+      <c r="AB35" s="460" t="n"/>
+      <c r="AC35" s="459" t="n"/>
+      <c r="AD35" s="459" t="n"/>
+      <c r="AE35" s="459" t="n"/>
+      <c r="AF35" s="459" t="n"/>
+      <c r="AG35" s="459" t="n"/>
+      <c r="AH35" s="459" t="n"/>
+      <c r="AI35" s="459" t="n"/>
+      <c r="AJ35" s="459" t="n"/>
+      <c r="AK35" s="459" t="n"/>
+      <c r="AL35" s="459" t="n"/>
+      <c r="AM35" s="459" t="n"/>
+      <c r="AN35" s="462" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="354" t="inlineStr">
+      <c r="A36" s="467" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="399" t="n"/>
-      <c r="C36" s="399" t="n"/>
-      <c r="D36" s="399" t="n"/>
-      <c r="E36" s="399" t="n"/>
-      <c r="F36" s="399" t="n"/>
-      <c r="G36" s="400" t="n"/>
-      <c r="H36" s="357" t="n"/>
-      <c r="I36" s="399" t="n"/>
-      <c r="J36" s="399" t="n"/>
-      <c r="K36" s="399" t="n"/>
-      <c r="L36" s="399" t="n"/>
-      <c r="M36" s="399" t="n"/>
-      <c r="N36" s="399" t="n"/>
-      <c r="O36" s="399" t="n"/>
-      <c r="P36" s="399" t="n"/>
-      <c r="Q36" s="399" t="n"/>
-      <c r="R36" s="399" t="n"/>
-      <c r="S36" s="399" t="n"/>
-      <c r="T36" s="400" t="n"/>
-      <c r="U36" s="358" t="inlineStr">
+      <c r="B36" s="468" t="n"/>
+      <c r="C36" s="468" t="n"/>
+      <c r="D36" s="468" t="n"/>
+      <c r="E36" s="468" t="n"/>
+      <c r="F36" s="468" t="n"/>
+      <c r="G36" s="468" t="n"/>
+      <c r="H36" s="469" t="n"/>
+      <c r="I36" s="468" t="n"/>
+      <c r="J36" s="468" t="n"/>
+      <c r="K36" s="468" t="n"/>
+      <c r="L36" s="468" t="n"/>
+      <c r="M36" s="468" t="n"/>
+      <c r="N36" s="468" t="n"/>
+      <c r="O36" s="468" t="n"/>
+      <c r="P36" s="468" t="n"/>
+      <c r="Q36" s="468" t="n"/>
+      <c r="R36" s="468" t="n"/>
+      <c r="S36" s="468" t="n"/>
+      <c r="T36" s="468" t="n"/>
+      <c r="U36" s="470" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="399" t="n"/>
-      <c r="W36" s="399" t="n"/>
-      <c r="X36" s="399" t="n"/>
-      <c r="Y36" s="399" t="n"/>
-      <c r="Z36" s="399" t="n"/>
-      <c r="AA36" s="400" t="n"/>
-      <c r="AB36" s="357" t="n"/>
-      <c r="AC36" s="399" t="n"/>
-      <c r="AD36" s="399" t="n"/>
-      <c r="AE36" s="399" t="n"/>
-      <c r="AF36" s="399" t="n"/>
-      <c r="AG36" s="399" t="n"/>
-      <c r="AH36" s="399" t="n"/>
-      <c r="AI36" s="399" t="n"/>
-      <c r="AJ36" s="399" t="n"/>
-      <c r="AK36" s="399" t="n"/>
-      <c r="AL36" s="399" t="n"/>
-      <c r="AM36" s="399" t="n"/>
-      <c r="AN36" s="400" t="n"/>
+      <c r="V36" s="468" t="n"/>
+      <c r="W36" s="468" t="n"/>
+      <c r="X36" s="468" t="n"/>
+      <c r="Y36" s="468" t="n"/>
+      <c r="Z36" s="468" t="n"/>
+      <c r="AA36" s="468" t="n"/>
+      <c r="AB36" s="469" t="n"/>
+      <c r="AC36" s="468" t="n"/>
+      <c r="AD36" s="468" t="n"/>
+      <c r="AE36" s="468" t="n"/>
+      <c r="AF36" s="468" t="n"/>
+      <c r="AG36" s="468" t="n"/>
+      <c r="AH36" s="468" t="n"/>
+      <c r="AI36" s="468" t="n"/>
+      <c r="AJ36" s="468" t="n"/>
+      <c r="AK36" s="468" t="n"/>
+      <c r="AL36" s="468" t="n"/>
+      <c r="AM36" s="468" t="n"/>
+      <c r="AN36" s="471" t="n"/>
     </row>
-    <row r="37" ht="4" customHeight="1" s="329">
+    <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="364" t="n"/>
       <c r="B37" s="352" t="n"/>
       <c r="C37" s="366" t="n"/>
@@ -6784,245 +7568,245 @@
       <c r="AM37" s="352" t="n"/>
       <c r="AN37" s="352" t="n"/>
     </row>
-    <row r="38" ht="20" customHeight="1" s="329">
-      <c r="A38" s="353" t="inlineStr">
+    <row r="38" ht="18" customHeight="1" s="329">
+      <c r="A38" s="455" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="399" t="n"/>
-      <c r="C38" s="399" t="n"/>
-      <c r="D38" s="399" t="n"/>
-      <c r="E38" s="399" t="n"/>
-      <c r="F38" s="399" t="n"/>
-      <c r="G38" s="399" t="n"/>
-      <c r="H38" s="399" t="n"/>
-      <c r="I38" s="399" t="n"/>
-      <c r="J38" s="399" t="n"/>
-      <c r="K38" s="399" t="n"/>
-      <c r="L38" s="399" t="n"/>
-      <c r="M38" s="399" t="n"/>
-      <c r="N38" s="399" t="n"/>
-      <c r="O38" s="399" t="n"/>
-      <c r="P38" s="399" t="n"/>
-      <c r="Q38" s="399" t="n"/>
-      <c r="R38" s="399" t="n"/>
-      <c r="S38" s="399" t="n"/>
-      <c r="T38" s="399" t="n"/>
-      <c r="U38" s="399" t="n"/>
-      <c r="V38" s="399" t="n"/>
-      <c r="W38" s="399" t="n"/>
-      <c r="X38" s="399" t="n"/>
-      <c r="Y38" s="399" t="n"/>
-      <c r="Z38" s="399" t="n"/>
-      <c r="AA38" s="399" t="n"/>
-      <c r="AB38" s="399" t="n"/>
-      <c r="AC38" s="399" t="n"/>
-      <c r="AD38" s="399" t="n"/>
-      <c r="AE38" s="399" t="n"/>
-      <c r="AF38" s="399" t="n"/>
-      <c r="AG38" s="399" t="n"/>
-      <c r="AH38" s="399" t="n"/>
-      <c r="AI38" s="399" t="n"/>
-      <c r="AJ38" s="399" t="n"/>
-      <c r="AK38" s="399" t="n"/>
-      <c r="AL38" s="399" t="n"/>
-      <c r="AM38" s="399" t="n"/>
-      <c r="AN38" s="400" t="n"/>
+      <c r="B38" s="456" t="n"/>
+      <c r="C38" s="456" t="n"/>
+      <c r="D38" s="456" t="n"/>
+      <c r="E38" s="456" t="n"/>
+      <c r="F38" s="456" t="n"/>
+      <c r="G38" s="456" t="n"/>
+      <c r="H38" s="456" t="n"/>
+      <c r="I38" s="456" t="n"/>
+      <c r="J38" s="456" t="n"/>
+      <c r="K38" s="456" t="n"/>
+      <c r="L38" s="456" t="n"/>
+      <c r="M38" s="456" t="n"/>
+      <c r="N38" s="456" t="n"/>
+      <c r="O38" s="456" t="n"/>
+      <c r="P38" s="456" t="n"/>
+      <c r="Q38" s="456" t="n"/>
+      <c r="R38" s="456" t="n"/>
+      <c r="S38" s="456" t="n"/>
+      <c r="T38" s="456" t="n"/>
+      <c r="U38" s="456" t="n"/>
+      <c r="V38" s="456" t="n"/>
+      <c r="W38" s="456" t="n"/>
+      <c r="X38" s="456" t="n"/>
+      <c r="Y38" s="456" t="n"/>
+      <c r="Z38" s="456" t="n"/>
+      <c r="AA38" s="456" t="n"/>
+      <c r="AB38" s="456" t="n"/>
+      <c r="AC38" s="456" t="n"/>
+      <c r="AD38" s="456" t="n"/>
+      <c r="AE38" s="456" t="n"/>
+      <c r="AF38" s="456" t="n"/>
+      <c r="AG38" s="456" t="n"/>
+      <c r="AH38" s="456" t="n"/>
+      <c r="AI38" s="456" t="n"/>
+      <c r="AJ38" s="456" t="n"/>
+      <c r="AK38" s="456" t="n"/>
+      <c r="AL38" s="456" t="n"/>
+      <c r="AM38" s="456" t="n"/>
+      <c r="AN38" s="457" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="329">
-      <c r="A39" s="377" t="inlineStr">
+    <row r="39" ht="26" customHeight="1" s="329">
+      <c r="A39" s="481" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="394" t="n"/>
-      <c r="C39" s="394" t="n"/>
-      <c r="D39" s="394" t="n"/>
-      <c r="E39" s="394" t="n"/>
-      <c r="F39" s="394" t="n"/>
-      <c r="G39" s="394" t="n"/>
-      <c r="H39" s="394" t="n"/>
-      <c r="I39" s="394" t="n"/>
-      <c r="J39" s="394" t="n"/>
-      <c r="K39" s="394" t="n"/>
-      <c r="L39" s="394" t="n"/>
-      <c r="M39" s="395" t="n"/>
-      <c r="N39" s="378" t="inlineStr">
+      <c r="B39" s="459" t="n"/>
+      <c r="C39" s="459" t="n"/>
+      <c r="D39" s="459" t="n"/>
+      <c r="E39" s="459" t="n"/>
+      <c r="F39" s="459" t="n"/>
+      <c r="G39" s="459" t="n"/>
+      <c r="H39" s="459" t="n"/>
+      <c r="I39" s="459" t="n"/>
+      <c r="J39" s="459" t="n"/>
+      <c r="K39" s="459" t="n"/>
+      <c r="L39" s="459" t="n"/>
+      <c r="M39" s="459" t="n"/>
+      <c r="N39" s="493" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="394" t="n"/>
-      <c r="P39" s="394" t="n"/>
-      <c r="Q39" s="394" t="n"/>
-      <c r="R39" s="394" t="n"/>
-      <c r="S39" s="394" t="n"/>
-      <c r="T39" s="394" t="n"/>
-      <c r="U39" s="394" t="n"/>
-      <c r="V39" s="394" t="n"/>
-      <c r="W39" s="394" t="n"/>
-      <c r="X39" s="394" t="n"/>
-      <c r="Y39" s="394" t="n"/>
-      <c r="Z39" s="394" t="n"/>
-      <c r="AA39" s="379" t="inlineStr">
+      <c r="O39" s="459" t="n"/>
+      <c r="P39" s="459" t="n"/>
+      <c r="Q39" s="459" t="n"/>
+      <c r="R39" s="459" t="n"/>
+      <c r="S39" s="459" t="n"/>
+      <c r="T39" s="459" t="n"/>
+      <c r="U39" s="459" t="n"/>
+      <c r="V39" s="459" t="n"/>
+      <c r="W39" s="459" t="n"/>
+      <c r="X39" s="459" t="n"/>
+      <c r="Y39" s="459" t="n"/>
+      <c r="Z39" s="459" t="n"/>
+      <c r="AA39" s="493" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="394" t="n"/>
-      <c r="AC39" s="394" t="n"/>
-      <c r="AD39" s="394" t="n"/>
-      <c r="AE39" s="394" t="n"/>
-      <c r="AF39" s="394" t="n"/>
-      <c r="AG39" s="394" t="n"/>
-      <c r="AH39" s="394" t="n"/>
-      <c r="AI39" s="394" t="n"/>
-      <c r="AJ39" s="394" t="n"/>
-      <c r="AK39" s="394" t="n"/>
-      <c r="AL39" s="394" t="n"/>
-      <c r="AM39" s="394" t="n"/>
-      <c r="AN39" s="395" t="n"/>
+      <c r="AB39" s="459" t="n"/>
+      <c r="AC39" s="459" t="n"/>
+      <c r="AD39" s="459" t="n"/>
+      <c r="AE39" s="459" t="n"/>
+      <c r="AF39" s="459" t="n"/>
+      <c r="AG39" s="459" t="n"/>
+      <c r="AH39" s="459" t="n"/>
+      <c r="AI39" s="459" t="n"/>
+      <c r="AJ39" s="459" t="n"/>
+      <c r="AK39" s="459" t="n"/>
+      <c r="AL39" s="459" t="n"/>
+      <c r="AM39" s="459" t="n"/>
+      <c r="AN39" s="462" t="n"/>
     </row>
-    <row r="40" ht="20" customHeight="1" s="329">
-      <c r="A40" s="380" t="inlineStr">
+    <row r="40" ht="26" customHeight="1" s="329">
+      <c r="A40" s="494" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="393" t="n"/>
-      <c r="C40" s="393" t="n"/>
-      <c r="D40" s="393" t="n"/>
-      <c r="E40" s="393" t="n"/>
-      <c r="F40" s="393" t="n"/>
-      <c r="G40" s="393" t="n"/>
-      <c r="H40" s="393" t="n"/>
-      <c r="I40" s="393" t="n"/>
-      <c r="J40" s="393" t="n"/>
-      <c r="K40" s="393" t="n"/>
-      <c r="L40" s="393" t="n"/>
-      <c r="M40" s="405" t="n"/>
-      <c r="N40" s="380" t="inlineStr">
+      <c r="B40" s="343" t="n"/>
+      <c r="C40" s="343" t="n"/>
+      <c r="D40" s="343" t="n"/>
+      <c r="E40" s="343" t="n"/>
+      <c r="F40" s="343" t="n"/>
+      <c r="G40" s="343" t="n"/>
+      <c r="H40" s="343" t="n"/>
+      <c r="I40" s="343" t="n"/>
+      <c r="J40" s="343" t="n"/>
+      <c r="K40" s="343" t="n"/>
+      <c r="L40" s="343" t="n"/>
+      <c r="M40" s="343" t="n"/>
+      <c r="N40" s="495" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="393" t="n"/>
-      <c r="P40" s="393" t="n"/>
-      <c r="Q40" s="393" t="n"/>
-      <c r="R40" s="393" t="n"/>
-      <c r="S40" s="393" t="n"/>
-      <c r="T40" s="393" t="n"/>
-      <c r="U40" s="393" t="n"/>
-      <c r="V40" s="393" t="n"/>
-      <c r="W40" s="393" t="n"/>
-      <c r="X40" s="393" t="n"/>
-      <c r="Y40" s="393" t="n"/>
-      <c r="Z40" s="405" t="n"/>
-      <c r="AA40" s="380" t="inlineStr">
+      <c r="O40" s="343" t="n"/>
+      <c r="P40" s="343" t="n"/>
+      <c r="Q40" s="343" t="n"/>
+      <c r="R40" s="343" t="n"/>
+      <c r="S40" s="343" t="n"/>
+      <c r="T40" s="343" t="n"/>
+      <c r="U40" s="343" t="n"/>
+      <c r="V40" s="343" t="n"/>
+      <c r="W40" s="343" t="n"/>
+      <c r="X40" s="343" t="n"/>
+      <c r="Y40" s="343" t="n"/>
+      <c r="Z40" s="343" t="n"/>
+      <c r="AA40" s="495" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="393" t="n"/>
-      <c r="AC40" s="393" t="n"/>
-      <c r="AD40" s="393" t="n"/>
-      <c r="AE40" s="393" t="n"/>
-      <c r="AF40" s="393" t="n"/>
-      <c r="AG40" s="393" t="n"/>
-      <c r="AH40" s="393" t="n"/>
-      <c r="AI40" s="393" t="n"/>
-      <c r="AJ40" s="393" t="n"/>
-      <c r="AK40" s="393" t="n"/>
-      <c r="AL40" s="393" t="n"/>
-      <c r="AM40" s="393" t="n"/>
-      <c r="AN40" s="405" t="n"/>
+      <c r="AB40" s="343" t="n"/>
+      <c r="AC40" s="343" t="n"/>
+      <c r="AD40" s="343" t="n"/>
+      <c r="AE40" s="343" t="n"/>
+      <c r="AF40" s="343" t="n"/>
+      <c r="AG40" s="343" t="n"/>
+      <c r="AH40" s="343" t="n"/>
+      <c r="AI40" s="343" t="n"/>
+      <c r="AJ40" s="343" t="n"/>
+      <c r="AK40" s="343" t="n"/>
+      <c r="AL40" s="343" t="n"/>
+      <c r="AM40" s="343" t="n"/>
+      <c r="AN40" s="466" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="406" t="n"/>
-      <c r="B41" s="383" t="n"/>
-      <c r="C41" s="383" t="n"/>
-      <c r="D41" s="383" t="n"/>
-      <c r="E41" s="383" t="n"/>
-      <c r="F41" s="383" t="n"/>
-      <c r="G41" s="383" t="n"/>
-      <c r="H41" s="383" t="n"/>
-      <c r="I41" s="383" t="n"/>
-      <c r="J41" s="383" t="n"/>
-      <c r="K41" s="383" t="n"/>
-      <c r="L41" s="383" t="n"/>
-      <c r="M41" s="407" t="n"/>
-      <c r="N41" s="406" t="n"/>
-      <c r="O41" s="383" t="n"/>
-      <c r="P41" s="383" t="n"/>
-      <c r="Q41" s="383" t="n"/>
-      <c r="R41" s="383" t="n"/>
-      <c r="S41" s="383" t="n"/>
-      <c r="T41" s="383" t="n"/>
-      <c r="U41" s="383" t="n"/>
-      <c r="V41" s="383" t="n"/>
-      <c r="W41" s="383" t="n"/>
-      <c r="X41" s="383" t="n"/>
-      <c r="Y41" s="383" t="n"/>
-      <c r="Z41" s="407" t="n"/>
-      <c r="AA41" s="406" t="n"/>
-      <c r="AB41" s="383" t="n"/>
-      <c r="AC41" s="383" t="n"/>
-      <c r="AD41" s="383" t="n"/>
-      <c r="AE41" s="383" t="n"/>
-      <c r="AF41" s="383" t="n"/>
-      <c r="AG41" s="383" t="n"/>
-      <c r="AH41" s="383" t="n"/>
-      <c r="AI41" s="383" t="n"/>
-      <c r="AJ41" s="383" t="n"/>
-      <c r="AK41" s="383" t="n"/>
-      <c r="AL41" s="383" t="n"/>
-      <c r="AM41" s="383" t="n"/>
-      <c r="AN41" s="407" t="n"/>
+      <c r="A41" s="474" t="n"/>
+      <c r="B41" s="343" t="n"/>
+      <c r="C41" s="343" t="n"/>
+      <c r="D41" s="343" t="n"/>
+      <c r="E41" s="343" t="n"/>
+      <c r="F41" s="343" t="n"/>
+      <c r="G41" s="343" t="n"/>
+      <c r="H41" s="343" t="n"/>
+      <c r="I41" s="343" t="n"/>
+      <c r="J41" s="343" t="n"/>
+      <c r="K41" s="343" t="n"/>
+      <c r="L41" s="343" t="n"/>
+      <c r="M41" s="343" t="n"/>
+      <c r="N41" s="472" t="n"/>
+      <c r="O41" s="343" t="n"/>
+      <c r="P41" s="343" t="n"/>
+      <c r="Q41" s="343" t="n"/>
+      <c r="R41" s="343" t="n"/>
+      <c r="S41" s="343" t="n"/>
+      <c r="T41" s="343" t="n"/>
+      <c r="U41" s="343" t="n"/>
+      <c r="V41" s="343" t="n"/>
+      <c r="W41" s="343" t="n"/>
+      <c r="X41" s="343" t="n"/>
+      <c r="Y41" s="343" t="n"/>
+      <c r="Z41" s="343" t="n"/>
+      <c r="AA41" s="472" t="n"/>
+      <c r="AB41" s="343" t="n"/>
+      <c r="AC41" s="343" t="n"/>
+      <c r="AD41" s="343" t="n"/>
+      <c r="AE41" s="343" t="n"/>
+      <c r="AF41" s="343" t="n"/>
+      <c r="AG41" s="343" t="n"/>
+      <c r="AH41" s="343" t="n"/>
+      <c r="AI41" s="343" t="n"/>
+      <c r="AJ41" s="343" t="n"/>
+      <c r="AK41" s="343" t="n"/>
+      <c r="AL41" s="343" t="n"/>
+      <c r="AM41" s="343" t="n"/>
+      <c r="AN41" s="466" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="408" t="n"/>
-      <c r="B42" s="403" t="n"/>
-      <c r="C42" s="403" t="n"/>
-      <c r="D42" s="403" t="n"/>
-      <c r="E42" s="403" t="n"/>
-      <c r="F42" s="403" t="n"/>
-      <c r="G42" s="403" t="n"/>
-      <c r="H42" s="403" t="n"/>
-      <c r="I42" s="403" t="n"/>
-      <c r="J42" s="403" t="n"/>
-      <c r="K42" s="403" t="n"/>
-      <c r="L42" s="403" t="n"/>
-      <c r="M42" s="404" t="n"/>
-      <c r="N42" s="408" t="n"/>
-      <c r="O42" s="403" t="n"/>
-      <c r="P42" s="403" t="n"/>
-      <c r="Q42" s="403" t="n"/>
-      <c r="R42" s="403" t="n"/>
-      <c r="S42" s="403" t="n"/>
-      <c r="T42" s="403" t="n"/>
-      <c r="U42" s="403" t="n"/>
-      <c r="V42" s="403" t="n"/>
-      <c r="W42" s="403" t="n"/>
-      <c r="X42" s="403" t="n"/>
-      <c r="Y42" s="403" t="n"/>
-      <c r="Z42" s="404" t="n"/>
-      <c r="AA42" s="408" t="n"/>
-      <c r="AB42" s="403" t="n"/>
-      <c r="AC42" s="403" t="n"/>
-      <c r="AD42" s="403" t="n"/>
-      <c r="AE42" s="403" t="n"/>
-      <c r="AF42" s="403" t="n"/>
-      <c r="AG42" s="403" t="n"/>
-      <c r="AH42" s="403" t="n"/>
-      <c r="AI42" s="403" t="n"/>
-      <c r="AJ42" s="403" t="n"/>
-      <c r="AK42" s="403" t="n"/>
-      <c r="AL42" s="403" t="n"/>
-      <c r="AM42" s="403" t="n"/>
-      <c r="AN42" s="404" t="n"/>
+      <c r="A42" s="475" t="n"/>
+      <c r="B42" s="468" t="n"/>
+      <c r="C42" s="468" t="n"/>
+      <c r="D42" s="468" t="n"/>
+      <c r="E42" s="468" t="n"/>
+      <c r="F42" s="468" t="n"/>
+      <c r="G42" s="468" t="n"/>
+      <c r="H42" s="468" t="n"/>
+      <c r="I42" s="468" t="n"/>
+      <c r="J42" s="468" t="n"/>
+      <c r="K42" s="468" t="n"/>
+      <c r="L42" s="468" t="n"/>
+      <c r="M42" s="468" t="n"/>
+      <c r="N42" s="476" t="n"/>
+      <c r="O42" s="468" t="n"/>
+      <c r="P42" s="468" t="n"/>
+      <c r="Q42" s="468" t="n"/>
+      <c r="R42" s="468" t="n"/>
+      <c r="S42" s="468" t="n"/>
+      <c r="T42" s="468" t="n"/>
+      <c r="U42" s="468" t="n"/>
+      <c r="V42" s="468" t="n"/>
+      <c r="W42" s="468" t="n"/>
+      <c r="X42" s="468" t="n"/>
+      <c r="Y42" s="468" t="n"/>
+      <c r="Z42" s="468" t="n"/>
+      <c r="AA42" s="476" t="n"/>
+      <c r="AB42" s="468" t="n"/>
+      <c r="AC42" s="468" t="n"/>
+      <c r="AD42" s="468" t="n"/>
+      <c r="AE42" s="468" t="n"/>
+      <c r="AF42" s="468" t="n"/>
+      <c r="AG42" s="468" t="n"/>
+      <c r="AH42" s="468" t="n"/>
+      <c r="AI42" s="468" t="n"/>
+      <c r="AJ42" s="468" t="n"/>
+      <c r="AK42" s="468" t="n"/>
+      <c r="AL42" s="468" t="n"/>
+      <c r="AM42" s="468" t="n"/>
+      <c r="AN42" s="471" t="n"/>
     </row>
-    <row r="43" ht="4" customHeight="1" s="329">
+    <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="386" t="n"/>
       <c r="B43" s="352" t="n"/>
       <c r="C43" s="352" t="n"/>
@@ -7065,56 +7849,56 @@
       <c r="AN43" s="352" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="387" t="inlineStr">
+      <c r="A44" s="496" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
         </is>
       </c>
-      <c r="B44" s="383" t="n"/>
-      <c r="C44" s="383" t="n"/>
-      <c r="D44" s="383" t="n"/>
-      <c r="E44" s="383" t="n"/>
-      <c r="F44" s="383" t="n"/>
-      <c r="G44" s="383" t="n"/>
-      <c r="H44" s="383" t="n"/>
-      <c r="I44" s="383" t="n"/>
-      <c r="J44" s="383" t="n"/>
-      <c r="K44" s="383" t="n"/>
-      <c r="L44" s="383" t="n"/>
-      <c r="M44" s="383" t="n"/>
-      <c r="N44" s="383" t="n"/>
-      <c r="O44" s="383" t="n"/>
-      <c r="P44" s="383" t="n"/>
-      <c r="Q44" s="383" t="n"/>
-      <c r="R44" s="383" t="n"/>
-      <c r="S44" s="383" t="n"/>
-      <c r="T44" s="383" t="n"/>
-      <c r="U44" s="383" t="n"/>
-      <c r="V44" s="383" t="n"/>
-      <c r="W44" s="383" t="n"/>
-      <c r="X44" s="383" t="n"/>
-      <c r="Y44" s="383" t="n"/>
-      <c r="Z44" s="383" t="n"/>
-      <c r="AA44" s="383" t="n"/>
-      <c r="AB44" s="383" t="n"/>
-      <c r="AC44" s="383" t="n"/>
-      <c r="AD44" s="383" t="n"/>
-      <c r="AE44" s="383" t="n"/>
-      <c r="AF44" s="383" t="n"/>
-      <c r="AG44" s="383" t="n"/>
-      <c r="AH44" s="383" t="n"/>
-      <c r="AI44" s="383" t="n"/>
-      <c r="AJ44" s="383" t="n"/>
-      <c r="AK44" s="383" t="n"/>
-      <c r="AL44" s="383" t="n"/>
-      <c r="AM44" s="383" t="n"/>
-      <c r="AN44" s="383" t="n"/>
+      <c r="B44" s="497" t="n"/>
+      <c r="C44" s="497" t="n"/>
+      <c r="D44" s="497" t="n"/>
+      <c r="E44" s="497" t="n"/>
+      <c r="F44" s="497" t="n"/>
+      <c r="G44" s="497" t="n"/>
+      <c r="H44" s="497" t="n"/>
+      <c r="I44" s="497" t="n"/>
+      <c r="J44" s="497" t="n"/>
+      <c r="K44" s="497" t="n"/>
+      <c r="L44" s="497" t="n"/>
+      <c r="M44" s="497" t="n"/>
+      <c r="N44" s="497" t="n"/>
+      <c r="O44" s="497" t="n"/>
+      <c r="P44" s="497" t="n"/>
+      <c r="Q44" s="497" t="n"/>
+      <c r="R44" s="497" t="n"/>
+      <c r="S44" s="497" t="n"/>
+      <c r="T44" s="497" t="n"/>
+      <c r="U44" s="497" t="n"/>
+      <c r="V44" s="497" t="n"/>
+      <c r="W44" s="497" t="n"/>
+      <c r="X44" s="497" t="n"/>
+      <c r="Y44" s="497" t="n"/>
+      <c r="Z44" s="497" t="n"/>
+      <c r="AA44" s="497" t="n"/>
+      <c r="AB44" s="497" t="n"/>
+      <c r="AC44" s="497" t="n"/>
+      <c r="AD44" s="497" t="n"/>
+      <c r="AE44" s="497" t="n"/>
+      <c r="AF44" s="497" t="n"/>
+      <c r="AG44" s="497" t="n"/>
+      <c r="AH44" s="497" t="n"/>
+      <c r="AI44" s="497" t="n"/>
+      <c r="AJ44" s="497" t="n"/>
+      <c r="AK44" s="497" t="n"/>
+      <c r="AL44" s="497" t="n"/>
+      <c r="AM44" s="497" t="n"/>
+      <c r="AN44" s="498" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
     <row r="47" ht="24" customHeight="1" s="329"/>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="119">
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A21:AN21"/>
@@ -7140,7 +7924,6 @@
     <mergeCell ref="F31:S31"/>
     <mergeCell ref="T30:AE30"/>
     <mergeCell ref="F28:S28"/>
-    <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A22:AN23"/>
     <mergeCell ref="T29:AE29"/>
     <mergeCell ref="AI1:AN1"/>
@@ -7254,6 +8037,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7424,7 +8208,7 @@
           <t>PROD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="347" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7437,12 +8221,12 @@
       <c r="G5" s="266" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="347" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
@@ -7451,12 +8235,12 @@
       <c r="G6" s="266" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="347" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7464,7 +8248,7 @@
       <c r="F7" s="266" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="347" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
@@ -7472,7 +8256,7 @@
       <c r="F8" s="266" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="347" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
@@ -7480,7 +8264,7 @@
       <c r="F9" s="266" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="347" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -7488,7 +8272,7 @@
       <c r="F10" s="266" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="347" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
@@ -7552,662 +8336,662 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="334" t="inlineStr">
+      <c r="A1" s="499" t="inlineStr">
         <is>
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
-      <c r="B1" s="347" t="n"/>
-      <c r="C1" s="347" t="n"/>
-      <c r="D1" s="347" t="n"/>
-      <c r="E1" s="347" t="n"/>
-      <c r="F1" s="347" t="n"/>
-      <c r="G1" s="347" t="n"/>
-      <c r="H1" s="347" t="n"/>
-      <c r="I1" s="347" t="n"/>
-      <c r="J1" s="347" t="n"/>
-      <c r="K1" s="347" t="n"/>
-      <c r="L1" s="347" t="n"/>
-      <c r="M1" s="347" t="n"/>
-      <c r="N1" s="347" t="n"/>
-      <c r="O1" s="347" t="n"/>
-      <c r="P1" s="347" t="n"/>
-      <c r="Q1" s="347" t="n"/>
-      <c r="R1" s="347" t="n"/>
-      <c r="S1" s="347" t="n"/>
-      <c r="T1" s="347" t="n"/>
-      <c r="U1" s="347" t="n"/>
-      <c r="V1" s="347" t="n"/>
-      <c r="W1" s="347" t="n"/>
-      <c r="X1" s="347" t="n"/>
-      <c r="Y1" s="347" t="n"/>
-      <c r="Z1" s="347" t="n"/>
-      <c r="AA1" s="347" t="n"/>
-      <c r="AB1" s="347" t="n"/>
-      <c r="AC1" s="347" t="n"/>
-      <c r="AD1" s="347" t="n"/>
-      <c r="AE1" s="347" t="n"/>
-      <c r="AF1" s="347" t="n"/>
-      <c r="AG1" s="347" t="n"/>
-      <c r="AH1" s="347" t="n"/>
-      <c r="AI1" s="347" t="n"/>
-      <c r="AJ1" s="347" t="n"/>
-      <c r="AK1" s="347" t="n"/>
-      <c r="AL1" s="347" t="n"/>
-      <c r="AM1" s="347" t="n"/>
-      <c r="AN1" s="347" t="n"/>
+      <c r="B1" s="459" t="n"/>
+      <c r="C1" s="459" t="n"/>
+      <c r="D1" s="459" t="n"/>
+      <c r="E1" s="459" t="n"/>
+      <c r="F1" s="459" t="n"/>
+      <c r="G1" s="459" t="n"/>
+      <c r="H1" s="459" t="n"/>
+      <c r="I1" s="459" t="n"/>
+      <c r="J1" s="459" t="n"/>
+      <c r="K1" s="459" t="n"/>
+      <c r="L1" s="459" t="n"/>
+      <c r="M1" s="459" t="n"/>
+      <c r="N1" s="459" t="n"/>
+      <c r="O1" s="459" t="n"/>
+      <c r="P1" s="459" t="n"/>
+      <c r="Q1" s="459" t="n"/>
+      <c r="R1" s="459" t="n"/>
+      <c r="S1" s="459" t="n"/>
+      <c r="T1" s="459" t="n"/>
+      <c r="U1" s="459" t="n"/>
+      <c r="V1" s="459" t="n"/>
+      <c r="W1" s="459" t="n"/>
+      <c r="X1" s="459" t="n"/>
+      <c r="Y1" s="459" t="n"/>
+      <c r="Z1" s="459" t="n"/>
+      <c r="AA1" s="459" t="n"/>
+      <c r="AB1" s="459" t="n"/>
+      <c r="AC1" s="459" t="n"/>
+      <c r="AD1" s="459" t="n"/>
+      <c r="AE1" s="459" t="n"/>
+      <c r="AF1" s="459" t="n"/>
+      <c r="AG1" s="459" t="n"/>
+      <c r="AH1" s="459" t="n"/>
+      <c r="AI1" s="459" t="n"/>
+      <c r="AJ1" s="459" t="n"/>
+      <c r="AK1" s="459" t="n"/>
+      <c r="AL1" s="459" t="n"/>
+      <c r="AM1" s="459" t="n"/>
+      <c r="AN1" s="462" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="335" t="inlineStr">
+      <c r="A2" s="500" t="inlineStr">
         <is>
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
-      <c r="B2" s="347" t="n"/>
-      <c r="C2" s="347" t="n"/>
-      <c r="D2" s="347" t="n"/>
-      <c r="E2" s="347" t="n"/>
-      <c r="F2" s="347" t="n"/>
-      <c r="G2" s="347" t="n"/>
-      <c r="H2" s="347" t="n"/>
-      <c r="I2" s="347" t="n"/>
-      <c r="J2" s="347" t="n"/>
-      <c r="K2" s="347" t="n"/>
-      <c r="L2" s="347" t="n"/>
-      <c r="M2" s="347" t="n"/>
-      <c r="N2" s="347" t="n"/>
-      <c r="O2" s="347" t="n"/>
-      <c r="P2" s="347" t="n"/>
-      <c r="Q2" s="347" t="n"/>
-      <c r="R2" s="347" t="n"/>
-      <c r="S2" s="347" t="n"/>
-      <c r="T2" s="347" t="n"/>
-      <c r="U2" s="347" t="n"/>
-      <c r="V2" s="347" t="n"/>
-      <c r="W2" s="347" t="n"/>
-      <c r="X2" s="347" t="n"/>
-      <c r="Y2" s="347" t="n"/>
-      <c r="Z2" s="347" t="n"/>
-      <c r="AA2" s="347" t="n"/>
-      <c r="AB2" s="347" t="n"/>
-      <c r="AC2" s="347" t="n"/>
-      <c r="AD2" s="347" t="n"/>
-      <c r="AE2" s="347" t="n"/>
-      <c r="AF2" s="347" t="n"/>
-      <c r="AG2" s="347" t="n"/>
-      <c r="AH2" s="347" t="n"/>
-      <c r="AI2" s="347" t="n"/>
-      <c r="AJ2" s="347" t="n"/>
-      <c r="AK2" s="347" t="n"/>
-      <c r="AL2" s="347" t="n"/>
-      <c r="AM2" s="347" t="n"/>
-      <c r="AN2" s="347" t="n"/>
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="343" t="n"/>
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="343" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="343" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="343" t="n"/>
+      <c r="S2" s="343" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="343" t="n"/>
+      <c r="Y2" s="343" t="n"/>
+      <c r="Z2" s="343" t="n"/>
+      <c r="AA2" s="343" t="n"/>
+      <c r="AB2" s="343" t="n"/>
+      <c r="AC2" s="343" t="n"/>
+      <c r="AD2" s="343" t="n"/>
+      <c r="AE2" s="343" t="n"/>
+      <c r="AF2" s="343" t="n"/>
+      <c r="AG2" s="343" t="n"/>
+      <c r="AH2" s="343" t="n"/>
+      <c r="AI2" s="343" t="n"/>
+      <c r="AJ2" s="343" t="n"/>
+      <c r="AK2" s="343" t="n"/>
+      <c r="AL2" s="343" t="n"/>
+      <c r="AM2" s="343" t="n"/>
+      <c r="AN2" s="466" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="347" t="n"/>
-      <c r="B3" s="347" t="n"/>
-      <c r="C3" s="347" t="n"/>
-      <c r="D3" s="347" t="n"/>
-      <c r="E3" s="347" t="n"/>
-      <c r="F3" s="347" t="n"/>
-      <c r="G3" s="347" t="n"/>
-      <c r="H3" s="347" t="n"/>
-      <c r="I3" s="347" t="n"/>
-      <c r="J3" s="347" t="n"/>
-      <c r="K3" s="347" t="n"/>
-      <c r="L3" s="347" t="n"/>
-      <c r="M3" s="347" t="n"/>
-      <c r="N3" s="347" t="n"/>
-      <c r="O3" s="347" t="n"/>
-      <c r="P3" s="347" t="n"/>
-      <c r="Q3" s="347" t="n"/>
-      <c r="R3" s="347" t="n"/>
-      <c r="S3" s="347" t="n"/>
-      <c r="T3" s="347" t="n"/>
-      <c r="U3" s="347" t="n"/>
-      <c r="V3" s="347" t="n"/>
-      <c r="W3" s="347" t="n"/>
-      <c r="X3" s="347" t="n"/>
-      <c r="Y3" s="347" t="n"/>
-      <c r="Z3" s="347" t="n"/>
-      <c r="AA3" s="347" t="n"/>
-      <c r="AB3" s="347" t="n"/>
-      <c r="AC3" s="347" t="n"/>
-      <c r="AD3" s="347" t="n"/>
-      <c r="AE3" s="347" t="n"/>
-      <c r="AF3" s="347" t="n"/>
-      <c r="AG3" s="347" t="n"/>
-      <c r="AH3" s="347" t="n"/>
-      <c r="AI3" s="347" t="n"/>
-      <c r="AJ3" s="347" t="n"/>
-      <c r="AK3" s="347" t="n"/>
-      <c r="AL3" s="347" t="n"/>
-      <c r="AM3" s="347" t="n"/>
-      <c r="AN3" s="347" t="n"/>
+      <c r="A3" s="475" t="n"/>
+      <c r="B3" s="468" t="n"/>
+      <c r="C3" s="468" t="n"/>
+      <c r="D3" s="468" t="n"/>
+      <c r="E3" s="468" t="n"/>
+      <c r="F3" s="468" t="n"/>
+      <c r="G3" s="468" t="n"/>
+      <c r="H3" s="468" t="n"/>
+      <c r="I3" s="468" t="n"/>
+      <c r="J3" s="468" t="n"/>
+      <c r="K3" s="468" t="n"/>
+      <c r="L3" s="468" t="n"/>
+      <c r="M3" s="468" t="n"/>
+      <c r="N3" s="468" t="n"/>
+      <c r="O3" s="468" t="n"/>
+      <c r="P3" s="468" t="n"/>
+      <c r="Q3" s="468" t="n"/>
+      <c r="R3" s="468" t="n"/>
+      <c r="S3" s="468" t="n"/>
+      <c r="T3" s="468" t="n"/>
+      <c r="U3" s="468" t="n"/>
+      <c r="V3" s="468" t="n"/>
+      <c r="W3" s="468" t="n"/>
+      <c r="X3" s="468" t="n"/>
+      <c r="Y3" s="468" t="n"/>
+      <c r="Z3" s="468" t="n"/>
+      <c r="AA3" s="468" t="n"/>
+      <c r="AB3" s="468" t="n"/>
+      <c r="AC3" s="468" t="n"/>
+      <c r="AD3" s="468" t="n"/>
+      <c r="AE3" s="468" t="n"/>
+      <c r="AF3" s="468" t="n"/>
+      <c r="AG3" s="468" t="n"/>
+      <c r="AH3" s="468" t="n"/>
+      <c r="AI3" s="468" t="n"/>
+      <c r="AJ3" s="468" t="n"/>
+      <c r="AK3" s="468" t="n"/>
+      <c r="AL3" s="468" t="n"/>
+      <c r="AM3" s="468" t="n"/>
+      <c r="AN3" s="471" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="388" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="329">
+      <c r="A4" s="477" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="388" t="inlineStr">
+      <c r="B4" s="478" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="388" t="inlineStr">
+      <c r="C4" s="478" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="388" t="inlineStr">
+      <c r="D4" s="478" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="388" t="inlineStr">
+      <c r="E4" s="478" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="388" t="inlineStr">
+      <c r="F4" s="478" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="388" t="inlineStr">
+      <c r="G4" s="478" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="388" t="inlineStr">
+      <c r="H4" s="478" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I4" s="347" t="n"/>
-      <c r="J4" s="347" t="n"/>
-      <c r="K4" s="347" t="n"/>
-      <c r="L4" s="347" t="n"/>
-      <c r="M4" s="347" t="n"/>
-      <c r="N4" s="347" t="n"/>
-      <c r="O4" s="347" t="n"/>
-      <c r="P4" s="347" t="n"/>
-      <c r="Q4" s="347" t="n"/>
-      <c r="R4" s="347" t="n"/>
-      <c r="S4" s="347" t="n"/>
-      <c r="T4" s="347" t="n"/>
-      <c r="U4" s="347" t="n"/>
-      <c r="V4" s="347" t="n"/>
-      <c r="W4" s="347" t="n"/>
-      <c r="X4" s="347" t="n"/>
-      <c r="Y4" s="347" t="n"/>
-      <c r="Z4" s="347" t="n"/>
-      <c r="AA4" s="347" t="n"/>
-      <c r="AB4" s="347" t="n"/>
-      <c r="AC4" s="347" t="n"/>
-      <c r="AD4" s="347" t="n"/>
-      <c r="AE4" s="347" t="n"/>
-      <c r="AF4" s="347" t="n"/>
-      <c r="AG4" s="347" t="n"/>
-      <c r="AH4" s="347" t="n"/>
-      <c r="AI4" s="347" t="n"/>
-      <c r="AJ4" s="347" t="n"/>
-      <c r="AK4" s="347" t="n"/>
-      <c r="AL4" s="347" t="n"/>
-      <c r="AM4" s="347" t="n"/>
-      <c r="AN4" s="347" t="n"/>
+      <c r="I4" s="478" t="n"/>
+      <c r="J4" s="478" t="n"/>
+      <c r="K4" s="478" t="n"/>
+      <c r="L4" s="478" t="n"/>
+      <c r="M4" s="478" t="n"/>
+      <c r="N4" s="478" t="n"/>
+      <c r="O4" s="478" t="n"/>
+      <c r="P4" s="478" t="n"/>
+      <c r="Q4" s="478" t="n"/>
+      <c r="R4" s="478" t="n"/>
+      <c r="S4" s="478" t="n"/>
+      <c r="T4" s="478" t="n"/>
+      <c r="U4" s="478" t="n"/>
+      <c r="V4" s="478" t="n"/>
+      <c r="W4" s="478" t="n"/>
+      <c r="X4" s="478" t="n"/>
+      <c r="Y4" s="478" t="n"/>
+      <c r="Z4" s="478" t="n"/>
+      <c r="AA4" s="478" t="n"/>
+      <c r="AB4" s="478" t="n"/>
+      <c r="AC4" s="478" t="n"/>
+      <c r="AD4" s="478" t="n"/>
+      <c r="AE4" s="478" t="n"/>
+      <c r="AF4" s="478" t="n"/>
+      <c r="AG4" s="478" t="n"/>
+      <c r="AH4" s="478" t="n"/>
+      <c r="AI4" s="478" t="n"/>
+      <c r="AJ4" s="478" t="n"/>
+      <c r="AK4" s="478" t="n"/>
+      <c r="AL4" s="478" t="n"/>
+      <c r="AM4" s="478" t="n"/>
+      <c r="AN4" s="480" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="347">
+      <c r="A5" s="501">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="347" t="n"/>
-      <c r="C5" s="347" t="n"/>
-      <c r="D5" s="347" t="n"/>
-      <c r="E5" s="347" t="n"/>
-      <c r="F5" s="347" t="n"/>
-      <c r="G5" s="347" t="n"/>
-      <c r="H5" s="347" t="n"/>
-      <c r="I5" s="347" t="n"/>
-      <c r="J5" s="347" t="n"/>
-      <c r="K5" s="347" t="n"/>
-      <c r="L5" s="347" t="n"/>
-      <c r="M5" s="347" t="n"/>
-      <c r="N5" s="347" t="n"/>
-      <c r="O5" s="347" t="n"/>
-      <c r="P5" s="347" t="n"/>
-      <c r="Q5" s="347" t="n"/>
-      <c r="R5" s="347" t="n"/>
-      <c r="S5" s="347" t="n"/>
-      <c r="T5" s="347" t="n"/>
-      <c r="U5" s="347" t="n"/>
-      <c r="V5" s="347" t="n"/>
-      <c r="W5" s="347" t="n"/>
-      <c r="X5" s="347" t="n"/>
-      <c r="Y5" s="347" t="n"/>
-      <c r="Z5" s="347" t="n"/>
-      <c r="AA5" s="347" t="n"/>
-      <c r="AB5" s="347" t="n"/>
-      <c r="AC5" s="347" t="n"/>
-      <c r="AD5" s="347" t="n"/>
-      <c r="AE5" s="347" t="n"/>
-      <c r="AF5" s="347" t="n"/>
-      <c r="AG5" s="347" t="n"/>
-      <c r="AH5" s="347" t="n"/>
-      <c r="AI5" s="347" t="n"/>
-      <c r="AJ5" s="347" t="n"/>
-      <c r="AK5" s="347" t="n"/>
-      <c r="AL5" s="347" t="n"/>
-      <c r="AM5" s="347" t="n"/>
-      <c r="AN5" s="347" t="n"/>
+      <c r="B5" s="459" t="n"/>
+      <c r="C5" s="459" t="n"/>
+      <c r="D5" s="459" t="n"/>
+      <c r="E5" s="459" t="n"/>
+      <c r="F5" s="459" t="n"/>
+      <c r="G5" s="459" t="n"/>
+      <c r="H5" s="459" t="n"/>
+      <c r="I5" s="459" t="n"/>
+      <c r="J5" s="459" t="n"/>
+      <c r="K5" s="459" t="n"/>
+      <c r="L5" s="459" t="n"/>
+      <c r="M5" s="459" t="n"/>
+      <c r="N5" s="459" t="n"/>
+      <c r="O5" s="459" t="n"/>
+      <c r="P5" s="459" t="n"/>
+      <c r="Q5" s="459" t="n"/>
+      <c r="R5" s="459" t="n"/>
+      <c r="S5" s="459" t="n"/>
+      <c r="T5" s="459" t="n"/>
+      <c r="U5" s="459" t="n"/>
+      <c r="V5" s="459" t="n"/>
+      <c r="W5" s="459" t="n"/>
+      <c r="X5" s="459" t="n"/>
+      <c r="Y5" s="459" t="n"/>
+      <c r="Z5" s="459" t="n"/>
+      <c r="AA5" s="459" t="n"/>
+      <c r="AB5" s="459" t="n"/>
+      <c r="AC5" s="459" t="n"/>
+      <c r="AD5" s="459" t="n"/>
+      <c r="AE5" s="459" t="n"/>
+      <c r="AF5" s="459" t="n"/>
+      <c r="AG5" s="459" t="n"/>
+      <c r="AH5" s="459" t="n"/>
+      <c r="AI5" s="459" t="n"/>
+      <c r="AJ5" s="459" t="n"/>
+      <c r="AK5" s="459" t="n"/>
+      <c r="AL5" s="459" t="n"/>
+      <c r="AM5" s="459" t="n"/>
+      <c r="AN5" s="462" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="347">
+      <c r="A6" s="474">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="347" t="n"/>
-      <c r="C6" s="347" t="n"/>
-      <c r="D6" s="347" t="n"/>
-      <c r="E6" s="347" t="n"/>
-      <c r="F6" s="347" t="n"/>
-      <c r="G6" s="347" t="n"/>
-      <c r="H6" s="347" t="n"/>
-      <c r="I6" s="347" t="n"/>
-      <c r="J6" s="347" t="n"/>
-      <c r="K6" s="347" t="n"/>
-      <c r="L6" s="347" t="n"/>
-      <c r="M6" s="347" t="n"/>
-      <c r="N6" s="347" t="n"/>
-      <c r="O6" s="347" t="n"/>
-      <c r="P6" s="347" t="n"/>
-      <c r="Q6" s="347" t="n"/>
-      <c r="R6" s="347" t="n"/>
-      <c r="S6" s="347" t="n"/>
-      <c r="T6" s="347" t="n"/>
-      <c r="U6" s="347" t="n"/>
-      <c r="V6" s="347" t="n"/>
-      <c r="W6" s="347" t="n"/>
-      <c r="X6" s="347" t="n"/>
-      <c r="Y6" s="347" t="n"/>
-      <c r="Z6" s="347" t="n"/>
-      <c r="AA6" s="347" t="n"/>
-      <c r="AB6" s="347" t="n"/>
-      <c r="AC6" s="347" t="n"/>
-      <c r="AD6" s="347" t="n"/>
-      <c r="AE6" s="347" t="n"/>
-      <c r="AF6" s="347" t="n"/>
-      <c r="AG6" s="347" t="n"/>
-      <c r="AH6" s="347" t="n"/>
-      <c r="AI6" s="347" t="n"/>
-      <c r="AJ6" s="347" t="n"/>
-      <c r="AK6" s="347" t="n"/>
-      <c r="AL6" s="347" t="n"/>
-      <c r="AM6" s="347" t="n"/>
-      <c r="AN6" s="347" t="n"/>
+      <c r="B6" s="343" t="n"/>
+      <c r="C6" s="343" t="n"/>
+      <c r="D6" s="343" t="n"/>
+      <c r="E6" s="343" t="n"/>
+      <c r="F6" s="343" t="n"/>
+      <c r="G6" s="343" t="n"/>
+      <c r="H6" s="343" t="n"/>
+      <c r="I6" s="343" t="n"/>
+      <c r="J6" s="343" t="n"/>
+      <c r="K6" s="343" t="n"/>
+      <c r="L6" s="343" t="n"/>
+      <c r="M6" s="343" t="n"/>
+      <c r="N6" s="343" t="n"/>
+      <c r="O6" s="343" t="n"/>
+      <c r="P6" s="343" t="n"/>
+      <c r="Q6" s="343" t="n"/>
+      <c r="R6" s="343" t="n"/>
+      <c r="S6" s="343" t="n"/>
+      <c r="T6" s="343" t="n"/>
+      <c r="U6" s="343" t="n"/>
+      <c r="V6" s="343" t="n"/>
+      <c r="W6" s="343" t="n"/>
+      <c r="X6" s="343" t="n"/>
+      <c r="Y6" s="343" t="n"/>
+      <c r="Z6" s="343" t="n"/>
+      <c r="AA6" s="343" t="n"/>
+      <c r="AB6" s="343" t="n"/>
+      <c r="AC6" s="343" t="n"/>
+      <c r="AD6" s="343" t="n"/>
+      <c r="AE6" s="343" t="n"/>
+      <c r="AF6" s="343" t="n"/>
+      <c r="AG6" s="343" t="n"/>
+      <c r="AH6" s="343" t="n"/>
+      <c r="AI6" s="343" t="n"/>
+      <c r="AJ6" s="343" t="n"/>
+      <c r="AK6" s="343" t="n"/>
+      <c r="AL6" s="343" t="n"/>
+      <c r="AM6" s="343" t="n"/>
+      <c r="AN6" s="466" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="347">
+      <c r="A7" s="474">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="347" t="n"/>
-      <c r="C7" s="347" t="n"/>
-      <c r="D7" s="347" t="n"/>
-      <c r="E7" s="347" t="n"/>
-      <c r="F7" s="347" t="n"/>
-      <c r="G7" s="347" t="n"/>
-      <c r="H7" s="347" t="n"/>
-      <c r="I7" s="347" t="n"/>
-      <c r="J7" s="347" t="n"/>
-      <c r="K7" s="347" t="n"/>
-      <c r="L7" s="347" t="n"/>
-      <c r="M7" s="347" t="n"/>
-      <c r="N7" s="347" t="n"/>
-      <c r="O7" s="347" t="n"/>
-      <c r="P7" s="347" t="n"/>
-      <c r="Q7" s="347" t="n"/>
-      <c r="R7" s="347" t="n"/>
-      <c r="S7" s="347" t="n"/>
-      <c r="T7" s="347" t="n"/>
-      <c r="U7" s="347" t="n"/>
-      <c r="V7" s="347" t="n"/>
-      <c r="W7" s="347" t="n"/>
-      <c r="X7" s="347" t="n"/>
-      <c r="Y7" s="347" t="n"/>
-      <c r="Z7" s="347" t="n"/>
-      <c r="AA7" s="347" t="n"/>
-      <c r="AB7" s="347" t="n"/>
-      <c r="AC7" s="347" t="n"/>
-      <c r="AD7" s="347" t="n"/>
-      <c r="AE7" s="347" t="n"/>
-      <c r="AF7" s="347" t="n"/>
-      <c r="AG7" s="347" t="n"/>
-      <c r="AH7" s="347" t="n"/>
-      <c r="AI7" s="347" t="n"/>
-      <c r="AJ7" s="347" t="n"/>
-      <c r="AK7" s="347" t="n"/>
-      <c r="AL7" s="347" t="n"/>
-      <c r="AM7" s="347" t="n"/>
-      <c r="AN7" s="347" t="n"/>
+      <c r="B7" s="343" t="n"/>
+      <c r="C7" s="343" t="n"/>
+      <c r="D7" s="343" t="n"/>
+      <c r="E7" s="343" t="n"/>
+      <c r="F7" s="343" t="n"/>
+      <c r="G7" s="343" t="n"/>
+      <c r="H7" s="343" t="n"/>
+      <c r="I7" s="343" t="n"/>
+      <c r="J7" s="343" t="n"/>
+      <c r="K7" s="343" t="n"/>
+      <c r="L7" s="343" t="n"/>
+      <c r="M7" s="343" t="n"/>
+      <c r="N7" s="343" t="n"/>
+      <c r="O7" s="343" t="n"/>
+      <c r="P7" s="343" t="n"/>
+      <c r="Q7" s="343" t="n"/>
+      <c r="R7" s="343" t="n"/>
+      <c r="S7" s="343" t="n"/>
+      <c r="T7" s="343" t="n"/>
+      <c r="U7" s="343" t="n"/>
+      <c r="V7" s="343" t="n"/>
+      <c r="W7" s="343" t="n"/>
+      <c r="X7" s="343" t="n"/>
+      <c r="Y7" s="343" t="n"/>
+      <c r="Z7" s="343" t="n"/>
+      <c r="AA7" s="343" t="n"/>
+      <c r="AB7" s="343" t="n"/>
+      <c r="AC7" s="343" t="n"/>
+      <c r="AD7" s="343" t="n"/>
+      <c r="AE7" s="343" t="n"/>
+      <c r="AF7" s="343" t="n"/>
+      <c r="AG7" s="343" t="n"/>
+      <c r="AH7" s="343" t="n"/>
+      <c r="AI7" s="343" t="n"/>
+      <c r="AJ7" s="343" t="n"/>
+      <c r="AK7" s="343" t="n"/>
+      <c r="AL7" s="343" t="n"/>
+      <c r="AM7" s="343" t="n"/>
+      <c r="AN7" s="466" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="383">
+      <c r="A8" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="383" t="n"/>
-      <c r="C8" s="383" t="n"/>
-      <c r="D8" s="383" t="n"/>
-      <c r="E8" s="383" t="n"/>
-      <c r="F8" s="383" t="n"/>
-      <c r="G8" s="383" t="n"/>
-      <c r="H8" s="383" t="n"/>
-      <c r="I8" s="383" t="n"/>
-      <c r="J8" s="383" t="n"/>
-      <c r="K8" s="383" t="n"/>
-      <c r="L8" s="383" t="n"/>
-      <c r="M8" s="383" t="n"/>
-      <c r="N8" s="383" t="n"/>
-      <c r="O8" s="383" t="n"/>
-      <c r="P8" s="383" t="n"/>
-      <c r="Q8" s="383" t="n"/>
-      <c r="R8" s="383" t="n"/>
-      <c r="S8" s="383" t="n"/>
-      <c r="T8" s="383" t="n"/>
-      <c r="U8" s="383" t="n"/>
-      <c r="V8" s="383" t="n"/>
-      <c r="W8" s="383" t="n"/>
-      <c r="X8" s="383" t="n"/>
-      <c r="Y8" s="383" t="n"/>
-      <c r="Z8" s="383" t="n"/>
-      <c r="AA8" s="383" t="n"/>
-      <c r="AB8" s="383" t="n"/>
-      <c r="AC8" s="383" t="n"/>
-      <c r="AD8" s="383" t="n"/>
-      <c r="AE8" s="383" t="n"/>
-      <c r="AF8" s="383" t="n"/>
-      <c r="AG8" s="383" t="n"/>
-      <c r="AH8" s="383" t="n"/>
-      <c r="AI8" s="383" t="n"/>
-      <c r="AJ8" s="383" t="n"/>
-      <c r="AK8" s="383" t="n"/>
-      <c r="AL8" s="383" t="n"/>
-      <c r="AM8" s="383" t="n"/>
-      <c r="AN8" s="383" t="n"/>
+      <c r="B8" s="355" t="n"/>
+      <c r="C8" s="355" t="n"/>
+      <c r="D8" s="355" t="n"/>
+      <c r="E8" s="355" t="n"/>
+      <c r="F8" s="355" t="n"/>
+      <c r="G8" s="355" t="n"/>
+      <c r="H8" s="355" t="n"/>
+      <c r="I8" s="355" t="n"/>
+      <c r="J8" s="355" t="n"/>
+      <c r="K8" s="355" t="n"/>
+      <c r="L8" s="355" t="n"/>
+      <c r="M8" s="355" t="n"/>
+      <c r="N8" s="355" t="n"/>
+      <c r="O8" s="355" t="n"/>
+      <c r="P8" s="355" t="n"/>
+      <c r="Q8" s="355" t="n"/>
+      <c r="R8" s="355" t="n"/>
+      <c r="S8" s="355" t="n"/>
+      <c r="T8" s="355" t="n"/>
+      <c r="U8" s="355" t="n"/>
+      <c r="V8" s="355" t="n"/>
+      <c r="W8" s="355" t="n"/>
+      <c r="X8" s="355" t="n"/>
+      <c r="Y8" s="355" t="n"/>
+      <c r="Z8" s="355" t="n"/>
+      <c r="AA8" s="355" t="n"/>
+      <c r="AB8" s="355" t="n"/>
+      <c r="AC8" s="355" t="n"/>
+      <c r="AD8" s="355" t="n"/>
+      <c r="AE8" s="355" t="n"/>
+      <c r="AF8" s="355" t="n"/>
+      <c r="AG8" s="355" t="n"/>
+      <c r="AH8" s="355" t="n"/>
+      <c r="AI8" s="355" t="n"/>
+      <c r="AJ8" s="355" t="n"/>
+      <c r="AK8" s="355" t="n"/>
+      <c r="AL8" s="355" t="n"/>
+      <c r="AM8" s="355" t="n"/>
+      <c r="AN8" s="503" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="383">
+      <c r="A9" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="383" t="n"/>
-      <c r="C9" s="383" t="n"/>
-      <c r="D9" s="383" t="n"/>
-      <c r="E9" s="383" t="n"/>
-      <c r="F9" s="383" t="n"/>
-      <c r="G9" s="383" t="n"/>
-      <c r="H9" s="383" t="n"/>
-      <c r="I9" s="383" t="n"/>
-      <c r="J9" s="383" t="n"/>
-      <c r="K9" s="383" t="n"/>
-      <c r="L9" s="383" t="n"/>
-      <c r="M9" s="383" t="n"/>
-      <c r="N9" s="383" t="n"/>
-      <c r="O9" s="383" t="n"/>
-      <c r="P9" s="383" t="n"/>
-      <c r="Q9" s="383" t="n"/>
-      <c r="R9" s="383" t="n"/>
-      <c r="S9" s="383" t="n"/>
-      <c r="T9" s="383" t="n"/>
-      <c r="U9" s="383" t="n"/>
-      <c r="V9" s="383" t="n"/>
-      <c r="W9" s="383" t="n"/>
-      <c r="X9" s="383" t="n"/>
-      <c r="Y9" s="383" t="n"/>
-      <c r="Z9" s="383" t="n"/>
-      <c r="AA9" s="383" t="n"/>
-      <c r="AB9" s="383" t="n"/>
-      <c r="AC9" s="383" t="n"/>
-      <c r="AD9" s="383" t="n"/>
-      <c r="AE9" s="383" t="n"/>
-      <c r="AF9" s="383" t="n"/>
-      <c r="AG9" s="383" t="n"/>
-      <c r="AH9" s="383" t="n"/>
-      <c r="AI9" s="383" t="n"/>
-      <c r="AJ9" s="383" t="n"/>
-      <c r="AK9" s="383" t="n"/>
-      <c r="AL9" s="383" t="n"/>
-      <c r="AM9" s="383" t="n"/>
-      <c r="AN9" s="383" t="n"/>
+      <c r="B9" s="355" t="n"/>
+      <c r="C9" s="355" t="n"/>
+      <c r="D9" s="355" t="n"/>
+      <c r="E9" s="355" t="n"/>
+      <c r="F9" s="355" t="n"/>
+      <c r="G9" s="355" t="n"/>
+      <c r="H9" s="355" t="n"/>
+      <c r="I9" s="355" t="n"/>
+      <c r="J9" s="355" t="n"/>
+      <c r="K9" s="355" t="n"/>
+      <c r="L9" s="355" t="n"/>
+      <c r="M9" s="355" t="n"/>
+      <c r="N9" s="355" t="n"/>
+      <c r="O9" s="355" t="n"/>
+      <c r="P9" s="355" t="n"/>
+      <c r="Q9" s="355" t="n"/>
+      <c r="R9" s="355" t="n"/>
+      <c r="S9" s="355" t="n"/>
+      <c r="T9" s="355" t="n"/>
+      <c r="U9" s="355" t="n"/>
+      <c r="V9" s="355" t="n"/>
+      <c r="W9" s="355" t="n"/>
+      <c r="X9" s="355" t="n"/>
+      <c r="Y9" s="355" t="n"/>
+      <c r="Z9" s="355" t="n"/>
+      <c r="AA9" s="355" t="n"/>
+      <c r="AB9" s="355" t="n"/>
+      <c r="AC9" s="355" t="n"/>
+      <c r="AD9" s="355" t="n"/>
+      <c r="AE9" s="355" t="n"/>
+      <c r="AF9" s="355" t="n"/>
+      <c r="AG9" s="355" t="n"/>
+      <c r="AH9" s="355" t="n"/>
+      <c r="AI9" s="355" t="n"/>
+      <c r="AJ9" s="355" t="n"/>
+      <c r="AK9" s="355" t="n"/>
+      <c r="AL9" s="355" t="n"/>
+      <c r="AM9" s="355" t="n"/>
+      <c r="AN9" s="503" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="383">
+      <c r="A10" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="383" t="n"/>
-      <c r="C10" s="383" t="n"/>
-      <c r="D10" s="383" t="n"/>
-      <c r="E10" s="383" t="n"/>
-      <c r="F10" s="383" t="n"/>
-      <c r="G10" s="383" t="n"/>
-      <c r="H10" s="383" t="n"/>
-      <c r="I10" s="383" t="n"/>
-      <c r="J10" s="383" t="n"/>
-      <c r="K10" s="383" t="n"/>
-      <c r="L10" s="383" t="n"/>
-      <c r="M10" s="383" t="n"/>
-      <c r="N10" s="383" t="n"/>
-      <c r="O10" s="383" t="n"/>
-      <c r="P10" s="383" t="n"/>
-      <c r="Q10" s="383" t="n"/>
-      <c r="R10" s="383" t="n"/>
-      <c r="S10" s="383" t="n"/>
-      <c r="T10" s="383" t="n"/>
-      <c r="U10" s="383" t="n"/>
-      <c r="V10" s="383" t="n"/>
-      <c r="W10" s="383" t="n"/>
-      <c r="X10" s="383" t="n"/>
-      <c r="Y10" s="383" t="n"/>
-      <c r="Z10" s="383" t="n"/>
-      <c r="AA10" s="383" t="n"/>
-      <c r="AB10" s="383" t="n"/>
-      <c r="AC10" s="383" t="n"/>
-      <c r="AD10" s="383" t="n"/>
-      <c r="AE10" s="383" t="n"/>
-      <c r="AF10" s="383" t="n"/>
-      <c r="AG10" s="383" t="n"/>
-      <c r="AH10" s="383" t="n"/>
-      <c r="AI10" s="383" t="n"/>
-      <c r="AJ10" s="383" t="n"/>
-      <c r="AK10" s="383" t="n"/>
-      <c r="AL10" s="383" t="n"/>
-      <c r="AM10" s="383" t="n"/>
-      <c r="AN10" s="383" t="n"/>
+      <c r="B10" s="355" t="n"/>
+      <c r="C10" s="355" t="n"/>
+      <c r="D10" s="355" t="n"/>
+      <c r="E10" s="355" t="n"/>
+      <c r="F10" s="355" t="n"/>
+      <c r="G10" s="355" t="n"/>
+      <c r="H10" s="355" t="n"/>
+      <c r="I10" s="355" t="n"/>
+      <c r="J10" s="355" t="n"/>
+      <c r="K10" s="355" t="n"/>
+      <c r="L10" s="355" t="n"/>
+      <c r="M10" s="355" t="n"/>
+      <c r="N10" s="355" t="n"/>
+      <c r="O10" s="355" t="n"/>
+      <c r="P10" s="355" t="n"/>
+      <c r="Q10" s="355" t="n"/>
+      <c r="R10" s="355" t="n"/>
+      <c r="S10" s="355" t="n"/>
+      <c r="T10" s="355" t="n"/>
+      <c r="U10" s="355" t="n"/>
+      <c r="V10" s="355" t="n"/>
+      <c r="W10" s="355" t="n"/>
+      <c r="X10" s="355" t="n"/>
+      <c r="Y10" s="355" t="n"/>
+      <c r="Z10" s="355" t="n"/>
+      <c r="AA10" s="355" t="n"/>
+      <c r="AB10" s="355" t="n"/>
+      <c r="AC10" s="355" t="n"/>
+      <c r="AD10" s="355" t="n"/>
+      <c r="AE10" s="355" t="n"/>
+      <c r="AF10" s="355" t="n"/>
+      <c r="AG10" s="355" t="n"/>
+      <c r="AH10" s="355" t="n"/>
+      <c r="AI10" s="355" t="n"/>
+      <c r="AJ10" s="355" t="n"/>
+      <c r="AK10" s="355" t="n"/>
+      <c r="AL10" s="355" t="n"/>
+      <c r="AM10" s="355" t="n"/>
+      <c r="AN10" s="503" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="383">
+      <c r="A11" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="383" t="n"/>
-      <c r="C11" s="383" t="n"/>
-      <c r="D11" s="383" t="n"/>
-      <c r="E11" s="383" t="n"/>
-      <c r="F11" s="383" t="n"/>
-      <c r="G11" s="383" t="n"/>
-      <c r="H11" s="383" t="n"/>
-      <c r="I11" s="383" t="n"/>
-      <c r="J11" s="383" t="n"/>
-      <c r="K11" s="383" t="n"/>
-      <c r="L11" s="383" t="n"/>
-      <c r="M11" s="383" t="n"/>
-      <c r="N11" s="383" t="n"/>
-      <c r="O11" s="383" t="n"/>
-      <c r="P11" s="383" t="n"/>
-      <c r="Q11" s="383" t="n"/>
-      <c r="R11" s="383" t="n"/>
-      <c r="S11" s="383" t="n"/>
-      <c r="T11" s="383" t="n"/>
-      <c r="U11" s="383" t="n"/>
-      <c r="V11" s="383" t="n"/>
-      <c r="W11" s="383" t="n"/>
-      <c r="X11" s="383" t="n"/>
-      <c r="Y11" s="383" t="n"/>
-      <c r="Z11" s="383" t="n"/>
-      <c r="AA11" s="383" t="n"/>
-      <c r="AB11" s="383" t="n"/>
-      <c r="AC11" s="383" t="n"/>
-      <c r="AD11" s="383" t="n"/>
-      <c r="AE11" s="383" t="n"/>
-      <c r="AF11" s="383" t="n"/>
-      <c r="AG11" s="383" t="n"/>
-      <c r="AH11" s="383" t="n"/>
-      <c r="AI11" s="383" t="n"/>
-      <c r="AJ11" s="383" t="n"/>
-      <c r="AK11" s="383" t="n"/>
-      <c r="AL11" s="383" t="n"/>
-      <c r="AM11" s="383" t="n"/>
-      <c r="AN11" s="383" t="n"/>
+      <c r="B11" s="355" t="n"/>
+      <c r="C11" s="355" t="n"/>
+      <c r="D11" s="355" t="n"/>
+      <c r="E11" s="355" t="n"/>
+      <c r="F11" s="355" t="n"/>
+      <c r="G11" s="355" t="n"/>
+      <c r="H11" s="355" t="n"/>
+      <c r="I11" s="355" t="n"/>
+      <c r="J11" s="355" t="n"/>
+      <c r="K11" s="355" t="n"/>
+      <c r="L11" s="355" t="n"/>
+      <c r="M11" s="355" t="n"/>
+      <c r="N11" s="355" t="n"/>
+      <c r="O11" s="355" t="n"/>
+      <c r="P11" s="355" t="n"/>
+      <c r="Q11" s="355" t="n"/>
+      <c r="R11" s="355" t="n"/>
+      <c r="S11" s="355" t="n"/>
+      <c r="T11" s="355" t="n"/>
+      <c r="U11" s="355" t="n"/>
+      <c r="V11" s="355" t="n"/>
+      <c r="W11" s="355" t="n"/>
+      <c r="X11" s="355" t="n"/>
+      <c r="Y11" s="355" t="n"/>
+      <c r="Z11" s="355" t="n"/>
+      <c r="AA11" s="355" t="n"/>
+      <c r="AB11" s="355" t="n"/>
+      <c r="AC11" s="355" t="n"/>
+      <c r="AD11" s="355" t="n"/>
+      <c r="AE11" s="355" t="n"/>
+      <c r="AF11" s="355" t="n"/>
+      <c r="AG11" s="355" t="n"/>
+      <c r="AH11" s="355" t="n"/>
+      <c r="AI11" s="355" t="n"/>
+      <c r="AJ11" s="355" t="n"/>
+      <c r="AK11" s="355" t="n"/>
+      <c r="AL11" s="355" t="n"/>
+      <c r="AM11" s="355" t="n"/>
+      <c r="AN11" s="503" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="383">
+      <c r="A12" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="383" t="n"/>
-      <c r="C12" s="383" t="n"/>
-      <c r="D12" s="383" t="n"/>
-      <c r="E12" s="383" t="n"/>
-      <c r="F12" s="383" t="n"/>
-      <c r="G12" s="383" t="n"/>
-      <c r="H12" s="383" t="n"/>
-      <c r="I12" s="383" t="n"/>
-      <c r="J12" s="383" t="n"/>
-      <c r="K12" s="383" t="n"/>
-      <c r="L12" s="383" t="n"/>
-      <c r="M12" s="383" t="n"/>
-      <c r="N12" s="383" t="n"/>
-      <c r="O12" s="383" t="n"/>
-      <c r="P12" s="383" t="n"/>
-      <c r="Q12" s="383" t="n"/>
-      <c r="R12" s="383" t="n"/>
-      <c r="S12" s="383" t="n"/>
-      <c r="T12" s="383" t="n"/>
-      <c r="U12" s="383" t="n"/>
-      <c r="V12" s="383" t="n"/>
-      <c r="W12" s="383" t="n"/>
-      <c r="X12" s="383" t="n"/>
-      <c r="Y12" s="383" t="n"/>
-      <c r="Z12" s="383" t="n"/>
-      <c r="AA12" s="383" t="n"/>
-      <c r="AB12" s="383" t="n"/>
-      <c r="AC12" s="383" t="n"/>
-      <c r="AD12" s="383" t="n"/>
-      <c r="AE12" s="383" t="n"/>
-      <c r="AF12" s="383" t="n"/>
-      <c r="AG12" s="383" t="n"/>
-      <c r="AH12" s="383" t="n"/>
-      <c r="AI12" s="383" t="n"/>
-      <c r="AJ12" s="383" t="n"/>
-      <c r="AK12" s="383" t="n"/>
-      <c r="AL12" s="383" t="n"/>
-      <c r="AM12" s="383" t="n"/>
-      <c r="AN12" s="383" t="n"/>
+      <c r="B12" s="355" t="n"/>
+      <c r="C12" s="355" t="n"/>
+      <c r="D12" s="355" t="n"/>
+      <c r="E12" s="355" t="n"/>
+      <c r="F12" s="355" t="n"/>
+      <c r="G12" s="355" t="n"/>
+      <c r="H12" s="355" t="n"/>
+      <c r="I12" s="355" t="n"/>
+      <c r="J12" s="355" t="n"/>
+      <c r="K12" s="355" t="n"/>
+      <c r="L12" s="355" t="n"/>
+      <c r="M12" s="355" t="n"/>
+      <c r="N12" s="355" t="n"/>
+      <c r="O12" s="355" t="n"/>
+      <c r="P12" s="355" t="n"/>
+      <c r="Q12" s="355" t="n"/>
+      <c r="R12" s="355" t="n"/>
+      <c r="S12" s="355" t="n"/>
+      <c r="T12" s="355" t="n"/>
+      <c r="U12" s="355" t="n"/>
+      <c r="V12" s="355" t="n"/>
+      <c r="W12" s="355" t="n"/>
+      <c r="X12" s="355" t="n"/>
+      <c r="Y12" s="355" t="n"/>
+      <c r="Z12" s="355" t="n"/>
+      <c r="AA12" s="355" t="n"/>
+      <c r="AB12" s="355" t="n"/>
+      <c r="AC12" s="355" t="n"/>
+      <c r="AD12" s="355" t="n"/>
+      <c r="AE12" s="355" t="n"/>
+      <c r="AF12" s="355" t="n"/>
+      <c r="AG12" s="355" t="n"/>
+      <c r="AH12" s="355" t="n"/>
+      <c r="AI12" s="355" t="n"/>
+      <c r="AJ12" s="355" t="n"/>
+      <c r="AK12" s="355" t="n"/>
+      <c r="AL12" s="355" t="n"/>
+      <c r="AM12" s="355" t="n"/>
+      <c r="AN12" s="503" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="383">
+      <c r="A13" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="383" t="n"/>
-      <c r="C13" s="383" t="n"/>
-      <c r="D13" s="383" t="n"/>
-      <c r="E13" s="383" t="n"/>
-      <c r="F13" s="383" t="n"/>
-      <c r="G13" s="383" t="n"/>
-      <c r="H13" s="383" t="n"/>
-      <c r="I13" s="383" t="n"/>
-      <c r="J13" s="383" t="n"/>
-      <c r="K13" s="383" t="n"/>
-      <c r="L13" s="383" t="n"/>
-      <c r="M13" s="383" t="n"/>
-      <c r="N13" s="383" t="n"/>
-      <c r="O13" s="383" t="n"/>
-      <c r="P13" s="383" t="n"/>
-      <c r="Q13" s="383" t="n"/>
-      <c r="R13" s="383" t="n"/>
-      <c r="S13" s="383" t="n"/>
-      <c r="T13" s="383" t="n"/>
-      <c r="U13" s="383" t="n"/>
-      <c r="V13" s="383" t="n"/>
-      <c r="W13" s="383" t="n"/>
-      <c r="X13" s="383" t="n"/>
-      <c r="Y13" s="383" t="n"/>
-      <c r="Z13" s="383" t="n"/>
-      <c r="AA13" s="383" t="n"/>
-      <c r="AB13" s="383" t="n"/>
-      <c r="AC13" s="383" t="n"/>
-      <c r="AD13" s="383" t="n"/>
-      <c r="AE13" s="383" t="n"/>
-      <c r="AF13" s="383" t="n"/>
-      <c r="AG13" s="383" t="n"/>
-      <c r="AH13" s="383" t="n"/>
-      <c r="AI13" s="383" t="n"/>
-      <c r="AJ13" s="383" t="n"/>
-      <c r="AK13" s="383" t="n"/>
-      <c r="AL13" s="383" t="n"/>
-      <c r="AM13" s="383" t="n"/>
-      <c r="AN13" s="383" t="n"/>
+      <c r="B13" s="355" t="n"/>
+      <c r="C13" s="355" t="n"/>
+      <c r="D13" s="355" t="n"/>
+      <c r="E13" s="355" t="n"/>
+      <c r="F13" s="355" t="n"/>
+      <c r="G13" s="355" t="n"/>
+      <c r="H13" s="355" t="n"/>
+      <c r="I13" s="355" t="n"/>
+      <c r="J13" s="355" t="n"/>
+      <c r="K13" s="355" t="n"/>
+      <c r="L13" s="355" t="n"/>
+      <c r="M13" s="355" t="n"/>
+      <c r="N13" s="355" t="n"/>
+      <c r="O13" s="355" t="n"/>
+      <c r="P13" s="355" t="n"/>
+      <c r="Q13" s="355" t="n"/>
+      <c r="R13" s="355" t="n"/>
+      <c r="S13" s="355" t="n"/>
+      <c r="T13" s="355" t="n"/>
+      <c r="U13" s="355" t="n"/>
+      <c r="V13" s="355" t="n"/>
+      <c r="W13" s="355" t="n"/>
+      <c r="X13" s="355" t="n"/>
+      <c r="Y13" s="355" t="n"/>
+      <c r="Z13" s="355" t="n"/>
+      <c r="AA13" s="355" t="n"/>
+      <c r="AB13" s="355" t="n"/>
+      <c r="AC13" s="355" t="n"/>
+      <c r="AD13" s="355" t="n"/>
+      <c r="AE13" s="355" t="n"/>
+      <c r="AF13" s="355" t="n"/>
+      <c r="AG13" s="355" t="n"/>
+      <c r="AH13" s="355" t="n"/>
+      <c r="AI13" s="355" t="n"/>
+      <c r="AJ13" s="355" t="n"/>
+      <c r="AK13" s="355" t="n"/>
+      <c r="AL13" s="355" t="n"/>
+      <c r="AM13" s="355" t="n"/>
+      <c r="AN13" s="503" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="383">
+      <c r="A14" s="504">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="383" t="n"/>
-      <c r="C14" s="383" t="n"/>
-      <c r="D14" s="383" t="n"/>
-      <c r="E14" s="383" t="n"/>
-      <c r="F14" s="383" t="n"/>
-      <c r="G14" s="383" t="n"/>
-      <c r="H14" s="383" t="n"/>
-      <c r="I14" s="383" t="n"/>
-      <c r="J14" s="383" t="n"/>
-      <c r="K14" s="383" t="n"/>
-      <c r="L14" s="383" t="n"/>
-      <c r="M14" s="383" t="n"/>
-      <c r="N14" s="383" t="n"/>
-      <c r="O14" s="383" t="n"/>
-      <c r="P14" s="383" t="n"/>
-      <c r="Q14" s="383" t="n"/>
-      <c r="R14" s="383" t="n"/>
-      <c r="S14" s="383" t="n"/>
-      <c r="T14" s="383" t="n"/>
-      <c r="U14" s="383" t="n"/>
-      <c r="V14" s="383" t="n"/>
-      <c r="W14" s="383" t="n"/>
-      <c r="X14" s="383" t="n"/>
-      <c r="Y14" s="383" t="n"/>
-      <c r="Z14" s="383" t="n"/>
-      <c r="AA14" s="383" t="n"/>
-      <c r="AB14" s="383" t="n"/>
-      <c r="AC14" s="383" t="n"/>
-      <c r="AD14" s="383" t="n"/>
-      <c r="AE14" s="383" t="n"/>
-      <c r="AF14" s="383" t="n"/>
-      <c r="AG14" s="383" t="n"/>
-      <c r="AH14" s="383" t="n"/>
-      <c r="AI14" s="383" t="n"/>
-      <c r="AJ14" s="383" t="n"/>
-      <c r="AK14" s="383" t="n"/>
-      <c r="AL14" s="383" t="n"/>
-      <c r="AM14" s="383" t="n"/>
-      <c r="AN14" s="383" t="n"/>
+      <c r="B14" s="505" t="n"/>
+      <c r="C14" s="505" t="n"/>
+      <c r="D14" s="505" t="n"/>
+      <c r="E14" s="505" t="n"/>
+      <c r="F14" s="505" t="n"/>
+      <c r="G14" s="505" t="n"/>
+      <c r="H14" s="505" t="n"/>
+      <c r="I14" s="505" t="n"/>
+      <c r="J14" s="505" t="n"/>
+      <c r="K14" s="505" t="n"/>
+      <c r="L14" s="505" t="n"/>
+      <c r="M14" s="505" t="n"/>
+      <c r="N14" s="505" t="n"/>
+      <c r="O14" s="505" t="n"/>
+      <c r="P14" s="505" t="n"/>
+      <c r="Q14" s="505" t="n"/>
+      <c r="R14" s="505" t="n"/>
+      <c r="S14" s="505" t="n"/>
+      <c r="T14" s="505" t="n"/>
+      <c r="U14" s="505" t="n"/>
+      <c r="V14" s="505" t="n"/>
+      <c r="W14" s="505" t="n"/>
+      <c r="X14" s="505" t="n"/>
+      <c r="Y14" s="505" t="n"/>
+      <c r="Z14" s="505" t="n"/>
+      <c r="AA14" s="505" t="n"/>
+      <c r="AB14" s="505" t="n"/>
+      <c r="AC14" s="505" t="n"/>
+      <c r="AD14" s="505" t="n"/>
+      <c r="AE14" s="505" t="n"/>
+      <c r="AF14" s="505" t="n"/>
+      <c r="AG14" s="505" t="n"/>
+      <c r="AH14" s="505" t="n"/>
+      <c r="AI14" s="505" t="n"/>
+      <c r="AJ14" s="505" t="n"/>
+      <c r="AK14" s="505" t="n"/>
+      <c r="AL14" s="505" t="n"/>
+      <c r="AM14" s="505" t="n"/>
+      <c r="AN14" s="506" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -8303,249 +9087,255 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="389" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="507" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="411" t="n"/>
-      <c r="C1" s="411" t="n"/>
-      <c r="D1" s="411" t="n"/>
-      <c r="E1" s="411" t="n"/>
-      <c r="F1" s="411" t="n"/>
-      <c r="G1" s="412" t="n"/>
-      <c r="H1" s="347" t="n"/>
-      <c r="I1" s="347" t="n"/>
-      <c r="J1" s="347" t="n"/>
-      <c r="K1" s="347" t="n"/>
-      <c r="L1" s="347" t="n"/>
-      <c r="M1" s="347" t="n"/>
-      <c r="N1" s="347" t="n"/>
-      <c r="O1" s="347" t="n"/>
-      <c r="P1" s="347" t="n"/>
-      <c r="Q1" s="347" t="n"/>
-      <c r="R1" s="347" t="n"/>
-      <c r="S1" s="347" t="n"/>
-      <c r="T1" s="347" t="n"/>
-      <c r="U1" s="347" t="n"/>
-      <c r="V1" s="347" t="n"/>
-      <c r="W1" s="347" t="n"/>
-      <c r="X1" s="347" t="n"/>
-      <c r="Y1" s="347" t="n"/>
-      <c r="Z1" s="347" t="n"/>
-      <c r="AA1" s="347" t="n"/>
-      <c r="AB1" s="347" t="n"/>
-      <c r="AC1" s="347" t="n"/>
-      <c r="AD1" s="347" t="n"/>
-      <c r="AE1" s="347" t="n"/>
-      <c r="AF1" s="347" t="n"/>
-      <c r="AG1" s="347" t="n"/>
-      <c r="AH1" s="347" t="n"/>
-      <c r="AI1" s="347" t="n"/>
-      <c r="AJ1" s="347" t="n"/>
-      <c r="AK1" s="347" t="n"/>
-      <c r="AL1" s="347" t="n"/>
-      <c r="AM1" s="347" t="n"/>
-      <c r="AN1" s="347" t="n"/>
+      <c r="B1" s="417" t="n"/>
+      <c r="C1" s="417" t="n"/>
+      <c r="D1" s="417" t="n"/>
+      <c r="E1" s="417" t="n"/>
+      <c r="F1" s="417" t="n"/>
+      <c r="G1" s="417" t="n"/>
+      <c r="H1" s="508" t="n"/>
+      <c r="I1" s="419" t="n"/>
+      <c r="J1" s="420" t="n"/>
+      <c r="K1" s="420" t="n"/>
+      <c r="L1" s="420" t="n"/>
+      <c r="M1" s="420" t="n"/>
+      <c r="N1" s="420" t="n"/>
+      <c r="O1" s="420" t="n"/>
+      <c r="P1" s="420" t="n"/>
+      <c r="Q1" s="420" t="n"/>
+      <c r="R1" s="420" t="n"/>
+      <c r="S1" s="420" t="n"/>
+      <c r="T1" s="420" t="n"/>
+      <c r="U1" s="420" t="n"/>
+      <c r="V1" s="420" t="n"/>
+      <c r="W1" s="420" t="n"/>
+      <c r="X1" s="420" t="n"/>
+      <c r="Y1" s="420" t="n"/>
+      <c r="Z1" s="420" t="n"/>
+      <c r="AA1" s="420" t="n"/>
+      <c r="AB1" s="420" t="n"/>
+      <c r="AC1" s="420" t="n"/>
+      <c r="AD1" s="421" t="n"/>
+      <c r="AE1" s="422" t="n"/>
+      <c r="AF1" s="423" t="n"/>
+      <c r="AG1" s="423" t="n"/>
+      <c r="AH1" s="424" t="n"/>
+      <c r="AI1" s="425" t="n"/>
+      <c r="AJ1" s="426" t="n"/>
+      <c r="AK1" s="426" t="n"/>
+      <c r="AL1" s="426" t="n"/>
+      <c r="AM1" s="426" t="n"/>
+      <c r="AN1" s="427" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="338" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="509" t="inlineStr">
         <is>
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
-      <c r="H2" s="347" t="n"/>
-      <c r="I2" s="347" t="n"/>
-      <c r="J2" s="347" t="n"/>
-      <c r="K2" s="347" t="n"/>
-      <c r="L2" s="347" t="n"/>
-      <c r="M2" s="347" t="n"/>
-      <c r="N2" s="347" t="n"/>
-      <c r="O2" s="347" t="n"/>
-      <c r="P2" s="347" t="n"/>
-      <c r="Q2" s="347" t="n"/>
-      <c r="R2" s="347" t="n"/>
-      <c r="S2" s="347" t="n"/>
-      <c r="T2" s="347" t="n"/>
-      <c r="U2" s="347" t="n"/>
-      <c r="V2" s="347" t="n"/>
-      <c r="W2" s="347" t="n"/>
-      <c r="X2" s="347" t="n"/>
-      <c r="Y2" s="347" t="n"/>
-      <c r="Z2" s="347" t="n"/>
-      <c r="AA2" s="347" t="n"/>
-      <c r="AB2" s="347" t="n"/>
-      <c r="AC2" s="347" t="n"/>
-      <c r="AD2" s="347" t="n"/>
-      <c r="AE2" s="347" t="n"/>
-      <c r="AF2" s="347" t="n"/>
-      <c r="AG2" s="347" t="n"/>
-      <c r="AH2" s="347" t="n"/>
-      <c r="AI2" s="347" t="n"/>
-      <c r="AJ2" s="347" t="n"/>
-      <c r="AK2" s="347" t="n"/>
-      <c r="AL2" s="347" t="n"/>
-      <c r="AM2" s="347" t="n"/>
-      <c r="AN2" s="347" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="510" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="431" t="n"/>
+      <c r="K2" s="431" t="n"/>
+      <c r="L2" s="431" t="n"/>
+      <c r="M2" s="431" t="n"/>
+      <c r="N2" s="431" t="n"/>
+      <c r="O2" s="431" t="n"/>
+      <c r="P2" s="431" t="n"/>
+      <c r="Q2" s="431" t="n"/>
+      <c r="R2" s="431" t="n"/>
+      <c r="S2" s="431" t="n"/>
+      <c r="T2" s="431" t="n"/>
+      <c r="U2" s="431" t="n"/>
+      <c r="V2" s="431" t="n"/>
+      <c r="W2" s="431" t="n"/>
+      <c r="X2" s="431" t="n"/>
+      <c r="Y2" s="431" t="n"/>
+      <c r="Z2" s="431" t="n"/>
+      <c r="AA2" s="431" t="n"/>
+      <c r="AB2" s="431" t="n"/>
+      <c r="AC2" s="431" t="n"/>
+      <c r="AD2" s="432" t="n"/>
+      <c r="AE2" s="433" t="n"/>
+      <c r="AF2" s="434" t="n"/>
+      <c r="AG2" s="434" t="n"/>
+      <c r="AH2" s="435" t="n"/>
+      <c r="AI2" s="436" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="438" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="347" t="n"/>
-      <c r="B3" s="347" t="n"/>
-      <c r="C3" s="347" t="n"/>
-      <c r="D3" s="347" t="n"/>
-      <c r="E3" s="347" t="n"/>
-      <c r="F3" s="347" t="n"/>
-      <c r="G3" s="347" t="n"/>
-      <c r="H3" s="347" t="n"/>
-      <c r="I3" s="347" t="n"/>
-      <c r="J3" s="347" t="n"/>
-      <c r="K3" s="347" t="n"/>
-      <c r="L3" s="347" t="n"/>
-      <c r="M3" s="347" t="n"/>
-      <c r="N3" s="347" t="n"/>
-      <c r="O3" s="347" t="n"/>
-      <c r="P3" s="347" t="n"/>
-      <c r="Q3" s="347" t="n"/>
-      <c r="R3" s="347" t="n"/>
-      <c r="S3" s="347" t="n"/>
-      <c r="T3" s="347" t="n"/>
-      <c r="U3" s="347" t="n"/>
-      <c r="V3" s="347" t="n"/>
-      <c r="W3" s="347" t="n"/>
-      <c r="X3" s="347" t="n"/>
-      <c r="Y3" s="347" t="n"/>
-      <c r="Z3" s="347" t="n"/>
-      <c r="AA3" s="347" t="n"/>
-      <c r="AB3" s="347" t="n"/>
-      <c r="AC3" s="347" t="n"/>
-      <c r="AD3" s="347" t="n"/>
-      <c r="AE3" s="347" t="n"/>
-      <c r="AF3" s="347" t="n"/>
-      <c r="AG3" s="347" t="n"/>
-      <c r="AH3" s="347" t="n"/>
-      <c r="AI3" s="347" t="n"/>
-      <c r="AJ3" s="347" t="n"/>
-      <c r="AK3" s="347" t="n"/>
-      <c r="AL3" s="347" t="n"/>
-      <c r="AM3" s="347" t="n"/>
-      <c r="AN3" s="347" t="n"/>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="511" t="n"/>
+      <c r="B3" s="512" t="n"/>
+      <c r="C3" s="512" t="n"/>
+      <c r="D3" s="512" t="n"/>
+      <c r="E3" s="512" t="n"/>
+      <c r="F3" s="512" t="n"/>
+      <c r="G3" s="512" t="n"/>
+      <c r="H3" s="510" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="431" t="n"/>
+      <c r="K3" s="431" t="n"/>
+      <c r="L3" s="431" t="n"/>
+      <c r="M3" s="431" t="n"/>
+      <c r="N3" s="431" t="n"/>
+      <c r="O3" s="431" t="n"/>
+      <c r="P3" s="431" t="n"/>
+      <c r="Q3" s="431" t="n"/>
+      <c r="R3" s="431" t="n"/>
+      <c r="S3" s="431" t="n"/>
+      <c r="T3" s="431" t="n"/>
+      <c r="U3" s="431" t="n"/>
+      <c r="V3" s="431" t="n"/>
+      <c r="W3" s="431" t="n"/>
+      <c r="X3" s="431" t="n"/>
+      <c r="Y3" s="431" t="n"/>
+      <c r="Z3" s="431" t="n"/>
+      <c r="AA3" s="431" t="n"/>
+      <c r="AB3" s="431" t="n"/>
+      <c r="AC3" s="431" t="n"/>
+      <c r="AD3" s="432" t="n"/>
+      <c r="AE3" s="433" t="n"/>
+      <c r="AF3" s="434" t="n"/>
+      <c r="AG3" s="434" t="n"/>
+      <c r="AH3" s="435" t="n"/>
+      <c r="AI3" s="436" t="n"/>
+      <c r="AJ3" s="437" t="n"/>
+      <c r="AK3" s="437" t="n"/>
+      <c r="AL3" s="437" t="n"/>
+      <c r="AM3" s="437" t="n"/>
+      <c r="AN3" s="438" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="388" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="513" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="388" t="inlineStr">
+      <c r="B4" s="514" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="388" t="inlineStr">
+      <c r="C4" s="514" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="347" t="n"/>
-      <c r="E4" s="347" t="n"/>
-      <c r="F4" s="347" t="n"/>
-      <c r="G4" s="347" t="n"/>
-      <c r="H4" s="347" t="n"/>
-      <c r="I4" s="347" t="n"/>
-      <c r="J4" s="347" t="n"/>
-      <c r="K4" s="347" t="n"/>
-      <c r="L4" s="347" t="n"/>
-      <c r="M4" s="347" t="n"/>
-      <c r="N4" s="347" t="n"/>
-      <c r="O4" s="347" t="n"/>
-      <c r="P4" s="347" t="n"/>
-      <c r="Q4" s="347" t="n"/>
-      <c r="R4" s="347" t="n"/>
-      <c r="S4" s="347" t="n"/>
-      <c r="T4" s="347" t="n"/>
-      <c r="U4" s="347" t="n"/>
-      <c r="V4" s="347" t="n"/>
-      <c r="W4" s="347" t="n"/>
-      <c r="X4" s="347" t="n"/>
-      <c r="Y4" s="347" t="n"/>
-      <c r="Z4" s="347" t="n"/>
-      <c r="AA4" s="347" t="n"/>
-      <c r="AB4" s="347" t="n"/>
-      <c r="AC4" s="347" t="n"/>
-      <c r="AD4" s="347" t="n"/>
-      <c r="AE4" s="347" t="n"/>
-      <c r="AF4" s="347" t="n"/>
-      <c r="AG4" s="347" t="n"/>
-      <c r="AH4" s="347" t="n"/>
-      <c r="AI4" s="347" t="n"/>
-      <c r="AJ4" s="347" t="n"/>
-      <c r="AK4" s="347" t="n"/>
-      <c r="AL4" s="347" t="n"/>
-      <c r="AM4" s="347" t="n"/>
-      <c r="AN4" s="347" t="n"/>
+      <c r="D4" s="512" t="n"/>
+      <c r="E4" s="512" t="n"/>
+      <c r="F4" s="512" t="n"/>
+      <c r="G4" s="512" t="n"/>
+      <c r="H4" s="510" t="n"/>
+      <c r="I4" s="439" t="n"/>
+      <c r="J4" s="440" t="n"/>
+      <c r="K4" s="440" t="n"/>
+      <c r="L4" s="440" t="n"/>
+      <c r="M4" s="440" t="n"/>
+      <c r="N4" s="440" t="n"/>
+      <c r="O4" s="440" t="n"/>
+      <c r="P4" s="440" t="n"/>
+      <c r="Q4" s="440" t="n"/>
+      <c r="R4" s="440" t="n"/>
+      <c r="S4" s="440" t="n"/>
+      <c r="T4" s="440" t="n"/>
+      <c r="U4" s="440" t="n"/>
+      <c r="V4" s="440" t="n"/>
+      <c r="W4" s="440" t="n"/>
+      <c r="X4" s="440" t="n"/>
+      <c r="Y4" s="440" t="n"/>
+      <c r="Z4" s="440" t="n"/>
+      <c r="AA4" s="440" t="n"/>
+      <c r="AB4" s="440" t="n"/>
+      <c r="AC4" s="440" t="n"/>
+      <c r="AD4" s="441" t="n"/>
+      <c r="AE4" s="433" t="n"/>
+      <c r="AF4" s="434" t="n"/>
+      <c r="AG4" s="434" t="n"/>
+      <c r="AH4" s="435" t="n"/>
+      <c r="AI4" s="436" t="n"/>
+      <c r="AJ4" s="437" t="n"/>
+      <c r="AK4" s="437" t="n"/>
+      <c r="AL4" s="437" t="n"/>
+      <c r="AM4" s="437" t="n"/>
+      <c r="AN4" s="438" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="390" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="515" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="391" t="inlineStr">
+      <c r="B5" s="516" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="391" t="inlineStr">
+      <c r="C5" s="516" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="347" t="n"/>
-      <c r="E5" s="347" t="n"/>
-      <c r="F5" s="347" t="n"/>
-      <c r="G5" s="347" t="n"/>
-      <c r="H5" s="347" t="n"/>
-      <c r="I5" s="347" t="n"/>
-      <c r="J5" s="347" t="n"/>
-      <c r="K5" s="347" t="n"/>
-      <c r="L5" s="347" t="n"/>
-      <c r="M5" s="347" t="n"/>
-      <c r="N5" s="347" t="n"/>
-      <c r="O5" s="347" t="n"/>
-      <c r="P5" s="347" t="n"/>
-      <c r="Q5" s="347" t="n"/>
-      <c r="R5" s="347" t="n"/>
-      <c r="S5" s="347" t="n"/>
-      <c r="T5" s="347" t="n"/>
-      <c r="U5" s="347" t="n"/>
-      <c r="V5" s="347" t="n"/>
-      <c r="W5" s="347" t="n"/>
-      <c r="X5" s="347" t="n"/>
-      <c r="Y5" s="347" t="n"/>
-      <c r="Z5" s="347" t="n"/>
-      <c r="AA5" s="347" t="n"/>
-      <c r="AB5" s="347" t="n"/>
-      <c r="AC5" s="347" t="n"/>
-      <c r="AD5" s="347" t="n"/>
-      <c r="AE5" s="347" t="n"/>
-      <c r="AF5" s="347" t="n"/>
-      <c r="AG5" s="347" t="n"/>
-      <c r="AH5" s="347" t="n"/>
-      <c r="AI5" s="347" t="n"/>
-      <c r="AJ5" s="347" t="n"/>
-      <c r="AK5" s="347" t="n"/>
-      <c r="AL5" s="347" t="n"/>
-      <c r="AM5" s="347" t="n"/>
-      <c r="AN5" s="347" t="n"/>
+      <c r="D5" s="517" t="n"/>
+      <c r="E5" s="517" t="n"/>
+      <c r="F5" s="517" t="n"/>
+      <c r="G5" s="517" t="n"/>
+      <c r="H5" s="518" t="n"/>
+      <c r="I5" s="445" t="n"/>
+      <c r="J5" s="446" t="n"/>
+      <c r="K5" s="446" t="n"/>
+      <c r="L5" s="446" t="n"/>
+      <c r="M5" s="446" t="n"/>
+      <c r="N5" s="446" t="n"/>
+      <c r="O5" s="446" t="n"/>
+      <c r="P5" s="446" t="n"/>
+      <c r="Q5" s="446" t="n"/>
+      <c r="R5" s="446" t="n"/>
+      <c r="S5" s="446" t="n"/>
+      <c r="T5" s="446" t="n"/>
+      <c r="U5" s="446" t="n"/>
+      <c r="V5" s="446" t="n"/>
+      <c r="W5" s="446" t="n"/>
+      <c r="X5" s="446" t="n"/>
+      <c r="Y5" s="446" t="n"/>
+      <c r="Z5" s="446" t="n"/>
+      <c r="AA5" s="446" t="n"/>
+      <c r="AB5" s="446" t="n"/>
+      <c r="AC5" s="446" t="n"/>
+      <c r="AD5" s="447" t="n"/>
+      <c r="AE5" s="448" t="n"/>
+      <c r="AF5" s="449" t="n"/>
+      <c r="AG5" s="449" t="n"/>
+      <c r="AH5" s="450" t="n"/>
+      <c r="AI5" s="451" t="n"/>
+      <c r="AJ5" s="452" t="n"/>
+      <c r="AK5" s="452" t="n"/>
+      <c r="AL5" s="452" t="n"/>
+      <c r="AM5" s="452" t="n"/>
+      <c r="AN5" s="453" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="390" t="inlineStr">
+      <c r="A6" s="519" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="391" t="inlineStr">
+      <c r="B6" s="520" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -8553,7 +9343,7 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="391" t="inlineStr">
+      <c r="C6" s="521" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -8561,475 +9351,475 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="347" t="n"/>
-      <c r="E6" s="347" t="n"/>
-      <c r="F6" s="347" t="n"/>
-      <c r="G6" s="347" t="n"/>
-      <c r="H6" s="347" t="n"/>
-      <c r="I6" s="347" t="n"/>
-      <c r="J6" s="347" t="n"/>
-      <c r="K6" s="347" t="n"/>
-      <c r="L6" s="347" t="n"/>
-      <c r="M6" s="347" t="n"/>
-      <c r="N6" s="347" t="n"/>
-      <c r="O6" s="347" t="n"/>
-      <c r="P6" s="347" t="n"/>
-      <c r="Q6" s="347" t="n"/>
-      <c r="R6" s="347" t="n"/>
-      <c r="S6" s="347" t="n"/>
-      <c r="T6" s="347" t="n"/>
-      <c r="U6" s="347" t="n"/>
-      <c r="V6" s="347" t="n"/>
-      <c r="W6" s="347" t="n"/>
-      <c r="X6" s="347" t="n"/>
-      <c r="Y6" s="347" t="n"/>
-      <c r="Z6" s="347" t="n"/>
-      <c r="AA6" s="347" t="n"/>
-      <c r="AB6" s="347" t="n"/>
-      <c r="AC6" s="347" t="n"/>
-      <c r="AD6" s="347" t="n"/>
-      <c r="AE6" s="347" t="n"/>
-      <c r="AF6" s="347" t="n"/>
-      <c r="AG6" s="347" t="n"/>
-      <c r="AH6" s="347" t="n"/>
-      <c r="AI6" s="347" t="n"/>
-      <c r="AJ6" s="347" t="n"/>
-      <c r="AK6" s="347" t="n"/>
-      <c r="AL6" s="347" t="n"/>
-      <c r="AM6" s="347" t="n"/>
-      <c r="AN6" s="347" t="n"/>
+      <c r="D6" s="459" t="n"/>
+      <c r="E6" s="459" t="n"/>
+      <c r="F6" s="459" t="n"/>
+      <c r="G6" s="459" t="n"/>
+      <c r="H6" s="459" t="n"/>
+      <c r="I6" s="459" t="n"/>
+      <c r="J6" s="459" t="n"/>
+      <c r="K6" s="459" t="n"/>
+      <c r="L6" s="459" t="n"/>
+      <c r="M6" s="459" t="n"/>
+      <c r="N6" s="459" t="n"/>
+      <c r="O6" s="459" t="n"/>
+      <c r="P6" s="459" t="n"/>
+      <c r="Q6" s="459" t="n"/>
+      <c r="R6" s="459" t="n"/>
+      <c r="S6" s="459" t="n"/>
+      <c r="T6" s="459" t="n"/>
+      <c r="U6" s="459" t="n"/>
+      <c r="V6" s="459" t="n"/>
+      <c r="W6" s="459" t="n"/>
+      <c r="X6" s="459" t="n"/>
+      <c r="Y6" s="459" t="n"/>
+      <c r="Z6" s="459" t="n"/>
+      <c r="AA6" s="459" t="n"/>
+      <c r="AB6" s="459" t="n"/>
+      <c r="AC6" s="459" t="n"/>
+      <c r="AD6" s="459" t="n"/>
+      <c r="AE6" s="459" t="n"/>
+      <c r="AF6" s="459" t="n"/>
+      <c r="AG6" s="459" t="n"/>
+      <c r="AH6" s="459" t="n"/>
+      <c r="AI6" s="459" t="n"/>
+      <c r="AJ6" s="459" t="n"/>
+      <c r="AK6" s="459" t="n"/>
+      <c r="AL6" s="459" t="n"/>
+      <c r="AM6" s="459" t="n"/>
+      <c r="AN6" s="462" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="390" t="inlineStr">
+      <c r="A7" s="522" t="inlineStr">
         <is>
           <t>SOP-401</t>
         </is>
       </c>
-      <c r="B7" s="391" t="inlineStr">
+      <c r="B7" s="523" t="inlineStr">
         <is>
           <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="391" t="inlineStr">
+      <c r="C7" s="524" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
         </is>
       </c>
-      <c r="D7" s="347" t="n"/>
-      <c r="E7" s="347" t="n"/>
-      <c r="F7" s="347" t="n"/>
-      <c r="G7" s="347" t="n"/>
-      <c r="H7" s="347" t="n"/>
-      <c r="I7" s="347" t="n"/>
-      <c r="J7" s="347" t="n"/>
-      <c r="K7" s="347" t="n"/>
-      <c r="L7" s="347" t="n"/>
-      <c r="M7" s="347" t="n"/>
-      <c r="N7" s="347" t="n"/>
-      <c r="O7" s="347" t="n"/>
-      <c r="P7" s="347" t="n"/>
-      <c r="Q7" s="347" t="n"/>
-      <c r="R7" s="347" t="n"/>
-      <c r="S7" s="347" t="n"/>
-      <c r="T7" s="347" t="n"/>
-      <c r="U7" s="347" t="n"/>
-      <c r="V7" s="347" t="n"/>
-      <c r="W7" s="347" t="n"/>
-      <c r="X7" s="347" t="n"/>
-      <c r="Y7" s="347" t="n"/>
-      <c r="Z7" s="347" t="n"/>
-      <c r="AA7" s="347" t="n"/>
-      <c r="AB7" s="347" t="n"/>
-      <c r="AC7" s="347" t="n"/>
-      <c r="AD7" s="347" t="n"/>
-      <c r="AE7" s="347" t="n"/>
-      <c r="AF7" s="347" t="n"/>
-      <c r="AG7" s="347" t="n"/>
-      <c r="AH7" s="347" t="n"/>
-      <c r="AI7" s="347" t="n"/>
-      <c r="AJ7" s="347" t="n"/>
-      <c r="AK7" s="347" t="n"/>
-      <c r="AL7" s="347" t="n"/>
-      <c r="AM7" s="347" t="n"/>
-      <c r="AN7" s="347" t="n"/>
+      <c r="D7" s="343" t="n"/>
+      <c r="E7" s="343" t="n"/>
+      <c r="F7" s="343" t="n"/>
+      <c r="G7" s="343" t="n"/>
+      <c r="H7" s="343" t="n"/>
+      <c r="I7" s="343" t="n"/>
+      <c r="J7" s="343" t="n"/>
+      <c r="K7" s="343" t="n"/>
+      <c r="L7" s="343" t="n"/>
+      <c r="M7" s="343" t="n"/>
+      <c r="N7" s="343" t="n"/>
+      <c r="O7" s="343" t="n"/>
+      <c r="P7" s="343" t="n"/>
+      <c r="Q7" s="343" t="n"/>
+      <c r="R7" s="343" t="n"/>
+      <c r="S7" s="343" t="n"/>
+      <c r="T7" s="343" t="n"/>
+      <c r="U7" s="343" t="n"/>
+      <c r="V7" s="343" t="n"/>
+      <c r="W7" s="343" t="n"/>
+      <c r="X7" s="343" t="n"/>
+      <c r="Y7" s="343" t="n"/>
+      <c r="Z7" s="343" t="n"/>
+      <c r="AA7" s="343" t="n"/>
+      <c r="AB7" s="343" t="n"/>
+      <c r="AC7" s="343" t="n"/>
+      <c r="AD7" s="343" t="n"/>
+      <c r="AE7" s="343" t="n"/>
+      <c r="AF7" s="343" t="n"/>
+      <c r="AG7" s="343" t="n"/>
+      <c r="AH7" s="343" t="n"/>
+      <c r="AI7" s="343" t="n"/>
+      <c r="AJ7" s="343" t="n"/>
+      <c r="AK7" s="343" t="n"/>
+      <c r="AL7" s="343" t="n"/>
+      <c r="AM7" s="343" t="n"/>
+      <c r="AN7" s="466" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="354" t="inlineStr">
+      <c r="A8" s="463" t="inlineStr">
         <is>
           <t>WI-206</t>
         </is>
       </c>
-      <c r="B8" s="392" t="inlineStr">
+      <c r="B8" s="464" t="inlineStr">
         <is>
           <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
         </is>
       </c>
-      <c r="C8" s="392" t="inlineStr">
+      <c r="C8" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
         </is>
       </c>
-      <c r="D8" s="383" t="n"/>
-      <c r="E8" s="383" t="n"/>
-      <c r="F8" s="383" t="n"/>
-      <c r="G8" s="383" t="n"/>
-      <c r="H8" s="383" t="n"/>
-      <c r="I8" s="383" t="n"/>
-      <c r="J8" s="383" t="n"/>
-      <c r="K8" s="383" t="n"/>
-      <c r="L8" s="383" t="n"/>
-      <c r="M8" s="383" t="n"/>
-      <c r="N8" s="383" t="n"/>
-      <c r="O8" s="383" t="n"/>
-      <c r="P8" s="383" t="n"/>
-      <c r="Q8" s="383" t="n"/>
-      <c r="R8" s="383" t="n"/>
-      <c r="S8" s="383" t="n"/>
-      <c r="T8" s="383" t="n"/>
-      <c r="U8" s="383" t="n"/>
-      <c r="V8" s="383" t="n"/>
-      <c r="W8" s="383" t="n"/>
-      <c r="X8" s="383" t="n"/>
-      <c r="Y8" s="383" t="n"/>
-      <c r="Z8" s="383" t="n"/>
-      <c r="AA8" s="383" t="n"/>
-      <c r="AB8" s="383" t="n"/>
-      <c r="AC8" s="383" t="n"/>
-      <c r="AD8" s="383" t="n"/>
-      <c r="AE8" s="383" t="n"/>
-      <c r="AF8" s="383" t="n"/>
-      <c r="AG8" s="383" t="n"/>
-      <c r="AH8" s="383" t="n"/>
-      <c r="AI8" s="383" t="n"/>
-      <c r="AJ8" s="383" t="n"/>
-      <c r="AK8" s="383" t="n"/>
-      <c r="AL8" s="383" t="n"/>
-      <c r="AM8" s="383" t="n"/>
-      <c r="AN8" s="383" t="n"/>
+      <c r="D8" s="355" t="n"/>
+      <c r="E8" s="355" t="n"/>
+      <c r="F8" s="355" t="n"/>
+      <c r="G8" s="355" t="n"/>
+      <c r="H8" s="355" t="n"/>
+      <c r="I8" s="355" t="n"/>
+      <c r="J8" s="355" t="n"/>
+      <c r="K8" s="355" t="n"/>
+      <c r="L8" s="355" t="n"/>
+      <c r="M8" s="355" t="n"/>
+      <c r="N8" s="355" t="n"/>
+      <c r="O8" s="355" t="n"/>
+      <c r="P8" s="355" t="n"/>
+      <c r="Q8" s="355" t="n"/>
+      <c r="R8" s="355" t="n"/>
+      <c r="S8" s="355" t="n"/>
+      <c r="T8" s="355" t="n"/>
+      <c r="U8" s="355" t="n"/>
+      <c r="V8" s="355" t="n"/>
+      <c r="W8" s="355" t="n"/>
+      <c r="X8" s="355" t="n"/>
+      <c r="Y8" s="355" t="n"/>
+      <c r="Z8" s="355" t="n"/>
+      <c r="AA8" s="355" t="n"/>
+      <c r="AB8" s="355" t="n"/>
+      <c r="AC8" s="355" t="n"/>
+      <c r="AD8" s="355" t="n"/>
+      <c r="AE8" s="355" t="n"/>
+      <c r="AF8" s="355" t="n"/>
+      <c r="AG8" s="355" t="n"/>
+      <c r="AH8" s="355" t="n"/>
+      <c r="AI8" s="355" t="n"/>
+      <c r="AJ8" s="355" t="n"/>
+      <c r="AK8" s="355" t="n"/>
+      <c r="AL8" s="355" t="n"/>
+      <c r="AM8" s="355" t="n"/>
+      <c r="AN8" s="503" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="354" t="inlineStr">
+      <c r="A9" s="463" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B9" s="392" t="inlineStr">
+      <c r="B9" s="464" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C9" s="392" t="inlineStr">
+      <c r="C9" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
-      <c r="D9" s="383" t="n"/>
-      <c r="E9" s="383" t="n"/>
-      <c r="F9" s="383" t="n"/>
-      <c r="G9" s="383" t="n"/>
-      <c r="H9" s="383" t="n"/>
-      <c r="I9" s="383" t="n"/>
-      <c r="J9" s="383" t="n"/>
-      <c r="K9" s="383" t="n"/>
-      <c r="L9" s="383" t="n"/>
-      <c r="M9" s="383" t="n"/>
-      <c r="N9" s="383" t="n"/>
-      <c r="O9" s="383" t="n"/>
-      <c r="P9" s="383" t="n"/>
-      <c r="Q9" s="383" t="n"/>
-      <c r="R9" s="383" t="n"/>
-      <c r="S9" s="383" t="n"/>
-      <c r="T9" s="383" t="n"/>
-      <c r="U9" s="383" t="n"/>
-      <c r="V9" s="383" t="n"/>
-      <c r="W9" s="383" t="n"/>
-      <c r="X9" s="383" t="n"/>
-      <c r="Y9" s="383" t="n"/>
-      <c r="Z9" s="383" t="n"/>
-      <c r="AA9" s="383" t="n"/>
-      <c r="AB9" s="383" t="n"/>
-      <c r="AC9" s="383" t="n"/>
-      <c r="AD9" s="383" t="n"/>
-      <c r="AE9" s="383" t="n"/>
-      <c r="AF9" s="383" t="n"/>
-      <c r="AG9" s="383" t="n"/>
-      <c r="AH9" s="383" t="n"/>
-      <c r="AI9" s="383" t="n"/>
-      <c r="AJ9" s="383" t="n"/>
-      <c r="AK9" s="383" t="n"/>
-      <c r="AL9" s="383" t="n"/>
-      <c r="AM9" s="383" t="n"/>
-      <c r="AN9" s="383" t="n"/>
+      <c r="D9" s="355" t="n"/>
+      <c r="E9" s="355" t="n"/>
+      <c r="F9" s="355" t="n"/>
+      <c r="G9" s="355" t="n"/>
+      <c r="H9" s="355" t="n"/>
+      <c r="I9" s="355" t="n"/>
+      <c r="J9" s="355" t="n"/>
+      <c r="K9" s="355" t="n"/>
+      <c r="L9" s="355" t="n"/>
+      <c r="M9" s="355" t="n"/>
+      <c r="N9" s="355" t="n"/>
+      <c r="O9" s="355" t="n"/>
+      <c r="P9" s="355" t="n"/>
+      <c r="Q9" s="355" t="n"/>
+      <c r="R9" s="355" t="n"/>
+      <c r="S9" s="355" t="n"/>
+      <c r="T9" s="355" t="n"/>
+      <c r="U9" s="355" t="n"/>
+      <c r="V9" s="355" t="n"/>
+      <c r="W9" s="355" t="n"/>
+      <c r="X9" s="355" t="n"/>
+      <c r="Y9" s="355" t="n"/>
+      <c r="Z9" s="355" t="n"/>
+      <c r="AA9" s="355" t="n"/>
+      <c r="AB9" s="355" t="n"/>
+      <c r="AC9" s="355" t="n"/>
+      <c r="AD9" s="355" t="n"/>
+      <c r="AE9" s="355" t="n"/>
+      <c r="AF9" s="355" t="n"/>
+      <c r="AG9" s="355" t="n"/>
+      <c r="AH9" s="355" t="n"/>
+      <c r="AI9" s="355" t="n"/>
+      <c r="AJ9" s="355" t="n"/>
+      <c r="AK9" s="355" t="n"/>
+      <c r="AL9" s="355" t="n"/>
+      <c r="AM9" s="355" t="n"/>
+      <c r="AN9" s="503" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="354" t="inlineStr">
+      <c r="A10" s="463" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B10" s="392" t="inlineStr">
+      <c r="B10" s="464" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C10" s="392" t="inlineStr">
+      <c r="C10" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
-      <c r="D10" s="383" t="n"/>
-      <c r="E10" s="383" t="n"/>
-      <c r="F10" s="383" t="n"/>
-      <c r="G10" s="383" t="n"/>
-      <c r="H10" s="383" t="n"/>
-      <c r="I10" s="383" t="n"/>
-      <c r="J10" s="383" t="n"/>
-      <c r="K10" s="383" t="n"/>
-      <c r="L10" s="383" t="n"/>
-      <c r="M10" s="383" t="n"/>
-      <c r="N10" s="383" t="n"/>
-      <c r="O10" s="383" t="n"/>
-      <c r="P10" s="383" t="n"/>
-      <c r="Q10" s="383" t="n"/>
-      <c r="R10" s="383" t="n"/>
-      <c r="S10" s="383" t="n"/>
-      <c r="T10" s="383" t="n"/>
-      <c r="U10" s="383" t="n"/>
-      <c r="V10" s="383" t="n"/>
-      <c r="W10" s="383" t="n"/>
-      <c r="X10" s="383" t="n"/>
-      <c r="Y10" s="383" t="n"/>
-      <c r="Z10" s="383" t="n"/>
-      <c r="AA10" s="383" t="n"/>
-      <c r="AB10" s="383" t="n"/>
-      <c r="AC10" s="383" t="n"/>
-      <c r="AD10" s="383" t="n"/>
-      <c r="AE10" s="383" t="n"/>
-      <c r="AF10" s="383" t="n"/>
-      <c r="AG10" s="383" t="n"/>
-      <c r="AH10" s="383" t="n"/>
-      <c r="AI10" s="383" t="n"/>
-      <c r="AJ10" s="383" t="n"/>
-      <c r="AK10" s="383" t="n"/>
-      <c r="AL10" s="383" t="n"/>
-      <c r="AM10" s="383" t="n"/>
-      <c r="AN10" s="383" t="n"/>
+      <c r="D10" s="355" t="n"/>
+      <c r="E10" s="355" t="n"/>
+      <c r="F10" s="355" t="n"/>
+      <c r="G10" s="355" t="n"/>
+      <c r="H10" s="355" t="n"/>
+      <c r="I10" s="355" t="n"/>
+      <c r="J10" s="355" t="n"/>
+      <c r="K10" s="355" t="n"/>
+      <c r="L10" s="355" t="n"/>
+      <c r="M10" s="355" t="n"/>
+      <c r="N10" s="355" t="n"/>
+      <c r="O10" s="355" t="n"/>
+      <c r="P10" s="355" t="n"/>
+      <c r="Q10" s="355" t="n"/>
+      <c r="R10" s="355" t="n"/>
+      <c r="S10" s="355" t="n"/>
+      <c r="T10" s="355" t="n"/>
+      <c r="U10" s="355" t="n"/>
+      <c r="V10" s="355" t="n"/>
+      <c r="W10" s="355" t="n"/>
+      <c r="X10" s="355" t="n"/>
+      <c r="Y10" s="355" t="n"/>
+      <c r="Z10" s="355" t="n"/>
+      <c r="AA10" s="355" t="n"/>
+      <c r="AB10" s="355" t="n"/>
+      <c r="AC10" s="355" t="n"/>
+      <c r="AD10" s="355" t="n"/>
+      <c r="AE10" s="355" t="n"/>
+      <c r="AF10" s="355" t="n"/>
+      <c r="AG10" s="355" t="n"/>
+      <c r="AH10" s="355" t="n"/>
+      <c r="AI10" s="355" t="n"/>
+      <c r="AJ10" s="355" t="n"/>
+      <c r="AK10" s="355" t="n"/>
+      <c r="AL10" s="355" t="n"/>
+      <c r="AM10" s="355" t="n"/>
+      <c r="AN10" s="503" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="354" t="inlineStr">
+      <c r="A11" s="463" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B11" s="392" t="inlineStr">
+      <c r="B11" s="464" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C11" s="392" t="inlineStr">
+      <c r="C11" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
-      <c r="D11" s="383" t="n"/>
-      <c r="E11" s="383" t="n"/>
-      <c r="F11" s="383" t="n"/>
-      <c r="G11" s="383" t="n"/>
-      <c r="H11" s="383" t="n"/>
-      <c r="I11" s="383" t="n"/>
-      <c r="J11" s="383" t="n"/>
-      <c r="K11" s="383" t="n"/>
-      <c r="L11" s="383" t="n"/>
-      <c r="M11" s="383" t="n"/>
-      <c r="N11" s="383" t="n"/>
-      <c r="O11" s="383" t="n"/>
-      <c r="P11" s="383" t="n"/>
-      <c r="Q11" s="383" t="n"/>
-      <c r="R11" s="383" t="n"/>
-      <c r="S11" s="383" t="n"/>
-      <c r="T11" s="383" t="n"/>
-      <c r="U11" s="383" t="n"/>
-      <c r="V11" s="383" t="n"/>
-      <c r="W11" s="383" t="n"/>
-      <c r="X11" s="383" t="n"/>
-      <c r="Y11" s="383" t="n"/>
-      <c r="Z11" s="383" t="n"/>
-      <c r="AA11" s="383" t="n"/>
-      <c r="AB11" s="383" t="n"/>
-      <c r="AC11" s="383" t="n"/>
-      <c r="AD11" s="383" t="n"/>
-      <c r="AE11" s="383" t="n"/>
-      <c r="AF11" s="383" t="n"/>
-      <c r="AG11" s="383" t="n"/>
-      <c r="AH11" s="383" t="n"/>
-      <c r="AI11" s="383" t="n"/>
-      <c r="AJ11" s="383" t="n"/>
-      <c r="AK11" s="383" t="n"/>
-      <c r="AL11" s="383" t="n"/>
-      <c r="AM11" s="383" t="n"/>
-      <c r="AN11" s="383" t="n"/>
+      <c r="D11" s="355" t="n"/>
+      <c r="E11" s="355" t="n"/>
+      <c r="F11" s="355" t="n"/>
+      <c r="G11" s="355" t="n"/>
+      <c r="H11" s="355" t="n"/>
+      <c r="I11" s="355" t="n"/>
+      <c r="J11" s="355" t="n"/>
+      <c r="K11" s="355" t="n"/>
+      <c r="L11" s="355" t="n"/>
+      <c r="M11" s="355" t="n"/>
+      <c r="N11" s="355" t="n"/>
+      <c r="O11" s="355" t="n"/>
+      <c r="P11" s="355" t="n"/>
+      <c r="Q11" s="355" t="n"/>
+      <c r="R11" s="355" t="n"/>
+      <c r="S11" s="355" t="n"/>
+      <c r="T11" s="355" t="n"/>
+      <c r="U11" s="355" t="n"/>
+      <c r="V11" s="355" t="n"/>
+      <c r="W11" s="355" t="n"/>
+      <c r="X11" s="355" t="n"/>
+      <c r="Y11" s="355" t="n"/>
+      <c r="Z11" s="355" t="n"/>
+      <c r="AA11" s="355" t="n"/>
+      <c r="AB11" s="355" t="n"/>
+      <c r="AC11" s="355" t="n"/>
+      <c r="AD11" s="355" t="n"/>
+      <c r="AE11" s="355" t="n"/>
+      <c r="AF11" s="355" t="n"/>
+      <c r="AG11" s="355" t="n"/>
+      <c r="AH11" s="355" t="n"/>
+      <c r="AI11" s="355" t="n"/>
+      <c r="AJ11" s="355" t="n"/>
+      <c r="AK11" s="355" t="n"/>
+      <c r="AL11" s="355" t="n"/>
+      <c r="AM11" s="355" t="n"/>
+      <c r="AN11" s="503" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="354" t="inlineStr">
+      <c r="A12" s="463" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B12" s="392" t="inlineStr">
+      <c r="B12" s="464" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C12" s="392" t="inlineStr">
+      <c r="C12" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
-      <c r="D12" s="383" t="n"/>
-      <c r="E12" s="383" t="n"/>
-      <c r="F12" s="383" t="n"/>
-      <c r="G12" s="383" t="n"/>
-      <c r="H12" s="383" t="n"/>
-      <c r="I12" s="383" t="n"/>
-      <c r="J12" s="383" t="n"/>
-      <c r="K12" s="383" t="n"/>
-      <c r="L12" s="383" t="n"/>
-      <c r="M12" s="383" t="n"/>
-      <c r="N12" s="383" t="n"/>
-      <c r="O12" s="383" t="n"/>
-      <c r="P12" s="383" t="n"/>
-      <c r="Q12" s="383" t="n"/>
-      <c r="R12" s="383" t="n"/>
-      <c r="S12" s="383" t="n"/>
-      <c r="T12" s="383" t="n"/>
-      <c r="U12" s="383" t="n"/>
-      <c r="V12" s="383" t="n"/>
-      <c r="W12" s="383" t="n"/>
-      <c r="X12" s="383" t="n"/>
-      <c r="Y12" s="383" t="n"/>
-      <c r="Z12" s="383" t="n"/>
-      <c r="AA12" s="383" t="n"/>
-      <c r="AB12" s="383" t="n"/>
-      <c r="AC12" s="383" t="n"/>
-      <c r="AD12" s="383" t="n"/>
-      <c r="AE12" s="383" t="n"/>
-      <c r="AF12" s="383" t="n"/>
-      <c r="AG12" s="383" t="n"/>
-      <c r="AH12" s="383" t="n"/>
-      <c r="AI12" s="383" t="n"/>
-      <c r="AJ12" s="383" t="n"/>
-      <c r="AK12" s="383" t="n"/>
-      <c r="AL12" s="383" t="n"/>
-      <c r="AM12" s="383" t="n"/>
-      <c r="AN12" s="383" t="n"/>
+      <c r="D12" s="355" t="n"/>
+      <c r="E12" s="355" t="n"/>
+      <c r="F12" s="355" t="n"/>
+      <c r="G12" s="355" t="n"/>
+      <c r="H12" s="355" t="n"/>
+      <c r="I12" s="355" t="n"/>
+      <c r="J12" s="355" t="n"/>
+      <c r="K12" s="355" t="n"/>
+      <c r="L12" s="355" t="n"/>
+      <c r="M12" s="355" t="n"/>
+      <c r="N12" s="355" t="n"/>
+      <c r="O12" s="355" t="n"/>
+      <c r="P12" s="355" t="n"/>
+      <c r="Q12" s="355" t="n"/>
+      <c r="R12" s="355" t="n"/>
+      <c r="S12" s="355" t="n"/>
+      <c r="T12" s="355" t="n"/>
+      <c r="U12" s="355" t="n"/>
+      <c r="V12" s="355" t="n"/>
+      <c r="W12" s="355" t="n"/>
+      <c r="X12" s="355" t="n"/>
+      <c r="Y12" s="355" t="n"/>
+      <c r="Z12" s="355" t="n"/>
+      <c r="AA12" s="355" t="n"/>
+      <c r="AB12" s="355" t="n"/>
+      <c r="AC12" s="355" t="n"/>
+      <c r="AD12" s="355" t="n"/>
+      <c r="AE12" s="355" t="n"/>
+      <c r="AF12" s="355" t="n"/>
+      <c r="AG12" s="355" t="n"/>
+      <c r="AH12" s="355" t="n"/>
+      <c r="AI12" s="355" t="n"/>
+      <c r="AJ12" s="355" t="n"/>
+      <c r="AK12" s="355" t="n"/>
+      <c r="AL12" s="355" t="n"/>
+      <c r="AM12" s="355" t="n"/>
+      <c r="AN12" s="503" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="383" t="inlineStr">
+      <c r="A13" s="502" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B13" s="383" t="inlineStr">
+      <c r="B13" s="526" t="inlineStr">
         <is>
           <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
         </is>
       </c>
-      <c r="C13" s="383" t="inlineStr">
+      <c r="C13" s="355" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D13" s="383" t="n"/>
-      <c r="E13" s="383" t="n"/>
-      <c r="F13" s="383" t="n"/>
-      <c r="G13" s="383" t="n"/>
-      <c r="H13" s="383" t="n"/>
-      <c r="I13" s="383" t="n"/>
-      <c r="J13" s="383" t="n"/>
-      <c r="K13" s="383" t="n"/>
-      <c r="L13" s="383" t="n"/>
-      <c r="M13" s="383" t="n"/>
-      <c r="N13" s="383" t="n"/>
-      <c r="O13" s="383" t="n"/>
-      <c r="P13" s="383" t="n"/>
-      <c r="Q13" s="383" t="n"/>
-      <c r="R13" s="383" t="n"/>
-      <c r="S13" s="383" t="n"/>
-      <c r="T13" s="383" t="n"/>
-      <c r="U13" s="383" t="n"/>
-      <c r="V13" s="383" t="n"/>
-      <c r="W13" s="383" t="n"/>
-      <c r="X13" s="383" t="n"/>
-      <c r="Y13" s="383" t="n"/>
-      <c r="Z13" s="383" t="n"/>
-      <c r="AA13" s="383" t="n"/>
-      <c r="AB13" s="383" t="n"/>
-      <c r="AC13" s="383" t="n"/>
-      <c r="AD13" s="383" t="n"/>
-      <c r="AE13" s="383" t="n"/>
-      <c r="AF13" s="383" t="n"/>
-      <c r="AG13" s="383" t="n"/>
-      <c r="AH13" s="383" t="n"/>
-      <c r="AI13" s="383" t="n"/>
-      <c r="AJ13" s="383" t="n"/>
-      <c r="AK13" s="383" t="n"/>
-      <c r="AL13" s="383" t="n"/>
-      <c r="AM13" s="383" t="n"/>
-      <c r="AN13" s="383" t="n"/>
+      <c r="D13" s="355" t="n"/>
+      <c r="E13" s="355" t="n"/>
+      <c r="F13" s="355" t="n"/>
+      <c r="G13" s="355" t="n"/>
+      <c r="H13" s="355" t="n"/>
+      <c r="I13" s="355" t="n"/>
+      <c r="J13" s="355" t="n"/>
+      <c r="K13" s="355" t="n"/>
+      <c r="L13" s="355" t="n"/>
+      <c r="M13" s="355" t="n"/>
+      <c r="N13" s="355" t="n"/>
+      <c r="O13" s="355" t="n"/>
+      <c r="P13" s="355" t="n"/>
+      <c r="Q13" s="355" t="n"/>
+      <c r="R13" s="355" t="n"/>
+      <c r="S13" s="355" t="n"/>
+      <c r="T13" s="355" t="n"/>
+      <c r="U13" s="355" t="n"/>
+      <c r="V13" s="355" t="n"/>
+      <c r="W13" s="355" t="n"/>
+      <c r="X13" s="355" t="n"/>
+      <c r="Y13" s="355" t="n"/>
+      <c r="Z13" s="355" t="n"/>
+      <c r="AA13" s="355" t="n"/>
+      <c r="AB13" s="355" t="n"/>
+      <c r="AC13" s="355" t="n"/>
+      <c r="AD13" s="355" t="n"/>
+      <c r="AE13" s="355" t="n"/>
+      <c r="AF13" s="355" t="n"/>
+      <c r="AG13" s="355" t="n"/>
+      <c r="AH13" s="355" t="n"/>
+      <c r="AI13" s="355" t="n"/>
+      <c r="AJ13" s="355" t="n"/>
+      <c r="AK13" s="355" t="n"/>
+      <c r="AL13" s="355" t="n"/>
+      <c r="AM13" s="355" t="n"/>
+      <c r="AN13" s="503" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="383" t="inlineStr">
+      <c r="A14" s="504" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B14" s="383" t="inlineStr">
+      <c r="B14" s="527" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
         </is>
       </c>
-      <c r="C14" s="383" t="inlineStr">
+      <c r="C14" s="505" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D14" s="383" t="n"/>
-      <c r="E14" s="383" t="n"/>
-      <c r="F14" s="383" t="n"/>
-      <c r="G14" s="383" t="n"/>
-      <c r="H14" s="383" t="n"/>
-      <c r="I14" s="383" t="n"/>
-      <c r="J14" s="383" t="n"/>
-      <c r="K14" s="383" t="n"/>
-      <c r="L14" s="383" t="n"/>
-      <c r="M14" s="383" t="n"/>
-      <c r="N14" s="383" t="n"/>
-      <c r="O14" s="383" t="n"/>
-      <c r="P14" s="383" t="n"/>
-      <c r="Q14" s="383" t="n"/>
-      <c r="R14" s="383" t="n"/>
-      <c r="S14" s="383" t="n"/>
-      <c r="T14" s="383" t="n"/>
-      <c r="U14" s="383" t="n"/>
-      <c r="V14" s="383" t="n"/>
-      <c r="W14" s="383" t="n"/>
-      <c r="X14" s="383" t="n"/>
-      <c r="Y14" s="383" t="n"/>
-      <c r="Z14" s="383" t="n"/>
-      <c r="AA14" s="383" t="n"/>
-      <c r="AB14" s="383" t="n"/>
-      <c r="AC14" s="383" t="n"/>
-      <c r="AD14" s="383" t="n"/>
-      <c r="AE14" s="383" t="n"/>
-      <c r="AF14" s="383" t="n"/>
-      <c r="AG14" s="383" t="n"/>
-      <c r="AH14" s="383" t="n"/>
-      <c r="AI14" s="383" t="n"/>
-      <c r="AJ14" s="383" t="n"/>
-      <c r="AK14" s="383" t="n"/>
-      <c r="AL14" s="383" t="n"/>
-      <c r="AM14" s="383" t="n"/>
-      <c r="AN14" s="383" t="n"/>
+      <c r="D14" s="505" t="n"/>
+      <c r="E14" s="505" t="n"/>
+      <c r="F14" s="505" t="n"/>
+      <c r="G14" s="505" t="n"/>
+      <c r="H14" s="505" t="n"/>
+      <c r="I14" s="505" t="n"/>
+      <c r="J14" s="505" t="n"/>
+      <c r="K14" s="505" t="n"/>
+      <c r="L14" s="505" t="n"/>
+      <c r="M14" s="505" t="n"/>
+      <c r="N14" s="505" t="n"/>
+      <c r="O14" s="505" t="n"/>
+      <c r="P14" s="505" t="n"/>
+      <c r="Q14" s="505" t="n"/>
+      <c r="R14" s="505" t="n"/>
+      <c r="S14" s="505" t="n"/>
+      <c r="T14" s="505" t="n"/>
+      <c r="U14" s="505" t="n"/>
+      <c r="V14" s="505" t="n"/>
+      <c r="W14" s="505" t="n"/>
+      <c r="X14" s="505" t="n"/>
+      <c r="Y14" s="505" t="n"/>
+      <c r="Z14" s="505" t="n"/>
+      <c r="AA14" s="505" t="n"/>
+      <c r="AB14" s="505" t="n"/>
+      <c r="AC14" s="505" t="n"/>
+      <c r="AD14" s="505" t="n"/>
+      <c r="AE14" s="505" t="n"/>
+      <c r="AF14" s="505" t="n"/>
+      <c r="AG14" s="505" t="n"/>
+      <c r="AH14" s="505" t="n"/>
+      <c r="AI14" s="505" t="n"/>
+      <c r="AJ14" s="505" t="n"/>
+      <c r="AK14" s="505" t="n"/>
+      <c r="AL14" s="505" t="n"/>
+      <c r="AM14" s="505" t="n"/>
+      <c r="AN14" s="506" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -9054,6 +9844,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9108,249 +9899,255 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="389" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="507" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="411" t="n"/>
-      <c r="C1" s="411" t="n"/>
-      <c r="D1" s="411" t="n"/>
-      <c r="E1" s="411" t="n"/>
-      <c r="F1" s="411" t="n"/>
-      <c r="G1" s="412" t="n"/>
-      <c r="H1" s="347" t="n"/>
-      <c r="I1" s="347" t="n"/>
-      <c r="J1" s="347" t="n"/>
-      <c r="K1" s="347" t="n"/>
-      <c r="L1" s="347" t="n"/>
-      <c r="M1" s="347" t="n"/>
-      <c r="N1" s="347" t="n"/>
-      <c r="O1" s="347" t="n"/>
-      <c r="P1" s="347" t="n"/>
-      <c r="Q1" s="347" t="n"/>
-      <c r="R1" s="347" t="n"/>
-      <c r="S1" s="347" t="n"/>
-      <c r="T1" s="347" t="n"/>
-      <c r="U1" s="347" t="n"/>
-      <c r="V1" s="347" t="n"/>
-      <c r="W1" s="347" t="n"/>
-      <c r="X1" s="347" t="n"/>
-      <c r="Y1" s="347" t="n"/>
-      <c r="Z1" s="347" t="n"/>
-      <c r="AA1" s="347" t="n"/>
-      <c r="AB1" s="347" t="n"/>
-      <c r="AC1" s="347" t="n"/>
-      <c r="AD1" s="347" t="n"/>
-      <c r="AE1" s="347" t="n"/>
-      <c r="AF1" s="347" t="n"/>
-      <c r="AG1" s="347" t="n"/>
-      <c r="AH1" s="347" t="n"/>
-      <c r="AI1" s="347" t="n"/>
-      <c r="AJ1" s="347" t="n"/>
-      <c r="AK1" s="347" t="n"/>
-      <c r="AL1" s="347" t="n"/>
-      <c r="AM1" s="347" t="n"/>
-      <c r="AN1" s="347" t="n"/>
+      <c r="B1" s="417" t="n"/>
+      <c r="C1" s="417" t="n"/>
+      <c r="D1" s="417" t="n"/>
+      <c r="E1" s="417" t="n"/>
+      <c r="F1" s="417" t="n"/>
+      <c r="G1" s="417" t="n"/>
+      <c r="H1" s="508" t="n"/>
+      <c r="I1" s="419" t="n"/>
+      <c r="J1" s="420" t="n"/>
+      <c r="K1" s="420" t="n"/>
+      <c r="L1" s="420" t="n"/>
+      <c r="M1" s="420" t="n"/>
+      <c r="N1" s="420" t="n"/>
+      <c r="O1" s="420" t="n"/>
+      <c r="P1" s="420" t="n"/>
+      <c r="Q1" s="420" t="n"/>
+      <c r="R1" s="420" t="n"/>
+      <c r="S1" s="420" t="n"/>
+      <c r="T1" s="420" t="n"/>
+      <c r="U1" s="420" t="n"/>
+      <c r="V1" s="420" t="n"/>
+      <c r="W1" s="420" t="n"/>
+      <c r="X1" s="420" t="n"/>
+      <c r="Y1" s="420" t="n"/>
+      <c r="Z1" s="420" t="n"/>
+      <c r="AA1" s="420" t="n"/>
+      <c r="AB1" s="420" t="n"/>
+      <c r="AC1" s="420" t="n"/>
+      <c r="AD1" s="421" t="n"/>
+      <c r="AE1" s="422" t="n"/>
+      <c r="AF1" s="423" t="n"/>
+      <c r="AG1" s="423" t="n"/>
+      <c r="AH1" s="424" t="n"/>
+      <c r="AI1" s="425" t="n"/>
+      <c r="AJ1" s="426" t="n"/>
+      <c r="AK1" s="426" t="n"/>
+      <c r="AL1" s="426" t="n"/>
+      <c r="AM1" s="426" t="n"/>
+      <c r="AN1" s="427" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="338" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="509" t="inlineStr">
         <is>
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="H2" s="347" t="n"/>
-      <c r="I2" s="347" t="n"/>
-      <c r="J2" s="347" t="n"/>
-      <c r="K2" s="347" t="n"/>
-      <c r="L2" s="347" t="n"/>
-      <c r="M2" s="347" t="n"/>
-      <c r="N2" s="347" t="n"/>
-      <c r="O2" s="347" t="n"/>
-      <c r="P2" s="347" t="n"/>
-      <c r="Q2" s="347" t="n"/>
-      <c r="R2" s="347" t="n"/>
-      <c r="S2" s="347" t="n"/>
-      <c r="T2" s="347" t="n"/>
-      <c r="U2" s="347" t="n"/>
-      <c r="V2" s="347" t="n"/>
-      <c r="W2" s="347" t="n"/>
-      <c r="X2" s="347" t="n"/>
-      <c r="Y2" s="347" t="n"/>
-      <c r="Z2" s="347" t="n"/>
-      <c r="AA2" s="347" t="n"/>
-      <c r="AB2" s="347" t="n"/>
-      <c r="AC2" s="347" t="n"/>
-      <c r="AD2" s="347" t="n"/>
-      <c r="AE2" s="347" t="n"/>
-      <c r="AF2" s="347" t="n"/>
-      <c r="AG2" s="347" t="n"/>
-      <c r="AH2" s="347" t="n"/>
-      <c r="AI2" s="347" t="n"/>
-      <c r="AJ2" s="347" t="n"/>
-      <c r="AK2" s="347" t="n"/>
-      <c r="AL2" s="347" t="n"/>
-      <c r="AM2" s="347" t="n"/>
-      <c r="AN2" s="347" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="510" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="431" t="n"/>
+      <c r="K2" s="431" t="n"/>
+      <c r="L2" s="431" t="n"/>
+      <c r="M2" s="431" t="n"/>
+      <c r="N2" s="431" t="n"/>
+      <c r="O2" s="431" t="n"/>
+      <c r="P2" s="431" t="n"/>
+      <c r="Q2" s="431" t="n"/>
+      <c r="R2" s="431" t="n"/>
+      <c r="S2" s="431" t="n"/>
+      <c r="T2" s="431" t="n"/>
+      <c r="U2" s="431" t="n"/>
+      <c r="V2" s="431" t="n"/>
+      <c r="W2" s="431" t="n"/>
+      <c r="X2" s="431" t="n"/>
+      <c r="Y2" s="431" t="n"/>
+      <c r="Z2" s="431" t="n"/>
+      <c r="AA2" s="431" t="n"/>
+      <c r="AB2" s="431" t="n"/>
+      <c r="AC2" s="431" t="n"/>
+      <c r="AD2" s="432" t="n"/>
+      <c r="AE2" s="433" t="n"/>
+      <c r="AF2" s="434" t="n"/>
+      <c r="AG2" s="434" t="n"/>
+      <c r="AH2" s="435" t="n"/>
+      <c r="AI2" s="436" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="438" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="347" t="n"/>
-      <c r="B3" s="347" t="n"/>
-      <c r="C3" s="347" t="n"/>
-      <c r="D3" s="347" t="n"/>
-      <c r="E3" s="347" t="n"/>
-      <c r="F3" s="347" t="n"/>
-      <c r="G3" s="347" t="n"/>
-      <c r="H3" s="347" t="n"/>
-      <c r="I3" s="347" t="n"/>
-      <c r="J3" s="347" t="n"/>
-      <c r="K3" s="347" t="n"/>
-      <c r="L3" s="347" t="n"/>
-      <c r="M3" s="347" t="n"/>
-      <c r="N3" s="347" t="n"/>
-      <c r="O3" s="347" t="n"/>
-      <c r="P3" s="347" t="n"/>
-      <c r="Q3" s="347" t="n"/>
-      <c r="R3" s="347" t="n"/>
-      <c r="S3" s="347" t="n"/>
-      <c r="T3" s="347" t="n"/>
-      <c r="U3" s="347" t="n"/>
-      <c r="V3" s="347" t="n"/>
-      <c r="W3" s="347" t="n"/>
-      <c r="X3" s="347" t="n"/>
-      <c r="Y3" s="347" t="n"/>
-      <c r="Z3" s="347" t="n"/>
-      <c r="AA3" s="347" t="n"/>
-      <c r="AB3" s="347" t="n"/>
-      <c r="AC3" s="347" t="n"/>
-      <c r="AD3" s="347" t="n"/>
-      <c r="AE3" s="347" t="n"/>
-      <c r="AF3" s="347" t="n"/>
-      <c r="AG3" s="347" t="n"/>
-      <c r="AH3" s="347" t="n"/>
-      <c r="AI3" s="347" t="n"/>
-      <c r="AJ3" s="347" t="n"/>
-      <c r="AK3" s="347" t="n"/>
-      <c r="AL3" s="347" t="n"/>
-      <c r="AM3" s="347" t="n"/>
-      <c r="AN3" s="347" t="n"/>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="511" t="n"/>
+      <c r="B3" s="512" t="n"/>
+      <c r="C3" s="512" t="n"/>
+      <c r="D3" s="512" t="n"/>
+      <c r="E3" s="512" t="n"/>
+      <c r="F3" s="512" t="n"/>
+      <c r="G3" s="512" t="n"/>
+      <c r="H3" s="510" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="431" t="n"/>
+      <c r="K3" s="431" t="n"/>
+      <c r="L3" s="431" t="n"/>
+      <c r="M3" s="431" t="n"/>
+      <c r="N3" s="431" t="n"/>
+      <c r="O3" s="431" t="n"/>
+      <c r="P3" s="431" t="n"/>
+      <c r="Q3" s="431" t="n"/>
+      <c r="R3" s="431" t="n"/>
+      <c r="S3" s="431" t="n"/>
+      <c r="T3" s="431" t="n"/>
+      <c r="U3" s="431" t="n"/>
+      <c r="V3" s="431" t="n"/>
+      <c r="W3" s="431" t="n"/>
+      <c r="X3" s="431" t="n"/>
+      <c r="Y3" s="431" t="n"/>
+      <c r="Z3" s="431" t="n"/>
+      <c r="AA3" s="431" t="n"/>
+      <c r="AB3" s="431" t="n"/>
+      <c r="AC3" s="431" t="n"/>
+      <c r="AD3" s="432" t="n"/>
+      <c r="AE3" s="433" t="n"/>
+      <c r="AF3" s="434" t="n"/>
+      <c r="AG3" s="434" t="n"/>
+      <c r="AH3" s="435" t="n"/>
+      <c r="AI3" s="436" t="n"/>
+      <c r="AJ3" s="437" t="n"/>
+      <c r="AK3" s="437" t="n"/>
+      <c r="AL3" s="437" t="n"/>
+      <c r="AM3" s="437" t="n"/>
+      <c r="AN3" s="438" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="388" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="513" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="388" t="inlineStr">
+      <c r="B4" s="514" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="388" t="inlineStr">
+      <c r="C4" s="514" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="347" t="n"/>
-      <c r="E4" s="347" t="n"/>
-      <c r="F4" s="347" t="n"/>
-      <c r="G4" s="347" t="n"/>
-      <c r="H4" s="347" t="n"/>
-      <c r="I4" s="347" t="n"/>
-      <c r="J4" s="347" t="n"/>
-      <c r="K4" s="347" t="n"/>
-      <c r="L4" s="347" t="n"/>
-      <c r="M4" s="347" t="n"/>
-      <c r="N4" s="347" t="n"/>
-      <c r="O4" s="347" t="n"/>
-      <c r="P4" s="347" t="n"/>
-      <c r="Q4" s="347" t="n"/>
-      <c r="R4" s="347" t="n"/>
-      <c r="S4" s="347" t="n"/>
-      <c r="T4" s="347" t="n"/>
-      <c r="U4" s="347" t="n"/>
-      <c r="V4" s="347" t="n"/>
-      <c r="W4" s="347" t="n"/>
-      <c r="X4" s="347" t="n"/>
-      <c r="Y4" s="347" t="n"/>
-      <c r="Z4" s="347" t="n"/>
-      <c r="AA4" s="347" t="n"/>
-      <c r="AB4" s="347" t="n"/>
-      <c r="AC4" s="347" t="n"/>
-      <c r="AD4" s="347" t="n"/>
-      <c r="AE4" s="347" t="n"/>
-      <c r="AF4" s="347" t="n"/>
-      <c r="AG4" s="347" t="n"/>
-      <c r="AH4" s="347" t="n"/>
-      <c r="AI4" s="347" t="n"/>
-      <c r="AJ4" s="347" t="n"/>
-      <c r="AK4" s="347" t="n"/>
-      <c r="AL4" s="347" t="n"/>
-      <c r="AM4" s="347" t="n"/>
-      <c r="AN4" s="347" t="n"/>
+      <c r="D4" s="512" t="n"/>
+      <c r="E4" s="512" t="n"/>
+      <c r="F4" s="512" t="n"/>
+      <c r="G4" s="512" t="n"/>
+      <c r="H4" s="510" t="n"/>
+      <c r="I4" s="439" t="n"/>
+      <c r="J4" s="440" t="n"/>
+      <c r="K4" s="440" t="n"/>
+      <c r="L4" s="440" t="n"/>
+      <c r="M4" s="440" t="n"/>
+      <c r="N4" s="440" t="n"/>
+      <c r="O4" s="440" t="n"/>
+      <c r="P4" s="440" t="n"/>
+      <c r="Q4" s="440" t="n"/>
+      <c r="R4" s="440" t="n"/>
+      <c r="S4" s="440" t="n"/>
+      <c r="T4" s="440" t="n"/>
+      <c r="U4" s="440" t="n"/>
+      <c r="V4" s="440" t="n"/>
+      <c r="W4" s="440" t="n"/>
+      <c r="X4" s="440" t="n"/>
+      <c r="Y4" s="440" t="n"/>
+      <c r="Z4" s="440" t="n"/>
+      <c r="AA4" s="440" t="n"/>
+      <c r="AB4" s="440" t="n"/>
+      <c r="AC4" s="440" t="n"/>
+      <c r="AD4" s="441" t="n"/>
+      <c r="AE4" s="433" t="n"/>
+      <c r="AF4" s="434" t="n"/>
+      <c r="AG4" s="434" t="n"/>
+      <c r="AH4" s="435" t="n"/>
+      <c r="AI4" s="436" t="n"/>
+      <c r="AJ4" s="437" t="n"/>
+      <c r="AK4" s="437" t="n"/>
+      <c r="AL4" s="437" t="n"/>
+      <c r="AM4" s="437" t="n"/>
+      <c r="AN4" s="438" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="390" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="515" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="391" t="inlineStr">
+      <c r="B5" s="516" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="391" t="inlineStr">
+      <c r="C5" s="516" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="347" t="n"/>
-      <c r="E5" s="347" t="n"/>
-      <c r="F5" s="347" t="n"/>
-      <c r="G5" s="347" t="n"/>
-      <c r="H5" s="347" t="n"/>
-      <c r="I5" s="347" t="n"/>
-      <c r="J5" s="347" t="n"/>
-      <c r="K5" s="347" t="n"/>
-      <c r="L5" s="347" t="n"/>
-      <c r="M5" s="347" t="n"/>
-      <c r="N5" s="347" t="n"/>
-      <c r="O5" s="347" t="n"/>
-      <c r="P5" s="347" t="n"/>
-      <c r="Q5" s="347" t="n"/>
-      <c r="R5" s="347" t="n"/>
-      <c r="S5" s="347" t="n"/>
-      <c r="T5" s="347" t="n"/>
-      <c r="U5" s="347" t="n"/>
-      <c r="V5" s="347" t="n"/>
-      <c r="W5" s="347" t="n"/>
-      <c r="X5" s="347" t="n"/>
-      <c r="Y5" s="347" t="n"/>
-      <c r="Z5" s="347" t="n"/>
-      <c r="AA5" s="347" t="n"/>
-      <c r="AB5" s="347" t="n"/>
-      <c r="AC5" s="347" t="n"/>
-      <c r="AD5" s="347" t="n"/>
-      <c r="AE5" s="347" t="n"/>
-      <c r="AF5" s="347" t="n"/>
-      <c r="AG5" s="347" t="n"/>
-      <c r="AH5" s="347" t="n"/>
-      <c r="AI5" s="347" t="n"/>
-      <c r="AJ5" s="347" t="n"/>
-      <c r="AK5" s="347" t="n"/>
-      <c r="AL5" s="347" t="n"/>
-      <c r="AM5" s="347" t="n"/>
-      <c r="AN5" s="347" t="n"/>
+      <c r="D5" s="517" t="n"/>
+      <c r="E5" s="517" t="n"/>
+      <c r="F5" s="517" t="n"/>
+      <c r="G5" s="517" t="n"/>
+      <c r="H5" s="518" t="n"/>
+      <c r="I5" s="445" t="n"/>
+      <c r="J5" s="446" t="n"/>
+      <c r="K5" s="446" t="n"/>
+      <c r="L5" s="446" t="n"/>
+      <c r="M5" s="446" t="n"/>
+      <c r="N5" s="446" t="n"/>
+      <c r="O5" s="446" t="n"/>
+      <c r="P5" s="446" t="n"/>
+      <c r="Q5" s="446" t="n"/>
+      <c r="R5" s="446" t="n"/>
+      <c r="S5" s="446" t="n"/>
+      <c r="T5" s="446" t="n"/>
+      <c r="U5" s="446" t="n"/>
+      <c r="V5" s="446" t="n"/>
+      <c r="W5" s="446" t="n"/>
+      <c r="X5" s="446" t="n"/>
+      <c r="Y5" s="446" t="n"/>
+      <c r="Z5" s="446" t="n"/>
+      <c r="AA5" s="446" t="n"/>
+      <c r="AB5" s="446" t="n"/>
+      <c r="AC5" s="446" t="n"/>
+      <c r="AD5" s="447" t="n"/>
+      <c r="AE5" s="448" t="n"/>
+      <c r="AF5" s="449" t="n"/>
+      <c r="AG5" s="449" t="n"/>
+      <c r="AH5" s="450" t="n"/>
+      <c r="AI5" s="451" t="n"/>
+      <c r="AJ5" s="452" t="n"/>
+      <c r="AK5" s="452" t="n"/>
+      <c r="AL5" s="452" t="n"/>
+      <c r="AM5" s="452" t="n"/>
+      <c r="AN5" s="453" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="390" t="inlineStr">
+      <c r="A6" s="519" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="391" t="inlineStr">
+      <c r="B6" s="520" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -9358,7 +10155,7 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="391" t="inlineStr">
+      <c r="C6" s="521" t="inlineStr">
         <is>
           <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
@@ -9366,475 +10163,475 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="347" t="n"/>
-      <c r="E6" s="347" t="n"/>
-      <c r="F6" s="347" t="n"/>
-      <c r="G6" s="347" t="n"/>
-      <c r="H6" s="347" t="n"/>
-      <c r="I6" s="347" t="n"/>
-      <c r="J6" s="347" t="n"/>
-      <c r="K6" s="347" t="n"/>
-      <c r="L6" s="347" t="n"/>
-      <c r="M6" s="347" t="n"/>
-      <c r="N6" s="347" t="n"/>
-      <c r="O6" s="347" t="n"/>
-      <c r="P6" s="347" t="n"/>
-      <c r="Q6" s="347" t="n"/>
-      <c r="R6" s="347" t="n"/>
-      <c r="S6" s="347" t="n"/>
-      <c r="T6" s="347" t="n"/>
-      <c r="U6" s="347" t="n"/>
-      <c r="V6" s="347" t="n"/>
-      <c r="W6" s="347" t="n"/>
-      <c r="X6" s="347" t="n"/>
-      <c r="Y6" s="347" t="n"/>
-      <c r="Z6" s="347" t="n"/>
-      <c r="AA6" s="347" t="n"/>
-      <c r="AB6" s="347" t="n"/>
-      <c r="AC6" s="347" t="n"/>
-      <c r="AD6" s="347" t="n"/>
-      <c r="AE6" s="347" t="n"/>
-      <c r="AF6" s="347" t="n"/>
-      <c r="AG6" s="347" t="n"/>
-      <c r="AH6" s="347" t="n"/>
-      <c r="AI6" s="347" t="n"/>
-      <c r="AJ6" s="347" t="n"/>
-      <c r="AK6" s="347" t="n"/>
-      <c r="AL6" s="347" t="n"/>
-      <c r="AM6" s="347" t="n"/>
-      <c r="AN6" s="347" t="n"/>
+      <c r="D6" s="459" t="n"/>
+      <c r="E6" s="459" t="n"/>
+      <c r="F6" s="459" t="n"/>
+      <c r="G6" s="459" t="n"/>
+      <c r="H6" s="459" t="n"/>
+      <c r="I6" s="459" t="n"/>
+      <c r="J6" s="459" t="n"/>
+      <c r="K6" s="459" t="n"/>
+      <c r="L6" s="459" t="n"/>
+      <c r="M6" s="459" t="n"/>
+      <c r="N6" s="459" t="n"/>
+      <c r="O6" s="459" t="n"/>
+      <c r="P6" s="459" t="n"/>
+      <c r="Q6" s="459" t="n"/>
+      <c r="R6" s="459" t="n"/>
+      <c r="S6" s="459" t="n"/>
+      <c r="T6" s="459" t="n"/>
+      <c r="U6" s="459" t="n"/>
+      <c r="V6" s="459" t="n"/>
+      <c r="W6" s="459" t="n"/>
+      <c r="X6" s="459" t="n"/>
+      <c r="Y6" s="459" t="n"/>
+      <c r="Z6" s="459" t="n"/>
+      <c r="AA6" s="459" t="n"/>
+      <c r="AB6" s="459" t="n"/>
+      <c r="AC6" s="459" t="n"/>
+      <c r="AD6" s="459" t="n"/>
+      <c r="AE6" s="459" t="n"/>
+      <c r="AF6" s="459" t="n"/>
+      <c r="AG6" s="459" t="n"/>
+      <c r="AH6" s="459" t="n"/>
+      <c r="AI6" s="459" t="n"/>
+      <c r="AJ6" s="459" t="n"/>
+      <c r="AK6" s="459" t="n"/>
+      <c r="AL6" s="459" t="n"/>
+      <c r="AM6" s="459" t="n"/>
+      <c r="AN6" s="462" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="390" t="inlineStr">
+      <c r="A7" s="522" t="inlineStr">
         <is>
           <t>SOP-401</t>
         </is>
       </c>
-      <c r="B7" s="391" t="inlineStr">
+      <c r="B7" s="523" t="inlineStr">
         <is>
           <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="391" t="inlineStr">
+      <c r="C7" s="524" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
         </is>
       </c>
-      <c r="D7" s="347" t="n"/>
-      <c r="E7" s="347" t="n"/>
-      <c r="F7" s="347" t="n"/>
-      <c r="G7" s="347" t="n"/>
-      <c r="H7" s="347" t="n"/>
-      <c r="I7" s="347" t="n"/>
-      <c r="J7" s="347" t="n"/>
-      <c r="K7" s="347" t="n"/>
-      <c r="L7" s="347" t="n"/>
-      <c r="M7" s="347" t="n"/>
-      <c r="N7" s="347" t="n"/>
-      <c r="O7" s="347" t="n"/>
-      <c r="P7" s="347" t="n"/>
-      <c r="Q7" s="347" t="n"/>
-      <c r="R7" s="347" t="n"/>
-      <c r="S7" s="347" t="n"/>
-      <c r="T7" s="347" t="n"/>
-      <c r="U7" s="347" t="n"/>
-      <c r="V7" s="347" t="n"/>
-      <c r="W7" s="347" t="n"/>
-      <c r="X7" s="347" t="n"/>
-      <c r="Y7" s="347" t="n"/>
-      <c r="Z7" s="347" t="n"/>
-      <c r="AA7" s="347" t="n"/>
-      <c r="AB7" s="347" t="n"/>
-      <c r="AC7" s="347" t="n"/>
-      <c r="AD7" s="347" t="n"/>
-      <c r="AE7" s="347" t="n"/>
-      <c r="AF7" s="347" t="n"/>
-      <c r="AG7" s="347" t="n"/>
-      <c r="AH7" s="347" t="n"/>
-      <c r="AI7" s="347" t="n"/>
-      <c r="AJ7" s="347" t="n"/>
-      <c r="AK7" s="347" t="n"/>
-      <c r="AL7" s="347" t="n"/>
-      <c r="AM7" s="347" t="n"/>
-      <c r="AN7" s="347" t="n"/>
+      <c r="D7" s="343" t="n"/>
+      <c r="E7" s="343" t="n"/>
+      <c r="F7" s="343" t="n"/>
+      <c r="G7" s="343" t="n"/>
+      <c r="H7" s="343" t="n"/>
+      <c r="I7" s="343" t="n"/>
+      <c r="J7" s="343" t="n"/>
+      <c r="K7" s="343" t="n"/>
+      <c r="L7" s="343" t="n"/>
+      <c r="M7" s="343" t="n"/>
+      <c r="N7" s="343" t="n"/>
+      <c r="O7" s="343" t="n"/>
+      <c r="P7" s="343" t="n"/>
+      <c r="Q7" s="343" t="n"/>
+      <c r="R7" s="343" t="n"/>
+      <c r="S7" s="343" t="n"/>
+      <c r="T7" s="343" t="n"/>
+      <c r="U7" s="343" t="n"/>
+      <c r="V7" s="343" t="n"/>
+      <c r="W7" s="343" t="n"/>
+      <c r="X7" s="343" t="n"/>
+      <c r="Y7" s="343" t="n"/>
+      <c r="Z7" s="343" t="n"/>
+      <c r="AA7" s="343" t="n"/>
+      <c r="AB7" s="343" t="n"/>
+      <c r="AC7" s="343" t="n"/>
+      <c r="AD7" s="343" t="n"/>
+      <c r="AE7" s="343" t="n"/>
+      <c r="AF7" s="343" t="n"/>
+      <c r="AG7" s="343" t="n"/>
+      <c r="AH7" s="343" t="n"/>
+      <c r="AI7" s="343" t="n"/>
+      <c r="AJ7" s="343" t="n"/>
+      <c r="AK7" s="343" t="n"/>
+      <c r="AL7" s="343" t="n"/>
+      <c r="AM7" s="343" t="n"/>
+      <c r="AN7" s="466" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="354" t="inlineStr">
+      <c r="A8" s="463" t="inlineStr">
         <is>
           <t>WI-206</t>
         </is>
       </c>
-      <c r="B8" s="392" t="inlineStr">
+      <c r="B8" s="464" t="inlineStr">
         <is>
           <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
         </is>
       </c>
-      <c r="C8" s="392" t="inlineStr">
+      <c r="C8" s="525" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
         </is>
       </c>
-      <c r="D8" s="383" t="n"/>
-      <c r="E8" s="383" t="n"/>
-      <c r="F8" s="383" t="n"/>
-      <c r="G8" s="383" t="n"/>
-      <c r="H8" s="383" t="n"/>
-      <c r="I8" s="383" t="n"/>
-      <c r="J8" s="383" t="n"/>
-      <c r="K8" s="383" t="n"/>
-      <c r="L8" s="383" t="n"/>
-      <c r="M8" s="383" t="n"/>
-      <c r="N8" s="383" t="n"/>
-      <c r="O8" s="383" t="n"/>
-      <c r="P8" s="383" t="n"/>
-      <c r="Q8" s="383" t="n"/>
-      <c r="R8" s="383" t="n"/>
-      <c r="S8" s="383" t="n"/>
-      <c r="T8" s="383" t="n"/>
-      <c r="U8" s="383" t="n"/>
-      <c r="V8" s="383" t="n"/>
-      <c r="W8" s="383" t="n"/>
-      <c r="X8" s="383" t="n"/>
-      <c r="Y8" s="383" t="n"/>
-      <c r="Z8" s="383" t="n"/>
-      <c r="AA8" s="383" t="n"/>
-      <c r="AB8" s="383" t="n"/>
-      <c r="AC8" s="383" t="n"/>
-      <c r="AD8" s="383" t="n"/>
-      <c r="AE8" s="383" t="n"/>
-      <c r="AF8" s="383" t="n"/>
-      <c r="AG8" s="383" t="n"/>
-      <c r="AH8" s="383" t="n"/>
-      <c r="AI8" s="383" t="n"/>
-      <c r="AJ8" s="383" t="n"/>
-      <c r="AK8" s="383" t="n"/>
-      <c r="AL8" s="383" t="n"/>
-      <c r="AM8" s="383" t="n"/>
-      <c r="AN8" s="383" t="n"/>
+      <c r="D8" s="355" t="n"/>
+      <c r="E8" s="355" t="n"/>
+      <c r="F8" s="355" t="n"/>
+      <c r="G8" s="355" t="n"/>
+      <c r="H8" s="355" t="n"/>
+      <c r="I8" s="355" t="n"/>
+      <c r="J8" s="355" t="n"/>
+      <c r="K8" s="355" t="n"/>
+      <c r="L8" s="355" t="n"/>
+      <c r="M8" s="355" t="n"/>
+      <c r="N8" s="355" t="n"/>
+      <c r="O8" s="355" t="n"/>
+      <c r="P8" s="355" t="n"/>
+      <c r="Q8" s="355" t="n"/>
+      <c r="R8" s="355" t="n"/>
+      <c r="S8" s="355" t="n"/>
+      <c r="T8" s="355" t="n"/>
+      <c r="U8" s="355" t="n"/>
+      <c r="V8" s="355" t="n"/>
+      <c r="W8" s="355" t="n"/>
+      <c r="X8" s="355" t="n"/>
+      <c r="Y8" s="355" t="n"/>
+      <c r="Z8" s="355" t="n"/>
+      <c r="AA8" s="355" t="n"/>
+      <c r="AB8" s="355" t="n"/>
+      <c r="AC8" s="355" t="n"/>
+      <c r="AD8" s="355" t="n"/>
+      <c r="AE8" s="355" t="n"/>
+      <c r="AF8" s="355" t="n"/>
+      <c r="AG8" s="355" t="n"/>
+      <c r="AH8" s="355" t="n"/>
+      <c r="AI8" s="355" t="n"/>
+      <c r="AJ8" s="355" t="n"/>
+      <c r="AK8" s="355" t="n"/>
+      <c r="AL8" s="355" t="n"/>
+      <c r="AM8" s="355" t="n"/>
+      <c r="AN8" s="503" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="383" t="inlineStr">
+      <c r="A9" s="502" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B9" s="383" t="inlineStr">
+      <c r="B9" s="526" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C9" s="383" t="inlineStr">
+      <c r="C9" s="355" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
-      <c r="D9" s="383" t="n"/>
-      <c r="E9" s="383" t="n"/>
-      <c r="F9" s="383" t="n"/>
-      <c r="G9" s="383" t="n"/>
-      <c r="H9" s="383" t="n"/>
-      <c r="I9" s="383" t="n"/>
-      <c r="J9" s="383" t="n"/>
-      <c r="K9" s="383" t="n"/>
-      <c r="L9" s="383" t="n"/>
-      <c r="M9" s="383" t="n"/>
-      <c r="N9" s="383" t="n"/>
-      <c r="O9" s="383" t="n"/>
-      <c r="P9" s="383" t="n"/>
-      <c r="Q9" s="383" t="n"/>
-      <c r="R9" s="383" t="n"/>
-      <c r="S9" s="383" t="n"/>
-      <c r="T9" s="383" t="n"/>
-      <c r="U9" s="383" t="n"/>
-      <c r="V9" s="383" t="n"/>
-      <c r="W9" s="383" t="n"/>
-      <c r="X9" s="383" t="n"/>
-      <c r="Y9" s="383" t="n"/>
-      <c r="Z9" s="383" t="n"/>
-      <c r="AA9" s="383" t="n"/>
-      <c r="AB9" s="383" t="n"/>
-      <c r="AC9" s="383" t="n"/>
-      <c r="AD9" s="383" t="n"/>
-      <c r="AE9" s="383" t="n"/>
-      <c r="AF9" s="383" t="n"/>
-      <c r="AG9" s="383" t="n"/>
-      <c r="AH9" s="383" t="n"/>
-      <c r="AI9" s="383" t="n"/>
-      <c r="AJ9" s="383" t="n"/>
-      <c r="AK9" s="383" t="n"/>
-      <c r="AL9" s="383" t="n"/>
-      <c r="AM9" s="383" t="n"/>
-      <c r="AN9" s="383" t="n"/>
+      <c r="D9" s="355" t="n"/>
+      <c r="E9" s="355" t="n"/>
+      <c r="F9" s="355" t="n"/>
+      <c r="G9" s="355" t="n"/>
+      <c r="H9" s="355" t="n"/>
+      <c r="I9" s="355" t="n"/>
+      <c r="J9" s="355" t="n"/>
+      <c r="K9" s="355" t="n"/>
+      <c r="L9" s="355" t="n"/>
+      <c r="M9" s="355" t="n"/>
+      <c r="N9" s="355" t="n"/>
+      <c r="O9" s="355" t="n"/>
+      <c r="P9" s="355" t="n"/>
+      <c r="Q9" s="355" t="n"/>
+      <c r="R9" s="355" t="n"/>
+      <c r="S9" s="355" t="n"/>
+      <c r="T9" s="355" t="n"/>
+      <c r="U9" s="355" t="n"/>
+      <c r="V9" s="355" t="n"/>
+      <c r="W9" s="355" t="n"/>
+      <c r="X9" s="355" t="n"/>
+      <c r="Y9" s="355" t="n"/>
+      <c r="Z9" s="355" t="n"/>
+      <c r="AA9" s="355" t="n"/>
+      <c r="AB9" s="355" t="n"/>
+      <c r="AC9" s="355" t="n"/>
+      <c r="AD9" s="355" t="n"/>
+      <c r="AE9" s="355" t="n"/>
+      <c r="AF9" s="355" t="n"/>
+      <c r="AG9" s="355" t="n"/>
+      <c r="AH9" s="355" t="n"/>
+      <c r="AI9" s="355" t="n"/>
+      <c r="AJ9" s="355" t="n"/>
+      <c r="AK9" s="355" t="n"/>
+      <c r="AL9" s="355" t="n"/>
+      <c r="AM9" s="355" t="n"/>
+      <c r="AN9" s="503" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="383" t="inlineStr">
+      <c r="A10" s="502" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B10" s="383" t="inlineStr">
+      <c r="B10" s="526" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C10" s="383" t="inlineStr">
+      <c r="C10" s="355" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
-      <c r="D10" s="383" t="n"/>
-      <c r="E10" s="383" t="n"/>
-      <c r="F10" s="383" t="n"/>
-      <c r="G10" s="383" t="n"/>
-      <c r="H10" s="383" t="n"/>
-      <c r="I10" s="383" t="n"/>
-      <c r="J10" s="383" t="n"/>
-      <c r="K10" s="383" t="n"/>
-      <c r="L10" s="383" t="n"/>
-      <c r="M10" s="383" t="n"/>
-      <c r="N10" s="383" t="n"/>
-      <c r="O10" s="383" t="n"/>
-      <c r="P10" s="383" t="n"/>
-      <c r="Q10" s="383" t="n"/>
-      <c r="R10" s="383" t="n"/>
-      <c r="S10" s="383" t="n"/>
-      <c r="T10" s="383" t="n"/>
-      <c r="U10" s="383" t="n"/>
-      <c r="V10" s="383" t="n"/>
-      <c r="W10" s="383" t="n"/>
-      <c r="X10" s="383" t="n"/>
-      <c r="Y10" s="383" t="n"/>
-      <c r="Z10" s="383" t="n"/>
-      <c r="AA10" s="383" t="n"/>
-      <c r="AB10" s="383" t="n"/>
-      <c r="AC10" s="383" t="n"/>
-      <c r="AD10" s="383" t="n"/>
-      <c r="AE10" s="383" t="n"/>
-      <c r="AF10" s="383" t="n"/>
-      <c r="AG10" s="383" t="n"/>
-      <c r="AH10" s="383" t="n"/>
-      <c r="AI10" s="383" t="n"/>
-      <c r="AJ10" s="383" t="n"/>
-      <c r="AK10" s="383" t="n"/>
-      <c r="AL10" s="383" t="n"/>
-      <c r="AM10" s="383" t="n"/>
-      <c r="AN10" s="383" t="n"/>
+      <c r="D10" s="355" t="n"/>
+      <c r="E10" s="355" t="n"/>
+      <c r="F10" s="355" t="n"/>
+      <c r="G10" s="355" t="n"/>
+      <c r="H10" s="355" t="n"/>
+      <c r="I10" s="355" t="n"/>
+      <c r="J10" s="355" t="n"/>
+      <c r="K10" s="355" t="n"/>
+      <c r="L10" s="355" t="n"/>
+      <c r="M10" s="355" t="n"/>
+      <c r="N10" s="355" t="n"/>
+      <c r="O10" s="355" t="n"/>
+      <c r="P10" s="355" t="n"/>
+      <c r="Q10" s="355" t="n"/>
+      <c r="R10" s="355" t="n"/>
+      <c r="S10" s="355" t="n"/>
+      <c r="T10" s="355" t="n"/>
+      <c r="U10" s="355" t="n"/>
+      <c r="V10" s="355" t="n"/>
+      <c r="W10" s="355" t="n"/>
+      <c r="X10" s="355" t="n"/>
+      <c r="Y10" s="355" t="n"/>
+      <c r="Z10" s="355" t="n"/>
+      <c r="AA10" s="355" t="n"/>
+      <c r="AB10" s="355" t="n"/>
+      <c r="AC10" s="355" t="n"/>
+      <c r="AD10" s="355" t="n"/>
+      <c r="AE10" s="355" t="n"/>
+      <c r="AF10" s="355" t="n"/>
+      <c r="AG10" s="355" t="n"/>
+      <c r="AH10" s="355" t="n"/>
+      <c r="AI10" s="355" t="n"/>
+      <c r="AJ10" s="355" t="n"/>
+      <c r="AK10" s="355" t="n"/>
+      <c r="AL10" s="355" t="n"/>
+      <c r="AM10" s="355" t="n"/>
+      <c r="AN10" s="503" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="383" t="inlineStr">
+      <c r="A11" s="502" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B11" s="383" t="inlineStr">
+      <c r="B11" s="526" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C11" s="383" t="inlineStr">
+      <c r="C11" s="355" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
-      <c r="D11" s="383" t="n"/>
-      <c r="E11" s="383" t="n"/>
-      <c r="F11" s="383" t="n"/>
-      <c r="G11" s="383" t="n"/>
-      <c r="H11" s="383" t="n"/>
-      <c r="I11" s="383" t="n"/>
-      <c r="J11" s="383" t="n"/>
-      <c r="K11" s="383" t="n"/>
-      <c r="L11" s="383" t="n"/>
-      <c r="M11" s="383" t="n"/>
-      <c r="N11" s="383" t="n"/>
-      <c r="O11" s="383" t="n"/>
-      <c r="P11" s="383" t="n"/>
-      <c r="Q11" s="383" t="n"/>
-      <c r="R11" s="383" t="n"/>
-      <c r="S11" s="383" t="n"/>
-      <c r="T11" s="383" t="n"/>
-      <c r="U11" s="383" t="n"/>
-      <c r="V11" s="383" t="n"/>
-      <c r="W11" s="383" t="n"/>
-      <c r="X11" s="383" t="n"/>
-      <c r="Y11" s="383" t="n"/>
-      <c r="Z11" s="383" t="n"/>
-      <c r="AA11" s="383" t="n"/>
-      <c r="AB11" s="383" t="n"/>
-      <c r="AC11" s="383" t="n"/>
-      <c r="AD11" s="383" t="n"/>
-      <c r="AE11" s="383" t="n"/>
-      <c r="AF11" s="383" t="n"/>
-      <c r="AG11" s="383" t="n"/>
-      <c r="AH11" s="383" t="n"/>
-      <c r="AI11" s="383" t="n"/>
-      <c r="AJ11" s="383" t="n"/>
-      <c r="AK11" s="383" t="n"/>
-      <c r="AL11" s="383" t="n"/>
-      <c r="AM11" s="383" t="n"/>
-      <c r="AN11" s="383" t="n"/>
+      <c r="D11" s="355" t="n"/>
+      <c r="E11" s="355" t="n"/>
+      <c r="F11" s="355" t="n"/>
+      <c r="G11" s="355" t="n"/>
+      <c r="H11" s="355" t="n"/>
+      <c r="I11" s="355" t="n"/>
+      <c r="J11" s="355" t="n"/>
+      <c r="K11" s="355" t="n"/>
+      <c r="L11" s="355" t="n"/>
+      <c r="M11" s="355" t="n"/>
+      <c r="N11" s="355" t="n"/>
+      <c r="O11" s="355" t="n"/>
+      <c r="P11" s="355" t="n"/>
+      <c r="Q11" s="355" t="n"/>
+      <c r="R11" s="355" t="n"/>
+      <c r="S11" s="355" t="n"/>
+      <c r="T11" s="355" t="n"/>
+      <c r="U11" s="355" t="n"/>
+      <c r="V11" s="355" t="n"/>
+      <c r="W11" s="355" t="n"/>
+      <c r="X11" s="355" t="n"/>
+      <c r="Y11" s="355" t="n"/>
+      <c r="Z11" s="355" t="n"/>
+      <c r="AA11" s="355" t="n"/>
+      <c r="AB11" s="355" t="n"/>
+      <c r="AC11" s="355" t="n"/>
+      <c r="AD11" s="355" t="n"/>
+      <c r="AE11" s="355" t="n"/>
+      <c r="AF11" s="355" t="n"/>
+      <c r="AG11" s="355" t="n"/>
+      <c r="AH11" s="355" t="n"/>
+      <c r="AI11" s="355" t="n"/>
+      <c r="AJ11" s="355" t="n"/>
+      <c r="AK11" s="355" t="n"/>
+      <c r="AL11" s="355" t="n"/>
+      <c r="AM11" s="355" t="n"/>
+      <c r="AN11" s="503" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="383" t="inlineStr">
+      <c r="A12" s="502" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B12" s="383" t="inlineStr">
+      <c r="B12" s="526" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C12" s="383" t="inlineStr">
+      <c r="C12" s="355" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
-      <c r="D12" s="383" t="n"/>
-      <c r="E12" s="383" t="n"/>
-      <c r="F12" s="383" t="n"/>
-      <c r="G12" s="383" t="n"/>
-      <c r="H12" s="383" t="n"/>
-      <c r="I12" s="383" t="n"/>
-      <c r="J12" s="383" t="n"/>
-      <c r="K12" s="383" t="n"/>
-      <c r="L12" s="383" t="n"/>
-      <c r="M12" s="383" t="n"/>
-      <c r="N12" s="383" t="n"/>
-      <c r="O12" s="383" t="n"/>
-      <c r="P12" s="383" t="n"/>
-      <c r="Q12" s="383" t="n"/>
-      <c r="R12" s="383" t="n"/>
-      <c r="S12" s="383" t="n"/>
-      <c r="T12" s="383" t="n"/>
-      <c r="U12" s="383" t="n"/>
-      <c r="V12" s="383" t="n"/>
-      <c r="W12" s="383" t="n"/>
-      <c r="X12" s="383" t="n"/>
-      <c r="Y12" s="383" t="n"/>
-      <c r="Z12" s="383" t="n"/>
-      <c r="AA12" s="383" t="n"/>
-      <c r="AB12" s="383" t="n"/>
-      <c r="AC12" s="383" t="n"/>
-      <c r="AD12" s="383" t="n"/>
-      <c r="AE12" s="383" t="n"/>
-      <c r="AF12" s="383" t="n"/>
-      <c r="AG12" s="383" t="n"/>
-      <c r="AH12" s="383" t="n"/>
-      <c r="AI12" s="383" t="n"/>
-      <c r="AJ12" s="383" t="n"/>
-      <c r="AK12" s="383" t="n"/>
-      <c r="AL12" s="383" t="n"/>
-      <c r="AM12" s="383" t="n"/>
-      <c r="AN12" s="383" t="n"/>
+      <c r="D12" s="355" t="n"/>
+      <c r="E12" s="355" t="n"/>
+      <c r="F12" s="355" t="n"/>
+      <c r="G12" s="355" t="n"/>
+      <c r="H12" s="355" t="n"/>
+      <c r="I12" s="355" t="n"/>
+      <c r="J12" s="355" t="n"/>
+      <c r="K12" s="355" t="n"/>
+      <c r="L12" s="355" t="n"/>
+      <c r="M12" s="355" t="n"/>
+      <c r="N12" s="355" t="n"/>
+      <c r="O12" s="355" t="n"/>
+      <c r="P12" s="355" t="n"/>
+      <c r="Q12" s="355" t="n"/>
+      <c r="R12" s="355" t="n"/>
+      <c r="S12" s="355" t="n"/>
+      <c r="T12" s="355" t="n"/>
+      <c r="U12" s="355" t="n"/>
+      <c r="V12" s="355" t="n"/>
+      <c r="W12" s="355" t="n"/>
+      <c r="X12" s="355" t="n"/>
+      <c r="Y12" s="355" t="n"/>
+      <c r="Z12" s="355" t="n"/>
+      <c r="AA12" s="355" t="n"/>
+      <c r="AB12" s="355" t="n"/>
+      <c r="AC12" s="355" t="n"/>
+      <c r="AD12" s="355" t="n"/>
+      <c r="AE12" s="355" t="n"/>
+      <c r="AF12" s="355" t="n"/>
+      <c r="AG12" s="355" t="n"/>
+      <c r="AH12" s="355" t="n"/>
+      <c r="AI12" s="355" t="n"/>
+      <c r="AJ12" s="355" t="n"/>
+      <c r="AK12" s="355" t="n"/>
+      <c r="AL12" s="355" t="n"/>
+      <c r="AM12" s="355" t="n"/>
+      <c r="AN12" s="503" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="383" t="inlineStr">
+      <c r="A13" s="502" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B13" s="383" t="inlineStr">
+      <c r="B13" s="526" t="inlineStr">
         <is>
           <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
         </is>
       </c>
-      <c r="C13" s="383" t="inlineStr">
+      <c r="C13" s="355" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D13" s="383" t="n"/>
-      <c r="E13" s="383" t="n"/>
-      <c r="F13" s="383" t="n"/>
-      <c r="G13" s="383" t="n"/>
-      <c r="H13" s="383" t="n"/>
-      <c r="I13" s="383" t="n"/>
-      <c r="J13" s="383" t="n"/>
-      <c r="K13" s="383" t="n"/>
-      <c r="L13" s="383" t="n"/>
-      <c r="M13" s="383" t="n"/>
-      <c r="N13" s="383" t="n"/>
-      <c r="O13" s="383" t="n"/>
-      <c r="P13" s="383" t="n"/>
-      <c r="Q13" s="383" t="n"/>
-      <c r="R13" s="383" t="n"/>
-      <c r="S13" s="383" t="n"/>
-      <c r="T13" s="383" t="n"/>
-      <c r="U13" s="383" t="n"/>
-      <c r="V13" s="383" t="n"/>
-      <c r="W13" s="383" t="n"/>
-      <c r="X13" s="383" t="n"/>
-      <c r="Y13" s="383" t="n"/>
-      <c r="Z13" s="383" t="n"/>
-      <c r="AA13" s="383" t="n"/>
-      <c r="AB13" s="383" t="n"/>
-      <c r="AC13" s="383" t="n"/>
-      <c r="AD13" s="383" t="n"/>
-      <c r="AE13" s="383" t="n"/>
-      <c r="AF13" s="383" t="n"/>
-      <c r="AG13" s="383" t="n"/>
-      <c r="AH13" s="383" t="n"/>
-      <c r="AI13" s="383" t="n"/>
-      <c r="AJ13" s="383" t="n"/>
-      <c r="AK13" s="383" t="n"/>
-      <c r="AL13" s="383" t="n"/>
-      <c r="AM13" s="383" t="n"/>
-      <c r="AN13" s="383" t="n"/>
+      <c r="D13" s="355" t="n"/>
+      <c r="E13" s="355" t="n"/>
+      <c r="F13" s="355" t="n"/>
+      <c r="G13" s="355" t="n"/>
+      <c r="H13" s="355" t="n"/>
+      <c r="I13" s="355" t="n"/>
+      <c r="J13" s="355" t="n"/>
+      <c r="K13" s="355" t="n"/>
+      <c r="L13" s="355" t="n"/>
+      <c r="M13" s="355" t="n"/>
+      <c r="N13" s="355" t="n"/>
+      <c r="O13" s="355" t="n"/>
+      <c r="P13" s="355" t="n"/>
+      <c r="Q13" s="355" t="n"/>
+      <c r="R13" s="355" t="n"/>
+      <c r="S13" s="355" t="n"/>
+      <c r="T13" s="355" t="n"/>
+      <c r="U13" s="355" t="n"/>
+      <c r="V13" s="355" t="n"/>
+      <c r="W13" s="355" t="n"/>
+      <c r="X13" s="355" t="n"/>
+      <c r="Y13" s="355" t="n"/>
+      <c r="Z13" s="355" t="n"/>
+      <c r="AA13" s="355" t="n"/>
+      <c r="AB13" s="355" t="n"/>
+      <c r="AC13" s="355" t="n"/>
+      <c r="AD13" s="355" t="n"/>
+      <c r="AE13" s="355" t="n"/>
+      <c r="AF13" s="355" t="n"/>
+      <c r="AG13" s="355" t="n"/>
+      <c r="AH13" s="355" t="n"/>
+      <c r="AI13" s="355" t="n"/>
+      <c r="AJ13" s="355" t="n"/>
+      <c r="AK13" s="355" t="n"/>
+      <c r="AL13" s="355" t="n"/>
+      <c r="AM13" s="355" t="n"/>
+      <c r="AN13" s="503" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="383" t="inlineStr">
+      <c r="A14" s="504" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B14" s="383" t="inlineStr">
+      <c r="B14" s="527" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
         </is>
       </c>
-      <c r="C14" s="383" t="inlineStr">
+      <c r="C14" s="505" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D14" s="383" t="n"/>
-      <c r="E14" s="383" t="n"/>
-      <c r="F14" s="383" t="n"/>
-      <c r="G14" s="383" t="n"/>
-      <c r="H14" s="383" t="n"/>
-      <c r="I14" s="383" t="n"/>
-      <c r="J14" s="383" t="n"/>
-      <c r="K14" s="383" t="n"/>
-      <c r="L14" s="383" t="n"/>
-      <c r="M14" s="383" t="n"/>
-      <c r="N14" s="383" t="n"/>
-      <c r="O14" s="383" t="n"/>
-      <c r="P14" s="383" t="n"/>
-      <c r="Q14" s="383" t="n"/>
-      <c r="R14" s="383" t="n"/>
-      <c r="S14" s="383" t="n"/>
-      <c r="T14" s="383" t="n"/>
-      <c r="U14" s="383" t="n"/>
-      <c r="V14" s="383" t="n"/>
-      <c r="W14" s="383" t="n"/>
-      <c r="X14" s="383" t="n"/>
-      <c r="Y14" s="383" t="n"/>
-      <c r="Z14" s="383" t="n"/>
-      <c r="AA14" s="383" t="n"/>
-      <c r="AB14" s="383" t="n"/>
-      <c r="AC14" s="383" t="n"/>
-      <c r="AD14" s="383" t="n"/>
-      <c r="AE14" s="383" t="n"/>
-      <c r="AF14" s="383" t="n"/>
-      <c r="AG14" s="383" t="n"/>
-      <c r="AH14" s="383" t="n"/>
-      <c r="AI14" s="383" t="n"/>
-      <c r="AJ14" s="383" t="n"/>
-      <c r="AK14" s="383" t="n"/>
-      <c r="AL14" s="383" t="n"/>
-      <c r="AM14" s="383" t="n"/>
-      <c r="AN14" s="383" t="n"/>
+      <c r="D14" s="505" t="n"/>
+      <c r="E14" s="505" t="n"/>
+      <c r="F14" s="505" t="n"/>
+      <c r="G14" s="505" t="n"/>
+      <c r="H14" s="505" t="n"/>
+      <c r="I14" s="505" t="n"/>
+      <c r="J14" s="505" t="n"/>
+      <c r="K14" s="505" t="n"/>
+      <c r="L14" s="505" t="n"/>
+      <c r="M14" s="505" t="n"/>
+      <c r="N14" s="505" t="n"/>
+      <c r="O14" s="505" t="n"/>
+      <c r="P14" s="505" t="n"/>
+      <c r="Q14" s="505" t="n"/>
+      <c r="R14" s="505" t="n"/>
+      <c r="S14" s="505" t="n"/>
+      <c r="T14" s="505" t="n"/>
+      <c r="U14" s="505" t="n"/>
+      <c r="V14" s="505" t="n"/>
+      <c r="W14" s="505" t="n"/>
+      <c r="X14" s="505" t="n"/>
+      <c r="Y14" s="505" t="n"/>
+      <c r="Z14" s="505" t="n"/>
+      <c r="AA14" s="505" t="n"/>
+      <c r="AB14" s="505" t="n"/>
+      <c r="AC14" s="505" t="n"/>
+      <c r="AD14" s="505" t="n"/>
+      <c r="AE14" s="505" t="n"/>
+      <c r="AF14" s="505" t="n"/>
+      <c r="AG14" s="505" t="n"/>
+      <c r="AH14" s="505" t="n"/>
+      <c r="AI14" s="505" t="n"/>
+      <c r="AJ14" s="505" t="n"/>
+      <c r="AK14" s="505" t="n"/>
+      <c r="AL14" s="505" t="n"/>
+      <c r="AM14" s="505" t="n"/>
+      <c r="AN14" s="506" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329"/>
     <row r="16" ht="20" customHeight="1" s="329"/>
@@ -9859,5 +10656,6 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -769,7 +769,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="321">
+  <borders count="354">
     <border>
       <left/>
       <right/>
@@ -4199,12 +4199,403 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="528">
+  <cellXfs count="571">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5401,6 +5792,93 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="343" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5501,6 +5979,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5531,6 +6012,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5561,6 +6045,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5763,7 +6250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:CU44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -5809,246 +6296,168 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="416" t="n"/>
-      <c r="B1" s="417" t="n"/>
-      <c r="C1" s="417" t="n"/>
-      <c r="D1" s="417" t="n"/>
-      <c r="E1" s="417" t="n"/>
-      <c r="F1" s="417" t="n"/>
-      <c r="G1" s="417" t="n"/>
-      <c r="H1" s="418" t="n"/>
-      <c r="I1" s="419" t="inlineStr">
+      <c r="A1" s="528" t="n"/>
+      <c r="B1" s="529" t="n"/>
+      <c r="C1" s="529" t="n"/>
+      <c r="D1" s="529" t="n"/>
+      <c r="E1" s="529" t="n"/>
+      <c r="F1" s="529" t="n"/>
+      <c r="G1" s="529" t="n"/>
+      <c r="H1" s="530" t="n"/>
+      <c r="I1" s="531" t="inlineStr">
         <is>
           <t>Outsource Dispatch Checklist</t>
         </is>
       </c>
-      <c r="J1" s="420" t="n"/>
-      <c r="K1" s="420" t="n"/>
-      <c r="L1" s="420" t="n"/>
-      <c r="M1" s="420" t="n"/>
-      <c r="N1" s="420" t="n"/>
-      <c r="O1" s="420" t="n"/>
-      <c r="P1" s="420" t="n"/>
-      <c r="Q1" s="420" t="n"/>
-      <c r="R1" s="420" t="n"/>
-      <c r="S1" s="420" t="n"/>
-      <c r="T1" s="420" t="n"/>
-      <c r="U1" s="420" t="n"/>
-      <c r="V1" s="420" t="n"/>
-      <c r="W1" s="420" t="n"/>
-      <c r="X1" s="420" t="n"/>
-      <c r="Y1" s="420" t="n"/>
-      <c r="Z1" s="420" t="n"/>
-      <c r="AA1" s="420" t="n"/>
-      <c r="AB1" s="420" t="n"/>
-      <c r="AC1" s="420" t="n"/>
-      <c r="AD1" s="421" t="n"/>
-      <c r="AE1" s="422" t="n"/>
-      <c r="AF1" s="423" t="n"/>
-      <c r="AG1" s="423" t="n"/>
-      <c r="AH1" s="424" t="n"/>
-      <c r="AI1" s="425" t="inlineStr">
+      <c r="J1" s="529" t="n"/>
+      <c r="K1" s="529" t="n"/>
+      <c r="L1" s="529" t="n"/>
+      <c r="M1" s="529" t="n"/>
+      <c r="N1" s="529" t="n"/>
+      <c r="O1" s="529" t="n"/>
+      <c r="P1" s="529" t="n"/>
+      <c r="Q1" s="529" t="n"/>
+      <c r="R1" s="529" t="n"/>
+      <c r="S1" s="529" t="n"/>
+      <c r="T1" s="529" t="n"/>
+      <c r="U1" s="529" t="n"/>
+      <c r="V1" s="529" t="n"/>
+      <c r="W1" s="529" t="n"/>
+      <c r="X1" s="529" t="n"/>
+      <c r="Y1" s="529" t="n"/>
+      <c r="Z1" s="529" t="n"/>
+      <c r="AA1" s="529" t="n"/>
+      <c r="AB1" s="529" t="n"/>
+      <c r="AC1" s="529" t="n"/>
+      <c r="AD1" s="530" t="n"/>
+      <c r="AE1" s="532" t="n"/>
+      <c r="AF1" s="529" t="n"/>
+      <c r="AG1" s="529" t="n"/>
+      <c r="AH1" s="533" t="n"/>
+      <c r="AI1" s="534" t="inlineStr">
         <is>
           <t>FRM-404</t>
         </is>
       </c>
-      <c r="AJ1" s="426" t="n"/>
-      <c r="AK1" s="426" t="n"/>
-      <c r="AL1" s="426" t="n"/>
-      <c r="AM1" s="426" t="n"/>
-      <c r="AN1" s="427" t="n"/>
+      <c r="AJ1" s="529" t="n"/>
+      <c r="AK1" s="529" t="n"/>
+      <c r="AL1" s="529" t="n"/>
+      <c r="AM1" s="529" t="n"/>
+      <c r="AN1" s="530" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="428" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="429" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="431" t="n"/>
-      <c r="K2" s="431" t="n"/>
-      <c r="L2" s="431" t="n"/>
-      <c r="M2" s="431" t="n"/>
-      <c r="N2" s="431" t="n"/>
-      <c r="O2" s="431" t="n"/>
-      <c r="P2" s="431" t="n"/>
-      <c r="Q2" s="431" t="n"/>
-      <c r="R2" s="431" t="n"/>
-      <c r="S2" s="431" t="n"/>
-      <c r="T2" s="431" t="n"/>
-      <c r="U2" s="431" t="n"/>
-      <c r="V2" s="431" t="n"/>
-      <c r="W2" s="431" t="n"/>
-      <c r="X2" s="431" t="n"/>
-      <c r="Y2" s="431" t="n"/>
-      <c r="Z2" s="431" t="n"/>
-      <c r="AA2" s="431" t="n"/>
-      <c r="AB2" s="431" t="n"/>
-      <c r="AC2" s="431" t="n"/>
-      <c r="AD2" s="432" t="n"/>
-      <c r="AE2" s="433" t="n"/>
-      <c r="AF2" s="434" t="n"/>
-      <c r="AG2" s="434" t="n"/>
-      <c r="AH2" s="435" t="n"/>
-      <c r="AI2" s="436" t="inlineStr">
+      <c r="A2" s="535" t="n"/>
+      <c r="H2" s="536" t="n"/>
+      <c r="I2" s="535" t="n"/>
+      <c r="AD2" s="536" t="n"/>
+      <c r="AE2" s="537" t="n"/>
+      <c r="AF2" s="410" t="n"/>
+      <c r="AG2" s="410" t="n"/>
+      <c r="AH2" s="538" t="n"/>
+      <c r="AI2" s="539" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="437" t="n"/>
-      <c r="AK2" s="437" t="n"/>
-      <c r="AL2" s="437" t="n"/>
-      <c r="AM2" s="437" t="n"/>
-      <c r="AN2" s="438" t="n"/>
+      <c r="AJ2" s="410" t="n"/>
+      <c r="AK2" s="410" t="n"/>
+      <c r="AL2" s="410" t="n"/>
+      <c r="AM2" s="410" t="n"/>
+      <c r="AN2" s="540" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="428" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="429" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="431" t="n"/>
-      <c r="K3" s="431" t="n"/>
-      <c r="L3" s="431" t="n"/>
-      <c r="M3" s="431" t="n"/>
-      <c r="N3" s="431" t="n"/>
-      <c r="O3" s="431" t="n"/>
-      <c r="P3" s="431" t="n"/>
-      <c r="Q3" s="431" t="n"/>
-      <c r="R3" s="431" t="n"/>
-      <c r="S3" s="431" t="n"/>
-      <c r="T3" s="431" t="n"/>
-      <c r="U3" s="431" t="n"/>
-      <c r="V3" s="431" t="n"/>
-      <c r="W3" s="431" t="n"/>
-      <c r="X3" s="431" t="n"/>
-      <c r="Y3" s="431" t="n"/>
-      <c r="Z3" s="431" t="n"/>
-      <c r="AA3" s="431" t="n"/>
-      <c r="AB3" s="431" t="n"/>
-      <c r="AC3" s="431" t="n"/>
-      <c r="AD3" s="432" t="n"/>
-      <c r="AE3" s="433" t="n"/>
-      <c r="AF3" s="434" t="n"/>
-      <c r="AG3" s="434" t="n"/>
-      <c r="AH3" s="435" t="n"/>
-      <c r="AI3" s="436" t="inlineStr">
+      <c r="A3" s="535" t="n"/>
+      <c r="H3" s="536" t="n"/>
+      <c r="I3" s="535" t="n"/>
+      <c r="AD3" s="536" t="n"/>
+      <c r="AE3" s="537" t="n"/>
+      <c r="AF3" s="410" t="n"/>
+      <c r="AG3" s="410" t="n"/>
+      <c r="AH3" s="538" t="n"/>
+      <c r="AI3" s="539" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="437" t="n"/>
-      <c r="AK3" s="437" t="n"/>
-      <c r="AL3" s="437" t="n"/>
-      <c r="AM3" s="437" t="n"/>
-      <c r="AN3" s="438" t="n"/>
+      <c r="AJ3" s="410" t="n"/>
+      <c r="AK3" s="410" t="n"/>
+      <c r="AL3" s="410" t="n"/>
+      <c r="AM3" s="410" t="n"/>
+      <c r="AN3" s="540" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="428" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="429" t="n"/>
-      <c r="I4" s="439" t="inlineStr">
+      <c r="A4" s="535" t="n"/>
+      <c r="H4" s="536" t="n"/>
+      <c r="I4" s="541" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="440" t="n"/>
-      <c r="K4" s="440" t="n"/>
-      <c r="L4" s="440" t="n"/>
-      <c r="M4" s="440" t="n"/>
-      <c r="N4" s="440" t="n"/>
-      <c r="O4" s="440" t="n"/>
-      <c r="P4" s="440" t="n"/>
-      <c r="Q4" s="440" t="n"/>
-      <c r="R4" s="440" t="n"/>
-      <c r="S4" s="440" t="n"/>
-      <c r="T4" s="440" t="n"/>
-      <c r="U4" s="440" t="n"/>
-      <c r="V4" s="440" t="n"/>
-      <c r="W4" s="440" t="n"/>
-      <c r="X4" s="440" t="n"/>
-      <c r="Y4" s="440" t="n"/>
-      <c r="Z4" s="440" t="n"/>
-      <c r="AA4" s="440" t="n"/>
-      <c r="AB4" s="440" t="n"/>
-      <c r="AC4" s="440" t="n"/>
-      <c r="AD4" s="441" t="n"/>
-      <c r="AE4" s="433" t="n"/>
-      <c r="AF4" s="434" t="n"/>
-      <c r="AG4" s="434" t="n"/>
-      <c r="AH4" s="435" t="n"/>
-      <c r="AI4" s="436" t="inlineStr">
+      <c r="AD4" s="536" t="n"/>
+      <c r="AE4" s="537" t="n"/>
+      <c r="AF4" s="410" t="n"/>
+      <c r="AG4" s="410" t="n"/>
+      <c r="AH4" s="538" t="n"/>
+      <c r="AI4" s="539" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="437" t="n"/>
-      <c r="AK4" s="437" t="n"/>
-      <c r="AL4" s="437" t="n"/>
-      <c r="AM4" s="437" t="n"/>
-      <c r="AN4" s="438" t="n"/>
+      <c r="AJ4" s="410" t="n"/>
+      <c r="AK4" s="410" t="n"/>
+      <c r="AL4" s="410" t="n"/>
+      <c r="AM4" s="410" t="n"/>
+      <c r="AN4" s="540" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="442" t="n"/>
-      <c r="B5" s="443" t="n"/>
-      <c r="C5" s="443" t="n"/>
-      <c r="D5" s="443" t="n"/>
-      <c r="E5" s="443" t="n"/>
-      <c r="F5" s="443" t="n"/>
-      <c r="G5" s="443" t="n"/>
-      <c r="H5" s="444" t="n"/>
-      <c r="I5" s="445" t="inlineStr">
+      <c r="A5" s="542" t="n"/>
+      <c r="B5" s="543" t="n"/>
+      <c r="C5" s="543" t="n"/>
+      <c r="D5" s="543" t="n"/>
+      <c r="E5" s="543" t="n"/>
+      <c r="F5" s="543" t="n"/>
+      <c r="G5" s="543" t="n"/>
+      <c r="H5" s="544" t="n"/>
+      <c r="I5" s="545" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="446" t="n"/>
-      <c r="K5" s="446" t="n"/>
-      <c r="L5" s="446" t="n"/>
-      <c r="M5" s="446" t="n"/>
-      <c r="N5" s="446" t="n"/>
-      <c r="O5" s="446" t="n"/>
-      <c r="P5" s="446" t="n"/>
-      <c r="Q5" s="446" t="n"/>
-      <c r="R5" s="446" t="n"/>
-      <c r="S5" s="446" t="n"/>
-      <c r="T5" s="446" t="n"/>
-      <c r="U5" s="446" t="n"/>
-      <c r="V5" s="446" t="n"/>
-      <c r="W5" s="446" t="n"/>
-      <c r="X5" s="446" t="n"/>
-      <c r="Y5" s="446" t="n"/>
-      <c r="Z5" s="446" t="n"/>
-      <c r="AA5" s="446" t="n"/>
-      <c r="AB5" s="446" t="n"/>
-      <c r="AC5" s="446" t="n"/>
-      <c r="AD5" s="447" t="n"/>
-      <c r="AE5" s="448" t="n"/>
-      <c r="AF5" s="449" t="n"/>
-      <c r="AG5" s="449" t="n"/>
-      <c r="AH5" s="450" t="n"/>
-      <c r="AI5" s="451" t="inlineStr">
+      <c r="J5" s="543" t="n"/>
+      <c r="K5" s="543" t="n"/>
+      <c r="L5" s="543" t="n"/>
+      <c r="M5" s="543" t="n"/>
+      <c r="N5" s="543" t="n"/>
+      <c r="O5" s="543" t="n"/>
+      <c r="P5" s="543" t="n"/>
+      <c r="Q5" s="543" t="n"/>
+      <c r="R5" s="543" t="n"/>
+      <c r="S5" s="543" t="n"/>
+      <c r="T5" s="543" t="n"/>
+      <c r="U5" s="543" t="n"/>
+      <c r="V5" s="543" t="n"/>
+      <c r="W5" s="543" t="n"/>
+      <c r="X5" s="543" t="n"/>
+      <c r="Y5" s="543" t="n"/>
+      <c r="Z5" s="543" t="n"/>
+      <c r="AA5" s="543" t="n"/>
+      <c r="AB5" s="543" t="n"/>
+      <c r="AC5" s="543" t="n"/>
+      <c r="AD5" s="544" t="n"/>
+      <c r="AE5" s="546" t="n"/>
+      <c r="AF5" s="547" t="n"/>
+      <c r="AG5" s="547" t="n"/>
+      <c r="AH5" s="548" t="n"/>
+      <c r="AI5" s="549" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="452" t="n"/>
-      <c r="AK5" s="452" t="n"/>
-      <c r="AL5" s="452" t="n"/>
-      <c r="AM5" s="452" t="n"/>
-      <c r="AN5" s="453" t="n"/>
+      <c r="AJ5" s="547" t="n"/>
+      <c r="AK5" s="547" t="n"/>
+      <c r="AL5" s="547" t="n"/>
+      <c r="AM5" s="547" t="n"/>
+      <c r="AN5" s="550" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1" s="329">
       <c r="A6" s="454" t="n"/>
@@ -6093,50 +6502,50 @@
       <c r="AN6" s="454" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="329">
-      <c r="A7" s="455" t="inlineStr">
+      <c r="A7" s="551" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="456" t="n"/>
-      <c r="C7" s="456" t="n"/>
-      <c r="D7" s="456" t="n"/>
-      <c r="E7" s="456" t="n"/>
-      <c r="F7" s="456" t="n"/>
-      <c r="G7" s="456" t="n"/>
-      <c r="H7" s="456" t="n"/>
-      <c r="I7" s="456" t="n"/>
-      <c r="J7" s="456" t="n"/>
-      <c r="K7" s="456" t="n"/>
-      <c r="L7" s="456" t="n"/>
-      <c r="M7" s="456" t="n"/>
-      <c r="N7" s="456" t="n"/>
-      <c r="O7" s="456" t="n"/>
-      <c r="P7" s="456" t="n"/>
-      <c r="Q7" s="456" t="n"/>
-      <c r="R7" s="456" t="n"/>
-      <c r="S7" s="456" t="n"/>
-      <c r="T7" s="456" t="n"/>
-      <c r="U7" s="456" t="n"/>
-      <c r="V7" s="456" t="n"/>
-      <c r="W7" s="456" t="n"/>
-      <c r="X7" s="456" t="n"/>
-      <c r="Y7" s="456" t="n"/>
-      <c r="Z7" s="456" t="n"/>
-      <c r="AA7" s="456" t="n"/>
-      <c r="AB7" s="456" t="n"/>
-      <c r="AC7" s="456" t="n"/>
-      <c r="AD7" s="456" t="n"/>
-      <c r="AE7" s="456" t="n"/>
-      <c r="AF7" s="456" t="n"/>
-      <c r="AG7" s="456" t="n"/>
-      <c r="AH7" s="456" t="n"/>
-      <c r="AI7" s="456" t="n"/>
-      <c r="AJ7" s="456" t="n"/>
-      <c r="AK7" s="456" t="n"/>
-      <c r="AL7" s="456" t="n"/>
-      <c r="AM7" s="456" t="n"/>
-      <c r="AN7" s="457" t="n"/>
+      <c r="B7" s="552" t="n"/>
+      <c r="C7" s="552" t="n"/>
+      <c r="D7" s="552" t="n"/>
+      <c r="E7" s="552" t="n"/>
+      <c r="F7" s="552" t="n"/>
+      <c r="G7" s="552" t="n"/>
+      <c r="H7" s="552" t="n"/>
+      <c r="I7" s="552" t="n"/>
+      <c r="J7" s="552" t="n"/>
+      <c r="K7" s="552" t="n"/>
+      <c r="L7" s="552" t="n"/>
+      <c r="M7" s="552" t="n"/>
+      <c r="N7" s="552" t="n"/>
+      <c r="O7" s="552" t="n"/>
+      <c r="P7" s="552" t="n"/>
+      <c r="Q7" s="552" t="n"/>
+      <c r="R7" s="552" t="n"/>
+      <c r="S7" s="552" t="n"/>
+      <c r="T7" s="552" t="n"/>
+      <c r="U7" s="552" t="n"/>
+      <c r="V7" s="552" t="n"/>
+      <c r="W7" s="552" t="n"/>
+      <c r="X7" s="552" t="n"/>
+      <c r="Y7" s="552" t="n"/>
+      <c r="Z7" s="552" t="n"/>
+      <c r="AA7" s="552" t="n"/>
+      <c r="AB7" s="552" t="n"/>
+      <c r="AC7" s="552" t="n"/>
+      <c r="AD7" s="552" t="n"/>
+      <c r="AE7" s="552" t="n"/>
+      <c r="AF7" s="552" t="n"/>
+      <c r="AG7" s="552" t="n"/>
+      <c r="AH7" s="552" t="n"/>
+      <c r="AI7" s="552" t="n"/>
+      <c r="AJ7" s="552" t="n"/>
+      <c r="AK7" s="552" t="n"/>
+      <c r="AL7" s="552" t="n"/>
+      <c r="AM7" s="552" t="n"/>
+      <c r="AN7" s="553" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
       <c r="A8" s="458" t="inlineStr">
@@ -6144,49 +6553,49 @@
           <t>Outsource Dispatch ID</t>
         </is>
       </c>
-      <c r="B8" s="459" t="n"/>
-      <c r="C8" s="459" t="n"/>
-      <c r="D8" s="459" t="n"/>
-      <c r="E8" s="459" t="n"/>
-      <c r="F8" s="459" t="n"/>
-      <c r="G8" s="459" t="n"/>
+      <c r="B8" s="554" t="n"/>
+      <c r="C8" s="554" t="n"/>
+      <c r="D8" s="554" t="n"/>
+      <c r="E8" s="554" t="n"/>
+      <c r="F8" s="554" t="n"/>
+      <c r="G8" s="554" t="n"/>
       <c r="H8" s="460" t="n"/>
-      <c r="I8" s="459" t="n"/>
-      <c r="J8" s="459" t="n"/>
-      <c r="K8" s="459" t="n"/>
-      <c r="L8" s="459" t="n"/>
-      <c r="M8" s="459" t="n"/>
-      <c r="N8" s="459" t="n"/>
-      <c r="O8" s="459" t="n"/>
-      <c r="P8" s="459" t="n"/>
-      <c r="Q8" s="459" t="n"/>
-      <c r="R8" s="459" t="n"/>
-      <c r="S8" s="459" t="n"/>
-      <c r="T8" s="459" t="n"/>
+      <c r="I8" s="554" t="n"/>
+      <c r="J8" s="554" t="n"/>
+      <c r="K8" s="554" t="n"/>
+      <c r="L8" s="554" t="n"/>
+      <c r="M8" s="554" t="n"/>
+      <c r="N8" s="554" t="n"/>
+      <c r="O8" s="554" t="n"/>
+      <c r="P8" s="554" t="n"/>
+      <c r="Q8" s="554" t="n"/>
+      <c r="R8" s="554" t="n"/>
+      <c r="S8" s="554" t="n"/>
+      <c r="T8" s="554" t="n"/>
       <c r="U8" s="461" t="inlineStr">
         <is>
           <t>Dispatch Gate Status</t>
         </is>
       </c>
-      <c r="V8" s="459" t="n"/>
-      <c r="W8" s="459" t="n"/>
-      <c r="X8" s="459" t="n"/>
-      <c r="Y8" s="459" t="n"/>
-      <c r="Z8" s="459" t="n"/>
-      <c r="AA8" s="459" t="n"/>
-      <c r="AB8" s="460" t="n"/>
-      <c r="AC8" s="459" t="n"/>
-      <c r="AD8" s="459" t="n"/>
-      <c r="AE8" s="459" t="n"/>
-      <c r="AF8" s="459" t="n"/>
-      <c r="AG8" s="459" t="n"/>
-      <c r="AH8" s="459" t="n"/>
-      <c r="AI8" s="459" t="n"/>
-      <c r="AJ8" s="459" t="n"/>
-      <c r="AK8" s="459" t="n"/>
-      <c r="AL8" s="459" t="n"/>
-      <c r="AM8" s="459" t="n"/>
-      <c r="AN8" s="462" t="n"/>
+      <c r="V8" s="554" t="n"/>
+      <c r="W8" s="554" t="n"/>
+      <c r="X8" s="554" t="n"/>
+      <c r="Y8" s="554" t="n"/>
+      <c r="Z8" s="554" t="n"/>
+      <c r="AA8" s="554" t="n"/>
+      <c r="AB8" s="555" t="n"/>
+      <c r="AC8" s="554" t="n"/>
+      <c r="AD8" s="554" t="n"/>
+      <c r="AE8" s="554" t="n"/>
+      <c r="AF8" s="554" t="n"/>
+      <c r="AG8" s="554" t="n"/>
+      <c r="AH8" s="554" t="n"/>
+      <c r="AI8" s="554" t="n"/>
+      <c r="AJ8" s="554" t="n"/>
+      <c r="AK8" s="554" t="n"/>
+      <c r="AL8" s="554" t="n"/>
+      <c r="AM8" s="554" t="n"/>
+      <c r="AN8" s="556" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
       <c r="A9" s="463" t="inlineStr">
@@ -6194,49 +6603,49 @@
           <t>Supplier / Processor</t>
         </is>
       </c>
-      <c r="B9" s="343" t="n"/>
-      <c r="C9" s="343" t="n"/>
-      <c r="D9" s="343" t="n"/>
-      <c r="E9" s="343" t="n"/>
-      <c r="F9" s="343" t="n"/>
-      <c r="G9" s="343" t="n"/>
+      <c r="B9" s="411" t="n"/>
+      <c r="C9" s="411" t="n"/>
+      <c r="D9" s="411" t="n"/>
+      <c r="E9" s="411" t="n"/>
+      <c r="F9" s="411" t="n"/>
+      <c r="G9" s="411" t="n"/>
       <c r="H9" s="464" t="n"/>
-      <c r="I9" s="343" t="n"/>
-      <c r="J9" s="343" t="n"/>
-      <c r="K9" s="343" t="n"/>
-      <c r="L9" s="343" t="n"/>
-      <c r="M9" s="343" t="n"/>
-      <c r="N9" s="343" t="n"/>
-      <c r="O9" s="343" t="n"/>
-      <c r="P9" s="343" t="n"/>
-      <c r="Q9" s="343" t="n"/>
-      <c r="R9" s="343" t="n"/>
-      <c r="S9" s="343" t="n"/>
-      <c r="T9" s="343" t="n"/>
+      <c r="I9" s="411" t="n"/>
+      <c r="J9" s="411" t="n"/>
+      <c r="K9" s="411" t="n"/>
+      <c r="L9" s="411" t="n"/>
+      <c r="M9" s="411" t="n"/>
+      <c r="N9" s="411" t="n"/>
+      <c r="O9" s="411" t="n"/>
+      <c r="P9" s="411" t="n"/>
+      <c r="Q9" s="411" t="n"/>
+      <c r="R9" s="411" t="n"/>
+      <c r="S9" s="411" t="n"/>
+      <c r="T9" s="411" t="n"/>
       <c r="U9" s="465" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="V9" s="343" t="n"/>
-      <c r="W9" s="343" t="n"/>
-      <c r="X9" s="343" t="n"/>
-      <c r="Y9" s="343" t="n"/>
-      <c r="Z9" s="343" t="n"/>
-      <c r="AA9" s="343" t="n"/>
-      <c r="AB9" s="464" t="n"/>
-      <c r="AC9" s="343" t="n"/>
-      <c r="AD9" s="343" t="n"/>
-      <c r="AE9" s="343" t="n"/>
-      <c r="AF9" s="343" t="n"/>
-      <c r="AG9" s="343" t="n"/>
-      <c r="AH9" s="343" t="n"/>
-      <c r="AI9" s="343" t="n"/>
-      <c r="AJ9" s="343" t="n"/>
-      <c r="AK9" s="343" t="n"/>
-      <c r="AL9" s="343" t="n"/>
-      <c r="AM9" s="343" t="n"/>
-      <c r="AN9" s="466" t="n"/>
+      <c r="V9" s="411" t="n"/>
+      <c r="W9" s="411" t="n"/>
+      <c r="X9" s="411" t="n"/>
+      <c r="Y9" s="411" t="n"/>
+      <c r="Z9" s="411" t="n"/>
+      <c r="AA9" s="411" t="n"/>
+      <c r="AB9" s="557" t="n"/>
+      <c r="AC9" s="411" t="n"/>
+      <c r="AD9" s="411" t="n"/>
+      <c r="AE9" s="411" t="n"/>
+      <c r="AF9" s="411" t="n"/>
+      <c r="AG9" s="411" t="n"/>
+      <c r="AH9" s="411" t="n"/>
+      <c r="AI9" s="411" t="n"/>
+      <c r="AJ9" s="411" t="n"/>
+      <c r="AK9" s="411" t="n"/>
+      <c r="AL9" s="411" t="n"/>
+      <c r="AM9" s="411" t="n"/>
+      <c r="AN9" s="558" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
       <c r="A10" s="463" t="inlineStr">
@@ -6244,49 +6653,49 @@
           <t>PO / Work Order</t>
         </is>
       </c>
-      <c r="B10" s="343" t="n"/>
-      <c r="C10" s="343" t="n"/>
-      <c r="D10" s="343" t="n"/>
-      <c r="E10" s="343" t="n"/>
-      <c r="F10" s="343" t="n"/>
-      <c r="G10" s="343" t="n"/>
+      <c r="B10" s="411" t="n"/>
+      <c r="C10" s="411" t="n"/>
+      <c r="D10" s="411" t="n"/>
+      <c r="E10" s="411" t="n"/>
+      <c r="F10" s="411" t="n"/>
+      <c r="G10" s="411" t="n"/>
       <c r="H10" s="464" t="n"/>
-      <c r="I10" s="343" t="n"/>
-      <c r="J10" s="343" t="n"/>
-      <c r="K10" s="343" t="n"/>
-      <c r="L10" s="343" t="n"/>
-      <c r="M10" s="343" t="n"/>
-      <c r="N10" s="343" t="n"/>
-      <c r="O10" s="343" t="n"/>
-      <c r="P10" s="343" t="n"/>
-      <c r="Q10" s="343" t="n"/>
-      <c r="R10" s="343" t="n"/>
-      <c r="S10" s="343" t="n"/>
-      <c r="T10" s="343" t="n"/>
+      <c r="I10" s="411" t="n"/>
+      <c r="J10" s="411" t="n"/>
+      <c r="K10" s="411" t="n"/>
+      <c r="L10" s="411" t="n"/>
+      <c r="M10" s="411" t="n"/>
+      <c r="N10" s="411" t="n"/>
+      <c r="O10" s="411" t="n"/>
+      <c r="P10" s="411" t="n"/>
+      <c r="Q10" s="411" t="n"/>
+      <c r="R10" s="411" t="n"/>
+      <c r="S10" s="411" t="n"/>
+      <c r="T10" s="411" t="n"/>
       <c r="U10" s="465" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="343" t="n"/>
-      <c r="W10" s="343" t="n"/>
-      <c r="X10" s="343" t="n"/>
-      <c r="Y10" s="343" t="n"/>
-      <c r="Z10" s="343" t="n"/>
-      <c r="AA10" s="343" t="n"/>
-      <c r="AB10" s="464" t="n"/>
-      <c r="AC10" s="343" t="n"/>
-      <c r="AD10" s="343" t="n"/>
-      <c r="AE10" s="343" t="n"/>
-      <c r="AF10" s="343" t="n"/>
-      <c r="AG10" s="343" t="n"/>
-      <c r="AH10" s="343" t="n"/>
-      <c r="AI10" s="343" t="n"/>
-      <c r="AJ10" s="343" t="n"/>
-      <c r="AK10" s="343" t="n"/>
-      <c r="AL10" s="343" t="n"/>
-      <c r="AM10" s="343" t="n"/>
-      <c r="AN10" s="466" t="n"/>
+      <c r="V10" s="411" t="n"/>
+      <c r="W10" s="411" t="n"/>
+      <c r="X10" s="411" t="n"/>
+      <c r="Y10" s="411" t="n"/>
+      <c r="Z10" s="411" t="n"/>
+      <c r="AA10" s="411" t="n"/>
+      <c r="AB10" s="557" t="n"/>
+      <c r="AC10" s="411" t="n"/>
+      <c r="AD10" s="411" t="n"/>
+      <c r="AE10" s="411" t="n"/>
+      <c r="AF10" s="411" t="n"/>
+      <c r="AG10" s="411" t="n"/>
+      <c r="AH10" s="411" t="n"/>
+      <c r="AI10" s="411" t="n"/>
+      <c r="AJ10" s="411" t="n"/>
+      <c r="AK10" s="411" t="n"/>
+      <c r="AL10" s="411" t="n"/>
+      <c r="AM10" s="411" t="n"/>
+      <c r="AN10" s="558" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1" s="329">
       <c r="A11" s="463" t="inlineStr">
@@ -6294,49 +6703,49 @@
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="343" t="n"/>
-      <c r="C11" s="343" t="n"/>
-      <c r="D11" s="343" t="n"/>
-      <c r="E11" s="343" t="n"/>
-      <c r="F11" s="343" t="n"/>
-      <c r="G11" s="343" t="n"/>
+      <c r="B11" s="411" t="n"/>
+      <c r="C11" s="411" t="n"/>
+      <c r="D11" s="411" t="n"/>
+      <c r="E11" s="411" t="n"/>
+      <c r="F11" s="411" t="n"/>
+      <c r="G11" s="411" t="n"/>
       <c r="H11" s="464" t="n"/>
-      <c r="I11" s="343" t="n"/>
-      <c r="J11" s="343" t="n"/>
-      <c r="K11" s="343" t="n"/>
-      <c r="L11" s="343" t="n"/>
-      <c r="M11" s="343" t="n"/>
-      <c r="N11" s="343" t="n"/>
-      <c r="O11" s="343" t="n"/>
-      <c r="P11" s="343" t="n"/>
-      <c r="Q11" s="343" t="n"/>
-      <c r="R11" s="343" t="n"/>
-      <c r="S11" s="343" t="n"/>
-      <c r="T11" s="343" t="n"/>
+      <c r="I11" s="411" t="n"/>
+      <c r="J11" s="411" t="n"/>
+      <c r="K11" s="411" t="n"/>
+      <c r="L11" s="411" t="n"/>
+      <c r="M11" s="411" t="n"/>
+      <c r="N11" s="411" t="n"/>
+      <c r="O11" s="411" t="n"/>
+      <c r="P11" s="411" t="n"/>
+      <c r="Q11" s="411" t="n"/>
+      <c r="R11" s="411" t="n"/>
+      <c r="S11" s="411" t="n"/>
+      <c r="T11" s="411" t="n"/>
       <c r="U11" s="465" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="343" t="n"/>
-      <c r="W11" s="343" t="n"/>
-      <c r="X11" s="343" t="n"/>
-      <c r="Y11" s="343" t="n"/>
-      <c r="Z11" s="343" t="n"/>
-      <c r="AA11" s="343" t="n"/>
-      <c r="AB11" s="464" t="n"/>
-      <c r="AC11" s="343" t="n"/>
-      <c r="AD11" s="343" t="n"/>
-      <c r="AE11" s="343" t="n"/>
-      <c r="AF11" s="343" t="n"/>
-      <c r="AG11" s="343" t="n"/>
-      <c r="AH11" s="343" t="n"/>
-      <c r="AI11" s="343" t="n"/>
-      <c r="AJ11" s="343" t="n"/>
-      <c r="AK11" s="343" t="n"/>
-      <c r="AL11" s="343" t="n"/>
-      <c r="AM11" s="343" t="n"/>
-      <c r="AN11" s="466" t="n"/>
+      <c r="V11" s="411" t="n"/>
+      <c r="W11" s="411" t="n"/>
+      <c r="X11" s="411" t="n"/>
+      <c r="Y11" s="411" t="n"/>
+      <c r="Z11" s="411" t="n"/>
+      <c r="AA11" s="411" t="n"/>
+      <c r="AB11" s="557" t="n"/>
+      <c r="AC11" s="411" t="n"/>
+      <c r="AD11" s="411" t="n"/>
+      <c r="AE11" s="411" t="n"/>
+      <c r="AF11" s="411" t="n"/>
+      <c r="AG11" s="411" t="n"/>
+      <c r="AH11" s="411" t="n"/>
+      <c r="AI11" s="411" t="n"/>
+      <c r="AJ11" s="411" t="n"/>
+      <c r="AK11" s="411" t="n"/>
+      <c r="AL11" s="411" t="n"/>
+      <c r="AM11" s="411" t="n"/>
+      <c r="AN11" s="558" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
       <c r="A12" s="463" t="inlineStr">
@@ -6344,49 +6753,49 @@
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="343" t="n"/>
-      <c r="C12" s="343" t="n"/>
-      <c r="D12" s="343" t="n"/>
-      <c r="E12" s="343" t="n"/>
-      <c r="F12" s="343" t="n"/>
-      <c r="G12" s="343" t="n"/>
+      <c r="B12" s="411" t="n"/>
+      <c r="C12" s="411" t="n"/>
+      <c r="D12" s="411" t="n"/>
+      <c r="E12" s="411" t="n"/>
+      <c r="F12" s="411" t="n"/>
+      <c r="G12" s="411" t="n"/>
       <c r="H12" s="464" t="n"/>
-      <c r="I12" s="343" t="n"/>
-      <c r="J12" s="343" t="n"/>
-      <c r="K12" s="343" t="n"/>
-      <c r="L12" s="343" t="n"/>
-      <c r="M12" s="343" t="n"/>
-      <c r="N12" s="343" t="n"/>
-      <c r="O12" s="343" t="n"/>
-      <c r="P12" s="343" t="n"/>
-      <c r="Q12" s="343" t="n"/>
-      <c r="R12" s="343" t="n"/>
-      <c r="S12" s="343" t="n"/>
-      <c r="T12" s="343" t="n"/>
+      <c r="I12" s="411" t="n"/>
+      <c r="J12" s="411" t="n"/>
+      <c r="K12" s="411" t="n"/>
+      <c r="L12" s="411" t="n"/>
+      <c r="M12" s="411" t="n"/>
+      <c r="N12" s="411" t="n"/>
+      <c r="O12" s="411" t="n"/>
+      <c r="P12" s="411" t="n"/>
+      <c r="Q12" s="411" t="n"/>
+      <c r="R12" s="411" t="n"/>
+      <c r="S12" s="411" t="n"/>
+      <c r="T12" s="411" t="n"/>
       <c r="U12" s="465" t="inlineStr">
         <is>
           <t>Approval State</t>
         </is>
       </c>
-      <c r="V12" s="343" t="n"/>
-      <c r="W12" s="343" t="n"/>
-      <c r="X12" s="343" t="n"/>
-      <c r="Y12" s="343" t="n"/>
-      <c r="Z12" s="343" t="n"/>
-      <c r="AA12" s="343" t="n"/>
-      <c r="AB12" s="464" t="n"/>
-      <c r="AC12" s="343" t="n"/>
-      <c r="AD12" s="343" t="n"/>
-      <c r="AE12" s="343" t="n"/>
-      <c r="AF12" s="343" t="n"/>
-      <c r="AG12" s="343" t="n"/>
-      <c r="AH12" s="343" t="n"/>
-      <c r="AI12" s="343" t="n"/>
-      <c r="AJ12" s="343" t="n"/>
-      <c r="AK12" s="343" t="n"/>
-      <c r="AL12" s="343" t="n"/>
-      <c r="AM12" s="343" t="n"/>
-      <c r="AN12" s="466" t="n"/>
+      <c r="V12" s="411" t="n"/>
+      <c r="W12" s="411" t="n"/>
+      <c r="X12" s="411" t="n"/>
+      <c r="Y12" s="411" t="n"/>
+      <c r="Z12" s="411" t="n"/>
+      <c r="AA12" s="411" t="n"/>
+      <c r="AB12" s="557" t="n"/>
+      <c r="AC12" s="411" t="n"/>
+      <c r="AD12" s="411" t="n"/>
+      <c r="AE12" s="411" t="n"/>
+      <c r="AF12" s="411" t="n"/>
+      <c r="AG12" s="411" t="n"/>
+      <c r="AH12" s="411" t="n"/>
+      <c r="AI12" s="411" t="n"/>
+      <c r="AJ12" s="411" t="n"/>
+      <c r="AK12" s="411" t="n"/>
+      <c r="AL12" s="411" t="n"/>
+      <c r="AM12" s="411" t="n"/>
+      <c r="AN12" s="558" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1" s="329">
       <c r="A13" s="467" t="inlineStr">
@@ -6394,49 +6803,49 @@
           <t>Route Step / Due Date</t>
         </is>
       </c>
-      <c r="B13" s="468" t="n"/>
-      <c r="C13" s="468" t="n"/>
-      <c r="D13" s="468" t="n"/>
-      <c r="E13" s="468" t="n"/>
-      <c r="F13" s="468" t="n"/>
-      <c r="G13" s="468" t="n"/>
+      <c r="B13" s="547" t="n"/>
+      <c r="C13" s="547" t="n"/>
+      <c r="D13" s="547" t="n"/>
+      <c r="E13" s="547" t="n"/>
+      <c r="F13" s="547" t="n"/>
+      <c r="G13" s="547" t="n"/>
       <c r="H13" s="469" t="n"/>
-      <c r="I13" s="468" t="n"/>
-      <c r="J13" s="468" t="n"/>
-      <c r="K13" s="468" t="n"/>
-      <c r="L13" s="468" t="n"/>
-      <c r="M13" s="468" t="n"/>
-      <c r="N13" s="468" t="n"/>
-      <c r="O13" s="468" t="n"/>
-      <c r="P13" s="468" t="n"/>
-      <c r="Q13" s="468" t="n"/>
-      <c r="R13" s="468" t="n"/>
-      <c r="S13" s="468" t="n"/>
-      <c r="T13" s="468" t="n"/>
+      <c r="I13" s="547" t="n"/>
+      <c r="J13" s="547" t="n"/>
+      <c r="K13" s="547" t="n"/>
+      <c r="L13" s="547" t="n"/>
+      <c r="M13" s="547" t="n"/>
+      <c r="N13" s="547" t="n"/>
+      <c r="O13" s="547" t="n"/>
+      <c r="P13" s="547" t="n"/>
+      <c r="Q13" s="547" t="n"/>
+      <c r="R13" s="547" t="n"/>
+      <c r="S13" s="547" t="n"/>
+      <c r="T13" s="547" t="n"/>
       <c r="U13" s="470" t="inlineStr">
         <is>
           <t>Package Ref</t>
         </is>
       </c>
-      <c r="V13" s="468" t="n"/>
-      <c r="W13" s="468" t="n"/>
-      <c r="X13" s="468" t="n"/>
-      <c r="Y13" s="468" t="n"/>
-      <c r="Z13" s="468" t="n"/>
-      <c r="AA13" s="468" t="n"/>
-      <c r="AB13" s="469" t="n"/>
-      <c r="AC13" s="468" t="n"/>
-      <c r="AD13" s="468" t="n"/>
-      <c r="AE13" s="468" t="n"/>
-      <c r="AF13" s="468" t="n"/>
-      <c r="AG13" s="468" t="n"/>
-      <c r="AH13" s="468" t="n"/>
-      <c r="AI13" s="468" t="n"/>
-      <c r="AJ13" s="468" t="n"/>
-      <c r="AK13" s="468" t="n"/>
-      <c r="AL13" s="468" t="n"/>
-      <c r="AM13" s="468" t="n"/>
-      <c r="AN13" s="471" t="n"/>
+      <c r="V13" s="547" t="n"/>
+      <c r="W13" s="547" t="n"/>
+      <c r="X13" s="547" t="n"/>
+      <c r="Y13" s="547" t="n"/>
+      <c r="Z13" s="547" t="n"/>
+      <c r="AA13" s="547" t="n"/>
+      <c r="AB13" s="559" t="n"/>
+      <c r="AC13" s="547" t="n"/>
+      <c r="AD13" s="547" t="n"/>
+      <c r="AE13" s="547" t="n"/>
+      <c r="AF13" s="547" t="n"/>
+      <c r="AG13" s="547" t="n"/>
+      <c r="AH13" s="547" t="n"/>
+      <c r="AI13" s="547" t="n"/>
+      <c r="AJ13" s="547" t="n"/>
+      <c r="AK13" s="547" t="n"/>
+      <c r="AL13" s="547" t="n"/>
+      <c r="AM13" s="547" t="n"/>
+      <c r="AN13" s="550" t="n"/>
     </row>
     <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="359" t="n"/>
@@ -6481,50 +6890,50 @@
       <c r="AN14" s="352" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="329">
-      <c r="A15" s="455" t="inlineStr">
+      <c r="A15" s="551" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
         </is>
       </c>
-      <c r="B15" s="456" t="n"/>
-      <c r="C15" s="456" t="n"/>
-      <c r="D15" s="456" t="n"/>
-      <c r="E15" s="456" t="n"/>
-      <c r="F15" s="456" t="n"/>
-      <c r="G15" s="456" t="n"/>
-      <c r="H15" s="456" t="n"/>
-      <c r="I15" s="456" t="n"/>
-      <c r="J15" s="456" t="n"/>
-      <c r="K15" s="456" t="n"/>
-      <c r="L15" s="456" t="n"/>
-      <c r="M15" s="456" t="n"/>
-      <c r="N15" s="456" t="n"/>
-      <c r="O15" s="456" t="n"/>
-      <c r="P15" s="456" t="n"/>
-      <c r="Q15" s="456" t="n"/>
-      <c r="R15" s="456" t="n"/>
-      <c r="S15" s="456" t="n"/>
-      <c r="T15" s="456" t="n"/>
-      <c r="U15" s="456" t="n"/>
-      <c r="V15" s="456" t="n"/>
-      <c r="W15" s="456" t="n"/>
-      <c r="X15" s="456" t="n"/>
-      <c r="Y15" s="456" t="n"/>
-      <c r="Z15" s="456" t="n"/>
-      <c r="AA15" s="456" t="n"/>
-      <c r="AB15" s="456" t="n"/>
-      <c r="AC15" s="456" t="n"/>
-      <c r="AD15" s="456" t="n"/>
-      <c r="AE15" s="456" t="n"/>
-      <c r="AF15" s="456" t="n"/>
-      <c r="AG15" s="456" t="n"/>
-      <c r="AH15" s="456" t="n"/>
-      <c r="AI15" s="456" t="n"/>
-      <c r="AJ15" s="456" t="n"/>
-      <c r="AK15" s="456" t="n"/>
-      <c r="AL15" s="456" t="n"/>
-      <c r="AM15" s="456" t="n"/>
-      <c r="AN15" s="457" t="n"/>
+      <c r="B15" s="552" t="n"/>
+      <c r="C15" s="552" t="n"/>
+      <c r="D15" s="552" t="n"/>
+      <c r="E15" s="552" t="n"/>
+      <c r="F15" s="552" t="n"/>
+      <c r="G15" s="552" t="n"/>
+      <c r="H15" s="552" t="n"/>
+      <c r="I15" s="552" t="n"/>
+      <c r="J15" s="552" t="n"/>
+      <c r="K15" s="552" t="n"/>
+      <c r="L15" s="552" t="n"/>
+      <c r="M15" s="552" t="n"/>
+      <c r="N15" s="552" t="n"/>
+      <c r="O15" s="552" t="n"/>
+      <c r="P15" s="552" t="n"/>
+      <c r="Q15" s="552" t="n"/>
+      <c r="R15" s="552" t="n"/>
+      <c r="S15" s="552" t="n"/>
+      <c r="T15" s="552" t="n"/>
+      <c r="U15" s="552" t="n"/>
+      <c r="V15" s="552" t="n"/>
+      <c r="W15" s="552" t="n"/>
+      <c r="X15" s="552" t="n"/>
+      <c r="Y15" s="552" t="n"/>
+      <c r="Z15" s="552" t="n"/>
+      <c r="AA15" s="552" t="n"/>
+      <c r="AB15" s="552" t="n"/>
+      <c r="AC15" s="552" t="n"/>
+      <c r="AD15" s="552" t="n"/>
+      <c r="AE15" s="552" t="n"/>
+      <c r="AF15" s="552" t="n"/>
+      <c r="AG15" s="552" t="n"/>
+      <c r="AH15" s="552" t="n"/>
+      <c r="AI15" s="552" t="n"/>
+      <c r="AJ15" s="552" t="n"/>
+      <c r="AK15" s="552" t="n"/>
+      <c r="AL15" s="552" t="n"/>
+      <c r="AM15" s="552" t="n"/>
+      <c r="AN15" s="553" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
       <c r="A16" s="458" t="inlineStr">
@@ -6532,49 +6941,49 @@
           <t>Release Status</t>
         </is>
       </c>
-      <c r="B16" s="459" t="n"/>
-      <c r="C16" s="459" t="n"/>
-      <c r="D16" s="459" t="n"/>
-      <c r="E16" s="459" t="n"/>
-      <c r="F16" s="459" t="n"/>
-      <c r="G16" s="459" t="n"/>
+      <c r="B16" s="554" t="n"/>
+      <c r="C16" s="554" t="n"/>
+      <c r="D16" s="554" t="n"/>
+      <c r="E16" s="554" t="n"/>
+      <c r="F16" s="554" t="n"/>
+      <c r="G16" s="554" t="n"/>
       <c r="H16" s="460" t="n"/>
-      <c r="I16" s="459" t="n"/>
-      <c r="J16" s="459" t="n"/>
-      <c r="K16" s="459" t="n"/>
-      <c r="L16" s="459" t="n"/>
-      <c r="M16" s="459" t="n"/>
-      <c r="N16" s="459" t="n"/>
-      <c r="O16" s="459" t="n"/>
-      <c r="P16" s="459" t="n"/>
-      <c r="Q16" s="459" t="n"/>
-      <c r="R16" s="459" t="n"/>
-      <c r="S16" s="459" t="n"/>
-      <c r="T16" s="459" t="n"/>
+      <c r="I16" s="554" t="n"/>
+      <c r="J16" s="554" t="n"/>
+      <c r="K16" s="554" t="n"/>
+      <c r="L16" s="554" t="n"/>
+      <c r="M16" s="554" t="n"/>
+      <c r="N16" s="554" t="n"/>
+      <c r="O16" s="554" t="n"/>
+      <c r="P16" s="554" t="n"/>
+      <c r="Q16" s="554" t="n"/>
+      <c r="R16" s="554" t="n"/>
+      <c r="S16" s="554" t="n"/>
+      <c r="T16" s="554" t="n"/>
       <c r="U16" s="461" t="inlineStr">
         <is>
           <t>Linked Route / Package</t>
         </is>
       </c>
-      <c r="V16" s="459" t="n"/>
-      <c r="W16" s="459" t="n"/>
-      <c r="X16" s="459" t="n"/>
-      <c r="Y16" s="459" t="n"/>
-      <c r="Z16" s="459" t="n"/>
-      <c r="AA16" s="459" t="n"/>
-      <c r="AB16" s="460" t="n"/>
-      <c r="AC16" s="459" t="n"/>
-      <c r="AD16" s="459" t="n"/>
-      <c r="AE16" s="459" t="n"/>
-      <c r="AF16" s="459" t="n"/>
-      <c r="AG16" s="459" t="n"/>
-      <c r="AH16" s="459" t="n"/>
-      <c r="AI16" s="459" t="n"/>
-      <c r="AJ16" s="459" t="n"/>
-      <c r="AK16" s="459" t="n"/>
-      <c r="AL16" s="459" t="n"/>
-      <c r="AM16" s="459" t="n"/>
-      <c r="AN16" s="462" t="n"/>
+      <c r="V16" s="554" t="n"/>
+      <c r="W16" s="554" t="n"/>
+      <c r="X16" s="554" t="n"/>
+      <c r="Y16" s="554" t="n"/>
+      <c r="Z16" s="554" t="n"/>
+      <c r="AA16" s="554" t="n"/>
+      <c r="AB16" s="555" t="n"/>
+      <c r="AC16" s="554" t="n"/>
+      <c r="AD16" s="554" t="n"/>
+      <c r="AE16" s="554" t="n"/>
+      <c r="AF16" s="554" t="n"/>
+      <c r="AG16" s="554" t="n"/>
+      <c r="AH16" s="554" t="n"/>
+      <c r="AI16" s="554" t="n"/>
+      <c r="AJ16" s="554" t="n"/>
+      <c r="AK16" s="554" t="n"/>
+      <c r="AL16" s="554" t="n"/>
+      <c r="AM16" s="554" t="n"/>
+      <c r="AN16" s="556" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
       <c r="A17" s="463" t="inlineStr">
@@ -6582,309 +6991,309 @@
           <t>Supplier / Customer Spec Ref</t>
         </is>
       </c>
-      <c r="B17" s="343" t="n"/>
-      <c r="C17" s="343" t="n"/>
-      <c r="D17" s="343" t="n"/>
-      <c r="E17" s="343" t="n"/>
-      <c r="F17" s="343" t="n"/>
-      <c r="G17" s="343" t="n"/>
+      <c r="B17" s="411" t="n"/>
+      <c r="C17" s="411" t="n"/>
+      <c r="D17" s="411" t="n"/>
+      <c r="E17" s="411" t="n"/>
+      <c r="F17" s="411" t="n"/>
+      <c r="G17" s="411" t="n"/>
       <c r="H17" s="464" t="n"/>
-      <c r="I17" s="343" t="n"/>
-      <c r="J17" s="343" t="n"/>
-      <c r="K17" s="343" t="n"/>
-      <c r="L17" s="343" t="n"/>
-      <c r="M17" s="343" t="n"/>
-      <c r="N17" s="343" t="n"/>
-      <c r="O17" s="343" t="n"/>
-      <c r="P17" s="343" t="n"/>
-      <c r="Q17" s="343" t="n"/>
-      <c r="R17" s="343" t="n"/>
-      <c r="S17" s="343" t="n"/>
-      <c r="T17" s="343" t="n"/>
+      <c r="I17" s="411" t="n"/>
+      <c r="J17" s="411" t="n"/>
+      <c r="K17" s="411" t="n"/>
+      <c r="L17" s="411" t="n"/>
+      <c r="M17" s="411" t="n"/>
+      <c r="N17" s="411" t="n"/>
+      <c r="O17" s="411" t="n"/>
+      <c r="P17" s="411" t="n"/>
+      <c r="Q17" s="411" t="n"/>
+      <c r="R17" s="411" t="n"/>
+      <c r="S17" s="411" t="n"/>
+      <c r="T17" s="411" t="n"/>
       <c r="U17" s="465" t="inlineStr">
         <is>
           <t>Open Actions Present (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="343" t="n"/>
-      <c r="W17" s="343" t="n"/>
-      <c r="X17" s="343" t="n"/>
-      <c r="Y17" s="343" t="n"/>
-      <c r="Z17" s="343" t="n"/>
-      <c r="AA17" s="343" t="n"/>
-      <c r="AB17" s="464" t="n"/>
-      <c r="AC17" s="343" t="n"/>
-      <c r="AD17" s="343" t="n"/>
-      <c r="AE17" s="343" t="n"/>
-      <c r="AF17" s="343" t="n"/>
-      <c r="AG17" s="343" t="n"/>
-      <c r="AH17" s="343" t="n"/>
-      <c r="AI17" s="343" t="n"/>
-      <c r="AJ17" s="343" t="n"/>
-      <c r="AK17" s="343" t="n"/>
-      <c r="AL17" s="343" t="n"/>
-      <c r="AM17" s="343" t="n"/>
-      <c r="AN17" s="466" t="n"/>
+      <c r="V17" s="411" t="n"/>
+      <c r="W17" s="411" t="n"/>
+      <c r="X17" s="411" t="n"/>
+      <c r="Y17" s="411" t="n"/>
+      <c r="Z17" s="411" t="n"/>
+      <c r="AA17" s="411" t="n"/>
+      <c r="AB17" s="557" t="n"/>
+      <c r="AC17" s="411" t="n"/>
+      <c r="AD17" s="411" t="n"/>
+      <c r="AE17" s="411" t="n"/>
+      <c r="AF17" s="411" t="n"/>
+      <c r="AG17" s="411" t="n"/>
+      <c r="AH17" s="411" t="n"/>
+      <c r="AI17" s="411" t="n"/>
+      <c r="AJ17" s="411" t="n"/>
+      <c r="AK17" s="411" t="n"/>
+      <c r="AL17" s="411" t="n"/>
+      <c r="AM17" s="411" t="n"/>
+      <c r="AN17" s="558" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="463" t="inlineStr">
+      <c r="A18" s="560" t="inlineStr">
         <is>
           <t>DISPATCH NOTES / CONDITIONALS</t>
         </is>
       </c>
-      <c r="B18" s="343" t="n"/>
-      <c r="C18" s="343" t="n"/>
-      <c r="D18" s="343" t="n"/>
-      <c r="E18" s="343" t="n"/>
-      <c r="F18" s="343" t="n"/>
-      <c r="G18" s="343" t="n"/>
-      <c r="H18" s="472" t="n"/>
-      <c r="I18" s="343" t="n"/>
-      <c r="J18" s="343" t="n"/>
-      <c r="K18" s="343" t="n"/>
-      <c r="L18" s="343" t="n"/>
-      <c r="M18" s="343" t="n"/>
-      <c r="N18" s="343" t="n"/>
-      <c r="O18" s="343" t="n"/>
-      <c r="P18" s="343" t="n"/>
-      <c r="Q18" s="343" t="n"/>
-      <c r="R18" s="343" t="n"/>
-      <c r="S18" s="343" t="n"/>
-      <c r="T18" s="343" t="n"/>
-      <c r="U18" s="472" t="n"/>
-      <c r="V18" s="343" t="n"/>
-      <c r="W18" s="343" t="n"/>
-      <c r="X18" s="343" t="n"/>
-      <c r="Y18" s="343" t="n"/>
-      <c r="Z18" s="343" t="n"/>
-      <c r="AA18" s="343" t="n"/>
-      <c r="AB18" s="472" t="n"/>
-      <c r="AC18" s="343" t="n"/>
-      <c r="AD18" s="343" t="n"/>
-      <c r="AE18" s="343" t="n"/>
-      <c r="AF18" s="343" t="n"/>
-      <c r="AG18" s="343" t="n"/>
-      <c r="AH18" s="343" t="n"/>
-      <c r="AI18" s="343" t="n"/>
-      <c r="AJ18" s="343" t="n"/>
-      <c r="AK18" s="343" t="n"/>
-      <c r="AL18" s="343" t="n"/>
-      <c r="AM18" s="343" t="n"/>
-      <c r="AN18" s="466" t="n"/>
+      <c r="B18" s="411" t="n"/>
+      <c r="C18" s="411" t="n"/>
+      <c r="D18" s="411" t="n"/>
+      <c r="E18" s="411" t="n"/>
+      <c r="F18" s="411" t="n"/>
+      <c r="G18" s="411" t="n"/>
+      <c r="H18" s="411" t="n"/>
+      <c r="I18" s="411" t="n"/>
+      <c r="J18" s="411" t="n"/>
+      <c r="K18" s="411" t="n"/>
+      <c r="L18" s="411" t="n"/>
+      <c r="M18" s="411" t="n"/>
+      <c r="N18" s="411" t="n"/>
+      <c r="O18" s="411" t="n"/>
+      <c r="P18" s="411" t="n"/>
+      <c r="Q18" s="411" t="n"/>
+      <c r="R18" s="411" t="n"/>
+      <c r="S18" s="411" t="n"/>
+      <c r="T18" s="411" t="n"/>
+      <c r="U18" s="411" t="n"/>
+      <c r="V18" s="411" t="n"/>
+      <c r="W18" s="411" t="n"/>
+      <c r="X18" s="411" t="n"/>
+      <c r="Y18" s="411" t="n"/>
+      <c r="Z18" s="411" t="n"/>
+      <c r="AA18" s="411" t="n"/>
+      <c r="AB18" s="411" t="n"/>
+      <c r="AC18" s="411" t="n"/>
+      <c r="AD18" s="411" t="n"/>
+      <c r="AE18" s="411" t="n"/>
+      <c r="AF18" s="411" t="n"/>
+      <c r="AG18" s="411" t="n"/>
+      <c r="AH18" s="411" t="n"/>
+      <c r="AI18" s="411" t="n"/>
+      <c r="AJ18" s="411" t="n"/>
+      <c r="AK18" s="411" t="n"/>
+      <c r="AL18" s="411" t="n"/>
+      <c r="AM18" s="411" t="n"/>
+      <c r="AN18" s="558" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="473" t="n"/>
-      <c r="B19" s="343" t="n"/>
-      <c r="C19" s="343" t="n"/>
-      <c r="D19" s="343" t="n"/>
-      <c r="E19" s="343" t="n"/>
-      <c r="F19" s="343" t="n"/>
-      <c r="G19" s="343" t="n"/>
-      <c r="H19" s="472" t="n"/>
-      <c r="I19" s="343" t="n"/>
-      <c r="J19" s="343" t="n"/>
-      <c r="K19" s="343" t="n"/>
-      <c r="L19" s="343" t="n"/>
-      <c r="M19" s="343" t="n"/>
-      <c r="N19" s="343" t="n"/>
-      <c r="O19" s="343" t="n"/>
-      <c r="P19" s="343" t="n"/>
-      <c r="Q19" s="343" t="n"/>
-      <c r="R19" s="343" t="n"/>
-      <c r="S19" s="343" t="n"/>
-      <c r="T19" s="343" t="n"/>
-      <c r="U19" s="472" t="n"/>
-      <c r="V19" s="343" t="n"/>
-      <c r="W19" s="343" t="n"/>
-      <c r="X19" s="343" t="n"/>
-      <c r="Y19" s="343" t="n"/>
-      <c r="Z19" s="343" t="n"/>
-      <c r="AA19" s="343" t="n"/>
-      <c r="AB19" s="472" t="n"/>
-      <c r="AC19" s="343" t="n"/>
-      <c r="AD19" s="343" t="n"/>
-      <c r="AE19" s="343" t="n"/>
-      <c r="AF19" s="343" t="n"/>
-      <c r="AG19" s="343" t="n"/>
-      <c r="AH19" s="343" t="n"/>
-      <c r="AI19" s="343" t="n"/>
-      <c r="AJ19" s="343" t="n"/>
-      <c r="AK19" s="343" t="n"/>
-      <c r="AL19" s="343" t="n"/>
-      <c r="AM19" s="343" t="n"/>
-      <c r="AN19" s="466" t="n"/>
+      <c r="A19" s="561" t="n"/>
+      <c r="B19" s="410" t="n"/>
+      <c r="C19" s="410" t="n"/>
+      <c r="D19" s="410" t="n"/>
+      <c r="E19" s="410" t="n"/>
+      <c r="F19" s="410" t="n"/>
+      <c r="G19" s="410" t="n"/>
+      <c r="H19" s="410" t="n"/>
+      <c r="I19" s="410" t="n"/>
+      <c r="J19" s="410" t="n"/>
+      <c r="K19" s="410" t="n"/>
+      <c r="L19" s="410" t="n"/>
+      <c r="M19" s="410" t="n"/>
+      <c r="N19" s="410" t="n"/>
+      <c r="O19" s="410" t="n"/>
+      <c r="P19" s="410" t="n"/>
+      <c r="Q19" s="410" t="n"/>
+      <c r="R19" s="410" t="n"/>
+      <c r="S19" s="410" t="n"/>
+      <c r="T19" s="410" t="n"/>
+      <c r="U19" s="410" t="n"/>
+      <c r="V19" s="410" t="n"/>
+      <c r="W19" s="410" t="n"/>
+      <c r="X19" s="410" t="n"/>
+      <c r="Y19" s="410" t="n"/>
+      <c r="Z19" s="410" t="n"/>
+      <c r="AA19" s="410" t="n"/>
+      <c r="AB19" s="410" t="n"/>
+      <c r="AC19" s="410" t="n"/>
+      <c r="AD19" s="410" t="n"/>
+      <c r="AE19" s="410" t="n"/>
+      <c r="AF19" s="410" t="n"/>
+      <c r="AG19" s="410" t="n"/>
+      <c r="AH19" s="410" t="n"/>
+      <c r="AI19" s="410" t="n"/>
+      <c r="AJ19" s="410" t="n"/>
+      <c r="AK19" s="410" t="n"/>
+      <c r="AL19" s="410" t="n"/>
+      <c r="AM19" s="410" t="n"/>
+      <c r="AN19" s="540" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="474" t="n"/>
-      <c r="B20" s="343" t="n"/>
-      <c r="C20" s="343" t="n"/>
-      <c r="D20" s="343" t="n"/>
-      <c r="E20" s="343" t="n"/>
-      <c r="F20" s="343" t="n"/>
-      <c r="G20" s="343" t="n"/>
-      <c r="H20" s="472" t="n"/>
-      <c r="I20" s="343" t="n"/>
-      <c r="J20" s="343" t="n"/>
-      <c r="K20" s="343" t="n"/>
-      <c r="L20" s="343" t="n"/>
-      <c r="M20" s="343" t="n"/>
-      <c r="N20" s="343" t="n"/>
-      <c r="O20" s="343" t="n"/>
-      <c r="P20" s="343" t="n"/>
-      <c r="Q20" s="343" t="n"/>
-      <c r="R20" s="343" t="n"/>
-      <c r="S20" s="343" t="n"/>
-      <c r="T20" s="343" t="n"/>
-      <c r="U20" s="472" t="n"/>
-      <c r="V20" s="343" t="n"/>
-      <c r="W20" s="343" t="n"/>
-      <c r="X20" s="343" t="n"/>
-      <c r="Y20" s="343" t="n"/>
-      <c r="Z20" s="343" t="n"/>
-      <c r="AA20" s="343" t="n"/>
-      <c r="AB20" s="472" t="n"/>
-      <c r="AC20" s="343" t="n"/>
-      <c r="AD20" s="343" t="n"/>
-      <c r="AE20" s="343" t="n"/>
-      <c r="AF20" s="343" t="n"/>
-      <c r="AG20" s="343" t="n"/>
-      <c r="AH20" s="343" t="n"/>
-      <c r="AI20" s="343" t="n"/>
-      <c r="AJ20" s="343" t="n"/>
-      <c r="AK20" s="343" t="n"/>
-      <c r="AL20" s="343" t="n"/>
-      <c r="AM20" s="343" t="n"/>
-      <c r="AN20" s="466" t="n"/>
+      <c r="A20" s="562" t="n"/>
+      <c r="B20" s="415" t="n"/>
+      <c r="C20" s="415" t="n"/>
+      <c r="D20" s="415" t="n"/>
+      <c r="E20" s="415" t="n"/>
+      <c r="F20" s="415" t="n"/>
+      <c r="G20" s="415" t="n"/>
+      <c r="H20" s="415" t="n"/>
+      <c r="I20" s="415" t="n"/>
+      <c r="J20" s="415" t="n"/>
+      <c r="K20" s="415" t="n"/>
+      <c r="L20" s="415" t="n"/>
+      <c r="M20" s="415" t="n"/>
+      <c r="N20" s="415" t="n"/>
+      <c r="O20" s="415" t="n"/>
+      <c r="P20" s="415" t="n"/>
+      <c r="Q20" s="415" t="n"/>
+      <c r="R20" s="415" t="n"/>
+      <c r="S20" s="415" t="n"/>
+      <c r="T20" s="415" t="n"/>
+      <c r="U20" s="415" t="n"/>
+      <c r="V20" s="415" t="n"/>
+      <c r="W20" s="415" t="n"/>
+      <c r="X20" s="415" t="n"/>
+      <c r="Y20" s="415" t="n"/>
+      <c r="Z20" s="415" t="n"/>
+      <c r="AA20" s="415" t="n"/>
+      <c r="AB20" s="415" t="n"/>
+      <c r="AC20" s="415" t="n"/>
+      <c r="AD20" s="415" t="n"/>
+      <c r="AE20" s="415" t="n"/>
+      <c r="AF20" s="415" t="n"/>
+      <c r="AG20" s="415" t="n"/>
+      <c r="AH20" s="415" t="n"/>
+      <c r="AI20" s="415" t="n"/>
+      <c r="AJ20" s="415" t="n"/>
+      <c r="AK20" s="415" t="n"/>
+      <c r="AL20" s="415" t="n"/>
+      <c r="AM20" s="415" t="n"/>
+      <c r="AN20" s="563" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="463" t="inlineStr">
+      <c r="A21" s="560" t="inlineStr">
         <is>
           <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
         </is>
       </c>
-      <c r="B21" s="343" t="n"/>
-      <c r="C21" s="343" t="n"/>
-      <c r="D21" s="343" t="n"/>
-      <c r="E21" s="343" t="n"/>
-      <c r="F21" s="343" t="n"/>
-      <c r="G21" s="343" t="n"/>
-      <c r="H21" s="472" t="n"/>
-      <c r="I21" s="343" t="n"/>
-      <c r="J21" s="343" t="n"/>
-      <c r="K21" s="343" t="n"/>
-      <c r="L21" s="343" t="n"/>
-      <c r="M21" s="343" t="n"/>
-      <c r="N21" s="343" t="n"/>
-      <c r="O21" s="343" t="n"/>
-      <c r="P21" s="343" t="n"/>
-      <c r="Q21" s="343" t="n"/>
-      <c r="R21" s="343" t="n"/>
-      <c r="S21" s="343" t="n"/>
-      <c r="T21" s="343" t="n"/>
-      <c r="U21" s="472" t="n"/>
-      <c r="V21" s="343" t="n"/>
-      <c r="W21" s="343" t="n"/>
-      <c r="X21" s="343" t="n"/>
-      <c r="Y21" s="343" t="n"/>
-      <c r="Z21" s="343" t="n"/>
-      <c r="AA21" s="343" t="n"/>
-      <c r="AB21" s="472" t="n"/>
-      <c r="AC21" s="343" t="n"/>
-      <c r="AD21" s="343" t="n"/>
-      <c r="AE21" s="343" t="n"/>
-      <c r="AF21" s="343" t="n"/>
-      <c r="AG21" s="343" t="n"/>
-      <c r="AH21" s="343" t="n"/>
-      <c r="AI21" s="343" t="n"/>
-      <c r="AJ21" s="343" t="n"/>
-      <c r="AK21" s="343" t="n"/>
-      <c r="AL21" s="343" t="n"/>
-      <c r="AM21" s="343" t="n"/>
-      <c r="AN21" s="466" t="n"/>
+      <c r="B21" s="411" t="n"/>
+      <c r="C21" s="411" t="n"/>
+      <c r="D21" s="411" t="n"/>
+      <c r="E21" s="411" t="n"/>
+      <c r="F21" s="411" t="n"/>
+      <c r="G21" s="411" t="n"/>
+      <c r="H21" s="411" t="n"/>
+      <c r="I21" s="411" t="n"/>
+      <c r="J21" s="411" t="n"/>
+      <c r="K21" s="411" t="n"/>
+      <c r="L21" s="411" t="n"/>
+      <c r="M21" s="411" t="n"/>
+      <c r="N21" s="411" t="n"/>
+      <c r="O21" s="411" t="n"/>
+      <c r="P21" s="411" t="n"/>
+      <c r="Q21" s="411" t="n"/>
+      <c r="R21" s="411" t="n"/>
+      <c r="S21" s="411" t="n"/>
+      <c r="T21" s="411" t="n"/>
+      <c r="U21" s="411" t="n"/>
+      <c r="V21" s="411" t="n"/>
+      <c r="W21" s="411" t="n"/>
+      <c r="X21" s="411" t="n"/>
+      <c r="Y21" s="411" t="n"/>
+      <c r="Z21" s="411" t="n"/>
+      <c r="AA21" s="411" t="n"/>
+      <c r="AB21" s="411" t="n"/>
+      <c r="AC21" s="411" t="n"/>
+      <c r="AD21" s="411" t="n"/>
+      <c r="AE21" s="411" t="n"/>
+      <c r="AF21" s="411" t="n"/>
+      <c r="AG21" s="411" t="n"/>
+      <c r="AH21" s="411" t="n"/>
+      <c r="AI21" s="411" t="n"/>
+      <c r="AJ21" s="411" t="n"/>
+      <c r="AK21" s="411" t="n"/>
+      <c r="AL21" s="411" t="n"/>
+      <c r="AM21" s="411" t="n"/>
+      <c r="AN21" s="558" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="473" t="n"/>
-      <c r="B22" s="343" t="n"/>
-      <c r="C22" s="343" t="n"/>
-      <c r="D22" s="343" t="n"/>
-      <c r="E22" s="343" t="n"/>
-      <c r="F22" s="343" t="n"/>
-      <c r="G22" s="343" t="n"/>
-      <c r="H22" s="472" t="n"/>
-      <c r="I22" s="343" t="n"/>
-      <c r="J22" s="343" t="n"/>
-      <c r="K22" s="343" t="n"/>
-      <c r="L22" s="343" t="n"/>
-      <c r="M22" s="343" t="n"/>
-      <c r="N22" s="343" t="n"/>
-      <c r="O22" s="343" t="n"/>
-      <c r="P22" s="343" t="n"/>
-      <c r="Q22" s="343" t="n"/>
-      <c r="R22" s="343" t="n"/>
-      <c r="S22" s="343" t="n"/>
-      <c r="T22" s="343" t="n"/>
-      <c r="U22" s="472" t="n"/>
-      <c r="V22" s="343" t="n"/>
-      <c r="W22" s="343" t="n"/>
-      <c r="X22" s="343" t="n"/>
-      <c r="Y22" s="343" t="n"/>
-      <c r="Z22" s="343" t="n"/>
-      <c r="AA22" s="343" t="n"/>
-      <c r="AB22" s="472" t="n"/>
-      <c r="AC22" s="343" t="n"/>
-      <c r="AD22" s="343" t="n"/>
-      <c r="AE22" s="343" t="n"/>
-      <c r="AF22" s="343" t="n"/>
-      <c r="AG22" s="343" t="n"/>
-      <c r="AH22" s="343" t="n"/>
-      <c r="AI22" s="343" t="n"/>
-      <c r="AJ22" s="343" t="n"/>
-      <c r="AK22" s="343" t="n"/>
-      <c r="AL22" s="343" t="n"/>
-      <c r="AM22" s="343" t="n"/>
-      <c r="AN22" s="466" t="n"/>
+      <c r="A22" s="561" t="n"/>
+      <c r="B22" s="410" t="n"/>
+      <c r="C22" s="410" t="n"/>
+      <c r="D22" s="410" t="n"/>
+      <c r="E22" s="410" t="n"/>
+      <c r="F22" s="410" t="n"/>
+      <c r="G22" s="410" t="n"/>
+      <c r="H22" s="410" t="n"/>
+      <c r="I22" s="410" t="n"/>
+      <c r="J22" s="410" t="n"/>
+      <c r="K22" s="410" t="n"/>
+      <c r="L22" s="410" t="n"/>
+      <c r="M22" s="410" t="n"/>
+      <c r="N22" s="410" t="n"/>
+      <c r="O22" s="410" t="n"/>
+      <c r="P22" s="410" t="n"/>
+      <c r="Q22" s="410" t="n"/>
+      <c r="R22" s="410" t="n"/>
+      <c r="S22" s="410" t="n"/>
+      <c r="T22" s="410" t="n"/>
+      <c r="U22" s="410" t="n"/>
+      <c r="V22" s="410" t="n"/>
+      <c r="W22" s="410" t="n"/>
+      <c r="X22" s="410" t="n"/>
+      <c r="Y22" s="410" t="n"/>
+      <c r="Z22" s="410" t="n"/>
+      <c r="AA22" s="410" t="n"/>
+      <c r="AB22" s="410" t="n"/>
+      <c r="AC22" s="410" t="n"/>
+      <c r="AD22" s="410" t="n"/>
+      <c r="AE22" s="410" t="n"/>
+      <c r="AF22" s="410" t="n"/>
+      <c r="AG22" s="410" t="n"/>
+      <c r="AH22" s="410" t="n"/>
+      <c r="AI22" s="410" t="n"/>
+      <c r="AJ22" s="410" t="n"/>
+      <c r="AK22" s="410" t="n"/>
+      <c r="AL22" s="410" t="n"/>
+      <c r="AM22" s="410" t="n"/>
+      <c r="AN22" s="540" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="475" t="n"/>
-      <c r="B23" s="468" t="n"/>
-      <c r="C23" s="468" t="n"/>
-      <c r="D23" s="468" t="n"/>
-      <c r="E23" s="468" t="n"/>
-      <c r="F23" s="468" t="n"/>
-      <c r="G23" s="468" t="n"/>
-      <c r="H23" s="476" t="n"/>
-      <c r="I23" s="468" t="n"/>
-      <c r="J23" s="468" t="n"/>
-      <c r="K23" s="468" t="n"/>
-      <c r="L23" s="468" t="n"/>
-      <c r="M23" s="468" t="n"/>
-      <c r="N23" s="468" t="n"/>
-      <c r="O23" s="468" t="n"/>
-      <c r="P23" s="468" t="n"/>
-      <c r="Q23" s="468" t="n"/>
-      <c r="R23" s="468" t="n"/>
-      <c r="S23" s="468" t="n"/>
-      <c r="T23" s="468" t="n"/>
-      <c r="U23" s="476" t="n"/>
-      <c r="V23" s="468" t="n"/>
-      <c r="W23" s="468" t="n"/>
-      <c r="X23" s="468" t="n"/>
-      <c r="Y23" s="468" t="n"/>
-      <c r="Z23" s="468" t="n"/>
-      <c r="AA23" s="468" t="n"/>
-      <c r="AB23" s="476" t="n"/>
-      <c r="AC23" s="468" t="n"/>
-      <c r="AD23" s="468" t="n"/>
-      <c r="AE23" s="468" t="n"/>
-      <c r="AF23" s="468" t="n"/>
-      <c r="AG23" s="468" t="n"/>
-      <c r="AH23" s="468" t="n"/>
-      <c r="AI23" s="468" t="n"/>
-      <c r="AJ23" s="468" t="n"/>
-      <c r="AK23" s="468" t="n"/>
-      <c r="AL23" s="468" t="n"/>
-      <c r="AM23" s="468" t="n"/>
-      <c r="AN23" s="471" t="n"/>
+      <c r="A23" s="562" t="n"/>
+      <c r="B23" s="415" t="n"/>
+      <c r="C23" s="415" t="n"/>
+      <c r="D23" s="415" t="n"/>
+      <c r="E23" s="415" t="n"/>
+      <c r="F23" s="415" t="n"/>
+      <c r="G23" s="415" t="n"/>
+      <c r="H23" s="415" t="n"/>
+      <c r="I23" s="415" t="n"/>
+      <c r="J23" s="415" t="n"/>
+      <c r="K23" s="415" t="n"/>
+      <c r="L23" s="415" t="n"/>
+      <c r="M23" s="415" t="n"/>
+      <c r="N23" s="415" t="n"/>
+      <c r="O23" s="415" t="n"/>
+      <c r="P23" s="415" t="n"/>
+      <c r="Q23" s="415" t="n"/>
+      <c r="R23" s="415" t="n"/>
+      <c r="S23" s="415" t="n"/>
+      <c r="T23" s="415" t="n"/>
+      <c r="U23" s="415" t="n"/>
+      <c r="V23" s="415" t="n"/>
+      <c r="W23" s="415" t="n"/>
+      <c r="X23" s="415" t="n"/>
+      <c r="Y23" s="415" t="n"/>
+      <c r="Z23" s="415" t="n"/>
+      <c r="AA23" s="415" t="n"/>
+      <c r="AB23" s="415" t="n"/>
+      <c r="AC23" s="415" t="n"/>
+      <c r="AD23" s="415" t="n"/>
+      <c r="AE23" s="415" t="n"/>
+      <c r="AF23" s="415" t="n"/>
+      <c r="AG23" s="415" t="n"/>
+      <c r="AH23" s="415" t="n"/>
+      <c r="AI23" s="415" t="n"/>
+      <c r="AJ23" s="415" t="n"/>
+      <c r="AK23" s="415" t="n"/>
+      <c r="AL23" s="415" t="n"/>
+      <c r="AM23" s="415" t="n"/>
+      <c r="AN23" s="563" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="364" t="n"/>
@@ -6929,50 +7338,50 @@
       <c r="AN24" s="352" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="329">
-      <c r="A25" s="455" t="inlineStr">
+      <c r="A25" s="551" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
         </is>
       </c>
-      <c r="B25" s="456" t="n"/>
-      <c r="C25" s="456" t="n"/>
-      <c r="D25" s="456" t="n"/>
-      <c r="E25" s="456" t="n"/>
-      <c r="F25" s="456" t="n"/>
-      <c r="G25" s="456" t="n"/>
-      <c r="H25" s="456" t="n"/>
-      <c r="I25" s="456" t="n"/>
-      <c r="J25" s="456" t="n"/>
-      <c r="K25" s="456" t="n"/>
-      <c r="L25" s="456" t="n"/>
-      <c r="M25" s="456" t="n"/>
-      <c r="N25" s="456" t="n"/>
-      <c r="O25" s="456" t="n"/>
-      <c r="P25" s="456" t="n"/>
-      <c r="Q25" s="456" t="n"/>
-      <c r="R25" s="456" t="n"/>
-      <c r="S25" s="456" t="n"/>
-      <c r="T25" s="456" t="n"/>
-      <c r="U25" s="456" t="n"/>
-      <c r="V25" s="456" t="n"/>
-      <c r="W25" s="456" t="n"/>
-      <c r="X25" s="456" t="n"/>
-      <c r="Y25" s="456" t="n"/>
-      <c r="Z25" s="456" t="n"/>
-      <c r="AA25" s="456" t="n"/>
-      <c r="AB25" s="456" t="n"/>
-      <c r="AC25" s="456" t="n"/>
-      <c r="AD25" s="456" t="n"/>
-      <c r="AE25" s="456" t="n"/>
-      <c r="AF25" s="456" t="n"/>
-      <c r="AG25" s="456" t="n"/>
-      <c r="AH25" s="456" t="n"/>
-      <c r="AI25" s="456" t="n"/>
-      <c r="AJ25" s="456" t="n"/>
-      <c r="AK25" s="456" t="n"/>
-      <c r="AL25" s="456" t="n"/>
-      <c r="AM25" s="456" t="n"/>
-      <c r="AN25" s="457" t="n"/>
+      <c r="B25" s="552" t="n"/>
+      <c r="C25" s="552" t="n"/>
+      <c r="D25" s="552" t="n"/>
+      <c r="E25" s="552" t="n"/>
+      <c r="F25" s="552" t="n"/>
+      <c r="G25" s="552" t="n"/>
+      <c r="H25" s="552" t="n"/>
+      <c r="I25" s="552" t="n"/>
+      <c r="J25" s="552" t="n"/>
+      <c r="K25" s="552" t="n"/>
+      <c r="L25" s="552" t="n"/>
+      <c r="M25" s="552" t="n"/>
+      <c r="N25" s="552" t="n"/>
+      <c r="O25" s="552" t="n"/>
+      <c r="P25" s="552" t="n"/>
+      <c r="Q25" s="552" t="n"/>
+      <c r="R25" s="552" t="n"/>
+      <c r="S25" s="552" t="n"/>
+      <c r="T25" s="552" t="n"/>
+      <c r="U25" s="552" t="n"/>
+      <c r="V25" s="552" t="n"/>
+      <c r="W25" s="552" t="n"/>
+      <c r="X25" s="552" t="n"/>
+      <c r="Y25" s="552" t="n"/>
+      <c r="Z25" s="552" t="n"/>
+      <c r="AA25" s="552" t="n"/>
+      <c r="AB25" s="552" t="n"/>
+      <c r="AC25" s="552" t="n"/>
+      <c r="AD25" s="552" t="n"/>
+      <c r="AE25" s="552" t="n"/>
+      <c r="AF25" s="552" t="n"/>
+      <c r="AG25" s="552" t="n"/>
+      <c r="AH25" s="552" t="n"/>
+      <c r="AI25" s="552" t="n"/>
+      <c r="AJ25" s="552" t="n"/>
+      <c r="AK25" s="552" t="n"/>
+      <c r="AL25" s="552" t="n"/>
+      <c r="AM25" s="552" t="n"/>
+      <c r="AN25" s="553" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="329">
       <c r="A26" s="477" t="inlineStr">
@@ -6980,363 +7389,363 @@
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="478" t="n"/>
+      <c r="B26" s="552" t="n"/>
       <c r="C26" s="479" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="478" t="n"/>
-      <c r="E26" s="478" t="n"/>
+      <c r="D26" s="552" t="n"/>
+      <c r="E26" s="552" t="n"/>
       <c r="F26" s="479" t="inlineStr">
         <is>
           <t>Requirement / Check</t>
         </is>
       </c>
-      <c r="G26" s="478" t="n"/>
-      <c r="H26" s="478" t="n"/>
-      <c r="I26" s="478" t="n"/>
-      <c r="J26" s="478" t="n"/>
-      <c r="K26" s="478" t="n"/>
-      <c r="L26" s="478" t="n"/>
-      <c r="M26" s="478" t="n"/>
-      <c r="N26" s="478" t="n"/>
-      <c r="O26" s="478" t="n"/>
-      <c r="P26" s="478" t="n"/>
-      <c r="Q26" s="478" t="n"/>
-      <c r="R26" s="478" t="n"/>
-      <c r="S26" s="478" t="n"/>
+      <c r="G26" s="552" t="n"/>
+      <c r="H26" s="552" t="n"/>
+      <c r="I26" s="552" t="n"/>
+      <c r="J26" s="552" t="n"/>
+      <c r="K26" s="552" t="n"/>
+      <c r="L26" s="552" t="n"/>
+      <c r="M26" s="552" t="n"/>
+      <c r="N26" s="552" t="n"/>
+      <c r="O26" s="552" t="n"/>
+      <c r="P26" s="552" t="n"/>
+      <c r="Q26" s="552" t="n"/>
+      <c r="R26" s="552" t="n"/>
+      <c r="S26" s="552" t="n"/>
       <c r="T26" s="479" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="478" t="n"/>
-      <c r="V26" s="478" t="n"/>
-      <c r="W26" s="478" t="n"/>
-      <c r="X26" s="478" t="n"/>
-      <c r="Y26" s="478" t="n"/>
-      <c r="Z26" s="478" t="n"/>
-      <c r="AA26" s="478" t="n"/>
-      <c r="AB26" s="478" t="n"/>
-      <c r="AC26" s="478" t="n"/>
-      <c r="AD26" s="478" t="n"/>
-      <c r="AE26" s="478" t="n"/>
+      <c r="U26" s="552" t="n"/>
+      <c r="V26" s="552" t="n"/>
+      <c r="W26" s="552" t="n"/>
+      <c r="X26" s="552" t="n"/>
+      <c r="Y26" s="552" t="n"/>
+      <c r="Z26" s="552" t="n"/>
+      <c r="AA26" s="552" t="n"/>
+      <c r="AB26" s="552" t="n"/>
+      <c r="AC26" s="552" t="n"/>
+      <c r="AD26" s="552" t="n"/>
+      <c r="AE26" s="552" t="n"/>
       <c r="AF26" s="479" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="478" t="n"/>
-      <c r="AH26" s="478" t="n"/>
-      <c r="AI26" s="478" t="n"/>
+      <c r="AG26" s="552" t="n"/>
+      <c r="AH26" s="552" t="n"/>
+      <c r="AI26" s="552" t="n"/>
       <c r="AJ26" s="479" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="478" t="n"/>
-      <c r="AL26" s="478" t="n"/>
-      <c r="AM26" s="479" t="inlineStr">
+      <c r="AK26" s="552" t="n"/>
+      <c r="AL26" s="552" t="n"/>
+      <c r="AM26" s="564" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="480" t="n"/>
+      <c r="AN26" s="553" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
       <c r="A27" s="481">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="459" t="n"/>
+      <c r="B27" s="554" t="n"/>
       <c r="C27" s="482" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="459" t="n"/>
-      <c r="E27" s="459" t="n"/>
+      <c r="D27" s="554" t="n"/>
+      <c r="E27" s="554" t="n"/>
       <c r="F27" s="460" t="n"/>
-      <c r="G27" s="459" t="n"/>
-      <c r="H27" s="459" t="n"/>
-      <c r="I27" s="459" t="n"/>
-      <c r="J27" s="459" t="n"/>
-      <c r="K27" s="459" t="n"/>
-      <c r="L27" s="459" t="n"/>
-      <c r="M27" s="459" t="n"/>
-      <c r="N27" s="459" t="n"/>
-      <c r="O27" s="459" t="n"/>
-      <c r="P27" s="459" t="n"/>
-      <c r="Q27" s="459" t="n"/>
-      <c r="R27" s="459" t="n"/>
-      <c r="S27" s="459" t="n"/>
+      <c r="G27" s="554" t="n"/>
+      <c r="H27" s="554" t="n"/>
+      <c r="I27" s="554" t="n"/>
+      <c r="J27" s="554" t="n"/>
+      <c r="K27" s="554" t="n"/>
+      <c r="L27" s="554" t="n"/>
+      <c r="M27" s="554" t="n"/>
+      <c r="N27" s="554" t="n"/>
+      <c r="O27" s="554" t="n"/>
+      <c r="P27" s="554" t="n"/>
+      <c r="Q27" s="554" t="n"/>
+      <c r="R27" s="554" t="n"/>
+      <c r="S27" s="554" t="n"/>
       <c r="T27" s="483" t="n"/>
-      <c r="U27" s="459" t="n"/>
-      <c r="V27" s="459" t="n"/>
-      <c r="W27" s="459" t="n"/>
-      <c r="X27" s="459" t="n"/>
-      <c r="Y27" s="459" t="n"/>
-      <c r="Z27" s="459" t="n"/>
-      <c r="AA27" s="459" t="n"/>
-      <c r="AB27" s="459" t="n"/>
-      <c r="AC27" s="459" t="n"/>
-      <c r="AD27" s="459" t="n"/>
-      <c r="AE27" s="459" t="n"/>
+      <c r="U27" s="554" t="n"/>
+      <c r="V27" s="554" t="n"/>
+      <c r="W27" s="554" t="n"/>
+      <c r="X27" s="554" t="n"/>
+      <c r="Y27" s="554" t="n"/>
+      <c r="Z27" s="554" t="n"/>
+      <c r="AA27" s="554" t="n"/>
+      <c r="AB27" s="554" t="n"/>
+      <c r="AC27" s="554" t="n"/>
+      <c r="AD27" s="554" t="n"/>
+      <c r="AE27" s="554" t="n"/>
       <c r="AF27" s="460" t="n"/>
-      <c r="AG27" s="459" t="n"/>
-      <c r="AH27" s="459" t="n"/>
-      <c r="AI27" s="459" t="n"/>
+      <c r="AG27" s="554" t="n"/>
+      <c r="AH27" s="554" t="n"/>
+      <c r="AI27" s="554" t="n"/>
       <c r="AJ27" s="460" t="n"/>
-      <c r="AK27" s="459" t="n"/>
-      <c r="AL27" s="459" t="n"/>
-      <c r="AM27" s="484" t="n"/>
-      <c r="AN27" s="462" t="n"/>
+      <c r="AK27" s="554" t="n"/>
+      <c r="AL27" s="554" t="n"/>
+      <c r="AM27" s="565" t="n"/>
+      <c r="AN27" s="556" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
       <c r="A28" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="343" t="n"/>
+      <c r="B28" s="411" t="n"/>
       <c r="C28" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="343" t="n"/>
-      <c r="E28" s="343" t="n"/>
+      <c r="D28" s="411" t="n"/>
+      <c r="E28" s="411" t="n"/>
       <c r="F28" s="464" t="n"/>
-      <c r="G28" s="343" t="n"/>
-      <c r="H28" s="343" t="n"/>
-      <c r="I28" s="343" t="n"/>
-      <c r="J28" s="343" t="n"/>
-      <c r="K28" s="343" t="n"/>
-      <c r="L28" s="343" t="n"/>
-      <c r="M28" s="343" t="n"/>
-      <c r="N28" s="343" t="n"/>
-      <c r="O28" s="343" t="n"/>
-      <c r="P28" s="343" t="n"/>
-      <c r="Q28" s="343" t="n"/>
-      <c r="R28" s="343" t="n"/>
-      <c r="S28" s="343" t="n"/>
+      <c r="G28" s="411" t="n"/>
+      <c r="H28" s="411" t="n"/>
+      <c r="I28" s="411" t="n"/>
+      <c r="J28" s="411" t="n"/>
+      <c r="K28" s="411" t="n"/>
+      <c r="L28" s="411" t="n"/>
+      <c r="M28" s="411" t="n"/>
+      <c r="N28" s="411" t="n"/>
+      <c r="O28" s="411" t="n"/>
+      <c r="P28" s="411" t="n"/>
+      <c r="Q28" s="411" t="n"/>
+      <c r="R28" s="411" t="n"/>
+      <c r="S28" s="411" t="n"/>
       <c r="T28" s="487" t="n"/>
-      <c r="U28" s="343" t="n"/>
-      <c r="V28" s="343" t="n"/>
-      <c r="W28" s="343" t="n"/>
-      <c r="X28" s="343" t="n"/>
-      <c r="Y28" s="343" t="n"/>
-      <c r="Z28" s="343" t="n"/>
-      <c r="AA28" s="343" t="n"/>
-      <c r="AB28" s="343" t="n"/>
-      <c r="AC28" s="343" t="n"/>
-      <c r="AD28" s="343" t="n"/>
-      <c r="AE28" s="343" t="n"/>
+      <c r="U28" s="411" t="n"/>
+      <c r="V28" s="411" t="n"/>
+      <c r="W28" s="411" t="n"/>
+      <c r="X28" s="411" t="n"/>
+      <c r="Y28" s="411" t="n"/>
+      <c r="Z28" s="411" t="n"/>
+      <c r="AA28" s="411" t="n"/>
+      <c r="AB28" s="411" t="n"/>
+      <c r="AC28" s="411" t="n"/>
+      <c r="AD28" s="411" t="n"/>
+      <c r="AE28" s="411" t="n"/>
       <c r="AF28" s="464" t="n"/>
-      <c r="AG28" s="343" t="n"/>
-      <c r="AH28" s="343" t="n"/>
-      <c r="AI28" s="343" t="n"/>
+      <c r="AG28" s="411" t="n"/>
+      <c r="AH28" s="411" t="n"/>
+      <c r="AI28" s="411" t="n"/>
       <c r="AJ28" s="464" t="n"/>
-      <c r="AK28" s="343" t="n"/>
-      <c r="AL28" s="343" t="n"/>
-      <c r="AM28" s="488" t="n"/>
-      <c r="AN28" s="466" t="n"/>
+      <c r="AK28" s="411" t="n"/>
+      <c r="AL28" s="411" t="n"/>
+      <c r="AM28" s="566" t="n"/>
+      <c r="AN28" s="558" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
       <c r="A29" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="343" t="n"/>
+      <c r="B29" s="411" t="n"/>
       <c r="C29" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="343" t="n"/>
-      <c r="E29" s="343" t="n"/>
+      <c r="D29" s="411" t="n"/>
+      <c r="E29" s="411" t="n"/>
       <c r="F29" s="464" t="n"/>
-      <c r="G29" s="343" t="n"/>
-      <c r="H29" s="343" t="n"/>
-      <c r="I29" s="343" t="n"/>
-      <c r="J29" s="343" t="n"/>
-      <c r="K29" s="343" t="n"/>
-      <c r="L29" s="343" t="n"/>
-      <c r="M29" s="343" t="n"/>
-      <c r="N29" s="343" t="n"/>
-      <c r="O29" s="343" t="n"/>
-      <c r="P29" s="343" t="n"/>
-      <c r="Q29" s="343" t="n"/>
-      <c r="R29" s="343" t="n"/>
-      <c r="S29" s="343" t="n"/>
+      <c r="G29" s="411" t="n"/>
+      <c r="H29" s="411" t="n"/>
+      <c r="I29" s="411" t="n"/>
+      <c r="J29" s="411" t="n"/>
+      <c r="K29" s="411" t="n"/>
+      <c r="L29" s="411" t="n"/>
+      <c r="M29" s="411" t="n"/>
+      <c r="N29" s="411" t="n"/>
+      <c r="O29" s="411" t="n"/>
+      <c r="P29" s="411" t="n"/>
+      <c r="Q29" s="411" t="n"/>
+      <c r="R29" s="411" t="n"/>
+      <c r="S29" s="411" t="n"/>
       <c r="T29" s="487" t="n"/>
-      <c r="U29" s="343" t="n"/>
-      <c r="V29" s="343" t="n"/>
-      <c r="W29" s="343" t="n"/>
-      <c r="X29" s="343" t="n"/>
-      <c r="Y29" s="343" t="n"/>
-      <c r="Z29" s="343" t="n"/>
-      <c r="AA29" s="343" t="n"/>
-      <c r="AB29" s="343" t="n"/>
-      <c r="AC29" s="343" t="n"/>
-      <c r="AD29" s="343" t="n"/>
-      <c r="AE29" s="343" t="n"/>
+      <c r="U29" s="411" t="n"/>
+      <c r="V29" s="411" t="n"/>
+      <c r="W29" s="411" t="n"/>
+      <c r="X29" s="411" t="n"/>
+      <c r="Y29" s="411" t="n"/>
+      <c r="Z29" s="411" t="n"/>
+      <c r="AA29" s="411" t="n"/>
+      <c r="AB29" s="411" t="n"/>
+      <c r="AC29" s="411" t="n"/>
+      <c r="AD29" s="411" t="n"/>
+      <c r="AE29" s="411" t="n"/>
       <c r="AF29" s="464" t="n"/>
-      <c r="AG29" s="343" t="n"/>
-      <c r="AH29" s="343" t="n"/>
-      <c r="AI29" s="343" t="n"/>
+      <c r="AG29" s="411" t="n"/>
+      <c r="AH29" s="411" t="n"/>
+      <c r="AI29" s="411" t="n"/>
       <c r="AJ29" s="464" t="n"/>
-      <c r="AK29" s="343" t="n"/>
-      <c r="AL29" s="343" t="n"/>
-      <c r="AM29" s="488" t="n"/>
-      <c r="AN29" s="466" t="n"/>
+      <c r="AK29" s="411" t="n"/>
+      <c r="AL29" s="411" t="n"/>
+      <c r="AM29" s="566" t="n"/>
+      <c r="AN29" s="558" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
       <c r="A30" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="343" t="n"/>
+      <c r="B30" s="411" t="n"/>
       <c r="C30" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="343" t="n"/>
-      <c r="E30" s="343" t="n"/>
+      <c r="D30" s="411" t="n"/>
+      <c r="E30" s="411" t="n"/>
       <c r="F30" s="464" t="n"/>
-      <c r="G30" s="343" t="n"/>
-      <c r="H30" s="343" t="n"/>
-      <c r="I30" s="343" t="n"/>
-      <c r="J30" s="343" t="n"/>
-      <c r="K30" s="343" t="n"/>
-      <c r="L30" s="343" t="n"/>
-      <c r="M30" s="343" t="n"/>
-      <c r="N30" s="343" t="n"/>
-      <c r="O30" s="343" t="n"/>
-      <c r="P30" s="343" t="n"/>
-      <c r="Q30" s="343" t="n"/>
-      <c r="R30" s="343" t="n"/>
-      <c r="S30" s="343" t="n"/>
+      <c r="G30" s="411" t="n"/>
+      <c r="H30" s="411" t="n"/>
+      <c r="I30" s="411" t="n"/>
+      <c r="J30" s="411" t="n"/>
+      <c r="K30" s="411" t="n"/>
+      <c r="L30" s="411" t="n"/>
+      <c r="M30" s="411" t="n"/>
+      <c r="N30" s="411" t="n"/>
+      <c r="O30" s="411" t="n"/>
+      <c r="P30" s="411" t="n"/>
+      <c r="Q30" s="411" t="n"/>
+      <c r="R30" s="411" t="n"/>
+      <c r="S30" s="411" t="n"/>
       <c r="T30" s="487" t="n"/>
-      <c r="U30" s="343" t="n"/>
-      <c r="V30" s="343" t="n"/>
-      <c r="W30" s="343" t="n"/>
-      <c r="X30" s="343" t="n"/>
-      <c r="Y30" s="343" t="n"/>
-      <c r="Z30" s="343" t="n"/>
-      <c r="AA30" s="343" t="n"/>
-      <c r="AB30" s="343" t="n"/>
-      <c r="AC30" s="343" t="n"/>
-      <c r="AD30" s="343" t="n"/>
-      <c r="AE30" s="343" t="n"/>
+      <c r="U30" s="411" t="n"/>
+      <c r="V30" s="411" t="n"/>
+      <c r="W30" s="411" t="n"/>
+      <c r="X30" s="411" t="n"/>
+      <c r="Y30" s="411" t="n"/>
+      <c r="Z30" s="411" t="n"/>
+      <c r="AA30" s="411" t="n"/>
+      <c r="AB30" s="411" t="n"/>
+      <c r="AC30" s="411" t="n"/>
+      <c r="AD30" s="411" t="n"/>
+      <c r="AE30" s="411" t="n"/>
       <c r="AF30" s="464" t="n"/>
-      <c r="AG30" s="343" t="n"/>
-      <c r="AH30" s="343" t="n"/>
-      <c r="AI30" s="343" t="n"/>
+      <c r="AG30" s="411" t="n"/>
+      <c r="AH30" s="411" t="n"/>
+      <c r="AI30" s="411" t="n"/>
       <c r="AJ30" s="464" t="n"/>
-      <c r="AK30" s="343" t="n"/>
-      <c r="AL30" s="343" t="n"/>
-      <c r="AM30" s="488" t="n"/>
-      <c r="AN30" s="466" t="n"/>
+      <c r="AK30" s="411" t="n"/>
+      <c r="AL30" s="411" t="n"/>
+      <c r="AM30" s="566" t="n"/>
+      <c r="AN30" s="558" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
       <c r="A31" s="485">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="343" t="n"/>
+      <c r="B31" s="411" t="n"/>
       <c r="C31" s="486" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="343" t="n"/>
-      <c r="E31" s="343" t="n"/>
+      <c r="D31" s="411" t="n"/>
+      <c r="E31" s="411" t="n"/>
       <c r="F31" s="464" t="n"/>
-      <c r="G31" s="343" t="n"/>
-      <c r="H31" s="343" t="n"/>
-      <c r="I31" s="343" t="n"/>
-      <c r="J31" s="343" t="n"/>
-      <c r="K31" s="343" t="n"/>
-      <c r="L31" s="343" t="n"/>
-      <c r="M31" s="343" t="n"/>
-      <c r="N31" s="343" t="n"/>
-      <c r="O31" s="343" t="n"/>
-      <c r="P31" s="343" t="n"/>
-      <c r="Q31" s="343" t="n"/>
-      <c r="R31" s="343" t="n"/>
-      <c r="S31" s="343" t="n"/>
+      <c r="G31" s="411" t="n"/>
+      <c r="H31" s="411" t="n"/>
+      <c r="I31" s="411" t="n"/>
+      <c r="J31" s="411" t="n"/>
+      <c r="K31" s="411" t="n"/>
+      <c r="L31" s="411" t="n"/>
+      <c r="M31" s="411" t="n"/>
+      <c r="N31" s="411" t="n"/>
+      <c r="O31" s="411" t="n"/>
+      <c r="P31" s="411" t="n"/>
+      <c r="Q31" s="411" t="n"/>
+      <c r="R31" s="411" t="n"/>
+      <c r="S31" s="411" t="n"/>
       <c r="T31" s="487" t="n"/>
-      <c r="U31" s="343" t="n"/>
-      <c r="V31" s="343" t="n"/>
-      <c r="W31" s="343" t="n"/>
-      <c r="X31" s="343" t="n"/>
-      <c r="Y31" s="343" t="n"/>
-      <c r="Z31" s="343" t="n"/>
-      <c r="AA31" s="343" t="n"/>
-      <c r="AB31" s="343" t="n"/>
-      <c r="AC31" s="343" t="n"/>
-      <c r="AD31" s="343" t="n"/>
-      <c r="AE31" s="343" t="n"/>
+      <c r="U31" s="411" t="n"/>
+      <c r="V31" s="411" t="n"/>
+      <c r="W31" s="411" t="n"/>
+      <c r="X31" s="411" t="n"/>
+      <c r="Y31" s="411" t="n"/>
+      <c r="Z31" s="411" t="n"/>
+      <c r="AA31" s="411" t="n"/>
+      <c r="AB31" s="411" t="n"/>
+      <c r="AC31" s="411" t="n"/>
+      <c r="AD31" s="411" t="n"/>
+      <c r="AE31" s="411" t="n"/>
       <c r="AF31" s="464" t="n"/>
-      <c r="AG31" s="343" t="n"/>
-      <c r="AH31" s="343" t="n"/>
-      <c r="AI31" s="343" t="n"/>
+      <c r="AG31" s="411" t="n"/>
+      <c r="AH31" s="411" t="n"/>
+      <c r="AI31" s="411" t="n"/>
       <c r="AJ31" s="464" t="n"/>
-      <c r="AK31" s="343" t="n"/>
-      <c r="AL31" s="343" t="n"/>
-      <c r="AM31" s="488" t="n"/>
-      <c r="AN31" s="466" t="n"/>
+      <c r="AK31" s="411" t="n"/>
+      <c r="AL31" s="411" t="n"/>
+      <c r="AM31" s="566" t="n"/>
+      <c r="AN31" s="558" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
       <c r="A32" s="489">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="468" t="n"/>
+      <c r="B32" s="547" t="n"/>
       <c r="C32" s="490" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="468" t="n"/>
-      <c r="E32" s="468" t="n"/>
+      <c r="D32" s="547" t="n"/>
+      <c r="E32" s="547" t="n"/>
       <c r="F32" s="469" t="n"/>
-      <c r="G32" s="468" t="n"/>
-      <c r="H32" s="468" t="n"/>
-      <c r="I32" s="468" t="n"/>
-      <c r="J32" s="468" t="n"/>
-      <c r="K32" s="468" t="n"/>
-      <c r="L32" s="468" t="n"/>
-      <c r="M32" s="468" t="n"/>
-      <c r="N32" s="468" t="n"/>
-      <c r="O32" s="468" t="n"/>
-      <c r="P32" s="468" t="n"/>
-      <c r="Q32" s="468" t="n"/>
-      <c r="R32" s="468" t="n"/>
-      <c r="S32" s="468" t="n"/>
+      <c r="G32" s="547" t="n"/>
+      <c r="H32" s="547" t="n"/>
+      <c r="I32" s="547" t="n"/>
+      <c r="J32" s="547" t="n"/>
+      <c r="K32" s="547" t="n"/>
+      <c r="L32" s="547" t="n"/>
+      <c r="M32" s="547" t="n"/>
+      <c r="N32" s="547" t="n"/>
+      <c r="O32" s="547" t="n"/>
+      <c r="P32" s="547" t="n"/>
+      <c r="Q32" s="547" t="n"/>
+      <c r="R32" s="547" t="n"/>
+      <c r="S32" s="547" t="n"/>
       <c r="T32" s="491" t="n"/>
-      <c r="U32" s="468" t="n"/>
-      <c r="V32" s="468" t="n"/>
-      <c r="W32" s="468" t="n"/>
-      <c r="X32" s="468" t="n"/>
-      <c r="Y32" s="468" t="n"/>
-      <c r="Z32" s="468" t="n"/>
-      <c r="AA32" s="468" t="n"/>
-      <c r="AB32" s="468" t="n"/>
-      <c r="AC32" s="468" t="n"/>
-      <c r="AD32" s="468" t="n"/>
-      <c r="AE32" s="468" t="n"/>
+      <c r="U32" s="547" t="n"/>
+      <c r="V32" s="547" t="n"/>
+      <c r="W32" s="547" t="n"/>
+      <c r="X32" s="547" t="n"/>
+      <c r="Y32" s="547" t="n"/>
+      <c r="Z32" s="547" t="n"/>
+      <c r="AA32" s="547" t="n"/>
+      <c r="AB32" s="547" t="n"/>
+      <c r="AC32" s="547" t="n"/>
+      <c r="AD32" s="547" t="n"/>
+      <c r="AE32" s="547" t="n"/>
       <c r="AF32" s="469" t="n"/>
-      <c r="AG32" s="468" t="n"/>
-      <c r="AH32" s="468" t="n"/>
-      <c r="AI32" s="468" t="n"/>
+      <c r="AG32" s="547" t="n"/>
+      <c r="AH32" s="547" t="n"/>
+      <c r="AI32" s="547" t="n"/>
       <c r="AJ32" s="469" t="n"/>
-      <c r="AK32" s="468" t="n"/>
-      <c r="AL32" s="468" t="n"/>
-      <c r="AM32" s="492" t="n"/>
-      <c r="AN32" s="471" t="n"/>
+      <c r="AK32" s="547" t="n"/>
+      <c r="AL32" s="547" t="n"/>
+      <c r="AM32" s="567" t="n"/>
+      <c r="AN32" s="550" t="n"/>
     </row>
     <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="359" t="n"/>
@@ -7381,50 +7790,50 @@
       <c r="AN33" s="352" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="329">
-      <c r="A34" s="455" t="inlineStr">
+      <c r="A34" s="551" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="456" t="n"/>
-      <c r="C34" s="456" t="n"/>
-      <c r="D34" s="456" t="n"/>
-      <c r="E34" s="456" t="n"/>
-      <c r="F34" s="456" t="n"/>
-      <c r="G34" s="456" t="n"/>
-      <c r="H34" s="456" t="n"/>
-      <c r="I34" s="456" t="n"/>
-      <c r="J34" s="456" t="n"/>
-      <c r="K34" s="456" t="n"/>
-      <c r="L34" s="456" t="n"/>
-      <c r="M34" s="456" t="n"/>
-      <c r="N34" s="456" t="n"/>
-      <c r="O34" s="456" t="n"/>
-      <c r="P34" s="456" t="n"/>
-      <c r="Q34" s="456" t="n"/>
-      <c r="R34" s="456" t="n"/>
-      <c r="S34" s="456" t="n"/>
-      <c r="T34" s="456" t="n"/>
-      <c r="U34" s="456" t="n"/>
-      <c r="V34" s="456" t="n"/>
-      <c r="W34" s="456" t="n"/>
-      <c r="X34" s="456" t="n"/>
-      <c r="Y34" s="456" t="n"/>
-      <c r="Z34" s="456" t="n"/>
-      <c r="AA34" s="456" t="n"/>
-      <c r="AB34" s="456" t="n"/>
-      <c r="AC34" s="456" t="n"/>
-      <c r="AD34" s="456" t="n"/>
-      <c r="AE34" s="456" t="n"/>
-      <c r="AF34" s="456" t="n"/>
-      <c r="AG34" s="456" t="n"/>
-      <c r="AH34" s="456" t="n"/>
-      <c r="AI34" s="456" t="n"/>
-      <c r="AJ34" s="456" t="n"/>
-      <c r="AK34" s="456" t="n"/>
-      <c r="AL34" s="456" t="n"/>
-      <c r="AM34" s="456" t="n"/>
-      <c r="AN34" s="457" t="n"/>
+      <c r="B34" s="552" t="n"/>
+      <c r="C34" s="552" t="n"/>
+      <c r="D34" s="552" t="n"/>
+      <c r="E34" s="552" t="n"/>
+      <c r="F34" s="552" t="n"/>
+      <c r="G34" s="552" t="n"/>
+      <c r="H34" s="552" t="n"/>
+      <c r="I34" s="552" t="n"/>
+      <c r="J34" s="552" t="n"/>
+      <c r="K34" s="552" t="n"/>
+      <c r="L34" s="552" t="n"/>
+      <c r="M34" s="552" t="n"/>
+      <c r="N34" s="552" t="n"/>
+      <c r="O34" s="552" t="n"/>
+      <c r="P34" s="552" t="n"/>
+      <c r="Q34" s="552" t="n"/>
+      <c r="R34" s="552" t="n"/>
+      <c r="S34" s="552" t="n"/>
+      <c r="T34" s="552" t="n"/>
+      <c r="U34" s="552" t="n"/>
+      <c r="V34" s="552" t="n"/>
+      <c r="W34" s="552" t="n"/>
+      <c r="X34" s="552" t="n"/>
+      <c r="Y34" s="552" t="n"/>
+      <c r="Z34" s="552" t="n"/>
+      <c r="AA34" s="552" t="n"/>
+      <c r="AB34" s="552" t="n"/>
+      <c r="AC34" s="552" t="n"/>
+      <c r="AD34" s="552" t="n"/>
+      <c r="AE34" s="552" t="n"/>
+      <c r="AF34" s="552" t="n"/>
+      <c r="AG34" s="552" t="n"/>
+      <c r="AH34" s="552" t="n"/>
+      <c r="AI34" s="552" t="n"/>
+      <c r="AJ34" s="552" t="n"/>
+      <c r="AK34" s="552" t="n"/>
+      <c r="AL34" s="552" t="n"/>
+      <c r="AM34" s="552" t="n"/>
+      <c r="AN34" s="553" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
       <c r="A35" s="458" t="inlineStr">
@@ -7432,49 +7841,49 @@
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="459" t="n"/>
-      <c r="C35" s="459" t="n"/>
-      <c r="D35" s="459" t="n"/>
-      <c r="E35" s="459" t="n"/>
-      <c r="F35" s="459" t="n"/>
-      <c r="G35" s="459" t="n"/>
+      <c r="B35" s="554" t="n"/>
+      <c r="C35" s="554" t="n"/>
+      <c r="D35" s="554" t="n"/>
+      <c r="E35" s="554" t="n"/>
+      <c r="F35" s="554" t="n"/>
+      <c r="G35" s="554" t="n"/>
       <c r="H35" s="460" t="n"/>
-      <c r="I35" s="459" t="n"/>
-      <c r="J35" s="459" t="n"/>
-      <c r="K35" s="459" t="n"/>
-      <c r="L35" s="459" t="n"/>
-      <c r="M35" s="459" t="n"/>
-      <c r="N35" s="459" t="n"/>
-      <c r="O35" s="459" t="n"/>
-      <c r="P35" s="459" t="n"/>
-      <c r="Q35" s="459" t="n"/>
-      <c r="R35" s="459" t="n"/>
-      <c r="S35" s="459" t="n"/>
-      <c r="T35" s="459" t="n"/>
+      <c r="I35" s="554" t="n"/>
+      <c r="J35" s="554" t="n"/>
+      <c r="K35" s="554" t="n"/>
+      <c r="L35" s="554" t="n"/>
+      <c r="M35" s="554" t="n"/>
+      <c r="N35" s="554" t="n"/>
+      <c r="O35" s="554" t="n"/>
+      <c r="P35" s="554" t="n"/>
+      <c r="Q35" s="554" t="n"/>
+      <c r="R35" s="554" t="n"/>
+      <c r="S35" s="554" t="n"/>
+      <c r="T35" s="554" t="n"/>
       <c r="U35" s="461" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="459" t="n"/>
-      <c r="W35" s="459" t="n"/>
-      <c r="X35" s="459" t="n"/>
-      <c r="Y35" s="459" t="n"/>
-      <c r="Z35" s="459" t="n"/>
-      <c r="AA35" s="459" t="n"/>
-      <c r="AB35" s="460" t="n"/>
-      <c r="AC35" s="459" t="n"/>
-      <c r="AD35" s="459" t="n"/>
-      <c r="AE35" s="459" t="n"/>
-      <c r="AF35" s="459" t="n"/>
-      <c r="AG35" s="459" t="n"/>
-      <c r="AH35" s="459" t="n"/>
-      <c r="AI35" s="459" t="n"/>
-      <c r="AJ35" s="459" t="n"/>
-      <c r="AK35" s="459" t="n"/>
-      <c r="AL35" s="459" t="n"/>
-      <c r="AM35" s="459" t="n"/>
-      <c r="AN35" s="462" t="n"/>
+      <c r="V35" s="554" t="n"/>
+      <c r="W35" s="554" t="n"/>
+      <c r="X35" s="554" t="n"/>
+      <c r="Y35" s="554" t="n"/>
+      <c r="Z35" s="554" t="n"/>
+      <c r="AA35" s="554" t="n"/>
+      <c r="AB35" s="555" t="n"/>
+      <c r="AC35" s="554" t="n"/>
+      <c r="AD35" s="554" t="n"/>
+      <c r="AE35" s="554" t="n"/>
+      <c r="AF35" s="554" t="n"/>
+      <c r="AG35" s="554" t="n"/>
+      <c r="AH35" s="554" t="n"/>
+      <c r="AI35" s="554" t="n"/>
+      <c r="AJ35" s="554" t="n"/>
+      <c r="AK35" s="554" t="n"/>
+      <c r="AL35" s="554" t="n"/>
+      <c r="AM35" s="554" t="n"/>
+      <c r="AN35" s="556" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
       <c r="A36" s="467" t="inlineStr">
@@ -7482,49 +7891,49 @@
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="468" t="n"/>
-      <c r="C36" s="468" t="n"/>
-      <c r="D36" s="468" t="n"/>
-      <c r="E36" s="468" t="n"/>
-      <c r="F36" s="468" t="n"/>
-      <c r="G36" s="468" t="n"/>
+      <c r="B36" s="547" t="n"/>
+      <c r="C36" s="547" t="n"/>
+      <c r="D36" s="547" t="n"/>
+      <c r="E36" s="547" t="n"/>
+      <c r="F36" s="547" t="n"/>
+      <c r="G36" s="547" t="n"/>
       <c r="H36" s="469" t="n"/>
-      <c r="I36" s="468" t="n"/>
-      <c r="J36" s="468" t="n"/>
-      <c r="K36" s="468" t="n"/>
-      <c r="L36" s="468" t="n"/>
-      <c r="M36" s="468" t="n"/>
-      <c r="N36" s="468" t="n"/>
-      <c r="O36" s="468" t="n"/>
-      <c r="P36" s="468" t="n"/>
-      <c r="Q36" s="468" t="n"/>
-      <c r="R36" s="468" t="n"/>
-      <c r="S36" s="468" t="n"/>
-      <c r="T36" s="468" t="n"/>
+      <c r="I36" s="547" t="n"/>
+      <c r="J36" s="547" t="n"/>
+      <c r="K36" s="547" t="n"/>
+      <c r="L36" s="547" t="n"/>
+      <c r="M36" s="547" t="n"/>
+      <c r="N36" s="547" t="n"/>
+      <c r="O36" s="547" t="n"/>
+      <c r="P36" s="547" t="n"/>
+      <c r="Q36" s="547" t="n"/>
+      <c r="R36" s="547" t="n"/>
+      <c r="S36" s="547" t="n"/>
+      <c r="T36" s="547" t="n"/>
       <c r="U36" s="470" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="468" t="n"/>
-      <c r="W36" s="468" t="n"/>
-      <c r="X36" s="468" t="n"/>
-      <c r="Y36" s="468" t="n"/>
-      <c r="Z36" s="468" t="n"/>
-      <c r="AA36" s="468" t="n"/>
-      <c r="AB36" s="469" t="n"/>
-      <c r="AC36" s="468" t="n"/>
-      <c r="AD36" s="468" t="n"/>
-      <c r="AE36" s="468" t="n"/>
-      <c r="AF36" s="468" t="n"/>
-      <c r="AG36" s="468" t="n"/>
-      <c r="AH36" s="468" t="n"/>
-      <c r="AI36" s="468" t="n"/>
-      <c r="AJ36" s="468" t="n"/>
-      <c r="AK36" s="468" t="n"/>
-      <c r="AL36" s="468" t="n"/>
-      <c r="AM36" s="468" t="n"/>
-      <c r="AN36" s="471" t="n"/>
+      <c r="V36" s="547" t="n"/>
+      <c r="W36" s="547" t="n"/>
+      <c r="X36" s="547" t="n"/>
+      <c r="Y36" s="547" t="n"/>
+      <c r="Z36" s="547" t="n"/>
+      <c r="AA36" s="547" t="n"/>
+      <c r="AB36" s="559" t="n"/>
+      <c r="AC36" s="547" t="n"/>
+      <c r="AD36" s="547" t="n"/>
+      <c r="AE36" s="547" t="n"/>
+      <c r="AF36" s="547" t="n"/>
+      <c r="AG36" s="547" t="n"/>
+      <c r="AH36" s="547" t="n"/>
+      <c r="AI36" s="547" t="n"/>
+      <c r="AJ36" s="547" t="n"/>
+      <c r="AK36" s="547" t="n"/>
+      <c r="AL36" s="547" t="n"/>
+      <c r="AM36" s="547" t="n"/>
+      <c r="AN36" s="550" t="n"/>
     </row>
     <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="364" t="n"/>
@@ -7569,50 +7978,50 @@
       <c r="AN37" s="352" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="329">
-      <c r="A38" s="455" t="inlineStr">
+      <c r="A38" s="551" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="456" t="n"/>
-      <c r="C38" s="456" t="n"/>
-      <c r="D38" s="456" t="n"/>
-      <c r="E38" s="456" t="n"/>
-      <c r="F38" s="456" t="n"/>
-      <c r="G38" s="456" t="n"/>
-      <c r="H38" s="456" t="n"/>
-      <c r="I38" s="456" t="n"/>
-      <c r="J38" s="456" t="n"/>
-      <c r="K38" s="456" t="n"/>
-      <c r="L38" s="456" t="n"/>
-      <c r="M38" s="456" t="n"/>
-      <c r="N38" s="456" t="n"/>
-      <c r="O38" s="456" t="n"/>
-      <c r="P38" s="456" t="n"/>
-      <c r="Q38" s="456" t="n"/>
-      <c r="R38" s="456" t="n"/>
-      <c r="S38" s="456" t="n"/>
-      <c r="T38" s="456" t="n"/>
-      <c r="U38" s="456" t="n"/>
-      <c r="V38" s="456" t="n"/>
-      <c r="W38" s="456" t="n"/>
-      <c r="X38" s="456" t="n"/>
-      <c r="Y38" s="456" t="n"/>
-      <c r="Z38" s="456" t="n"/>
-      <c r="AA38" s="456" t="n"/>
-      <c r="AB38" s="456" t="n"/>
-      <c r="AC38" s="456" t="n"/>
-      <c r="AD38" s="456" t="n"/>
-      <c r="AE38" s="456" t="n"/>
-      <c r="AF38" s="456" t="n"/>
-      <c r="AG38" s="456" t="n"/>
-      <c r="AH38" s="456" t="n"/>
-      <c r="AI38" s="456" t="n"/>
-      <c r="AJ38" s="456" t="n"/>
-      <c r="AK38" s="456" t="n"/>
-      <c r="AL38" s="456" t="n"/>
-      <c r="AM38" s="456" t="n"/>
-      <c r="AN38" s="457" t="n"/>
+      <c r="B38" s="552" t="n"/>
+      <c r="C38" s="552" t="n"/>
+      <c r="D38" s="552" t="n"/>
+      <c r="E38" s="552" t="n"/>
+      <c r="F38" s="552" t="n"/>
+      <c r="G38" s="552" t="n"/>
+      <c r="H38" s="552" t="n"/>
+      <c r="I38" s="552" t="n"/>
+      <c r="J38" s="552" t="n"/>
+      <c r="K38" s="552" t="n"/>
+      <c r="L38" s="552" t="n"/>
+      <c r="M38" s="552" t="n"/>
+      <c r="N38" s="552" t="n"/>
+      <c r="O38" s="552" t="n"/>
+      <c r="P38" s="552" t="n"/>
+      <c r="Q38" s="552" t="n"/>
+      <c r="R38" s="552" t="n"/>
+      <c r="S38" s="552" t="n"/>
+      <c r="T38" s="552" t="n"/>
+      <c r="U38" s="552" t="n"/>
+      <c r="V38" s="552" t="n"/>
+      <c r="W38" s="552" t="n"/>
+      <c r="X38" s="552" t="n"/>
+      <c r="Y38" s="552" t="n"/>
+      <c r="Z38" s="552" t="n"/>
+      <c r="AA38" s="552" t="n"/>
+      <c r="AB38" s="552" t="n"/>
+      <c r="AC38" s="552" t="n"/>
+      <c r="AD38" s="552" t="n"/>
+      <c r="AE38" s="552" t="n"/>
+      <c r="AF38" s="552" t="n"/>
+      <c r="AG38" s="552" t="n"/>
+      <c r="AH38" s="552" t="n"/>
+      <c r="AI38" s="552" t="n"/>
+      <c r="AJ38" s="552" t="n"/>
+      <c r="AK38" s="552" t="n"/>
+      <c r="AL38" s="552" t="n"/>
+      <c r="AM38" s="552" t="n"/>
+      <c r="AN38" s="553" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="329">
       <c r="A39" s="481" t="inlineStr">
@@ -7620,53 +8029,53 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="459" t="n"/>
-      <c r="C39" s="459" t="n"/>
-      <c r="D39" s="459" t="n"/>
-      <c r="E39" s="459" t="n"/>
-      <c r="F39" s="459" t="n"/>
-      <c r="G39" s="459" t="n"/>
-      <c r="H39" s="459" t="n"/>
-      <c r="I39" s="459" t="n"/>
-      <c r="J39" s="459" t="n"/>
-      <c r="K39" s="459" t="n"/>
-      <c r="L39" s="459" t="n"/>
-      <c r="M39" s="459" t="n"/>
+      <c r="B39" s="554" t="n"/>
+      <c r="C39" s="554" t="n"/>
+      <c r="D39" s="554" t="n"/>
+      <c r="E39" s="554" t="n"/>
+      <c r="F39" s="554" t="n"/>
+      <c r="G39" s="554" t="n"/>
+      <c r="H39" s="554" t="n"/>
+      <c r="I39" s="554" t="n"/>
+      <c r="J39" s="554" t="n"/>
+      <c r="K39" s="554" t="n"/>
+      <c r="L39" s="554" t="n"/>
+      <c r="M39" s="554" t="n"/>
       <c r="N39" s="493" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="459" t="n"/>
-      <c r="P39" s="459" t="n"/>
-      <c r="Q39" s="459" t="n"/>
-      <c r="R39" s="459" t="n"/>
-      <c r="S39" s="459" t="n"/>
-      <c r="T39" s="459" t="n"/>
-      <c r="U39" s="459" t="n"/>
-      <c r="V39" s="459" t="n"/>
-      <c r="W39" s="459" t="n"/>
-      <c r="X39" s="459" t="n"/>
-      <c r="Y39" s="459" t="n"/>
-      <c r="Z39" s="459" t="n"/>
-      <c r="AA39" s="493" t="inlineStr">
+      <c r="O39" s="554" t="n"/>
+      <c r="P39" s="554" t="n"/>
+      <c r="Q39" s="554" t="n"/>
+      <c r="R39" s="554" t="n"/>
+      <c r="S39" s="554" t="n"/>
+      <c r="T39" s="554" t="n"/>
+      <c r="U39" s="554" t="n"/>
+      <c r="V39" s="554" t="n"/>
+      <c r="W39" s="554" t="n"/>
+      <c r="X39" s="554" t="n"/>
+      <c r="Y39" s="554" t="n"/>
+      <c r="Z39" s="554" t="n"/>
+      <c r="AA39" s="568" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="459" t="n"/>
-      <c r="AC39" s="459" t="n"/>
-      <c r="AD39" s="459" t="n"/>
-      <c r="AE39" s="459" t="n"/>
-      <c r="AF39" s="459" t="n"/>
-      <c r="AG39" s="459" t="n"/>
-      <c r="AH39" s="459" t="n"/>
-      <c r="AI39" s="459" t="n"/>
-      <c r="AJ39" s="459" t="n"/>
-      <c r="AK39" s="459" t="n"/>
-      <c r="AL39" s="459" t="n"/>
-      <c r="AM39" s="459" t="n"/>
-      <c r="AN39" s="462" t="n"/>
+      <c r="AB39" s="554" t="n"/>
+      <c r="AC39" s="554" t="n"/>
+      <c r="AD39" s="554" t="n"/>
+      <c r="AE39" s="554" t="n"/>
+      <c r="AF39" s="554" t="n"/>
+      <c r="AG39" s="554" t="n"/>
+      <c r="AH39" s="554" t="n"/>
+      <c r="AI39" s="554" t="n"/>
+      <c r="AJ39" s="554" t="n"/>
+      <c r="AK39" s="554" t="n"/>
+      <c r="AL39" s="554" t="n"/>
+      <c r="AM39" s="554" t="n"/>
+      <c r="AN39" s="556" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1" s="329">
       <c r="A40" s="494" t="inlineStr">
@@ -7674,137 +8083,101 @@
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="343" t="n"/>
-      <c r="C40" s="343" t="n"/>
-      <c r="D40" s="343" t="n"/>
-      <c r="E40" s="343" t="n"/>
-      <c r="F40" s="343" t="n"/>
-      <c r="G40" s="343" t="n"/>
-      <c r="H40" s="343" t="n"/>
-      <c r="I40" s="343" t="n"/>
-      <c r="J40" s="343" t="n"/>
-      <c r="K40" s="343" t="n"/>
-      <c r="L40" s="343" t="n"/>
-      <c r="M40" s="343" t="n"/>
+      <c r="B40" s="410" t="n"/>
+      <c r="C40" s="410" t="n"/>
+      <c r="D40" s="410" t="n"/>
+      <c r="E40" s="410" t="n"/>
+      <c r="F40" s="410" t="n"/>
+      <c r="G40" s="410" t="n"/>
+      <c r="H40" s="410" t="n"/>
+      <c r="I40" s="410" t="n"/>
+      <c r="J40" s="410" t="n"/>
+      <c r="K40" s="410" t="n"/>
+      <c r="L40" s="410" t="n"/>
+      <c r="M40" s="410" t="n"/>
       <c r="N40" s="495" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="343" t="n"/>
-      <c r="P40" s="343" t="n"/>
-      <c r="Q40" s="343" t="n"/>
-      <c r="R40" s="343" t="n"/>
-      <c r="S40" s="343" t="n"/>
-      <c r="T40" s="343" t="n"/>
-      <c r="U40" s="343" t="n"/>
-      <c r="V40" s="343" t="n"/>
-      <c r="W40" s="343" t="n"/>
-      <c r="X40" s="343" t="n"/>
-      <c r="Y40" s="343" t="n"/>
-      <c r="Z40" s="343" t="n"/>
-      <c r="AA40" s="495" t="inlineStr">
+      <c r="O40" s="410" t="n"/>
+      <c r="P40" s="410" t="n"/>
+      <c r="Q40" s="410" t="n"/>
+      <c r="R40" s="410" t="n"/>
+      <c r="S40" s="410" t="n"/>
+      <c r="T40" s="410" t="n"/>
+      <c r="U40" s="410" t="n"/>
+      <c r="V40" s="410" t="n"/>
+      <c r="W40" s="410" t="n"/>
+      <c r="X40" s="410" t="n"/>
+      <c r="Y40" s="410" t="n"/>
+      <c r="Z40" s="410" t="n"/>
+      <c r="AA40" s="569" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="343" t="n"/>
-      <c r="AC40" s="343" t="n"/>
-      <c r="AD40" s="343" t="n"/>
-      <c r="AE40" s="343" t="n"/>
-      <c r="AF40" s="343" t="n"/>
-      <c r="AG40" s="343" t="n"/>
-      <c r="AH40" s="343" t="n"/>
-      <c r="AI40" s="343" t="n"/>
-      <c r="AJ40" s="343" t="n"/>
-      <c r="AK40" s="343" t="n"/>
-      <c r="AL40" s="343" t="n"/>
-      <c r="AM40" s="343" t="n"/>
-      <c r="AN40" s="466" t="n"/>
+      <c r="AB40" s="410" t="n"/>
+      <c r="AC40" s="410" t="n"/>
+      <c r="AD40" s="410" t="n"/>
+      <c r="AE40" s="410" t="n"/>
+      <c r="AF40" s="410" t="n"/>
+      <c r="AG40" s="410" t="n"/>
+      <c r="AH40" s="410" t="n"/>
+      <c r="AI40" s="410" t="n"/>
+      <c r="AJ40" s="410" t="n"/>
+      <c r="AK40" s="410" t="n"/>
+      <c r="AL40" s="410" t="n"/>
+      <c r="AM40" s="410" t="n"/>
+      <c r="AN40" s="540" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="474" t="n"/>
-      <c r="B41" s="343" t="n"/>
-      <c r="C41" s="343" t="n"/>
-      <c r="D41" s="343" t="n"/>
-      <c r="E41" s="343" t="n"/>
-      <c r="F41" s="343" t="n"/>
-      <c r="G41" s="343" t="n"/>
-      <c r="H41" s="343" t="n"/>
-      <c r="I41" s="343" t="n"/>
-      <c r="J41" s="343" t="n"/>
-      <c r="K41" s="343" t="n"/>
-      <c r="L41" s="343" t="n"/>
-      <c r="M41" s="343" t="n"/>
-      <c r="N41" s="472" t="n"/>
-      <c r="O41" s="343" t="n"/>
-      <c r="P41" s="343" t="n"/>
-      <c r="Q41" s="343" t="n"/>
-      <c r="R41" s="343" t="n"/>
-      <c r="S41" s="343" t="n"/>
-      <c r="T41" s="343" t="n"/>
-      <c r="U41" s="343" t="n"/>
-      <c r="V41" s="343" t="n"/>
-      <c r="W41" s="343" t="n"/>
-      <c r="X41" s="343" t="n"/>
-      <c r="Y41" s="343" t="n"/>
-      <c r="Z41" s="343" t="n"/>
-      <c r="AA41" s="472" t="n"/>
-      <c r="AB41" s="343" t="n"/>
-      <c r="AC41" s="343" t="n"/>
-      <c r="AD41" s="343" t="n"/>
-      <c r="AE41" s="343" t="n"/>
-      <c r="AF41" s="343" t="n"/>
-      <c r="AG41" s="343" t="n"/>
-      <c r="AH41" s="343" t="n"/>
-      <c r="AI41" s="343" t="n"/>
-      <c r="AJ41" s="343" t="n"/>
-      <c r="AK41" s="343" t="n"/>
-      <c r="AL41" s="343" t="n"/>
-      <c r="AM41" s="343" t="n"/>
-      <c r="AN41" s="466" t="n"/>
+      <c r="A41" s="535" t="n"/>
+      <c r="N41" s="413" t="n"/>
+      <c r="AA41" s="413" t="n"/>
+      <c r="AN41" s="536" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="475" t="n"/>
-      <c r="B42" s="468" t="n"/>
-      <c r="C42" s="468" t="n"/>
-      <c r="D42" s="468" t="n"/>
-      <c r="E42" s="468" t="n"/>
-      <c r="F42" s="468" t="n"/>
-      <c r="G42" s="468" t="n"/>
-      <c r="H42" s="468" t="n"/>
-      <c r="I42" s="468" t="n"/>
-      <c r="J42" s="468" t="n"/>
-      <c r="K42" s="468" t="n"/>
-      <c r="L42" s="468" t="n"/>
-      <c r="M42" s="468" t="n"/>
-      <c r="N42" s="476" t="n"/>
-      <c r="O42" s="468" t="n"/>
-      <c r="P42" s="468" t="n"/>
-      <c r="Q42" s="468" t="n"/>
-      <c r="R42" s="468" t="n"/>
-      <c r="S42" s="468" t="n"/>
-      <c r="T42" s="468" t="n"/>
-      <c r="U42" s="468" t="n"/>
-      <c r="V42" s="468" t="n"/>
-      <c r="W42" s="468" t="n"/>
-      <c r="X42" s="468" t="n"/>
-      <c r="Y42" s="468" t="n"/>
-      <c r="Z42" s="468" t="n"/>
-      <c r="AA42" s="476" t="n"/>
-      <c r="AB42" s="468" t="n"/>
-      <c r="AC42" s="468" t="n"/>
-      <c r="AD42" s="468" t="n"/>
-      <c r="AE42" s="468" t="n"/>
-      <c r="AF42" s="468" t="n"/>
-      <c r="AG42" s="468" t="n"/>
-      <c r="AH42" s="468" t="n"/>
-      <c r="AI42" s="468" t="n"/>
-      <c r="AJ42" s="468" t="n"/>
-      <c r="AK42" s="468" t="n"/>
-      <c r="AL42" s="468" t="n"/>
-      <c r="AM42" s="468" t="n"/>
-      <c r="AN42" s="471" t="n"/>
+      <c r="A42" s="562" t="n"/>
+      <c r="B42" s="415" t="n"/>
+      <c r="C42" s="415" t="n"/>
+      <c r="D42" s="415" t="n"/>
+      <c r="E42" s="415" t="n"/>
+      <c r="F42" s="415" t="n"/>
+      <c r="G42" s="415" t="n"/>
+      <c r="H42" s="415" t="n"/>
+      <c r="I42" s="415" t="n"/>
+      <c r="J42" s="415" t="n"/>
+      <c r="K42" s="415" t="n"/>
+      <c r="L42" s="415" t="n"/>
+      <c r="M42" s="415" t="n"/>
+      <c r="N42" s="414" t="n"/>
+      <c r="O42" s="415" t="n"/>
+      <c r="P42" s="415" t="n"/>
+      <c r="Q42" s="415" t="n"/>
+      <c r="R42" s="415" t="n"/>
+      <c r="S42" s="415" t="n"/>
+      <c r="T42" s="415" t="n"/>
+      <c r="U42" s="415" t="n"/>
+      <c r="V42" s="415" t="n"/>
+      <c r="W42" s="415" t="n"/>
+      <c r="X42" s="415" t="n"/>
+      <c r="Y42" s="415" t="n"/>
+      <c r="Z42" s="415" t="n"/>
+      <c r="AA42" s="414" t="n"/>
+      <c r="AB42" s="415" t="n"/>
+      <c r="AC42" s="415" t="n"/>
+      <c r="AD42" s="415" t="n"/>
+      <c r="AE42" s="415" t="n"/>
+      <c r="AF42" s="415" t="n"/>
+      <c r="AG42" s="415" t="n"/>
+      <c r="AH42" s="415" t="n"/>
+      <c r="AI42" s="415" t="n"/>
+      <c r="AJ42" s="415" t="n"/>
+      <c r="AK42" s="415" t="n"/>
+      <c r="AL42" s="415" t="n"/>
+      <c r="AM42" s="415" t="n"/>
+      <c r="AN42" s="563" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="386" t="n"/>
@@ -7849,50 +8222,50 @@
       <c r="AN43" s="352" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="496" t="inlineStr">
+      <c r="A44" s="570" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
         </is>
       </c>
-      <c r="B44" s="497" t="n"/>
-      <c r="C44" s="497" t="n"/>
-      <c r="D44" s="497" t="n"/>
-      <c r="E44" s="497" t="n"/>
-      <c r="F44" s="497" t="n"/>
-      <c r="G44" s="497" t="n"/>
-      <c r="H44" s="497" t="n"/>
-      <c r="I44" s="497" t="n"/>
-      <c r="J44" s="497" t="n"/>
-      <c r="K44" s="497" t="n"/>
-      <c r="L44" s="497" t="n"/>
-      <c r="M44" s="497" t="n"/>
-      <c r="N44" s="497" t="n"/>
-      <c r="O44" s="497" t="n"/>
-      <c r="P44" s="497" t="n"/>
-      <c r="Q44" s="497" t="n"/>
-      <c r="R44" s="497" t="n"/>
-      <c r="S44" s="497" t="n"/>
-      <c r="T44" s="497" t="n"/>
-      <c r="U44" s="497" t="n"/>
-      <c r="V44" s="497" t="n"/>
-      <c r="W44" s="497" t="n"/>
-      <c r="X44" s="497" t="n"/>
-      <c r="Y44" s="497" t="n"/>
-      <c r="Z44" s="497" t="n"/>
-      <c r="AA44" s="497" t="n"/>
-      <c r="AB44" s="497" t="n"/>
-      <c r="AC44" s="497" t="n"/>
-      <c r="AD44" s="497" t="n"/>
-      <c r="AE44" s="497" t="n"/>
-      <c r="AF44" s="497" t="n"/>
-      <c r="AG44" s="497" t="n"/>
-      <c r="AH44" s="497" t="n"/>
-      <c r="AI44" s="497" t="n"/>
-      <c r="AJ44" s="497" t="n"/>
-      <c r="AK44" s="497" t="n"/>
-      <c r="AL44" s="497" t="n"/>
-      <c r="AM44" s="497" t="n"/>
-      <c r="AN44" s="498" t="n"/>
+      <c r="B44" s="552" t="n"/>
+      <c r="C44" s="552" t="n"/>
+      <c r="D44" s="552" t="n"/>
+      <c r="E44" s="552" t="n"/>
+      <c r="F44" s="552" t="n"/>
+      <c r="G44" s="552" t="n"/>
+      <c r="H44" s="552" t="n"/>
+      <c r="I44" s="552" t="n"/>
+      <c r="J44" s="552" t="n"/>
+      <c r="K44" s="552" t="n"/>
+      <c r="L44" s="552" t="n"/>
+      <c r="M44" s="552" t="n"/>
+      <c r="N44" s="552" t="n"/>
+      <c r="O44" s="552" t="n"/>
+      <c r="P44" s="552" t="n"/>
+      <c r="Q44" s="552" t="n"/>
+      <c r="R44" s="552" t="n"/>
+      <c r="S44" s="552" t="n"/>
+      <c r="T44" s="552" t="n"/>
+      <c r="U44" s="552" t="n"/>
+      <c r="V44" s="552" t="n"/>
+      <c r="W44" s="552" t="n"/>
+      <c r="X44" s="552" t="n"/>
+      <c r="Y44" s="552" t="n"/>
+      <c r="Z44" s="552" t="n"/>
+      <c r="AA44" s="552" t="n"/>
+      <c r="AB44" s="552" t="n"/>
+      <c r="AC44" s="552" t="n"/>
+      <c r="AD44" s="552" t="n"/>
+      <c r="AE44" s="552" t="n"/>
+      <c r="AF44" s="552" t="n"/>
+      <c r="AG44" s="552" t="n"/>
+      <c r="AH44" s="552" t="n"/>
+      <c r="AI44" s="552" t="n"/>
+      <c r="AJ44" s="552" t="n"/>
+      <c r="AK44" s="552" t="n"/>
+      <c r="AL44" s="552" t="n"/>
+      <c r="AM44" s="552" t="n"/>
+      <c r="AN44" s="553" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -8047,7 +8420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="329" min="1" max="1"/>
@@ -8290,7 +8663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:CU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9042,7 +9415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:CU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9093,12 +9466,12 @@
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="417" t="n"/>
-      <c r="C1" s="417" t="n"/>
-      <c r="D1" s="417" t="n"/>
-      <c r="E1" s="417" t="n"/>
-      <c r="F1" s="417" t="n"/>
-      <c r="G1" s="417" t="n"/>
+      <c r="B1" s="529" t="n"/>
+      <c r="C1" s="529" t="n"/>
+      <c r="D1" s="529" t="n"/>
+      <c r="E1" s="529" t="n"/>
+      <c r="F1" s="529" t="n"/>
+      <c r="G1" s="529" t="n"/>
       <c r="H1" s="508" t="n"/>
       <c r="I1" s="419" t="n"/>
       <c r="J1" s="420" t="n"/>
@@ -9139,12 +9512,6 @@
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="510" t="n"/>
       <c r="I2" s="430" t="n"/>
       <c r="J2" s="431" t="n"/>
@@ -9854,7 +10221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:CU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9905,12 +10272,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="417" t="n"/>
-      <c r="C1" s="417" t="n"/>
-      <c r="D1" s="417" t="n"/>
-      <c r="E1" s="417" t="n"/>
-      <c r="F1" s="417" t="n"/>
-      <c r="G1" s="417" t="n"/>
+      <c r="B1" s="529" t="n"/>
+      <c r="C1" s="529" t="n"/>
+      <c r="D1" s="529" t="n"/>
+      <c r="E1" s="529" t="n"/>
+      <c r="F1" s="529" t="n"/>
+      <c r="G1" s="529" t="n"/>
       <c r="H1" s="508" t="n"/>
       <c r="I1" s="419" t="n"/>
       <c r="J1" s="420" t="n"/>
@@ -9951,12 +10318,6 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="510" t="n"/>
       <c r="I2" s="430" t="n"/>
       <c r="J2" s="431" t="n"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPATCH_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DISPATCH_GATE'!$A$1:$AN$44</definedName>
@@ -6250,7 +6250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU44"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -8420,7 +8420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="329" min="1" max="1"/>
@@ -8663,7 +8663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9415,7 +9415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -10221,7 +10221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -15,10 +15,387 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
+  </si>
+  <si>
+    <t>  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
+  </si>
+  <si>
+    <t>  4. FINAL DECISION / CLOSURE</t>
+  </si>
+  <si>
+    <t>  5. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$27)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ACTION_STATUS</t>
+  </si>
+  <si>
+    <t>ANNEX-ENG-002</t>
+  </si>
+  <si>
+    <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-001</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-002</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-003</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Approval State</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
+  </si>
+  <si>
+    <t>Condition / Exception</t>
+  </si>
+  <si>
+    <t>Conditional Action Required (YES/NO)</t>
+  </si>
+  <si>
+    <t>Conditions / Exceptions / Actions</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>DISPATCH NOTES / CONDITIONALS</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>Dispatch Gate Status</t>
+  </si>
+  <si>
+    <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Epicor transaction + M365 evidence</t>
+  </si>
+  <si>
+    <t>Evidence / Criteria</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-404</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INEFFECTIVE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Linked Route / Package</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open Actions Present (YES/NO)</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Outsource Dispatch Checklist</t>
+  </si>
+  <si>
+    <t>Outsource Dispatch ID</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PO / Work Order</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Package Ref</t>
+  </si>
+  <si>
+    <t>Part / Lot / Qty</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>Purchasing + QA</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Release Status</t>
+  </si>
+  <si>
+    <t>Required Action</t>
+  </si>
+  <si>
+    <t>Requirement / Check</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Route Step / Due Date</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP-401</t>
+  </si>
+  <si>
+    <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Supplier / Customer Spec Ref</t>
+  </si>
+  <si>
+    <t>Supplier / Processor</t>
+  </si>
+  <si>
+    <t>Supplier-Quality Owner</t>
+  </si>
+  <si>
+    <t>Target Closeout</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Upstream References / Import Guidance</t>
+  </si>
+  <si>
+    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI-206</t>
+  </si>
+  <si>
+    <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="87">
+  <fonts count="88">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -510,8 +887,13 @@
       <color rgb="000C2D48"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -768,8 +1150,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="354">
+  <borders count="357">
     <border>
       <left/>
       <right/>
@@ -4590,12 +4977,46 @@
         <color rgb="002C9CD7"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="571">
+  <cellXfs count="574">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5879,6 +6300,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8222,50 +8652,50 @@
       <c r="AN43" s="352" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="570" t="inlineStr">
+      <c r="A44" s="571" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
         </is>
       </c>
-      <c r="B44" s="552" t="n"/>
-      <c r="C44" s="552" t="n"/>
-      <c r="D44" s="552" t="n"/>
-      <c r="E44" s="552" t="n"/>
-      <c r="F44" s="552" t="n"/>
-      <c r="G44" s="552" t="n"/>
-      <c r="H44" s="552" t="n"/>
-      <c r="I44" s="552" t="n"/>
-      <c r="J44" s="552" t="n"/>
-      <c r="K44" s="552" t="n"/>
-      <c r="L44" s="552" t="n"/>
-      <c r="M44" s="552" t="n"/>
-      <c r="N44" s="552" t="n"/>
-      <c r="O44" s="552" t="n"/>
-      <c r="P44" s="552" t="n"/>
-      <c r="Q44" s="552" t="n"/>
-      <c r="R44" s="552" t="n"/>
-      <c r="S44" s="552" t="n"/>
-      <c r="T44" s="552" t="n"/>
-      <c r="U44" s="552" t="n"/>
-      <c r="V44" s="552" t="n"/>
-      <c r="W44" s="552" t="n"/>
-      <c r="X44" s="552" t="n"/>
-      <c r="Y44" s="552" t="n"/>
-      <c r="Z44" s="552" t="n"/>
-      <c r="AA44" s="552" t="n"/>
-      <c r="AB44" s="552" t="n"/>
-      <c r="AC44" s="552" t="n"/>
-      <c r="AD44" s="552" t="n"/>
-      <c r="AE44" s="552" t="n"/>
-      <c r="AF44" s="552" t="n"/>
-      <c r="AG44" s="552" t="n"/>
-      <c r="AH44" s="552" t="n"/>
-      <c r="AI44" s="552" t="n"/>
-      <c r="AJ44" s="552" t="n"/>
-      <c r="AK44" s="552" t="n"/>
-      <c r="AL44" s="552" t="n"/>
-      <c r="AM44" s="552" t="n"/>
-      <c r="AN44" s="553" t="n"/>
+      <c r="B44" s="572" t="n"/>
+      <c r="C44" s="572" t="n"/>
+      <c r="D44" s="572" t="n"/>
+      <c r="E44" s="572" t="n"/>
+      <c r="F44" s="572" t="n"/>
+      <c r="G44" s="572" t="n"/>
+      <c r="H44" s="572" t="n"/>
+      <c r="I44" s="572" t="n"/>
+      <c r="J44" s="572" t="n"/>
+      <c r="K44" s="572" t="n"/>
+      <c r="L44" s="572" t="n"/>
+      <c r="M44" s="572" t="n"/>
+      <c r="N44" s="572" t="n"/>
+      <c r="O44" s="572" t="n"/>
+      <c r="P44" s="572" t="n"/>
+      <c r="Q44" s="572" t="n"/>
+      <c r="R44" s="572" t="n"/>
+      <c r="S44" s="572" t="n"/>
+      <c r="T44" s="572" t="n"/>
+      <c r="U44" s="572" t="n"/>
+      <c r="V44" s="572" t="n"/>
+      <c r="W44" s="572" t="n"/>
+      <c r="X44" s="572" t="n"/>
+      <c r="Y44" s="572" t="n"/>
+      <c r="Z44" s="572" t="n"/>
+      <c r="AA44" s="572" t="n"/>
+      <c r="AB44" s="572" t="n"/>
+      <c r="AC44" s="572" t="n"/>
+      <c r="AD44" s="572" t="n"/>
+      <c r="AE44" s="572" t="n"/>
+      <c r="AF44" s="572" t="n"/>
+      <c r="AG44" s="572" t="n"/>
+      <c r="AH44" s="572" t="n"/>
+      <c r="AI44" s="572" t="n"/>
+      <c r="AJ44" s="572" t="n"/>
+      <c r="AK44" s="572" t="n"/>
+      <c r="AL44" s="572" t="n"/>
+      <c r="AM44" s="572" t="n"/>
+      <c r="AN44" s="573" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -6,8 +6,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPATCH_GATE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DISPATCH_GATE'!$A$1:$AN$44</definedName>
@@ -16,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>  1. REFERENCE INFORMATION</t>
   </si>
@@ -45,34 +43,7 @@
     <t>ACTION_STATUS</t>
   </si>
   <si>
-    <t>ANNEX-ENG-002</t>
-  </si>
-  <si>
-    <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-001</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-002</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-003</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-  </si>
-  <si>
     <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Approval State</t>
   </si>
   <si>
     <t>Approved by</t>
@@ -87,12 +58,6 @@
     <t>Cat.</t>
   </si>
   <si>
-    <t>Close When</t>
-  </si>
-  <si>
-    <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
-  </si>
-  <si>
     <t>Condition / Exception</t>
   </si>
   <si>
@@ -100,9 +65,6 @@
   </si>
   <si>
     <t>Conditions / Exceptions / Actions</t>
-  </si>
-  <si>
-    <t>Cross-Reference Boundary</t>
   </si>
   <si>
     <t>DISPATCH NOTES / CONDITIONALS</t>
@@ -117,37 +79,25 @@
     <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
   </si>
   <si>
-    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-  </si>
-  <si>
     <t>Due Date</t>
   </si>
   <si>
     <t>ENG</t>
   </si>
   <si>
-    <t>Epicor transaction + M365 evidence</t>
-  </si>
-  <si>
     <t>Evidence / Criteria</t>
-  </si>
-  <si>
-    <t>Evidence Package Ref</t>
   </si>
   <si>
     <t>Evidence Ref</t>
   </si>
   <si>
-    <t>Evidence Reference / Attachment Guidance</t>
+    <t>Expected Return Date</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
     <t>FRM-404</t>
-  </si>
-  <si>
-    <t>Field</t>
   </si>
   <si>
     <t>Final Decision</t>
@@ -210,15 +160,6 @@
     <t>Open Actions Present (YES/NO)</t>
   </si>
   <si>
-    <t>Open When</t>
-  </si>
-  <si>
-    <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
-  </si>
-  <si>
-    <t>Operational trigger</t>
-  </si>
-  <si>
     <t>Outsource Dispatch Checklist</t>
   </si>
   <si>
@@ -261,6 +202,9 @@
     <t>QA</t>
   </si>
   <si>
+    <t>Qty Dispatched</t>
+  </si>
+  <si>
     <t>Quality Management System · Controlled Document</t>
   </si>
   <si>
@@ -277,9 +221,6 @@
   </si>
   <si>
     <t>Ref.</t>
-  </si>
-  <si>
-    <t>Release / closure rule</t>
   </si>
   <si>
     <t>Release Status</t>
@@ -303,16 +244,7 @@
     <t>SALES</t>
   </si>
   <si>
-    <t>SOP-401</t>
-  </si>
-  <si>
-    <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
-  </si>
-  <si>
     <t>STATUS</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
   </si>
   <si>
     <t>Status</t>
@@ -330,34 +262,13 @@
     <t>Target Closeout</t>
   </si>
   <si>
-    <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-  </si>
-  <si>
-    <t>Upstream References / Import Guidance</t>
-  </si>
-  <si>
-    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-  </si>
-  <si>
     <t>V0</t>
   </si>
   <si>
     <t>VERIFIED</t>
   </si>
   <si>
-    <t>Value / Reference</t>
-  </si>
-  <si>
     <t>WHS</t>
-  </si>
-  <si>
-    <t>WI-206</t>
-  </si>
-  <si>
-    <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
   </si>
   <si>
     <t>YES</t>
@@ -367,24 +278,6 @@
   </si>
   <si>
     <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
   </si>
   <si>
     <t>—</t>
@@ -1156,7 +1049,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="357">
+  <borders count="362">
     <border>
       <left/>
       <right/>
@@ -5011,12 +4904,70 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="574">
+  <cellXfs count="577">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6311,6 +6262,11 @@
     <xf numFmtId="0" fontId="87" fillId="52" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6387,72 +6343,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1303776" cy="376089"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1303776" cy="376089"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -7180,7 +7070,7 @@
     <row r="12" ht="20" customHeight="1" s="329">
       <c r="A12" s="463" t="inlineStr">
         <is>
-          <t>Evidence Package Ref</t>
+          <t>Qty Dispatched</t>
         </is>
       </c>
       <c r="B12" s="411" t="n"/>
@@ -7204,7 +7094,7 @@
       <c r="T12" s="411" t="n"/>
       <c r="U12" s="465" t="inlineStr">
         <is>
-          <t>Approval State</t>
+          <t>Expected Return Date</t>
         </is>
       </c>
       <c r="V12" s="411" t="n"/>
@@ -9837,1616 +9727,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="507" t="inlineStr">
-        <is>
-          <t>Upstream References / Import Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="529" t="n"/>
-      <c r="C1" s="529" t="n"/>
-      <c r="D1" s="529" t="n"/>
-      <c r="E1" s="529" t="n"/>
-      <c r="F1" s="529" t="n"/>
-      <c r="G1" s="529" t="n"/>
-      <c r="H1" s="508" t="n"/>
-      <c r="I1" s="419" t="n"/>
-      <c r="J1" s="420" t="n"/>
-      <c r="K1" s="420" t="n"/>
-      <c r="L1" s="420" t="n"/>
-      <c r="M1" s="420" t="n"/>
-      <c r="N1" s="420" t="n"/>
-      <c r="O1" s="420" t="n"/>
-      <c r="P1" s="420" t="n"/>
-      <c r="Q1" s="420" t="n"/>
-      <c r="R1" s="420" t="n"/>
-      <c r="S1" s="420" t="n"/>
-      <c r="T1" s="420" t="n"/>
-      <c r="U1" s="420" t="n"/>
-      <c r="V1" s="420" t="n"/>
-      <c r="W1" s="420" t="n"/>
-      <c r="X1" s="420" t="n"/>
-      <c r="Y1" s="420" t="n"/>
-      <c r="Z1" s="420" t="n"/>
-      <c r="AA1" s="420" t="n"/>
-      <c r="AB1" s="420" t="n"/>
-      <c r="AC1" s="420" t="n"/>
-      <c r="AD1" s="421" t="n"/>
-      <c r="AE1" s="422" t="n"/>
-      <c r="AF1" s="423" t="n"/>
-      <c r="AG1" s="423" t="n"/>
-      <c r="AH1" s="424" t="n"/>
-      <c r="AI1" s="425" t="n"/>
-      <c r="AJ1" s="426" t="n"/>
-      <c r="AK1" s="426" t="n"/>
-      <c r="AL1" s="426" t="n"/>
-      <c r="AM1" s="426" t="n"/>
-      <c r="AN1" s="427" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="509" t="inlineStr">
-        <is>
-          <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
-        </is>
-      </c>
-      <c r="H2" s="510" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="431" t="n"/>
-      <c r="K2" s="431" t="n"/>
-      <c r="L2" s="431" t="n"/>
-      <c r="M2" s="431" t="n"/>
-      <c r="N2" s="431" t="n"/>
-      <c r="O2" s="431" t="n"/>
-      <c r="P2" s="431" t="n"/>
-      <c r="Q2" s="431" t="n"/>
-      <c r="R2" s="431" t="n"/>
-      <c r="S2" s="431" t="n"/>
-      <c r="T2" s="431" t="n"/>
-      <c r="U2" s="431" t="n"/>
-      <c r="V2" s="431" t="n"/>
-      <c r="W2" s="431" t="n"/>
-      <c r="X2" s="431" t="n"/>
-      <c r="Y2" s="431" t="n"/>
-      <c r="Z2" s="431" t="n"/>
-      <c r="AA2" s="431" t="n"/>
-      <c r="AB2" s="431" t="n"/>
-      <c r="AC2" s="431" t="n"/>
-      <c r="AD2" s="432" t="n"/>
-      <c r="AE2" s="433" t="n"/>
-      <c r="AF2" s="434" t="n"/>
-      <c r="AG2" s="434" t="n"/>
-      <c r="AH2" s="435" t="n"/>
-      <c r="AI2" s="436" t="n"/>
-      <c r="AJ2" s="437" t="n"/>
-      <c r="AK2" s="437" t="n"/>
-      <c r="AL2" s="437" t="n"/>
-      <c r="AM2" s="437" t="n"/>
-      <c r="AN2" s="438" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="511" t="n"/>
-      <c r="B3" s="512" t="n"/>
-      <c r="C3" s="512" t="n"/>
-      <c r="D3" s="512" t="n"/>
-      <c r="E3" s="512" t="n"/>
-      <c r="F3" s="512" t="n"/>
-      <c r="G3" s="512" t="n"/>
-      <c r="H3" s="510" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="431" t="n"/>
-      <c r="K3" s="431" t="n"/>
-      <c r="L3" s="431" t="n"/>
-      <c r="M3" s="431" t="n"/>
-      <c r="N3" s="431" t="n"/>
-      <c r="O3" s="431" t="n"/>
-      <c r="P3" s="431" t="n"/>
-      <c r="Q3" s="431" t="n"/>
-      <c r="R3" s="431" t="n"/>
-      <c r="S3" s="431" t="n"/>
-      <c r="T3" s="431" t="n"/>
-      <c r="U3" s="431" t="n"/>
-      <c r="V3" s="431" t="n"/>
-      <c r="W3" s="431" t="n"/>
-      <c r="X3" s="431" t="n"/>
-      <c r="Y3" s="431" t="n"/>
-      <c r="Z3" s="431" t="n"/>
-      <c r="AA3" s="431" t="n"/>
-      <c r="AB3" s="431" t="n"/>
-      <c r="AC3" s="431" t="n"/>
-      <c r="AD3" s="432" t="n"/>
-      <c r="AE3" s="433" t="n"/>
-      <c r="AF3" s="434" t="n"/>
-      <c r="AG3" s="434" t="n"/>
-      <c r="AH3" s="435" t="n"/>
-      <c r="AI3" s="436" t="n"/>
-      <c r="AJ3" s="437" t="n"/>
-      <c r="AK3" s="437" t="n"/>
-      <c r="AL3" s="437" t="n"/>
-      <c r="AM3" s="437" t="n"/>
-      <c r="AN3" s="438" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="513" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="514" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="514" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="512" t="n"/>
-      <c r="E4" s="512" t="n"/>
-      <c r="F4" s="512" t="n"/>
-      <c r="G4" s="512" t="n"/>
-      <c r="H4" s="510" t="n"/>
-      <c r="I4" s="439" t="n"/>
-      <c r="J4" s="440" t="n"/>
-      <c r="K4" s="440" t="n"/>
-      <c r="L4" s="440" t="n"/>
-      <c r="M4" s="440" t="n"/>
-      <c r="N4" s="440" t="n"/>
-      <c r="O4" s="440" t="n"/>
-      <c r="P4" s="440" t="n"/>
-      <c r="Q4" s="440" t="n"/>
-      <c r="R4" s="440" t="n"/>
-      <c r="S4" s="440" t="n"/>
-      <c r="T4" s="440" t="n"/>
-      <c r="U4" s="440" t="n"/>
-      <c r="V4" s="440" t="n"/>
-      <c r="W4" s="440" t="n"/>
-      <c r="X4" s="440" t="n"/>
-      <c r="Y4" s="440" t="n"/>
-      <c r="Z4" s="440" t="n"/>
-      <c r="AA4" s="440" t="n"/>
-      <c r="AB4" s="440" t="n"/>
-      <c r="AC4" s="440" t="n"/>
-      <c r="AD4" s="441" t="n"/>
-      <c r="AE4" s="433" t="n"/>
-      <c r="AF4" s="434" t="n"/>
-      <c r="AG4" s="434" t="n"/>
-      <c r="AH4" s="435" t="n"/>
-      <c r="AI4" s="436" t="n"/>
-      <c r="AJ4" s="437" t="n"/>
-      <c r="AK4" s="437" t="n"/>
-      <c r="AL4" s="437" t="n"/>
-      <c r="AM4" s="437" t="n"/>
-      <c r="AN4" s="438" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="515" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="516" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="516" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="517" t="n"/>
-      <c r="E5" s="517" t="n"/>
-      <c r="F5" s="517" t="n"/>
-      <c r="G5" s="517" t="n"/>
-      <c r="H5" s="518" t="n"/>
-      <c r="I5" s="445" t="n"/>
-      <c r="J5" s="446" t="n"/>
-      <c r="K5" s="446" t="n"/>
-      <c r="L5" s="446" t="n"/>
-      <c r="M5" s="446" t="n"/>
-      <c r="N5" s="446" t="n"/>
-      <c r="O5" s="446" t="n"/>
-      <c r="P5" s="446" t="n"/>
-      <c r="Q5" s="446" t="n"/>
-      <c r="R5" s="446" t="n"/>
-      <c r="S5" s="446" t="n"/>
-      <c r="T5" s="446" t="n"/>
-      <c r="U5" s="446" t="n"/>
-      <c r="V5" s="446" t="n"/>
-      <c r="W5" s="446" t="n"/>
-      <c r="X5" s="446" t="n"/>
-      <c r="Y5" s="446" t="n"/>
-      <c r="Z5" s="446" t="n"/>
-      <c r="AA5" s="446" t="n"/>
-      <c r="AB5" s="446" t="n"/>
-      <c r="AC5" s="446" t="n"/>
-      <c r="AD5" s="447" t="n"/>
-      <c r="AE5" s="448" t="n"/>
-      <c r="AF5" s="449" t="n"/>
-      <c r="AG5" s="449" t="n"/>
-      <c r="AH5" s="450" t="n"/>
-      <c r="AI5" s="451" t="n"/>
-      <c r="AJ5" s="452" t="n"/>
-      <c r="AK5" s="452" t="n"/>
-      <c r="AL5" s="452" t="n"/>
-      <c r="AM5" s="452" t="n"/>
-      <c r="AN5" s="453" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="519" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="520" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="521" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="459" t="n"/>
-      <c r="E6" s="459" t="n"/>
-      <c r="F6" s="459" t="n"/>
-      <c r="G6" s="459" t="n"/>
-      <c r="H6" s="459" t="n"/>
-      <c r="I6" s="459" t="n"/>
-      <c r="J6" s="459" t="n"/>
-      <c r="K6" s="459" t="n"/>
-      <c r="L6" s="459" t="n"/>
-      <c r="M6" s="459" t="n"/>
-      <c r="N6" s="459" t="n"/>
-      <c r="O6" s="459" t="n"/>
-      <c r="P6" s="459" t="n"/>
-      <c r="Q6" s="459" t="n"/>
-      <c r="R6" s="459" t="n"/>
-      <c r="S6" s="459" t="n"/>
-      <c r="T6" s="459" t="n"/>
-      <c r="U6" s="459" t="n"/>
-      <c r="V6" s="459" t="n"/>
-      <c r="W6" s="459" t="n"/>
-      <c r="X6" s="459" t="n"/>
-      <c r="Y6" s="459" t="n"/>
-      <c r="Z6" s="459" t="n"/>
-      <c r="AA6" s="459" t="n"/>
-      <c r="AB6" s="459" t="n"/>
-      <c r="AC6" s="459" t="n"/>
-      <c r="AD6" s="459" t="n"/>
-      <c r="AE6" s="459" t="n"/>
-      <c r="AF6" s="459" t="n"/>
-      <c r="AG6" s="459" t="n"/>
-      <c r="AH6" s="459" t="n"/>
-      <c r="AI6" s="459" t="n"/>
-      <c r="AJ6" s="459" t="n"/>
-      <c r="AK6" s="459" t="n"/>
-      <c r="AL6" s="459" t="n"/>
-      <c r="AM6" s="459" t="n"/>
-      <c r="AN6" s="462" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="522" t="inlineStr">
-        <is>
-          <t>SOP-401</t>
-        </is>
-      </c>
-      <c r="B7" s="523" t="inlineStr">
-        <is>
-          <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="524" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
-        </is>
-      </c>
-      <c r="D7" s="343" t="n"/>
-      <c r="E7" s="343" t="n"/>
-      <c r="F7" s="343" t="n"/>
-      <c r="G7" s="343" t="n"/>
-      <c r="H7" s="343" t="n"/>
-      <c r="I7" s="343" t="n"/>
-      <c r="J7" s="343" t="n"/>
-      <c r="K7" s="343" t="n"/>
-      <c r="L7" s="343" t="n"/>
-      <c r="M7" s="343" t="n"/>
-      <c r="N7" s="343" t="n"/>
-      <c r="O7" s="343" t="n"/>
-      <c r="P7" s="343" t="n"/>
-      <c r="Q7" s="343" t="n"/>
-      <c r="R7" s="343" t="n"/>
-      <c r="S7" s="343" t="n"/>
-      <c r="T7" s="343" t="n"/>
-      <c r="U7" s="343" t="n"/>
-      <c r="V7" s="343" t="n"/>
-      <c r="W7" s="343" t="n"/>
-      <c r="X7" s="343" t="n"/>
-      <c r="Y7" s="343" t="n"/>
-      <c r="Z7" s="343" t="n"/>
-      <c r="AA7" s="343" t="n"/>
-      <c r="AB7" s="343" t="n"/>
-      <c r="AC7" s="343" t="n"/>
-      <c r="AD7" s="343" t="n"/>
-      <c r="AE7" s="343" t="n"/>
-      <c r="AF7" s="343" t="n"/>
-      <c r="AG7" s="343" t="n"/>
-      <c r="AH7" s="343" t="n"/>
-      <c r="AI7" s="343" t="n"/>
-      <c r="AJ7" s="343" t="n"/>
-      <c r="AK7" s="343" t="n"/>
-      <c r="AL7" s="343" t="n"/>
-      <c r="AM7" s="343" t="n"/>
-      <c r="AN7" s="466" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="463" t="inlineStr">
-        <is>
-          <t>WI-206</t>
-        </is>
-      </c>
-      <c r="B8" s="464" t="inlineStr">
-        <is>
-          <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
-        </is>
-      </c>
-      <c r="C8" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
-        </is>
-      </c>
-      <c r="D8" s="355" t="n"/>
-      <c r="E8" s="355" t="n"/>
-      <c r="F8" s="355" t="n"/>
-      <c r="G8" s="355" t="n"/>
-      <c r="H8" s="355" t="n"/>
-      <c r="I8" s="355" t="n"/>
-      <c r="J8" s="355" t="n"/>
-      <c r="K8" s="355" t="n"/>
-      <c r="L8" s="355" t="n"/>
-      <c r="M8" s="355" t="n"/>
-      <c r="N8" s="355" t="n"/>
-      <c r="O8" s="355" t="n"/>
-      <c r="P8" s="355" t="n"/>
-      <c r="Q8" s="355" t="n"/>
-      <c r="R8" s="355" t="n"/>
-      <c r="S8" s="355" t="n"/>
-      <c r="T8" s="355" t="n"/>
-      <c r="U8" s="355" t="n"/>
-      <c r="V8" s="355" t="n"/>
-      <c r="W8" s="355" t="n"/>
-      <c r="X8" s="355" t="n"/>
-      <c r="Y8" s="355" t="n"/>
-      <c r="Z8" s="355" t="n"/>
-      <c r="AA8" s="355" t="n"/>
-      <c r="AB8" s="355" t="n"/>
-      <c r="AC8" s="355" t="n"/>
-      <c r="AD8" s="355" t="n"/>
-      <c r="AE8" s="355" t="n"/>
-      <c r="AF8" s="355" t="n"/>
-      <c r="AG8" s="355" t="n"/>
-      <c r="AH8" s="355" t="n"/>
-      <c r="AI8" s="355" t="n"/>
-      <c r="AJ8" s="355" t="n"/>
-      <c r="AK8" s="355" t="n"/>
-      <c r="AL8" s="355" t="n"/>
-      <c r="AM8" s="355" t="n"/>
-      <c r="AN8" s="503" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="463" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001</t>
-        </is>
-      </c>
-      <c r="B9" s="464" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-        </is>
-      </c>
-      <c r="C9" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-        </is>
-      </c>
-      <c r="D9" s="355" t="n"/>
-      <c r="E9" s="355" t="n"/>
-      <c r="F9" s="355" t="n"/>
-      <c r="G9" s="355" t="n"/>
-      <c r="H9" s="355" t="n"/>
-      <c r="I9" s="355" t="n"/>
-      <c r="J9" s="355" t="n"/>
-      <c r="K9" s="355" t="n"/>
-      <c r="L9" s="355" t="n"/>
-      <c r="M9" s="355" t="n"/>
-      <c r="N9" s="355" t="n"/>
-      <c r="O9" s="355" t="n"/>
-      <c r="P9" s="355" t="n"/>
-      <c r="Q9" s="355" t="n"/>
-      <c r="R9" s="355" t="n"/>
-      <c r="S9" s="355" t="n"/>
-      <c r="T9" s="355" t="n"/>
-      <c r="U9" s="355" t="n"/>
-      <c r="V9" s="355" t="n"/>
-      <c r="W9" s="355" t="n"/>
-      <c r="X9" s="355" t="n"/>
-      <c r="Y9" s="355" t="n"/>
-      <c r="Z9" s="355" t="n"/>
-      <c r="AA9" s="355" t="n"/>
-      <c r="AB9" s="355" t="n"/>
-      <c r="AC9" s="355" t="n"/>
-      <c r="AD9" s="355" t="n"/>
-      <c r="AE9" s="355" t="n"/>
-      <c r="AF9" s="355" t="n"/>
-      <c r="AG9" s="355" t="n"/>
-      <c r="AH9" s="355" t="n"/>
-      <c r="AI9" s="355" t="n"/>
-      <c r="AJ9" s="355" t="n"/>
-      <c r="AK9" s="355" t="n"/>
-      <c r="AL9" s="355" t="n"/>
-      <c r="AM9" s="355" t="n"/>
-      <c r="AN9" s="503" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="463" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002</t>
-        </is>
-      </c>
-      <c r="B10" s="464" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-        </is>
-      </c>
-      <c r="C10" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-        </is>
-      </c>
-      <c r="D10" s="355" t="n"/>
-      <c r="E10" s="355" t="n"/>
-      <c r="F10" s="355" t="n"/>
-      <c r="G10" s="355" t="n"/>
-      <c r="H10" s="355" t="n"/>
-      <c r="I10" s="355" t="n"/>
-      <c r="J10" s="355" t="n"/>
-      <c r="K10" s="355" t="n"/>
-      <c r="L10" s="355" t="n"/>
-      <c r="M10" s="355" t="n"/>
-      <c r="N10" s="355" t="n"/>
-      <c r="O10" s="355" t="n"/>
-      <c r="P10" s="355" t="n"/>
-      <c r="Q10" s="355" t="n"/>
-      <c r="R10" s="355" t="n"/>
-      <c r="S10" s="355" t="n"/>
-      <c r="T10" s="355" t="n"/>
-      <c r="U10" s="355" t="n"/>
-      <c r="V10" s="355" t="n"/>
-      <c r="W10" s="355" t="n"/>
-      <c r="X10" s="355" t="n"/>
-      <c r="Y10" s="355" t="n"/>
-      <c r="Z10" s="355" t="n"/>
-      <c r="AA10" s="355" t="n"/>
-      <c r="AB10" s="355" t="n"/>
-      <c r="AC10" s="355" t="n"/>
-      <c r="AD10" s="355" t="n"/>
-      <c r="AE10" s="355" t="n"/>
-      <c r="AF10" s="355" t="n"/>
-      <c r="AG10" s="355" t="n"/>
-      <c r="AH10" s="355" t="n"/>
-      <c r="AI10" s="355" t="n"/>
-      <c r="AJ10" s="355" t="n"/>
-      <c r="AK10" s="355" t="n"/>
-      <c r="AL10" s="355" t="n"/>
-      <c r="AM10" s="355" t="n"/>
-      <c r="AN10" s="503" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="463" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003</t>
-        </is>
-      </c>
-      <c r="B11" s="464" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-        </is>
-      </c>
-      <c r="C11" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
-        </is>
-      </c>
-      <c r="D11" s="355" t="n"/>
-      <c r="E11" s="355" t="n"/>
-      <c r="F11" s="355" t="n"/>
-      <c r="G11" s="355" t="n"/>
-      <c r="H11" s="355" t="n"/>
-      <c r="I11" s="355" t="n"/>
-      <c r="J11" s="355" t="n"/>
-      <c r="K11" s="355" t="n"/>
-      <c r="L11" s="355" t="n"/>
-      <c r="M11" s="355" t="n"/>
-      <c r="N11" s="355" t="n"/>
-      <c r="O11" s="355" t="n"/>
-      <c r="P11" s="355" t="n"/>
-      <c r="Q11" s="355" t="n"/>
-      <c r="R11" s="355" t="n"/>
-      <c r="S11" s="355" t="n"/>
-      <c r="T11" s="355" t="n"/>
-      <c r="U11" s="355" t="n"/>
-      <c r="V11" s="355" t="n"/>
-      <c r="W11" s="355" t="n"/>
-      <c r="X11" s="355" t="n"/>
-      <c r="Y11" s="355" t="n"/>
-      <c r="Z11" s="355" t="n"/>
-      <c r="AA11" s="355" t="n"/>
-      <c r="AB11" s="355" t="n"/>
-      <c r="AC11" s="355" t="n"/>
-      <c r="AD11" s="355" t="n"/>
-      <c r="AE11" s="355" t="n"/>
-      <c r="AF11" s="355" t="n"/>
-      <c r="AG11" s="355" t="n"/>
-      <c r="AH11" s="355" t="n"/>
-      <c r="AI11" s="355" t="n"/>
-      <c r="AJ11" s="355" t="n"/>
-      <c r="AK11" s="355" t="n"/>
-      <c r="AL11" s="355" t="n"/>
-      <c r="AM11" s="355" t="n"/>
-      <c r="AN11" s="503" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="463" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002</t>
-        </is>
-      </c>
-      <c r="B12" s="464" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-        </is>
-      </c>
-      <c r="C12" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-        </is>
-      </c>
-      <c r="D12" s="355" t="n"/>
-      <c r="E12" s="355" t="n"/>
-      <c r="F12" s="355" t="n"/>
-      <c r="G12" s="355" t="n"/>
-      <c r="H12" s="355" t="n"/>
-      <c r="I12" s="355" t="n"/>
-      <c r="J12" s="355" t="n"/>
-      <c r="K12" s="355" t="n"/>
-      <c r="L12" s="355" t="n"/>
-      <c r="M12" s="355" t="n"/>
-      <c r="N12" s="355" t="n"/>
-      <c r="O12" s="355" t="n"/>
-      <c r="P12" s="355" t="n"/>
-      <c r="Q12" s="355" t="n"/>
-      <c r="R12" s="355" t="n"/>
-      <c r="S12" s="355" t="n"/>
-      <c r="T12" s="355" t="n"/>
-      <c r="U12" s="355" t="n"/>
-      <c r="V12" s="355" t="n"/>
-      <c r="W12" s="355" t="n"/>
-      <c r="X12" s="355" t="n"/>
-      <c r="Y12" s="355" t="n"/>
-      <c r="Z12" s="355" t="n"/>
-      <c r="AA12" s="355" t="n"/>
-      <c r="AB12" s="355" t="n"/>
-      <c r="AC12" s="355" t="n"/>
-      <c r="AD12" s="355" t="n"/>
-      <c r="AE12" s="355" t="n"/>
-      <c r="AF12" s="355" t="n"/>
-      <c r="AG12" s="355" t="n"/>
-      <c r="AH12" s="355" t="n"/>
-      <c r="AI12" s="355" t="n"/>
-      <c r="AJ12" s="355" t="n"/>
-      <c r="AK12" s="355" t="n"/>
-      <c r="AL12" s="355" t="n"/>
-      <c r="AM12" s="355" t="n"/>
-      <c r="AN12" s="503" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="502" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B13" s="526" t="inlineStr">
-        <is>
-          <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C13" s="355" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D13" s="355" t="n"/>
-      <c r="E13" s="355" t="n"/>
-      <c r="F13" s="355" t="n"/>
-      <c r="G13" s="355" t="n"/>
-      <c r="H13" s="355" t="n"/>
-      <c r="I13" s="355" t="n"/>
-      <c r="J13" s="355" t="n"/>
-      <c r="K13" s="355" t="n"/>
-      <c r="L13" s="355" t="n"/>
-      <c r="M13" s="355" t="n"/>
-      <c r="N13" s="355" t="n"/>
-      <c r="O13" s="355" t="n"/>
-      <c r="P13" s="355" t="n"/>
-      <c r="Q13" s="355" t="n"/>
-      <c r="R13" s="355" t="n"/>
-      <c r="S13" s="355" t="n"/>
-      <c r="T13" s="355" t="n"/>
-      <c r="U13" s="355" t="n"/>
-      <c r="V13" s="355" t="n"/>
-      <c r="W13" s="355" t="n"/>
-      <c r="X13" s="355" t="n"/>
-      <c r="Y13" s="355" t="n"/>
-      <c r="Z13" s="355" t="n"/>
-      <c r="AA13" s="355" t="n"/>
-      <c r="AB13" s="355" t="n"/>
-      <c r="AC13" s="355" t="n"/>
-      <c r="AD13" s="355" t="n"/>
-      <c r="AE13" s="355" t="n"/>
-      <c r="AF13" s="355" t="n"/>
-      <c r="AG13" s="355" t="n"/>
-      <c r="AH13" s="355" t="n"/>
-      <c r="AI13" s="355" t="n"/>
-      <c r="AJ13" s="355" t="n"/>
-      <c r="AK13" s="355" t="n"/>
-      <c r="AL13" s="355" t="n"/>
-      <c r="AM13" s="355" t="n"/>
-      <c r="AN13" s="503" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="504" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B14" s="527" t="inlineStr">
-        <is>
-          <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
-        </is>
-      </c>
-      <c r="C14" s="505" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D14" s="505" t="n"/>
-      <c r="E14" s="505" t="n"/>
-      <c r="F14" s="505" t="n"/>
-      <c r="G14" s="505" t="n"/>
-      <c r="H14" s="505" t="n"/>
-      <c r="I14" s="505" t="n"/>
-      <c r="J14" s="505" t="n"/>
-      <c r="K14" s="505" t="n"/>
-      <c r="L14" s="505" t="n"/>
-      <c r="M14" s="505" t="n"/>
-      <c r="N14" s="505" t="n"/>
-      <c r="O14" s="505" t="n"/>
-      <c r="P14" s="505" t="n"/>
-      <c r="Q14" s="505" t="n"/>
-      <c r="R14" s="505" t="n"/>
-      <c r="S14" s="505" t="n"/>
-      <c r="T14" s="505" t="n"/>
-      <c r="U14" s="505" t="n"/>
-      <c r="V14" s="505" t="n"/>
-      <c r="W14" s="505" t="n"/>
-      <c r="X14" s="505" t="n"/>
-      <c r="Y14" s="505" t="n"/>
-      <c r="Z14" s="505" t="n"/>
-      <c r="AA14" s="505" t="n"/>
-      <c r="AB14" s="505" t="n"/>
-      <c r="AC14" s="505" t="n"/>
-      <c r="AD14" s="505" t="n"/>
-      <c r="AE14" s="505" t="n"/>
-      <c r="AF14" s="505" t="n"/>
-      <c r="AG14" s="505" t="n"/>
-      <c r="AH14" s="505" t="n"/>
-      <c r="AI14" s="505" t="n"/>
-      <c r="AJ14" s="505" t="n"/>
-      <c r="AK14" s="505" t="n"/>
-      <c r="AL14" s="505" t="n"/>
-      <c r="AM14" s="505" t="n"/>
-      <c r="AN14" s="506" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="329"/>
-    <row r="16" ht="20" customHeight="1" s="329"/>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
-    <row r="24" ht="20" customHeight="1" s="329"/>
-    <row r="25" ht="20" customHeight="1" s="329"/>
-    <row r="26" ht="20" customHeight="1" s="329"/>
-    <row r="27" ht="20" customHeight="1" s="329"/>
-    <row r="28" ht="20" customHeight="1" s="329"/>
-    <row r="29" ht="20" customHeight="1" s="329"/>
-    <row r="30" ht="20" customHeight="1" s="329"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="507" t="inlineStr">
-        <is>
-          <t>Evidence Reference / Attachment Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="529" t="n"/>
-      <c r="C1" s="529" t="n"/>
-      <c r="D1" s="529" t="n"/>
-      <c r="E1" s="529" t="n"/>
-      <c r="F1" s="529" t="n"/>
-      <c r="G1" s="529" t="n"/>
-      <c r="H1" s="508" t="n"/>
-      <c r="I1" s="419" t="n"/>
-      <c r="J1" s="420" t="n"/>
-      <c r="K1" s="420" t="n"/>
-      <c r="L1" s="420" t="n"/>
-      <c r="M1" s="420" t="n"/>
-      <c r="N1" s="420" t="n"/>
-      <c r="O1" s="420" t="n"/>
-      <c r="P1" s="420" t="n"/>
-      <c r="Q1" s="420" t="n"/>
-      <c r="R1" s="420" t="n"/>
-      <c r="S1" s="420" t="n"/>
-      <c r="T1" s="420" t="n"/>
-      <c r="U1" s="420" t="n"/>
-      <c r="V1" s="420" t="n"/>
-      <c r="W1" s="420" t="n"/>
-      <c r="X1" s="420" t="n"/>
-      <c r="Y1" s="420" t="n"/>
-      <c r="Z1" s="420" t="n"/>
-      <c r="AA1" s="420" t="n"/>
-      <c r="AB1" s="420" t="n"/>
-      <c r="AC1" s="420" t="n"/>
-      <c r="AD1" s="421" t="n"/>
-      <c r="AE1" s="422" t="n"/>
-      <c r="AF1" s="423" t="n"/>
-      <c r="AG1" s="423" t="n"/>
-      <c r="AH1" s="424" t="n"/>
-      <c r="AI1" s="425" t="n"/>
-      <c r="AJ1" s="426" t="n"/>
-      <c r="AK1" s="426" t="n"/>
-      <c r="AL1" s="426" t="n"/>
-      <c r="AM1" s="426" t="n"/>
-      <c r="AN1" s="427" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="509" t="inlineStr">
-        <is>
-          <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-        </is>
-      </c>
-      <c r="H2" s="510" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="431" t="n"/>
-      <c r="K2" s="431" t="n"/>
-      <c r="L2" s="431" t="n"/>
-      <c r="M2" s="431" t="n"/>
-      <c r="N2" s="431" t="n"/>
-      <c r="O2" s="431" t="n"/>
-      <c r="P2" s="431" t="n"/>
-      <c r="Q2" s="431" t="n"/>
-      <c r="R2" s="431" t="n"/>
-      <c r="S2" s="431" t="n"/>
-      <c r="T2" s="431" t="n"/>
-      <c r="U2" s="431" t="n"/>
-      <c r="V2" s="431" t="n"/>
-      <c r="W2" s="431" t="n"/>
-      <c r="X2" s="431" t="n"/>
-      <c r="Y2" s="431" t="n"/>
-      <c r="Z2" s="431" t="n"/>
-      <c r="AA2" s="431" t="n"/>
-      <c r="AB2" s="431" t="n"/>
-      <c r="AC2" s="431" t="n"/>
-      <c r="AD2" s="432" t="n"/>
-      <c r="AE2" s="433" t="n"/>
-      <c r="AF2" s="434" t="n"/>
-      <c r="AG2" s="434" t="n"/>
-      <c r="AH2" s="435" t="n"/>
-      <c r="AI2" s="436" t="n"/>
-      <c r="AJ2" s="437" t="n"/>
-      <c r="AK2" s="437" t="n"/>
-      <c r="AL2" s="437" t="n"/>
-      <c r="AM2" s="437" t="n"/>
-      <c r="AN2" s="438" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="511" t="n"/>
-      <c r="B3" s="512" t="n"/>
-      <c r="C3" s="512" t="n"/>
-      <c r="D3" s="512" t="n"/>
-      <c r="E3" s="512" t="n"/>
-      <c r="F3" s="512" t="n"/>
-      <c r="G3" s="512" t="n"/>
-      <c r="H3" s="510" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="431" t="n"/>
-      <c r="K3" s="431" t="n"/>
-      <c r="L3" s="431" t="n"/>
-      <c r="M3" s="431" t="n"/>
-      <c r="N3" s="431" t="n"/>
-      <c r="O3" s="431" t="n"/>
-      <c r="P3" s="431" t="n"/>
-      <c r="Q3" s="431" t="n"/>
-      <c r="R3" s="431" t="n"/>
-      <c r="S3" s="431" t="n"/>
-      <c r="T3" s="431" t="n"/>
-      <c r="U3" s="431" t="n"/>
-      <c r="V3" s="431" t="n"/>
-      <c r="W3" s="431" t="n"/>
-      <c r="X3" s="431" t="n"/>
-      <c r="Y3" s="431" t="n"/>
-      <c r="Z3" s="431" t="n"/>
-      <c r="AA3" s="431" t="n"/>
-      <c r="AB3" s="431" t="n"/>
-      <c r="AC3" s="431" t="n"/>
-      <c r="AD3" s="432" t="n"/>
-      <c r="AE3" s="433" t="n"/>
-      <c r="AF3" s="434" t="n"/>
-      <c r="AG3" s="434" t="n"/>
-      <c r="AH3" s="435" t="n"/>
-      <c r="AI3" s="436" t="n"/>
-      <c r="AJ3" s="437" t="n"/>
-      <c r="AK3" s="437" t="n"/>
-      <c r="AL3" s="437" t="n"/>
-      <c r="AM3" s="437" t="n"/>
-      <c r="AN3" s="438" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="513" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="514" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="514" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="512" t="n"/>
-      <c r="E4" s="512" t="n"/>
-      <c r="F4" s="512" t="n"/>
-      <c r="G4" s="512" t="n"/>
-      <c r="H4" s="510" t="n"/>
-      <c r="I4" s="439" t="n"/>
-      <c r="J4" s="440" t="n"/>
-      <c r="K4" s="440" t="n"/>
-      <c r="L4" s="440" t="n"/>
-      <c r="M4" s="440" t="n"/>
-      <c r="N4" s="440" t="n"/>
-      <c r="O4" s="440" t="n"/>
-      <c r="P4" s="440" t="n"/>
-      <c r="Q4" s="440" t="n"/>
-      <c r="R4" s="440" t="n"/>
-      <c r="S4" s="440" t="n"/>
-      <c r="T4" s="440" t="n"/>
-      <c r="U4" s="440" t="n"/>
-      <c r="V4" s="440" t="n"/>
-      <c r="W4" s="440" t="n"/>
-      <c r="X4" s="440" t="n"/>
-      <c r="Y4" s="440" t="n"/>
-      <c r="Z4" s="440" t="n"/>
-      <c r="AA4" s="440" t="n"/>
-      <c r="AB4" s="440" t="n"/>
-      <c r="AC4" s="440" t="n"/>
-      <c r="AD4" s="441" t="n"/>
-      <c r="AE4" s="433" t="n"/>
-      <c r="AF4" s="434" t="n"/>
-      <c r="AG4" s="434" t="n"/>
-      <c r="AH4" s="435" t="n"/>
-      <c r="AI4" s="436" t="n"/>
-      <c r="AJ4" s="437" t="n"/>
-      <c r="AK4" s="437" t="n"/>
-      <c r="AL4" s="437" t="n"/>
-      <c r="AM4" s="437" t="n"/>
-      <c r="AN4" s="438" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="515" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="516" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="516" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="517" t="n"/>
-      <c r="E5" s="517" t="n"/>
-      <c r="F5" s="517" t="n"/>
-      <c r="G5" s="517" t="n"/>
-      <c r="H5" s="518" t="n"/>
-      <c r="I5" s="445" t="n"/>
-      <c r="J5" s="446" t="n"/>
-      <c r="K5" s="446" t="n"/>
-      <c r="L5" s="446" t="n"/>
-      <c r="M5" s="446" t="n"/>
-      <c r="N5" s="446" t="n"/>
-      <c r="O5" s="446" t="n"/>
-      <c r="P5" s="446" t="n"/>
-      <c r="Q5" s="446" t="n"/>
-      <c r="R5" s="446" t="n"/>
-      <c r="S5" s="446" t="n"/>
-      <c r="T5" s="446" t="n"/>
-      <c r="U5" s="446" t="n"/>
-      <c r="V5" s="446" t="n"/>
-      <c r="W5" s="446" t="n"/>
-      <c r="X5" s="446" t="n"/>
-      <c r="Y5" s="446" t="n"/>
-      <c r="Z5" s="446" t="n"/>
-      <c r="AA5" s="446" t="n"/>
-      <c r="AB5" s="446" t="n"/>
-      <c r="AC5" s="446" t="n"/>
-      <c r="AD5" s="447" t="n"/>
-      <c r="AE5" s="448" t="n"/>
-      <c r="AF5" s="449" t="n"/>
-      <c r="AG5" s="449" t="n"/>
-      <c r="AH5" s="450" t="n"/>
-      <c r="AI5" s="451" t="n"/>
-      <c r="AJ5" s="452" t="n"/>
-      <c r="AK5" s="452" t="n"/>
-      <c r="AL5" s="452" t="n"/>
-      <c r="AM5" s="452" t="n"/>
-      <c r="AN5" s="453" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="519" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="520" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="521" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-401; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-206; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="459" t="n"/>
-      <c r="E6" s="459" t="n"/>
-      <c r="F6" s="459" t="n"/>
-      <c r="G6" s="459" t="n"/>
-      <c r="H6" s="459" t="n"/>
-      <c r="I6" s="459" t="n"/>
-      <c r="J6" s="459" t="n"/>
-      <c r="K6" s="459" t="n"/>
-      <c r="L6" s="459" t="n"/>
-      <c r="M6" s="459" t="n"/>
-      <c r="N6" s="459" t="n"/>
-      <c r="O6" s="459" t="n"/>
-      <c r="P6" s="459" t="n"/>
-      <c r="Q6" s="459" t="n"/>
-      <c r="R6" s="459" t="n"/>
-      <c r="S6" s="459" t="n"/>
-      <c r="T6" s="459" t="n"/>
-      <c r="U6" s="459" t="n"/>
-      <c r="V6" s="459" t="n"/>
-      <c r="W6" s="459" t="n"/>
-      <c r="X6" s="459" t="n"/>
-      <c r="Y6" s="459" t="n"/>
-      <c r="Z6" s="459" t="n"/>
-      <c r="AA6" s="459" t="n"/>
-      <c r="AB6" s="459" t="n"/>
-      <c r="AC6" s="459" t="n"/>
-      <c r="AD6" s="459" t="n"/>
-      <c r="AE6" s="459" t="n"/>
-      <c r="AF6" s="459" t="n"/>
-      <c r="AG6" s="459" t="n"/>
-      <c r="AH6" s="459" t="n"/>
-      <c r="AI6" s="459" t="n"/>
-      <c r="AJ6" s="459" t="n"/>
-      <c r="AK6" s="459" t="n"/>
-      <c r="AL6" s="459" t="n"/>
-      <c r="AM6" s="459" t="n"/>
-      <c r="AN6" s="462" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="522" t="inlineStr">
-        <is>
-          <t>SOP-401</t>
-        </is>
-      </c>
-      <c r="B7" s="523" t="inlineStr">
-        <is>
-          <t>SOP-401 — Kiểm soát nhà cung cấp, mua hàng và công đoạn đặc biệt thuê ngoài | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="524" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-401-supplier-control-and-special-process.html</t>
-        </is>
-      </c>
-      <c r="D7" s="343" t="n"/>
-      <c r="E7" s="343" t="n"/>
-      <c r="F7" s="343" t="n"/>
-      <c r="G7" s="343" t="n"/>
-      <c r="H7" s="343" t="n"/>
-      <c r="I7" s="343" t="n"/>
-      <c r="J7" s="343" t="n"/>
-      <c r="K7" s="343" t="n"/>
-      <c r="L7" s="343" t="n"/>
-      <c r="M7" s="343" t="n"/>
-      <c r="N7" s="343" t="n"/>
-      <c r="O7" s="343" t="n"/>
-      <c r="P7" s="343" t="n"/>
-      <c r="Q7" s="343" t="n"/>
-      <c r="R7" s="343" t="n"/>
-      <c r="S7" s="343" t="n"/>
-      <c r="T7" s="343" t="n"/>
-      <c r="U7" s="343" t="n"/>
-      <c r="V7" s="343" t="n"/>
-      <c r="W7" s="343" t="n"/>
-      <c r="X7" s="343" t="n"/>
-      <c r="Y7" s="343" t="n"/>
-      <c r="Z7" s="343" t="n"/>
-      <c r="AA7" s="343" t="n"/>
-      <c r="AB7" s="343" t="n"/>
-      <c r="AC7" s="343" t="n"/>
-      <c r="AD7" s="343" t="n"/>
-      <c r="AE7" s="343" t="n"/>
-      <c r="AF7" s="343" t="n"/>
-      <c r="AG7" s="343" t="n"/>
-      <c r="AH7" s="343" t="n"/>
-      <c r="AI7" s="343" t="n"/>
-      <c r="AJ7" s="343" t="n"/>
-      <c r="AK7" s="343" t="n"/>
-      <c r="AL7" s="343" t="n"/>
-      <c r="AM7" s="343" t="n"/>
-      <c r="AN7" s="466" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="463" t="inlineStr">
-        <is>
-          <t>WI-206</t>
-        </is>
-      </c>
-      <c r="B8" s="464" t="inlineStr">
-        <is>
-          <t>WI-206 — Ship release pack, nhãn SSCC, đối soát kiện và bàn giao Ship Confirm</t>
-        </is>
-      </c>
-      <c r="C8" s="525" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/02-WI-200/wi-206-ship-release-pack-sscc-label-and-pack-reconciliation.html</t>
-        </is>
-      </c>
-      <c r="D8" s="355" t="n"/>
-      <c r="E8" s="355" t="n"/>
-      <c r="F8" s="355" t="n"/>
-      <c r="G8" s="355" t="n"/>
-      <c r="H8" s="355" t="n"/>
-      <c r="I8" s="355" t="n"/>
-      <c r="J8" s="355" t="n"/>
-      <c r="K8" s="355" t="n"/>
-      <c r="L8" s="355" t="n"/>
-      <c r="M8" s="355" t="n"/>
-      <c r="N8" s="355" t="n"/>
-      <c r="O8" s="355" t="n"/>
-      <c r="P8" s="355" t="n"/>
-      <c r="Q8" s="355" t="n"/>
-      <c r="R8" s="355" t="n"/>
-      <c r="S8" s="355" t="n"/>
-      <c r="T8" s="355" t="n"/>
-      <c r="U8" s="355" t="n"/>
-      <c r="V8" s="355" t="n"/>
-      <c r="W8" s="355" t="n"/>
-      <c r="X8" s="355" t="n"/>
-      <c r="Y8" s="355" t="n"/>
-      <c r="Z8" s="355" t="n"/>
-      <c r="AA8" s="355" t="n"/>
-      <c r="AB8" s="355" t="n"/>
-      <c r="AC8" s="355" t="n"/>
-      <c r="AD8" s="355" t="n"/>
-      <c r="AE8" s="355" t="n"/>
-      <c r="AF8" s="355" t="n"/>
-      <c r="AG8" s="355" t="n"/>
-      <c r="AH8" s="355" t="n"/>
-      <c r="AI8" s="355" t="n"/>
-      <c r="AJ8" s="355" t="n"/>
-      <c r="AK8" s="355" t="n"/>
-      <c r="AL8" s="355" t="n"/>
-      <c r="AM8" s="355" t="n"/>
-      <c r="AN8" s="503" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="502" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001</t>
-        </is>
-      </c>
-      <c r="B9" s="526" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-        </is>
-      </c>
-      <c r="C9" s="355" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-        </is>
-      </c>
-      <c r="D9" s="355" t="n"/>
-      <c r="E9" s="355" t="n"/>
-      <c r="F9" s="355" t="n"/>
-      <c r="G9" s="355" t="n"/>
-      <c r="H9" s="355" t="n"/>
-      <c r="I9" s="355" t="n"/>
-      <c r="J9" s="355" t="n"/>
-      <c r="K9" s="355" t="n"/>
-      <c r="L9" s="355" t="n"/>
-      <c r="M9" s="355" t="n"/>
-      <c r="N9" s="355" t="n"/>
-      <c r="O9" s="355" t="n"/>
-      <c r="P9" s="355" t="n"/>
-      <c r="Q9" s="355" t="n"/>
-      <c r="R9" s="355" t="n"/>
-      <c r="S9" s="355" t="n"/>
-      <c r="T9" s="355" t="n"/>
-      <c r="U9" s="355" t="n"/>
-      <c r="V9" s="355" t="n"/>
-      <c r="W9" s="355" t="n"/>
-      <c r="X9" s="355" t="n"/>
-      <c r="Y9" s="355" t="n"/>
-      <c r="Z9" s="355" t="n"/>
-      <c r="AA9" s="355" t="n"/>
-      <c r="AB9" s="355" t="n"/>
-      <c r="AC9" s="355" t="n"/>
-      <c r="AD9" s="355" t="n"/>
-      <c r="AE9" s="355" t="n"/>
-      <c r="AF9" s="355" t="n"/>
-      <c r="AG9" s="355" t="n"/>
-      <c r="AH9" s="355" t="n"/>
-      <c r="AI9" s="355" t="n"/>
-      <c r="AJ9" s="355" t="n"/>
-      <c r="AK9" s="355" t="n"/>
-      <c r="AL9" s="355" t="n"/>
-      <c r="AM9" s="355" t="n"/>
-      <c r="AN9" s="503" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="502" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002</t>
-        </is>
-      </c>
-      <c r="B10" s="526" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-        </is>
-      </c>
-      <c r="C10" s="355" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-        </is>
-      </c>
-      <c r="D10" s="355" t="n"/>
-      <c r="E10" s="355" t="n"/>
-      <c r="F10" s="355" t="n"/>
-      <c r="G10" s="355" t="n"/>
-      <c r="H10" s="355" t="n"/>
-      <c r="I10" s="355" t="n"/>
-      <c r="J10" s="355" t="n"/>
-      <c r="K10" s="355" t="n"/>
-      <c r="L10" s="355" t="n"/>
-      <c r="M10" s="355" t="n"/>
-      <c r="N10" s="355" t="n"/>
-      <c r="O10" s="355" t="n"/>
-      <c r="P10" s="355" t="n"/>
-      <c r="Q10" s="355" t="n"/>
-      <c r="R10" s="355" t="n"/>
-      <c r="S10" s="355" t="n"/>
-      <c r="T10" s="355" t="n"/>
-      <c r="U10" s="355" t="n"/>
-      <c r="V10" s="355" t="n"/>
-      <c r="W10" s="355" t="n"/>
-      <c r="X10" s="355" t="n"/>
-      <c r="Y10" s="355" t="n"/>
-      <c r="Z10" s="355" t="n"/>
-      <c r="AA10" s="355" t="n"/>
-      <c r="AB10" s="355" t="n"/>
-      <c r="AC10" s="355" t="n"/>
-      <c r="AD10" s="355" t="n"/>
-      <c r="AE10" s="355" t="n"/>
-      <c r="AF10" s="355" t="n"/>
-      <c r="AG10" s="355" t="n"/>
-      <c r="AH10" s="355" t="n"/>
-      <c r="AI10" s="355" t="n"/>
-      <c r="AJ10" s="355" t="n"/>
-      <c r="AK10" s="355" t="n"/>
-      <c r="AL10" s="355" t="n"/>
-      <c r="AM10" s="355" t="n"/>
-      <c r="AN10" s="503" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="502" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003</t>
-        </is>
-      </c>
-      <c r="B11" s="526" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-        </is>
-      </c>
-      <c r="C11" s="355" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
-        </is>
-      </c>
-      <c r="D11" s="355" t="n"/>
-      <c r="E11" s="355" t="n"/>
-      <c r="F11" s="355" t="n"/>
-      <c r="G11" s="355" t="n"/>
-      <c r="H11" s="355" t="n"/>
-      <c r="I11" s="355" t="n"/>
-      <c r="J11" s="355" t="n"/>
-      <c r="K11" s="355" t="n"/>
-      <c r="L11" s="355" t="n"/>
-      <c r="M11" s="355" t="n"/>
-      <c r="N11" s="355" t="n"/>
-      <c r="O11" s="355" t="n"/>
-      <c r="P11" s="355" t="n"/>
-      <c r="Q11" s="355" t="n"/>
-      <c r="R11" s="355" t="n"/>
-      <c r="S11" s="355" t="n"/>
-      <c r="T11" s="355" t="n"/>
-      <c r="U11" s="355" t="n"/>
-      <c r="V11" s="355" t="n"/>
-      <c r="W11" s="355" t="n"/>
-      <c r="X11" s="355" t="n"/>
-      <c r="Y11" s="355" t="n"/>
-      <c r="Z11" s="355" t="n"/>
-      <c r="AA11" s="355" t="n"/>
-      <c r="AB11" s="355" t="n"/>
-      <c r="AC11" s="355" t="n"/>
-      <c r="AD11" s="355" t="n"/>
-      <c r="AE11" s="355" t="n"/>
-      <c r="AF11" s="355" t="n"/>
-      <c r="AG11" s="355" t="n"/>
-      <c r="AH11" s="355" t="n"/>
-      <c r="AI11" s="355" t="n"/>
-      <c r="AJ11" s="355" t="n"/>
-      <c r="AK11" s="355" t="n"/>
-      <c r="AL11" s="355" t="n"/>
-      <c r="AM11" s="355" t="n"/>
-      <c r="AN11" s="503" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="502" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002</t>
-        </is>
-      </c>
-      <c r="B12" s="526" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-        </is>
-      </c>
-      <c r="C12" s="355" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-        </is>
-      </c>
-      <c r="D12" s="355" t="n"/>
-      <c r="E12" s="355" t="n"/>
-      <c r="F12" s="355" t="n"/>
-      <c r="G12" s="355" t="n"/>
-      <c r="H12" s="355" t="n"/>
-      <c r="I12" s="355" t="n"/>
-      <c r="J12" s="355" t="n"/>
-      <c r="K12" s="355" t="n"/>
-      <c r="L12" s="355" t="n"/>
-      <c r="M12" s="355" t="n"/>
-      <c r="N12" s="355" t="n"/>
-      <c r="O12" s="355" t="n"/>
-      <c r="P12" s="355" t="n"/>
-      <c r="Q12" s="355" t="n"/>
-      <c r="R12" s="355" t="n"/>
-      <c r="S12" s="355" t="n"/>
-      <c r="T12" s="355" t="n"/>
-      <c r="U12" s="355" t="n"/>
-      <c r="V12" s="355" t="n"/>
-      <c r="W12" s="355" t="n"/>
-      <c r="X12" s="355" t="n"/>
-      <c r="Y12" s="355" t="n"/>
-      <c r="Z12" s="355" t="n"/>
-      <c r="AA12" s="355" t="n"/>
-      <c r="AB12" s="355" t="n"/>
-      <c r="AC12" s="355" t="n"/>
-      <c r="AD12" s="355" t="n"/>
-      <c r="AE12" s="355" t="n"/>
-      <c r="AF12" s="355" t="n"/>
-      <c r="AG12" s="355" t="n"/>
-      <c r="AH12" s="355" t="n"/>
-      <c r="AI12" s="355" t="n"/>
-      <c r="AJ12" s="355" t="n"/>
-      <c r="AK12" s="355" t="n"/>
-      <c r="AL12" s="355" t="n"/>
-      <c r="AM12" s="355" t="n"/>
-      <c r="AN12" s="503" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="502" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B13" s="526" t="inlineStr">
-        <is>
-          <t>Open before the gate or release decision is taken. Never complete it retrospectively after the job, lot or shipment has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C13" s="355" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D13" s="355" t="n"/>
-      <c r="E13" s="355" t="n"/>
-      <c r="F13" s="355" t="n"/>
-      <c r="G13" s="355" t="n"/>
-      <c r="H13" s="355" t="n"/>
-      <c r="I13" s="355" t="n"/>
-      <c r="J13" s="355" t="n"/>
-      <c r="K13" s="355" t="n"/>
-      <c r="L13" s="355" t="n"/>
-      <c r="M13" s="355" t="n"/>
-      <c r="N13" s="355" t="n"/>
-      <c r="O13" s="355" t="n"/>
-      <c r="P13" s="355" t="n"/>
-      <c r="Q13" s="355" t="n"/>
-      <c r="R13" s="355" t="n"/>
-      <c r="S13" s="355" t="n"/>
-      <c r="T13" s="355" t="n"/>
-      <c r="U13" s="355" t="n"/>
-      <c r="V13" s="355" t="n"/>
-      <c r="W13" s="355" t="n"/>
-      <c r="X13" s="355" t="n"/>
-      <c r="Y13" s="355" t="n"/>
-      <c r="Z13" s="355" t="n"/>
-      <c r="AA13" s="355" t="n"/>
-      <c r="AB13" s="355" t="n"/>
-      <c r="AC13" s="355" t="n"/>
-      <c r="AD13" s="355" t="n"/>
-      <c r="AE13" s="355" t="n"/>
-      <c r="AF13" s="355" t="n"/>
-      <c r="AG13" s="355" t="n"/>
-      <c r="AH13" s="355" t="n"/>
-      <c r="AI13" s="355" t="n"/>
-      <c r="AJ13" s="355" t="n"/>
-      <c r="AK13" s="355" t="n"/>
-      <c r="AL13" s="355" t="n"/>
-      <c r="AM13" s="355" t="n"/>
-      <c r="AN13" s="503" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="504" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B14" s="527" t="inlineStr">
-        <is>
-          <t>Close only after the final gate disposition is recorded, all conditional actions are opened with owner and due date, and the evidence link is complete.</t>
-        </is>
-      </c>
-      <c r="C14" s="505" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D14" s="505" t="n"/>
-      <c r="E14" s="505" t="n"/>
-      <c r="F14" s="505" t="n"/>
-      <c r="G14" s="505" t="n"/>
-      <c r="H14" s="505" t="n"/>
-      <c r="I14" s="505" t="n"/>
-      <c r="J14" s="505" t="n"/>
-      <c r="K14" s="505" t="n"/>
-      <c r="L14" s="505" t="n"/>
-      <c r="M14" s="505" t="n"/>
-      <c r="N14" s="505" t="n"/>
-      <c r="O14" s="505" t="n"/>
-      <c r="P14" s="505" t="n"/>
-      <c r="Q14" s="505" t="n"/>
-      <c r="R14" s="505" t="n"/>
-      <c r="S14" s="505" t="n"/>
-      <c r="T14" s="505" t="n"/>
-      <c r="U14" s="505" t="n"/>
-      <c r="V14" s="505" t="n"/>
-      <c r="W14" s="505" t="n"/>
-      <c r="X14" s="505" t="n"/>
-      <c r="Y14" s="505" t="n"/>
-      <c r="Z14" s="505" t="n"/>
-      <c r="AA14" s="505" t="n"/>
-      <c r="AB14" s="505" t="n"/>
-      <c r="AC14" s="505" t="n"/>
-      <c r="AD14" s="505" t="n"/>
-      <c r="AE14" s="505" t="n"/>
-      <c r="AF14" s="505" t="n"/>
-      <c r="AG14" s="505" t="n"/>
-      <c r="AH14" s="505" t="n"/>
-      <c r="AI14" s="505" t="n"/>
-      <c r="AJ14" s="505" t="n"/>
-      <c r="AK14" s="505" t="n"/>
-      <c r="AL14" s="505" t="n"/>
-      <c r="AM14" s="505" t="n"/>
-      <c r="AN14" s="506" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="329"/>
-    <row r="16" ht="20" customHeight="1" s="329"/>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
-    <row r="24" ht="20" customHeight="1" s="329"/>
-    <row r="25" ht="20" customHeight="1" s="329"/>
-    <row r="26" ht="20" customHeight="1" s="329"/>
-    <row r="27" ht="20" customHeight="1" s="329"/>
-    <row r="28" ht="20" customHeight="1" s="329"/>
-    <row r="29" ht="20" customHeight="1" s="329"/>
-    <row r="30" ht="20" customHeight="1" s="329"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -13,282 +13,10 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
-  </si>
-  <si>
-    <t>  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
-  </si>
-  <si>
-    <t>  4. FINAL DECISION / CLOSURE</t>
-  </si>
-  <si>
-    <t>  5. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$27)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$5)+1</t>
-  </si>
-  <si>
-    <t>ACTION_STATUS</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Condition / Exception</t>
-  </si>
-  <si>
-    <t>Conditional Action Required (YES/NO)</t>
-  </si>
-  <si>
-    <t>Conditions / Exceptions / Actions</t>
-  </si>
-  <si>
-    <t>DISPATCH NOTES / CONDITIONALS</t>
-  </si>
-  <si>
-    <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>Dispatch Gate Status</t>
-  </si>
-  <si>
-    <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>Evidence / Criteria</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Expected Return Date</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-404</t>
-  </si>
-  <si>
-    <t>Final Decision</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INEFFECTIVE</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Linked Route / Package</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OVERDUE</t>
-  </si>
-  <si>
-    <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Open Actions Present (YES/NO)</t>
-  </si>
-  <si>
-    <t>Outsource Dispatch Checklist</t>
-  </si>
-  <si>
-    <t>Outsource Dispatch ID</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PO / Work Order</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Package Ref</t>
-  </si>
-  <si>
-    <t>Part / Lot / Qty</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Prepared by / Date-Time</t>
-  </si>
-  <si>
-    <t>Purchasing + QA</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Qty Dispatched</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Release Status</t>
-  </si>
-  <si>
-    <t>Required Action</t>
-  </si>
-  <si>
-    <t>Requirement / Check</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Route Step / Due Date</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Supplier / Customer Spec Ref</t>
-  </si>
-  <si>
-    <t>Supplier / Processor</t>
-  </si>
-  <si>
-    <t>Supplier-Quality Owner</t>
-  </si>
-  <si>
-    <t>Target Closeout</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VERIFIED</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="88">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -785,6 +513,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="53">
     <fill>
@@ -1049,7 +780,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="362">
+  <borders count="363">
     <border>
       <left/>
       <right/>
@@ -4962,12 +4693,22 @@
         <color rgb="00F9A825"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="577">
+  <cellXfs count="597">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6267,6 +6008,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -8541,7 +8316,7 @@
       <c r="AM43" s="352" t="n"/>
       <c r="AN43" s="352" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1" s="329">
+    <row r="44" ht="26" customHeight="1" s="329">
       <c r="A44" s="571" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
@@ -8740,250 +8515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" style="329" min="1" max="1"/>
-    <col width="18" customWidth="1" style="329" min="2" max="2"/>
-    <col width="18" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="18" customWidth="1" style="329" min="6" max="6"/>
-    <col width="20" customWidth="1" style="329" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="265" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-      <c r="B1" s="265" t="inlineStr">
-        <is>
-          <t>DISPOSITION_GATE</t>
-        </is>
-      </c>
-      <c r="C1" s="265" t="inlineStr">
-        <is>
-          <t>YES_NO</t>
-        </is>
-      </c>
-      <c r="D1" s="265" t="inlineStr">
-        <is>
-          <t>OWNER_DEPT</t>
-        </is>
-      </c>
-      <c r="E1" s="265" t="inlineStr">
-        <is>
-          <t>ACTION_STATUS</t>
-        </is>
-      </c>
-      <c r="F1" s="265" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="G1" s="265" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="266" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="266" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="C2" s="266" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D2" s="266" t="inlineStr">
-        <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="E2" s="266" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F2" s="266" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G2" s="266" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B3" s="266" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="C3" s="266" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D3" s="266" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="E3" s="266" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="F3" s="266" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="G3" s="266" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="266" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B4" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C4" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D4" s="266" t="inlineStr">
-        <is>
-          <t>PLANNING</t>
-        </is>
-      </c>
-      <c r="E4" s="266" t="inlineStr">
-        <is>
-          <t>OVERDUE</t>
-        </is>
-      </c>
-      <c r="F4" s="266" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="G4" s="266" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" s="266" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="C5" s="266" t="n"/>
-      <c r="D5" s="266" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
-      </c>
-      <c r="E5" s="347" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="F5" s="266" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="G5" s="266" t="n"/>
-    </row>
-    <row r="6">
-      <c r="D6" s="347" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E6" s="347" t="inlineStr">
-        <is>
-          <t>INEFFECTIVE</t>
-        </is>
-      </c>
-      <c r="F6" s="266" t="n"/>
-      <c r="G6" s="266" t="n"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="347" t="inlineStr">
-        <is>
-          <t>PUR</t>
-        </is>
-      </c>
-      <c r="E7" s="347" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="F7" s="266" t="n"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="347" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="F8" s="266" t="n"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="347" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F9" s="266" t="n"/>
-    </row>
-    <row r="10">
-      <c r="D10" s="347" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F10" s="266" t="n"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="347" t="inlineStr">
-        <is>
-          <t>MGT</t>
-        </is>
-      </c>
-      <c r="F11" s="266" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9028,673 +8560,2167 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="499" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="577" t="n"/>
+      <c r="B1" s="578" t="n"/>
+      <c r="C1" s="578" t="n"/>
+      <c r="D1" s="578" t="n"/>
+      <c r="E1" s="578" t="n"/>
+      <c r="F1" s="578" t="n"/>
+      <c r="G1" s="578" t="n"/>
+      <c r="H1" s="579" t="n"/>
+      <c r="I1" s="580" t="inlineStr">
+        <is>
+          <t>Outsource Dispatch Checklist</t>
+        </is>
+      </c>
+      <c r="J1" s="578" t="n"/>
+      <c r="K1" s="578" t="n"/>
+      <c r="L1" s="578" t="n"/>
+      <c r="M1" s="578" t="n"/>
+      <c r="N1" s="578" t="n"/>
+      <c r="O1" s="578" t="n"/>
+      <c r="P1" s="578" t="n"/>
+      <c r="Q1" s="578" t="n"/>
+      <c r="R1" s="578" t="n"/>
+      <c r="S1" s="578" t="n"/>
+      <c r="T1" s="578" t="n"/>
+      <c r="U1" s="578" t="n"/>
+      <c r="V1" s="578" t="n"/>
+      <c r="W1" s="578" t="n"/>
+      <c r="X1" s="578" t="n"/>
+      <c r="Y1" s="578" t="n"/>
+      <c r="Z1" s="578" t="n"/>
+      <c r="AA1" s="578" t="n"/>
+      <c r="AB1" s="578" t="n"/>
+      <c r="AC1" s="578" t="n"/>
+      <c r="AD1" s="579" t="n"/>
+      <c r="AE1" s="423" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="578" t="n"/>
+      <c r="AG1" s="578" t="n"/>
+      <c r="AH1" s="581" t="n"/>
+      <c r="AI1" s="426" t="n"/>
+      <c r="AJ1" s="578" t="n"/>
+      <c r="AK1" s="578" t="n"/>
+      <c r="AL1" s="578" t="n"/>
+      <c r="AM1" s="578" t="n"/>
+      <c r="AN1" s="579" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="582" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="583" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="583" t="n"/>
+      <c r="AE2" s="584" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="585" t="n"/>
+      <c r="AI2" s="586" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="583" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="582" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="583" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="583" t="n"/>
+      <c r="AE3" s="584" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="585" t="n"/>
+      <c r="AI3" s="586" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="583" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="582" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="583" t="n"/>
+      <c r="I4" s="587" t="inlineStr">
+        <is>
+          <t>Quality Management System · Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="583" t="n"/>
+      <c r="AE4" s="584" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="585" t="n"/>
+      <c r="AI4" s="586" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="583" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="588" t="n"/>
+      <c r="B5" s="589" t="n"/>
+      <c r="C5" s="589" t="n"/>
+      <c r="D5" s="589" t="n"/>
+      <c r="E5" s="589" t="n"/>
+      <c r="F5" s="589" t="n"/>
+      <c r="G5" s="589" t="n"/>
+      <c r="H5" s="590" t="n"/>
+      <c r="I5" s="591" t="inlineStr">
+        <is>
+          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="J5" s="589" t="n"/>
+      <c r="K5" s="589" t="n"/>
+      <c r="L5" s="589" t="n"/>
+      <c r="M5" s="589" t="n"/>
+      <c r="N5" s="589" t="n"/>
+      <c r="O5" s="589" t="n"/>
+      <c r="P5" s="589" t="n"/>
+      <c r="Q5" s="589" t="n"/>
+      <c r="R5" s="589" t="n"/>
+      <c r="S5" s="589" t="n"/>
+      <c r="T5" s="589" t="n"/>
+      <c r="U5" s="589" t="n"/>
+      <c r="V5" s="589" t="n"/>
+      <c r="W5" s="589" t="n"/>
+      <c r="X5" s="589" t="n"/>
+      <c r="Y5" s="589" t="n"/>
+      <c r="Z5" s="589" t="n"/>
+      <c r="AA5" s="589" t="n"/>
+      <c r="AB5" s="589" t="n"/>
+      <c r="AC5" s="589" t="n"/>
+      <c r="AD5" s="590" t="n"/>
+      <c r="AE5" s="592" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="589" t="n"/>
+      <c r="AG5" s="589" t="n"/>
+      <c r="AH5" s="593" t="n"/>
+      <c r="AI5" s="594" t="n"/>
+      <c r="AJ5" s="589" t="n"/>
+      <c r="AK5" s="589" t="n"/>
+      <c r="AL5" s="589" t="n"/>
+      <c r="AM5" s="589" t="n"/>
+      <c r="AN5" s="590" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="595" t="n"/>
+      <c r="B6" s="595" t="n"/>
+      <c r="C6" s="595" t="n"/>
+      <c r="D6" s="595" t="n"/>
+      <c r="E6" s="595" t="n"/>
+      <c r="F6" s="595" t="n"/>
+      <c r="G6" s="595" t="n"/>
+      <c r="H6" s="595" t="n"/>
+      <c r="I6" s="595" t="n"/>
+      <c r="J6" s="595" t="n"/>
+      <c r="K6" s="595" t="n"/>
+      <c r="L6" s="595" t="n"/>
+      <c r="M6" s="595" t="n"/>
+      <c r="N6" s="595" t="n"/>
+      <c r="O6" s="595" t="n"/>
+      <c r="P6" s="595" t="n"/>
+      <c r="Q6" s="595" t="n"/>
+      <c r="R6" s="595" t="n"/>
+      <c r="S6" s="595" t="n"/>
+      <c r="T6" s="595" t="n"/>
+      <c r="U6" s="595" t="n"/>
+      <c r="V6" s="595" t="n"/>
+      <c r="W6" s="595" t="n"/>
+      <c r="X6" s="595" t="n"/>
+      <c r="Y6" s="595" t="n"/>
+      <c r="Z6" s="595" t="n"/>
+      <c r="AA6" s="595" t="n"/>
+      <c r="AB6" s="595" t="n"/>
+      <c r="AC6" s="595" t="n"/>
+      <c r="AD6" s="595" t="n"/>
+      <c r="AE6" s="595" t="n"/>
+      <c r="AF6" s="595" t="n"/>
+      <c r="AG6" s="595" t="n"/>
+      <c r="AH6" s="595" t="n"/>
+      <c r="AI6" s="595" t="n"/>
+      <c r="AJ6" s="595" t="n"/>
+      <c r="AK6" s="595" t="n"/>
+      <c r="AL6" s="595" t="n"/>
+      <c r="AM6" s="595" t="n"/>
+      <c r="AN6" s="595" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="265" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="B7" s="265" t="inlineStr">
+        <is>
+          <t>DISPOSITION_GATE</t>
+        </is>
+      </c>
+      <c r="C7" s="265" t="inlineStr">
+        <is>
+          <t>YES_NO</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>OWNER_DEPT</t>
+        </is>
+      </c>
+      <c r="E7" s="265" t="inlineStr">
+        <is>
+          <t>ACTION_STATUS</t>
+        </is>
+      </c>
+      <c r="F7" s="265" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="G7" s="596" t="n"/>
+      <c r="H7" s="596" t="n"/>
+      <c r="I7" s="596" t="n"/>
+      <c r="J7" s="596" t="n"/>
+      <c r="K7" s="596" t="n"/>
+      <c r="L7" s="596" t="n"/>
+      <c r="M7" s="596" t="n"/>
+      <c r="N7" s="596" t="n"/>
+      <c r="O7" s="596" t="n"/>
+      <c r="P7" s="596" t="n"/>
+      <c r="Q7" s="596" t="n"/>
+      <c r="R7" s="596" t="n"/>
+      <c r="S7" s="596" t="n"/>
+      <c r="T7" s="596" t="n"/>
+      <c r="U7" s="596" t="n"/>
+      <c r="V7" s="596" t="n"/>
+      <c r="W7" s="596" t="n"/>
+      <c r="X7" s="596" t="n"/>
+      <c r="Y7" s="596" t="n"/>
+      <c r="Z7" s="596" t="n"/>
+      <c r="AA7" s="596" t="n"/>
+      <c r="AB7" s="596" t="n"/>
+      <c r="AC7" s="596" t="n"/>
+      <c r="AD7" s="596" t="n"/>
+      <c r="AE7" s="596" t="n"/>
+      <c r="AF7" s="596" t="n"/>
+      <c r="AG7" s="596" t="n"/>
+      <c r="AH7" s="596" t="n"/>
+      <c r="AI7" s="596" t="n"/>
+      <c r="AJ7" s="596" t="n"/>
+      <c r="AK7" s="596" t="n"/>
+      <c r="AL7" s="596" t="n"/>
+      <c r="AM7" s="596" t="n"/>
+      <c r="AN7" s="596" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="266" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="266" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="C8" s="266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" s="266" t="inlineStr">
+        <is>
+          <t>SALES</t>
+        </is>
+      </c>
+      <c r="E8" s="266" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F8" s="266" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G8" s="596" t="n"/>
+      <c r="H8" s="596" t="n"/>
+      <c r="I8" s="596" t="n"/>
+      <c r="J8" s="596" t="n"/>
+      <c r="K8" s="596" t="n"/>
+      <c r="L8" s="596" t="n"/>
+      <c r="M8" s="596" t="n"/>
+      <c r="N8" s="596" t="n"/>
+      <c r="O8" s="596" t="n"/>
+      <c r="P8" s="596" t="n"/>
+      <c r="Q8" s="596" t="n"/>
+      <c r="R8" s="596" t="n"/>
+      <c r="S8" s="596" t="n"/>
+      <c r="T8" s="596" t="n"/>
+      <c r="U8" s="596" t="n"/>
+      <c r="V8" s="596" t="n"/>
+      <c r="W8" s="596" t="n"/>
+      <c r="X8" s="596" t="n"/>
+      <c r="Y8" s="596" t="n"/>
+      <c r="Z8" s="596" t="n"/>
+      <c r="AA8" s="596" t="n"/>
+      <c r="AB8" s="596" t="n"/>
+      <c r="AC8" s="596" t="n"/>
+      <c r="AD8" s="596" t="n"/>
+      <c r="AE8" s="596" t="n"/>
+      <c r="AF8" s="596" t="n"/>
+      <c r="AG8" s="596" t="n"/>
+      <c r="AH8" s="596" t="n"/>
+      <c r="AI8" s="596" t="n"/>
+      <c r="AJ8" s="596" t="n"/>
+      <c r="AK8" s="596" t="n"/>
+      <c r="AL8" s="596" t="n"/>
+      <c r="AM8" s="596" t="n"/>
+      <c r="AN8" s="596" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B9" s="266" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="C9" s="266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D9" s="266" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="E9" s="266" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F9" s="266" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="G9" s="596" t="n"/>
+      <c r="H9" s="596" t="n"/>
+      <c r="I9" s="596" t="n"/>
+      <c r="J9" s="596" t="n"/>
+      <c r="K9" s="596" t="n"/>
+      <c r="L9" s="596" t="n"/>
+      <c r="M9" s="596" t="n"/>
+      <c r="N9" s="596" t="n"/>
+      <c r="O9" s="596" t="n"/>
+      <c r="P9" s="596" t="n"/>
+      <c r="Q9" s="596" t="n"/>
+      <c r="R9" s="596" t="n"/>
+      <c r="S9" s="596" t="n"/>
+      <c r="T9" s="596" t="n"/>
+      <c r="U9" s="596" t="n"/>
+      <c r="V9" s="596" t="n"/>
+      <c r="W9" s="596" t="n"/>
+      <c r="X9" s="596" t="n"/>
+      <c r="Y9" s="596" t="n"/>
+      <c r="Z9" s="596" t="n"/>
+      <c r="AA9" s="596" t="n"/>
+      <c r="AB9" s="596" t="n"/>
+      <c r="AC9" s="596" t="n"/>
+      <c r="AD9" s="596" t="n"/>
+      <c r="AE9" s="596" t="n"/>
+      <c r="AF9" s="596" t="n"/>
+      <c r="AG9" s="596" t="n"/>
+      <c r="AH9" s="596" t="n"/>
+      <c r="AI9" s="596" t="n"/>
+      <c r="AJ9" s="596" t="n"/>
+      <c r="AK9" s="596" t="n"/>
+      <c r="AL9" s="596" t="n"/>
+      <c r="AM9" s="596" t="n"/>
+      <c r="AN9" s="596" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="266" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B10" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D10" s="266" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="E10" s="266" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="F10" s="266" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G10" s="596" t="n"/>
+      <c r="H10" s="596" t="n"/>
+      <c r="I10" s="596" t="n"/>
+      <c r="J10" s="596" t="n"/>
+      <c r="K10" s="596" t="n"/>
+      <c r="L10" s="596" t="n"/>
+      <c r="M10" s="596" t="n"/>
+      <c r="N10" s="596" t="n"/>
+      <c r="O10" s="596" t="n"/>
+      <c r="P10" s="596" t="n"/>
+      <c r="Q10" s="596" t="n"/>
+      <c r="R10" s="596" t="n"/>
+      <c r="S10" s="596" t="n"/>
+      <c r="T10" s="596" t="n"/>
+      <c r="U10" s="596" t="n"/>
+      <c r="V10" s="596" t="n"/>
+      <c r="W10" s="596" t="n"/>
+      <c r="X10" s="596" t="n"/>
+      <c r="Y10" s="596" t="n"/>
+      <c r="Z10" s="596" t="n"/>
+      <c r="AA10" s="596" t="n"/>
+      <c r="AB10" s="596" t="n"/>
+      <c r="AC10" s="596" t="n"/>
+      <c r="AD10" s="596" t="n"/>
+      <c r="AE10" s="596" t="n"/>
+      <c r="AF10" s="596" t="n"/>
+      <c r="AG10" s="596" t="n"/>
+      <c r="AH10" s="596" t="n"/>
+      <c r="AI10" s="596" t="n"/>
+      <c r="AJ10" s="596" t="n"/>
+      <c r="AK10" s="596" t="n"/>
+      <c r="AL10" s="596" t="n"/>
+      <c r="AM10" s="596" t="n"/>
+      <c r="AN10" s="596" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B11" s="266" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="C11" s="596" t="n"/>
+      <c r="D11" s="266" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E11" s="347" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F11" s="266" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="G11" s="596" t="n"/>
+      <c r="H11" s="596" t="n"/>
+      <c r="I11" s="596" t="n"/>
+      <c r="J11" s="596" t="n"/>
+      <c r="K11" s="596" t="n"/>
+      <c r="L11" s="596" t="n"/>
+      <c r="M11" s="596" t="n"/>
+      <c r="N11" s="596" t="n"/>
+      <c r="O11" s="596" t="n"/>
+      <c r="P11" s="596" t="n"/>
+      <c r="Q11" s="596" t="n"/>
+      <c r="R11" s="596" t="n"/>
+      <c r="S11" s="596" t="n"/>
+      <c r="T11" s="596" t="n"/>
+      <c r="U11" s="596" t="n"/>
+      <c r="V11" s="596" t="n"/>
+      <c r="W11" s="596" t="n"/>
+      <c r="X11" s="596" t="n"/>
+      <c r="Y11" s="596" t="n"/>
+      <c r="Z11" s="596" t="n"/>
+      <c r="AA11" s="596" t="n"/>
+      <c r="AB11" s="596" t="n"/>
+      <c r="AC11" s="596" t="n"/>
+      <c r="AD11" s="596" t="n"/>
+      <c r="AE11" s="596" t="n"/>
+      <c r="AF11" s="596" t="n"/>
+      <c r="AG11" s="596" t="n"/>
+      <c r="AH11" s="596" t="n"/>
+      <c r="AI11" s="596" t="n"/>
+      <c r="AJ11" s="596" t="n"/>
+      <c r="AK11" s="596" t="n"/>
+      <c r="AL11" s="596" t="n"/>
+      <c r="AM11" s="596" t="n"/>
+      <c r="AN11" s="596" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="596" t="n"/>
+      <c r="B12" s="596" t="n"/>
+      <c r="C12" s="596" t="n"/>
+      <c r="D12" s="347" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E12" s="347" t="inlineStr">
+        <is>
+          <t>INEFFECTIVE</t>
+        </is>
+      </c>
+      <c r="F12" s="596" t="n"/>
+      <c r="G12" s="596" t="n"/>
+      <c r="H12" s="596" t="n"/>
+      <c r="I12" s="596" t="n"/>
+      <c r="J12" s="596" t="n"/>
+      <c r="K12" s="596" t="n"/>
+      <c r="L12" s="596" t="n"/>
+      <c r="M12" s="596" t="n"/>
+      <c r="N12" s="596" t="n"/>
+      <c r="O12" s="596" t="n"/>
+      <c r="P12" s="596" t="n"/>
+      <c r="Q12" s="596" t="n"/>
+      <c r="R12" s="596" t="n"/>
+      <c r="S12" s="596" t="n"/>
+      <c r="T12" s="596" t="n"/>
+      <c r="U12" s="596" t="n"/>
+      <c r="V12" s="596" t="n"/>
+      <c r="W12" s="596" t="n"/>
+      <c r="X12" s="596" t="n"/>
+      <c r="Y12" s="596" t="n"/>
+      <c r="Z12" s="596" t="n"/>
+      <c r="AA12" s="596" t="n"/>
+      <c r="AB12" s="596" t="n"/>
+      <c r="AC12" s="596" t="n"/>
+      <c r="AD12" s="596" t="n"/>
+      <c r="AE12" s="596" t="n"/>
+      <c r="AF12" s="596" t="n"/>
+      <c r="AG12" s="596" t="n"/>
+      <c r="AH12" s="596" t="n"/>
+      <c r="AI12" s="596" t="n"/>
+      <c r="AJ12" s="596" t="n"/>
+      <c r="AK12" s="596" t="n"/>
+      <c r="AL12" s="596" t="n"/>
+      <c r="AM12" s="596" t="n"/>
+      <c r="AN12" s="596" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="596" t="n"/>
+      <c r="B13" s="596" t="n"/>
+      <c r="C13" s="596" t="n"/>
+      <c r="D13" s="347" t="inlineStr">
+        <is>
+          <t>PUR</t>
+        </is>
+      </c>
+      <c r="E13" s="347" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="F13" s="596" t="n"/>
+      <c r="G13" s="596" t="n"/>
+      <c r="H13" s="596" t="n"/>
+      <c r="I13" s="596" t="n"/>
+      <c r="J13" s="596" t="n"/>
+      <c r="K13" s="596" t="n"/>
+      <c r="L13" s="596" t="n"/>
+      <c r="M13" s="596" t="n"/>
+      <c r="N13" s="596" t="n"/>
+      <c r="O13" s="596" t="n"/>
+      <c r="P13" s="596" t="n"/>
+      <c r="Q13" s="596" t="n"/>
+      <c r="R13" s="596" t="n"/>
+      <c r="S13" s="596" t="n"/>
+      <c r="T13" s="596" t="n"/>
+      <c r="U13" s="596" t="n"/>
+      <c r="V13" s="596" t="n"/>
+      <c r="W13" s="596" t="n"/>
+      <c r="X13" s="596" t="n"/>
+      <c r="Y13" s="596" t="n"/>
+      <c r="Z13" s="596" t="n"/>
+      <c r="AA13" s="596" t="n"/>
+      <c r="AB13" s="596" t="n"/>
+      <c r="AC13" s="596" t="n"/>
+      <c r="AD13" s="596" t="n"/>
+      <c r="AE13" s="596" t="n"/>
+      <c r="AF13" s="596" t="n"/>
+      <c r="AG13" s="596" t="n"/>
+      <c r="AH13" s="596" t="n"/>
+      <c r="AI13" s="596" t="n"/>
+      <c r="AJ13" s="596" t="n"/>
+      <c r="AK13" s="596" t="n"/>
+      <c r="AL13" s="596" t="n"/>
+      <c r="AM13" s="596" t="n"/>
+      <c r="AN13" s="596" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="596" t="n"/>
+      <c r="B14" s="596" t="n"/>
+      <c r="C14" s="596" t="n"/>
+      <c r="D14" s="347" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="E14" s="596" t="n"/>
+      <c r="F14" s="596" t="n"/>
+      <c r="G14" s="596" t="n"/>
+      <c r="H14" s="596" t="n"/>
+      <c r="I14" s="596" t="n"/>
+      <c r="J14" s="596" t="n"/>
+      <c r="K14" s="596" t="n"/>
+      <c r="L14" s="596" t="n"/>
+      <c r="M14" s="596" t="n"/>
+      <c r="N14" s="596" t="n"/>
+      <c r="O14" s="596" t="n"/>
+      <c r="P14" s="596" t="n"/>
+      <c r="Q14" s="596" t="n"/>
+      <c r="R14" s="596" t="n"/>
+      <c r="S14" s="596" t="n"/>
+      <c r="T14" s="596" t="n"/>
+      <c r="U14" s="596" t="n"/>
+      <c r="V14" s="596" t="n"/>
+      <c r="W14" s="596" t="n"/>
+      <c r="X14" s="596" t="n"/>
+      <c r="Y14" s="596" t="n"/>
+      <c r="Z14" s="596" t="n"/>
+      <c r="AA14" s="596" t="n"/>
+      <c r="AB14" s="596" t="n"/>
+      <c r="AC14" s="596" t="n"/>
+      <c r="AD14" s="596" t="n"/>
+      <c r="AE14" s="596" t="n"/>
+      <c r="AF14" s="596" t="n"/>
+      <c r="AG14" s="596" t="n"/>
+      <c r="AH14" s="596" t="n"/>
+      <c r="AI14" s="596" t="n"/>
+      <c r="AJ14" s="596" t="n"/>
+      <c r="AK14" s="596" t="n"/>
+      <c r="AL14" s="596" t="n"/>
+      <c r="AM14" s="596" t="n"/>
+      <c r="AN14" s="596" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="596" t="n"/>
+      <c r="B15" s="596" t="n"/>
+      <c r="C15" s="596" t="n"/>
+      <c r="D15" s="347" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E15" s="596" t="n"/>
+      <c r="F15" s="596" t="n"/>
+      <c r="G15" s="596" t="n"/>
+      <c r="H15" s="596" t="n"/>
+      <c r="I15" s="596" t="n"/>
+      <c r="J15" s="596" t="n"/>
+      <c r="K15" s="596" t="n"/>
+      <c r="L15" s="596" t="n"/>
+      <c r="M15" s="596" t="n"/>
+      <c r="N15" s="596" t="n"/>
+      <c r="O15" s="596" t="n"/>
+      <c r="P15" s="596" t="n"/>
+      <c r="Q15" s="596" t="n"/>
+      <c r="R15" s="596" t="n"/>
+      <c r="S15" s="596" t="n"/>
+      <c r="T15" s="596" t="n"/>
+      <c r="U15" s="596" t="n"/>
+      <c r="V15" s="596" t="n"/>
+      <c r="W15" s="596" t="n"/>
+      <c r="X15" s="596" t="n"/>
+      <c r="Y15" s="596" t="n"/>
+      <c r="Z15" s="596" t="n"/>
+      <c r="AA15" s="596" t="n"/>
+      <c r="AB15" s="596" t="n"/>
+      <c r="AC15" s="596" t="n"/>
+      <c r="AD15" s="596" t="n"/>
+      <c r="AE15" s="596" t="n"/>
+      <c r="AF15" s="596" t="n"/>
+      <c r="AG15" s="596" t="n"/>
+      <c r="AH15" s="596" t="n"/>
+      <c r="AI15" s="596" t="n"/>
+      <c r="AJ15" s="596" t="n"/>
+      <c r="AK15" s="596" t="n"/>
+      <c r="AL15" s="596" t="n"/>
+      <c r="AM15" s="596" t="n"/>
+      <c r="AN15" s="596" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="596" t="n"/>
+      <c r="B16" s="596" t="n"/>
+      <c r="C16" s="596" t="n"/>
+      <c r="D16" s="347" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E16" s="596" t="n"/>
+      <c r="F16" s="596" t="n"/>
+      <c r="G16" s="596" t="n"/>
+      <c r="H16" s="596" t="n"/>
+      <c r="I16" s="596" t="n"/>
+      <c r="J16" s="596" t="n"/>
+      <c r="K16" s="596" t="n"/>
+      <c r="L16" s="596" t="n"/>
+      <c r="M16" s="596" t="n"/>
+      <c r="N16" s="596" t="n"/>
+      <c r="O16" s="596" t="n"/>
+      <c r="P16" s="596" t="n"/>
+      <c r="Q16" s="596" t="n"/>
+      <c r="R16" s="596" t="n"/>
+      <c r="S16" s="596" t="n"/>
+      <c r="T16" s="596" t="n"/>
+      <c r="U16" s="596" t="n"/>
+      <c r="V16" s="596" t="n"/>
+      <c r="W16" s="596" t="n"/>
+      <c r="X16" s="596" t="n"/>
+      <c r="Y16" s="596" t="n"/>
+      <c r="Z16" s="596" t="n"/>
+      <c r="AA16" s="596" t="n"/>
+      <c r="AB16" s="596" t="n"/>
+      <c r="AC16" s="596" t="n"/>
+      <c r="AD16" s="596" t="n"/>
+      <c r="AE16" s="596" t="n"/>
+      <c r="AF16" s="596" t="n"/>
+      <c r="AG16" s="596" t="n"/>
+      <c r="AH16" s="596" t="n"/>
+      <c r="AI16" s="596" t="n"/>
+      <c r="AJ16" s="596" t="n"/>
+      <c r="AK16" s="596" t="n"/>
+      <c r="AL16" s="596" t="n"/>
+      <c r="AM16" s="596" t="n"/>
+      <c r="AN16" s="596" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="596" t="n"/>
+      <c r="B17" s="596" t="n"/>
+      <c r="C17" s="596" t="n"/>
+      <c r="D17" s="347" t="inlineStr">
+        <is>
+          <t>MGT</t>
+        </is>
+      </c>
+      <c r="E17" s="596" t="n"/>
+      <c r="F17" s="596" t="n"/>
+      <c r="G17" s="596" t="n"/>
+      <c r="H17" s="596" t="n"/>
+      <c r="I17" s="596" t="n"/>
+      <c r="J17" s="596" t="n"/>
+      <c r="K17" s="596" t="n"/>
+      <c r="L17" s="596" t="n"/>
+      <c r="M17" s="596" t="n"/>
+      <c r="N17" s="596" t="n"/>
+      <c r="O17" s="596" t="n"/>
+      <c r="P17" s="596" t="n"/>
+      <c r="Q17" s="596" t="n"/>
+      <c r="R17" s="596" t="n"/>
+      <c r="S17" s="596" t="n"/>
+      <c r="T17" s="596" t="n"/>
+      <c r="U17" s="596" t="n"/>
+      <c r="V17" s="596" t="n"/>
+      <c r="W17" s="596" t="n"/>
+      <c r="X17" s="596" t="n"/>
+      <c r="Y17" s="596" t="n"/>
+      <c r="Z17" s="596" t="n"/>
+      <c r="AA17" s="596" t="n"/>
+      <c r="AB17" s="596" t="n"/>
+      <c r="AC17" s="596" t="n"/>
+      <c r="AD17" s="596" t="n"/>
+      <c r="AE17" s="596" t="n"/>
+      <c r="AF17" s="596" t="n"/>
+      <c r="AG17" s="596" t="n"/>
+      <c r="AH17" s="596" t="n"/>
+      <c r="AI17" s="596" t="n"/>
+      <c r="AJ17" s="596" t="n"/>
+      <c r="AK17" s="596" t="n"/>
+      <c r="AL17" s="596" t="n"/>
+      <c r="AM17" s="596" t="n"/>
+      <c r="AN17" s="596" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="596" t="n"/>
+      <c r="B18" s="596" t="n"/>
+      <c r="C18" s="596" t="n"/>
+      <c r="D18" s="596" t="n"/>
+      <c r="E18" s="596" t="n"/>
+      <c r="F18" s="596" t="n"/>
+      <c r="G18" s="596" t="n"/>
+      <c r="H18" s="596" t="n"/>
+      <c r="I18" s="596" t="n"/>
+      <c r="J18" s="596" t="n"/>
+      <c r="K18" s="596" t="n"/>
+      <c r="L18" s="596" t="n"/>
+      <c r="M18" s="596" t="n"/>
+      <c r="N18" s="596" t="n"/>
+      <c r="O18" s="596" t="n"/>
+      <c r="P18" s="596" t="n"/>
+      <c r="Q18" s="596" t="n"/>
+      <c r="R18" s="596" t="n"/>
+      <c r="S18" s="596" t="n"/>
+      <c r="T18" s="596" t="n"/>
+      <c r="U18" s="596" t="n"/>
+      <c r="V18" s="596" t="n"/>
+      <c r="W18" s="596" t="n"/>
+      <c r="X18" s="596" t="n"/>
+      <c r="Y18" s="596" t="n"/>
+      <c r="Z18" s="596" t="n"/>
+      <c r="AA18" s="596" t="n"/>
+      <c r="AB18" s="596" t="n"/>
+      <c r="AC18" s="596" t="n"/>
+      <c r="AD18" s="596" t="n"/>
+      <c r="AE18" s="596" t="n"/>
+      <c r="AF18" s="596" t="n"/>
+      <c r="AG18" s="596" t="n"/>
+      <c r="AH18" s="596" t="n"/>
+      <c r="AI18" s="596" t="n"/>
+      <c r="AJ18" s="596" t="n"/>
+      <c r="AK18" s="596" t="n"/>
+      <c r="AL18" s="596" t="n"/>
+      <c r="AM18" s="596" t="n"/>
+      <c r="AN18" s="596" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="596" t="n"/>
+      <c r="B19" s="596" t="n"/>
+      <c r="C19" s="596" t="n"/>
+      <c r="D19" s="596" t="n"/>
+      <c r="E19" s="596" t="n"/>
+      <c r="F19" s="596" t="n"/>
+      <c r="G19" s="596" t="n"/>
+      <c r="H19" s="596" t="n"/>
+      <c r="I19" s="596" t="n"/>
+      <c r="J19" s="596" t="n"/>
+      <c r="K19" s="596" t="n"/>
+      <c r="L19" s="596" t="n"/>
+      <c r="M19" s="596" t="n"/>
+      <c r="N19" s="596" t="n"/>
+      <c r="O19" s="596" t="n"/>
+      <c r="P19" s="596" t="n"/>
+      <c r="Q19" s="596" t="n"/>
+      <c r="R19" s="596" t="n"/>
+      <c r="S19" s="596" t="n"/>
+      <c r="T19" s="596" t="n"/>
+      <c r="U19" s="596" t="n"/>
+      <c r="V19" s="596" t="n"/>
+      <c r="W19" s="596" t="n"/>
+      <c r="X19" s="596" t="n"/>
+      <c r="Y19" s="596" t="n"/>
+      <c r="Z19" s="596" t="n"/>
+      <c r="AA19" s="596" t="n"/>
+      <c r="AB19" s="596" t="n"/>
+      <c r="AC19" s="596" t="n"/>
+      <c r="AD19" s="596" t="n"/>
+      <c r="AE19" s="596" t="n"/>
+      <c r="AF19" s="596" t="n"/>
+      <c r="AG19" s="596" t="n"/>
+      <c r="AH19" s="596" t="n"/>
+      <c r="AI19" s="596" t="n"/>
+      <c r="AJ19" s="596" t="n"/>
+      <c r="AK19" s="596" t="n"/>
+      <c r="AL19" s="596" t="n"/>
+      <c r="AM19" s="596" t="n"/>
+      <c r="AN19" s="596" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="596" t="n"/>
+      <c r="B20" s="596" t="n"/>
+      <c r="C20" s="596" t="n"/>
+      <c r="D20" s="596" t="n"/>
+      <c r="E20" s="596" t="n"/>
+      <c r="F20" s="596" t="n"/>
+      <c r="G20" s="596" t="n"/>
+      <c r="H20" s="596" t="n"/>
+      <c r="I20" s="596" t="n"/>
+      <c r="J20" s="596" t="n"/>
+      <c r="K20" s="596" t="n"/>
+      <c r="L20" s="596" t="n"/>
+      <c r="M20" s="596" t="n"/>
+      <c r="N20" s="596" t="n"/>
+      <c r="O20" s="596" t="n"/>
+      <c r="P20" s="596" t="n"/>
+      <c r="Q20" s="596" t="n"/>
+      <c r="R20" s="596" t="n"/>
+      <c r="S20" s="596" t="n"/>
+      <c r="T20" s="596" t="n"/>
+      <c r="U20" s="596" t="n"/>
+      <c r="V20" s="596" t="n"/>
+      <c r="W20" s="596" t="n"/>
+      <c r="X20" s="596" t="n"/>
+      <c r="Y20" s="596" t="n"/>
+      <c r="Z20" s="596" t="n"/>
+      <c r="AA20" s="596" t="n"/>
+      <c r="AB20" s="596" t="n"/>
+      <c r="AC20" s="596" t="n"/>
+      <c r="AD20" s="596" t="n"/>
+      <c r="AE20" s="596" t="n"/>
+      <c r="AF20" s="596" t="n"/>
+      <c r="AG20" s="596" t="n"/>
+      <c r="AH20" s="596" t="n"/>
+      <c r="AI20" s="596" t="n"/>
+      <c r="AJ20" s="596" t="n"/>
+      <c r="AK20" s="596" t="n"/>
+      <c r="AL20" s="596" t="n"/>
+      <c r="AM20" s="596" t="n"/>
+      <c r="AN20" s="596" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="577" t="n"/>
+      <c r="B1" s="578" t="n"/>
+      <c r="C1" s="578" t="n"/>
+      <c r="D1" s="578" t="n"/>
+      <c r="E1" s="578" t="n"/>
+      <c r="F1" s="578" t="n"/>
+      <c r="G1" s="578" t="n"/>
+      <c r="H1" s="579" t="n"/>
+      <c r="I1" s="580" t="inlineStr">
+        <is>
+          <t>Outsource Dispatch Checklist</t>
+        </is>
+      </c>
+      <c r="J1" s="578" t="n"/>
+      <c r="K1" s="578" t="n"/>
+      <c r="L1" s="578" t="n"/>
+      <c r="M1" s="578" t="n"/>
+      <c r="N1" s="578" t="n"/>
+      <c r="O1" s="578" t="n"/>
+      <c r="P1" s="578" t="n"/>
+      <c r="Q1" s="578" t="n"/>
+      <c r="R1" s="578" t="n"/>
+      <c r="S1" s="578" t="n"/>
+      <c r="T1" s="578" t="n"/>
+      <c r="U1" s="578" t="n"/>
+      <c r="V1" s="578" t="n"/>
+      <c r="W1" s="578" t="n"/>
+      <c r="X1" s="578" t="n"/>
+      <c r="Y1" s="578" t="n"/>
+      <c r="Z1" s="578" t="n"/>
+      <c r="AA1" s="578" t="n"/>
+      <c r="AB1" s="578" t="n"/>
+      <c r="AC1" s="578" t="n"/>
+      <c r="AD1" s="579" t="n"/>
+      <c r="AE1" s="423" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="578" t="n"/>
+      <c r="AG1" s="578" t="n"/>
+      <c r="AH1" s="581" t="n"/>
+      <c r="AI1" s="426" t="n"/>
+      <c r="AJ1" s="578" t="n"/>
+      <c r="AK1" s="578" t="n"/>
+      <c r="AL1" s="578" t="n"/>
+      <c r="AM1" s="578" t="n"/>
+      <c r="AN1" s="579" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="582" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="583" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="583" t="n"/>
+      <c r="AE2" s="584" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="585" t="n"/>
+      <c r="AI2" s="586" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="583" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="582" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="583" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="583" t="n"/>
+      <c r="AE3" s="584" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="585" t="n"/>
+      <c r="AI3" s="586" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="583" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="582" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="583" t="n"/>
+      <c r="I4" s="587" t="inlineStr">
+        <is>
+          <t>Quality Management System · Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="583" t="n"/>
+      <c r="AE4" s="584" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="585" t="n"/>
+      <c r="AI4" s="586" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="583" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="588" t="n"/>
+      <c r="B5" s="589" t="n"/>
+      <c r="C5" s="589" t="n"/>
+      <c r="D5" s="589" t="n"/>
+      <c r="E5" s="589" t="n"/>
+      <c r="F5" s="589" t="n"/>
+      <c r="G5" s="589" t="n"/>
+      <c r="H5" s="590" t="n"/>
+      <c r="I5" s="591" t="inlineStr">
+        <is>
+          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="J5" s="589" t="n"/>
+      <c r="K5" s="589" t="n"/>
+      <c r="L5" s="589" t="n"/>
+      <c r="M5" s="589" t="n"/>
+      <c r="N5" s="589" t="n"/>
+      <c r="O5" s="589" t="n"/>
+      <c r="P5" s="589" t="n"/>
+      <c r="Q5" s="589" t="n"/>
+      <c r="R5" s="589" t="n"/>
+      <c r="S5" s="589" t="n"/>
+      <c r="T5" s="589" t="n"/>
+      <c r="U5" s="589" t="n"/>
+      <c r="V5" s="589" t="n"/>
+      <c r="W5" s="589" t="n"/>
+      <c r="X5" s="589" t="n"/>
+      <c r="Y5" s="589" t="n"/>
+      <c r="Z5" s="589" t="n"/>
+      <c r="AA5" s="589" t="n"/>
+      <c r="AB5" s="589" t="n"/>
+      <c r="AC5" s="589" t="n"/>
+      <c r="AD5" s="590" t="n"/>
+      <c r="AE5" s="592" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="589" t="n"/>
+      <c r="AG5" s="589" t="n"/>
+      <c r="AH5" s="593" t="n"/>
+      <c r="AI5" s="594" t="n"/>
+      <c r="AJ5" s="589" t="n"/>
+      <c r="AK5" s="589" t="n"/>
+      <c r="AL5" s="589" t="n"/>
+      <c r="AM5" s="589" t="n"/>
+      <c r="AN5" s="590" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="595" t="n"/>
+      <c r="B6" s="595" t="n"/>
+      <c r="C6" s="595" t="n"/>
+      <c r="D6" s="595" t="n"/>
+      <c r="E6" s="595" t="n"/>
+      <c r="F6" s="595" t="n"/>
+      <c r="G6" s="595" t="n"/>
+      <c r="H6" s="595" t="n"/>
+      <c r="I6" s="595" t="n"/>
+      <c r="J6" s="595" t="n"/>
+      <c r="K6" s="595" t="n"/>
+      <c r="L6" s="595" t="n"/>
+      <c r="M6" s="595" t="n"/>
+      <c r="N6" s="595" t="n"/>
+      <c r="O6" s="595" t="n"/>
+      <c r="P6" s="595" t="n"/>
+      <c r="Q6" s="595" t="n"/>
+      <c r="R6" s="595" t="n"/>
+      <c r="S6" s="595" t="n"/>
+      <c r="T6" s="595" t="n"/>
+      <c r="U6" s="595" t="n"/>
+      <c r="V6" s="595" t="n"/>
+      <c r="W6" s="595" t="n"/>
+      <c r="X6" s="595" t="n"/>
+      <c r="Y6" s="595" t="n"/>
+      <c r="Z6" s="595" t="n"/>
+      <c r="AA6" s="595" t="n"/>
+      <c r="AB6" s="595" t="n"/>
+      <c r="AC6" s="595" t="n"/>
+      <c r="AD6" s="595" t="n"/>
+      <c r="AE6" s="595" t="n"/>
+      <c r="AF6" s="595" t="n"/>
+      <c r="AG6" s="595" t="n"/>
+      <c r="AH6" s="595" t="n"/>
+      <c r="AI6" s="595" t="n"/>
+      <c r="AJ6" s="595" t="n"/>
+      <c r="AK6" s="595" t="n"/>
+      <c r="AL6" s="595" t="n"/>
+      <c r="AM6" s="595" t="n"/>
+      <c r="AN6" s="595" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="329">
+      <c r="A7" s="499" t="inlineStr">
         <is>
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
-      <c r="B1" s="459" t="n"/>
-      <c r="C1" s="459" t="n"/>
-      <c r="D1" s="459" t="n"/>
-      <c r="E1" s="459" t="n"/>
-      <c r="F1" s="459" t="n"/>
-      <c r="G1" s="459" t="n"/>
-      <c r="H1" s="459" t="n"/>
-      <c r="I1" s="459" t="n"/>
-      <c r="J1" s="459" t="n"/>
-      <c r="K1" s="459" t="n"/>
-      <c r="L1" s="459" t="n"/>
-      <c r="M1" s="459" t="n"/>
-      <c r="N1" s="459" t="n"/>
-      <c r="O1" s="459" t="n"/>
-      <c r="P1" s="459" t="n"/>
-      <c r="Q1" s="459" t="n"/>
-      <c r="R1" s="459" t="n"/>
-      <c r="S1" s="459" t="n"/>
-      <c r="T1" s="459" t="n"/>
-      <c r="U1" s="459" t="n"/>
-      <c r="V1" s="459" t="n"/>
-      <c r="W1" s="459" t="n"/>
-      <c r="X1" s="459" t="n"/>
-      <c r="Y1" s="459" t="n"/>
-      <c r="Z1" s="459" t="n"/>
-      <c r="AA1" s="459" t="n"/>
-      <c r="AB1" s="459" t="n"/>
-      <c r="AC1" s="459" t="n"/>
-      <c r="AD1" s="459" t="n"/>
-      <c r="AE1" s="459" t="n"/>
-      <c r="AF1" s="459" t="n"/>
-      <c r="AG1" s="459" t="n"/>
-      <c r="AH1" s="459" t="n"/>
-      <c r="AI1" s="459" t="n"/>
-      <c r="AJ1" s="459" t="n"/>
-      <c r="AK1" s="459" t="n"/>
-      <c r="AL1" s="459" t="n"/>
-      <c r="AM1" s="459" t="n"/>
-      <c r="AN1" s="462" t="n"/>
+      <c r="B7" s="596" t="n"/>
+      <c r="C7" s="596" t="n"/>
+      <c r="D7" s="596" t="n"/>
+      <c r="E7" s="596" t="n"/>
+      <c r="F7" s="596" t="n"/>
+      <c r="G7" s="596" t="n"/>
+      <c r="H7" s="596" t="n"/>
+      <c r="I7" s="596" t="n"/>
+      <c r="J7" s="596" t="n"/>
+      <c r="K7" s="596" t="n"/>
+      <c r="L7" s="596" t="n"/>
+      <c r="M7" s="596" t="n"/>
+      <c r="N7" s="596" t="n"/>
+      <c r="O7" s="596" t="n"/>
+      <c r="P7" s="596" t="n"/>
+      <c r="Q7" s="596" t="n"/>
+      <c r="R7" s="596" t="n"/>
+      <c r="S7" s="596" t="n"/>
+      <c r="T7" s="596" t="n"/>
+      <c r="U7" s="596" t="n"/>
+      <c r="V7" s="596" t="n"/>
+      <c r="W7" s="596" t="n"/>
+      <c r="X7" s="596" t="n"/>
+      <c r="Y7" s="596" t="n"/>
+      <c r="Z7" s="596" t="n"/>
+      <c r="AA7" s="596" t="n"/>
+      <c r="AB7" s="596" t="n"/>
+      <c r="AC7" s="596" t="n"/>
+      <c r="AD7" s="596" t="n"/>
+      <c r="AE7" s="596" t="n"/>
+      <c r="AF7" s="596" t="n"/>
+      <c r="AG7" s="596" t="n"/>
+      <c r="AH7" s="596" t="n"/>
+      <c r="AI7" s="596" t="n"/>
+      <c r="AJ7" s="596" t="n"/>
+      <c r="AK7" s="596" t="n"/>
+      <c r="AL7" s="596" t="n"/>
+      <c r="AM7" s="596" t="n"/>
+      <c r="AN7" s="596" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="500" t="inlineStr">
+    <row r="8" ht="20" customHeight="1" s="329">
+      <c r="A8" s="500" t="inlineStr">
         <is>
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
       </c>
-      <c r="B2" s="343" t="n"/>
-      <c r="C2" s="343" t="n"/>
-      <c r="D2" s="343" t="n"/>
-      <c r="E2" s="343" t="n"/>
-      <c r="F2" s="343" t="n"/>
-      <c r="G2" s="343" t="n"/>
-      <c r="H2" s="343" t="n"/>
-      <c r="I2" s="343" t="n"/>
-      <c r="J2" s="343" t="n"/>
-      <c r="K2" s="343" t="n"/>
-      <c r="L2" s="343" t="n"/>
-      <c r="M2" s="343" t="n"/>
-      <c r="N2" s="343" t="n"/>
-      <c r="O2" s="343" t="n"/>
-      <c r="P2" s="343" t="n"/>
-      <c r="Q2" s="343" t="n"/>
-      <c r="R2" s="343" t="n"/>
-      <c r="S2" s="343" t="n"/>
-      <c r="T2" s="343" t="n"/>
-      <c r="U2" s="343" t="n"/>
-      <c r="V2" s="343" t="n"/>
-      <c r="W2" s="343" t="n"/>
-      <c r="X2" s="343" t="n"/>
-      <c r="Y2" s="343" t="n"/>
-      <c r="Z2" s="343" t="n"/>
-      <c r="AA2" s="343" t="n"/>
-      <c r="AB2" s="343" t="n"/>
-      <c r="AC2" s="343" t="n"/>
-      <c r="AD2" s="343" t="n"/>
-      <c r="AE2" s="343" t="n"/>
-      <c r="AF2" s="343" t="n"/>
-      <c r="AG2" s="343" t="n"/>
-      <c r="AH2" s="343" t="n"/>
-      <c r="AI2" s="343" t="n"/>
-      <c r="AJ2" s="343" t="n"/>
-      <c r="AK2" s="343" t="n"/>
-      <c r="AL2" s="343" t="n"/>
-      <c r="AM2" s="343" t="n"/>
-      <c r="AN2" s="466" t="n"/>
+      <c r="B8" s="596" t="n"/>
+      <c r="C8" s="596" t="n"/>
+      <c r="D8" s="596" t="n"/>
+      <c r="E8" s="596" t="n"/>
+      <c r="F8" s="596" t="n"/>
+      <c r="G8" s="596" t="n"/>
+      <c r="H8" s="596" t="n"/>
+      <c r="I8" s="596" t="n"/>
+      <c r="J8" s="596" t="n"/>
+      <c r="K8" s="596" t="n"/>
+      <c r="L8" s="596" t="n"/>
+      <c r="M8" s="596" t="n"/>
+      <c r="N8" s="596" t="n"/>
+      <c r="O8" s="596" t="n"/>
+      <c r="P8" s="596" t="n"/>
+      <c r="Q8" s="596" t="n"/>
+      <c r="R8" s="596" t="n"/>
+      <c r="S8" s="596" t="n"/>
+      <c r="T8" s="596" t="n"/>
+      <c r="U8" s="596" t="n"/>
+      <c r="V8" s="596" t="n"/>
+      <c r="W8" s="596" t="n"/>
+      <c r="X8" s="596" t="n"/>
+      <c r="Y8" s="596" t="n"/>
+      <c r="Z8" s="596" t="n"/>
+      <c r="AA8" s="596" t="n"/>
+      <c r="AB8" s="596" t="n"/>
+      <c r="AC8" s="596" t="n"/>
+      <c r="AD8" s="596" t="n"/>
+      <c r="AE8" s="596" t="n"/>
+      <c r="AF8" s="596" t="n"/>
+      <c r="AG8" s="596" t="n"/>
+      <c r="AH8" s="596" t="n"/>
+      <c r="AI8" s="596" t="n"/>
+      <c r="AJ8" s="596" t="n"/>
+      <c r="AK8" s="596" t="n"/>
+      <c r="AL8" s="596" t="n"/>
+      <c r="AM8" s="596" t="n"/>
+      <c r="AN8" s="596" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="475" t="n"/>
-      <c r="B3" s="468" t="n"/>
-      <c r="C3" s="468" t="n"/>
-      <c r="D3" s="468" t="n"/>
-      <c r="E3" s="468" t="n"/>
-      <c r="F3" s="468" t="n"/>
-      <c r="G3" s="468" t="n"/>
-      <c r="H3" s="468" t="n"/>
-      <c r="I3" s="468" t="n"/>
-      <c r="J3" s="468" t="n"/>
-      <c r="K3" s="468" t="n"/>
-      <c r="L3" s="468" t="n"/>
-      <c r="M3" s="468" t="n"/>
-      <c r="N3" s="468" t="n"/>
-      <c r="O3" s="468" t="n"/>
-      <c r="P3" s="468" t="n"/>
-      <c r="Q3" s="468" t="n"/>
-      <c r="R3" s="468" t="n"/>
-      <c r="S3" s="468" t="n"/>
-      <c r="T3" s="468" t="n"/>
-      <c r="U3" s="468" t="n"/>
-      <c r="V3" s="468" t="n"/>
-      <c r="W3" s="468" t="n"/>
-      <c r="X3" s="468" t="n"/>
-      <c r="Y3" s="468" t="n"/>
-      <c r="Z3" s="468" t="n"/>
-      <c r="AA3" s="468" t="n"/>
-      <c r="AB3" s="468" t="n"/>
-      <c r="AC3" s="468" t="n"/>
-      <c r="AD3" s="468" t="n"/>
-      <c r="AE3" s="468" t="n"/>
-      <c r="AF3" s="468" t="n"/>
-      <c r="AG3" s="468" t="n"/>
-      <c r="AH3" s="468" t="n"/>
-      <c r="AI3" s="468" t="n"/>
-      <c r="AJ3" s="468" t="n"/>
-      <c r="AK3" s="468" t="n"/>
-      <c r="AL3" s="468" t="n"/>
-      <c r="AM3" s="468" t="n"/>
-      <c r="AN3" s="471" t="n"/>
+    <row r="9" ht="20" customHeight="1" s="329">
+      <c r="A9" s="596" t="n"/>
+      <c r="B9" s="596" t="n"/>
+      <c r="C9" s="596" t="n"/>
+      <c r="D9" s="596" t="n"/>
+      <c r="E9" s="596" t="n"/>
+      <c r="F9" s="596" t="n"/>
+      <c r="G9" s="596" t="n"/>
+      <c r="H9" s="596" t="n"/>
+      <c r="I9" s="596" t="n"/>
+      <c r="J9" s="596" t="n"/>
+      <c r="K9" s="596" t="n"/>
+      <c r="L9" s="596" t="n"/>
+      <c r="M9" s="596" t="n"/>
+      <c r="N9" s="596" t="n"/>
+      <c r="O9" s="596" t="n"/>
+      <c r="P9" s="596" t="n"/>
+      <c r="Q9" s="596" t="n"/>
+      <c r="R9" s="596" t="n"/>
+      <c r="S9" s="596" t="n"/>
+      <c r="T9" s="596" t="n"/>
+      <c r="U9" s="596" t="n"/>
+      <c r="V9" s="596" t="n"/>
+      <c r="W9" s="596" t="n"/>
+      <c r="X9" s="596" t="n"/>
+      <c r="Y9" s="596" t="n"/>
+      <c r="Z9" s="596" t="n"/>
+      <c r="AA9" s="596" t="n"/>
+      <c r="AB9" s="596" t="n"/>
+      <c r="AC9" s="596" t="n"/>
+      <c r="AD9" s="596" t="n"/>
+      <c r="AE9" s="596" t="n"/>
+      <c r="AF9" s="596" t="n"/>
+      <c r="AG9" s="596" t="n"/>
+      <c r="AH9" s="596" t="n"/>
+      <c r="AI9" s="596" t="n"/>
+      <c r="AJ9" s="596" t="n"/>
+      <c r="AK9" s="596" t="n"/>
+      <c r="AL9" s="596" t="n"/>
+      <c r="AM9" s="596" t="n"/>
+      <c r="AN9" s="596" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1" s="329">
-      <c r="A4" s="477" t="inlineStr">
+    <row r="10" ht="20" customHeight="1" s="329">
+      <c r="A10" s="477" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="478" t="inlineStr">
+      <c r="B10" s="478" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="478" t="inlineStr">
+      <c r="C10" s="478" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="478" t="inlineStr">
+      <c r="D10" s="478" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="478" t="inlineStr">
+      <c r="E10" s="478" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="478" t="inlineStr">
+      <c r="F10" s="478" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="478" t="inlineStr">
+      <c r="G10" s="478" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="478" t="inlineStr">
+      <c r="H10" s="478" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I4" s="478" t="n"/>
-      <c r="J4" s="478" t="n"/>
-      <c r="K4" s="478" t="n"/>
-      <c r="L4" s="478" t="n"/>
-      <c r="M4" s="478" t="n"/>
-      <c r="N4" s="478" t="n"/>
-      <c r="O4" s="478" t="n"/>
-      <c r="P4" s="478" t="n"/>
-      <c r="Q4" s="478" t="n"/>
-      <c r="R4" s="478" t="n"/>
-      <c r="S4" s="478" t="n"/>
-      <c r="T4" s="478" t="n"/>
-      <c r="U4" s="478" t="n"/>
-      <c r="V4" s="478" t="n"/>
-      <c r="W4" s="478" t="n"/>
-      <c r="X4" s="478" t="n"/>
-      <c r="Y4" s="478" t="n"/>
-      <c r="Z4" s="478" t="n"/>
-      <c r="AA4" s="478" t="n"/>
-      <c r="AB4" s="478" t="n"/>
-      <c r="AC4" s="478" t="n"/>
-      <c r="AD4" s="478" t="n"/>
-      <c r="AE4" s="478" t="n"/>
-      <c r="AF4" s="478" t="n"/>
-      <c r="AG4" s="478" t="n"/>
-      <c r="AH4" s="478" t="n"/>
-      <c r="AI4" s="478" t="n"/>
-      <c r="AJ4" s="478" t="n"/>
-      <c r="AK4" s="478" t="n"/>
-      <c r="AL4" s="478" t="n"/>
-      <c r="AM4" s="478" t="n"/>
-      <c r="AN4" s="480" t="n"/>
+      <c r="I10" s="596" t="n"/>
+      <c r="J10" s="596" t="n"/>
+      <c r="K10" s="596" t="n"/>
+      <c r="L10" s="596" t="n"/>
+      <c r="M10" s="596" t="n"/>
+      <c r="N10" s="596" t="n"/>
+      <c r="O10" s="596" t="n"/>
+      <c r="P10" s="596" t="n"/>
+      <c r="Q10" s="596" t="n"/>
+      <c r="R10" s="596" t="n"/>
+      <c r="S10" s="596" t="n"/>
+      <c r="T10" s="596" t="n"/>
+      <c r="U10" s="596" t="n"/>
+      <c r="V10" s="596" t="n"/>
+      <c r="W10" s="596" t="n"/>
+      <c r="X10" s="596" t="n"/>
+      <c r="Y10" s="596" t="n"/>
+      <c r="Z10" s="596" t="n"/>
+      <c r="AA10" s="596" t="n"/>
+      <c r="AB10" s="596" t="n"/>
+      <c r="AC10" s="596" t="n"/>
+      <c r="AD10" s="596" t="n"/>
+      <c r="AE10" s="596" t="n"/>
+      <c r="AF10" s="596" t="n"/>
+      <c r="AG10" s="596" t="n"/>
+      <c r="AH10" s="596" t="n"/>
+      <c r="AI10" s="596" t="n"/>
+      <c r="AJ10" s="596" t="n"/>
+      <c r="AK10" s="596" t="n"/>
+      <c r="AL10" s="596" t="n"/>
+      <c r="AM10" s="596" t="n"/>
+      <c r="AN10" s="596" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="501">
+    <row r="11" ht="20" customHeight="1" s="329">
+      <c r="A11" s="501">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="459" t="n"/>
-      <c r="C5" s="459" t="n"/>
-      <c r="D5" s="459" t="n"/>
-      <c r="E5" s="459" t="n"/>
-      <c r="F5" s="459" t="n"/>
-      <c r="G5" s="459" t="n"/>
-      <c r="H5" s="459" t="n"/>
-      <c r="I5" s="459" t="n"/>
-      <c r="J5" s="459" t="n"/>
-      <c r="K5" s="459" t="n"/>
-      <c r="L5" s="459" t="n"/>
-      <c r="M5" s="459" t="n"/>
-      <c r="N5" s="459" t="n"/>
-      <c r="O5" s="459" t="n"/>
-      <c r="P5" s="459" t="n"/>
-      <c r="Q5" s="459" t="n"/>
-      <c r="R5" s="459" t="n"/>
-      <c r="S5" s="459" t="n"/>
-      <c r="T5" s="459" t="n"/>
-      <c r="U5" s="459" t="n"/>
-      <c r="V5" s="459" t="n"/>
-      <c r="W5" s="459" t="n"/>
-      <c r="X5" s="459" t="n"/>
-      <c r="Y5" s="459" t="n"/>
-      <c r="Z5" s="459" t="n"/>
-      <c r="AA5" s="459" t="n"/>
-      <c r="AB5" s="459" t="n"/>
-      <c r="AC5" s="459" t="n"/>
-      <c r="AD5" s="459" t="n"/>
-      <c r="AE5" s="459" t="n"/>
-      <c r="AF5" s="459" t="n"/>
-      <c r="AG5" s="459" t="n"/>
-      <c r="AH5" s="459" t="n"/>
-      <c r="AI5" s="459" t="n"/>
-      <c r="AJ5" s="459" t="n"/>
-      <c r="AK5" s="459" t="n"/>
-      <c r="AL5" s="459" t="n"/>
-      <c r="AM5" s="459" t="n"/>
-      <c r="AN5" s="462" t="n"/>
+      <c r="B11" s="596" t="n"/>
+      <c r="C11" s="596" t="n"/>
+      <c r="D11" s="596" t="n"/>
+      <c r="E11" s="596" t="n"/>
+      <c r="F11" s="596" t="n"/>
+      <c r="G11" s="596" t="n"/>
+      <c r="H11" s="596" t="n"/>
+      <c r="I11" s="596" t="n"/>
+      <c r="J11" s="596" t="n"/>
+      <c r="K11" s="596" t="n"/>
+      <c r="L11" s="596" t="n"/>
+      <c r="M11" s="596" t="n"/>
+      <c r="N11" s="596" t="n"/>
+      <c r="O11" s="596" t="n"/>
+      <c r="P11" s="596" t="n"/>
+      <c r="Q11" s="596" t="n"/>
+      <c r="R11" s="596" t="n"/>
+      <c r="S11" s="596" t="n"/>
+      <c r="T11" s="596" t="n"/>
+      <c r="U11" s="596" t="n"/>
+      <c r="V11" s="596" t="n"/>
+      <c r="W11" s="596" t="n"/>
+      <c r="X11" s="596" t="n"/>
+      <c r="Y11" s="596" t="n"/>
+      <c r="Z11" s="596" t="n"/>
+      <c r="AA11" s="596" t="n"/>
+      <c r="AB11" s="596" t="n"/>
+      <c r="AC11" s="596" t="n"/>
+      <c r="AD11" s="596" t="n"/>
+      <c r="AE11" s="596" t="n"/>
+      <c r="AF11" s="596" t="n"/>
+      <c r="AG11" s="596" t="n"/>
+      <c r="AH11" s="596" t="n"/>
+      <c r="AI11" s="596" t="n"/>
+      <c r="AJ11" s="596" t="n"/>
+      <c r="AK11" s="596" t="n"/>
+      <c r="AL11" s="596" t="n"/>
+      <c r="AM11" s="596" t="n"/>
+      <c r="AN11" s="596" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="474">
+    <row r="12" ht="20" customHeight="1" s="329">
+      <c r="A12" s="474">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="343" t="n"/>
-      <c r="C6" s="343" t="n"/>
-      <c r="D6" s="343" t="n"/>
-      <c r="E6" s="343" t="n"/>
-      <c r="F6" s="343" t="n"/>
-      <c r="G6" s="343" t="n"/>
-      <c r="H6" s="343" t="n"/>
-      <c r="I6" s="343" t="n"/>
-      <c r="J6" s="343" t="n"/>
-      <c r="K6" s="343" t="n"/>
-      <c r="L6" s="343" t="n"/>
-      <c r="M6" s="343" t="n"/>
-      <c r="N6" s="343" t="n"/>
-      <c r="O6" s="343" t="n"/>
-      <c r="P6" s="343" t="n"/>
-      <c r="Q6" s="343" t="n"/>
-      <c r="R6" s="343" t="n"/>
-      <c r="S6" s="343" t="n"/>
-      <c r="T6" s="343" t="n"/>
-      <c r="U6" s="343" t="n"/>
-      <c r="V6" s="343" t="n"/>
-      <c r="W6" s="343" t="n"/>
-      <c r="X6" s="343" t="n"/>
-      <c r="Y6" s="343" t="n"/>
-      <c r="Z6" s="343" t="n"/>
-      <c r="AA6" s="343" t="n"/>
-      <c r="AB6" s="343" t="n"/>
-      <c r="AC6" s="343" t="n"/>
-      <c r="AD6" s="343" t="n"/>
-      <c r="AE6" s="343" t="n"/>
-      <c r="AF6" s="343" t="n"/>
-      <c r="AG6" s="343" t="n"/>
-      <c r="AH6" s="343" t="n"/>
-      <c r="AI6" s="343" t="n"/>
-      <c r="AJ6" s="343" t="n"/>
-      <c r="AK6" s="343" t="n"/>
-      <c r="AL6" s="343" t="n"/>
-      <c r="AM6" s="343" t="n"/>
-      <c r="AN6" s="466" t="n"/>
+      <c r="B12" s="596" t="n"/>
+      <c r="C12" s="596" t="n"/>
+      <c r="D12" s="596" t="n"/>
+      <c r="E12" s="596" t="n"/>
+      <c r="F12" s="596" t="n"/>
+      <c r="G12" s="596" t="n"/>
+      <c r="H12" s="596" t="n"/>
+      <c r="I12" s="596" t="n"/>
+      <c r="J12" s="596" t="n"/>
+      <c r="K12" s="596" t="n"/>
+      <c r="L12" s="596" t="n"/>
+      <c r="M12" s="596" t="n"/>
+      <c r="N12" s="596" t="n"/>
+      <c r="O12" s="596" t="n"/>
+      <c r="P12" s="596" t="n"/>
+      <c r="Q12" s="596" t="n"/>
+      <c r="R12" s="596" t="n"/>
+      <c r="S12" s="596" t="n"/>
+      <c r="T12" s="596" t="n"/>
+      <c r="U12" s="596" t="n"/>
+      <c r="V12" s="596" t="n"/>
+      <c r="W12" s="596" t="n"/>
+      <c r="X12" s="596" t="n"/>
+      <c r="Y12" s="596" t="n"/>
+      <c r="Z12" s="596" t="n"/>
+      <c r="AA12" s="596" t="n"/>
+      <c r="AB12" s="596" t="n"/>
+      <c r="AC12" s="596" t="n"/>
+      <c r="AD12" s="596" t="n"/>
+      <c r="AE12" s="596" t="n"/>
+      <c r="AF12" s="596" t="n"/>
+      <c r="AG12" s="596" t="n"/>
+      <c r="AH12" s="596" t="n"/>
+      <c r="AI12" s="596" t="n"/>
+      <c r="AJ12" s="596" t="n"/>
+      <c r="AK12" s="596" t="n"/>
+      <c r="AL12" s="596" t="n"/>
+      <c r="AM12" s="596" t="n"/>
+      <c r="AN12" s="596" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="474">
+    <row r="13" ht="20" customHeight="1" s="329">
+      <c r="A13" s="474">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="343" t="n"/>
-      <c r="C7" s="343" t="n"/>
-      <c r="D7" s="343" t="n"/>
-      <c r="E7" s="343" t="n"/>
-      <c r="F7" s="343" t="n"/>
-      <c r="G7" s="343" t="n"/>
-      <c r="H7" s="343" t="n"/>
-      <c r="I7" s="343" t="n"/>
-      <c r="J7" s="343" t="n"/>
-      <c r="K7" s="343" t="n"/>
-      <c r="L7" s="343" t="n"/>
-      <c r="M7" s="343" t="n"/>
-      <c r="N7" s="343" t="n"/>
-      <c r="O7" s="343" t="n"/>
-      <c r="P7" s="343" t="n"/>
-      <c r="Q7" s="343" t="n"/>
-      <c r="R7" s="343" t="n"/>
-      <c r="S7" s="343" t="n"/>
-      <c r="T7" s="343" t="n"/>
-      <c r="U7" s="343" t="n"/>
-      <c r="V7" s="343" t="n"/>
-      <c r="W7" s="343" t="n"/>
-      <c r="X7" s="343" t="n"/>
-      <c r="Y7" s="343" t="n"/>
-      <c r="Z7" s="343" t="n"/>
-      <c r="AA7" s="343" t="n"/>
-      <c r="AB7" s="343" t="n"/>
-      <c r="AC7" s="343" t="n"/>
-      <c r="AD7" s="343" t="n"/>
-      <c r="AE7" s="343" t="n"/>
-      <c r="AF7" s="343" t="n"/>
-      <c r="AG7" s="343" t="n"/>
-      <c r="AH7" s="343" t="n"/>
-      <c r="AI7" s="343" t="n"/>
-      <c r="AJ7" s="343" t="n"/>
-      <c r="AK7" s="343" t="n"/>
-      <c r="AL7" s="343" t="n"/>
-      <c r="AM7" s="343" t="n"/>
-      <c r="AN7" s="466" t="n"/>
+      <c r="B13" s="596" t="n"/>
+      <c r="C13" s="596" t="n"/>
+      <c r="D13" s="596" t="n"/>
+      <c r="E13" s="596" t="n"/>
+      <c r="F13" s="596" t="n"/>
+      <c r="G13" s="596" t="n"/>
+      <c r="H13" s="596" t="n"/>
+      <c r="I13" s="596" t="n"/>
+      <c r="J13" s="596" t="n"/>
+      <c r="K13" s="596" t="n"/>
+      <c r="L13" s="596" t="n"/>
+      <c r="M13" s="596" t="n"/>
+      <c r="N13" s="596" t="n"/>
+      <c r="O13" s="596" t="n"/>
+      <c r="P13" s="596" t="n"/>
+      <c r="Q13" s="596" t="n"/>
+      <c r="R13" s="596" t="n"/>
+      <c r="S13" s="596" t="n"/>
+      <c r="T13" s="596" t="n"/>
+      <c r="U13" s="596" t="n"/>
+      <c r="V13" s="596" t="n"/>
+      <c r="W13" s="596" t="n"/>
+      <c r="X13" s="596" t="n"/>
+      <c r="Y13" s="596" t="n"/>
+      <c r="Z13" s="596" t="n"/>
+      <c r="AA13" s="596" t="n"/>
+      <c r="AB13" s="596" t="n"/>
+      <c r="AC13" s="596" t="n"/>
+      <c r="AD13" s="596" t="n"/>
+      <c r="AE13" s="596" t="n"/>
+      <c r="AF13" s="596" t="n"/>
+      <c r="AG13" s="596" t="n"/>
+      <c r="AH13" s="596" t="n"/>
+      <c r="AI13" s="596" t="n"/>
+      <c r="AJ13" s="596" t="n"/>
+      <c r="AK13" s="596" t="n"/>
+      <c r="AL13" s="596" t="n"/>
+      <c r="AM13" s="596" t="n"/>
+      <c r="AN13" s="596" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="502">
+    <row r="14" ht="20" customHeight="1" s="329">
+      <c r="A14" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="355" t="n"/>
-      <c r="C8" s="355" t="n"/>
-      <c r="D8" s="355" t="n"/>
-      <c r="E8" s="355" t="n"/>
-      <c r="F8" s="355" t="n"/>
-      <c r="G8" s="355" t="n"/>
-      <c r="H8" s="355" t="n"/>
-      <c r="I8" s="355" t="n"/>
-      <c r="J8" s="355" t="n"/>
-      <c r="K8" s="355" t="n"/>
-      <c r="L8" s="355" t="n"/>
-      <c r="M8" s="355" t="n"/>
-      <c r="N8" s="355" t="n"/>
-      <c r="O8" s="355" t="n"/>
-      <c r="P8" s="355" t="n"/>
-      <c r="Q8" s="355" t="n"/>
-      <c r="R8" s="355" t="n"/>
-      <c r="S8" s="355" t="n"/>
-      <c r="T8" s="355" t="n"/>
-      <c r="U8" s="355" t="n"/>
-      <c r="V8" s="355" t="n"/>
-      <c r="W8" s="355" t="n"/>
-      <c r="X8" s="355" t="n"/>
-      <c r="Y8" s="355" t="n"/>
-      <c r="Z8" s="355" t="n"/>
-      <c r="AA8" s="355" t="n"/>
-      <c r="AB8" s="355" t="n"/>
-      <c r="AC8" s="355" t="n"/>
-      <c r="AD8" s="355" t="n"/>
-      <c r="AE8" s="355" t="n"/>
-      <c r="AF8" s="355" t="n"/>
-      <c r="AG8" s="355" t="n"/>
-      <c r="AH8" s="355" t="n"/>
-      <c r="AI8" s="355" t="n"/>
-      <c r="AJ8" s="355" t="n"/>
-      <c r="AK8" s="355" t="n"/>
-      <c r="AL8" s="355" t="n"/>
-      <c r="AM8" s="355" t="n"/>
-      <c r="AN8" s="503" t="n"/>
+      <c r="B14" s="596" t="n"/>
+      <c r="C14" s="596" t="n"/>
+      <c r="D14" s="596" t="n"/>
+      <c r="E14" s="596" t="n"/>
+      <c r="F14" s="596" t="n"/>
+      <c r="G14" s="596" t="n"/>
+      <c r="H14" s="596" t="n"/>
+      <c r="I14" s="596" t="n"/>
+      <c r="J14" s="596" t="n"/>
+      <c r="K14" s="596" t="n"/>
+      <c r="L14" s="596" t="n"/>
+      <c r="M14" s="596" t="n"/>
+      <c r="N14" s="596" t="n"/>
+      <c r="O14" s="596" t="n"/>
+      <c r="P14" s="596" t="n"/>
+      <c r="Q14" s="596" t="n"/>
+      <c r="R14" s="596" t="n"/>
+      <c r="S14" s="596" t="n"/>
+      <c r="T14" s="596" t="n"/>
+      <c r="U14" s="596" t="n"/>
+      <c r="V14" s="596" t="n"/>
+      <c r="W14" s="596" t="n"/>
+      <c r="X14" s="596" t="n"/>
+      <c r="Y14" s="596" t="n"/>
+      <c r="Z14" s="596" t="n"/>
+      <c r="AA14" s="596" t="n"/>
+      <c r="AB14" s="596" t="n"/>
+      <c r="AC14" s="596" t="n"/>
+      <c r="AD14" s="596" t="n"/>
+      <c r="AE14" s="596" t="n"/>
+      <c r="AF14" s="596" t="n"/>
+      <c r="AG14" s="596" t="n"/>
+      <c r="AH14" s="596" t="n"/>
+      <c r="AI14" s="596" t="n"/>
+      <c r="AJ14" s="596" t="n"/>
+      <c r="AK14" s="596" t="n"/>
+      <c r="AL14" s="596" t="n"/>
+      <c r="AM14" s="596" t="n"/>
+      <c r="AN14" s="596" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="502">
+    <row r="15" ht="20" customHeight="1" s="329">
+      <c r="A15" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="355" t="n"/>
-      <c r="C9" s="355" t="n"/>
-      <c r="D9" s="355" t="n"/>
-      <c r="E9" s="355" t="n"/>
-      <c r="F9" s="355" t="n"/>
-      <c r="G9" s="355" t="n"/>
-      <c r="H9" s="355" t="n"/>
-      <c r="I9" s="355" t="n"/>
-      <c r="J9" s="355" t="n"/>
-      <c r="K9" s="355" t="n"/>
-      <c r="L9" s="355" t="n"/>
-      <c r="M9" s="355" t="n"/>
-      <c r="N9" s="355" t="n"/>
-      <c r="O9" s="355" t="n"/>
-      <c r="P9" s="355" t="n"/>
-      <c r="Q9" s="355" t="n"/>
-      <c r="R9" s="355" t="n"/>
-      <c r="S9" s="355" t="n"/>
-      <c r="T9" s="355" t="n"/>
-      <c r="U9" s="355" t="n"/>
-      <c r="V9" s="355" t="n"/>
-      <c r="W9" s="355" t="n"/>
-      <c r="X9" s="355" t="n"/>
-      <c r="Y9" s="355" t="n"/>
-      <c r="Z9" s="355" t="n"/>
-      <c r="AA9" s="355" t="n"/>
-      <c r="AB9" s="355" t="n"/>
-      <c r="AC9" s="355" t="n"/>
-      <c r="AD9" s="355" t="n"/>
-      <c r="AE9" s="355" t="n"/>
-      <c r="AF9" s="355" t="n"/>
-      <c r="AG9" s="355" t="n"/>
-      <c r="AH9" s="355" t="n"/>
-      <c r="AI9" s="355" t="n"/>
-      <c r="AJ9" s="355" t="n"/>
-      <c r="AK9" s="355" t="n"/>
-      <c r="AL9" s="355" t="n"/>
-      <c r="AM9" s="355" t="n"/>
-      <c r="AN9" s="503" t="n"/>
+      <c r="B15" s="596" t="n"/>
+      <c r="C15" s="596" t="n"/>
+      <c r="D15" s="596" t="n"/>
+      <c r="E15" s="596" t="n"/>
+      <c r="F15" s="596" t="n"/>
+      <c r="G15" s="596" t="n"/>
+      <c r="H15" s="596" t="n"/>
+      <c r="I15" s="596" t="n"/>
+      <c r="J15" s="596" t="n"/>
+      <c r="K15" s="596" t="n"/>
+      <c r="L15" s="596" t="n"/>
+      <c r="M15" s="596" t="n"/>
+      <c r="N15" s="596" t="n"/>
+      <c r="O15" s="596" t="n"/>
+      <c r="P15" s="596" t="n"/>
+      <c r="Q15" s="596" t="n"/>
+      <c r="R15" s="596" t="n"/>
+      <c r="S15" s="596" t="n"/>
+      <c r="T15" s="596" t="n"/>
+      <c r="U15" s="596" t="n"/>
+      <c r="V15" s="596" t="n"/>
+      <c r="W15" s="596" t="n"/>
+      <c r="X15" s="596" t="n"/>
+      <c r="Y15" s="596" t="n"/>
+      <c r="Z15" s="596" t="n"/>
+      <c r="AA15" s="596" t="n"/>
+      <c r="AB15" s="596" t="n"/>
+      <c r="AC15" s="596" t="n"/>
+      <c r="AD15" s="596" t="n"/>
+      <c r="AE15" s="596" t="n"/>
+      <c r="AF15" s="596" t="n"/>
+      <c r="AG15" s="596" t="n"/>
+      <c r="AH15" s="596" t="n"/>
+      <c r="AI15" s="596" t="n"/>
+      <c r="AJ15" s="596" t="n"/>
+      <c r="AK15" s="596" t="n"/>
+      <c r="AL15" s="596" t="n"/>
+      <c r="AM15" s="596" t="n"/>
+      <c r="AN15" s="596" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="502">
+    <row r="16" ht="20" customHeight="1" s="329">
+      <c r="A16" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="355" t="n"/>
-      <c r="C10" s="355" t="n"/>
-      <c r="D10" s="355" t="n"/>
-      <c r="E10" s="355" t="n"/>
-      <c r="F10" s="355" t="n"/>
-      <c r="G10" s="355" t="n"/>
-      <c r="H10" s="355" t="n"/>
-      <c r="I10" s="355" t="n"/>
-      <c r="J10" s="355" t="n"/>
-      <c r="K10" s="355" t="n"/>
-      <c r="L10" s="355" t="n"/>
-      <c r="M10" s="355" t="n"/>
-      <c r="N10" s="355" t="n"/>
-      <c r="O10" s="355" t="n"/>
-      <c r="P10" s="355" t="n"/>
-      <c r="Q10" s="355" t="n"/>
-      <c r="R10" s="355" t="n"/>
-      <c r="S10" s="355" t="n"/>
-      <c r="T10" s="355" t="n"/>
-      <c r="U10" s="355" t="n"/>
-      <c r="V10" s="355" t="n"/>
-      <c r="W10" s="355" t="n"/>
-      <c r="X10" s="355" t="n"/>
-      <c r="Y10" s="355" t="n"/>
-      <c r="Z10" s="355" t="n"/>
-      <c r="AA10" s="355" t="n"/>
-      <c r="AB10" s="355" t="n"/>
-      <c r="AC10" s="355" t="n"/>
-      <c r="AD10" s="355" t="n"/>
-      <c r="AE10" s="355" t="n"/>
-      <c r="AF10" s="355" t="n"/>
-      <c r="AG10" s="355" t="n"/>
-      <c r="AH10" s="355" t="n"/>
-      <c r="AI10" s="355" t="n"/>
-      <c r="AJ10" s="355" t="n"/>
-      <c r="AK10" s="355" t="n"/>
-      <c r="AL10" s="355" t="n"/>
-      <c r="AM10" s="355" t="n"/>
-      <c r="AN10" s="503" t="n"/>
+      <c r="B16" s="596" t="n"/>
+      <c r="C16" s="596" t="n"/>
+      <c r="D16" s="596" t="n"/>
+      <c r="E16" s="596" t="n"/>
+      <c r="F16" s="596" t="n"/>
+      <c r="G16" s="596" t="n"/>
+      <c r="H16" s="596" t="n"/>
+      <c r="I16" s="596" t="n"/>
+      <c r="J16" s="596" t="n"/>
+      <c r="K16" s="596" t="n"/>
+      <c r="L16" s="596" t="n"/>
+      <c r="M16" s="596" t="n"/>
+      <c r="N16" s="596" t="n"/>
+      <c r="O16" s="596" t="n"/>
+      <c r="P16" s="596" t="n"/>
+      <c r="Q16" s="596" t="n"/>
+      <c r="R16" s="596" t="n"/>
+      <c r="S16" s="596" t="n"/>
+      <c r="T16" s="596" t="n"/>
+      <c r="U16" s="596" t="n"/>
+      <c r="V16" s="596" t="n"/>
+      <c r="W16" s="596" t="n"/>
+      <c r="X16" s="596" t="n"/>
+      <c r="Y16" s="596" t="n"/>
+      <c r="Z16" s="596" t="n"/>
+      <c r="AA16" s="596" t="n"/>
+      <c r="AB16" s="596" t="n"/>
+      <c r="AC16" s="596" t="n"/>
+      <c r="AD16" s="596" t="n"/>
+      <c r="AE16" s="596" t="n"/>
+      <c r="AF16" s="596" t="n"/>
+      <c r="AG16" s="596" t="n"/>
+      <c r="AH16" s="596" t="n"/>
+      <c r="AI16" s="596" t="n"/>
+      <c r="AJ16" s="596" t="n"/>
+      <c r="AK16" s="596" t="n"/>
+      <c r="AL16" s="596" t="n"/>
+      <c r="AM16" s="596" t="n"/>
+      <c r="AN16" s="596" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="502">
+    <row r="17" ht="20" customHeight="1" s="329">
+      <c r="A17" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="355" t="n"/>
-      <c r="C11" s="355" t="n"/>
-      <c r="D11" s="355" t="n"/>
-      <c r="E11" s="355" t="n"/>
-      <c r="F11" s="355" t="n"/>
-      <c r="G11" s="355" t="n"/>
-      <c r="H11" s="355" t="n"/>
-      <c r="I11" s="355" t="n"/>
-      <c r="J11" s="355" t="n"/>
-      <c r="K11" s="355" t="n"/>
-      <c r="L11" s="355" t="n"/>
-      <c r="M11" s="355" t="n"/>
-      <c r="N11" s="355" t="n"/>
-      <c r="O11" s="355" t="n"/>
-      <c r="P11" s="355" t="n"/>
-      <c r="Q11" s="355" t="n"/>
-      <c r="R11" s="355" t="n"/>
-      <c r="S11" s="355" t="n"/>
-      <c r="T11" s="355" t="n"/>
-      <c r="U11" s="355" t="n"/>
-      <c r="V11" s="355" t="n"/>
-      <c r="W11" s="355" t="n"/>
-      <c r="X11" s="355" t="n"/>
-      <c r="Y11" s="355" t="n"/>
-      <c r="Z11" s="355" t="n"/>
-      <c r="AA11" s="355" t="n"/>
-      <c r="AB11" s="355" t="n"/>
-      <c r="AC11" s="355" t="n"/>
-      <c r="AD11" s="355" t="n"/>
-      <c r="AE11" s="355" t="n"/>
-      <c r="AF11" s="355" t="n"/>
-      <c r="AG11" s="355" t="n"/>
-      <c r="AH11" s="355" t="n"/>
-      <c r="AI11" s="355" t="n"/>
-      <c r="AJ11" s="355" t="n"/>
-      <c r="AK11" s="355" t="n"/>
-      <c r="AL11" s="355" t="n"/>
-      <c r="AM11" s="355" t="n"/>
-      <c r="AN11" s="503" t="n"/>
+      <c r="B17" s="596" t="n"/>
+      <c r="C17" s="596" t="n"/>
+      <c r="D17" s="596" t="n"/>
+      <c r="E17" s="596" t="n"/>
+      <c r="F17" s="596" t="n"/>
+      <c r="G17" s="596" t="n"/>
+      <c r="H17" s="596" t="n"/>
+      <c r="I17" s="596" t="n"/>
+      <c r="J17" s="596" t="n"/>
+      <c r="K17" s="596" t="n"/>
+      <c r="L17" s="596" t="n"/>
+      <c r="M17" s="596" t="n"/>
+      <c r="N17" s="596" t="n"/>
+      <c r="O17" s="596" t="n"/>
+      <c r="P17" s="596" t="n"/>
+      <c r="Q17" s="596" t="n"/>
+      <c r="R17" s="596" t="n"/>
+      <c r="S17" s="596" t="n"/>
+      <c r="T17" s="596" t="n"/>
+      <c r="U17" s="596" t="n"/>
+      <c r="V17" s="596" t="n"/>
+      <c r="W17" s="596" t="n"/>
+      <c r="X17" s="596" t="n"/>
+      <c r="Y17" s="596" t="n"/>
+      <c r="Z17" s="596" t="n"/>
+      <c r="AA17" s="596" t="n"/>
+      <c r="AB17" s="596" t="n"/>
+      <c r="AC17" s="596" t="n"/>
+      <c r="AD17" s="596" t="n"/>
+      <c r="AE17" s="596" t="n"/>
+      <c r="AF17" s="596" t="n"/>
+      <c r="AG17" s="596" t="n"/>
+      <c r="AH17" s="596" t="n"/>
+      <c r="AI17" s="596" t="n"/>
+      <c r="AJ17" s="596" t="n"/>
+      <c r="AK17" s="596" t="n"/>
+      <c r="AL17" s="596" t="n"/>
+      <c r="AM17" s="596" t="n"/>
+      <c r="AN17" s="596" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="502">
+    <row r="18" ht="20" customHeight="1" s="329">
+      <c r="A18" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="355" t="n"/>
-      <c r="C12" s="355" t="n"/>
-      <c r="D12" s="355" t="n"/>
-      <c r="E12" s="355" t="n"/>
-      <c r="F12" s="355" t="n"/>
-      <c r="G12" s="355" t="n"/>
-      <c r="H12" s="355" t="n"/>
-      <c r="I12" s="355" t="n"/>
-      <c r="J12" s="355" t="n"/>
-      <c r="K12" s="355" t="n"/>
-      <c r="L12" s="355" t="n"/>
-      <c r="M12" s="355" t="n"/>
-      <c r="N12" s="355" t="n"/>
-      <c r="O12" s="355" t="n"/>
-      <c r="P12" s="355" t="n"/>
-      <c r="Q12" s="355" t="n"/>
-      <c r="R12" s="355" t="n"/>
-      <c r="S12" s="355" t="n"/>
-      <c r="T12" s="355" t="n"/>
-      <c r="U12" s="355" t="n"/>
-      <c r="V12" s="355" t="n"/>
-      <c r="W12" s="355" t="n"/>
-      <c r="X12" s="355" t="n"/>
-      <c r="Y12" s="355" t="n"/>
-      <c r="Z12" s="355" t="n"/>
-      <c r="AA12" s="355" t="n"/>
-      <c r="AB12" s="355" t="n"/>
-      <c r="AC12" s="355" t="n"/>
-      <c r="AD12" s="355" t="n"/>
-      <c r="AE12" s="355" t="n"/>
-      <c r="AF12" s="355" t="n"/>
-      <c r="AG12" s="355" t="n"/>
-      <c r="AH12" s="355" t="n"/>
-      <c r="AI12" s="355" t="n"/>
-      <c r="AJ12" s="355" t="n"/>
-      <c r="AK12" s="355" t="n"/>
-      <c r="AL12" s="355" t="n"/>
-      <c r="AM12" s="355" t="n"/>
-      <c r="AN12" s="503" t="n"/>
+      <c r="B18" s="596" t="n"/>
+      <c r="C18" s="596" t="n"/>
+      <c r="D18" s="596" t="n"/>
+      <c r="E18" s="596" t="n"/>
+      <c r="F18" s="596" t="n"/>
+      <c r="G18" s="596" t="n"/>
+      <c r="H18" s="596" t="n"/>
+      <c r="I18" s="596" t="n"/>
+      <c r="J18" s="596" t="n"/>
+      <c r="K18" s="596" t="n"/>
+      <c r="L18" s="596" t="n"/>
+      <c r="M18" s="596" t="n"/>
+      <c r="N18" s="596" t="n"/>
+      <c r="O18" s="596" t="n"/>
+      <c r="P18" s="596" t="n"/>
+      <c r="Q18" s="596" t="n"/>
+      <c r="R18" s="596" t="n"/>
+      <c r="S18" s="596" t="n"/>
+      <c r="T18" s="596" t="n"/>
+      <c r="U18" s="596" t="n"/>
+      <c r="V18" s="596" t="n"/>
+      <c r="W18" s="596" t="n"/>
+      <c r="X18" s="596" t="n"/>
+      <c r="Y18" s="596" t="n"/>
+      <c r="Z18" s="596" t="n"/>
+      <c r="AA18" s="596" t="n"/>
+      <c r="AB18" s="596" t="n"/>
+      <c r="AC18" s="596" t="n"/>
+      <c r="AD18" s="596" t="n"/>
+      <c r="AE18" s="596" t="n"/>
+      <c r="AF18" s="596" t="n"/>
+      <c r="AG18" s="596" t="n"/>
+      <c r="AH18" s="596" t="n"/>
+      <c r="AI18" s="596" t="n"/>
+      <c r="AJ18" s="596" t="n"/>
+      <c r="AK18" s="596" t="n"/>
+      <c r="AL18" s="596" t="n"/>
+      <c r="AM18" s="596" t="n"/>
+      <c r="AN18" s="596" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="502">
+    <row r="19" ht="20" customHeight="1" s="329">
+      <c r="A19" s="502">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="355" t="n"/>
-      <c r="C13" s="355" t="n"/>
-      <c r="D13" s="355" t="n"/>
-      <c r="E13" s="355" t="n"/>
-      <c r="F13" s="355" t="n"/>
-      <c r="G13" s="355" t="n"/>
-      <c r="H13" s="355" t="n"/>
-      <c r="I13" s="355" t="n"/>
-      <c r="J13" s="355" t="n"/>
-      <c r="K13" s="355" t="n"/>
-      <c r="L13" s="355" t="n"/>
-      <c r="M13" s="355" t="n"/>
-      <c r="N13" s="355" t="n"/>
-      <c r="O13" s="355" t="n"/>
-      <c r="P13" s="355" t="n"/>
-      <c r="Q13" s="355" t="n"/>
-      <c r="R13" s="355" t="n"/>
-      <c r="S13" s="355" t="n"/>
-      <c r="T13" s="355" t="n"/>
-      <c r="U13" s="355" t="n"/>
-      <c r="V13" s="355" t="n"/>
-      <c r="W13" s="355" t="n"/>
-      <c r="X13" s="355" t="n"/>
-      <c r="Y13" s="355" t="n"/>
-      <c r="Z13" s="355" t="n"/>
-      <c r="AA13" s="355" t="n"/>
-      <c r="AB13" s="355" t="n"/>
-      <c r="AC13" s="355" t="n"/>
-      <c r="AD13" s="355" t="n"/>
-      <c r="AE13" s="355" t="n"/>
-      <c r="AF13" s="355" t="n"/>
-      <c r="AG13" s="355" t="n"/>
-      <c r="AH13" s="355" t="n"/>
-      <c r="AI13" s="355" t="n"/>
-      <c r="AJ13" s="355" t="n"/>
-      <c r="AK13" s="355" t="n"/>
-      <c r="AL13" s="355" t="n"/>
-      <c r="AM13" s="355" t="n"/>
-      <c r="AN13" s="503" t="n"/>
+      <c r="B19" s="596" t="n"/>
+      <c r="C19" s="596" t="n"/>
+      <c r="D19" s="596" t="n"/>
+      <c r="E19" s="596" t="n"/>
+      <c r="F19" s="596" t="n"/>
+      <c r="G19" s="596" t="n"/>
+      <c r="H19" s="596" t="n"/>
+      <c r="I19" s="596" t="n"/>
+      <c r="J19" s="596" t="n"/>
+      <c r="K19" s="596" t="n"/>
+      <c r="L19" s="596" t="n"/>
+      <c r="M19" s="596" t="n"/>
+      <c r="N19" s="596" t="n"/>
+      <c r="O19" s="596" t="n"/>
+      <c r="P19" s="596" t="n"/>
+      <c r="Q19" s="596" t="n"/>
+      <c r="R19" s="596" t="n"/>
+      <c r="S19" s="596" t="n"/>
+      <c r="T19" s="596" t="n"/>
+      <c r="U19" s="596" t="n"/>
+      <c r="V19" s="596" t="n"/>
+      <c r="W19" s="596" t="n"/>
+      <c r="X19" s="596" t="n"/>
+      <c r="Y19" s="596" t="n"/>
+      <c r="Z19" s="596" t="n"/>
+      <c r="AA19" s="596" t="n"/>
+      <c r="AB19" s="596" t="n"/>
+      <c r="AC19" s="596" t="n"/>
+      <c r="AD19" s="596" t="n"/>
+      <c r="AE19" s="596" t="n"/>
+      <c r="AF19" s="596" t="n"/>
+      <c r="AG19" s="596" t="n"/>
+      <c r="AH19" s="596" t="n"/>
+      <c r="AI19" s="596" t="n"/>
+      <c r="AJ19" s="596" t="n"/>
+      <c r="AK19" s="596" t="n"/>
+      <c r="AL19" s="596" t="n"/>
+      <c r="AM19" s="596" t="n"/>
+      <c r="AN19" s="596" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="504">
+    <row r="20" ht="20" customHeight="1" s="329">
+      <c r="A20" s="504">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="505" t="n"/>
-      <c r="C14" s="505" t="n"/>
-      <c r="D14" s="505" t="n"/>
-      <c r="E14" s="505" t="n"/>
-      <c r="F14" s="505" t="n"/>
-      <c r="G14" s="505" t="n"/>
-      <c r="H14" s="505" t="n"/>
-      <c r="I14" s="505" t="n"/>
-      <c r="J14" s="505" t="n"/>
-      <c r="K14" s="505" t="n"/>
-      <c r="L14" s="505" t="n"/>
-      <c r="M14" s="505" t="n"/>
-      <c r="N14" s="505" t="n"/>
-      <c r="O14" s="505" t="n"/>
-      <c r="P14" s="505" t="n"/>
-      <c r="Q14" s="505" t="n"/>
-      <c r="R14" s="505" t="n"/>
-      <c r="S14" s="505" t="n"/>
-      <c r="T14" s="505" t="n"/>
-      <c r="U14" s="505" t="n"/>
-      <c r="V14" s="505" t="n"/>
-      <c r="W14" s="505" t="n"/>
-      <c r="X14" s="505" t="n"/>
-      <c r="Y14" s="505" t="n"/>
-      <c r="Z14" s="505" t="n"/>
-      <c r="AA14" s="505" t="n"/>
-      <c r="AB14" s="505" t="n"/>
-      <c r="AC14" s="505" t="n"/>
-      <c r="AD14" s="505" t="n"/>
-      <c r="AE14" s="505" t="n"/>
-      <c r="AF14" s="505" t="n"/>
-      <c r="AG14" s="505" t="n"/>
-      <c r="AH14" s="505" t="n"/>
-      <c r="AI14" s="505" t="n"/>
-      <c r="AJ14" s="505" t="n"/>
-      <c r="AK14" s="505" t="n"/>
-      <c r="AL14" s="505" t="n"/>
-      <c r="AM14" s="505" t="n"/>
-      <c r="AN14" s="506" t="n"/>
+      <c r="B20" s="596" t="n"/>
+      <c r="C20" s="596" t="n"/>
+      <c r="D20" s="596" t="n"/>
+      <c r="E20" s="596" t="n"/>
+      <c r="F20" s="596" t="n"/>
+      <c r="G20" s="596" t="n"/>
+      <c r="H20" s="596" t="n"/>
+      <c r="I20" s="596" t="n"/>
+      <c r="J20" s="596" t="n"/>
+      <c r="K20" s="596" t="n"/>
+      <c r="L20" s="596" t="n"/>
+      <c r="M20" s="596" t="n"/>
+      <c r="N20" s="596" t="n"/>
+      <c r="O20" s="596" t="n"/>
+      <c r="P20" s="596" t="n"/>
+      <c r="Q20" s="596" t="n"/>
+      <c r="R20" s="596" t="n"/>
+      <c r="S20" s="596" t="n"/>
+      <c r="T20" s="596" t="n"/>
+      <c r="U20" s="596" t="n"/>
+      <c r="V20" s="596" t="n"/>
+      <c r="W20" s="596" t="n"/>
+      <c r="X20" s="596" t="n"/>
+      <c r="Y20" s="596" t="n"/>
+      <c r="Z20" s="596" t="n"/>
+      <c r="AA20" s="596" t="n"/>
+      <c r="AB20" s="596" t="n"/>
+      <c r="AC20" s="596" t="n"/>
+      <c r="AD20" s="596" t="n"/>
+      <c r="AE20" s="596" t="n"/>
+      <c r="AF20" s="596" t="n"/>
+      <c r="AG20" s="596" t="n"/>
+      <c r="AH20" s="596" t="n"/>
+      <c r="AI20" s="596" t="n"/>
+      <c r="AJ20" s="596" t="n"/>
+      <c r="AK20" s="596" t="n"/>
+      <c r="AL20" s="596" t="n"/>
+      <c r="AM20" s="596" t="n"/>
+      <c r="AN20" s="596" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="329"/>
-    <row r="16" ht="20" customHeight="1" s="329"/>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
+    <row r="21" ht="20" customHeight="1" s="329">
+      <c r="A21" s="596" t="n"/>
+      <c r="B21" s="596" t="n"/>
+      <c r="C21" s="596" t="n"/>
+      <c r="D21" s="596" t="n"/>
+      <c r="E21" s="596" t="n"/>
+      <c r="F21" s="596" t="n"/>
+      <c r="G21" s="596" t="n"/>
+      <c r="H21" s="596" t="n"/>
+      <c r="I21" s="596" t="n"/>
+      <c r="J21" s="596" t="n"/>
+      <c r="K21" s="596" t="n"/>
+      <c r="L21" s="596" t="n"/>
+      <c r="M21" s="596" t="n"/>
+      <c r="N21" s="596" t="n"/>
+      <c r="O21" s="596" t="n"/>
+      <c r="P21" s="596" t="n"/>
+      <c r="Q21" s="596" t="n"/>
+      <c r="R21" s="596" t="n"/>
+      <c r="S21" s="596" t="n"/>
+      <c r="T21" s="596" t="n"/>
+      <c r="U21" s="596" t="n"/>
+      <c r="V21" s="596" t="n"/>
+      <c r="W21" s="596" t="n"/>
+      <c r="X21" s="596" t="n"/>
+      <c r="Y21" s="596" t="n"/>
+      <c r="Z21" s="596" t="n"/>
+      <c r="AA21" s="596" t="n"/>
+      <c r="AB21" s="596" t="n"/>
+      <c r="AC21" s="596" t="n"/>
+      <c r="AD21" s="596" t="n"/>
+      <c r="AE21" s="596" t="n"/>
+      <c r="AF21" s="596" t="n"/>
+      <c r="AG21" s="596" t="n"/>
+      <c r="AH21" s="596" t="n"/>
+      <c r="AI21" s="596" t="n"/>
+      <c r="AJ21" s="596" t="n"/>
+      <c r="AK21" s="596" t="n"/>
+      <c r="AL21" s="596" t="n"/>
+      <c r="AM21" s="596" t="n"/>
+      <c r="AN21" s="596" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="329">
+      <c r="A22" s="596" t="n"/>
+      <c r="B22" s="596" t="n"/>
+      <c r="C22" s="596" t="n"/>
+      <c r="D22" s="596" t="n"/>
+      <c r="E22" s="596" t="n"/>
+      <c r="F22" s="596" t="n"/>
+      <c r="G22" s="596" t="n"/>
+      <c r="H22" s="596" t="n"/>
+      <c r="I22" s="596" t="n"/>
+      <c r="J22" s="596" t="n"/>
+      <c r="K22" s="596" t="n"/>
+      <c r="L22" s="596" t="n"/>
+      <c r="M22" s="596" t="n"/>
+      <c r="N22" s="596" t="n"/>
+      <c r="O22" s="596" t="n"/>
+      <c r="P22" s="596" t="n"/>
+      <c r="Q22" s="596" t="n"/>
+      <c r="R22" s="596" t="n"/>
+      <c r="S22" s="596" t="n"/>
+      <c r="T22" s="596" t="n"/>
+      <c r="U22" s="596" t="n"/>
+      <c r="V22" s="596" t="n"/>
+      <c r="W22" s="596" t="n"/>
+      <c r="X22" s="596" t="n"/>
+      <c r="Y22" s="596" t="n"/>
+      <c r="Z22" s="596" t="n"/>
+      <c r="AA22" s="596" t="n"/>
+      <c r="AB22" s="596" t="n"/>
+      <c r="AC22" s="596" t="n"/>
+      <c r="AD22" s="596" t="n"/>
+      <c r="AE22" s="596" t="n"/>
+      <c r="AF22" s="596" t="n"/>
+      <c r="AG22" s="596" t="n"/>
+      <c r="AH22" s="596" t="n"/>
+      <c r="AI22" s="596" t="n"/>
+      <c r="AJ22" s="596" t="n"/>
+      <c r="AK22" s="596" t="n"/>
+      <c r="AL22" s="596" t="n"/>
+      <c r="AM22" s="596" t="n"/>
+      <c r="AN22" s="596" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="329">
+      <c r="A23" s="596" t="n"/>
+      <c r="B23" s="596" t="n"/>
+      <c r="C23" s="596" t="n"/>
+      <c r="D23" s="596" t="n"/>
+      <c r="E23" s="596" t="n"/>
+      <c r="F23" s="596" t="n"/>
+      <c r="G23" s="596" t="n"/>
+      <c r="H23" s="596" t="n"/>
+      <c r="I23" s="596" t="n"/>
+      <c r="J23" s="596" t="n"/>
+      <c r="K23" s="596" t="n"/>
+      <c r="L23" s="596" t="n"/>
+      <c r="M23" s="596" t="n"/>
+      <c r="N23" s="596" t="n"/>
+      <c r="O23" s="596" t="n"/>
+      <c r="P23" s="596" t="n"/>
+      <c r="Q23" s="596" t="n"/>
+      <c r="R23" s="596" t="n"/>
+      <c r="S23" s="596" t="n"/>
+      <c r="T23" s="596" t="n"/>
+      <c r="U23" s="596" t="n"/>
+      <c r="V23" s="596" t="n"/>
+      <c r="W23" s="596" t="n"/>
+      <c r="X23" s="596" t="n"/>
+      <c r="Y23" s="596" t="n"/>
+      <c r="Z23" s="596" t="n"/>
+      <c r="AA23" s="596" t="n"/>
+      <c r="AB23" s="596" t="n"/>
+      <c r="AC23" s="596" t="n"/>
+      <c r="AD23" s="596" t="n"/>
+      <c r="AE23" s="596" t="n"/>
+      <c r="AF23" s="596" t="n"/>
+      <c r="AG23" s="596" t="n"/>
+      <c r="AH23" s="596" t="n"/>
+      <c r="AI23" s="596" t="n"/>
+      <c r="AJ23" s="596" t="n"/>
+      <c r="AK23" s="596" t="n"/>
+      <c r="AL23" s="596" t="n"/>
+      <c r="AM23" s="596" t="n"/>
+      <c r="AN23" s="596" t="n"/>
+    </row>
     <row r="24" ht="20" customHeight="1" s="329"/>
     <row r="25" ht="20" customHeight="1" s="329"/>
     <row r="26" ht="20" customHeight="1" s="329"/>
@@ -9713,6 +10739,22 @@
     <row r="39" ht="20" customHeight="1" s="329"/>
     <row r="40" ht="20" customHeight="1" s="329"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LISTS!$E$2:$E$7</formula1>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="89">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -516,6 +516,11 @@
     <font>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001B3A6B"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="53">
     <fill>
@@ -780,7 +785,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="363">
+  <borders count="383">
     <border>
       <left/>
       <right/>
@@ -4703,12 +4708,253 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="597">
+  <cellXfs count="692">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6042,6 +6288,239 @@
     </xf>
     <xf numFmtId="0" fontId="88" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6126,7 +6605,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6140,9 +6619,66 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -6348,49 +6884,49 @@
   <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="40" max="40"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
+    <row r="1" hidden="1" s="329">
       <c r="A1" s="528" t="n"/>
       <c r="B1" s="529" t="n"/>
       <c r="C1" s="529" t="n"/>
@@ -6441,506 +6977,580 @@
       <c r="AN1" s="530" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="535" t="n"/>
-      <c r="H2" s="536" t="n"/>
-      <c r="I2" s="535" t="n"/>
-      <c r="AD2" s="536" t="n"/>
-      <c r="AE2" s="537" t="n"/>
-      <c r="AF2" s="410" t="n"/>
-      <c r="AG2" s="410" t="n"/>
-      <c r="AH2" s="538" t="n"/>
-      <c r="AI2" s="539" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="597" t="n"/>
+      <c r="C2" s="597" t="n"/>
+      <c r="D2" s="597" t="n"/>
+      <c r="E2" s="597" t="n"/>
+      <c r="F2" s="597" t="n"/>
+      <c r="G2" s="597" t="n"/>
+      <c r="H2" s="598" t="n"/>
+      <c r="I2" s="597" t="n"/>
+      <c r="J2" s="597" t="n"/>
+      <c r="K2" s="597" t="n"/>
+      <c r="L2" s="597" t="n"/>
+      <c r="M2" s="597" t="n"/>
+      <c r="N2" s="597" t="n"/>
+      <c r="O2" s="597" t="n"/>
+      <c r="P2" s="597" t="n"/>
+      <c r="Q2" s="597" t="n"/>
+      <c r="R2" s="597" t="n"/>
+      <c r="S2" s="597" t="n"/>
+      <c r="T2" s="597" t="n"/>
+      <c r="U2" s="597" t="n"/>
+      <c r="V2" s="597" t="n"/>
+      <c r="W2" s="597" t="n"/>
+      <c r="X2" s="597" t="n"/>
+      <c r="Y2" s="597" t="n"/>
+      <c r="Z2" s="597" t="n"/>
+      <c r="AA2" s="597" t="n"/>
+      <c r="AB2" s="597" t="n"/>
+      <c r="AC2" s="597" t="n"/>
+      <c r="AD2" s="598" t="n"/>
+      <c r="AE2" s="599" t="n"/>
+      <c r="AF2" s="600" t="n"/>
+      <c r="AG2" s="600" t="n"/>
+      <c r="AH2" s="601" t="n"/>
+      <c r="AI2" s="602" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="410" t="n"/>
-      <c r="AK2" s="410" t="n"/>
-      <c r="AL2" s="410" t="n"/>
-      <c r="AM2" s="410" t="n"/>
-      <c r="AN2" s="540" t="n"/>
+      <c r="AJ2" s="603" t="n"/>
+      <c r="AK2" s="603" t="n"/>
+      <c r="AL2" s="603" t="n"/>
+      <c r="AM2" s="603" t="n"/>
+      <c r="AN2" s="604" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="535" t="n"/>
-      <c r="H3" s="536" t="n"/>
-      <c r="I3" s="535" t="n"/>
-      <c r="AD3" s="536" t="n"/>
-      <c r="AE3" s="537" t="n"/>
-      <c r="AF3" s="410" t="n"/>
-      <c r="AG3" s="410" t="n"/>
-      <c r="AH3" s="538" t="n"/>
-      <c r="AI3" s="539" t="inlineStr">
+      <c r="A3" s="605" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="606" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="606" t="n"/>
+      <c r="AE3" s="607" t="n"/>
+      <c r="AF3" s="608" t="n"/>
+      <c r="AG3" s="608" t="n"/>
+      <c r="AH3" s="609" t="n"/>
+      <c r="AI3" s="610" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="410" t="n"/>
-      <c r="AK3" s="410" t="n"/>
-      <c r="AL3" s="410" t="n"/>
-      <c r="AM3" s="410" t="n"/>
-      <c r="AN3" s="540" t="n"/>
+      <c r="AJ3" s="611" t="n"/>
+      <c r="AK3" s="611" t="n"/>
+      <c r="AL3" s="611" t="n"/>
+      <c r="AM3" s="611" t="n"/>
+      <c r="AN3" s="612" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="535" t="n"/>
-      <c r="H4" s="536" t="n"/>
-      <c r="I4" s="541" t="inlineStr">
+      <c r="A4" s="605" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="606" t="n"/>
+      <c r="I4" s="613" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AD4" s="536" t="n"/>
-      <c r="AE4" s="537" t="n"/>
-      <c r="AF4" s="410" t="n"/>
-      <c r="AG4" s="410" t="n"/>
-      <c r="AH4" s="538" t="n"/>
-      <c r="AI4" s="539" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="606" t="n"/>
+      <c r="AE4" s="607" t="n"/>
+      <c r="AF4" s="608" t="n"/>
+      <c r="AG4" s="608" t="n"/>
+      <c r="AH4" s="609" t="n"/>
+      <c r="AI4" s="610" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="410" t="n"/>
-      <c r="AK4" s="410" t="n"/>
-      <c r="AL4" s="410" t="n"/>
-      <c r="AM4" s="410" t="n"/>
-      <c r="AN4" s="540" t="n"/>
+      <c r="AJ4" s="611" t="n"/>
+      <c r="AK4" s="611" t="n"/>
+      <c r="AL4" s="611" t="n"/>
+      <c r="AM4" s="611" t="n"/>
+      <c r="AN4" s="612" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="542" t="n"/>
-      <c r="B5" s="543" t="n"/>
-      <c r="C5" s="543" t="n"/>
-      <c r="D5" s="543" t="n"/>
-      <c r="E5" s="543" t="n"/>
-      <c r="F5" s="543" t="n"/>
-      <c r="G5" s="543" t="n"/>
-      <c r="H5" s="544" t="n"/>
-      <c r="I5" s="545" t="inlineStr">
+      <c r="A5" s="605" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="606" t="n"/>
+      <c r="I5" s="614" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="543" t="n"/>
-      <c r="K5" s="543" t="n"/>
-      <c r="L5" s="543" t="n"/>
-      <c r="M5" s="543" t="n"/>
-      <c r="N5" s="543" t="n"/>
-      <c r="O5" s="543" t="n"/>
-      <c r="P5" s="543" t="n"/>
-      <c r="Q5" s="543" t="n"/>
-      <c r="R5" s="543" t="n"/>
-      <c r="S5" s="543" t="n"/>
-      <c r="T5" s="543" t="n"/>
-      <c r="U5" s="543" t="n"/>
-      <c r="V5" s="543" t="n"/>
-      <c r="W5" s="543" t="n"/>
-      <c r="X5" s="543" t="n"/>
-      <c r="Y5" s="543" t="n"/>
-      <c r="Z5" s="543" t="n"/>
-      <c r="AA5" s="543" t="n"/>
-      <c r="AB5" s="543" t="n"/>
-      <c r="AC5" s="543" t="n"/>
-      <c r="AD5" s="544" t="n"/>
-      <c r="AE5" s="546" t="n"/>
-      <c r="AF5" s="547" t="n"/>
-      <c r="AG5" s="547" t="n"/>
-      <c r="AH5" s="548" t="n"/>
-      <c r="AI5" s="549" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="606" t="n"/>
+      <c r="AE5" s="607" t="n"/>
+      <c r="AF5" s="608" t="n"/>
+      <c r="AG5" s="608" t="n"/>
+      <c r="AH5" s="609" t="n"/>
+      <c r="AI5" s="610" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="547" t="n"/>
-      <c r="AK5" s="547" t="n"/>
-      <c r="AL5" s="547" t="n"/>
-      <c r="AM5" s="547" t="n"/>
-      <c r="AN5" s="550" t="n"/>
+      <c r="AJ5" s="611" t="n"/>
+      <c r="AK5" s="611" t="n"/>
+      <c r="AL5" s="611" t="n"/>
+      <c r="AM5" s="611" t="n"/>
+      <c r="AN5" s="612" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="454" t="n"/>
-      <c r="B6" s="454" t="n"/>
-      <c r="C6" s="454" t="n"/>
-      <c r="D6" s="454" t="n"/>
-      <c r="E6" s="454" t="n"/>
-      <c r="F6" s="454" t="n"/>
-      <c r="G6" s="454" t="n"/>
-      <c r="H6" s="454" t="n"/>
-      <c r="I6" s="454" t="n"/>
-      <c r="J6" s="454" t="n"/>
-      <c r="K6" s="454" t="n"/>
-      <c r="L6" s="454" t="n"/>
-      <c r="M6" s="454" t="n"/>
-      <c r="N6" s="454" t="n"/>
-      <c r="O6" s="454" t="n"/>
-      <c r="P6" s="454" t="n"/>
-      <c r="Q6" s="454" t="n"/>
-      <c r="R6" s="454" t="n"/>
-      <c r="S6" s="454" t="n"/>
-      <c r="T6" s="454" t="n"/>
-      <c r="U6" s="454" t="n"/>
-      <c r="V6" s="454" t="n"/>
-      <c r="W6" s="454" t="n"/>
-      <c r="X6" s="454" t="n"/>
-      <c r="Y6" s="454" t="n"/>
-      <c r="Z6" s="454" t="n"/>
-      <c r="AA6" s="454" t="n"/>
-      <c r="AB6" s="454" t="n"/>
-      <c r="AC6" s="454" t="n"/>
-      <c r="AD6" s="454" t="n"/>
-      <c r="AE6" s="454" t="n"/>
-      <c r="AF6" s="454" t="n"/>
-      <c r="AG6" s="454" t="n"/>
-      <c r="AH6" s="454" t="n"/>
-      <c r="AI6" s="454" t="n"/>
-      <c r="AJ6" s="454" t="n"/>
-      <c r="AK6" s="454" t="n"/>
-      <c r="AL6" s="454" t="n"/>
-      <c r="AM6" s="454" t="n"/>
-      <c r="AN6" s="454" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="615" t="n"/>
+      <c r="B6" s="616" t="n"/>
+      <c r="C6" s="616" t="n"/>
+      <c r="D6" s="616" t="n"/>
+      <c r="E6" s="616" t="n"/>
+      <c r="F6" s="616" t="n"/>
+      <c r="G6" s="616" t="n"/>
+      <c r="H6" s="617" t="n"/>
+      <c r="I6" s="616" t="n"/>
+      <c r="J6" s="616" t="n"/>
+      <c r="K6" s="616" t="n"/>
+      <c r="L6" s="616" t="n"/>
+      <c r="M6" s="616" t="n"/>
+      <c r="N6" s="616" t="n"/>
+      <c r="O6" s="616" t="n"/>
+      <c r="P6" s="616" t="n"/>
+      <c r="Q6" s="616" t="n"/>
+      <c r="R6" s="616" t="n"/>
+      <c r="S6" s="616" t="n"/>
+      <c r="T6" s="616" t="n"/>
+      <c r="U6" s="616" t="n"/>
+      <c r="V6" s="616" t="n"/>
+      <c r="W6" s="616" t="n"/>
+      <c r="X6" s="616" t="n"/>
+      <c r="Y6" s="616" t="n"/>
+      <c r="Z6" s="616" t="n"/>
+      <c r="AA6" s="616" t="n"/>
+      <c r="AB6" s="616" t="n"/>
+      <c r="AC6" s="616" t="n"/>
+      <c r="AD6" s="617" t="n"/>
+      <c r="AE6" s="618" t="n"/>
+      <c r="AF6" s="618" t="n"/>
+      <c r="AG6" s="618" t="n"/>
+      <c r="AH6" s="619" t="n"/>
+      <c r="AI6" s="620" t="n"/>
+      <c r="AJ6" s="620" t="n"/>
+      <c r="AK6" s="620" t="n"/>
+      <c r="AL6" s="620" t="n"/>
+      <c r="AM6" s="620" t="n"/>
+      <c r="AN6" s="621" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="329">
-      <c r="A7" s="551" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="552" t="n"/>
-      <c r="C7" s="552" t="n"/>
-      <c r="D7" s="552" t="n"/>
-      <c r="E7" s="552" t="n"/>
-      <c r="F7" s="552" t="n"/>
-      <c r="G7" s="552" t="n"/>
-      <c r="H7" s="552" t="n"/>
-      <c r="I7" s="552" t="n"/>
-      <c r="J7" s="552" t="n"/>
-      <c r="K7" s="552" t="n"/>
-      <c r="L7" s="552" t="n"/>
-      <c r="M7" s="552" t="n"/>
-      <c r="N7" s="552" t="n"/>
-      <c r="O7" s="552" t="n"/>
-      <c r="P7" s="552" t="n"/>
-      <c r="Q7" s="552" t="n"/>
-      <c r="R7" s="552" t="n"/>
-      <c r="S7" s="552" t="n"/>
-      <c r="T7" s="552" t="n"/>
-      <c r="U7" s="552" t="n"/>
-      <c r="V7" s="552" t="n"/>
-      <c r="W7" s="552" t="n"/>
-      <c r="X7" s="552" t="n"/>
-      <c r="Y7" s="552" t="n"/>
-      <c r="Z7" s="552" t="n"/>
-      <c r="AA7" s="552" t="n"/>
-      <c r="AB7" s="552" t="n"/>
-      <c r="AC7" s="552" t="n"/>
-      <c r="AD7" s="552" t="n"/>
-      <c r="AE7" s="552" t="n"/>
-      <c r="AF7" s="552" t="n"/>
-      <c r="AG7" s="552" t="n"/>
-      <c r="AH7" s="552" t="n"/>
-      <c r="AI7" s="552" t="n"/>
-      <c r="AJ7" s="552" t="n"/>
-      <c r="AK7" s="552" t="n"/>
-      <c r="AL7" s="552" t="n"/>
-      <c r="AM7" s="552" t="n"/>
-      <c r="AN7" s="553" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="622" t="n"/>
+      <c r="B7" s="623" t="n"/>
+      <c r="C7" s="623" t="n"/>
+      <c r="D7" s="623" t="n"/>
+      <c r="E7" s="623" t="n"/>
+      <c r="F7" s="623" t="n"/>
+      <c r="G7" s="623" t="n"/>
+      <c r="H7" s="623" t="n"/>
+      <c r="I7" s="623" t="n"/>
+      <c r="J7" s="623" t="n"/>
+      <c r="K7" s="623" t="n"/>
+      <c r="L7" s="623" t="n"/>
+      <c r="M7" s="623" t="n"/>
+      <c r="N7" s="623" t="n"/>
+      <c r="O7" s="623" t="n"/>
+      <c r="P7" s="623" t="n"/>
+      <c r="Q7" s="623" t="n"/>
+      <c r="R7" s="623" t="n"/>
+      <c r="S7" s="623" t="n"/>
+      <c r="T7" s="623" t="n"/>
+      <c r="U7" s="623" t="n"/>
+      <c r="V7" s="623" t="n"/>
+      <c r="W7" s="623" t="n"/>
+      <c r="X7" s="623" t="n"/>
+      <c r="Y7" s="623" t="n"/>
+      <c r="Z7" s="623" t="n"/>
+      <c r="AA7" s="623" t="n"/>
+      <c r="AB7" s="623" t="n"/>
+      <c r="AC7" s="623" t="n"/>
+      <c r="AD7" s="623" t="n"/>
+      <c r="AE7" s="623" t="n"/>
+      <c r="AF7" s="623" t="n"/>
+      <c r="AG7" s="623" t="n"/>
+      <c r="AH7" s="623" t="n"/>
+      <c r="AI7" s="623" t="n"/>
+      <c r="AJ7" s="623" t="n"/>
+      <c r="AK7" s="623" t="n"/>
+      <c r="AL7" s="623" t="n"/>
+      <c r="AM7" s="623" t="n"/>
+      <c r="AN7" s="623" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="458" t="inlineStr">
+      <c r="A8" s="624" t="inlineStr">
         <is>
           <t>Outsource Dispatch ID</t>
         </is>
       </c>
-      <c r="B8" s="554" t="n"/>
-      <c r="C8" s="554" t="n"/>
-      <c r="D8" s="554" t="n"/>
-      <c r="E8" s="554" t="n"/>
-      <c r="F8" s="554" t="n"/>
-      <c r="G8" s="554" t="n"/>
-      <c r="H8" s="460" t="n"/>
-      <c r="I8" s="554" t="n"/>
-      <c r="J8" s="554" t="n"/>
-      <c r="K8" s="554" t="n"/>
-      <c r="L8" s="554" t="n"/>
-      <c r="M8" s="554" t="n"/>
-      <c r="N8" s="554" t="n"/>
-      <c r="O8" s="554" t="n"/>
-      <c r="P8" s="554" t="n"/>
-      <c r="Q8" s="554" t="n"/>
-      <c r="R8" s="554" t="n"/>
-      <c r="S8" s="554" t="n"/>
-      <c r="T8" s="554" t="n"/>
-      <c r="U8" s="461" t="inlineStr">
+      <c r="B8" s="317" t="n"/>
+      <c r="C8" s="317" t="n"/>
+      <c r="D8" s="317" t="n"/>
+      <c r="E8" s="317" t="n"/>
+      <c r="F8" s="317" t="n"/>
+      <c r="G8" s="317" t="n"/>
+      <c r="H8" s="625" t="n"/>
+      <c r="I8" s="317" t="n"/>
+      <c r="J8" s="317" t="n"/>
+      <c r="K8" s="317" t="n"/>
+      <c r="L8" s="317" t="n"/>
+      <c r="M8" s="317" t="n"/>
+      <c r="N8" s="317" t="n"/>
+      <c r="O8" s="317" t="n"/>
+      <c r="P8" s="317" t="n"/>
+      <c r="Q8" s="317" t="n"/>
+      <c r="R8" s="317" t="n"/>
+      <c r="S8" s="317" t="n"/>
+      <c r="T8" s="317" t="n"/>
+      <c r="U8" s="626" t="inlineStr">
         <is>
           <t>Dispatch Gate Status</t>
         </is>
       </c>
-      <c r="V8" s="554" t="n"/>
-      <c r="W8" s="554" t="n"/>
-      <c r="X8" s="554" t="n"/>
-      <c r="Y8" s="554" t="n"/>
-      <c r="Z8" s="554" t="n"/>
-      <c r="AA8" s="554" t="n"/>
-      <c r="AB8" s="555" t="n"/>
-      <c r="AC8" s="554" t="n"/>
-      <c r="AD8" s="554" t="n"/>
-      <c r="AE8" s="554" t="n"/>
-      <c r="AF8" s="554" t="n"/>
-      <c r="AG8" s="554" t="n"/>
-      <c r="AH8" s="554" t="n"/>
-      <c r="AI8" s="554" t="n"/>
-      <c r="AJ8" s="554" t="n"/>
-      <c r="AK8" s="554" t="n"/>
-      <c r="AL8" s="554" t="n"/>
-      <c r="AM8" s="554" t="n"/>
-      <c r="AN8" s="556" t="n"/>
+      <c r="V8" s="317" t="n"/>
+      <c r="W8" s="317" t="n"/>
+      <c r="X8" s="317" t="n"/>
+      <c r="Y8" s="317" t="n"/>
+      <c r="Z8" s="317" t="n"/>
+      <c r="AA8" s="317" t="n"/>
+      <c r="AB8" s="627" t="n"/>
+      <c r="AC8" s="317" t="n"/>
+      <c r="AD8" s="317" t="n"/>
+      <c r="AE8" s="317" t="n"/>
+      <c r="AF8" s="317" t="n"/>
+      <c r="AG8" s="317" t="n"/>
+      <c r="AH8" s="317" t="n"/>
+      <c r="AI8" s="317" t="n"/>
+      <c r="AJ8" s="317" t="n"/>
+      <c r="AK8" s="317" t="n"/>
+      <c r="AL8" s="317" t="n"/>
+      <c r="AM8" s="317" t="n"/>
+      <c r="AN8" s="319" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="463" t="inlineStr">
+      <c r="A9" s="628" t="inlineStr">
         <is>
           <t>Supplier / Processor</t>
         </is>
       </c>
-      <c r="B9" s="411" t="n"/>
-      <c r="C9" s="411" t="n"/>
-      <c r="D9" s="411" t="n"/>
-      <c r="E9" s="411" t="n"/>
-      <c r="F9" s="411" t="n"/>
-      <c r="G9" s="411" t="n"/>
-      <c r="H9" s="464" t="n"/>
-      <c r="I9" s="411" t="n"/>
-      <c r="J9" s="411" t="n"/>
-      <c r="K9" s="411" t="n"/>
-      <c r="L9" s="411" t="n"/>
-      <c r="M9" s="411" t="n"/>
-      <c r="N9" s="411" t="n"/>
-      <c r="O9" s="411" t="n"/>
-      <c r="P9" s="411" t="n"/>
-      <c r="Q9" s="411" t="n"/>
-      <c r="R9" s="411" t="n"/>
-      <c r="S9" s="411" t="n"/>
-      <c r="T9" s="411" t="n"/>
-      <c r="U9" s="465" t="inlineStr">
+      <c r="B9" s="684" t="n"/>
+      <c r="C9" s="684" t="n"/>
+      <c r="D9" s="684" t="n"/>
+      <c r="E9" s="684" t="n"/>
+      <c r="F9" s="684" t="n"/>
+      <c r="G9" s="684" t="n"/>
+      <c r="H9" s="629" t="n"/>
+      <c r="I9" s="684" t="n"/>
+      <c r="J9" s="684" t="n"/>
+      <c r="K9" s="684" t="n"/>
+      <c r="L9" s="684" t="n"/>
+      <c r="M9" s="684" t="n"/>
+      <c r="N9" s="684" t="n"/>
+      <c r="O9" s="684" t="n"/>
+      <c r="P9" s="684" t="n"/>
+      <c r="Q9" s="684" t="n"/>
+      <c r="R9" s="684" t="n"/>
+      <c r="S9" s="684" t="n"/>
+      <c r="T9" s="684" t="n"/>
+      <c r="U9" s="630" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="V9" s="411" t="n"/>
-      <c r="W9" s="411" t="n"/>
-      <c r="X9" s="411" t="n"/>
-      <c r="Y9" s="411" t="n"/>
-      <c r="Z9" s="411" t="n"/>
-      <c r="AA9" s="411" t="n"/>
-      <c r="AB9" s="557" t="n"/>
-      <c r="AC9" s="411" t="n"/>
-      <c r="AD9" s="411" t="n"/>
-      <c r="AE9" s="411" t="n"/>
-      <c r="AF9" s="411" t="n"/>
-      <c r="AG9" s="411" t="n"/>
-      <c r="AH9" s="411" t="n"/>
-      <c r="AI9" s="411" t="n"/>
-      <c r="AJ9" s="411" t="n"/>
-      <c r="AK9" s="411" t="n"/>
-      <c r="AL9" s="411" t="n"/>
-      <c r="AM9" s="411" t="n"/>
-      <c r="AN9" s="558" t="n"/>
+      <c r="V9" s="684" t="n"/>
+      <c r="W9" s="684" t="n"/>
+      <c r="X9" s="684" t="n"/>
+      <c r="Y9" s="684" t="n"/>
+      <c r="Z9" s="684" t="n"/>
+      <c r="AA9" s="684" t="n"/>
+      <c r="AB9" s="631" t="n"/>
+      <c r="AC9" s="684" t="n"/>
+      <c r="AD9" s="684" t="n"/>
+      <c r="AE9" s="684" t="n"/>
+      <c r="AF9" s="684" t="n"/>
+      <c r="AG9" s="684" t="n"/>
+      <c r="AH9" s="684" t="n"/>
+      <c r="AI9" s="684" t="n"/>
+      <c r="AJ9" s="684" t="n"/>
+      <c r="AK9" s="684" t="n"/>
+      <c r="AL9" s="684" t="n"/>
+      <c r="AM9" s="684" t="n"/>
+      <c r="AN9" s="685" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="463" t="inlineStr">
+      <c r="A10" s="628" t="inlineStr">
         <is>
           <t>PO / Work Order</t>
         </is>
       </c>
-      <c r="B10" s="411" t="n"/>
-      <c r="C10" s="411" t="n"/>
-      <c r="D10" s="411" t="n"/>
-      <c r="E10" s="411" t="n"/>
-      <c r="F10" s="411" t="n"/>
-      <c r="G10" s="411" t="n"/>
-      <c r="H10" s="464" t="n"/>
-      <c r="I10" s="411" t="n"/>
-      <c r="J10" s="411" t="n"/>
-      <c r="K10" s="411" t="n"/>
-      <c r="L10" s="411" t="n"/>
-      <c r="M10" s="411" t="n"/>
-      <c r="N10" s="411" t="n"/>
-      <c r="O10" s="411" t="n"/>
-      <c r="P10" s="411" t="n"/>
-      <c r="Q10" s="411" t="n"/>
-      <c r="R10" s="411" t="n"/>
-      <c r="S10" s="411" t="n"/>
-      <c r="T10" s="411" t="n"/>
-      <c r="U10" s="465" t="inlineStr">
+      <c r="B10" s="684" t="n"/>
+      <c r="C10" s="684" t="n"/>
+      <c r="D10" s="684" t="n"/>
+      <c r="E10" s="684" t="n"/>
+      <c r="F10" s="684" t="n"/>
+      <c r="G10" s="684" t="n"/>
+      <c r="H10" s="629" t="n"/>
+      <c r="I10" s="684" t="n"/>
+      <c r="J10" s="684" t="n"/>
+      <c r="K10" s="684" t="n"/>
+      <c r="L10" s="684" t="n"/>
+      <c r="M10" s="684" t="n"/>
+      <c r="N10" s="684" t="n"/>
+      <c r="O10" s="684" t="n"/>
+      <c r="P10" s="684" t="n"/>
+      <c r="Q10" s="684" t="n"/>
+      <c r="R10" s="684" t="n"/>
+      <c r="S10" s="684" t="n"/>
+      <c r="T10" s="684" t="n"/>
+      <c r="U10" s="630" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="411" t="n"/>
-      <c r="W10" s="411" t="n"/>
-      <c r="X10" s="411" t="n"/>
-      <c r="Y10" s="411" t="n"/>
-      <c r="Z10" s="411" t="n"/>
-      <c r="AA10" s="411" t="n"/>
-      <c r="AB10" s="557" t="n"/>
-      <c r="AC10" s="411" t="n"/>
-      <c r="AD10" s="411" t="n"/>
-      <c r="AE10" s="411" t="n"/>
-      <c r="AF10" s="411" t="n"/>
-      <c r="AG10" s="411" t="n"/>
-      <c r="AH10" s="411" t="n"/>
-      <c r="AI10" s="411" t="n"/>
-      <c r="AJ10" s="411" t="n"/>
-      <c r="AK10" s="411" t="n"/>
-      <c r="AL10" s="411" t="n"/>
-      <c r="AM10" s="411" t="n"/>
-      <c r="AN10" s="558" t="n"/>
+      <c r="V10" s="684" t="n"/>
+      <c r="W10" s="684" t="n"/>
+      <c r="X10" s="684" t="n"/>
+      <c r="Y10" s="684" t="n"/>
+      <c r="Z10" s="684" t="n"/>
+      <c r="AA10" s="684" t="n"/>
+      <c r="AB10" s="631" t="n"/>
+      <c r="AC10" s="684" t="n"/>
+      <c r="AD10" s="684" t="n"/>
+      <c r="AE10" s="684" t="n"/>
+      <c r="AF10" s="684" t="n"/>
+      <c r="AG10" s="684" t="n"/>
+      <c r="AH10" s="684" t="n"/>
+      <c r="AI10" s="684" t="n"/>
+      <c r="AJ10" s="684" t="n"/>
+      <c r="AK10" s="684" t="n"/>
+      <c r="AL10" s="684" t="n"/>
+      <c r="AM10" s="684" t="n"/>
+      <c r="AN10" s="685" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1" s="329">
-      <c r="A11" s="463" t="inlineStr">
+      <c r="A11" s="628" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="411" t="n"/>
-      <c r="C11" s="411" t="n"/>
-      <c r="D11" s="411" t="n"/>
-      <c r="E11" s="411" t="n"/>
-      <c r="F11" s="411" t="n"/>
-      <c r="G11" s="411" t="n"/>
-      <c r="H11" s="464" t="n"/>
-      <c r="I11" s="411" t="n"/>
-      <c r="J11" s="411" t="n"/>
-      <c r="K11" s="411" t="n"/>
-      <c r="L11" s="411" t="n"/>
-      <c r="M11" s="411" t="n"/>
-      <c r="N11" s="411" t="n"/>
-      <c r="O11" s="411" t="n"/>
-      <c r="P11" s="411" t="n"/>
-      <c r="Q11" s="411" t="n"/>
-      <c r="R11" s="411" t="n"/>
-      <c r="S11" s="411" t="n"/>
-      <c r="T11" s="411" t="n"/>
-      <c r="U11" s="465" t="inlineStr">
+      <c r="B11" s="684" t="n"/>
+      <c r="C11" s="684" t="n"/>
+      <c r="D11" s="684" t="n"/>
+      <c r="E11" s="684" t="n"/>
+      <c r="F11" s="684" t="n"/>
+      <c r="G11" s="684" t="n"/>
+      <c r="H11" s="629" t="n"/>
+      <c r="I11" s="684" t="n"/>
+      <c r="J11" s="684" t="n"/>
+      <c r="K11" s="684" t="n"/>
+      <c r="L11" s="684" t="n"/>
+      <c r="M11" s="684" t="n"/>
+      <c r="N11" s="684" t="n"/>
+      <c r="O11" s="684" t="n"/>
+      <c r="P11" s="684" t="n"/>
+      <c r="Q11" s="684" t="n"/>
+      <c r="R11" s="684" t="n"/>
+      <c r="S11" s="684" t="n"/>
+      <c r="T11" s="684" t="n"/>
+      <c r="U11" s="630" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="411" t="n"/>
-      <c r="W11" s="411" t="n"/>
-      <c r="X11" s="411" t="n"/>
-      <c r="Y11" s="411" t="n"/>
-      <c r="Z11" s="411" t="n"/>
-      <c r="AA11" s="411" t="n"/>
-      <c r="AB11" s="557" t="n"/>
-      <c r="AC11" s="411" t="n"/>
-      <c r="AD11" s="411" t="n"/>
-      <c r="AE11" s="411" t="n"/>
-      <c r="AF11" s="411" t="n"/>
-      <c r="AG11" s="411" t="n"/>
-      <c r="AH11" s="411" t="n"/>
-      <c r="AI11" s="411" t="n"/>
-      <c r="AJ11" s="411" t="n"/>
-      <c r="AK11" s="411" t="n"/>
-      <c r="AL11" s="411" t="n"/>
-      <c r="AM11" s="411" t="n"/>
-      <c r="AN11" s="558" t="n"/>
+      <c r="V11" s="684" t="n"/>
+      <c r="W11" s="684" t="n"/>
+      <c r="X11" s="684" t="n"/>
+      <c r="Y11" s="684" t="n"/>
+      <c r="Z11" s="684" t="n"/>
+      <c r="AA11" s="684" t="n"/>
+      <c r="AB11" s="631" t="n"/>
+      <c r="AC11" s="684" t="n"/>
+      <c r="AD11" s="684" t="n"/>
+      <c r="AE11" s="684" t="n"/>
+      <c r="AF11" s="684" t="n"/>
+      <c r="AG11" s="684" t="n"/>
+      <c r="AH11" s="684" t="n"/>
+      <c r="AI11" s="684" t="n"/>
+      <c r="AJ11" s="684" t="n"/>
+      <c r="AK11" s="684" t="n"/>
+      <c r="AL11" s="684" t="n"/>
+      <c r="AM11" s="684" t="n"/>
+      <c r="AN11" s="685" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="463" t="inlineStr">
+      <c r="A12" s="628" t="inlineStr">
         <is>
           <t>Qty Dispatched</t>
         </is>
       </c>
-      <c r="B12" s="411" t="n"/>
-      <c r="C12" s="411" t="n"/>
-      <c r="D12" s="411" t="n"/>
-      <c r="E12" s="411" t="n"/>
-      <c r="F12" s="411" t="n"/>
-      <c r="G12" s="411" t="n"/>
-      <c r="H12" s="464" t="n"/>
-      <c r="I12" s="411" t="n"/>
-      <c r="J12" s="411" t="n"/>
-      <c r="K12" s="411" t="n"/>
-      <c r="L12" s="411" t="n"/>
-      <c r="M12" s="411" t="n"/>
-      <c r="N12" s="411" t="n"/>
-      <c r="O12" s="411" t="n"/>
-      <c r="P12" s="411" t="n"/>
-      <c r="Q12" s="411" t="n"/>
-      <c r="R12" s="411" t="n"/>
-      <c r="S12" s="411" t="n"/>
-      <c r="T12" s="411" t="n"/>
-      <c r="U12" s="465" t="inlineStr">
+      <c r="B12" s="684" t="n"/>
+      <c r="C12" s="684" t="n"/>
+      <c r="D12" s="684" t="n"/>
+      <c r="E12" s="684" t="n"/>
+      <c r="F12" s="684" t="n"/>
+      <c r="G12" s="684" t="n"/>
+      <c r="H12" s="629" t="n"/>
+      <c r="I12" s="684" t="n"/>
+      <c r="J12" s="684" t="n"/>
+      <c r="K12" s="684" t="n"/>
+      <c r="L12" s="684" t="n"/>
+      <c r="M12" s="684" t="n"/>
+      <c r="N12" s="684" t="n"/>
+      <c r="O12" s="684" t="n"/>
+      <c r="P12" s="684" t="n"/>
+      <c r="Q12" s="684" t="n"/>
+      <c r="R12" s="684" t="n"/>
+      <c r="S12" s="684" t="n"/>
+      <c r="T12" s="684" t="n"/>
+      <c r="U12" s="630" t="inlineStr">
         <is>
           <t>Expected Return Date</t>
         </is>
       </c>
-      <c r="V12" s="411" t="n"/>
-      <c r="W12" s="411" t="n"/>
-      <c r="X12" s="411" t="n"/>
-      <c r="Y12" s="411" t="n"/>
-      <c r="Z12" s="411" t="n"/>
-      <c r="AA12" s="411" t="n"/>
-      <c r="AB12" s="557" t="n"/>
-      <c r="AC12" s="411" t="n"/>
-      <c r="AD12" s="411" t="n"/>
-      <c r="AE12" s="411" t="n"/>
-      <c r="AF12" s="411" t="n"/>
-      <c r="AG12" s="411" t="n"/>
-      <c r="AH12" s="411" t="n"/>
-      <c r="AI12" s="411" t="n"/>
-      <c r="AJ12" s="411" t="n"/>
-      <c r="AK12" s="411" t="n"/>
-      <c r="AL12" s="411" t="n"/>
-      <c r="AM12" s="411" t="n"/>
-      <c r="AN12" s="558" t="n"/>
+      <c r="V12" s="684" t="n"/>
+      <c r="W12" s="684" t="n"/>
+      <c r="X12" s="684" t="n"/>
+      <c r="Y12" s="684" t="n"/>
+      <c r="Z12" s="684" t="n"/>
+      <c r="AA12" s="684" t="n"/>
+      <c r="AB12" s="631" t="n"/>
+      <c r="AC12" s="684" t="n"/>
+      <c r="AD12" s="684" t="n"/>
+      <c r="AE12" s="684" t="n"/>
+      <c r="AF12" s="684" t="n"/>
+      <c r="AG12" s="684" t="n"/>
+      <c r="AH12" s="684" t="n"/>
+      <c r="AI12" s="684" t="n"/>
+      <c r="AJ12" s="684" t="n"/>
+      <c r="AK12" s="684" t="n"/>
+      <c r="AL12" s="684" t="n"/>
+      <c r="AM12" s="684" t="n"/>
+      <c r="AN12" s="685" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1" s="329">
-      <c r="A13" s="467" t="inlineStr">
+      <c r="A13" s="632" t="inlineStr">
         <is>
           <t>Route Step / Due Date</t>
         </is>
       </c>
-      <c r="B13" s="547" t="n"/>
-      <c r="C13" s="547" t="n"/>
-      <c r="D13" s="547" t="n"/>
-      <c r="E13" s="547" t="n"/>
-      <c r="F13" s="547" t="n"/>
-      <c r="G13" s="547" t="n"/>
-      <c r="H13" s="469" t="n"/>
-      <c r="I13" s="547" t="n"/>
-      <c r="J13" s="547" t="n"/>
-      <c r="K13" s="547" t="n"/>
-      <c r="L13" s="547" t="n"/>
-      <c r="M13" s="547" t="n"/>
-      <c r="N13" s="547" t="n"/>
-      <c r="O13" s="547" t="n"/>
-      <c r="P13" s="547" t="n"/>
-      <c r="Q13" s="547" t="n"/>
-      <c r="R13" s="547" t="n"/>
-      <c r="S13" s="547" t="n"/>
-      <c r="T13" s="547" t="n"/>
-      <c r="U13" s="470" t="inlineStr">
+      <c r="B13" s="686" t="n"/>
+      <c r="C13" s="686" t="n"/>
+      <c r="D13" s="686" t="n"/>
+      <c r="E13" s="686" t="n"/>
+      <c r="F13" s="686" t="n"/>
+      <c r="G13" s="686" t="n"/>
+      <c r="H13" s="633" t="n"/>
+      <c r="I13" s="686" t="n"/>
+      <c r="J13" s="686" t="n"/>
+      <c r="K13" s="686" t="n"/>
+      <c r="L13" s="686" t="n"/>
+      <c r="M13" s="686" t="n"/>
+      <c r="N13" s="686" t="n"/>
+      <c r="O13" s="686" t="n"/>
+      <c r="P13" s="686" t="n"/>
+      <c r="Q13" s="686" t="n"/>
+      <c r="R13" s="686" t="n"/>
+      <c r="S13" s="686" t="n"/>
+      <c r="T13" s="686" t="n"/>
+      <c r="U13" s="634" t="inlineStr">
         <is>
           <t>Package Ref</t>
         </is>
       </c>
-      <c r="V13" s="547" t="n"/>
-      <c r="W13" s="547" t="n"/>
-      <c r="X13" s="547" t="n"/>
-      <c r="Y13" s="547" t="n"/>
-      <c r="Z13" s="547" t="n"/>
-      <c r="AA13" s="547" t="n"/>
-      <c r="AB13" s="559" t="n"/>
-      <c r="AC13" s="547" t="n"/>
-      <c r="AD13" s="547" t="n"/>
-      <c r="AE13" s="547" t="n"/>
-      <c r="AF13" s="547" t="n"/>
-      <c r="AG13" s="547" t="n"/>
-      <c r="AH13" s="547" t="n"/>
-      <c r="AI13" s="547" t="n"/>
-      <c r="AJ13" s="547" t="n"/>
-      <c r="AK13" s="547" t="n"/>
-      <c r="AL13" s="547" t="n"/>
-      <c r="AM13" s="547" t="n"/>
-      <c r="AN13" s="550" t="n"/>
+      <c r="V13" s="686" t="n"/>
+      <c r="W13" s="686" t="n"/>
+      <c r="X13" s="686" t="n"/>
+      <c r="Y13" s="686" t="n"/>
+      <c r="Z13" s="686" t="n"/>
+      <c r="AA13" s="686" t="n"/>
+      <c r="AB13" s="635" t="n"/>
+      <c r="AC13" s="686" t="n"/>
+      <c r="AD13" s="686" t="n"/>
+      <c r="AE13" s="686" t="n"/>
+      <c r="AF13" s="686" t="n"/>
+      <c r="AG13" s="686" t="n"/>
+      <c r="AH13" s="686" t="n"/>
+      <c r="AI13" s="686" t="n"/>
+      <c r="AJ13" s="686" t="n"/>
+      <c r="AK13" s="686" t="n"/>
+      <c r="AL13" s="686" t="n"/>
+      <c r="AM13" s="686" t="n"/>
+      <c r="AN13" s="687" t="n"/>
     </row>
     <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="359" t="n"/>
@@ -6985,410 +7595,410 @@
       <c r="AN14" s="352" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="329">
-      <c r="A15" s="551" t="inlineStr">
+      <c r="A15" s="636" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. DISPATCH REQUIREMENTS / GATE CRITERIA</t>
         </is>
       </c>
-      <c r="B15" s="552" t="n"/>
-      <c r="C15" s="552" t="n"/>
-      <c r="D15" s="552" t="n"/>
-      <c r="E15" s="552" t="n"/>
-      <c r="F15" s="552" t="n"/>
-      <c r="G15" s="552" t="n"/>
-      <c r="H15" s="552" t="n"/>
-      <c r="I15" s="552" t="n"/>
-      <c r="J15" s="552" t="n"/>
-      <c r="K15" s="552" t="n"/>
-      <c r="L15" s="552" t="n"/>
-      <c r="M15" s="552" t="n"/>
-      <c r="N15" s="552" t="n"/>
-      <c r="O15" s="552" t="n"/>
-      <c r="P15" s="552" t="n"/>
-      <c r="Q15" s="552" t="n"/>
-      <c r="R15" s="552" t="n"/>
-      <c r="S15" s="552" t="n"/>
-      <c r="T15" s="552" t="n"/>
-      <c r="U15" s="552" t="n"/>
-      <c r="V15" s="552" t="n"/>
-      <c r="W15" s="552" t="n"/>
-      <c r="X15" s="552" t="n"/>
-      <c r="Y15" s="552" t="n"/>
-      <c r="Z15" s="552" t="n"/>
-      <c r="AA15" s="552" t="n"/>
-      <c r="AB15" s="552" t="n"/>
-      <c r="AC15" s="552" t="n"/>
-      <c r="AD15" s="552" t="n"/>
-      <c r="AE15" s="552" t="n"/>
-      <c r="AF15" s="552" t="n"/>
-      <c r="AG15" s="552" t="n"/>
-      <c r="AH15" s="552" t="n"/>
-      <c r="AI15" s="552" t="n"/>
-      <c r="AJ15" s="552" t="n"/>
-      <c r="AK15" s="552" t="n"/>
-      <c r="AL15" s="552" t="n"/>
-      <c r="AM15" s="552" t="n"/>
-      <c r="AN15" s="553" t="n"/>
+      <c r="B15" s="285" t="n"/>
+      <c r="C15" s="285" t="n"/>
+      <c r="D15" s="285" t="n"/>
+      <c r="E15" s="285" t="n"/>
+      <c r="F15" s="285" t="n"/>
+      <c r="G15" s="285" t="n"/>
+      <c r="H15" s="285" t="n"/>
+      <c r="I15" s="285" t="n"/>
+      <c r="J15" s="285" t="n"/>
+      <c r="K15" s="285" t="n"/>
+      <c r="L15" s="285" t="n"/>
+      <c r="M15" s="285" t="n"/>
+      <c r="N15" s="285" t="n"/>
+      <c r="O15" s="285" t="n"/>
+      <c r="P15" s="285" t="n"/>
+      <c r="Q15" s="285" t="n"/>
+      <c r="R15" s="285" t="n"/>
+      <c r="S15" s="285" t="n"/>
+      <c r="T15" s="285" t="n"/>
+      <c r="U15" s="285" t="n"/>
+      <c r="V15" s="285" t="n"/>
+      <c r="W15" s="285" t="n"/>
+      <c r="X15" s="285" t="n"/>
+      <c r="Y15" s="285" t="n"/>
+      <c r="Z15" s="285" t="n"/>
+      <c r="AA15" s="285" t="n"/>
+      <c r="AB15" s="285" t="n"/>
+      <c r="AC15" s="285" t="n"/>
+      <c r="AD15" s="285" t="n"/>
+      <c r="AE15" s="285" t="n"/>
+      <c r="AF15" s="285" t="n"/>
+      <c r="AG15" s="285" t="n"/>
+      <c r="AH15" s="285" t="n"/>
+      <c r="AI15" s="285" t="n"/>
+      <c r="AJ15" s="285" t="n"/>
+      <c r="AK15" s="285" t="n"/>
+      <c r="AL15" s="285" t="n"/>
+      <c r="AM15" s="285" t="n"/>
+      <c r="AN15" s="286" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="458" t="inlineStr">
+      <c r="A16" s="624" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="B16" s="554" t="n"/>
-      <c r="C16" s="554" t="n"/>
-      <c r="D16" s="554" t="n"/>
-      <c r="E16" s="554" t="n"/>
-      <c r="F16" s="554" t="n"/>
-      <c r="G16" s="554" t="n"/>
-      <c r="H16" s="460" t="n"/>
-      <c r="I16" s="554" t="n"/>
-      <c r="J16" s="554" t="n"/>
-      <c r="K16" s="554" t="n"/>
-      <c r="L16" s="554" t="n"/>
-      <c r="M16" s="554" t="n"/>
-      <c r="N16" s="554" t="n"/>
-      <c r="O16" s="554" t="n"/>
-      <c r="P16" s="554" t="n"/>
-      <c r="Q16" s="554" t="n"/>
-      <c r="R16" s="554" t="n"/>
-      <c r="S16" s="554" t="n"/>
-      <c r="T16" s="554" t="n"/>
-      <c r="U16" s="461" t="inlineStr">
+      <c r="B16" s="317" t="n"/>
+      <c r="C16" s="317" t="n"/>
+      <c r="D16" s="317" t="n"/>
+      <c r="E16" s="317" t="n"/>
+      <c r="F16" s="317" t="n"/>
+      <c r="G16" s="317" t="n"/>
+      <c r="H16" s="625" t="n"/>
+      <c r="I16" s="317" t="n"/>
+      <c r="J16" s="317" t="n"/>
+      <c r="K16" s="317" t="n"/>
+      <c r="L16" s="317" t="n"/>
+      <c r="M16" s="317" t="n"/>
+      <c r="N16" s="317" t="n"/>
+      <c r="O16" s="317" t="n"/>
+      <c r="P16" s="317" t="n"/>
+      <c r="Q16" s="317" t="n"/>
+      <c r="R16" s="317" t="n"/>
+      <c r="S16" s="317" t="n"/>
+      <c r="T16" s="317" t="n"/>
+      <c r="U16" s="626" t="inlineStr">
         <is>
           <t>Linked Route / Package</t>
         </is>
       </c>
-      <c r="V16" s="554" t="n"/>
-      <c r="W16" s="554" t="n"/>
-      <c r="X16" s="554" t="n"/>
-      <c r="Y16" s="554" t="n"/>
-      <c r="Z16" s="554" t="n"/>
-      <c r="AA16" s="554" t="n"/>
-      <c r="AB16" s="555" t="n"/>
-      <c r="AC16" s="554" t="n"/>
-      <c r="AD16" s="554" t="n"/>
-      <c r="AE16" s="554" t="n"/>
-      <c r="AF16" s="554" t="n"/>
-      <c r="AG16" s="554" t="n"/>
-      <c r="AH16" s="554" t="n"/>
-      <c r="AI16" s="554" t="n"/>
-      <c r="AJ16" s="554" t="n"/>
-      <c r="AK16" s="554" t="n"/>
-      <c r="AL16" s="554" t="n"/>
-      <c r="AM16" s="554" t="n"/>
-      <c r="AN16" s="556" t="n"/>
+      <c r="V16" s="317" t="n"/>
+      <c r="W16" s="317" t="n"/>
+      <c r="X16" s="317" t="n"/>
+      <c r="Y16" s="317" t="n"/>
+      <c r="Z16" s="317" t="n"/>
+      <c r="AA16" s="317" t="n"/>
+      <c r="AB16" s="627" t="n"/>
+      <c r="AC16" s="317" t="n"/>
+      <c r="AD16" s="317" t="n"/>
+      <c r="AE16" s="317" t="n"/>
+      <c r="AF16" s="317" t="n"/>
+      <c r="AG16" s="317" t="n"/>
+      <c r="AH16" s="317" t="n"/>
+      <c r="AI16" s="317" t="n"/>
+      <c r="AJ16" s="317" t="n"/>
+      <c r="AK16" s="317" t="n"/>
+      <c r="AL16" s="317" t="n"/>
+      <c r="AM16" s="317" t="n"/>
+      <c r="AN16" s="319" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="463" t="inlineStr">
+      <c r="A17" s="628" t="inlineStr">
         <is>
           <t>Supplier / Customer Spec Ref</t>
         </is>
       </c>
-      <c r="B17" s="411" t="n"/>
-      <c r="C17" s="411" t="n"/>
-      <c r="D17" s="411" t="n"/>
-      <c r="E17" s="411" t="n"/>
-      <c r="F17" s="411" t="n"/>
-      <c r="G17" s="411" t="n"/>
-      <c r="H17" s="464" t="n"/>
-      <c r="I17" s="411" t="n"/>
-      <c r="J17" s="411" t="n"/>
-      <c r="K17" s="411" t="n"/>
-      <c r="L17" s="411" t="n"/>
-      <c r="M17" s="411" t="n"/>
-      <c r="N17" s="411" t="n"/>
-      <c r="O17" s="411" t="n"/>
-      <c r="P17" s="411" t="n"/>
-      <c r="Q17" s="411" t="n"/>
-      <c r="R17" s="411" t="n"/>
-      <c r="S17" s="411" t="n"/>
-      <c r="T17" s="411" t="n"/>
-      <c r="U17" s="465" t="inlineStr">
+      <c r="B17" s="684" t="n"/>
+      <c r="C17" s="684" t="n"/>
+      <c r="D17" s="684" t="n"/>
+      <c r="E17" s="684" t="n"/>
+      <c r="F17" s="684" t="n"/>
+      <c r="G17" s="684" t="n"/>
+      <c r="H17" s="629" t="n"/>
+      <c r="I17" s="684" t="n"/>
+      <c r="J17" s="684" t="n"/>
+      <c r="K17" s="684" t="n"/>
+      <c r="L17" s="684" t="n"/>
+      <c r="M17" s="684" t="n"/>
+      <c r="N17" s="684" t="n"/>
+      <c r="O17" s="684" t="n"/>
+      <c r="P17" s="684" t="n"/>
+      <c r="Q17" s="684" t="n"/>
+      <c r="R17" s="684" t="n"/>
+      <c r="S17" s="684" t="n"/>
+      <c r="T17" s="684" t="n"/>
+      <c r="U17" s="630" t="inlineStr">
         <is>
           <t>Open Actions Present (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="411" t="n"/>
-      <c r="W17" s="411" t="n"/>
-      <c r="X17" s="411" t="n"/>
-      <c r="Y17" s="411" t="n"/>
-      <c r="Z17" s="411" t="n"/>
-      <c r="AA17" s="411" t="n"/>
-      <c r="AB17" s="557" t="n"/>
-      <c r="AC17" s="411" t="n"/>
-      <c r="AD17" s="411" t="n"/>
-      <c r="AE17" s="411" t="n"/>
-      <c r="AF17" s="411" t="n"/>
-      <c r="AG17" s="411" t="n"/>
-      <c r="AH17" s="411" t="n"/>
-      <c r="AI17" s="411" t="n"/>
-      <c r="AJ17" s="411" t="n"/>
-      <c r="AK17" s="411" t="n"/>
-      <c r="AL17" s="411" t="n"/>
-      <c r="AM17" s="411" t="n"/>
-      <c r="AN17" s="558" t="n"/>
+      <c r="V17" s="684" t="n"/>
+      <c r="W17" s="684" t="n"/>
+      <c r="X17" s="684" t="n"/>
+      <c r="Y17" s="684" t="n"/>
+      <c r="Z17" s="684" t="n"/>
+      <c r="AA17" s="684" t="n"/>
+      <c r="AB17" s="631" t="n"/>
+      <c r="AC17" s="684" t="n"/>
+      <c r="AD17" s="684" t="n"/>
+      <c r="AE17" s="684" t="n"/>
+      <c r="AF17" s="684" t="n"/>
+      <c r="AG17" s="684" t="n"/>
+      <c r="AH17" s="684" t="n"/>
+      <c r="AI17" s="684" t="n"/>
+      <c r="AJ17" s="684" t="n"/>
+      <c r="AK17" s="684" t="n"/>
+      <c r="AL17" s="684" t="n"/>
+      <c r="AM17" s="684" t="n"/>
+      <c r="AN17" s="685" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="560" t="inlineStr">
+      <c r="A18" s="637" t="inlineStr">
         <is>
           <t>DISPATCH NOTES / CONDITIONALS</t>
         </is>
       </c>
-      <c r="B18" s="411" t="n"/>
-      <c r="C18" s="411" t="n"/>
-      <c r="D18" s="411" t="n"/>
-      <c r="E18" s="411" t="n"/>
-      <c r="F18" s="411" t="n"/>
-      <c r="G18" s="411" t="n"/>
-      <c r="H18" s="411" t="n"/>
-      <c r="I18" s="411" t="n"/>
-      <c r="J18" s="411" t="n"/>
-      <c r="K18" s="411" t="n"/>
-      <c r="L18" s="411" t="n"/>
-      <c r="M18" s="411" t="n"/>
-      <c r="N18" s="411" t="n"/>
-      <c r="O18" s="411" t="n"/>
-      <c r="P18" s="411" t="n"/>
-      <c r="Q18" s="411" t="n"/>
-      <c r="R18" s="411" t="n"/>
-      <c r="S18" s="411" t="n"/>
-      <c r="T18" s="411" t="n"/>
-      <c r="U18" s="411" t="n"/>
-      <c r="V18" s="411" t="n"/>
-      <c r="W18" s="411" t="n"/>
-      <c r="X18" s="411" t="n"/>
-      <c r="Y18" s="411" t="n"/>
-      <c r="Z18" s="411" t="n"/>
-      <c r="AA18" s="411" t="n"/>
-      <c r="AB18" s="411" t="n"/>
-      <c r="AC18" s="411" t="n"/>
-      <c r="AD18" s="411" t="n"/>
-      <c r="AE18" s="411" t="n"/>
-      <c r="AF18" s="411" t="n"/>
-      <c r="AG18" s="411" t="n"/>
-      <c r="AH18" s="411" t="n"/>
-      <c r="AI18" s="411" t="n"/>
-      <c r="AJ18" s="411" t="n"/>
-      <c r="AK18" s="411" t="n"/>
-      <c r="AL18" s="411" t="n"/>
-      <c r="AM18" s="411" t="n"/>
-      <c r="AN18" s="558" t="n"/>
+      <c r="B18" s="684" t="n"/>
+      <c r="C18" s="684" t="n"/>
+      <c r="D18" s="684" t="n"/>
+      <c r="E18" s="684" t="n"/>
+      <c r="F18" s="684" t="n"/>
+      <c r="G18" s="684" t="n"/>
+      <c r="H18" s="684" t="n"/>
+      <c r="I18" s="684" t="n"/>
+      <c r="J18" s="684" t="n"/>
+      <c r="K18" s="684" t="n"/>
+      <c r="L18" s="684" t="n"/>
+      <c r="M18" s="684" t="n"/>
+      <c r="N18" s="684" t="n"/>
+      <c r="O18" s="684" t="n"/>
+      <c r="P18" s="684" t="n"/>
+      <c r="Q18" s="684" t="n"/>
+      <c r="R18" s="684" t="n"/>
+      <c r="S18" s="684" t="n"/>
+      <c r="T18" s="684" t="n"/>
+      <c r="U18" s="684" t="n"/>
+      <c r="V18" s="684" t="n"/>
+      <c r="W18" s="684" t="n"/>
+      <c r="X18" s="684" t="n"/>
+      <c r="Y18" s="684" t="n"/>
+      <c r="Z18" s="684" t="n"/>
+      <c r="AA18" s="684" t="n"/>
+      <c r="AB18" s="684" t="n"/>
+      <c r="AC18" s="684" t="n"/>
+      <c r="AD18" s="684" t="n"/>
+      <c r="AE18" s="684" t="n"/>
+      <c r="AF18" s="684" t="n"/>
+      <c r="AG18" s="684" t="n"/>
+      <c r="AH18" s="684" t="n"/>
+      <c r="AI18" s="684" t="n"/>
+      <c r="AJ18" s="684" t="n"/>
+      <c r="AK18" s="684" t="n"/>
+      <c r="AL18" s="684" t="n"/>
+      <c r="AM18" s="684" t="n"/>
+      <c r="AN18" s="685" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="561" t="n"/>
-      <c r="B19" s="410" t="n"/>
-      <c r="C19" s="410" t="n"/>
-      <c r="D19" s="410" t="n"/>
-      <c r="E19" s="410" t="n"/>
-      <c r="F19" s="410" t="n"/>
-      <c r="G19" s="410" t="n"/>
-      <c r="H19" s="410" t="n"/>
-      <c r="I19" s="410" t="n"/>
-      <c r="J19" s="410" t="n"/>
-      <c r="K19" s="410" t="n"/>
-      <c r="L19" s="410" t="n"/>
-      <c r="M19" s="410" t="n"/>
-      <c r="N19" s="410" t="n"/>
-      <c r="O19" s="410" t="n"/>
-      <c r="P19" s="410" t="n"/>
-      <c r="Q19" s="410" t="n"/>
-      <c r="R19" s="410" t="n"/>
-      <c r="S19" s="410" t="n"/>
-      <c r="T19" s="410" t="n"/>
-      <c r="U19" s="410" t="n"/>
-      <c r="V19" s="410" t="n"/>
-      <c r="W19" s="410" t="n"/>
-      <c r="X19" s="410" t="n"/>
-      <c r="Y19" s="410" t="n"/>
-      <c r="Z19" s="410" t="n"/>
-      <c r="AA19" s="410" t="n"/>
-      <c r="AB19" s="410" t="n"/>
-      <c r="AC19" s="410" t="n"/>
-      <c r="AD19" s="410" t="n"/>
-      <c r="AE19" s="410" t="n"/>
-      <c r="AF19" s="410" t="n"/>
-      <c r="AG19" s="410" t="n"/>
-      <c r="AH19" s="410" t="n"/>
-      <c r="AI19" s="410" t="n"/>
-      <c r="AJ19" s="410" t="n"/>
-      <c r="AK19" s="410" t="n"/>
-      <c r="AL19" s="410" t="n"/>
-      <c r="AM19" s="410" t="n"/>
-      <c r="AN19" s="540" t="n"/>
+      <c r="A19" s="638" t="n"/>
+      <c r="B19" s="688" t="n"/>
+      <c r="C19" s="688" t="n"/>
+      <c r="D19" s="688" t="n"/>
+      <c r="E19" s="688" t="n"/>
+      <c r="F19" s="688" t="n"/>
+      <c r="G19" s="688" t="n"/>
+      <c r="H19" s="688" t="n"/>
+      <c r="I19" s="688" t="n"/>
+      <c r="J19" s="688" t="n"/>
+      <c r="K19" s="688" t="n"/>
+      <c r="L19" s="688" t="n"/>
+      <c r="M19" s="688" t="n"/>
+      <c r="N19" s="688" t="n"/>
+      <c r="O19" s="688" t="n"/>
+      <c r="P19" s="688" t="n"/>
+      <c r="Q19" s="688" t="n"/>
+      <c r="R19" s="688" t="n"/>
+      <c r="S19" s="688" t="n"/>
+      <c r="T19" s="688" t="n"/>
+      <c r="U19" s="688" t="n"/>
+      <c r="V19" s="688" t="n"/>
+      <c r="W19" s="688" t="n"/>
+      <c r="X19" s="688" t="n"/>
+      <c r="Y19" s="688" t="n"/>
+      <c r="Z19" s="688" t="n"/>
+      <c r="AA19" s="688" t="n"/>
+      <c r="AB19" s="688" t="n"/>
+      <c r="AC19" s="688" t="n"/>
+      <c r="AD19" s="688" t="n"/>
+      <c r="AE19" s="688" t="n"/>
+      <c r="AF19" s="688" t="n"/>
+      <c r="AG19" s="688" t="n"/>
+      <c r="AH19" s="688" t="n"/>
+      <c r="AI19" s="688" t="n"/>
+      <c r="AJ19" s="688" t="n"/>
+      <c r="AK19" s="688" t="n"/>
+      <c r="AL19" s="688" t="n"/>
+      <c r="AM19" s="688" t="n"/>
+      <c r="AN19" s="689" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="562" t="n"/>
-      <c r="B20" s="415" t="n"/>
-      <c r="C20" s="415" t="n"/>
-      <c r="D20" s="415" t="n"/>
-      <c r="E20" s="415" t="n"/>
-      <c r="F20" s="415" t="n"/>
-      <c r="G20" s="415" t="n"/>
-      <c r="H20" s="415" t="n"/>
-      <c r="I20" s="415" t="n"/>
-      <c r="J20" s="415" t="n"/>
-      <c r="K20" s="415" t="n"/>
-      <c r="L20" s="415" t="n"/>
-      <c r="M20" s="415" t="n"/>
-      <c r="N20" s="415" t="n"/>
-      <c r="O20" s="415" t="n"/>
-      <c r="P20" s="415" t="n"/>
-      <c r="Q20" s="415" t="n"/>
-      <c r="R20" s="415" t="n"/>
-      <c r="S20" s="415" t="n"/>
-      <c r="T20" s="415" t="n"/>
-      <c r="U20" s="415" t="n"/>
-      <c r="V20" s="415" t="n"/>
-      <c r="W20" s="415" t="n"/>
-      <c r="X20" s="415" t="n"/>
-      <c r="Y20" s="415" t="n"/>
-      <c r="Z20" s="415" t="n"/>
-      <c r="AA20" s="415" t="n"/>
-      <c r="AB20" s="415" t="n"/>
-      <c r="AC20" s="415" t="n"/>
-      <c r="AD20" s="415" t="n"/>
-      <c r="AE20" s="415" t="n"/>
-      <c r="AF20" s="415" t="n"/>
-      <c r="AG20" s="415" t="n"/>
-      <c r="AH20" s="415" t="n"/>
-      <c r="AI20" s="415" t="n"/>
-      <c r="AJ20" s="415" t="n"/>
-      <c r="AK20" s="415" t="n"/>
-      <c r="AL20" s="415" t="n"/>
-      <c r="AM20" s="415" t="n"/>
-      <c r="AN20" s="563" t="n"/>
+      <c r="A20" s="279" t="n"/>
+      <c r="B20" s="322" t="n"/>
+      <c r="C20" s="322" t="n"/>
+      <c r="D20" s="322" t="n"/>
+      <c r="E20" s="322" t="n"/>
+      <c r="F20" s="322" t="n"/>
+      <c r="G20" s="322" t="n"/>
+      <c r="H20" s="322" t="n"/>
+      <c r="I20" s="322" t="n"/>
+      <c r="J20" s="322" t="n"/>
+      <c r="K20" s="322" t="n"/>
+      <c r="L20" s="322" t="n"/>
+      <c r="M20" s="322" t="n"/>
+      <c r="N20" s="322" t="n"/>
+      <c r="O20" s="322" t="n"/>
+      <c r="P20" s="322" t="n"/>
+      <c r="Q20" s="322" t="n"/>
+      <c r="R20" s="322" t="n"/>
+      <c r="S20" s="322" t="n"/>
+      <c r="T20" s="322" t="n"/>
+      <c r="U20" s="322" t="n"/>
+      <c r="V20" s="322" t="n"/>
+      <c r="W20" s="322" t="n"/>
+      <c r="X20" s="322" t="n"/>
+      <c r="Y20" s="322" t="n"/>
+      <c r="Z20" s="322" t="n"/>
+      <c r="AA20" s="322" t="n"/>
+      <c r="AB20" s="322" t="n"/>
+      <c r="AC20" s="322" t="n"/>
+      <c r="AD20" s="322" t="n"/>
+      <c r="AE20" s="322" t="n"/>
+      <c r="AF20" s="322" t="n"/>
+      <c r="AG20" s="322" t="n"/>
+      <c r="AH20" s="322" t="n"/>
+      <c r="AI20" s="322" t="n"/>
+      <c r="AJ20" s="322" t="n"/>
+      <c r="AK20" s="322" t="n"/>
+      <c r="AL20" s="322" t="n"/>
+      <c r="AM20" s="322" t="n"/>
+      <c r="AN20" s="324" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="560" t="inlineStr">
+      <c r="A21" s="637" t="inlineStr">
         <is>
           <t>REQUIRED OUTPUT / FLOW-DOWN / CERTIFICATES</t>
         </is>
       </c>
-      <c r="B21" s="411" t="n"/>
-      <c r="C21" s="411" t="n"/>
-      <c r="D21" s="411" t="n"/>
-      <c r="E21" s="411" t="n"/>
-      <c r="F21" s="411" t="n"/>
-      <c r="G21" s="411" t="n"/>
-      <c r="H21" s="411" t="n"/>
-      <c r="I21" s="411" t="n"/>
-      <c r="J21" s="411" t="n"/>
-      <c r="K21" s="411" t="n"/>
-      <c r="L21" s="411" t="n"/>
-      <c r="M21" s="411" t="n"/>
-      <c r="N21" s="411" t="n"/>
-      <c r="O21" s="411" t="n"/>
-      <c r="P21" s="411" t="n"/>
-      <c r="Q21" s="411" t="n"/>
-      <c r="R21" s="411" t="n"/>
-      <c r="S21" s="411" t="n"/>
-      <c r="T21" s="411" t="n"/>
-      <c r="U21" s="411" t="n"/>
-      <c r="V21" s="411" t="n"/>
-      <c r="W21" s="411" t="n"/>
-      <c r="X21" s="411" t="n"/>
-      <c r="Y21" s="411" t="n"/>
-      <c r="Z21" s="411" t="n"/>
-      <c r="AA21" s="411" t="n"/>
-      <c r="AB21" s="411" t="n"/>
-      <c r="AC21" s="411" t="n"/>
-      <c r="AD21" s="411" t="n"/>
-      <c r="AE21" s="411" t="n"/>
-      <c r="AF21" s="411" t="n"/>
-      <c r="AG21" s="411" t="n"/>
-      <c r="AH21" s="411" t="n"/>
-      <c r="AI21" s="411" t="n"/>
-      <c r="AJ21" s="411" t="n"/>
-      <c r="AK21" s="411" t="n"/>
-      <c r="AL21" s="411" t="n"/>
-      <c r="AM21" s="411" t="n"/>
-      <c r="AN21" s="558" t="n"/>
+      <c r="B21" s="684" t="n"/>
+      <c r="C21" s="684" t="n"/>
+      <c r="D21" s="684" t="n"/>
+      <c r="E21" s="684" t="n"/>
+      <c r="F21" s="684" t="n"/>
+      <c r="G21" s="684" t="n"/>
+      <c r="H21" s="684" t="n"/>
+      <c r="I21" s="684" t="n"/>
+      <c r="J21" s="684" t="n"/>
+      <c r="K21" s="684" t="n"/>
+      <c r="L21" s="684" t="n"/>
+      <c r="M21" s="684" t="n"/>
+      <c r="N21" s="684" t="n"/>
+      <c r="O21" s="684" t="n"/>
+      <c r="P21" s="684" t="n"/>
+      <c r="Q21" s="684" t="n"/>
+      <c r="R21" s="684" t="n"/>
+      <c r="S21" s="684" t="n"/>
+      <c r="T21" s="684" t="n"/>
+      <c r="U21" s="684" t="n"/>
+      <c r="V21" s="684" t="n"/>
+      <c r="W21" s="684" t="n"/>
+      <c r="X21" s="684" t="n"/>
+      <c r="Y21" s="684" t="n"/>
+      <c r="Z21" s="684" t="n"/>
+      <c r="AA21" s="684" t="n"/>
+      <c r="AB21" s="684" t="n"/>
+      <c r="AC21" s="684" t="n"/>
+      <c r="AD21" s="684" t="n"/>
+      <c r="AE21" s="684" t="n"/>
+      <c r="AF21" s="684" t="n"/>
+      <c r="AG21" s="684" t="n"/>
+      <c r="AH21" s="684" t="n"/>
+      <c r="AI21" s="684" t="n"/>
+      <c r="AJ21" s="684" t="n"/>
+      <c r="AK21" s="684" t="n"/>
+      <c r="AL21" s="684" t="n"/>
+      <c r="AM21" s="684" t="n"/>
+      <c r="AN21" s="685" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="561" t="n"/>
-      <c r="B22" s="410" t="n"/>
-      <c r="C22" s="410" t="n"/>
-      <c r="D22" s="410" t="n"/>
-      <c r="E22" s="410" t="n"/>
-      <c r="F22" s="410" t="n"/>
-      <c r="G22" s="410" t="n"/>
-      <c r="H22" s="410" t="n"/>
-      <c r="I22" s="410" t="n"/>
-      <c r="J22" s="410" t="n"/>
-      <c r="K22" s="410" t="n"/>
-      <c r="L22" s="410" t="n"/>
-      <c r="M22" s="410" t="n"/>
-      <c r="N22" s="410" t="n"/>
-      <c r="O22" s="410" t="n"/>
-      <c r="P22" s="410" t="n"/>
-      <c r="Q22" s="410" t="n"/>
-      <c r="R22" s="410" t="n"/>
-      <c r="S22" s="410" t="n"/>
-      <c r="T22" s="410" t="n"/>
-      <c r="U22" s="410" t="n"/>
-      <c r="V22" s="410" t="n"/>
-      <c r="W22" s="410" t="n"/>
-      <c r="X22" s="410" t="n"/>
-      <c r="Y22" s="410" t="n"/>
-      <c r="Z22" s="410" t="n"/>
-      <c r="AA22" s="410" t="n"/>
-      <c r="AB22" s="410" t="n"/>
-      <c r="AC22" s="410" t="n"/>
-      <c r="AD22" s="410" t="n"/>
-      <c r="AE22" s="410" t="n"/>
-      <c r="AF22" s="410" t="n"/>
-      <c r="AG22" s="410" t="n"/>
-      <c r="AH22" s="410" t="n"/>
-      <c r="AI22" s="410" t="n"/>
-      <c r="AJ22" s="410" t="n"/>
-      <c r="AK22" s="410" t="n"/>
-      <c r="AL22" s="410" t="n"/>
-      <c r="AM22" s="410" t="n"/>
-      <c r="AN22" s="540" t="n"/>
+      <c r="A22" s="638" t="n"/>
+      <c r="B22" s="688" t="n"/>
+      <c r="C22" s="688" t="n"/>
+      <c r="D22" s="688" t="n"/>
+      <c r="E22" s="688" t="n"/>
+      <c r="F22" s="688" t="n"/>
+      <c r="G22" s="688" t="n"/>
+      <c r="H22" s="688" t="n"/>
+      <c r="I22" s="688" t="n"/>
+      <c r="J22" s="688" t="n"/>
+      <c r="K22" s="688" t="n"/>
+      <c r="L22" s="688" t="n"/>
+      <c r="M22" s="688" t="n"/>
+      <c r="N22" s="688" t="n"/>
+      <c r="O22" s="688" t="n"/>
+      <c r="P22" s="688" t="n"/>
+      <c r="Q22" s="688" t="n"/>
+      <c r="R22" s="688" t="n"/>
+      <c r="S22" s="688" t="n"/>
+      <c r="T22" s="688" t="n"/>
+      <c r="U22" s="688" t="n"/>
+      <c r="V22" s="688" t="n"/>
+      <c r="W22" s="688" t="n"/>
+      <c r="X22" s="688" t="n"/>
+      <c r="Y22" s="688" t="n"/>
+      <c r="Z22" s="688" t="n"/>
+      <c r="AA22" s="688" t="n"/>
+      <c r="AB22" s="688" t="n"/>
+      <c r="AC22" s="688" t="n"/>
+      <c r="AD22" s="688" t="n"/>
+      <c r="AE22" s="688" t="n"/>
+      <c r="AF22" s="688" t="n"/>
+      <c r="AG22" s="688" t="n"/>
+      <c r="AH22" s="688" t="n"/>
+      <c r="AI22" s="688" t="n"/>
+      <c r="AJ22" s="688" t="n"/>
+      <c r="AK22" s="688" t="n"/>
+      <c r="AL22" s="688" t="n"/>
+      <c r="AM22" s="688" t="n"/>
+      <c r="AN22" s="689" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="562" t="n"/>
-      <c r="B23" s="415" t="n"/>
-      <c r="C23" s="415" t="n"/>
-      <c r="D23" s="415" t="n"/>
-      <c r="E23" s="415" t="n"/>
-      <c r="F23" s="415" t="n"/>
-      <c r="G23" s="415" t="n"/>
-      <c r="H23" s="415" t="n"/>
-      <c r="I23" s="415" t="n"/>
-      <c r="J23" s="415" t="n"/>
-      <c r="K23" s="415" t="n"/>
-      <c r="L23" s="415" t="n"/>
-      <c r="M23" s="415" t="n"/>
-      <c r="N23" s="415" t="n"/>
-      <c r="O23" s="415" t="n"/>
-      <c r="P23" s="415" t="n"/>
-      <c r="Q23" s="415" t="n"/>
-      <c r="R23" s="415" t="n"/>
-      <c r="S23" s="415" t="n"/>
-      <c r="T23" s="415" t="n"/>
-      <c r="U23" s="415" t="n"/>
-      <c r="V23" s="415" t="n"/>
-      <c r="W23" s="415" t="n"/>
-      <c r="X23" s="415" t="n"/>
-      <c r="Y23" s="415" t="n"/>
-      <c r="Z23" s="415" t="n"/>
-      <c r="AA23" s="415" t="n"/>
-      <c r="AB23" s="415" t="n"/>
-      <c r="AC23" s="415" t="n"/>
-      <c r="AD23" s="415" t="n"/>
-      <c r="AE23" s="415" t="n"/>
-      <c r="AF23" s="415" t="n"/>
-      <c r="AG23" s="415" t="n"/>
-      <c r="AH23" s="415" t="n"/>
-      <c r="AI23" s="415" t="n"/>
-      <c r="AJ23" s="415" t="n"/>
-      <c r="AK23" s="415" t="n"/>
-      <c r="AL23" s="415" t="n"/>
-      <c r="AM23" s="415" t="n"/>
-      <c r="AN23" s="563" t="n"/>
+      <c r="A23" s="279" t="n"/>
+      <c r="B23" s="322" t="n"/>
+      <c r="C23" s="322" t="n"/>
+      <c r="D23" s="322" t="n"/>
+      <c r="E23" s="322" t="n"/>
+      <c r="F23" s="322" t="n"/>
+      <c r="G23" s="322" t="n"/>
+      <c r="H23" s="322" t="n"/>
+      <c r="I23" s="322" t="n"/>
+      <c r="J23" s="322" t="n"/>
+      <c r="K23" s="322" t="n"/>
+      <c r="L23" s="322" t="n"/>
+      <c r="M23" s="322" t="n"/>
+      <c r="N23" s="322" t="n"/>
+      <c r="O23" s="322" t="n"/>
+      <c r="P23" s="322" t="n"/>
+      <c r="Q23" s="322" t="n"/>
+      <c r="R23" s="322" t="n"/>
+      <c r="S23" s="322" t="n"/>
+      <c r="T23" s="322" t="n"/>
+      <c r="U23" s="322" t="n"/>
+      <c r="V23" s="322" t="n"/>
+      <c r="W23" s="322" t="n"/>
+      <c r="X23" s="322" t="n"/>
+      <c r="Y23" s="322" t="n"/>
+      <c r="Z23" s="322" t="n"/>
+      <c r="AA23" s="322" t="n"/>
+      <c r="AB23" s="322" t="n"/>
+      <c r="AC23" s="322" t="n"/>
+      <c r="AD23" s="322" t="n"/>
+      <c r="AE23" s="322" t="n"/>
+      <c r="AF23" s="322" t="n"/>
+      <c r="AG23" s="322" t="n"/>
+      <c r="AH23" s="322" t="n"/>
+      <c r="AI23" s="322" t="n"/>
+      <c r="AJ23" s="322" t="n"/>
+      <c r="AK23" s="322" t="n"/>
+      <c r="AL23" s="322" t="n"/>
+      <c r="AM23" s="322" t="n"/>
+      <c r="AN23" s="324" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="364" t="n"/>
@@ -7433,414 +8043,414 @@
       <c r="AN24" s="352" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="329">
-      <c r="A25" s="551" t="inlineStr">
+      <c r="A25" s="636" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. REQUIREMENTS / EVIDENCE / IMPACT</t>
         </is>
       </c>
-      <c r="B25" s="552" t="n"/>
-      <c r="C25" s="552" t="n"/>
-      <c r="D25" s="552" t="n"/>
-      <c r="E25" s="552" t="n"/>
-      <c r="F25" s="552" t="n"/>
-      <c r="G25" s="552" t="n"/>
-      <c r="H25" s="552" t="n"/>
-      <c r="I25" s="552" t="n"/>
-      <c r="J25" s="552" t="n"/>
-      <c r="K25" s="552" t="n"/>
-      <c r="L25" s="552" t="n"/>
-      <c r="M25" s="552" t="n"/>
-      <c r="N25" s="552" t="n"/>
-      <c r="O25" s="552" t="n"/>
-      <c r="P25" s="552" t="n"/>
-      <c r="Q25" s="552" t="n"/>
-      <c r="R25" s="552" t="n"/>
-      <c r="S25" s="552" t="n"/>
-      <c r="T25" s="552" t="n"/>
-      <c r="U25" s="552" t="n"/>
-      <c r="V25" s="552" t="n"/>
-      <c r="W25" s="552" t="n"/>
-      <c r="X25" s="552" t="n"/>
-      <c r="Y25" s="552" t="n"/>
-      <c r="Z25" s="552" t="n"/>
-      <c r="AA25" s="552" t="n"/>
-      <c r="AB25" s="552" t="n"/>
-      <c r="AC25" s="552" t="n"/>
-      <c r="AD25" s="552" t="n"/>
-      <c r="AE25" s="552" t="n"/>
-      <c r="AF25" s="552" t="n"/>
-      <c r="AG25" s="552" t="n"/>
-      <c r="AH25" s="552" t="n"/>
-      <c r="AI25" s="552" t="n"/>
-      <c r="AJ25" s="552" t="n"/>
-      <c r="AK25" s="552" t="n"/>
-      <c r="AL25" s="552" t="n"/>
-      <c r="AM25" s="552" t="n"/>
-      <c r="AN25" s="553" t="n"/>
+      <c r="B25" s="285" t="n"/>
+      <c r="C25" s="285" t="n"/>
+      <c r="D25" s="285" t="n"/>
+      <c r="E25" s="285" t="n"/>
+      <c r="F25" s="285" t="n"/>
+      <c r="G25" s="285" t="n"/>
+      <c r="H25" s="285" t="n"/>
+      <c r="I25" s="285" t="n"/>
+      <c r="J25" s="285" t="n"/>
+      <c r="K25" s="285" t="n"/>
+      <c r="L25" s="285" t="n"/>
+      <c r="M25" s="285" t="n"/>
+      <c r="N25" s="285" t="n"/>
+      <c r="O25" s="285" t="n"/>
+      <c r="P25" s="285" t="n"/>
+      <c r="Q25" s="285" t="n"/>
+      <c r="R25" s="285" t="n"/>
+      <c r="S25" s="285" t="n"/>
+      <c r="T25" s="285" t="n"/>
+      <c r="U25" s="285" t="n"/>
+      <c r="V25" s="285" t="n"/>
+      <c r="W25" s="285" t="n"/>
+      <c r="X25" s="285" t="n"/>
+      <c r="Y25" s="285" t="n"/>
+      <c r="Z25" s="285" t="n"/>
+      <c r="AA25" s="285" t="n"/>
+      <c r="AB25" s="285" t="n"/>
+      <c r="AC25" s="285" t="n"/>
+      <c r="AD25" s="285" t="n"/>
+      <c r="AE25" s="285" t="n"/>
+      <c r="AF25" s="285" t="n"/>
+      <c r="AG25" s="285" t="n"/>
+      <c r="AH25" s="285" t="n"/>
+      <c r="AI25" s="285" t="n"/>
+      <c r="AJ25" s="285" t="n"/>
+      <c r="AK25" s="285" t="n"/>
+      <c r="AL25" s="285" t="n"/>
+      <c r="AM25" s="285" t="n"/>
+      <c r="AN25" s="286" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="329">
-      <c r="A26" s="477" t="inlineStr">
+      <c r="A26" s="639" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="552" t="n"/>
-      <c r="C26" s="479" t="inlineStr">
+      <c r="B26" s="285" t="n"/>
+      <c r="C26" s="640" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="552" t="n"/>
-      <c r="E26" s="552" t="n"/>
-      <c r="F26" s="479" t="inlineStr">
+      <c r="D26" s="285" t="n"/>
+      <c r="E26" s="285" t="n"/>
+      <c r="F26" s="640" t="inlineStr">
         <is>
           <t>Requirement / Check</t>
         </is>
       </c>
-      <c r="G26" s="552" t="n"/>
-      <c r="H26" s="552" t="n"/>
-      <c r="I26" s="552" t="n"/>
-      <c r="J26" s="552" t="n"/>
-      <c r="K26" s="552" t="n"/>
-      <c r="L26" s="552" t="n"/>
-      <c r="M26" s="552" t="n"/>
-      <c r="N26" s="552" t="n"/>
-      <c r="O26" s="552" t="n"/>
-      <c r="P26" s="552" t="n"/>
-      <c r="Q26" s="552" t="n"/>
-      <c r="R26" s="552" t="n"/>
-      <c r="S26" s="552" t="n"/>
-      <c r="T26" s="479" t="inlineStr">
+      <c r="G26" s="285" t="n"/>
+      <c r="H26" s="285" t="n"/>
+      <c r="I26" s="285" t="n"/>
+      <c r="J26" s="285" t="n"/>
+      <c r="K26" s="285" t="n"/>
+      <c r="L26" s="285" t="n"/>
+      <c r="M26" s="285" t="n"/>
+      <c r="N26" s="285" t="n"/>
+      <c r="O26" s="285" t="n"/>
+      <c r="P26" s="285" t="n"/>
+      <c r="Q26" s="285" t="n"/>
+      <c r="R26" s="285" t="n"/>
+      <c r="S26" s="285" t="n"/>
+      <c r="T26" s="640" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="552" t="n"/>
-      <c r="V26" s="552" t="n"/>
-      <c r="W26" s="552" t="n"/>
-      <c r="X26" s="552" t="n"/>
-      <c r="Y26" s="552" t="n"/>
-      <c r="Z26" s="552" t="n"/>
-      <c r="AA26" s="552" t="n"/>
-      <c r="AB26" s="552" t="n"/>
-      <c r="AC26" s="552" t="n"/>
-      <c r="AD26" s="552" t="n"/>
-      <c r="AE26" s="552" t="n"/>
-      <c r="AF26" s="479" t="inlineStr">
+      <c r="U26" s="285" t="n"/>
+      <c r="V26" s="285" t="n"/>
+      <c r="W26" s="285" t="n"/>
+      <c r="X26" s="285" t="n"/>
+      <c r="Y26" s="285" t="n"/>
+      <c r="Z26" s="285" t="n"/>
+      <c r="AA26" s="285" t="n"/>
+      <c r="AB26" s="285" t="n"/>
+      <c r="AC26" s="285" t="n"/>
+      <c r="AD26" s="285" t="n"/>
+      <c r="AE26" s="285" t="n"/>
+      <c r="AF26" s="640" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="552" t="n"/>
-      <c r="AH26" s="552" t="n"/>
-      <c r="AI26" s="552" t="n"/>
-      <c r="AJ26" s="479" t="inlineStr">
+      <c r="AG26" s="285" t="n"/>
+      <c r="AH26" s="285" t="n"/>
+      <c r="AI26" s="285" t="n"/>
+      <c r="AJ26" s="640" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="552" t="n"/>
-      <c r="AL26" s="552" t="n"/>
-      <c r="AM26" s="564" t="inlineStr">
+      <c r="AK26" s="285" t="n"/>
+      <c r="AL26" s="285" t="n"/>
+      <c r="AM26" s="641" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="553" t="n"/>
+      <c r="AN26" s="286" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="481">
+      <c r="A27" s="642">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="554" t="n"/>
-      <c r="C27" s="482" t="inlineStr">
+      <c r="B27" s="317" t="n"/>
+      <c r="C27" s="643" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="554" t="n"/>
-      <c r="E27" s="554" t="n"/>
-      <c r="F27" s="460" t="n"/>
-      <c r="G27" s="554" t="n"/>
-      <c r="H27" s="554" t="n"/>
-      <c r="I27" s="554" t="n"/>
-      <c r="J27" s="554" t="n"/>
-      <c r="K27" s="554" t="n"/>
-      <c r="L27" s="554" t="n"/>
-      <c r="M27" s="554" t="n"/>
-      <c r="N27" s="554" t="n"/>
-      <c r="O27" s="554" t="n"/>
-      <c r="P27" s="554" t="n"/>
-      <c r="Q27" s="554" t="n"/>
-      <c r="R27" s="554" t="n"/>
-      <c r="S27" s="554" t="n"/>
-      <c r="T27" s="483" t="n"/>
-      <c r="U27" s="554" t="n"/>
-      <c r="V27" s="554" t="n"/>
-      <c r="W27" s="554" t="n"/>
-      <c r="X27" s="554" t="n"/>
-      <c r="Y27" s="554" t="n"/>
-      <c r="Z27" s="554" t="n"/>
-      <c r="AA27" s="554" t="n"/>
-      <c r="AB27" s="554" t="n"/>
-      <c r="AC27" s="554" t="n"/>
-      <c r="AD27" s="554" t="n"/>
-      <c r="AE27" s="554" t="n"/>
-      <c r="AF27" s="460" t="n"/>
-      <c r="AG27" s="554" t="n"/>
-      <c r="AH27" s="554" t="n"/>
-      <c r="AI27" s="554" t="n"/>
-      <c r="AJ27" s="460" t="n"/>
-      <c r="AK27" s="554" t="n"/>
-      <c r="AL27" s="554" t="n"/>
-      <c r="AM27" s="565" t="n"/>
-      <c r="AN27" s="556" t="n"/>
+      <c r="D27" s="317" t="n"/>
+      <c r="E27" s="317" t="n"/>
+      <c r="F27" s="625" t="n"/>
+      <c r="G27" s="317" t="n"/>
+      <c r="H27" s="317" t="n"/>
+      <c r="I27" s="317" t="n"/>
+      <c r="J27" s="317" t="n"/>
+      <c r="K27" s="317" t="n"/>
+      <c r="L27" s="317" t="n"/>
+      <c r="M27" s="317" t="n"/>
+      <c r="N27" s="317" t="n"/>
+      <c r="O27" s="317" t="n"/>
+      <c r="P27" s="317" t="n"/>
+      <c r="Q27" s="317" t="n"/>
+      <c r="R27" s="317" t="n"/>
+      <c r="S27" s="317" t="n"/>
+      <c r="T27" s="644" t="n"/>
+      <c r="U27" s="317" t="n"/>
+      <c r="V27" s="317" t="n"/>
+      <c r="W27" s="317" t="n"/>
+      <c r="X27" s="317" t="n"/>
+      <c r="Y27" s="317" t="n"/>
+      <c r="Z27" s="317" t="n"/>
+      <c r="AA27" s="317" t="n"/>
+      <c r="AB27" s="317" t="n"/>
+      <c r="AC27" s="317" t="n"/>
+      <c r="AD27" s="317" t="n"/>
+      <c r="AE27" s="317" t="n"/>
+      <c r="AF27" s="625" t="n"/>
+      <c r="AG27" s="317" t="n"/>
+      <c r="AH27" s="317" t="n"/>
+      <c r="AI27" s="317" t="n"/>
+      <c r="AJ27" s="625" t="n"/>
+      <c r="AK27" s="317" t="n"/>
+      <c r="AL27" s="317" t="n"/>
+      <c r="AM27" s="645" t="n"/>
+      <c r="AN27" s="319" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="485">
+      <c r="A28" s="646">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="411" t="n"/>
-      <c r="C28" s="486" t="inlineStr">
+      <c r="B28" s="684" t="n"/>
+      <c r="C28" s="647" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="411" t="n"/>
-      <c r="E28" s="411" t="n"/>
-      <c r="F28" s="464" t="n"/>
-      <c r="G28" s="411" t="n"/>
-      <c r="H28" s="411" t="n"/>
-      <c r="I28" s="411" t="n"/>
-      <c r="J28" s="411" t="n"/>
-      <c r="K28" s="411" t="n"/>
-      <c r="L28" s="411" t="n"/>
-      <c r="M28" s="411" t="n"/>
-      <c r="N28" s="411" t="n"/>
-      <c r="O28" s="411" t="n"/>
-      <c r="P28" s="411" t="n"/>
-      <c r="Q28" s="411" t="n"/>
-      <c r="R28" s="411" t="n"/>
-      <c r="S28" s="411" t="n"/>
-      <c r="T28" s="487" t="n"/>
-      <c r="U28" s="411" t="n"/>
-      <c r="V28" s="411" t="n"/>
-      <c r="W28" s="411" t="n"/>
-      <c r="X28" s="411" t="n"/>
-      <c r="Y28" s="411" t="n"/>
-      <c r="Z28" s="411" t="n"/>
-      <c r="AA28" s="411" t="n"/>
-      <c r="AB28" s="411" t="n"/>
-      <c r="AC28" s="411" t="n"/>
-      <c r="AD28" s="411" t="n"/>
-      <c r="AE28" s="411" t="n"/>
-      <c r="AF28" s="464" t="n"/>
-      <c r="AG28" s="411" t="n"/>
-      <c r="AH28" s="411" t="n"/>
-      <c r="AI28" s="411" t="n"/>
-      <c r="AJ28" s="464" t="n"/>
-      <c r="AK28" s="411" t="n"/>
-      <c r="AL28" s="411" t="n"/>
-      <c r="AM28" s="566" t="n"/>
-      <c r="AN28" s="558" t="n"/>
+      <c r="D28" s="684" t="n"/>
+      <c r="E28" s="684" t="n"/>
+      <c r="F28" s="629" t="n"/>
+      <c r="G28" s="684" t="n"/>
+      <c r="H28" s="684" t="n"/>
+      <c r="I28" s="684" t="n"/>
+      <c r="J28" s="684" t="n"/>
+      <c r="K28" s="684" t="n"/>
+      <c r="L28" s="684" t="n"/>
+      <c r="M28" s="684" t="n"/>
+      <c r="N28" s="684" t="n"/>
+      <c r="O28" s="684" t="n"/>
+      <c r="P28" s="684" t="n"/>
+      <c r="Q28" s="684" t="n"/>
+      <c r="R28" s="684" t="n"/>
+      <c r="S28" s="684" t="n"/>
+      <c r="T28" s="648" t="n"/>
+      <c r="U28" s="684" t="n"/>
+      <c r="V28" s="684" t="n"/>
+      <c r="W28" s="684" t="n"/>
+      <c r="X28" s="684" t="n"/>
+      <c r="Y28" s="684" t="n"/>
+      <c r="Z28" s="684" t="n"/>
+      <c r="AA28" s="684" t="n"/>
+      <c r="AB28" s="684" t="n"/>
+      <c r="AC28" s="684" t="n"/>
+      <c r="AD28" s="684" t="n"/>
+      <c r="AE28" s="684" t="n"/>
+      <c r="AF28" s="629" t="n"/>
+      <c r="AG28" s="684" t="n"/>
+      <c r="AH28" s="684" t="n"/>
+      <c r="AI28" s="684" t="n"/>
+      <c r="AJ28" s="629" t="n"/>
+      <c r="AK28" s="684" t="n"/>
+      <c r="AL28" s="684" t="n"/>
+      <c r="AM28" s="649" t="n"/>
+      <c r="AN28" s="685" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="485">
+      <c r="A29" s="646">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="411" t="n"/>
-      <c r="C29" s="486" t="inlineStr">
+      <c r="B29" s="684" t="n"/>
+      <c r="C29" s="647" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="411" t="n"/>
-      <c r="E29" s="411" t="n"/>
-      <c r="F29" s="464" t="n"/>
-      <c r="G29" s="411" t="n"/>
-      <c r="H29" s="411" t="n"/>
-      <c r="I29" s="411" t="n"/>
-      <c r="J29" s="411" t="n"/>
-      <c r="K29" s="411" t="n"/>
-      <c r="L29" s="411" t="n"/>
-      <c r="M29" s="411" t="n"/>
-      <c r="N29" s="411" t="n"/>
-      <c r="O29" s="411" t="n"/>
-      <c r="P29" s="411" t="n"/>
-      <c r="Q29" s="411" t="n"/>
-      <c r="R29" s="411" t="n"/>
-      <c r="S29" s="411" t="n"/>
-      <c r="T29" s="487" t="n"/>
-      <c r="U29" s="411" t="n"/>
-      <c r="V29" s="411" t="n"/>
-      <c r="W29" s="411" t="n"/>
-      <c r="X29" s="411" t="n"/>
-      <c r="Y29" s="411" t="n"/>
-      <c r="Z29" s="411" t="n"/>
-      <c r="AA29" s="411" t="n"/>
-      <c r="AB29" s="411" t="n"/>
-      <c r="AC29" s="411" t="n"/>
-      <c r="AD29" s="411" t="n"/>
-      <c r="AE29" s="411" t="n"/>
-      <c r="AF29" s="464" t="n"/>
-      <c r="AG29" s="411" t="n"/>
-      <c r="AH29" s="411" t="n"/>
-      <c r="AI29" s="411" t="n"/>
-      <c r="AJ29" s="464" t="n"/>
-      <c r="AK29" s="411" t="n"/>
-      <c r="AL29" s="411" t="n"/>
-      <c r="AM29" s="566" t="n"/>
-      <c r="AN29" s="558" t="n"/>
+      <c r="D29" s="684" t="n"/>
+      <c r="E29" s="684" t="n"/>
+      <c r="F29" s="629" t="n"/>
+      <c r="G29" s="684" t="n"/>
+      <c r="H29" s="684" t="n"/>
+      <c r="I29" s="684" t="n"/>
+      <c r="J29" s="684" t="n"/>
+      <c r="K29" s="684" t="n"/>
+      <c r="L29" s="684" t="n"/>
+      <c r="M29" s="684" t="n"/>
+      <c r="N29" s="684" t="n"/>
+      <c r="O29" s="684" t="n"/>
+      <c r="P29" s="684" t="n"/>
+      <c r="Q29" s="684" t="n"/>
+      <c r="R29" s="684" t="n"/>
+      <c r="S29" s="684" t="n"/>
+      <c r="T29" s="648" t="n"/>
+      <c r="U29" s="684" t="n"/>
+      <c r="V29" s="684" t="n"/>
+      <c r="W29" s="684" t="n"/>
+      <c r="X29" s="684" t="n"/>
+      <c r="Y29" s="684" t="n"/>
+      <c r="Z29" s="684" t="n"/>
+      <c r="AA29" s="684" t="n"/>
+      <c r="AB29" s="684" t="n"/>
+      <c r="AC29" s="684" t="n"/>
+      <c r="AD29" s="684" t="n"/>
+      <c r="AE29" s="684" t="n"/>
+      <c r="AF29" s="629" t="n"/>
+      <c r="AG29" s="684" t="n"/>
+      <c r="AH29" s="684" t="n"/>
+      <c r="AI29" s="684" t="n"/>
+      <c r="AJ29" s="629" t="n"/>
+      <c r="AK29" s="684" t="n"/>
+      <c r="AL29" s="684" t="n"/>
+      <c r="AM29" s="649" t="n"/>
+      <c r="AN29" s="685" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="485">
+      <c r="A30" s="646">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="411" t="n"/>
-      <c r="C30" s="486" t="inlineStr">
+      <c r="B30" s="684" t="n"/>
+      <c r="C30" s="647" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="411" t="n"/>
-      <c r="E30" s="411" t="n"/>
-      <c r="F30" s="464" t="n"/>
-      <c r="G30" s="411" t="n"/>
-      <c r="H30" s="411" t="n"/>
-      <c r="I30" s="411" t="n"/>
-      <c r="J30" s="411" t="n"/>
-      <c r="K30" s="411" t="n"/>
-      <c r="L30" s="411" t="n"/>
-      <c r="M30" s="411" t="n"/>
-      <c r="N30" s="411" t="n"/>
-      <c r="O30" s="411" t="n"/>
-      <c r="P30" s="411" t="n"/>
-      <c r="Q30" s="411" t="n"/>
-      <c r="R30" s="411" t="n"/>
-      <c r="S30" s="411" t="n"/>
-      <c r="T30" s="487" t="n"/>
-      <c r="U30" s="411" t="n"/>
-      <c r="V30" s="411" t="n"/>
-      <c r="W30" s="411" t="n"/>
-      <c r="X30" s="411" t="n"/>
-      <c r="Y30" s="411" t="n"/>
-      <c r="Z30" s="411" t="n"/>
-      <c r="AA30" s="411" t="n"/>
-      <c r="AB30" s="411" t="n"/>
-      <c r="AC30" s="411" t="n"/>
-      <c r="AD30" s="411" t="n"/>
-      <c r="AE30" s="411" t="n"/>
-      <c r="AF30" s="464" t="n"/>
-      <c r="AG30" s="411" t="n"/>
-      <c r="AH30" s="411" t="n"/>
-      <c r="AI30" s="411" t="n"/>
-      <c r="AJ30" s="464" t="n"/>
-      <c r="AK30" s="411" t="n"/>
-      <c r="AL30" s="411" t="n"/>
-      <c r="AM30" s="566" t="n"/>
-      <c r="AN30" s="558" t="n"/>
+      <c r="D30" s="684" t="n"/>
+      <c r="E30" s="684" t="n"/>
+      <c r="F30" s="629" t="n"/>
+      <c r="G30" s="684" t="n"/>
+      <c r="H30" s="684" t="n"/>
+      <c r="I30" s="684" t="n"/>
+      <c r="J30" s="684" t="n"/>
+      <c r="K30" s="684" t="n"/>
+      <c r="L30" s="684" t="n"/>
+      <c r="M30" s="684" t="n"/>
+      <c r="N30" s="684" t="n"/>
+      <c r="O30" s="684" t="n"/>
+      <c r="P30" s="684" t="n"/>
+      <c r="Q30" s="684" t="n"/>
+      <c r="R30" s="684" t="n"/>
+      <c r="S30" s="684" t="n"/>
+      <c r="T30" s="648" t="n"/>
+      <c r="U30" s="684" t="n"/>
+      <c r="V30" s="684" t="n"/>
+      <c r="W30" s="684" t="n"/>
+      <c r="X30" s="684" t="n"/>
+      <c r="Y30" s="684" t="n"/>
+      <c r="Z30" s="684" t="n"/>
+      <c r="AA30" s="684" t="n"/>
+      <c r="AB30" s="684" t="n"/>
+      <c r="AC30" s="684" t="n"/>
+      <c r="AD30" s="684" t="n"/>
+      <c r="AE30" s="684" t="n"/>
+      <c r="AF30" s="629" t="n"/>
+      <c r="AG30" s="684" t="n"/>
+      <c r="AH30" s="684" t="n"/>
+      <c r="AI30" s="684" t="n"/>
+      <c r="AJ30" s="629" t="n"/>
+      <c r="AK30" s="684" t="n"/>
+      <c r="AL30" s="684" t="n"/>
+      <c r="AM30" s="649" t="n"/>
+      <c r="AN30" s="685" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="485">
+      <c r="A31" s="646">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="411" t="n"/>
-      <c r="C31" s="486" t="inlineStr">
+      <c r="B31" s="684" t="n"/>
+      <c r="C31" s="647" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="411" t="n"/>
-      <c r="E31" s="411" t="n"/>
-      <c r="F31" s="464" t="n"/>
-      <c r="G31" s="411" t="n"/>
-      <c r="H31" s="411" t="n"/>
-      <c r="I31" s="411" t="n"/>
-      <c r="J31" s="411" t="n"/>
-      <c r="K31" s="411" t="n"/>
-      <c r="L31" s="411" t="n"/>
-      <c r="M31" s="411" t="n"/>
-      <c r="N31" s="411" t="n"/>
-      <c r="O31" s="411" t="n"/>
-      <c r="P31" s="411" t="n"/>
-      <c r="Q31" s="411" t="n"/>
-      <c r="R31" s="411" t="n"/>
-      <c r="S31" s="411" t="n"/>
-      <c r="T31" s="487" t="n"/>
-      <c r="U31" s="411" t="n"/>
-      <c r="V31" s="411" t="n"/>
-      <c r="W31" s="411" t="n"/>
-      <c r="X31" s="411" t="n"/>
-      <c r="Y31" s="411" t="n"/>
-      <c r="Z31" s="411" t="n"/>
-      <c r="AA31" s="411" t="n"/>
-      <c r="AB31" s="411" t="n"/>
-      <c r="AC31" s="411" t="n"/>
-      <c r="AD31" s="411" t="n"/>
-      <c r="AE31" s="411" t="n"/>
-      <c r="AF31" s="464" t="n"/>
-      <c r="AG31" s="411" t="n"/>
-      <c r="AH31" s="411" t="n"/>
-      <c r="AI31" s="411" t="n"/>
-      <c r="AJ31" s="464" t="n"/>
-      <c r="AK31" s="411" t="n"/>
-      <c r="AL31" s="411" t="n"/>
-      <c r="AM31" s="566" t="n"/>
-      <c r="AN31" s="558" t="n"/>
+      <c r="D31" s="684" t="n"/>
+      <c r="E31" s="684" t="n"/>
+      <c r="F31" s="629" t="n"/>
+      <c r="G31" s="684" t="n"/>
+      <c r="H31" s="684" t="n"/>
+      <c r="I31" s="684" t="n"/>
+      <c r="J31" s="684" t="n"/>
+      <c r="K31" s="684" t="n"/>
+      <c r="L31" s="684" t="n"/>
+      <c r="M31" s="684" t="n"/>
+      <c r="N31" s="684" t="n"/>
+      <c r="O31" s="684" t="n"/>
+      <c r="P31" s="684" t="n"/>
+      <c r="Q31" s="684" t="n"/>
+      <c r="R31" s="684" t="n"/>
+      <c r="S31" s="684" t="n"/>
+      <c r="T31" s="648" t="n"/>
+      <c r="U31" s="684" t="n"/>
+      <c r="V31" s="684" t="n"/>
+      <c r="W31" s="684" t="n"/>
+      <c r="X31" s="684" t="n"/>
+      <c r="Y31" s="684" t="n"/>
+      <c r="Z31" s="684" t="n"/>
+      <c r="AA31" s="684" t="n"/>
+      <c r="AB31" s="684" t="n"/>
+      <c r="AC31" s="684" t="n"/>
+      <c r="AD31" s="684" t="n"/>
+      <c r="AE31" s="684" t="n"/>
+      <c r="AF31" s="629" t="n"/>
+      <c r="AG31" s="684" t="n"/>
+      <c r="AH31" s="684" t="n"/>
+      <c r="AI31" s="684" t="n"/>
+      <c r="AJ31" s="629" t="n"/>
+      <c r="AK31" s="684" t="n"/>
+      <c r="AL31" s="684" t="n"/>
+      <c r="AM31" s="649" t="n"/>
+      <c r="AN31" s="685" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="489">
+      <c r="A32" s="650">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="547" t="n"/>
-      <c r="C32" s="490" t="inlineStr">
+      <c r="B32" s="686" t="n"/>
+      <c r="C32" s="651" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="547" t="n"/>
-      <c r="E32" s="547" t="n"/>
-      <c r="F32" s="469" t="n"/>
-      <c r="G32" s="547" t="n"/>
-      <c r="H32" s="547" t="n"/>
-      <c r="I32" s="547" t="n"/>
-      <c r="J32" s="547" t="n"/>
-      <c r="K32" s="547" t="n"/>
-      <c r="L32" s="547" t="n"/>
-      <c r="M32" s="547" t="n"/>
-      <c r="N32" s="547" t="n"/>
-      <c r="O32" s="547" t="n"/>
-      <c r="P32" s="547" t="n"/>
-      <c r="Q32" s="547" t="n"/>
-      <c r="R32" s="547" t="n"/>
-      <c r="S32" s="547" t="n"/>
-      <c r="T32" s="491" t="n"/>
-      <c r="U32" s="547" t="n"/>
-      <c r="V32" s="547" t="n"/>
-      <c r="W32" s="547" t="n"/>
-      <c r="X32" s="547" t="n"/>
-      <c r="Y32" s="547" t="n"/>
-      <c r="Z32" s="547" t="n"/>
-      <c r="AA32" s="547" t="n"/>
-      <c r="AB32" s="547" t="n"/>
-      <c r="AC32" s="547" t="n"/>
-      <c r="AD32" s="547" t="n"/>
-      <c r="AE32" s="547" t="n"/>
-      <c r="AF32" s="469" t="n"/>
-      <c r="AG32" s="547" t="n"/>
-      <c r="AH32" s="547" t="n"/>
-      <c r="AI32" s="547" t="n"/>
-      <c r="AJ32" s="469" t="n"/>
-      <c r="AK32" s="547" t="n"/>
-      <c r="AL32" s="547" t="n"/>
-      <c r="AM32" s="567" t="n"/>
-      <c r="AN32" s="550" t="n"/>
+      <c r="D32" s="686" t="n"/>
+      <c r="E32" s="686" t="n"/>
+      <c r="F32" s="633" t="n"/>
+      <c r="G32" s="686" t="n"/>
+      <c r="H32" s="686" t="n"/>
+      <c r="I32" s="686" t="n"/>
+      <c r="J32" s="686" t="n"/>
+      <c r="K32" s="686" t="n"/>
+      <c r="L32" s="686" t="n"/>
+      <c r="M32" s="686" t="n"/>
+      <c r="N32" s="686" t="n"/>
+      <c r="O32" s="686" t="n"/>
+      <c r="P32" s="686" t="n"/>
+      <c r="Q32" s="686" t="n"/>
+      <c r="R32" s="686" t="n"/>
+      <c r="S32" s="686" t="n"/>
+      <c r="T32" s="652" t="n"/>
+      <c r="U32" s="686" t="n"/>
+      <c r="V32" s="686" t="n"/>
+      <c r="W32" s="686" t="n"/>
+      <c r="X32" s="686" t="n"/>
+      <c r="Y32" s="686" t="n"/>
+      <c r="Z32" s="686" t="n"/>
+      <c r="AA32" s="686" t="n"/>
+      <c r="AB32" s="686" t="n"/>
+      <c r="AC32" s="686" t="n"/>
+      <c r="AD32" s="686" t="n"/>
+      <c r="AE32" s="686" t="n"/>
+      <c r="AF32" s="633" t="n"/>
+      <c r="AG32" s="686" t="n"/>
+      <c r="AH32" s="686" t="n"/>
+      <c r="AI32" s="686" t="n"/>
+      <c r="AJ32" s="633" t="n"/>
+      <c r="AK32" s="686" t="n"/>
+      <c r="AL32" s="686" t="n"/>
+      <c r="AM32" s="653" t="n"/>
+      <c r="AN32" s="687" t="n"/>
     </row>
     <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="359" t="n"/>
@@ -7885,150 +8495,150 @@
       <c r="AN33" s="352" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="329">
-      <c r="A34" s="551" t="inlineStr">
+      <c r="A34" s="636" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="552" t="n"/>
-      <c r="C34" s="552" t="n"/>
-      <c r="D34" s="552" t="n"/>
-      <c r="E34" s="552" t="n"/>
-      <c r="F34" s="552" t="n"/>
-      <c r="G34" s="552" t="n"/>
-      <c r="H34" s="552" t="n"/>
-      <c r="I34" s="552" t="n"/>
-      <c r="J34" s="552" t="n"/>
-      <c r="K34" s="552" t="n"/>
-      <c r="L34" s="552" t="n"/>
-      <c r="M34" s="552" t="n"/>
-      <c r="N34" s="552" t="n"/>
-      <c r="O34" s="552" t="n"/>
-      <c r="P34" s="552" t="n"/>
-      <c r="Q34" s="552" t="n"/>
-      <c r="R34" s="552" t="n"/>
-      <c r="S34" s="552" t="n"/>
-      <c r="T34" s="552" t="n"/>
-      <c r="U34" s="552" t="n"/>
-      <c r="V34" s="552" t="n"/>
-      <c r="W34" s="552" t="n"/>
-      <c r="X34" s="552" t="n"/>
-      <c r="Y34" s="552" t="n"/>
-      <c r="Z34" s="552" t="n"/>
-      <c r="AA34" s="552" t="n"/>
-      <c r="AB34" s="552" t="n"/>
-      <c r="AC34" s="552" t="n"/>
-      <c r="AD34" s="552" t="n"/>
-      <c r="AE34" s="552" t="n"/>
-      <c r="AF34" s="552" t="n"/>
-      <c r="AG34" s="552" t="n"/>
-      <c r="AH34" s="552" t="n"/>
-      <c r="AI34" s="552" t="n"/>
-      <c r="AJ34" s="552" t="n"/>
-      <c r="AK34" s="552" t="n"/>
-      <c r="AL34" s="552" t="n"/>
-      <c r="AM34" s="552" t="n"/>
-      <c r="AN34" s="553" t="n"/>
+      <c r="B34" s="285" t="n"/>
+      <c r="C34" s="285" t="n"/>
+      <c r="D34" s="285" t="n"/>
+      <c r="E34" s="285" t="n"/>
+      <c r="F34" s="285" t="n"/>
+      <c r="G34" s="285" t="n"/>
+      <c r="H34" s="285" t="n"/>
+      <c r="I34" s="285" t="n"/>
+      <c r="J34" s="285" t="n"/>
+      <c r="K34" s="285" t="n"/>
+      <c r="L34" s="285" t="n"/>
+      <c r="M34" s="285" t="n"/>
+      <c r="N34" s="285" t="n"/>
+      <c r="O34" s="285" t="n"/>
+      <c r="P34" s="285" t="n"/>
+      <c r="Q34" s="285" t="n"/>
+      <c r="R34" s="285" t="n"/>
+      <c r="S34" s="285" t="n"/>
+      <c r="T34" s="285" t="n"/>
+      <c r="U34" s="285" t="n"/>
+      <c r="V34" s="285" t="n"/>
+      <c r="W34" s="285" t="n"/>
+      <c r="X34" s="285" t="n"/>
+      <c r="Y34" s="285" t="n"/>
+      <c r="Z34" s="285" t="n"/>
+      <c r="AA34" s="285" t="n"/>
+      <c r="AB34" s="285" t="n"/>
+      <c r="AC34" s="285" t="n"/>
+      <c r="AD34" s="285" t="n"/>
+      <c r="AE34" s="285" t="n"/>
+      <c r="AF34" s="285" t="n"/>
+      <c r="AG34" s="285" t="n"/>
+      <c r="AH34" s="285" t="n"/>
+      <c r="AI34" s="285" t="n"/>
+      <c r="AJ34" s="285" t="n"/>
+      <c r="AK34" s="285" t="n"/>
+      <c r="AL34" s="285" t="n"/>
+      <c r="AM34" s="285" t="n"/>
+      <c r="AN34" s="286" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="458" t="inlineStr">
+      <c r="A35" s="624" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="554" t="n"/>
-      <c r="C35" s="554" t="n"/>
-      <c r="D35" s="554" t="n"/>
-      <c r="E35" s="554" t="n"/>
-      <c r="F35" s="554" t="n"/>
-      <c r="G35" s="554" t="n"/>
-      <c r="H35" s="460" t="n"/>
-      <c r="I35" s="554" t="n"/>
-      <c r="J35" s="554" t="n"/>
-      <c r="K35" s="554" t="n"/>
-      <c r="L35" s="554" t="n"/>
-      <c r="M35" s="554" t="n"/>
-      <c r="N35" s="554" t="n"/>
-      <c r="O35" s="554" t="n"/>
-      <c r="P35" s="554" t="n"/>
-      <c r="Q35" s="554" t="n"/>
-      <c r="R35" s="554" t="n"/>
-      <c r="S35" s="554" t="n"/>
-      <c r="T35" s="554" t="n"/>
-      <c r="U35" s="461" t="inlineStr">
+      <c r="B35" s="317" t="n"/>
+      <c r="C35" s="317" t="n"/>
+      <c r="D35" s="317" t="n"/>
+      <c r="E35" s="317" t="n"/>
+      <c r="F35" s="317" t="n"/>
+      <c r="G35" s="317" t="n"/>
+      <c r="H35" s="625" t="n"/>
+      <c r="I35" s="317" t="n"/>
+      <c r="J35" s="317" t="n"/>
+      <c r="K35" s="317" t="n"/>
+      <c r="L35" s="317" t="n"/>
+      <c r="M35" s="317" t="n"/>
+      <c r="N35" s="317" t="n"/>
+      <c r="O35" s="317" t="n"/>
+      <c r="P35" s="317" t="n"/>
+      <c r="Q35" s="317" t="n"/>
+      <c r="R35" s="317" t="n"/>
+      <c r="S35" s="317" t="n"/>
+      <c r="T35" s="317" t="n"/>
+      <c r="U35" s="626" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="554" t="n"/>
-      <c r="W35" s="554" t="n"/>
-      <c r="X35" s="554" t="n"/>
-      <c r="Y35" s="554" t="n"/>
-      <c r="Z35" s="554" t="n"/>
-      <c r="AA35" s="554" t="n"/>
-      <c r="AB35" s="555" t="n"/>
-      <c r="AC35" s="554" t="n"/>
-      <c r="AD35" s="554" t="n"/>
-      <c r="AE35" s="554" t="n"/>
-      <c r="AF35" s="554" t="n"/>
-      <c r="AG35" s="554" t="n"/>
-      <c r="AH35" s="554" t="n"/>
-      <c r="AI35" s="554" t="n"/>
-      <c r="AJ35" s="554" t="n"/>
-      <c r="AK35" s="554" t="n"/>
-      <c r="AL35" s="554" t="n"/>
-      <c r="AM35" s="554" t="n"/>
-      <c r="AN35" s="556" t="n"/>
+      <c r="V35" s="317" t="n"/>
+      <c r="W35" s="317" t="n"/>
+      <c r="X35" s="317" t="n"/>
+      <c r="Y35" s="317" t="n"/>
+      <c r="Z35" s="317" t="n"/>
+      <c r="AA35" s="317" t="n"/>
+      <c r="AB35" s="627" t="n"/>
+      <c r="AC35" s="317" t="n"/>
+      <c r="AD35" s="317" t="n"/>
+      <c r="AE35" s="317" t="n"/>
+      <c r="AF35" s="317" t="n"/>
+      <c r="AG35" s="317" t="n"/>
+      <c r="AH35" s="317" t="n"/>
+      <c r="AI35" s="317" t="n"/>
+      <c r="AJ35" s="317" t="n"/>
+      <c r="AK35" s="317" t="n"/>
+      <c r="AL35" s="317" t="n"/>
+      <c r="AM35" s="317" t="n"/>
+      <c r="AN35" s="319" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="467" t="inlineStr">
+      <c r="A36" s="632" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="547" t="n"/>
-      <c r="C36" s="547" t="n"/>
-      <c r="D36" s="547" t="n"/>
-      <c r="E36" s="547" t="n"/>
-      <c r="F36" s="547" t="n"/>
-      <c r="G36" s="547" t="n"/>
-      <c r="H36" s="469" t="n"/>
-      <c r="I36" s="547" t="n"/>
-      <c r="J36" s="547" t="n"/>
-      <c r="K36" s="547" t="n"/>
-      <c r="L36" s="547" t="n"/>
-      <c r="M36" s="547" t="n"/>
-      <c r="N36" s="547" t="n"/>
-      <c r="O36" s="547" t="n"/>
-      <c r="P36" s="547" t="n"/>
-      <c r="Q36" s="547" t="n"/>
-      <c r="R36" s="547" t="n"/>
-      <c r="S36" s="547" t="n"/>
-      <c r="T36" s="547" t="n"/>
-      <c r="U36" s="470" t="inlineStr">
+      <c r="B36" s="686" t="n"/>
+      <c r="C36" s="686" t="n"/>
+      <c r="D36" s="686" t="n"/>
+      <c r="E36" s="686" t="n"/>
+      <c r="F36" s="686" t="n"/>
+      <c r="G36" s="686" t="n"/>
+      <c r="H36" s="633" t="n"/>
+      <c r="I36" s="686" t="n"/>
+      <c r="J36" s="686" t="n"/>
+      <c r="K36" s="686" t="n"/>
+      <c r="L36" s="686" t="n"/>
+      <c r="M36" s="686" t="n"/>
+      <c r="N36" s="686" t="n"/>
+      <c r="O36" s="686" t="n"/>
+      <c r="P36" s="686" t="n"/>
+      <c r="Q36" s="686" t="n"/>
+      <c r="R36" s="686" t="n"/>
+      <c r="S36" s="686" t="n"/>
+      <c r="T36" s="686" t="n"/>
+      <c r="U36" s="634" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="547" t="n"/>
-      <c r="W36" s="547" t="n"/>
-      <c r="X36" s="547" t="n"/>
-      <c r="Y36" s="547" t="n"/>
-      <c r="Z36" s="547" t="n"/>
-      <c r="AA36" s="547" t="n"/>
-      <c r="AB36" s="559" t="n"/>
-      <c r="AC36" s="547" t="n"/>
-      <c r="AD36" s="547" t="n"/>
-      <c r="AE36" s="547" t="n"/>
-      <c r="AF36" s="547" t="n"/>
-      <c r="AG36" s="547" t="n"/>
-      <c r="AH36" s="547" t="n"/>
-      <c r="AI36" s="547" t="n"/>
-      <c r="AJ36" s="547" t="n"/>
-      <c r="AK36" s="547" t="n"/>
-      <c r="AL36" s="547" t="n"/>
-      <c r="AM36" s="547" t="n"/>
-      <c r="AN36" s="550" t="n"/>
+      <c r="V36" s="686" t="n"/>
+      <c r="W36" s="686" t="n"/>
+      <c r="X36" s="686" t="n"/>
+      <c r="Y36" s="686" t="n"/>
+      <c r="Z36" s="686" t="n"/>
+      <c r="AA36" s="686" t="n"/>
+      <c r="AB36" s="635" t="n"/>
+      <c r="AC36" s="686" t="n"/>
+      <c r="AD36" s="686" t="n"/>
+      <c r="AE36" s="686" t="n"/>
+      <c r="AF36" s="686" t="n"/>
+      <c r="AG36" s="686" t="n"/>
+      <c r="AH36" s="686" t="n"/>
+      <c r="AI36" s="686" t="n"/>
+      <c r="AJ36" s="686" t="n"/>
+      <c r="AK36" s="686" t="n"/>
+      <c r="AL36" s="686" t="n"/>
+      <c r="AM36" s="686" t="n"/>
+      <c r="AN36" s="687" t="n"/>
     </row>
     <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="364" t="n"/>
@@ -8073,206 +8683,206 @@
       <c r="AN37" s="352" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="329">
-      <c r="A38" s="551" t="inlineStr">
+      <c r="A38" s="636" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="552" t="n"/>
-      <c r="C38" s="552" t="n"/>
-      <c r="D38" s="552" t="n"/>
-      <c r="E38" s="552" t="n"/>
-      <c r="F38" s="552" t="n"/>
-      <c r="G38" s="552" t="n"/>
-      <c r="H38" s="552" t="n"/>
-      <c r="I38" s="552" t="n"/>
-      <c r="J38" s="552" t="n"/>
-      <c r="K38" s="552" t="n"/>
-      <c r="L38" s="552" t="n"/>
-      <c r="M38" s="552" t="n"/>
-      <c r="N38" s="552" t="n"/>
-      <c r="O38" s="552" t="n"/>
-      <c r="P38" s="552" t="n"/>
-      <c r="Q38" s="552" t="n"/>
-      <c r="R38" s="552" t="n"/>
-      <c r="S38" s="552" t="n"/>
-      <c r="T38" s="552" t="n"/>
-      <c r="U38" s="552" t="n"/>
-      <c r="V38" s="552" t="n"/>
-      <c r="W38" s="552" t="n"/>
-      <c r="X38" s="552" t="n"/>
-      <c r="Y38" s="552" t="n"/>
-      <c r="Z38" s="552" t="n"/>
-      <c r="AA38" s="552" t="n"/>
-      <c r="AB38" s="552" t="n"/>
-      <c r="AC38" s="552" t="n"/>
-      <c r="AD38" s="552" t="n"/>
-      <c r="AE38" s="552" t="n"/>
-      <c r="AF38" s="552" t="n"/>
-      <c r="AG38" s="552" t="n"/>
-      <c r="AH38" s="552" t="n"/>
-      <c r="AI38" s="552" t="n"/>
-      <c r="AJ38" s="552" t="n"/>
-      <c r="AK38" s="552" t="n"/>
-      <c r="AL38" s="552" t="n"/>
-      <c r="AM38" s="552" t="n"/>
-      <c r="AN38" s="553" t="n"/>
+      <c r="B38" s="285" t="n"/>
+      <c r="C38" s="285" t="n"/>
+      <c r="D38" s="285" t="n"/>
+      <c r="E38" s="285" t="n"/>
+      <c r="F38" s="285" t="n"/>
+      <c r="G38" s="285" t="n"/>
+      <c r="H38" s="285" t="n"/>
+      <c r="I38" s="285" t="n"/>
+      <c r="J38" s="285" t="n"/>
+      <c r="K38" s="285" t="n"/>
+      <c r="L38" s="285" t="n"/>
+      <c r="M38" s="285" t="n"/>
+      <c r="N38" s="285" t="n"/>
+      <c r="O38" s="285" t="n"/>
+      <c r="P38" s="285" t="n"/>
+      <c r="Q38" s="285" t="n"/>
+      <c r="R38" s="285" t="n"/>
+      <c r="S38" s="285" t="n"/>
+      <c r="T38" s="285" t="n"/>
+      <c r="U38" s="285" t="n"/>
+      <c r="V38" s="285" t="n"/>
+      <c r="W38" s="285" t="n"/>
+      <c r="X38" s="285" t="n"/>
+      <c r="Y38" s="285" t="n"/>
+      <c r="Z38" s="285" t="n"/>
+      <c r="AA38" s="285" t="n"/>
+      <c r="AB38" s="285" t="n"/>
+      <c r="AC38" s="285" t="n"/>
+      <c r="AD38" s="285" t="n"/>
+      <c r="AE38" s="285" t="n"/>
+      <c r="AF38" s="285" t="n"/>
+      <c r="AG38" s="285" t="n"/>
+      <c r="AH38" s="285" t="n"/>
+      <c r="AI38" s="285" t="n"/>
+      <c r="AJ38" s="285" t="n"/>
+      <c r="AK38" s="285" t="n"/>
+      <c r="AL38" s="285" t="n"/>
+      <c r="AM38" s="285" t="n"/>
+      <c r="AN38" s="286" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="329">
-      <c r="A39" s="481" t="inlineStr">
+      <c r="A39" s="642" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="554" t="n"/>
-      <c r="C39" s="554" t="n"/>
-      <c r="D39" s="554" t="n"/>
-      <c r="E39" s="554" t="n"/>
-      <c r="F39" s="554" t="n"/>
-      <c r="G39" s="554" t="n"/>
-      <c r="H39" s="554" t="n"/>
-      <c r="I39" s="554" t="n"/>
-      <c r="J39" s="554" t="n"/>
-      <c r="K39" s="554" t="n"/>
-      <c r="L39" s="554" t="n"/>
-      <c r="M39" s="554" t="n"/>
-      <c r="N39" s="493" t="inlineStr">
+      <c r="B39" s="317" t="n"/>
+      <c r="C39" s="317" t="n"/>
+      <c r="D39" s="317" t="n"/>
+      <c r="E39" s="317" t="n"/>
+      <c r="F39" s="317" t="n"/>
+      <c r="G39" s="317" t="n"/>
+      <c r="H39" s="317" t="n"/>
+      <c r="I39" s="317" t="n"/>
+      <c r="J39" s="317" t="n"/>
+      <c r="K39" s="317" t="n"/>
+      <c r="L39" s="317" t="n"/>
+      <c r="M39" s="317" t="n"/>
+      <c r="N39" s="654" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="554" t="n"/>
-      <c r="P39" s="554" t="n"/>
-      <c r="Q39" s="554" t="n"/>
-      <c r="R39" s="554" t="n"/>
-      <c r="S39" s="554" t="n"/>
-      <c r="T39" s="554" t="n"/>
-      <c r="U39" s="554" t="n"/>
-      <c r="V39" s="554" t="n"/>
-      <c r="W39" s="554" t="n"/>
-      <c r="X39" s="554" t="n"/>
-      <c r="Y39" s="554" t="n"/>
-      <c r="Z39" s="554" t="n"/>
-      <c r="AA39" s="568" t="inlineStr">
+      <c r="O39" s="317" t="n"/>
+      <c r="P39" s="317" t="n"/>
+      <c r="Q39" s="317" t="n"/>
+      <c r="R39" s="317" t="n"/>
+      <c r="S39" s="317" t="n"/>
+      <c r="T39" s="317" t="n"/>
+      <c r="U39" s="317" t="n"/>
+      <c r="V39" s="317" t="n"/>
+      <c r="W39" s="317" t="n"/>
+      <c r="X39" s="317" t="n"/>
+      <c r="Y39" s="317" t="n"/>
+      <c r="Z39" s="317" t="n"/>
+      <c r="AA39" s="655" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="554" t="n"/>
-      <c r="AC39" s="554" t="n"/>
-      <c r="AD39" s="554" t="n"/>
-      <c r="AE39" s="554" t="n"/>
-      <c r="AF39" s="554" t="n"/>
-      <c r="AG39" s="554" t="n"/>
-      <c r="AH39" s="554" t="n"/>
-      <c r="AI39" s="554" t="n"/>
-      <c r="AJ39" s="554" t="n"/>
-      <c r="AK39" s="554" t="n"/>
-      <c r="AL39" s="554" t="n"/>
-      <c r="AM39" s="554" t="n"/>
-      <c r="AN39" s="556" t="n"/>
+      <c r="AB39" s="317" t="n"/>
+      <c r="AC39" s="317" t="n"/>
+      <c r="AD39" s="317" t="n"/>
+      <c r="AE39" s="317" t="n"/>
+      <c r="AF39" s="317" t="n"/>
+      <c r="AG39" s="317" t="n"/>
+      <c r="AH39" s="317" t="n"/>
+      <c r="AI39" s="317" t="n"/>
+      <c r="AJ39" s="317" t="n"/>
+      <c r="AK39" s="317" t="n"/>
+      <c r="AL39" s="317" t="n"/>
+      <c r="AM39" s="317" t="n"/>
+      <c r="AN39" s="319" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1" s="329">
-      <c r="A40" s="494" t="inlineStr">
+      <c r="A40" s="656" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="410" t="n"/>
-      <c r="C40" s="410" t="n"/>
-      <c r="D40" s="410" t="n"/>
-      <c r="E40" s="410" t="n"/>
-      <c r="F40" s="410" t="n"/>
-      <c r="G40" s="410" t="n"/>
-      <c r="H40" s="410" t="n"/>
-      <c r="I40" s="410" t="n"/>
-      <c r="J40" s="410" t="n"/>
-      <c r="K40" s="410" t="n"/>
-      <c r="L40" s="410" t="n"/>
-      <c r="M40" s="410" t="n"/>
-      <c r="N40" s="495" t="inlineStr">
+      <c r="B40" s="688" t="n"/>
+      <c r="C40" s="688" t="n"/>
+      <c r="D40" s="688" t="n"/>
+      <c r="E40" s="688" t="n"/>
+      <c r="F40" s="688" t="n"/>
+      <c r="G40" s="688" t="n"/>
+      <c r="H40" s="688" t="n"/>
+      <c r="I40" s="688" t="n"/>
+      <c r="J40" s="688" t="n"/>
+      <c r="K40" s="688" t="n"/>
+      <c r="L40" s="688" t="n"/>
+      <c r="M40" s="688" t="n"/>
+      <c r="N40" s="657" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="410" t="n"/>
-      <c r="P40" s="410" t="n"/>
-      <c r="Q40" s="410" t="n"/>
-      <c r="R40" s="410" t="n"/>
-      <c r="S40" s="410" t="n"/>
-      <c r="T40" s="410" t="n"/>
-      <c r="U40" s="410" t="n"/>
-      <c r="V40" s="410" t="n"/>
-      <c r="W40" s="410" t="n"/>
-      <c r="X40" s="410" t="n"/>
-      <c r="Y40" s="410" t="n"/>
-      <c r="Z40" s="410" t="n"/>
-      <c r="AA40" s="569" t="inlineStr">
+      <c r="O40" s="688" t="n"/>
+      <c r="P40" s="688" t="n"/>
+      <c r="Q40" s="688" t="n"/>
+      <c r="R40" s="688" t="n"/>
+      <c r="S40" s="688" t="n"/>
+      <c r="T40" s="688" t="n"/>
+      <c r="U40" s="688" t="n"/>
+      <c r="V40" s="688" t="n"/>
+      <c r="W40" s="688" t="n"/>
+      <c r="X40" s="688" t="n"/>
+      <c r="Y40" s="688" t="n"/>
+      <c r="Z40" s="688" t="n"/>
+      <c r="AA40" s="658" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="410" t="n"/>
-      <c r="AC40" s="410" t="n"/>
-      <c r="AD40" s="410" t="n"/>
-      <c r="AE40" s="410" t="n"/>
-      <c r="AF40" s="410" t="n"/>
-      <c r="AG40" s="410" t="n"/>
-      <c r="AH40" s="410" t="n"/>
-      <c r="AI40" s="410" t="n"/>
-      <c r="AJ40" s="410" t="n"/>
-      <c r="AK40" s="410" t="n"/>
-      <c r="AL40" s="410" t="n"/>
-      <c r="AM40" s="410" t="n"/>
-      <c r="AN40" s="540" t="n"/>
+      <c r="AB40" s="688" t="n"/>
+      <c r="AC40" s="688" t="n"/>
+      <c r="AD40" s="688" t="n"/>
+      <c r="AE40" s="688" t="n"/>
+      <c r="AF40" s="688" t="n"/>
+      <c r="AG40" s="688" t="n"/>
+      <c r="AH40" s="688" t="n"/>
+      <c r="AI40" s="688" t="n"/>
+      <c r="AJ40" s="688" t="n"/>
+      <c r="AK40" s="688" t="n"/>
+      <c r="AL40" s="688" t="n"/>
+      <c r="AM40" s="688" t="n"/>
+      <c r="AN40" s="689" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="535" t="n"/>
-      <c r="N41" s="413" t="n"/>
-      <c r="AA41" s="413" t="n"/>
-      <c r="AN41" s="536" t="n"/>
+      <c r="A41" s="328" t="n"/>
+      <c r="N41" s="690" t="n"/>
+      <c r="AA41" s="690" t="n"/>
+      <c r="AN41" s="330" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="562" t="n"/>
-      <c r="B42" s="415" t="n"/>
-      <c r="C42" s="415" t="n"/>
-      <c r="D42" s="415" t="n"/>
-      <c r="E42" s="415" t="n"/>
-      <c r="F42" s="415" t="n"/>
-      <c r="G42" s="415" t="n"/>
-      <c r="H42" s="415" t="n"/>
-      <c r="I42" s="415" t="n"/>
-      <c r="J42" s="415" t="n"/>
-      <c r="K42" s="415" t="n"/>
-      <c r="L42" s="415" t="n"/>
-      <c r="M42" s="415" t="n"/>
-      <c r="N42" s="414" t="n"/>
-      <c r="O42" s="415" t="n"/>
-      <c r="P42" s="415" t="n"/>
-      <c r="Q42" s="415" t="n"/>
-      <c r="R42" s="415" t="n"/>
-      <c r="S42" s="415" t="n"/>
-      <c r="T42" s="415" t="n"/>
-      <c r="U42" s="415" t="n"/>
-      <c r="V42" s="415" t="n"/>
-      <c r="W42" s="415" t="n"/>
-      <c r="X42" s="415" t="n"/>
-      <c r="Y42" s="415" t="n"/>
-      <c r="Z42" s="415" t="n"/>
-      <c r="AA42" s="414" t="n"/>
-      <c r="AB42" s="415" t="n"/>
-      <c r="AC42" s="415" t="n"/>
-      <c r="AD42" s="415" t="n"/>
-      <c r="AE42" s="415" t="n"/>
-      <c r="AF42" s="415" t="n"/>
-      <c r="AG42" s="415" t="n"/>
-      <c r="AH42" s="415" t="n"/>
-      <c r="AI42" s="415" t="n"/>
-      <c r="AJ42" s="415" t="n"/>
-      <c r="AK42" s="415" t="n"/>
-      <c r="AL42" s="415" t="n"/>
-      <c r="AM42" s="415" t="n"/>
-      <c r="AN42" s="563" t="n"/>
+      <c r="A42" s="279" t="n"/>
+      <c r="B42" s="322" t="n"/>
+      <c r="C42" s="322" t="n"/>
+      <c r="D42" s="322" t="n"/>
+      <c r="E42" s="322" t="n"/>
+      <c r="F42" s="322" t="n"/>
+      <c r="G42" s="322" t="n"/>
+      <c r="H42" s="322" t="n"/>
+      <c r="I42" s="322" t="n"/>
+      <c r="J42" s="322" t="n"/>
+      <c r="K42" s="322" t="n"/>
+      <c r="L42" s="322" t="n"/>
+      <c r="M42" s="322" t="n"/>
+      <c r="N42" s="691" t="n"/>
+      <c r="O42" s="322" t="n"/>
+      <c r="P42" s="322" t="n"/>
+      <c r="Q42" s="322" t="n"/>
+      <c r="R42" s="322" t="n"/>
+      <c r="S42" s="322" t="n"/>
+      <c r="T42" s="322" t="n"/>
+      <c r="U42" s="322" t="n"/>
+      <c r="V42" s="322" t="n"/>
+      <c r="W42" s="322" t="n"/>
+      <c r="X42" s="322" t="n"/>
+      <c r="Y42" s="322" t="n"/>
+      <c r="Z42" s="322" t="n"/>
+      <c r="AA42" s="691" t="n"/>
+      <c r="AB42" s="322" t="n"/>
+      <c r="AC42" s="322" t="n"/>
+      <c r="AD42" s="322" t="n"/>
+      <c r="AE42" s="322" t="n"/>
+      <c r="AF42" s="322" t="n"/>
+      <c r="AG42" s="322" t="n"/>
+      <c r="AH42" s="322" t="n"/>
+      <c r="AI42" s="322" t="n"/>
+      <c r="AJ42" s="322" t="n"/>
+      <c r="AK42" s="322" t="n"/>
+      <c r="AL42" s="322" t="n"/>
+      <c r="AM42" s="322" t="n"/>
+      <c r="AN42" s="324" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="386" t="n"/>
@@ -8317,50 +8927,50 @@
       <c r="AN43" s="352" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1" s="329">
-      <c r="A44" s="571" t="inlineStr">
+      <c r="A44" s="659" t="inlineStr">
         <is>
           <t>NOTICE: Release outsource dispatch only after required flow-down, evidence package and route-step controls are fully checked.</t>
         </is>
       </c>
-      <c r="B44" s="572" t="n"/>
-      <c r="C44" s="572" t="n"/>
-      <c r="D44" s="572" t="n"/>
-      <c r="E44" s="572" t="n"/>
-      <c r="F44" s="572" t="n"/>
-      <c r="G44" s="572" t="n"/>
-      <c r="H44" s="572" t="n"/>
-      <c r="I44" s="572" t="n"/>
-      <c r="J44" s="572" t="n"/>
-      <c r="K44" s="572" t="n"/>
-      <c r="L44" s="572" t="n"/>
-      <c r="M44" s="572" t="n"/>
-      <c r="N44" s="572" t="n"/>
-      <c r="O44" s="572" t="n"/>
-      <c r="P44" s="572" t="n"/>
-      <c r="Q44" s="572" t="n"/>
-      <c r="R44" s="572" t="n"/>
-      <c r="S44" s="572" t="n"/>
-      <c r="T44" s="572" t="n"/>
-      <c r="U44" s="572" t="n"/>
-      <c r="V44" s="572" t="n"/>
-      <c r="W44" s="572" t="n"/>
-      <c r="X44" s="572" t="n"/>
-      <c r="Y44" s="572" t="n"/>
-      <c r="Z44" s="572" t="n"/>
-      <c r="AA44" s="572" t="n"/>
-      <c r="AB44" s="572" t="n"/>
-      <c r="AC44" s="572" t="n"/>
-      <c r="AD44" s="572" t="n"/>
-      <c r="AE44" s="572" t="n"/>
-      <c r="AF44" s="572" t="n"/>
-      <c r="AG44" s="572" t="n"/>
-      <c r="AH44" s="572" t="n"/>
-      <c r="AI44" s="572" t="n"/>
-      <c r="AJ44" s="572" t="n"/>
-      <c r="AK44" s="572" t="n"/>
-      <c r="AL44" s="572" t="n"/>
-      <c r="AM44" s="572" t="n"/>
-      <c r="AN44" s="573" t="n"/>
+      <c r="B44" s="660" t="n"/>
+      <c r="C44" s="660" t="n"/>
+      <c r="D44" s="660" t="n"/>
+      <c r="E44" s="660" t="n"/>
+      <c r="F44" s="660" t="n"/>
+      <c r="G44" s="660" t="n"/>
+      <c r="H44" s="660" t="n"/>
+      <c r="I44" s="660" t="n"/>
+      <c r="J44" s="660" t="n"/>
+      <c r="K44" s="660" t="n"/>
+      <c r="L44" s="660" t="n"/>
+      <c r="M44" s="660" t="n"/>
+      <c r="N44" s="660" t="n"/>
+      <c r="O44" s="660" t="n"/>
+      <c r="P44" s="660" t="n"/>
+      <c r="Q44" s="660" t="n"/>
+      <c r="R44" s="660" t="n"/>
+      <c r="S44" s="660" t="n"/>
+      <c r="T44" s="660" t="n"/>
+      <c r="U44" s="660" t="n"/>
+      <c r="V44" s="660" t="n"/>
+      <c r="W44" s="660" t="n"/>
+      <c r="X44" s="660" t="n"/>
+      <c r="Y44" s="660" t="n"/>
+      <c r="Z44" s="660" t="n"/>
+      <c r="AA44" s="660" t="n"/>
+      <c r="AB44" s="660" t="n"/>
+      <c r="AC44" s="660" t="n"/>
+      <c r="AD44" s="660" t="n"/>
+      <c r="AE44" s="660" t="n"/>
+      <c r="AF44" s="660" t="n"/>
+      <c r="AG44" s="660" t="n"/>
+      <c r="AH44" s="660" t="n"/>
+      <c r="AI44" s="660" t="n"/>
+      <c r="AJ44" s="660" t="n"/>
+      <c r="AK44" s="660" t="n"/>
+      <c r="AL44" s="660" t="n"/>
+      <c r="AM44" s="660" t="n"/>
+      <c r="AN44" s="661" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -8560,355 +9170,331 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="577" t="n"/>
-      <c r="B1" s="578" t="n"/>
-      <c r="C1" s="578" t="n"/>
-      <c r="D1" s="578" t="n"/>
-      <c r="E1" s="578" t="n"/>
-      <c r="F1" s="578" t="n"/>
-      <c r="G1" s="578" t="n"/>
-      <c r="H1" s="579" t="n"/>
-      <c r="I1" s="580" t="inlineStr">
+    <row r="1" hidden="1" s="329">
+      <c r="A1" s="662" t="n"/>
+      <c r="B1" s="529" t="n"/>
+      <c r="C1" s="529" t="n"/>
+      <c r="D1" s="529" t="n"/>
+      <c r="E1" s="529" t="n"/>
+      <c r="F1" s="529" t="n"/>
+      <c r="G1" s="529" t="n"/>
+      <c r="H1" s="530" t="n"/>
+      <c r="I1" s="663" t="inlineStr">
         <is>
           <t>Outsource Dispatch Checklist</t>
         </is>
       </c>
-      <c r="J1" s="578" t="n"/>
-      <c r="K1" s="578" t="n"/>
-      <c r="L1" s="578" t="n"/>
-      <c r="M1" s="578" t="n"/>
-      <c r="N1" s="578" t="n"/>
-      <c r="O1" s="578" t="n"/>
-      <c r="P1" s="578" t="n"/>
-      <c r="Q1" s="578" t="n"/>
-      <c r="R1" s="578" t="n"/>
-      <c r="S1" s="578" t="n"/>
-      <c r="T1" s="578" t="n"/>
-      <c r="U1" s="578" t="n"/>
-      <c r="V1" s="578" t="n"/>
-      <c r="W1" s="578" t="n"/>
-      <c r="X1" s="578" t="n"/>
-      <c r="Y1" s="578" t="n"/>
-      <c r="Z1" s="578" t="n"/>
-      <c r="AA1" s="578" t="n"/>
-      <c r="AB1" s="578" t="n"/>
-      <c r="AC1" s="578" t="n"/>
-      <c r="AD1" s="579" t="n"/>
-      <c r="AE1" s="423" t="inlineStr">
+      <c r="J1" s="529" t="n"/>
+      <c r="K1" s="529" t="n"/>
+      <c r="L1" s="529" t="n"/>
+      <c r="M1" s="529" t="n"/>
+      <c r="N1" s="529" t="n"/>
+      <c r="O1" s="529" t="n"/>
+      <c r="P1" s="529" t="n"/>
+      <c r="Q1" s="529" t="n"/>
+      <c r="R1" s="529" t="n"/>
+      <c r="S1" s="529" t="n"/>
+      <c r="T1" s="529" t="n"/>
+      <c r="U1" s="529" t="n"/>
+      <c r="V1" s="529" t="n"/>
+      <c r="W1" s="529" t="n"/>
+      <c r="X1" s="529" t="n"/>
+      <c r="Y1" s="529" t="n"/>
+      <c r="Z1" s="529" t="n"/>
+      <c r="AA1" s="529" t="n"/>
+      <c r="AB1" s="529" t="n"/>
+      <c r="AC1" s="529" t="n"/>
+      <c r="AD1" s="530" t="n"/>
+      <c r="AE1" s="424" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="578" t="n"/>
-      <c r="AG1" s="578" t="n"/>
-      <c r="AH1" s="581" t="n"/>
-      <c r="AI1" s="426" t="n"/>
-      <c r="AJ1" s="578" t="n"/>
-      <c r="AK1" s="578" t="n"/>
-      <c r="AL1" s="578" t="n"/>
-      <c r="AM1" s="578" t="n"/>
-      <c r="AN1" s="579" t="n"/>
+      <c r="AF1" s="529" t="n"/>
+      <c r="AG1" s="529" t="n"/>
+      <c r="AH1" s="533" t="n"/>
+      <c r="AI1" s="427" t="n"/>
+      <c r="AJ1" s="529" t="n"/>
+      <c r="AK1" s="529" t="n"/>
+      <c r="AL1" s="529" t="n"/>
+      <c r="AM1" s="529" t="n"/>
+      <c r="AN1" s="530" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="582" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="583" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="583" t="n"/>
-      <c r="AE2" s="584" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="597" t="n"/>
+      <c r="C2" s="597" t="n"/>
+      <c r="D2" s="597" t="n"/>
+      <c r="E2" s="597" t="n"/>
+      <c r="F2" s="597" t="n"/>
+      <c r="G2" s="597" t="n"/>
+      <c r="H2" s="598" t="n"/>
+      <c r="I2" s="597" t="n"/>
+      <c r="J2" s="597" t="n"/>
+      <c r="K2" s="597" t="n"/>
+      <c r="L2" s="597" t="n"/>
+      <c r="M2" s="597" t="n"/>
+      <c r="N2" s="597" t="n"/>
+      <c r="O2" s="597" t="n"/>
+      <c r="P2" s="597" t="n"/>
+      <c r="Q2" s="597" t="n"/>
+      <c r="R2" s="597" t="n"/>
+      <c r="S2" s="597" t="n"/>
+      <c r="T2" s="597" t="n"/>
+      <c r="U2" s="597" t="n"/>
+      <c r="V2" s="597" t="n"/>
+      <c r="W2" s="597" t="n"/>
+      <c r="X2" s="597" t="n"/>
+      <c r="Y2" s="597" t="n"/>
+      <c r="Z2" s="597" t="n"/>
+      <c r="AA2" s="597" t="n"/>
+      <c r="AB2" s="597" t="n"/>
+      <c r="AC2" s="597" t="n"/>
+      <c r="AD2" s="598" t="n"/>
+      <c r="AE2" s="664" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="585" t="n"/>
-      <c r="AI2" s="586" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="583" t="n"/>
+      <c r="AF2" s="600" t="n"/>
+      <c r="AG2" s="600" t="n"/>
+      <c r="AH2" s="601" t="n"/>
+      <c r="AI2" s="665" t="n"/>
+      <c r="AJ2" s="603" t="n"/>
+      <c r="AK2" s="603" t="n"/>
+      <c r="AL2" s="603" t="n"/>
+      <c r="AM2" s="603" t="n"/>
+      <c r="AN2" s="604" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="582" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="583" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="583" t="n"/>
-      <c r="AE3" s="584" t="inlineStr">
+      <c r="A3" s="605" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="606" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="606" t="n"/>
+      <c r="AE3" s="666" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="585" t="n"/>
-      <c r="AI3" s="586" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="583" t="n"/>
+      <c r="AF3" s="608" t="n"/>
+      <c r="AG3" s="608" t="n"/>
+      <c r="AH3" s="609" t="n"/>
+      <c r="AI3" s="667" t="n"/>
+      <c r="AJ3" s="611" t="n"/>
+      <c r="AK3" s="611" t="n"/>
+      <c r="AL3" s="611" t="n"/>
+      <c r="AM3" s="611" t="n"/>
+      <c r="AN3" s="612" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="582" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="583" t="n"/>
-      <c r="I4" s="587" t="inlineStr">
+      <c r="A4" s="605" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="606" t="n"/>
+      <c r="I4" s="613" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="583" t="n"/>
-      <c r="AE4" s="584" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="606" t="n"/>
+      <c r="AE4" s="666" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="585" t="n"/>
-      <c r="AI4" s="586" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="583" t="n"/>
+      <c r="AF4" s="608" t="n"/>
+      <c r="AG4" s="608" t="n"/>
+      <c r="AH4" s="609" t="n"/>
+      <c r="AI4" s="667" t="n"/>
+      <c r="AJ4" s="611" t="n"/>
+      <c r="AK4" s="611" t="n"/>
+      <c r="AL4" s="611" t="n"/>
+      <c r="AM4" s="611" t="n"/>
+      <c r="AN4" s="612" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="588" t="n"/>
-      <c r="B5" s="589" t="n"/>
-      <c r="C5" s="589" t="n"/>
-      <c r="D5" s="589" t="n"/>
-      <c r="E5" s="589" t="n"/>
-      <c r="F5" s="589" t="n"/>
-      <c r="G5" s="589" t="n"/>
-      <c r="H5" s="590" t="n"/>
-      <c r="I5" s="591" t="inlineStr">
+      <c r="A5" s="605" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="606" t="n"/>
+      <c r="I5" s="614" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="589" t="n"/>
-      <c r="K5" s="589" t="n"/>
-      <c r="L5" s="589" t="n"/>
-      <c r="M5" s="589" t="n"/>
-      <c r="N5" s="589" t="n"/>
-      <c r="O5" s="589" t="n"/>
-      <c r="P5" s="589" t="n"/>
-      <c r="Q5" s="589" t="n"/>
-      <c r="R5" s="589" t="n"/>
-      <c r="S5" s="589" t="n"/>
-      <c r="T5" s="589" t="n"/>
-      <c r="U5" s="589" t="n"/>
-      <c r="V5" s="589" t="n"/>
-      <c r="W5" s="589" t="n"/>
-      <c r="X5" s="589" t="n"/>
-      <c r="Y5" s="589" t="n"/>
-      <c r="Z5" s="589" t="n"/>
-      <c r="AA5" s="589" t="n"/>
-      <c r="AB5" s="589" t="n"/>
-      <c r="AC5" s="589" t="n"/>
-      <c r="AD5" s="590" t="n"/>
-      <c r="AE5" s="592" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="606" t="n"/>
+      <c r="AE5" s="666" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="589" t="n"/>
-      <c r="AG5" s="589" t="n"/>
-      <c r="AH5" s="593" t="n"/>
-      <c r="AI5" s="594" t="n"/>
-      <c r="AJ5" s="589" t="n"/>
-      <c r="AK5" s="589" t="n"/>
-      <c r="AL5" s="589" t="n"/>
-      <c r="AM5" s="589" t="n"/>
-      <c r="AN5" s="590" t="n"/>
+      <c r="AF5" s="608" t="n"/>
+      <c r="AG5" s="608" t="n"/>
+      <c r="AH5" s="609" t="n"/>
+      <c r="AI5" s="667" t="n"/>
+      <c r="AJ5" s="611" t="n"/>
+      <c r="AK5" s="611" t="n"/>
+      <c r="AL5" s="611" t="n"/>
+      <c r="AM5" s="611" t="n"/>
+      <c r="AN5" s="612" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="595" t="n"/>
-      <c r="B6" s="595" t="n"/>
-      <c r="C6" s="595" t="n"/>
-      <c r="D6" s="595" t="n"/>
-      <c r="E6" s="595" t="n"/>
-      <c r="F6" s="595" t="n"/>
-      <c r="G6" s="595" t="n"/>
-      <c r="H6" s="595" t="n"/>
-      <c r="I6" s="595" t="n"/>
-      <c r="J6" s="595" t="n"/>
-      <c r="K6" s="595" t="n"/>
-      <c r="L6" s="595" t="n"/>
-      <c r="M6" s="595" t="n"/>
-      <c r="N6" s="595" t="n"/>
-      <c r="O6" s="595" t="n"/>
-      <c r="P6" s="595" t="n"/>
-      <c r="Q6" s="595" t="n"/>
-      <c r="R6" s="595" t="n"/>
-      <c r="S6" s="595" t="n"/>
-      <c r="T6" s="595" t="n"/>
-      <c r="U6" s="595" t="n"/>
-      <c r="V6" s="595" t="n"/>
-      <c r="W6" s="595" t="n"/>
-      <c r="X6" s="595" t="n"/>
-      <c r="Y6" s="595" t="n"/>
-      <c r="Z6" s="595" t="n"/>
-      <c r="AA6" s="595" t="n"/>
-      <c r="AB6" s="595" t="n"/>
-      <c r="AC6" s="595" t="n"/>
-      <c r="AD6" s="595" t="n"/>
-      <c r="AE6" s="595" t="n"/>
-      <c r="AF6" s="595" t="n"/>
-      <c r="AG6" s="595" t="n"/>
-      <c r="AH6" s="595" t="n"/>
-      <c r="AI6" s="595" t="n"/>
-      <c r="AJ6" s="595" t="n"/>
-      <c r="AK6" s="595" t="n"/>
-      <c r="AL6" s="595" t="n"/>
-      <c r="AM6" s="595" t="n"/>
-      <c r="AN6" s="595" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="668" t="n"/>
+      <c r="B6" s="669" t="n"/>
+      <c r="C6" s="669" t="n"/>
+      <c r="D6" s="669" t="n"/>
+      <c r="E6" s="669" t="n"/>
+      <c r="F6" s="669" t="n"/>
+      <c r="G6" s="669" t="n"/>
+      <c r="H6" s="670" t="n"/>
+      <c r="I6" s="669" t="n"/>
+      <c r="J6" s="669" t="n"/>
+      <c r="K6" s="669" t="n"/>
+      <c r="L6" s="669" t="n"/>
+      <c r="M6" s="669" t="n"/>
+      <c r="N6" s="669" t="n"/>
+      <c r="O6" s="669" t="n"/>
+      <c r="P6" s="669" t="n"/>
+      <c r="Q6" s="669" t="n"/>
+      <c r="R6" s="669" t="n"/>
+      <c r="S6" s="669" t="n"/>
+      <c r="T6" s="669" t="n"/>
+      <c r="U6" s="669" t="n"/>
+      <c r="V6" s="669" t="n"/>
+      <c r="W6" s="669" t="n"/>
+      <c r="X6" s="669" t="n"/>
+      <c r="Y6" s="669" t="n"/>
+      <c r="Z6" s="669" t="n"/>
+      <c r="AA6" s="669" t="n"/>
+      <c r="AB6" s="669" t="n"/>
+      <c r="AC6" s="669" t="n"/>
+      <c r="AD6" s="670" t="n"/>
+      <c r="AE6" s="671" t="n"/>
+      <c r="AF6" s="671" t="n"/>
+      <c r="AG6" s="671" t="n"/>
+      <c r="AH6" s="672" t="n"/>
+      <c r="AI6" s="673" t="n"/>
+      <c r="AJ6" s="673" t="n"/>
+      <c r="AK6" s="673" t="n"/>
+      <c r="AL6" s="673" t="n"/>
+      <c r="AM6" s="673" t="n"/>
+      <c r="AN6" s="674" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="265" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-      <c r="B7" s="265" t="inlineStr">
-        <is>
-          <t>DISPOSITION_GATE</t>
-        </is>
-      </c>
-      <c r="C7" s="265" t="inlineStr">
-        <is>
-          <t>YES_NO</t>
-        </is>
-      </c>
-      <c r="D7" s="265" t="inlineStr">
-        <is>
-          <t>OWNER_DEPT</t>
-        </is>
-      </c>
-      <c r="E7" s="265" t="inlineStr">
-        <is>
-          <t>ACTION_STATUS</t>
-        </is>
-      </c>
-      <c r="F7" s="265" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="G7" s="596" t="n"/>
-      <c r="H7" s="596" t="n"/>
-      <c r="I7" s="596" t="n"/>
-      <c r="J7" s="596" t="n"/>
-      <c r="K7" s="596" t="n"/>
-      <c r="L7" s="596" t="n"/>
-      <c r="M7" s="596" t="n"/>
-      <c r="N7" s="596" t="n"/>
-      <c r="O7" s="596" t="n"/>
-      <c r="P7" s="596" t="n"/>
-      <c r="Q7" s="596" t="n"/>
-      <c r="R7" s="596" t="n"/>
-      <c r="S7" s="596" t="n"/>
-      <c r="T7" s="596" t="n"/>
-      <c r="U7" s="596" t="n"/>
-      <c r="V7" s="596" t="n"/>
-      <c r="W7" s="596" t="n"/>
-      <c r="X7" s="596" t="n"/>
-      <c r="Y7" s="596" t="n"/>
-      <c r="Z7" s="596" t="n"/>
-      <c r="AA7" s="596" t="n"/>
-      <c r="AB7" s="596" t="n"/>
-      <c r="AC7" s="596" t="n"/>
-      <c r="AD7" s="596" t="n"/>
-      <c r="AE7" s="596" t="n"/>
-      <c r="AF7" s="596" t="n"/>
-      <c r="AG7" s="596" t="n"/>
-      <c r="AH7" s="596" t="n"/>
-      <c r="AI7" s="596" t="n"/>
-      <c r="AJ7" s="596" t="n"/>
-      <c r="AK7" s="596" t="n"/>
-      <c r="AL7" s="596" t="n"/>
-      <c r="AM7" s="596" t="n"/>
-      <c r="AN7" s="596" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="675" t="n"/>
+      <c r="B7" s="675" t="n"/>
+      <c r="C7" s="675" t="n"/>
+      <c r="D7" s="675" t="n"/>
+      <c r="E7" s="675" t="n"/>
+      <c r="F7" s="675" t="n"/>
+      <c r="G7" s="676" t="n"/>
+      <c r="H7" s="676" t="n"/>
+      <c r="I7" s="676" t="n"/>
+      <c r="J7" s="676" t="n"/>
+      <c r="K7" s="676" t="n"/>
+      <c r="L7" s="676" t="n"/>
+      <c r="M7" s="676" t="n"/>
+      <c r="N7" s="676" t="n"/>
+      <c r="O7" s="676" t="n"/>
+      <c r="P7" s="676" t="n"/>
+      <c r="Q7" s="676" t="n"/>
+      <c r="R7" s="676" t="n"/>
+      <c r="S7" s="676" t="n"/>
+      <c r="T7" s="676" t="n"/>
+      <c r="U7" s="676" t="n"/>
+      <c r="V7" s="676" t="n"/>
+      <c r="W7" s="676" t="n"/>
+      <c r="X7" s="676" t="n"/>
+      <c r="Y7" s="676" t="n"/>
+      <c r="Z7" s="676" t="n"/>
+      <c r="AA7" s="676" t="n"/>
+      <c r="AB7" s="676" t="n"/>
+      <c r="AC7" s="676" t="n"/>
+      <c r="AD7" s="676" t="n"/>
+      <c r="AE7" s="676" t="n"/>
+      <c r="AF7" s="676" t="n"/>
+      <c r="AG7" s="676" t="n"/>
+      <c r="AH7" s="676" t="n"/>
+      <c r="AI7" s="676" t="n"/>
+      <c r="AJ7" s="676" t="n"/>
+      <c r="AK7" s="676" t="n"/>
+      <c r="AL7" s="676" t="n"/>
+      <c r="AM7" s="676" t="n"/>
+      <c r="AN7" s="676" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
@@ -9599,6 +10185,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9653,338 +10240,334 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="577" t="n"/>
-      <c r="B1" s="578" t="n"/>
-      <c r="C1" s="578" t="n"/>
-      <c r="D1" s="578" t="n"/>
-      <c r="E1" s="578" t="n"/>
-      <c r="F1" s="578" t="n"/>
-      <c r="G1" s="578" t="n"/>
-      <c r="H1" s="579" t="n"/>
-      <c r="I1" s="580" t="inlineStr">
+    <row r="1" hidden="1" s="329">
+      <c r="A1" s="662" t="n"/>
+      <c r="B1" s="529" t="n"/>
+      <c r="C1" s="529" t="n"/>
+      <c r="D1" s="529" t="n"/>
+      <c r="E1" s="529" t="n"/>
+      <c r="F1" s="529" t="n"/>
+      <c r="G1" s="529" t="n"/>
+      <c r="H1" s="530" t="n"/>
+      <c r="I1" s="663" t="inlineStr">
         <is>
           <t>Outsource Dispatch Checklist</t>
         </is>
       </c>
-      <c r="J1" s="578" t="n"/>
-      <c r="K1" s="578" t="n"/>
-      <c r="L1" s="578" t="n"/>
-      <c r="M1" s="578" t="n"/>
-      <c r="N1" s="578" t="n"/>
-      <c r="O1" s="578" t="n"/>
-      <c r="P1" s="578" t="n"/>
-      <c r="Q1" s="578" t="n"/>
-      <c r="R1" s="578" t="n"/>
-      <c r="S1" s="578" t="n"/>
-      <c r="T1" s="578" t="n"/>
-      <c r="U1" s="578" t="n"/>
-      <c r="V1" s="578" t="n"/>
-      <c r="W1" s="578" t="n"/>
-      <c r="X1" s="578" t="n"/>
-      <c r="Y1" s="578" t="n"/>
-      <c r="Z1" s="578" t="n"/>
-      <c r="AA1" s="578" t="n"/>
-      <c r="AB1" s="578" t="n"/>
-      <c r="AC1" s="578" t="n"/>
-      <c r="AD1" s="579" t="n"/>
-      <c r="AE1" s="423" t="inlineStr">
+      <c r="J1" s="529" t="n"/>
+      <c r="K1" s="529" t="n"/>
+      <c r="L1" s="529" t="n"/>
+      <c r="M1" s="529" t="n"/>
+      <c r="N1" s="529" t="n"/>
+      <c r="O1" s="529" t="n"/>
+      <c r="P1" s="529" t="n"/>
+      <c r="Q1" s="529" t="n"/>
+      <c r="R1" s="529" t="n"/>
+      <c r="S1" s="529" t="n"/>
+      <c r="T1" s="529" t="n"/>
+      <c r="U1" s="529" t="n"/>
+      <c r="V1" s="529" t="n"/>
+      <c r="W1" s="529" t="n"/>
+      <c r="X1" s="529" t="n"/>
+      <c r="Y1" s="529" t="n"/>
+      <c r="Z1" s="529" t="n"/>
+      <c r="AA1" s="529" t="n"/>
+      <c r="AB1" s="529" t="n"/>
+      <c r="AC1" s="529" t="n"/>
+      <c r="AD1" s="530" t="n"/>
+      <c r="AE1" s="424" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="578" t="n"/>
-      <c r="AG1" s="578" t="n"/>
-      <c r="AH1" s="581" t="n"/>
-      <c r="AI1" s="426" t="n"/>
-      <c r="AJ1" s="578" t="n"/>
-      <c r="AK1" s="578" t="n"/>
-      <c r="AL1" s="578" t="n"/>
-      <c r="AM1" s="578" t="n"/>
-      <c r="AN1" s="579" t="n"/>
+      <c r="AF1" s="529" t="n"/>
+      <c r="AG1" s="529" t="n"/>
+      <c r="AH1" s="533" t="n"/>
+      <c r="AI1" s="427" t="n"/>
+      <c r="AJ1" s="529" t="n"/>
+      <c r="AK1" s="529" t="n"/>
+      <c r="AL1" s="529" t="n"/>
+      <c r="AM1" s="529" t="n"/>
+      <c r="AN1" s="530" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="582" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="583" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="583" t="n"/>
-      <c r="AE2" s="584" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="597" t="n"/>
+      <c r="C2" s="597" t="n"/>
+      <c r="D2" s="597" t="n"/>
+      <c r="E2" s="597" t="n"/>
+      <c r="F2" s="597" t="n"/>
+      <c r="G2" s="597" t="n"/>
+      <c r="H2" s="598" t="n"/>
+      <c r="I2" s="597" t="n"/>
+      <c r="J2" s="597" t="n"/>
+      <c r="K2" s="597" t="n"/>
+      <c r="L2" s="597" t="n"/>
+      <c r="M2" s="597" t="n"/>
+      <c r="N2" s="597" t="n"/>
+      <c r="O2" s="597" t="n"/>
+      <c r="P2" s="597" t="n"/>
+      <c r="Q2" s="597" t="n"/>
+      <c r="R2" s="597" t="n"/>
+      <c r="S2" s="597" t="n"/>
+      <c r="T2" s="597" t="n"/>
+      <c r="U2" s="597" t="n"/>
+      <c r="V2" s="597" t="n"/>
+      <c r="W2" s="597" t="n"/>
+      <c r="X2" s="597" t="n"/>
+      <c r="Y2" s="597" t="n"/>
+      <c r="Z2" s="597" t="n"/>
+      <c r="AA2" s="597" t="n"/>
+      <c r="AB2" s="597" t="n"/>
+      <c r="AC2" s="597" t="n"/>
+      <c r="AD2" s="598" t="n"/>
+      <c r="AE2" s="664" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="585" t="n"/>
-      <c r="AI2" s="586" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="583" t="n"/>
+      <c r="AF2" s="600" t="n"/>
+      <c r="AG2" s="600" t="n"/>
+      <c r="AH2" s="601" t="n"/>
+      <c r="AI2" s="665" t="n"/>
+      <c r="AJ2" s="603" t="n"/>
+      <c r="AK2" s="603" t="n"/>
+      <c r="AL2" s="603" t="n"/>
+      <c r="AM2" s="603" t="n"/>
+      <c r="AN2" s="604" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="582" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="583" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="583" t="n"/>
-      <c r="AE3" s="584" t="inlineStr">
+      <c r="A3" s="605" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="606" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="606" t="n"/>
+      <c r="AE3" s="666" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="585" t="n"/>
-      <c r="AI3" s="586" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="583" t="n"/>
+      <c r="AF3" s="608" t="n"/>
+      <c r="AG3" s="608" t="n"/>
+      <c r="AH3" s="609" t="n"/>
+      <c r="AI3" s="667" t="n"/>
+      <c r="AJ3" s="611" t="n"/>
+      <c r="AK3" s="611" t="n"/>
+      <c r="AL3" s="611" t="n"/>
+      <c r="AM3" s="611" t="n"/>
+      <c r="AN3" s="612" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="582" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="583" t="n"/>
-      <c r="I4" s="587" t="inlineStr">
+      <c r="A4" s="605" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="606" t="n"/>
+      <c r="I4" s="613" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="583" t="n"/>
-      <c r="AE4" s="584" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="606" t="n"/>
+      <c r="AE4" s="666" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="585" t="n"/>
-      <c r="AI4" s="586" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="583" t="n"/>
+      <c r="AF4" s="608" t="n"/>
+      <c r="AG4" s="608" t="n"/>
+      <c r="AH4" s="609" t="n"/>
+      <c r="AI4" s="667" t="n"/>
+      <c r="AJ4" s="611" t="n"/>
+      <c r="AK4" s="611" t="n"/>
+      <c r="AL4" s="611" t="n"/>
+      <c r="AM4" s="611" t="n"/>
+      <c r="AN4" s="612" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="588" t="n"/>
-      <c r="B5" s="589" t="n"/>
-      <c r="C5" s="589" t="n"/>
-      <c r="D5" s="589" t="n"/>
-      <c r="E5" s="589" t="n"/>
-      <c r="F5" s="589" t="n"/>
-      <c r="G5" s="589" t="n"/>
-      <c r="H5" s="590" t="n"/>
-      <c r="I5" s="591" t="inlineStr">
+      <c r="A5" s="605" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="606" t="n"/>
+      <c r="I5" s="614" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="589" t="n"/>
-      <c r="K5" s="589" t="n"/>
-      <c r="L5" s="589" t="n"/>
-      <c r="M5" s="589" t="n"/>
-      <c r="N5" s="589" t="n"/>
-      <c r="O5" s="589" t="n"/>
-      <c r="P5" s="589" t="n"/>
-      <c r="Q5" s="589" t="n"/>
-      <c r="R5" s="589" t="n"/>
-      <c r="S5" s="589" t="n"/>
-      <c r="T5" s="589" t="n"/>
-      <c r="U5" s="589" t="n"/>
-      <c r="V5" s="589" t="n"/>
-      <c r="W5" s="589" t="n"/>
-      <c r="X5" s="589" t="n"/>
-      <c r="Y5" s="589" t="n"/>
-      <c r="Z5" s="589" t="n"/>
-      <c r="AA5" s="589" t="n"/>
-      <c r="AB5" s="589" t="n"/>
-      <c r="AC5" s="589" t="n"/>
-      <c r="AD5" s="590" t="n"/>
-      <c r="AE5" s="592" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="606" t="n"/>
+      <c r="AE5" s="666" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="589" t="n"/>
-      <c r="AG5" s="589" t="n"/>
-      <c r="AH5" s="593" t="n"/>
-      <c r="AI5" s="594" t="n"/>
-      <c r="AJ5" s="589" t="n"/>
-      <c r="AK5" s="589" t="n"/>
-      <c r="AL5" s="589" t="n"/>
-      <c r="AM5" s="589" t="n"/>
-      <c r="AN5" s="590" t="n"/>
+      <c r="AF5" s="608" t="n"/>
+      <c r="AG5" s="608" t="n"/>
+      <c r="AH5" s="609" t="n"/>
+      <c r="AI5" s="667" t="n"/>
+      <c r="AJ5" s="611" t="n"/>
+      <c r="AK5" s="611" t="n"/>
+      <c r="AL5" s="611" t="n"/>
+      <c r="AM5" s="611" t="n"/>
+      <c r="AN5" s="612" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="595" t="n"/>
-      <c r="B6" s="595" t="n"/>
-      <c r="C6" s="595" t="n"/>
-      <c r="D6" s="595" t="n"/>
-      <c r="E6" s="595" t="n"/>
-      <c r="F6" s="595" t="n"/>
-      <c r="G6" s="595" t="n"/>
-      <c r="H6" s="595" t="n"/>
-      <c r="I6" s="595" t="n"/>
-      <c r="J6" s="595" t="n"/>
-      <c r="K6" s="595" t="n"/>
-      <c r="L6" s="595" t="n"/>
-      <c r="M6" s="595" t="n"/>
-      <c r="N6" s="595" t="n"/>
-      <c r="O6" s="595" t="n"/>
-      <c r="P6" s="595" t="n"/>
-      <c r="Q6" s="595" t="n"/>
-      <c r="R6" s="595" t="n"/>
-      <c r="S6" s="595" t="n"/>
-      <c r="T6" s="595" t="n"/>
-      <c r="U6" s="595" t="n"/>
-      <c r="V6" s="595" t="n"/>
-      <c r="W6" s="595" t="n"/>
-      <c r="X6" s="595" t="n"/>
-      <c r="Y6" s="595" t="n"/>
-      <c r="Z6" s="595" t="n"/>
-      <c r="AA6" s="595" t="n"/>
-      <c r="AB6" s="595" t="n"/>
-      <c r="AC6" s="595" t="n"/>
-      <c r="AD6" s="595" t="n"/>
-      <c r="AE6" s="595" t="n"/>
-      <c r="AF6" s="595" t="n"/>
-      <c r="AG6" s="595" t="n"/>
-      <c r="AH6" s="595" t="n"/>
-      <c r="AI6" s="595" t="n"/>
-      <c r="AJ6" s="595" t="n"/>
-      <c r="AK6" s="595" t="n"/>
-      <c r="AL6" s="595" t="n"/>
-      <c r="AM6" s="595" t="n"/>
-      <c r="AN6" s="595" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="668" t="n"/>
+      <c r="B6" s="669" t="n"/>
+      <c r="C6" s="669" t="n"/>
+      <c r="D6" s="669" t="n"/>
+      <c r="E6" s="669" t="n"/>
+      <c r="F6" s="669" t="n"/>
+      <c r="G6" s="669" t="n"/>
+      <c r="H6" s="670" t="n"/>
+      <c r="I6" s="669" t="n"/>
+      <c r="J6" s="669" t="n"/>
+      <c r="K6" s="669" t="n"/>
+      <c r="L6" s="669" t="n"/>
+      <c r="M6" s="669" t="n"/>
+      <c r="N6" s="669" t="n"/>
+      <c r="O6" s="669" t="n"/>
+      <c r="P6" s="669" t="n"/>
+      <c r="Q6" s="669" t="n"/>
+      <c r="R6" s="669" t="n"/>
+      <c r="S6" s="669" t="n"/>
+      <c r="T6" s="669" t="n"/>
+      <c r="U6" s="669" t="n"/>
+      <c r="V6" s="669" t="n"/>
+      <c r="W6" s="669" t="n"/>
+      <c r="X6" s="669" t="n"/>
+      <c r="Y6" s="669" t="n"/>
+      <c r="Z6" s="669" t="n"/>
+      <c r="AA6" s="669" t="n"/>
+      <c r="AB6" s="669" t="n"/>
+      <c r="AC6" s="669" t="n"/>
+      <c r="AD6" s="670" t="n"/>
+      <c r="AE6" s="671" t="n"/>
+      <c r="AF6" s="671" t="n"/>
+      <c r="AG6" s="671" t="n"/>
+      <c r="AH6" s="672" t="n"/>
+      <c r="AI6" s="673" t="n"/>
+      <c r="AJ6" s="673" t="n"/>
+      <c r="AK6" s="673" t="n"/>
+      <c r="AL6" s="673" t="n"/>
+      <c r="AM6" s="673" t="n"/>
+      <c r="AN6" s="674" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="499" t="inlineStr">
-        <is>
-          <t>Conditions / Exceptions / Actions</t>
-        </is>
-      </c>
-      <c r="B7" s="596" t="n"/>
-      <c r="C7" s="596" t="n"/>
-      <c r="D7" s="596" t="n"/>
-      <c r="E7" s="596" t="n"/>
-      <c r="F7" s="596" t="n"/>
-      <c r="G7" s="596" t="n"/>
-      <c r="H7" s="596" t="n"/>
-      <c r="I7" s="596" t="n"/>
-      <c r="J7" s="596" t="n"/>
-      <c r="K7" s="596" t="n"/>
-      <c r="L7" s="596" t="n"/>
-      <c r="M7" s="596" t="n"/>
-      <c r="N7" s="596" t="n"/>
-      <c r="O7" s="596" t="n"/>
-      <c r="P7" s="596" t="n"/>
-      <c r="Q7" s="596" t="n"/>
-      <c r="R7" s="596" t="n"/>
-      <c r="S7" s="596" t="n"/>
-      <c r="T7" s="596" t="n"/>
-      <c r="U7" s="596" t="n"/>
-      <c r="V7" s="596" t="n"/>
-      <c r="W7" s="596" t="n"/>
-      <c r="X7" s="596" t="n"/>
-      <c r="Y7" s="596" t="n"/>
-      <c r="Z7" s="596" t="n"/>
-      <c r="AA7" s="596" t="n"/>
-      <c r="AB7" s="596" t="n"/>
-      <c r="AC7" s="596" t="n"/>
-      <c r="AD7" s="596" t="n"/>
-      <c r="AE7" s="596" t="n"/>
-      <c r="AF7" s="596" t="n"/>
-      <c r="AG7" s="596" t="n"/>
-      <c r="AH7" s="596" t="n"/>
-      <c r="AI7" s="596" t="n"/>
-      <c r="AJ7" s="596" t="n"/>
-      <c r="AK7" s="596" t="n"/>
-      <c r="AL7" s="596" t="n"/>
-      <c r="AM7" s="596" t="n"/>
-      <c r="AN7" s="596" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="677" t="n"/>
+      <c r="B7" s="676" t="n"/>
+      <c r="C7" s="676" t="n"/>
+      <c r="D7" s="676" t="n"/>
+      <c r="E7" s="676" t="n"/>
+      <c r="F7" s="676" t="n"/>
+      <c r="G7" s="676" t="n"/>
+      <c r="H7" s="676" t="n"/>
+      <c r="I7" s="676" t="n"/>
+      <c r="J7" s="676" t="n"/>
+      <c r="K7" s="676" t="n"/>
+      <c r="L7" s="676" t="n"/>
+      <c r="M7" s="676" t="n"/>
+      <c r="N7" s="676" t="n"/>
+      <c r="O7" s="676" t="n"/>
+      <c r="P7" s="676" t="n"/>
+      <c r="Q7" s="676" t="n"/>
+      <c r="R7" s="676" t="n"/>
+      <c r="S7" s="676" t="n"/>
+      <c r="T7" s="676" t="n"/>
+      <c r="U7" s="676" t="n"/>
+      <c r="V7" s="676" t="n"/>
+      <c r="W7" s="676" t="n"/>
+      <c r="X7" s="676" t="n"/>
+      <c r="Y7" s="676" t="n"/>
+      <c r="Z7" s="676" t="n"/>
+      <c r="AA7" s="676" t="n"/>
+      <c r="AB7" s="676" t="n"/>
+      <c r="AC7" s="676" t="n"/>
+      <c r="AD7" s="676" t="n"/>
+      <c r="AE7" s="676" t="n"/>
+      <c r="AF7" s="676" t="n"/>
+      <c r="AG7" s="676" t="n"/>
+      <c r="AH7" s="676" t="n"/>
+      <c r="AI7" s="676" t="n"/>
+      <c r="AJ7" s="676" t="n"/>
+      <c r="AK7" s="676" t="n"/>
+      <c r="AL7" s="676" t="n"/>
+      <c r="AM7" s="676" t="n"/>
+      <c r="AN7" s="676" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="500" t="inlineStr">
+      <c r="A8" s="678" t="inlineStr">
         <is>
           <t>Dispatch gate for controlled outsource release and supplier package readiness.</t>
         </is>
@@ -10072,42 +10655,42 @@
       <c r="AN9" s="596" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="477" t="inlineStr">
+      <c r="A10" s="639" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B10" s="478" t="inlineStr">
+      <c r="B10" s="679" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C10" s="478" t="inlineStr">
+      <c r="C10" s="679" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D10" s="478" t="inlineStr">
+      <c r="D10" s="679" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E10" s="478" t="inlineStr">
+      <c r="E10" s="679" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F10" s="478" t="inlineStr">
+      <c r="F10" s="679" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G10" s="478" t="inlineStr">
+      <c r="G10" s="679" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H10" s="478" t="inlineStr">
+      <c r="H10" s="679" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -10146,7 +10729,7 @@
       <c r="AN10" s="596" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="501">
+      <c r="A11" s="680">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10191,7 +10774,7 @@
       <c r="AN11" s="596" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="474">
+      <c r="A12" s="681">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10236,7 +10819,7 @@
       <c r="AN12" s="596" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="474">
+      <c r="A13" s="681">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10281,7 +10864,7 @@
       <c r="AN13" s="596" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="502">
+      <c r="A14" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10326,7 +10909,7 @@
       <c r="AN14" s="596" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="502">
+      <c r="A15" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10371,7 +10954,7 @@
       <c r="AN15" s="596" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="502">
+      <c r="A16" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10416,7 +10999,7 @@
       <c r="AN16" s="596" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="502">
+      <c r="A17" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10461,7 +11044,7 @@
       <c r="AN17" s="596" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="502">
+      <c r="A18" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10506,7 +11089,7 @@
       <c r="AN18" s="596" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="502">
+      <c r="A19" s="682">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10551,7 +11134,7 @@
       <c r="AN19" s="596" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="504">
+      <c r="A20" s="683">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
@@ -10765,8 +11348,9 @@
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -4496,6 +4496,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4526,6 +4529,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPATCH_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DISPATCH_GATE'!$A$1:$AN$44</definedName>

--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPATCH_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DISPATCH_GATE'!$A$1:$AN$44</definedName>
@@ -4367,6 +4368,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -4457,72 +4493,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4734,7 +4704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AW44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -5260,7 +5230,7 @@
     <row r="13" ht="20" customHeight="1" s="329">
       <c r="A13" s="287" t="inlineStr">
         <is>
-          <t>Route Step / Due Date</t>
+          <t>Linked FRM-403</t>
         </is>
       </c>
       <c r="B13" s="317" t="n"/>
@@ -5284,7 +5254,7 @@
       <c r="T13" s="318" t="n"/>
       <c r="U13" s="289" t="inlineStr">
         <is>
-          <t>Package Ref</t>
+          <t>Ref: SOP-401</t>
         </is>
       </c>
       <c r="V13" s="317" t="n"/>
@@ -5293,7 +5263,11 @@
       <c r="Y13" s="317" t="n"/>
       <c r="Z13" s="317" t="n"/>
       <c r="AA13" s="318" t="n"/>
-      <c r="AB13" s="290" t="n"/>
+      <c r="AB13" s="290" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AC13" s="317" t="n"/>
       <c r="AD13" s="317" t="n"/>
       <c r="AE13" s="317" t="n"/>
@@ -6635,6 +6609,17 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="H16:T16"/>
   </mergeCells>
+  <conditionalFormatting sqref="AF27:AF32">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="H35:T35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LISTS!$B$2:$B$5</formula1>
@@ -7332,7 +7317,6 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7590,6 +7574,85 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-403; Parent ref: SOP-401; CF: checklist Result</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-404_Outsource_Dispatch_Checklist.xlsx
@@ -4968,6 +4968,82 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số công việc
+Job đang gửi parts ra ngoài.</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Nhà cung cấp
+NCC nhận parts.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày gửi
+Ngày xuất hàng.</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Người gửi
+Tên người thực hiện xuất hàng.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Xác nhận gửi hàng
+Kiểm tra trước khi giao parts cho NCC.</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Đếm số lượng
+Đếm parts trước khi đóng gói. Số lượng khớp PO.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Tài liệu đính kèm
+NCC phải nhận spec/drawing cùng với parts.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Yêu cầu đặc biệt
+Masking (che vùng không xử lý), orientation, xử lý nhẹ nhàng...</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Đóng gói
+Parts phải được bảo vệ khỏi hư hỏng khi vận chuyển.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Vận chuyển
+Ghi tracking number để theo dõi.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày trả hàng
+Xác nhận với NCC ngày trả hàng. Cập nhật vào job schedule.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5877,8 +5953,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5910,7 +5987,7 @@
       <c r="U14" s="491" t="n"/>
       <c r="V14" s="495" t="inlineStr">
         <is>
-          <t>Count verified.</t>
+          <t>Count verified before packing.</t>
         </is>
       </c>
       <c r="W14" s="493" t="n"/>
@@ -5933,8 +6010,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="inlineStr">
@@ -5966,7 +6044,7 @@
       <c r="U15" s="491" t="n"/>
       <c r="V15" s="495" t="inlineStr">
         <is>
-          <t>Physical copy or digital link confirmed.</t>
+          <t>Physical or digital copy confirmed.</t>
         </is>
       </c>
       <c r="W15" s="493" t="n"/>
@@ -5989,8 +6067,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="500" t="inlineStr">
@@ -6002,7 +6081,7 @@
       <c r="E16" s="491" t="n"/>
       <c r="F16" s="494" t="inlineStr">
         <is>
-          <t>Special requirements noted on PO (masking, orientation).</t>
+          <t>Special requirements noted on PO.</t>
         </is>
       </c>
       <c r="G16" s="493" t="n"/>
@@ -6022,7 +6101,7 @@
       <c r="U16" s="491" t="n"/>
       <c r="V16" s="495" t="inlineStr">
         <is>
-          <t>Requirements visible to supplier.</t>
+          <t>Masking, orientation, handling instructions visible.</t>
         </is>
       </c>
       <c r="W16" s="493" t="n"/>
@@ -6045,8 +6124,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="inlineStr">
@@ -6101,8 +6181,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="inlineStr">
@@ -6157,8 +6238,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="inlineStr">
@@ -6170,7 +6252,7 @@
       <c r="E19" s="491" t="n"/>
       <c r="F19" s="499" t="inlineStr">
         <is>
-          <t>Expected return date confirmed with supplier.</t>
+          <t>Expected return date confirmed.</t>
         </is>
       </c>
       <c r="G19" s="493" t="n"/>
@@ -6190,7 +6272,7 @@
       <c r="U19" s="491" t="n"/>
       <c r="V19" s="495" t="inlineStr">
         <is>
-          <t>Date documented.</t>
+          <t>Date documented and in job schedule.</t>
         </is>
       </c>
       <c r="W19" s="493" t="n"/>
@@ -6213,8 +6295,9 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="501" t="n"/>
@@ -6257,8 +6340,9 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="503" t="n">
-        <v>8</v>
+      <c r="A21" s="503">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="482" t="n"/>
       <c r="C21" s="504" t="n"/>
@@ -6734,6 +6818,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
